--- a/financial_models/opportunities/300481.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/300481.SZ_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4996C6D-8F52-4C84-AEB9-BD4DDBED4B2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C81056EF-C9FE-4C3E-84D4-CB689AA966D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2205" yWindow="2205" windowWidth="12690" windowHeight="7642" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3879,29 +3879,29 @@
     <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4319,7 +4319,7 @@
         <v>95</v>
       </c>
       <c r="C12" s="50">
-        <v>13.75</v>
+        <v>13.47</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>4013.0122725000001</v>
+        <v>3931.2927498600002</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4377,13 +4377,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="350" t="s">
+      <c r="B18" s="348" t="s">
         <v>360</v>
       </c>
-      <c r="C18" s="350"/>
-      <c r="D18" s="350"/>
-      <c r="E18" s="350"/>
-      <c r="F18" s="350"/>
+      <c r="C18" s="348"/>
+      <c r="D18" s="348"/>
+      <c r="E18" s="348"/>
+      <c r="F18" s="348"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>-6.1124992361572206E-2</v>
+        <v>-5.4450928827774248E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4508,7 +4508,7 @@
         <v>425</v>
       </c>
       <c r="F29" s="302">
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="30" spans="2:6">
@@ -4583,22 +4583,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="350" t="s">
+      <c r="B36" s="348" t="s">
         <v>361</v>
       </c>
-      <c r="C36" s="350"/>
-      <c r="D36" s="350"/>
-      <c r="E36" s="350"/>
-      <c r="F36" s="350"/>
+      <c r="C36" s="348"/>
+      <c r="D36" s="348"/>
+      <c r="E36" s="348"/>
+      <c r="F36" s="348"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="353" t="s">
+      <c r="B37" s="350" t="s">
         <v>340</v>
       </c>
-      <c r="C37" s="353"/>
-      <c r="D37" s="353"/>
-      <c r="E37" s="353"/>
-      <c r="F37" s="353"/>
+      <c r="C37" s="350"/>
+      <c r="D37" s="350"/>
+      <c r="E37" s="350"/>
+      <c r="F37" s="350"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4610,13 +4610,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="351" t="s">
+      <c r="B40" s="349" t="s">
         <v>232</v>
       </c>
-      <c r="C40" s="351"/>
-      <c r="D40" s="351"/>
-      <c r="E40" s="351"/>
-      <c r="F40" s="351"/>
+      <c r="C40" s="349"/>
+      <c r="D40" s="349"/>
+      <c r="E40" s="349"/>
+      <c r="F40" s="349"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4636,13 +4636,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="351" t="s">
+      <c r="B43" s="349" t="s">
         <v>234</v>
       </c>
-      <c r="C43" s="351"/>
-      <c r="D43" s="351"/>
-      <c r="E43" s="351"/>
-      <c r="F43" s="351"/>
+      <c r="C43" s="349"/>
+      <c r="D43" s="349"/>
+      <c r="E43" s="349"/>
+      <c r="F43" s="349"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4671,13 +4671,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="351" t="s">
+      <c r="B47" s="349" t="s">
         <v>237</v>
       </c>
-      <c r="C47" s="351"/>
-      <c r="D47" s="351"/>
-      <c r="E47" s="351"/>
-      <c r="F47" s="351"/>
+      <c r="C47" s="349"/>
+      <c r="D47" s="349"/>
+      <c r="E47" s="349"/>
+      <c r="F47" s="349"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4693,13 +4693,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="351" t="s">
+      <c r="B50" s="349" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="351"/>
-      <c r="D50" s="351"/>
-      <c r="E50" s="351"/>
-      <c r="F50" s="351"/>
+      <c r="C50" s="349"/>
+      <c r="D50" s="349"/>
+      <c r="E50" s="349"/>
+      <c r="F50" s="349"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4763,13 +4763,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="351" t="s">
+      <c r="B58" s="349" t="s">
         <v>242</v>
       </c>
-      <c r="C58" s="351"/>
-      <c r="D58" s="351"/>
-      <c r="E58" s="351"/>
-      <c r="F58" s="351"/>
+      <c r="C58" s="349"/>
+      <c r="D58" s="349"/>
+      <c r="E58" s="349"/>
+      <c r="F58" s="349"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4785,7 +4785,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="351" t="s">
+      <c r="B61" s="349" t="s">
         <v>339</v>
       </c>
       <c r="C61" s="352"/>
@@ -4807,22 +4807,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="350" t="s">
+      <c r="B64" s="348" t="s">
         <v>344</v>
       </c>
-      <c r="C64" s="350"/>
-      <c r="D64" s="350"/>
-      <c r="E64" s="350"/>
-      <c r="F64" s="350"/>
+      <c r="C64" s="348"/>
+      <c r="D64" s="348"/>
+      <c r="E64" s="348"/>
+      <c r="F64" s="348"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="350" t="s">
+      <c r="B65" s="348" t="s">
         <v>362</v>
       </c>
-      <c r="C65" s="350"/>
-      <c r="D65" s="350"/>
-      <c r="E65" s="350"/>
-      <c r="F65" s="350"/>
+      <c r="C65" s="348"/>
+      <c r="D65" s="348"/>
+      <c r="E65" s="348"/>
+      <c r="F65" s="348"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4856,7 +4856,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>3.2264739631381233E-2</v>
+        <v>3.2935424642278541E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4866,7 +4866,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>2.9090909090909091E-2</v>
+        <v>2.9695619896065329E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>449</v>
@@ -4957,22 +4957,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="350" t="s">
+      <c r="B80" s="348" t="s">
         <v>363</v>
       </c>
-      <c r="C80" s="350"/>
-      <c r="D80" s="350"/>
-      <c r="E80" s="350"/>
-      <c r="F80" s="350"/>
+      <c r="C80" s="348"/>
+      <c r="D80" s="348"/>
+      <c r="E80" s="348"/>
+      <c r="F80" s="348"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="353" t="s">
+      <c r="B81" s="350" t="s">
         <v>253</v>
       </c>
-      <c r="C81" s="353"/>
-      <c r="D81" s="353"/>
-      <c r="E81" s="353"/>
-      <c r="F81" s="353"/>
+      <c r="C81" s="350"/>
+      <c r="D81" s="350"/>
+      <c r="E81" s="350"/>
+      <c r="F81" s="350"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5016,22 +5016,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="350" t="s">
+      <c r="B89" s="348" t="s">
         <v>364</v>
       </c>
-      <c r="C89" s="350"/>
-      <c r="D89" s="350"/>
-      <c r="E89" s="350"/>
-      <c r="F89" s="350"/>
+      <c r="C89" s="348"/>
+      <c r="D89" s="348"/>
+      <c r="E89" s="348"/>
+      <c r="F89" s="348"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="350" t="s">
+      <c r="B90" s="348" t="s">
         <v>365</v>
       </c>
-      <c r="C90" s="350"/>
-      <c r="D90" s="350"/>
-      <c r="E90" s="350"/>
-      <c r="F90" s="350"/>
+      <c r="C90" s="348"/>
+      <c r="D90" s="348"/>
+      <c r="E90" s="348"/>
+      <c r="F90" s="348"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5068,13 +5068,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="350" t="s">
+      <c r="B97" s="348" t="s">
         <v>366</v>
       </c>
-      <c r="C97" s="350"/>
-      <c r="D97" s="350"/>
-      <c r="E97" s="350"/>
-      <c r="F97" s="350"/>
+      <c r="C97" s="348"/>
+      <c r="D97" s="348"/>
+      <c r="E97" s="348"/>
+      <c r="F97" s="348"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5087,13 +5087,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="350" t="s">
+      <c r="B101" s="348" t="s">
         <v>345</v>
       </c>
-      <c r="C101" s="350"/>
-      <c r="D101" s="350"/>
-      <c r="E101" s="350"/>
-      <c r="F101" s="350"/>
+      <c r="C101" s="348"/>
+      <c r="D101" s="348"/>
+      <c r="E101" s="348"/>
+      <c r="F101" s="348"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5215,13 +5215,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="350" t="s">
+      <c r="B116" s="348" t="s">
         <v>367</v>
       </c>
-      <c r="C116" s="350"/>
-      <c r="D116" s="350"/>
-      <c r="E116" s="350"/>
-      <c r="F116" s="350"/>
+      <c r="C116" s="348"/>
+      <c r="D116" s="348"/>
+      <c r="E116" s="348"/>
+      <c r="F116" s="348"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5260,13 +5260,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="351" t="s">
+      <c r="B123" s="349" t="s">
         <v>368</v>
       </c>
-      <c r="C123" s="351"/>
-      <c r="D123" s="351"/>
-      <c r="E123" s="351"/>
-      <c r="F123" s="351"/>
+      <c r="C123" s="349"/>
+      <c r="D123" s="349"/>
+      <c r="E123" s="349"/>
+      <c r="F123" s="349"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5409,13 +5409,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="354" t="s">
+      <c r="B134" s="353" t="s">
         <v>371</v>
       </c>
-      <c r="C134" s="354"/>
-      <c r="D134" s="354"/>
-      <c r="E134" s="354"/>
-      <c r="F134" s="354"/>
+      <c r="C134" s="353"/>
+      <c r="D134" s="353"/>
+      <c r="E134" s="353"/>
+      <c r="F134" s="353"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5428,22 +5428,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="355" t="s">
+      <c r="B138" s="351" t="s">
         <v>369</v>
       </c>
-      <c r="C138" s="355"/>
-      <c r="D138" s="355"/>
-      <c r="E138" s="355"/>
-      <c r="F138" s="355"/>
+      <c r="C138" s="351"/>
+      <c r="D138" s="351"/>
+      <c r="E138" s="351"/>
+      <c r="F138" s="351"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="350" t="s">
+      <c r="B139" s="348" t="s">
         <v>370</v>
       </c>
-      <c r="C139" s="350"/>
-      <c r="D139" s="350"/>
-      <c r="E139" s="350"/>
-      <c r="F139" s="350"/>
+      <c r="C139" s="348"/>
+      <c r="D139" s="348"/>
+      <c r="E139" s="348"/>
+      <c r="F139" s="348"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5465,7 +5465,7 @@
       </c>
       <c r="C142" s="224">
         <f>F29</f>
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -5500,7 +5500,7 @@
       </c>
       <c r="C146" s="297">
         <f>F29</f>
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="147" spans="2:4">
@@ -5510,7 +5510,7 @@
       </c>
       <c r="C147" s="216">
         <f>Scenarios!C81</f>
-        <v>0.69031028314322285</v>
+        <v>0.69031028314322296</v>
       </c>
     </row>
     <row r="148" spans="2:4">
@@ -5776,13 +5776,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="349" t="s">
+      <c r="B179" s="355" t="s">
         <v>377</v>
       </c>
-      <c r="C179" s="350"/>
-      <c r="D179" s="350"/>
-      <c r="E179" s="350"/>
-      <c r="F179" s="350"/>
+      <c r="C179" s="348"/>
+      <c r="D179" s="348"/>
+      <c r="E179" s="348"/>
+      <c r="F179" s="348"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5819,13 +5819,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="351" t="s">
+      <c r="B188" s="349" t="s">
         <v>382</v>
       </c>
-      <c r="C188" s="351"/>
-      <c r="D188" s="351"/>
-      <c r="E188" s="351"/>
-      <c r="F188" s="351"/>
+      <c r="C188" s="349"/>
+      <c r="D188" s="349"/>
+      <c r="E188" s="349"/>
+      <c r="F188" s="349"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5833,22 +5833,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="348" t="s">
+      <c r="B191" s="354" t="s">
         <v>383</v>
       </c>
-      <c r="C191" s="348"/>
-      <c r="D191" s="348"/>
-      <c r="E191" s="348"/>
-      <c r="F191" s="348"/>
+      <c r="C191" s="354"/>
+      <c r="D191" s="354"/>
+      <c r="E191" s="354"/>
+      <c r="F191" s="354"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="348" t="s">
+      <c r="B192" s="354" t="s">
         <v>384</v>
       </c>
-      <c r="C192" s="348"/>
-      <c r="D192" s="348"/>
-      <c r="E192" s="348"/>
-      <c r="F192" s="348"/>
+      <c r="C192" s="354"/>
+      <c r="D192" s="354"/>
+      <c r="E192" s="354"/>
+      <c r="F192" s="354"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5872,6 +5872,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5888,17 +5899,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13468,32 +13468,32 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>2.9090909090909091E-2</v>
+        <v>2.9695619896065329E-2</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>2.9090909090909091E-2</v>
+        <v>2.9695619896065329E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>2.9090909090909091E-2</v>
+        <v>2.9695619896065329E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>2.9090909090909091E-2</v>
+        <v>2.9695619896065329E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
-        <v>2.9090909090909091E-2</v>
+        <v>2.9695619896065329E-2</v>
       </c>
       <c r="K93" s="23">
         <f t="shared" si="39"/>
-        <v>1.4545454545454545E-2</v>
+        <v>1.4847809948032665E-2</v>
       </c>
       <c r="L93" s="23">
         <f t="shared" si="39"/>
-        <v>1.4545454545454545E-2</v>
+        <v>1.4847809948032665E-2</v>
       </c>
       <c r="M93" s="23">
         <f t="shared" si="39"/>
@@ -14667,50 +14667,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>3.2264739631381233E-2</v>
+        <v>3.2935424642278541E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>3.6765537418103698E-2</v>
+        <v>3.7529780215213498E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>4.8347488468979537E-2</v>
+        <v>4.9352484517332491E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>9.5092740002745618E-2</v>
+        <v>9.7069426506143447E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>6.1578829586687943E-2</v>
+        <v>6.2858864648623544E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>4.604848387557943E-2</v>
+        <v>4.7005690667350941E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>3.8256011691022544E-2</v>
+        <v>3.9051236878363767E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>2.6976690298585591E-2</v>
+        <v>2.7537452977398059E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>2.4523280846756992E-2</v>
+        <v>2.5033044665397821E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>1.6224876371842695E-2</v>
+        <v>1.6562141804961916E-2</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>1.5864415226504891E-2</v>
+        <v>1.619418777761264E-2</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14724,43 +14724,43 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.7727285887586332E-2</v>
+        <v>4.8719389825858356E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.8579210088872215E-2</v>
+        <v>5.9796892258499844E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10520821052385655</v>
+        <v>0.10739516664461972</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.2892799189664075E-2</v>
+        <v>6.4200147650919151E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.4517995178894633E-2</v>
+        <v>4.5443387803251759E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.6062803742646664E-2</v>
+        <v>3.6812438861276289E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.6350863844760396E-2</v>
+        <v>2.6898617510427277E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.83418636679487E-2</v>
+        <v>1.8723134776116899E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.6094169320784203E-2</v>
+        <v>1.6428717755069249E-2</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.4325798202502257E-2</v>
+        <v>1.4623587623192727E-2</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18480,7 +18480,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-13.75</v>
+        <v>-13.47</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18720,7 +18720,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>13.75</v>
+        <v>13.47</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19259,7 +19259,7 @@
       </c>
       <c r="C80" s="167">
         <f>Thesis!F29</f>
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="81" spans="2:8">
@@ -19268,7 +19268,7 @@
       </c>
       <c r="C81" s="116">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>0.69031028314322285</v>
+        <v>0.69031028314322296</v>
       </c>
       <c r="D81" s="116"/>
       <c r="E81" s="100"/>
@@ -19318,7 +19318,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>13.75</v>
+        <v>13.47</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19331,7 +19331,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>-6.1124992361572206E-2</v>
+        <v>-5.4450928827774248E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/300481.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/300481.SZ_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C81056EF-C9FE-4C3E-84D4-CB689AA966D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E554D39-EDF6-4748-AB19-1AE8C34F1C7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2205" yWindow="2205" windowWidth="12690" windowHeight="7642" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -2480,7 +2480,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="17">
+  <numFmts count="18">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="165" formatCode="#,##0&quot;mm&quot;"/>
     <numFmt numFmtId="166" formatCode="#,##0.00&quot;x&quot;"/>
@@ -2498,6 +2498,7 @@
     <numFmt numFmtId="178" formatCode="0.0\x"/>
     <numFmt numFmtId="179" formatCode="0\x"/>
     <numFmt numFmtId="180" formatCode="0.000000000000000%"/>
+    <numFmt numFmtId="181" formatCode="#,##0_);\(#,##0\);0;@"/>
   </numFmts>
   <fonts count="59">
     <font>
@@ -3146,7 +3147,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="360">
+  <cellXfs count="369">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3818,36 +3819,13 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="37" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="37" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="37" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="37" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="37" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="37" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="37" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="37" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="37" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
     <xf numFmtId="37" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -3862,10 +3840,6 @@
     </xf>
     <xf numFmtId="37" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="37" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="37" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="37" fontId="11" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="37" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -3877,6 +3851,48 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="181" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="181" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="181" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="181" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="181" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4377,13 +4393,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="348" t="s">
+      <c r="B18" s="357" t="s">
         <v>360</v>
       </c>
-      <c r="C18" s="348"/>
-      <c r="D18" s="348"/>
-      <c r="E18" s="348"/>
-      <c r="F18" s="348"/>
+      <c r="C18" s="357"/>
+      <c r="D18" s="357"/>
+      <c r="E18" s="357"/>
+      <c r="F18" s="357"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4508,7 +4524,7 @@
         <v>425</v>
       </c>
       <c r="F29" s="302">
-        <v>0.33699999999999997</v>
+        <v>0.33700000000000002</v>
       </c>
     </row>
     <row r="30" spans="2:6">
@@ -4583,22 +4599,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="348" t="s">
+      <c r="B36" s="357" t="s">
         <v>361</v>
       </c>
-      <c r="C36" s="348"/>
-      <c r="D36" s="348"/>
-      <c r="E36" s="348"/>
-      <c r="F36" s="348"/>
+      <c r="C36" s="357"/>
+      <c r="D36" s="357"/>
+      <c r="E36" s="357"/>
+      <c r="F36" s="357"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="350" t="s">
+      <c r="B37" s="359" t="s">
         <v>340</v>
       </c>
-      <c r="C37" s="350"/>
-      <c r="D37" s="350"/>
-      <c r="E37" s="350"/>
-      <c r="F37" s="350"/>
+      <c r="C37" s="359"/>
+      <c r="D37" s="359"/>
+      <c r="E37" s="359"/>
+      <c r="F37" s="359"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4610,19 +4626,19 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="349" t="s">
+      <c r="B40" s="358" t="s">
         <v>232</v>
       </c>
-      <c r="C40" s="349"/>
-      <c r="D40" s="349"/>
-      <c r="E40" s="349"/>
-      <c r="F40" s="349"/>
+      <c r="C40" s="358"/>
+      <c r="D40" s="358"/>
+      <c r="E40" s="358"/>
+      <c r="F40" s="358"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
         <v>233</v>
       </c>
-      <c r="C41" s="76">
+      <c r="C41" s="355">
         <f>Normalized_FCF!C8</f>
         <v>174475161</v>
       </c>
@@ -4636,19 +4652,19 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="349" t="s">
+      <c r="B43" s="358" t="s">
         <v>234</v>
       </c>
-      <c r="C43" s="349"/>
-      <c r="D43" s="349"/>
-      <c r="E43" s="349"/>
-      <c r="F43" s="349"/>
+      <c r="C43" s="358"/>
+      <c r="D43" s="358"/>
+      <c r="E43" s="358"/>
+      <c r="F43" s="358"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
         <v>235</v>
       </c>
-      <c r="C44" s="76">
+      <c r="C44" s="355">
         <f>Normalized_FCF!C9</f>
         <v>61093655</v>
       </c>
@@ -4661,7 +4677,7 @@
       <c r="B45" s="52" t="s">
         <v>236</v>
       </c>
-      <c r="C45" s="76">
+      <c r="C45" s="355">
         <f>Normalized_FCF!C10</f>
         <v>-61093655</v>
       </c>
@@ -4671,19 +4687,19 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="349" t="s">
+      <c r="B47" s="358" t="s">
         <v>237</v>
       </c>
-      <c r="C47" s="349"/>
-      <c r="D47" s="349"/>
-      <c r="E47" s="349"/>
-      <c r="F47" s="349"/>
+      <c r="C47" s="358"/>
+      <c r="D47" s="358"/>
+      <c r="E47" s="358"/>
+      <c r="F47" s="358"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
         <v>238</v>
       </c>
-      <c r="C48" s="76">
+      <c r="C48" s="355">
         <f>Normalized_FCF!C11</f>
         <v>0</v>
       </c>
@@ -4693,19 +4709,19 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="349" t="s">
+      <c r="B50" s="358" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="349"/>
-      <c r="D50" s="349"/>
-      <c r="E50" s="349"/>
-      <c r="F50" s="349"/>
+      <c r="C50" s="358"/>
+      <c r="D50" s="358"/>
+      <c r="E50" s="358"/>
+      <c r="F50" s="358"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
         <v>341</v>
       </c>
-      <c r="C51" s="340">
+      <c r="C51" s="356">
         <f>Normalized_FCF!C48</f>
         <v>3383184.8130000001</v>
       </c>
@@ -4720,7 +4736,7 @@
       <c r="B52" s="47" t="s">
         <v>342</v>
       </c>
-      <c r="C52" s="340">
+      <c r="C52" s="356">
         <f>Normalized_FCF!C47</f>
         <v>-5219951</v>
       </c>
@@ -4735,7 +4751,7 @@
       <c r="B53" s="47" t="s">
         <v>239</v>
       </c>
-      <c r="C53" s="76">
+      <c r="C53" s="355">
         <f>Normalized_FCF!C12</f>
         <v>-1836766.1869999999</v>
       </c>
@@ -4753,7 +4769,7 @@
       <c r="B56" s="47" t="s">
         <v>266</v>
       </c>
-      <c r="C56" s="76">
+      <c r="C56" s="355">
         <f>Normalized_FCF!C15</f>
         <v>0</v>
       </c>
@@ -4763,19 +4779,19 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="349" t="s">
+      <c r="B58" s="358" t="s">
         <v>242</v>
       </c>
-      <c r="C58" s="349"/>
-      <c r="D58" s="349"/>
-      <c r="E58" s="349"/>
-      <c r="F58" s="349"/>
+      <c r="C58" s="358"/>
+      <c r="D58" s="358"/>
+      <c r="E58" s="358"/>
+      <c r="F58" s="358"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
         <v>240</v>
       </c>
-      <c r="C59" s="76">
+      <c r="C59" s="355">
         <f>Normalized_FCF!C14</f>
         <v>-43159598.703249998</v>
       </c>
@@ -4785,19 +4801,19 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="349" t="s">
+      <c r="B61" s="358" t="s">
         <v>339</v>
       </c>
-      <c r="C61" s="352"/>
-      <c r="D61" s="352"/>
-      <c r="E61" s="352"/>
-      <c r="F61" s="352"/>
+      <c r="C61" s="361"/>
+      <c r="D61" s="361"/>
+      <c r="E61" s="361"/>
+      <c r="F61" s="361"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
         <v>243</v>
       </c>
-      <c r="C62" s="76">
+      <c r="C62" s="355">
         <f>Normalized_FCF!C17</f>
         <v>0</v>
       </c>
@@ -4807,28 +4823,28 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="348" t="s">
+      <c r="B64" s="357" t="s">
         <v>344</v>
       </c>
-      <c r="C64" s="348"/>
-      <c r="D64" s="348"/>
-      <c r="E64" s="348"/>
-      <c r="F64" s="348"/>
+      <c r="C64" s="357"/>
+      <c r="D64" s="357"/>
+      <c r="E64" s="357"/>
+      <c r="F64" s="357"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="348" t="s">
+      <c r="B65" s="357" t="s">
         <v>362</v>
       </c>
-      <c r="C65" s="348"/>
-      <c r="D65" s="348"/>
-      <c r="E65" s="348"/>
-      <c r="F65" s="348"/>
+      <c r="C65" s="357"/>
+      <c r="D65" s="357"/>
+      <c r="E65" s="357"/>
+      <c r="F65" s="357"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
         <v>271</v>
       </c>
-      <c r="C67" s="76">
+      <c r="C67" s="355">
         <f>Normalized_FCF!G19</f>
         <v>147540552.86390811</v>
       </c>
@@ -4841,7 +4857,7 @@
       <c r="B68" s="47" t="s">
         <v>249</v>
       </c>
-      <c r="C68" s="76">
+      <c r="C68" s="355">
         <f>Normalized_FCF!C19</f>
         <v>129478796.10975</v>
       </c>
@@ -4880,10 +4896,10 @@
       <c r="B72" s="210" t="s">
         <v>451</v>
       </c>
-      <c r="C72" s="344" t="s">
+      <c r="C72" s="329" t="s">
         <v>453</v>
       </c>
-      <c r="D72" s="344" t="s">
+      <c r="D72" s="329" t="s">
         <v>454</v>
       </c>
     </row>
@@ -4905,11 +4921,11 @@
         <f>Normalized_FCF!B117</f>
         <v>Pre-tax Profit/Sales</v>
       </c>
-      <c r="C74" s="343">
+      <c r="C74" s="328">
         <f>Normalized_FCF!C117</f>
         <v>0.12235120428336442</v>
       </c>
-      <c r="D74" s="343">
+      <c r="D74" s="328">
         <f>Normalized_FCF!G117</f>
         <v>0.12459084820450472</v>
       </c>
@@ -4919,11 +4935,11 @@
         <f>Normalized_FCF!B118</f>
         <v>Sales/Total Assets</v>
       </c>
-      <c r="C75" s="345">
+      <c r="C75" s="330">
         <f>Normalized_FCF!C118</f>
         <v>0.50157874313934503</v>
       </c>
-      <c r="D75" s="345">
+      <c r="D75" s="330">
         <f>Normalized_FCF!G118</f>
         <v>0.50157874313934503</v>
       </c>
@@ -4933,11 +4949,11 @@
         <f>Normalized_FCF!B119</f>
         <v>Total Assets/Equity</v>
       </c>
-      <c r="C76" s="345">
+      <c r="C76" s="330">
         <f>Normalized_FCF!C119</f>
         <v>1.1665094444773738</v>
       </c>
-      <c r="D76" s="345">
+      <c r="D76" s="330">
         <f>Normalized_FCF!G119</f>
         <v>1.1665094444773738</v>
       </c>
@@ -4957,22 +4973,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="348" t="s">
+      <c r="B80" s="357" t="s">
         <v>363</v>
       </c>
-      <c r="C80" s="348"/>
-      <c r="D80" s="348"/>
-      <c r="E80" s="348"/>
-      <c r="F80" s="348"/>
+      <c r="C80" s="357"/>
+      <c r="D80" s="357"/>
+      <c r="E80" s="357"/>
+      <c r="F80" s="357"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="350" t="s">
+      <c r="B81" s="359" t="s">
         <v>253</v>
       </c>
-      <c r="C81" s="350"/>
-      <c r="D81" s="350"/>
-      <c r="E81" s="350"/>
-      <c r="F81" s="350"/>
+      <c r="C81" s="359"/>
+      <c r="D81" s="359"/>
+      <c r="E81" s="359"/>
+      <c r="F81" s="359"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5016,22 +5032,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="348" t="s">
+      <c r="B89" s="357" t="s">
         <v>364</v>
       </c>
-      <c r="C89" s="348"/>
-      <c r="D89" s="348"/>
-      <c r="E89" s="348"/>
-      <c r="F89" s="348"/>
+      <c r="C89" s="357"/>
+      <c r="D89" s="357"/>
+      <c r="E89" s="357"/>
+      <c r="F89" s="357"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="348" t="s">
+      <c r="B90" s="357" t="s">
         <v>365</v>
       </c>
-      <c r="C90" s="348"/>
-      <c r="D90" s="348"/>
-      <c r="E90" s="348"/>
-      <c r="F90" s="348"/>
+      <c r="C90" s="357"/>
+      <c r="D90" s="357"/>
+      <c r="E90" s="357"/>
+      <c r="F90" s="357"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5068,13 +5084,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="348" t="s">
+      <c r="B97" s="357" t="s">
         <v>366</v>
       </c>
-      <c r="C97" s="348"/>
-      <c r="D97" s="348"/>
-      <c r="E97" s="348"/>
-      <c r="F97" s="348"/>
+      <c r="C97" s="357"/>
+      <c r="D97" s="357"/>
+      <c r="E97" s="357"/>
+      <c r="F97" s="357"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5087,19 +5103,19 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="348" t="s">
+      <c r="B101" s="357" t="s">
         <v>345</v>
       </c>
-      <c r="C101" s="348"/>
-      <c r="D101" s="348"/>
-      <c r="E101" s="348"/>
-      <c r="F101" s="348"/>
+      <c r="C101" s="357"/>
+      <c r="D101" s="357"/>
+      <c r="E101" s="357"/>
+      <c r="F101" s="357"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
         <v>256</v>
       </c>
-      <c r="C102" s="76">
+      <c r="C102" s="355">
         <f>DCF!C7</f>
         <v>100067739.72</v>
       </c>
@@ -5125,7 +5141,7 @@
       <c r="B104" s="296" t="s">
         <v>405</v>
       </c>
-      <c r="C104" s="346">
+      <c r="C104" s="331">
         <f>IF(BS!G31/BS!G27&gt;300%,"nm",BS!G31/BS!G27)</f>
         <v>4.1494671576720196E-2</v>
       </c>
@@ -5134,7 +5150,7 @@
       <c r="B105" s="296" t="s">
         <v>407</v>
       </c>
-      <c r="C105" s="347">
+      <c r="C105" s="332">
         <f>IF(BS!C50&gt;30,"nm",BS!C50)</f>
         <v>0.57353573509526667</v>
       </c>
@@ -5148,7 +5164,7 @@
       <c r="B108" s="47" t="s">
         <v>265</v>
       </c>
-      <c r="C108" s="76">
+      <c r="C108" s="355">
         <f>BS!C66</f>
         <v>1012553160.92</v>
       </c>
@@ -5161,7 +5177,7 @@
       <c r="B109" s="47" t="s">
         <v>267</v>
       </c>
-      <c r="C109" s="76">
+      <c r="C109" s="355">
         <f>DCF!C8</f>
         <v>787007506.71999991</v>
       </c>
@@ -5192,7 +5208,7 @@
       <c r="B113" s="47" t="s">
         <v>258</v>
       </c>
-      <c r="C113" s="76">
+      <c r="C113" s="355">
         <f>DCF!C9</f>
         <v>0</v>
       </c>
@@ -5215,13 +5231,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="348" t="s">
+      <c r="B116" s="357" t="s">
         <v>367</v>
       </c>
-      <c r="C116" s="348"/>
-      <c r="D116" s="348"/>
-      <c r="E116" s="348"/>
-      <c r="F116" s="348"/>
+      <c r="C116" s="357"/>
+      <c r="D116" s="357"/>
+      <c r="E116" s="357"/>
+      <c r="F116" s="357"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5260,13 +5276,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="349" t="s">
+      <c r="B123" s="358" t="s">
         <v>368</v>
       </c>
-      <c r="C123" s="349"/>
-      <c r="D123" s="349"/>
-      <c r="E123" s="349"/>
-      <c r="F123" s="349"/>
+      <c r="C123" s="358"/>
+      <c r="D123" s="358"/>
+      <c r="E123" s="358"/>
+      <c r="F123" s="358"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5409,13 +5425,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="353" t="s">
+      <c r="B134" s="362" t="s">
         <v>371</v>
       </c>
-      <c r="C134" s="353"/>
-      <c r="D134" s="353"/>
-      <c r="E134" s="353"/>
-      <c r="F134" s="353"/>
+      <c r="C134" s="362"/>
+      <c r="D134" s="362"/>
+      <c r="E134" s="362"/>
+      <c r="F134" s="362"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5428,22 +5444,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="351" t="s">
+      <c r="B138" s="360" t="s">
         <v>369</v>
       </c>
-      <c r="C138" s="351"/>
-      <c r="D138" s="351"/>
-      <c r="E138" s="351"/>
-      <c r="F138" s="351"/>
+      <c r="C138" s="360"/>
+      <c r="D138" s="360"/>
+      <c r="E138" s="360"/>
+      <c r="F138" s="360"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="348" t="s">
+      <c r="B139" s="357" t="s">
         <v>370</v>
       </c>
-      <c r="C139" s="348"/>
-      <c r="D139" s="348"/>
-      <c r="E139" s="348"/>
-      <c r="F139" s="348"/>
+      <c r="C139" s="357"/>
+      <c r="D139" s="357"/>
+      <c r="E139" s="357"/>
+      <c r="F139" s="357"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5465,7 +5481,7 @@
       </c>
       <c r="C142" s="224">
         <f>F29</f>
-        <v>0.33699999999999997</v>
+        <v>0.33700000000000002</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -5500,7 +5516,7 @@
       </c>
       <c r="C146" s="297">
         <f>F29</f>
-        <v>0.33699999999999997</v>
+        <v>0.33700000000000002</v>
       </c>
     </row>
     <row r="147" spans="2:4">
@@ -5510,7 +5526,7 @@
       </c>
       <c r="C147" s="216">
         <f>Scenarios!C81</f>
-        <v>0.69031028314322296</v>
+        <v>0.69031028314322285</v>
       </c>
     </row>
     <row r="148" spans="2:4">
@@ -5776,13 +5792,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="355" t="s">
+      <c r="B179" s="364" t="s">
         <v>377</v>
       </c>
-      <c r="C179" s="348"/>
-      <c r="D179" s="348"/>
-      <c r="E179" s="348"/>
-      <c r="F179" s="348"/>
+      <c r="C179" s="357"/>
+      <c r="D179" s="357"/>
+      <c r="E179" s="357"/>
+      <c r="F179" s="357"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5790,13 +5806,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="352" t="s">
+      <c r="B182" s="361" t="s">
         <v>381</v>
       </c>
-      <c r="C182" s="352"/>
-      <c r="D182" s="352"/>
-      <c r="E182" s="352"/>
-      <c r="F182" s="352"/>
+      <c r="C182" s="361"/>
+      <c r="D182" s="361"/>
+      <c r="E182" s="361"/>
+      <c r="F182" s="361"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -5819,13 +5835,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="349" t="s">
+      <c r="B188" s="358" t="s">
         <v>382</v>
       </c>
-      <c r="C188" s="349"/>
-      <c r="D188" s="349"/>
-      <c r="E188" s="349"/>
-      <c r="F188" s="349"/>
+      <c r="C188" s="358"/>
+      <c r="D188" s="358"/>
+      <c r="E188" s="358"/>
+      <c r="F188" s="358"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5833,22 +5849,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="354" t="s">
+      <c r="B191" s="363" t="s">
         <v>383</v>
       </c>
-      <c r="C191" s="354"/>
-      <c r="D191" s="354"/>
-      <c r="E191" s="354"/>
-      <c r="F191" s="354"/>
+      <c r="C191" s="363"/>
+      <c r="D191" s="363"/>
+      <c r="E191" s="363"/>
+      <c r="F191" s="363"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="354" t="s">
+      <c r="B192" s="363" t="s">
         <v>384</v>
       </c>
-      <c r="C192" s="354"/>
-      <c r="D192" s="354"/>
-      <c r="E192" s="354"/>
-      <c r="F192" s="354"/>
+      <c r="C192" s="363"/>
+      <c r="D192" s="363"/>
+      <c r="E192" s="363"/>
+      <c r="F192" s="363"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -6014,391 +6030,391 @@
       <c r="B4" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="334">
+      <c r="C4" s="321">
         <v>1411006911</v>
       </c>
-      <c r="D4" s="334">
+      <c r="D4" s="321">
         <v>1379201434</v>
       </c>
-      <c r="E4" s="334">
+      <c r="E4" s="321">
         <v>1596926914</v>
       </c>
-      <c r="F4" s="334">
+      <c r="F4" s="321">
         <v>1393260092</v>
       </c>
-      <c r="G4" s="334">
+      <c r="G4" s="321">
         <v>912941814</v>
       </c>
-      <c r="H4" s="334">
+      <c r="H4" s="321">
         <v>680253790</v>
       </c>
-      <c r="I4" s="334">
+      <c r="I4" s="321">
         <v>635842505</v>
       </c>
-      <c r="J4" s="334">
+      <c r="J4" s="321">
         <v>540919477</v>
       </c>
-      <c r="K4" s="334">
+      <c r="K4" s="321">
         <v>375797253</v>
       </c>
-      <c r="L4" s="334">
+      <c r="L4" s="321">
         <v>350212915</v>
       </c>
-      <c r="M4" s="334"/>
+      <c r="M4" s="321"/>
     </row>
     <row r="5" spans="2:13">
       <c r="B5" s="40" t="s">
         <v>43</v>
       </c>
-      <c r="C5" s="334">
+      <c r="C5" s="321">
         <v>1115025379</v>
       </c>
-      <c r="D5" s="334">
+      <c r="D5" s="321">
         <v>1033174066</v>
       </c>
-      <c r="E5" s="334">
+      <c r="E5" s="321">
         <v>1034288683</v>
       </c>
-      <c r="F5" s="334">
+      <c r="F5" s="321">
         <v>993330987</v>
       </c>
-      <c r="G5" s="334">
+      <c r="G5" s="321">
         <v>600104422</v>
       </c>
-      <c r="H5" s="334">
+      <c r="H5" s="321">
         <v>431395603</v>
       </c>
-      <c r="I5" s="334">
+      <c r="I5" s="321">
         <v>434340576</v>
       </c>
-      <c r="J5" s="334">
+      <c r="J5" s="321">
         <v>369324839</v>
       </c>
-      <c r="K5" s="334">
+      <c r="K5" s="321">
         <v>255166042</v>
       </c>
-      <c r="L5" s="334">
+      <c r="L5" s="321">
         <v>243249284</v>
       </c>
-      <c r="M5" s="334"/>
+      <c r="M5" s="321"/>
     </row>
     <row r="6" spans="2:13">
       <c r="B6" s="40" t="s">
         <v>54</v>
       </c>
-      <c r="C6" s="334">
+      <c r="C6" s="321">
         <v>43790640</v>
       </c>
-      <c r="D6" s="334">
+      <c r="D6" s="321">
         <v>38222426</v>
       </c>
-      <c r="E6" s="334">
+      <c r="E6" s="321">
         <v>41394520</v>
       </c>
-      <c r="F6" s="334">
+      <c r="F6" s="321">
         <v>35854036</v>
       </c>
-      <c r="G6" s="334">
+      <c r="G6" s="321">
         <v>28188973</v>
       </c>
-      <c r="H6" s="334">
+      <c r="H6" s="321">
         <v>22486501</v>
       </c>
-      <c r="I6" s="334">
+      <c r="I6" s="321">
         <v>21263075</v>
       </c>
-      <c r="J6" s="334">
+      <c r="J6" s="321">
         <v>61524619</v>
       </c>
-      <c r="K6" s="334">
+      <c r="K6" s="321">
         <v>44726842</v>
       </c>
-      <c r="L6" s="334">
+      <c r="L6" s="321">
         <v>33204787</v>
       </c>
-      <c r="M6" s="334"/>
+      <c r="M6" s="321"/>
     </row>
     <row r="7" spans="2:13">
       <c r="B7" s="69" t="s">
         <v>61</v>
       </c>
-      <c r="C7" s="335">
+      <c r="C7" s="322">
         <v>10699910</v>
       </c>
-      <c r="D7" s="335">
+      <c r="D7" s="322">
         <v>8156496</v>
       </c>
-      <c r="E7" s="335">
+      <c r="E7" s="322">
         <v>8760304</v>
       </c>
-      <c r="F7" s="335">
+      <c r="F7" s="322">
         <v>6582094</v>
       </c>
-      <c r="G7" s="335">
+      <c r="G7" s="322">
         <v>6591833</v>
       </c>
-      <c r="H7" s="335">
+      <c r="H7" s="322">
         <v>28503017</v>
       </c>
-      <c r="I7" s="335">
+      <c r="I7" s="322">
         <v>27458819</v>
       </c>
-      <c r="J7" s="335">
+      <c r="J7" s="322">
         <v>20907812</v>
       </c>
-      <c r="K7" s="335">
+      <c r="K7" s="322">
         <v>15460659</v>
       </c>
-      <c r="L7" s="335">
+      <c r="L7" s="322">
         <v>11888598</v>
       </c>
-      <c r="M7" s="335"/>
+      <c r="M7" s="322"/>
     </row>
     <row r="8" spans="2:13">
       <c r="B8" s="40" t="s">
         <v>49</v>
       </c>
-      <c r="C8" s="334">
+      <c r="C8" s="321">
         <v>77948987</v>
       </c>
-      <c r="D8" s="334">
+      <c r="D8" s="321">
         <v>79192247</v>
       </c>
-      <c r="E8" s="334">
+      <c r="E8" s="321">
         <v>74126277</v>
       </c>
-      <c r="F8" s="334">
+      <c r="F8" s="321">
         <v>79595413</v>
       </c>
-      <c r="G8" s="334">
+      <c r="G8" s="321">
         <v>69723237</v>
       </c>
-      <c r="H8" s="334">
+      <c r="H8" s="321">
         <v>50161359</v>
       </c>
-      <c r="I8" s="334">
+      <c r="I8" s="321">
         <v>52954564</v>
       </c>
-      <c r="J8" s="334"/>
-      <c r="K8" s="334"/>
-      <c r="L8" s="334"/>
-      <c r="M8" s="334"/>
+      <c r="J8" s="321"/>
+      <c r="K8" s="321"/>
+      <c r="L8" s="321"/>
+      <c r="M8" s="321"/>
     </row>
     <row r="9" spans="2:13">
       <c r="B9" s="40" t="s">
         <v>160</v>
       </c>
-      <c r="C9" s="334"/>
-      <c r="D9" s="334"/>
-      <c r="E9" s="334"/>
-      <c r="F9" s="334"/>
-      <c r="G9" s="334"/>
-      <c r="H9" s="334"/>
-      <c r="I9" s="334"/>
-      <c r="J9" s="334"/>
-      <c r="K9" s="334"/>
-      <c r="L9" s="334"/>
-      <c r="M9" s="334"/>
+      <c r="C9" s="321"/>
+      <c r="D9" s="321"/>
+      <c r="E9" s="321"/>
+      <c r="F9" s="321"/>
+      <c r="G9" s="321"/>
+      <c r="H9" s="321"/>
+      <c r="I9" s="321"/>
+      <c r="J9" s="321"/>
+      <c r="K9" s="321"/>
+      <c r="L9" s="321"/>
+      <c r="M9" s="321"/>
     </row>
     <row r="10" spans="2:13">
       <c r="B10" s="40" t="s">
         <v>168</v>
       </c>
-      <c r="C10" s="334"/>
-      <c r="D10" s="334"/>
-      <c r="E10" s="334"/>
-      <c r="F10" s="334"/>
-      <c r="G10" s="334"/>
-      <c r="H10" s="334"/>
-      <c r="I10" s="334"/>
-      <c r="J10" s="334"/>
-      <c r="K10" s="334"/>
-      <c r="L10" s="334"/>
-      <c r="M10" s="334"/>
+      <c r="C10" s="321"/>
+      <c r="D10" s="321"/>
+      <c r="E10" s="321"/>
+      <c r="F10" s="321"/>
+      <c r="G10" s="321"/>
+      <c r="H10" s="321"/>
+      <c r="I10" s="321"/>
+      <c r="J10" s="321"/>
+      <c r="K10" s="321"/>
+      <c r="L10" s="321"/>
+      <c r="M10" s="321"/>
     </row>
     <row r="11" spans="2:13">
       <c r="B11" s="40" t="s">
         <v>159</v>
       </c>
-      <c r="C11" s="334"/>
-      <c r="D11" s="334"/>
-      <c r="E11" s="334"/>
-      <c r="F11" s="334"/>
-      <c r="G11" s="334"/>
-      <c r="H11" s="334"/>
-      <c r="I11" s="334"/>
-      <c r="J11" s="334"/>
-      <c r="K11" s="334"/>
-      <c r="L11" s="334"/>
-      <c r="M11" s="334"/>
+      <c r="C11" s="321"/>
+      <c r="D11" s="321"/>
+      <c r="E11" s="321"/>
+      <c r="F11" s="321"/>
+      <c r="G11" s="321"/>
+      <c r="H11" s="321"/>
+      <c r="I11" s="321"/>
+      <c r="J11" s="321"/>
+      <c r="K11" s="321"/>
+      <c r="L11" s="321"/>
+      <c r="M11" s="321"/>
     </row>
     <row r="12" spans="2:13">
       <c r="B12" s="40" t="s">
         <v>39</v>
       </c>
-      <c r="C12" s="334">
+      <c r="C12" s="321">
         <v>5219951</v>
       </c>
-      <c r="D12" s="334">
+      <c r="D12" s="321">
         <v>8074436</v>
       </c>
-      <c r="E12" s="334">
+      <c r="E12" s="321">
         <v>4999986</v>
       </c>
-      <c r="F12" s="334">
+      <c r="F12" s="321">
         <v>32946</v>
       </c>
-      <c r="G12" s="334">
-        <v>0</v>
-      </c>
-      <c r="H12" s="334">
+      <c r="G12" s="321">
+        <v>0</v>
+      </c>
+      <c r="H12" s="321">
         <v>1902780</v>
       </c>
-      <c r="I12" s="334">
+      <c r="I12" s="321">
         <v>3158441</v>
       </c>
-      <c r="J12" s="334"/>
-      <c r="K12" s="334"/>
-      <c r="L12" s="334"/>
-      <c r="M12" s="334"/>
+      <c r="J12" s="321"/>
+      <c r="K12" s="321"/>
+      <c r="L12" s="321"/>
+      <c r="M12" s="321"/>
     </row>
     <row r="13" spans="2:13">
       <c r="B13" s="40" t="s">
         <v>67</v>
       </c>
-      <c r="C13" s="334">
+      <c r="C13" s="321">
         <v>30422495</v>
       </c>
-      <c r="D13" s="334">
+      <c r="D13" s="321">
         <v>14354714</v>
       </c>
-      <c r="E13" s="334">
+      <c r="E13" s="321">
         <v>2142657</v>
       </c>
-      <c r="F13" s="334">
+      <c r="F13" s="321">
         <v>2175704</v>
       </c>
-      <c r="G13" s="334">
+      <c r="G13" s="321">
         <v>2045796</v>
       </c>
-      <c r="H13" s="334">
+      <c r="H13" s="321">
         <v>5422489</v>
       </c>
-      <c r="I13" s="334">
+      <c r="I13" s="321">
         <v>3339969</v>
       </c>
-      <c r="J13" s="334"/>
-      <c r="K13" s="334"/>
-      <c r="L13" s="334"/>
-      <c r="M13" s="334"/>
+      <c r="J13" s="321"/>
+      <c r="K13" s="321"/>
+      <c r="L13" s="321"/>
+      <c r="M13" s="321"/>
     </row>
     <row r="14" spans="2:13">
       <c r="B14" s="40" t="s">
         <v>50</v>
       </c>
-      <c r="C14" s="334">
+      <c r="C14" s="321">
         <v>28257995</v>
       </c>
-      <c r="D14" s="334">
+      <c r="D14" s="321">
         <v>29716699</v>
       </c>
-      <c r="E14" s="334">
+      <c r="E14" s="321">
         <v>60986391</v>
       </c>
-      <c r="F14" s="334">
+      <c r="F14" s="321">
         <v>37814748</v>
       </c>
-      <c r="G14" s="334">
+      <c r="G14" s="321">
         <v>30587751</v>
       </c>
-      <c r="H14" s="334">
+      <c r="H14" s="321">
         <v>21993559</v>
       </c>
-      <c r="I14" s="334">
+      <c r="I14" s="321">
         <v>16485438</v>
       </c>
-      <c r="J14" s="334">
+      <c r="J14" s="321">
         <v>11657792</v>
       </c>
-      <c r="K14" s="334">
+      <c r="K14" s="321">
         <v>10793741</v>
       </c>
-      <c r="L14" s="334">
+      <c r="L14" s="321">
         <v>10094751</v>
       </c>
-      <c r="M14" s="334"/>
+      <c r="M14" s="321"/>
     </row>
     <row r="15" spans="2:13">
       <c r="B15" s="43" t="s">
         <v>42</v>
       </c>
-      <c r="C15" s="336">
+      <c r="C15" s="323">
         <v>191530184</v>
       </c>
-      <c r="D15" s="336">
+      <c r="D15" s="323">
         <v>235079089</v>
       </c>
-      <c r="E15" s="336">
+      <c r="E15" s="323">
         <v>422201840</v>
       </c>
-      <c r="F15" s="336">
+      <c r="F15" s="323">
         <v>252389575</v>
       </c>
-      <c r="G15" s="336">
+      <c r="G15" s="323">
         <v>178651261</v>
       </c>
-      <c r="H15" s="336">
+      <c r="H15" s="323">
         <v>144720474</v>
       </c>
-      <c r="I15" s="336">
+      <c r="I15" s="323">
         <v>105746340</v>
       </c>
-      <c r="J15" s="336">
+      <c r="J15" s="323">
         <v>73606124</v>
       </c>
-      <c r="K15" s="336">
+      <c r="K15" s="323">
         <v>64586099</v>
       </c>
-      <c r="L15" s="336">
+      <c r="L15" s="323">
         <v>57489604</v>
       </c>
-      <c r="M15" s="336"/>
+      <c r="M15" s="323"/>
     </row>
     <row r="16" spans="2:13">
       <c r="B16" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="C16" s="334">
+      <c r="C16" s="321">
         <v>-21781</v>
       </c>
-      <c r="D16" s="334">
+      <c r="D16" s="321">
         <v>-43122</v>
       </c>
-      <c r="E16" s="334">
+      <c r="E16" s="321">
         <v>-100415</v>
       </c>
-      <c r="F16" s="334">
+      <c r="F16" s="321">
         <v>-281178</v>
       </c>
-      <c r="G16" s="334">
+      <c r="G16" s="321">
         <v>-979278</v>
       </c>
-      <c r="H16" s="334">
+      <c r="H16" s="321">
         <v>-542989</v>
       </c>
-      <c r="I16" s="334">
+      <c r="I16" s="321">
         <v>126598</v>
       </c>
-      <c r="J16" s="334">
+      <c r="J16" s="321">
         <v>-556998</v>
       </c>
-      <c r="K16" s="334">
+      <c r="K16" s="321">
         <v>-303635</v>
       </c>
-      <c r="L16" s="334">
-        <v>0</v>
-      </c>
-      <c r="M16" s="334"/>
+      <c r="L16" s="321">
+        <v>0</v>
+      </c>
+      <c r="M16" s="321"/>
     </row>
     <row r="18" spans="2:13">
       <c r="B18" s="16" t="s">
@@ -6410,171 +6426,171 @@
       <c r="B19" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="C19" s="334">
+      <c r="C19" s="321">
         <v>61093655</v>
       </c>
-      <c r="D19" s="334">
+      <c r="D19" s="321">
         <v>58833476</v>
       </c>
-      <c r="E19" s="334">
+      <c r="E19" s="321">
         <v>54349703</v>
       </c>
-      <c r="F19" s="334">
+      <c r="F19" s="321">
         <v>41876368</v>
       </c>
-      <c r="G19" s="334">
+      <c r="G19" s="321">
         <v>32578395</v>
       </c>
-      <c r="H19" s="334">
+      <c r="H19" s="321">
         <v>25986482</v>
       </c>
-      <c r="I19" s="334">
+      <c r="I19" s="321">
         <v>19020963</v>
       </c>
-      <c r="J19" s="334"/>
-      <c r="K19" s="334"/>
-      <c r="L19" s="334"/>
-      <c r="M19" s="334"/>
+      <c r="J19" s="321"/>
+      <c r="K19" s="321"/>
+      <c r="L19" s="321"/>
+      <c r="M19" s="321"/>
     </row>
     <row r="20" spans="2:13">
       <c r="B20" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="C20" s="334"/>
-      <c r="D20" s="334"/>
-      <c r="E20" s="334"/>
-      <c r="F20" s="334"/>
-      <c r="G20" s="334"/>
-      <c r="H20" s="334"/>
-      <c r="I20" s="334"/>
-      <c r="J20" s="334"/>
-      <c r="K20" s="334"/>
-      <c r="L20" s="334"/>
-      <c r="M20" s="334"/>
+      <c r="C20" s="321"/>
+      <c r="D20" s="321"/>
+      <c r="E20" s="321"/>
+      <c r="F20" s="321"/>
+      <c r="G20" s="321"/>
+      <c r="H20" s="321"/>
+      <c r="I20" s="321"/>
+      <c r="J20" s="321"/>
+      <c r="K20" s="321"/>
+      <c r="L20" s="321"/>
+      <c r="M20" s="321"/>
     </row>
     <row r="21" spans="2:13">
       <c r="B21" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="C21" s="334"/>
-      <c r="D21" s="334"/>
-      <c r="E21" s="334"/>
-      <c r="F21" s="334"/>
-      <c r="G21" s="334"/>
-      <c r="H21" s="334"/>
-      <c r="I21" s="334"/>
-      <c r="J21" s="334"/>
-      <c r="K21" s="334"/>
-      <c r="L21" s="334"/>
-      <c r="M21" s="334"/>
+      <c r="C21" s="321"/>
+      <c r="D21" s="321"/>
+      <c r="E21" s="321"/>
+      <c r="F21" s="321"/>
+      <c r="G21" s="321"/>
+      <c r="H21" s="321"/>
+      <c r="I21" s="321"/>
+      <c r="J21" s="321"/>
+      <c r="K21" s="321"/>
+      <c r="L21" s="321"/>
+      <c r="M21" s="321"/>
     </row>
     <row r="22" spans="2:13">
       <c r="B22" s="27" t="s">
         <v>372</v>
       </c>
-      <c r="C22" s="334">
+      <c r="C22" s="321">
         <v>246703905</v>
       </c>
-      <c r="D22" s="334">
+      <c r="D22" s="321">
         <v>347046365</v>
       </c>
-      <c r="E22" s="334">
+      <c r="E22" s="321">
         <v>287027202</v>
       </c>
-      <c r="F22" s="334">
+      <c r="F22" s="321">
         <v>86266623</v>
       </c>
-      <c r="G22" s="334">
+      <c r="G22" s="321">
         <v>58267003</v>
       </c>
-      <c r="H22" s="334">
+      <c r="H22" s="321">
         <v>140210978</v>
       </c>
-      <c r="I22" s="334">
+      <c r="I22" s="321">
         <v>67874413</v>
       </c>
-      <c r="J22" s="334">
+      <c r="J22" s="321">
         <v>41999797</v>
       </c>
-      <c r="K22" s="334">
+      <c r="K22" s="321">
         <v>57929945</v>
       </c>
-      <c r="L22" s="334">
+      <c r="L22" s="321">
         <v>60165832</v>
       </c>
-      <c r="M22" s="334"/>
+      <c r="M22" s="321"/>
     </row>
     <row r="23" spans="2:13">
       <c r="B23" s="27" t="s">
         <v>374</v>
       </c>
-      <c r="C23" s="334">
+      <c r="C23" s="321">
         <v>12280558</v>
       </c>
-      <c r="D23" s="334">
+      <c r="D23" s="321">
         <v>-180077187</v>
       </c>
-      <c r="E23" s="334">
+      <c r="E23" s="321">
         <v>-489702029</v>
       </c>
-      <c r="F23" s="334">
+      <c r="F23" s="321">
         <v>-828815436</v>
       </c>
-      <c r="G23" s="334">
+      <c r="G23" s="321">
         <v>-33801434</v>
       </c>
-      <c r="H23" s="334">
+      <c r="H23" s="321">
         <v>-6498350</v>
       </c>
-      <c r="I23" s="334">
+      <c r="I23" s="321">
         <v>-148896881</v>
       </c>
-      <c r="J23" s="334">
+      <c r="J23" s="321">
         <v>-6933376</v>
       </c>
-      <c r="K23" s="334">
+      <c r="K23" s="321">
         <v>19848980</v>
       </c>
-      <c r="L23" s="334">
+      <c r="L23" s="321">
         <v>-129890596</v>
       </c>
-      <c r="M23" s="334"/>
+      <c r="M23" s="321"/>
     </row>
     <row r="24" spans="2:13">
       <c r="B24" s="27" t="s">
         <v>373</v>
       </c>
-      <c r="C24" s="334">
+      <c r="C24" s="321">
         <v>-205377752</v>
       </c>
-      <c r="D24" s="334">
+      <c r="D24" s="321">
         <v>-221433067</v>
       </c>
-      <c r="E24" s="334">
+      <c r="E24" s="321">
         <v>217556629</v>
       </c>
-      <c r="F24" s="334">
+      <c r="F24" s="321">
         <v>762126692</v>
       </c>
-      <c r="G24" s="334">
+      <c r="G24" s="321">
         <v>-51439436</v>
       </c>
-      <c r="H24" s="334">
+      <c r="H24" s="321">
         <v>-136361462</v>
       </c>
-      <c r="I24" s="334">
+      <c r="I24" s="321">
         <v>165513969</v>
       </c>
-      <c r="J24" s="334">
+      <c r="J24" s="321">
         <v>23237136</v>
       </c>
-      <c r="K24" s="334">
+      <c r="K24" s="321">
         <v>-20636100</v>
       </c>
-      <c r="L24" s="334">
+      <c r="L24" s="321">
         <v>93378802</v>
       </c>
-      <c r="M24" s="334"/>
+      <c r="M24" s="321"/>
     </row>
     <row r="25" spans="2:13">
       <c r="B25" s="24" t="str">
@@ -6623,186 +6639,186 @@
       <c r="B28" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="C28" s="323">
+      <c r="C28" s="318">
         <f>BS!C4</f>
         <v>435508276.29999995</v>
       </c>
-      <c r="D28" s="334">
+      <c r="D28" s="321">
         <v>286539091</v>
       </c>
-      <c r="E28" s="334">
+      <c r="E28" s="321">
         <v>273013471</v>
       </c>
-      <c r="F28" s="334">
+      <c r="F28" s="321">
         <v>232578044</v>
       </c>
-      <c r="G28" s="334">
+      <c r="G28" s="321">
         <v>139788443</v>
       </c>
-      <c r="H28" s="334">
+      <c r="H28" s="321">
         <v>109488661</v>
       </c>
-      <c r="I28" s="334">
+      <c r="I28" s="321">
         <v>124904314</v>
       </c>
-      <c r="J28" s="334">
+      <c r="J28" s="321">
         <v>104722300</v>
       </c>
-      <c r="K28" s="334">
+      <c r="K28" s="321">
         <v>68594092</v>
       </c>
-      <c r="L28" s="334">
+      <c r="L28" s="321">
         <v>56185706</v>
       </c>
-      <c r="M28" s="334"/>
+      <c r="M28" s="321"/>
     </row>
     <row r="29" spans="2:13">
       <c r="B29" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="C29" s="323">
+      <c r="C29" s="318">
         <f>BS!C6</f>
         <v>149619822.47999999</v>
       </c>
-      <c r="D29" s="334">
+      <c r="D29" s="321">
         <v>175557090</v>
       </c>
-      <c r="E29" s="334">
+      <c r="E29" s="321">
         <v>221536955</v>
       </c>
-      <c r="F29" s="334">
+      <c r="F29" s="321">
         <v>134930930</v>
       </c>
-      <c r="G29" s="334">
+      <c r="G29" s="321">
         <v>102812384</v>
       </c>
-      <c r="H29" s="334">
+      <c r="H29" s="321">
         <v>54993674</v>
       </c>
-      <c r="I29" s="334">
+      <c r="I29" s="321">
         <v>64663319</v>
       </c>
-      <c r="J29" s="334">
+      <c r="J29" s="321">
         <v>50945742</v>
       </c>
-      <c r="K29" s="334">
+      <c r="K29" s="321">
         <v>31346347</v>
       </c>
-      <c r="L29" s="334">
+      <c r="L29" s="321">
         <v>31941901</v>
       </c>
-      <c r="M29" s="334"/>
+      <c r="M29" s="321"/>
     </row>
     <row r="30" spans="2:13">
       <c r="B30" s="29" t="s">
         <v>40</v>
       </c>
-      <c r="C30" s="324">
+      <c r="C30" s="319">
         <f>BS!C33+BS!C42</f>
         <v>401550924.92000002</v>
       </c>
-      <c r="D30" s="336">
+      <c r="D30" s="323">
         <v>375837168</v>
       </c>
-      <c r="E30" s="336">
+      <c r="E30" s="323">
         <v>484715813</v>
       </c>
-      <c r="F30" s="336">
+      <c r="F30" s="323">
         <v>120473425</v>
       </c>
-      <c r="G30" s="336">
+      <c r="G30" s="323">
         <v>77386991</v>
       </c>
-      <c r="H30" s="336">
+      <c r="H30" s="323">
         <v>107878390</v>
       </c>
-      <c r="I30" s="336">
+      <c r="I30" s="323">
         <v>144733614</v>
       </c>
-      <c r="J30" s="336">
+      <c r="J30" s="323">
         <v>117054123</v>
       </c>
-      <c r="K30" s="336">
+      <c r="K30" s="323">
         <v>64103116</v>
       </c>
-      <c r="L30" s="336">
+      <c r="L30" s="323">
         <v>30979762</v>
       </c>
-      <c r="M30" s="336"/>
+      <c r="M30" s="323"/>
     </row>
     <row r="31" spans="2:13">
       <c r="B31" s="29" t="s">
         <v>30</v>
       </c>
-      <c r="C31" s="324">
+      <c r="C31" s="319">
         <f>BS!G27</f>
         <v>2411580473.29</v>
       </c>
-      <c r="D31" s="336">
+      <c r="D31" s="323">
         <v>2445882003</v>
       </c>
-      <c r="E31" s="336">
+      <c r="E31" s="323">
         <v>2319825981</v>
       </c>
-      <c r="F31" s="336">
+      <c r="F31" s="323">
         <v>1994747908</v>
       </c>
-      <c r="G31" s="336">
+      <c r="G31" s="323">
         <v>1001406127</v>
       </c>
-      <c r="H31" s="336">
+      <c r="H31" s="323">
         <v>868539655</v>
       </c>
-      <c r="I31" s="336">
+      <c r="I31" s="323">
         <v>768786181</v>
       </c>
-      <c r="J31" s="336">
+      <c r="J31" s="323">
         <v>515701210</v>
       </c>
-      <c r="K31" s="336">
+      <c r="K31" s="323">
         <v>457812342</v>
       </c>
-      <c r="L31" s="336">
+      <c r="L31" s="323">
         <v>432312719</v>
       </c>
-      <c r="M31" s="336"/>
+      <c r="M31" s="323"/>
     </row>
     <row r="32" spans="2:13">
       <c r="B32" s="26" t="s">
         <v>173</v>
       </c>
-      <c r="C32" s="323">
+      <c r="C32" s="318">
         <f>BS!G28</f>
         <v>-371705.83</v>
       </c>
-      <c r="D32" s="334">
+      <c r="D32" s="321">
         <v>-349925</v>
       </c>
-      <c r="E32" s="334">
+      <c r="E32" s="321">
         <v>-306803</v>
       </c>
-      <c r="F32" s="334">
+      <c r="F32" s="321">
         <v>-206387</v>
       </c>
-      <c r="G32" s="334">
+      <c r="G32" s="321">
         <v>1585988</v>
       </c>
-      <c r="H32" s="334">
+      <c r="H32" s="321">
         <v>2565266</v>
       </c>
-      <c r="I32" s="334">
+      <c r="I32" s="321">
         <v>3666589</v>
       </c>
-      <c r="J32" s="334">
+      <c r="J32" s="321">
         <v>3639300</v>
       </c>
-      <c r="K32" s="334">
+      <c r="K32" s="321">
         <v>578365</v>
       </c>
-      <c r="L32" s="334">
-        <v>0</v>
-      </c>
-      <c r="M32" s="334"/>
+      <c r="L32" s="321">
+        <v>0</v>
+      </c>
+      <c r="M32" s="321"/>
     </row>
     <row r="34" spans="2:13" ht="13.9">
       <c r="B34" s="36" t="s">
@@ -6829,47 +6845,47 @@
       <c r="B36" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="C36" s="323">
+      <c r="C36" s="318">
         <f t="shared" ref="C36:M36" si="1">IF(C$4="","",C4)</f>
         <v>1411006911</v>
       </c>
-      <c r="D36" s="323">
+      <c r="D36" s="318">
         <f t="shared" si="1"/>
         <v>1379201434</v>
       </c>
-      <c r="E36" s="323">
+      <c r="E36" s="318">
         <f t="shared" si="1"/>
         <v>1596926914</v>
       </c>
-      <c r="F36" s="323">
+      <c r="F36" s="318">
         <f t="shared" si="1"/>
         <v>1393260092</v>
       </c>
-      <c r="G36" s="323">
+      <c r="G36" s="318">
         <f t="shared" si="1"/>
         <v>912941814</v>
       </c>
-      <c r="H36" s="323">
+      <c r="H36" s="318">
         <f t="shared" si="1"/>
         <v>680253790</v>
       </c>
-      <c r="I36" s="323">
+      <c r="I36" s="318">
         <f t="shared" si="1"/>
         <v>635842505</v>
       </c>
-      <c r="J36" s="323">
+      <c r="J36" s="318">
         <f t="shared" si="1"/>
         <v>540919477</v>
       </c>
-      <c r="K36" s="323">
+      <c r="K36" s="318">
         <f t="shared" si="1"/>
         <v>375797253</v>
       </c>
-      <c r="L36" s="323">
+      <c r="L36" s="318">
         <f t="shared" si="1"/>
         <v>350212915</v>
       </c>
-      <c r="M36" s="323" t="str">
+      <c r="M36" s="318" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -6878,47 +6894,47 @@
       <c r="B37" s="40" t="s">
         <v>43</v>
       </c>
-      <c r="C37" s="323">
+      <c r="C37" s="318">
         <f t="shared" ref="C37:M37" si="2">IF(C$4="","",-C5)</f>
         <v>-1115025379</v>
       </c>
-      <c r="D37" s="323">
+      <c r="D37" s="318">
         <f t="shared" si="2"/>
         <v>-1033174066</v>
       </c>
-      <c r="E37" s="323">
+      <c r="E37" s="318">
         <f t="shared" si="2"/>
         <v>-1034288683</v>
       </c>
-      <c r="F37" s="323">
+      <c r="F37" s="318">
         <f t="shared" si="2"/>
         <v>-993330987</v>
       </c>
-      <c r="G37" s="323">
+      <c r="G37" s="318">
         <f t="shared" si="2"/>
         <v>-600104422</v>
       </c>
-      <c r="H37" s="323">
+      <c r="H37" s="318">
         <f t="shared" si="2"/>
         <v>-431395603</v>
       </c>
-      <c r="I37" s="323">
+      <c r="I37" s="318">
         <f t="shared" si="2"/>
         <v>-434340576</v>
       </c>
-      <c r="J37" s="323">
+      <c r="J37" s="318">
         <f t="shared" si="2"/>
         <v>-369324839</v>
       </c>
-      <c r="K37" s="323">
+      <c r="K37" s="318">
         <f t="shared" si="2"/>
         <v>-255166042</v>
       </c>
-      <c r="L37" s="323">
+      <c r="L37" s="318">
         <f t="shared" si="2"/>
         <v>-243249284</v>
       </c>
-      <c r="M37" s="323" t="str">
+      <c r="M37" s="318" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
@@ -6927,47 +6943,47 @@
       <c r="B38" s="31" t="s">
         <v>58</v>
       </c>
-      <c r="C38" s="319">
+      <c r="C38" s="317">
         <f>IF(C36="","",C36+C37)</f>
         <v>295981532</v>
       </c>
-      <c r="D38" s="319">
+      <c r="D38" s="317">
         <f t="shared" ref="D38" si="3">IF(D36="","",D36+D37)</f>
         <v>346027368</v>
       </c>
-      <c r="E38" s="319">
+      <c r="E38" s="317">
         <f t="shared" ref="E38" si="4">IF(E36="","",E36+E37)</f>
         <v>562638231</v>
       </c>
-      <c r="F38" s="319">
+      <c r="F38" s="317">
         <f t="shared" ref="F38" si="5">IF(F36="","",F36+F37)</f>
         <v>399929105</v>
       </c>
-      <c r="G38" s="319">
+      <c r="G38" s="317">
         <f t="shared" ref="G38" si="6">IF(G36="","",G36+G37)</f>
         <v>312837392</v>
       </c>
-      <c r="H38" s="319">
+      <c r="H38" s="317">
         <f t="shared" ref="H38" si="7">IF(H36="","",H36+H37)</f>
         <v>248858187</v>
       </c>
-      <c r="I38" s="319">
+      <c r="I38" s="317">
         <f t="shared" ref="I38" si="8">IF(I36="","",I36+I37)</f>
         <v>201501929</v>
       </c>
-      <c r="J38" s="319">
+      <c r="J38" s="317">
         <f t="shared" ref="J38" si="9">IF(J36="","",J36+J37)</f>
         <v>171594638</v>
       </c>
-      <c r="K38" s="319">
+      <c r="K38" s="317">
         <f t="shared" ref="K38" si="10">IF(K36="","",K36+K37)</f>
         <v>120631211</v>
       </c>
-      <c r="L38" s="319">
+      <c r="L38" s="317">
         <f t="shared" ref="L38" si="11">IF(L36="","",L36+L37)</f>
         <v>106963631</v>
       </c>
-      <c r="M38" s="319" t="str">
+      <c r="M38" s="317" t="str">
         <f t="shared" ref="M38" si="12">IF(M36="","",M36+M37)</f>
         <v/>
       </c>
@@ -6976,47 +6992,47 @@
       <c r="B39" s="40" t="s">
         <v>54</v>
       </c>
-      <c r="C39" s="323">
+      <c r="C39" s="318">
         <f t="shared" ref="C39:M39" si="13">IF(C$4="","",-C6)</f>
         <v>-43790640</v>
       </c>
-      <c r="D39" s="323">
+      <c r="D39" s="318">
         <f t="shared" si="13"/>
         <v>-38222426</v>
       </c>
-      <c r="E39" s="323">
+      <c r="E39" s="318">
         <f t="shared" si="13"/>
         <v>-41394520</v>
       </c>
-      <c r="F39" s="323">
+      <c r="F39" s="318">
         <f t="shared" si="13"/>
         <v>-35854036</v>
       </c>
-      <c r="G39" s="323">
+      <c r="G39" s="318">
         <f t="shared" si="13"/>
         <v>-28188973</v>
       </c>
-      <c r="H39" s="323">
+      <c r="H39" s="318">
         <f t="shared" si="13"/>
         <v>-22486501</v>
       </c>
-      <c r="I39" s="323">
+      <c r="I39" s="318">
         <f t="shared" si="13"/>
         <v>-21263075</v>
       </c>
-      <c r="J39" s="323">
+      <c r="J39" s="318">
         <f t="shared" si="13"/>
         <v>-61524619</v>
       </c>
-      <c r="K39" s="323">
+      <c r="K39" s="318">
         <f t="shared" si="13"/>
         <v>-44726842</v>
       </c>
-      <c r="L39" s="323">
+      <c r="L39" s="318">
         <f t="shared" si="13"/>
         <v>-33204787</v>
       </c>
-      <c r="M39" s="323" t="str">
+      <c r="M39" s="318" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
@@ -7025,47 +7041,47 @@
       <c r="B40" s="69" t="s">
         <v>61</v>
       </c>
-      <c r="C40" s="333">
+      <c r="C40" s="320">
         <f t="shared" ref="C40:M40" si="14">IF(C$4="","",-C7)</f>
         <v>-10699910</v>
       </c>
-      <c r="D40" s="333">
+      <c r="D40" s="320">
         <f t="shared" si="14"/>
         <v>-8156496</v>
       </c>
-      <c r="E40" s="333">
+      <c r="E40" s="320">
         <f t="shared" si="14"/>
         <v>-8760304</v>
       </c>
-      <c r="F40" s="333">
+      <c r="F40" s="320">
         <f t="shared" si="14"/>
         <v>-6582094</v>
       </c>
-      <c r="G40" s="333">
+      <c r="G40" s="320">
         <f t="shared" si="14"/>
         <v>-6591833</v>
       </c>
-      <c r="H40" s="333">
+      <c r="H40" s="320">
         <f t="shared" si="14"/>
         <v>-28503017</v>
       </c>
-      <c r="I40" s="333">
+      <c r="I40" s="320">
         <f t="shared" si="14"/>
         <v>-27458819</v>
       </c>
-      <c r="J40" s="333">
+      <c r="J40" s="320">
         <f t="shared" si="14"/>
         <v>-20907812</v>
       </c>
-      <c r="K40" s="333">
+      <c r="K40" s="320">
         <f t="shared" si="14"/>
         <v>-15460659</v>
       </c>
-      <c r="L40" s="333">
+      <c r="L40" s="320">
         <f t="shared" si="14"/>
         <v>-11888598</v>
       </c>
-      <c r="M40" s="333" t="str">
+      <c r="M40" s="320" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
@@ -7074,47 +7090,47 @@
       <c r="B41" s="69" t="s">
         <v>64</v>
       </c>
-      <c r="C41" s="333">
+      <c r="C41" s="320">
         <f>IF(C$4="","",C39-C40)</f>
         <v>-33090730</v>
       </c>
-      <c r="D41" s="333">
+      <c r="D41" s="320">
         <f t="shared" ref="D41:M41" si="15">IF(D$4="","",D39-D40)</f>
         <v>-30065930</v>
       </c>
-      <c r="E41" s="333">
+      <c r="E41" s="320">
         <f t="shared" si="15"/>
         <v>-32634216</v>
       </c>
-      <c r="F41" s="333">
+      <c r="F41" s="320">
         <f t="shared" si="15"/>
         <v>-29271942</v>
       </c>
-      <c r="G41" s="333">
+      <c r="G41" s="320">
         <f t="shared" si="15"/>
         <v>-21597140</v>
       </c>
-      <c r="H41" s="333">
+      <c r="H41" s="320">
         <f t="shared" si="15"/>
         <v>6016516</v>
       </c>
-      <c r="I41" s="333">
+      <c r="I41" s="320">
         <f t="shared" si="15"/>
         <v>6195744</v>
       </c>
-      <c r="J41" s="333">
+      <c r="J41" s="320">
         <f t="shared" si="15"/>
         <v>-40616807</v>
       </c>
-      <c r="K41" s="333">
+      <c r="K41" s="320">
         <f t="shared" si="15"/>
         <v>-29266183</v>
       </c>
-      <c r="L41" s="333">
+      <c r="L41" s="320">
         <f t="shared" si="15"/>
         <v>-21316189</v>
       </c>
-      <c r="M41" s="333" t="str">
+      <c r="M41" s="320" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
@@ -7123,47 +7139,47 @@
       <c r="B42" s="40" t="s">
         <v>49</v>
       </c>
-      <c r="C42" s="323">
+      <c r="C42" s="318">
         <f t="shared" ref="C42:M42" si="16">IF(C$4="","",-C8)</f>
         <v>-77948987</v>
       </c>
-      <c r="D42" s="323">
+      <c r="D42" s="318">
         <f t="shared" si="16"/>
         <v>-79192247</v>
       </c>
-      <c r="E42" s="323">
+      <c r="E42" s="318">
         <f t="shared" si="16"/>
         <v>-74126277</v>
       </c>
-      <c r="F42" s="323">
+      <c r="F42" s="318">
         <f t="shared" si="16"/>
         <v>-79595413</v>
       </c>
-      <c r="G42" s="323">
+      <c r="G42" s="318">
         <f t="shared" si="16"/>
         <v>-69723237</v>
       </c>
-      <c r="H42" s="323">
+      <c r="H42" s="318">
         <f t="shared" si="16"/>
         <v>-50161359</v>
       </c>
-      <c r="I42" s="323">
+      <c r="I42" s="318">
         <f t="shared" si="16"/>
         <v>-52954564</v>
       </c>
-      <c r="J42" s="323">
+      <c r="J42" s="318">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="K42" s="323">
+      <c r="K42" s="318">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="L42" s="323">
+      <c r="L42" s="318">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="M42" s="323" t="str">
+      <c r="M42" s="318" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
@@ -7172,47 +7188,47 @@
       <c r="B43" s="43" t="s">
         <v>153</v>
       </c>
-      <c r="C43" s="324">
+      <c r="C43" s="319">
         <f>IF(C$4="","",C38+C39+C42)</f>
         <v>174241905</v>
       </c>
-      <c r="D43" s="324">
+      <c r="D43" s="319">
         <f t="shared" ref="D43:M43" si="17">IF(D$4="","",D38+D39+D42)</f>
         <v>228612695</v>
       </c>
-      <c r="E43" s="324">
+      <c r="E43" s="319">
         <f t="shared" si="17"/>
         <v>447117434</v>
       </c>
-      <c r="F43" s="324">
+      <c r="F43" s="319">
         <f t="shared" si="17"/>
         <v>284479656</v>
       </c>
-      <c r="G43" s="324">
+      <c r="G43" s="319">
         <f t="shared" si="17"/>
         <v>214925182</v>
       </c>
-      <c r="H43" s="324">
+      <c r="H43" s="319">
         <f t="shared" si="17"/>
         <v>176210327</v>
       </c>
-      <c r="I43" s="324">
+      <c r="I43" s="319">
         <f t="shared" si="17"/>
         <v>127284290</v>
       </c>
-      <c r="J43" s="324">
+      <c r="J43" s="319">
         <f t="shared" si="17"/>
         <v>110070019</v>
       </c>
-      <c r="K43" s="324">
+      <c r="K43" s="319">
         <f t="shared" si="17"/>
         <v>75904369</v>
       </c>
-      <c r="L43" s="324">
+      <c r="L43" s="319">
         <f t="shared" si="17"/>
         <v>73758844</v>
       </c>
-      <c r="M43" s="324" t="str">
+      <c r="M43" s="319" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
@@ -7319,47 +7335,47 @@
       <c r="B46" s="40" t="s">
         <v>50</v>
       </c>
-      <c r="C46" s="323">
+      <c r="C46" s="318">
         <f t="shared" ref="C46:M46" si="20">IF(C$4="","",-C14)</f>
         <v>-28257995</v>
       </c>
-      <c r="D46" s="323">
+      <c r="D46" s="318">
         <f t="shared" si="20"/>
         <v>-29716699</v>
       </c>
-      <c r="E46" s="323">
+      <c r="E46" s="318">
         <f t="shared" si="20"/>
         <v>-60986391</v>
       </c>
-      <c r="F46" s="323">
+      <c r="F46" s="318">
         <f t="shared" si="20"/>
         <v>-37814748</v>
       </c>
-      <c r="G46" s="323">
+      <c r="G46" s="318">
         <f t="shared" si="20"/>
         <v>-30587751</v>
       </c>
-      <c r="H46" s="323">
+      <c r="H46" s="318">
         <f t="shared" si="20"/>
         <v>-21993559</v>
       </c>
-      <c r="I46" s="323">
+      <c r="I46" s="318">
         <f t="shared" si="20"/>
         <v>-16485438</v>
       </c>
-      <c r="J46" s="323">
+      <c r="J46" s="318">
         <f t="shared" si="20"/>
         <v>-11657792</v>
       </c>
-      <c r="K46" s="323">
+      <c r="K46" s="318">
         <f t="shared" si="20"/>
         <v>-10793741</v>
       </c>
-      <c r="L46" s="323">
+      <c r="L46" s="318">
         <f t="shared" si="20"/>
         <v>-10094751</v>
       </c>
-      <c r="M46" s="323" t="str">
+      <c r="M46" s="318" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
@@ -7368,47 +7384,47 @@
       <c r="B47" s="43" t="s">
         <v>42</v>
       </c>
-      <c r="C47" s="324">
+      <c r="C47" s="319">
         <f t="shared" ref="C47:M47" si="21">IF(C$4="","",C15)</f>
         <v>191530184</v>
       </c>
-      <c r="D47" s="324">
+      <c r="D47" s="319">
         <f t="shared" si="21"/>
         <v>235079089</v>
       </c>
-      <c r="E47" s="324">
+      <c r="E47" s="319">
         <f t="shared" si="21"/>
         <v>422201840</v>
       </c>
-      <c r="F47" s="324">
+      <c r="F47" s="319">
         <f t="shared" si="21"/>
         <v>252389575</v>
       </c>
-      <c r="G47" s="324">
+      <c r="G47" s="319">
         <f t="shared" si="21"/>
         <v>178651261</v>
       </c>
-      <c r="H47" s="324">
+      <c r="H47" s="319">
         <f t="shared" si="21"/>
         <v>144720474</v>
       </c>
-      <c r="I47" s="324">
+      <c r="I47" s="319">
         <f t="shared" si="21"/>
         <v>105746340</v>
       </c>
-      <c r="J47" s="324">
+      <c r="J47" s="319">
         <f t="shared" si="21"/>
         <v>73606124</v>
       </c>
-      <c r="K47" s="324">
+      <c r="K47" s="319">
         <f t="shared" si="21"/>
         <v>64586099</v>
       </c>
-      <c r="L47" s="324">
+      <c r="L47" s="319">
         <f t="shared" si="21"/>
         <v>57489604</v>
       </c>
-      <c r="M47" s="324" t="str">
+      <c r="M47" s="319" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
@@ -7417,47 +7433,47 @@
       <c r="B48" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="C48" s="323">
+      <c r="C48" s="318">
         <f t="shared" ref="C48:M48" si="22">IF(C$4="","",MIN(-C16,0))</f>
         <v>0</v>
       </c>
-      <c r="D48" s="323">
+      <c r="D48" s="318">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="E48" s="323">
+      <c r="E48" s="318">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="F48" s="323">
+      <c r="F48" s="318">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="G48" s="323">
+      <c r="G48" s="318">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="H48" s="323">
+      <c r="H48" s="318">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="I48" s="323">
+      <c r="I48" s="318">
         <f t="shared" si="22"/>
         <v>-126598</v>
       </c>
-      <c r="J48" s="323">
+      <c r="J48" s="318">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="K48" s="323">
+      <c r="K48" s="318">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="L48" s="323">
+      <c r="L48" s="318">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="M48" s="323" t="str">
+      <c r="M48" s="318" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
@@ -7471,47 +7487,47 @@
       <c r="B51" s="40" t="s">
         <v>39</v>
       </c>
-      <c r="C51" s="323">
+      <c r="C51" s="318">
         <f t="shared" ref="C51:M51" si="23">IF(C$4="","",-C12)</f>
         <v>-5219951</v>
       </c>
-      <c r="D51" s="323">
+      <c r="D51" s="318">
         <f t="shared" si="23"/>
         <v>-8074436</v>
       </c>
-      <c r="E51" s="323">
+      <c r="E51" s="318">
         <f t="shared" si="23"/>
         <v>-4999986</v>
       </c>
-      <c r="F51" s="323">
+      <c r="F51" s="318">
         <f t="shared" si="23"/>
         <v>-32946</v>
       </c>
-      <c r="G51" s="323">
+      <c r="G51" s="318">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="H51" s="323">
+      <c r="H51" s="318">
         <f t="shared" si="23"/>
         <v>-1902780</v>
       </c>
-      <c r="I51" s="323">
+      <c r="I51" s="318">
         <f t="shared" si="23"/>
         <v>-3158441</v>
       </c>
-      <c r="J51" s="323">
+      <c r="J51" s="318">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="K51" s="323">
+      <c r="K51" s="318">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="L51" s="323">
+      <c r="L51" s="318">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="M51" s="323" t="str">
+      <c r="M51" s="318" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
@@ -7520,47 +7536,47 @@
       <c r="B52" s="40" t="s">
         <v>67</v>
       </c>
-      <c r="C52" s="323">
+      <c r="C52" s="318">
         <f t="shared" ref="C52:M52" si="24">IF(C$4="","",C13)</f>
         <v>30422495</v>
       </c>
-      <c r="D52" s="323">
+      <c r="D52" s="318">
         <f t="shared" si="24"/>
         <v>14354714</v>
       </c>
-      <c r="E52" s="323">
+      <c r="E52" s="318">
         <f t="shared" si="24"/>
         <v>2142657</v>
       </c>
-      <c r="F52" s="323">
+      <c r="F52" s="318">
         <f t="shared" si="24"/>
         <v>2175704</v>
       </c>
-      <c r="G52" s="323">
+      <c r="G52" s="318">
         <f t="shared" si="24"/>
         <v>2045796</v>
       </c>
-      <c r="H52" s="323">
+      <c r="H52" s="318">
         <f t="shared" si="24"/>
         <v>5422489</v>
       </c>
-      <c r="I52" s="323">
+      <c r="I52" s="318">
         <f t="shared" si="24"/>
         <v>3339969</v>
       </c>
-      <c r="J52" s="323">
+      <c r="J52" s="318">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="K52" s="323">
+      <c r="K52" s="318">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="L52" s="323">
+      <c r="L52" s="318">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="M52" s="323" t="str">
+      <c r="M52" s="318" t="str">
         <f t="shared" si="24"/>
         <v/>
       </c>
@@ -7776,47 +7792,47 @@
       <c r="B61" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="C61" s="323">
+      <c r="C61" s="318">
         <f>IF(C$4="","",-C19)</f>
         <v>-61093655</v>
       </c>
-      <c r="D61" s="323">
+      <c r="D61" s="318">
         <f t="shared" ref="D61:M61" si="29">IF(D$4="","",-D19)</f>
         <v>-58833476</v>
       </c>
-      <c r="E61" s="323">
+      <c r="E61" s="318">
         <f t="shared" si="29"/>
         <v>-54349703</v>
       </c>
-      <c r="F61" s="323">
+      <c r="F61" s="318">
         <f t="shared" si="29"/>
         <v>-41876368</v>
       </c>
-      <c r="G61" s="323">
+      <c r="G61" s="318">
         <f t="shared" si="29"/>
         <v>-32578395</v>
       </c>
-      <c r="H61" s="323">
+      <c r="H61" s="318">
         <f t="shared" si="29"/>
         <v>-25986482</v>
       </c>
-      <c r="I61" s="323">
+      <c r="I61" s="318">
         <f t="shared" si="29"/>
         <v>-19020963</v>
       </c>
-      <c r="J61" s="323">
+      <c r="J61" s="318">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="K61" s="323">
+      <c r="K61" s="318">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="L61" s="323">
+      <c r="L61" s="318">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="M61" s="323" t="str">
+      <c r="M61" s="318" t="str">
         <f t="shared" si="29"/>
         <v/>
       </c>
@@ -7825,47 +7841,47 @@
       <c r="B62" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="C62" s="323">
+      <c r="C62" s="318">
         <f>IF(C$4="","",IF(C20=0,C61,-C20))</f>
         <v>-61093655</v>
       </c>
-      <c r="D62" s="323">
+      <c r="D62" s="318">
         <f t="shared" ref="D62:M62" si="30">IF(D$4="","",IF(D20=0,D61,-D20))</f>
         <v>-58833476</v>
       </c>
-      <c r="E62" s="323">
+      <c r="E62" s="318">
         <f t="shared" si="30"/>
         <v>-54349703</v>
       </c>
-      <c r="F62" s="323">
+      <c r="F62" s="318">
         <f t="shared" si="30"/>
         <v>-41876368</v>
       </c>
-      <c r="G62" s="323">
+      <c r="G62" s="318">
         <f t="shared" si="30"/>
         <v>-32578395</v>
       </c>
-      <c r="H62" s="323">
+      <c r="H62" s="318">
         <f t="shared" si="30"/>
         <v>-25986482</v>
       </c>
-      <c r="I62" s="323">
+      <c r="I62" s="318">
         <f t="shared" si="30"/>
         <v>-19020963</v>
       </c>
-      <c r="J62" s="323">
+      <c r="J62" s="318">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="K62" s="323">
+      <c r="K62" s="318">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="L62" s="323">
+      <c r="L62" s="318">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="M62" s="323" t="str">
+      <c r="M62" s="318" t="str">
         <f t="shared" si="30"/>
         <v/>
       </c>
@@ -7874,47 +7890,47 @@
       <c r="B63" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="C63" s="323">
+      <c r="C63" s="318">
         <f>IF(C$4="","",-C21)</f>
         <v>0</v>
       </c>
-      <c r="D63" s="323">
+      <c r="D63" s="318">
         <f t="shared" ref="D63:M63" si="31">IF(D$4="","",-D21)</f>
         <v>0</v>
       </c>
-      <c r="E63" s="323">
+      <c r="E63" s="318">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="F63" s="323">
+      <c r="F63" s="318">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="G63" s="323">
+      <c r="G63" s="318">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="H63" s="323">
+      <c r="H63" s="318">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="I63" s="323">
+      <c r="I63" s="318">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="J63" s="323">
+      <c r="J63" s="318">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="K63" s="323">
+      <c r="K63" s="318">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="L63" s="323">
+      <c r="L63" s="318">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="M63" s="323" t="str">
+      <c r="M63" s="318" t="str">
         <f t="shared" si="31"/>
         <v/>
       </c>
@@ -7923,47 +7939,47 @@
       <c r="B64" s="27" t="s">
         <v>394</v>
       </c>
-      <c r="C64" s="323">
+      <c r="C64" s="318">
         <f>IF(C$4="","",C22+C23+C24)</f>
         <v>53606711</v>
       </c>
-      <c r="D64" s="323">
+      <c r="D64" s="318">
         <f t="shared" ref="D64:M64" si="32">IF(D$4="","",D22+D23+D24)</f>
         <v>-54463889</v>
       </c>
-      <c r="E64" s="323">
+      <c r="E64" s="318">
         <f t="shared" si="32"/>
         <v>14881802</v>
       </c>
-      <c r="F64" s="323">
+      <c r="F64" s="318">
         <f t="shared" si="32"/>
         <v>19577879</v>
       </c>
-      <c r="G64" s="323">
+      <c r="G64" s="318">
         <f t="shared" si="32"/>
         <v>-26973867</v>
       </c>
-      <c r="H64" s="323">
+      <c r="H64" s="318">
         <f t="shared" si="32"/>
         <v>-2648834</v>
       </c>
-      <c r="I64" s="323">
+      <c r="I64" s="318">
         <f t="shared" si="32"/>
         <v>84491501</v>
       </c>
-      <c r="J64" s="323">
+      <c r="J64" s="318">
         <f t="shared" si="32"/>
         <v>58303557</v>
       </c>
-      <c r="K64" s="323">
+      <c r="K64" s="318">
         <f t="shared" si="32"/>
         <v>57142825</v>
       </c>
-      <c r="L64" s="323">
+      <c r="L64" s="318">
         <f t="shared" si="32"/>
         <v>23654038</v>
       </c>
-      <c r="M64" s="323" t="str">
+      <c r="M64" s="318" t="str">
         <f t="shared" si="32"/>
         <v/>
       </c>
@@ -8345,115 +8361,115 @@
       <c r="B77" s="93" t="s">
         <v>86</v>
       </c>
-      <c r="C77" s="333">
+      <c r="C77" s="320">
         <f t="shared" ref="C77:H78" si="40">IF(C$4="","",C28)</f>
         <v>435508276.29999995</v>
       </c>
-      <c r="D77" s="333">
+      <c r="D77" s="320">
         <f t="shared" si="40"/>
         <v>286539091</v>
       </c>
-      <c r="E77" s="333">
+      <c r="E77" s="320">
         <f t="shared" si="40"/>
         <v>273013471</v>
       </c>
-      <c r="F77" s="333">
+      <c r="F77" s="320">
         <f t="shared" si="40"/>
         <v>232578044</v>
       </c>
-      <c r="G77" s="333">
+      <c r="G77" s="320">
         <f t="shared" si="40"/>
         <v>139788443</v>
       </c>
-      <c r="H77" s="333">
+      <c r="H77" s="320">
         <f t="shared" si="40"/>
         <v>109488661</v>
       </c>
-      <c r="I77" s="337"/>
-      <c r="J77" s="337"/>
-      <c r="K77" s="337"/>
-      <c r="L77" s="337"/>
-      <c r="M77" s="337"/>
+      <c r="I77" s="324"/>
+      <c r="J77" s="324"/>
+      <c r="K77" s="324"/>
+      <c r="L77" s="324"/>
+      <c r="M77" s="324"/>
     </row>
     <row r="78" spans="2:13">
       <c r="B78" s="93" t="s">
         <v>87</v>
       </c>
-      <c r="C78" s="333">
+      <c r="C78" s="320">
         <f t="shared" si="40"/>
         <v>149619822.47999999</v>
       </c>
-      <c r="D78" s="333">
+      <c r="D78" s="320">
         <f t="shared" si="40"/>
         <v>175557090</v>
       </c>
-      <c r="E78" s="333">
+      <c r="E78" s="320">
         <f t="shared" si="40"/>
         <v>221536955</v>
       </c>
-      <c r="F78" s="333">
+      <c r="F78" s="320">
         <f t="shared" si="40"/>
         <v>134930930</v>
       </c>
-      <c r="G78" s="333">
+      <c r="G78" s="320">
         <f t="shared" si="40"/>
         <v>102812384</v>
       </c>
-      <c r="H78" s="333">
+      <c r="H78" s="320">
         <f t="shared" si="40"/>
         <v>54993674</v>
       </c>
-      <c r="I78" s="337"/>
-      <c r="J78" s="337"/>
-      <c r="K78" s="337"/>
-      <c r="L78" s="337"/>
-      <c r="M78" s="337"/>
+      <c r="I78" s="324"/>
+      <c r="J78" s="324"/>
+      <c r="K78" s="324"/>
+      <c r="L78" s="324"/>
+      <c r="M78" s="324"/>
     </row>
     <row r="79" spans="2:13">
       <c r="B79" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="C79" s="323">
+      <c r="C79" s="318">
         <f t="shared" ref="C79:M79" si="41">IF(C$4="","",C30)</f>
         <v>401550924.92000002</v>
       </c>
-      <c r="D79" s="323">
+      <c r="D79" s="318">
         <f t="shared" si="41"/>
         <v>375837168</v>
       </c>
-      <c r="E79" s="323">
+      <c r="E79" s="318">
         <f t="shared" si="41"/>
         <v>484715813</v>
       </c>
-      <c r="F79" s="323">
+      <c r="F79" s="318">
         <f t="shared" si="41"/>
         <v>120473425</v>
       </c>
-      <c r="G79" s="323">
+      <c r="G79" s="318">
         <f t="shared" si="41"/>
         <v>77386991</v>
       </c>
-      <c r="H79" s="323">
+      <c r="H79" s="318">
         <f t="shared" si="41"/>
         <v>107878390</v>
       </c>
-      <c r="I79" s="323">
+      <c r="I79" s="318">
         <f t="shared" si="41"/>
         <v>144733614</v>
       </c>
-      <c r="J79" s="323">
+      <c r="J79" s="318">
         <f t="shared" si="41"/>
         <v>117054123</v>
       </c>
-      <c r="K79" s="323">
+      <c r="K79" s="318">
         <f t="shared" si="41"/>
         <v>64103116</v>
       </c>
-      <c r="L79" s="323">
+      <c r="L79" s="318">
         <f t="shared" si="41"/>
         <v>30979762</v>
       </c>
-      <c r="M79" s="323" t="str">
+      <c r="M79" s="318" t="str">
         <f t="shared" si="41"/>
         <v/>
       </c>
@@ -8462,47 +8478,47 @@
       <c r="B80" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="C80" s="323">
+      <c r="C80" s="318">
         <f t="shared" ref="C80:M80" si="42">IF(C$4="","",C31)</f>
         <v>2411580473.29</v>
       </c>
-      <c r="D80" s="323">
+      <c r="D80" s="318">
         <f t="shared" si="42"/>
         <v>2445882003</v>
       </c>
-      <c r="E80" s="323">
+      <c r="E80" s="318">
         <f t="shared" si="42"/>
         <v>2319825981</v>
       </c>
-      <c r="F80" s="323">
+      <c r="F80" s="318">
         <f t="shared" si="42"/>
         <v>1994747908</v>
       </c>
-      <c r="G80" s="323">
+      <c r="G80" s="318">
         <f t="shared" si="42"/>
         <v>1001406127</v>
       </c>
-      <c r="H80" s="323">
+      <c r="H80" s="318">
         <f t="shared" si="42"/>
         <v>868539655</v>
       </c>
-      <c r="I80" s="323">
+      <c r="I80" s="318">
         <f t="shared" si="42"/>
         <v>768786181</v>
       </c>
-      <c r="J80" s="323">
+      <c r="J80" s="318">
         <f t="shared" si="42"/>
         <v>515701210</v>
       </c>
-      <c r="K80" s="323">
+      <c r="K80" s="318">
         <f t="shared" si="42"/>
         <v>457812342</v>
       </c>
-      <c r="L80" s="323">
+      <c r="L80" s="318">
         <f t="shared" si="42"/>
         <v>432312719</v>
       </c>
-      <c r="M80" s="323" t="str">
+      <c r="M80" s="318" t="str">
         <f t="shared" si="42"/>
         <v/>
       </c>
@@ -9585,11 +9601,11 @@
       <c r="B73" s="105" t="s">
         <v>318</v>
       </c>
-      <c r="C73" s="76">
+      <c r="C73" s="355">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
         <v>-112792265.10000001</v>
       </c>
-      <c r="D73" s="76">
+      <c r="D73" s="355">
         <f>(Normalized_FCF!C25+Normalized_FCF!C35-Normalized_FCF!C91)/12</f>
         <v>-112772827.10000001</v>
       </c>
@@ -9617,8 +9633,8 @@
       <c r="B75" s="80" t="s">
         <v>321</v>
       </c>
-      <c r="C75" s="341"/>
-      <c r="D75" s="342">
+      <c r="C75" s="326"/>
+      <c r="D75" s="327">
         <f>MAX(-D73*D76,G5)</f>
         <v>225545654.20000002</v>
       </c>
@@ -9922,54 +9938,54 @@
       <c r="B4" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="317">
+      <c r="C4" s="333">
         <f>G4</f>
         <v>1411006911</v>
       </c>
       <c r="D4" s="57"/>
       <c r="E4" s="266"/>
       <c r="F4" s="57"/>
-      <c r="G4" s="323">
+      <c r="G4" s="339">
         <f>Data!C36</f>
         <v>1411006911</v>
       </c>
-      <c r="H4" s="323">
+      <c r="H4" s="339">
         <f>Data!D36</f>
         <v>1379201434</v>
       </c>
-      <c r="I4" s="323">
+      <c r="I4" s="339">
         <f>Data!E36</f>
         <v>1596926914</v>
       </c>
-      <c r="J4" s="323">
+      <c r="J4" s="339">
         <f>Data!F36</f>
         <v>1393260092</v>
       </c>
-      <c r="K4" s="323">
+      <c r="K4" s="339">
         <f>Data!G36</f>
         <v>912941814</v>
       </c>
-      <c r="L4" s="323">
+      <c r="L4" s="339">
         <f>Data!H36</f>
         <v>680253790</v>
       </c>
-      <c r="M4" s="323">
+      <c r="M4" s="339">
         <f>Data!I36</f>
         <v>635842505</v>
       </c>
-      <c r="N4" s="323">
+      <c r="N4" s="339">
         <f>Data!J36</f>
         <v>540919477</v>
       </c>
-      <c r="O4" s="323">
+      <c r="O4" s="339">
         <f>Data!K36</f>
         <v>375797253</v>
       </c>
-      <c r="P4" s="323">
+      <c r="P4" s="339">
         <f>Data!L36</f>
         <v>350212915</v>
       </c>
-      <c r="Q4" s="323" t="str">
+      <c r="Q4" s="339" t="str">
         <f>Data!M36</f>
         <v/>
       </c>
@@ -9979,52 +9995,52 @@
       <c r="B5" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C5" s="318">
+      <c r="C5" s="334">
         <f>C25</f>
         <v>-1125725289</v>
       </c>
       <c r="E5" s="268"/>
-      <c r="G5" s="323">
+      <c r="G5" s="339">
         <f t="shared" ref="G5:Q5" si="1">G25</f>
         <v>-1125725289</v>
       </c>
-      <c r="H5" s="323">
+      <c r="H5" s="339">
         <f t="shared" si="1"/>
         <v>-1041330562</v>
       </c>
-      <c r="I5" s="323">
+      <c r="I5" s="339">
         <f t="shared" si="1"/>
         <v>-1043048987</v>
       </c>
-      <c r="J5" s="323">
+      <c r="J5" s="339">
         <f t="shared" si="1"/>
         <v>-999913081</v>
       </c>
-      <c r="K5" s="323">
+      <c r="K5" s="339">
         <f t="shared" si="1"/>
         <v>-606696255</v>
       </c>
-      <c r="L5" s="323">
+      <c r="L5" s="339">
         <f t="shared" si="1"/>
         <v>-459898620</v>
       </c>
-      <c r="M5" s="323">
+      <c r="M5" s="339">
         <f t="shared" si="1"/>
         <v>-461799395</v>
       </c>
-      <c r="N5" s="323">
+      <c r="N5" s="339">
         <f t="shared" si="1"/>
         <v>-390232651</v>
       </c>
-      <c r="O5" s="323">
+      <c r="O5" s="339">
         <f t="shared" si="1"/>
         <v>-270626701</v>
       </c>
-      <c r="P5" s="323">
+      <c r="P5" s="339">
         <f t="shared" si="1"/>
         <v>-255137882</v>
       </c>
-      <c r="Q5" s="323" t="str">
+      <c r="Q5" s="339" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -10034,52 +10050,52 @@
       <c r="B6" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="C6" s="319">
+      <c r="C6" s="335">
         <f>C4+C5</f>
         <v>285281622</v>
       </c>
       <c r="E6" s="268"/>
-      <c r="G6" s="319">
+      <c r="G6" s="335">
         <f>IF(G4="","",G4+G5)</f>
         <v>285281622</v>
       </c>
-      <c r="H6" s="319">
+      <c r="H6" s="335">
         <f t="shared" ref="H6:Q6" si="2">IF(H4="","",H4+H5)</f>
         <v>337870872</v>
       </c>
-      <c r="I6" s="319">
+      <c r="I6" s="335">
         <f t="shared" si="2"/>
         <v>553877927</v>
       </c>
-      <c r="J6" s="319">
+      <c r="J6" s="335">
         <f t="shared" si="2"/>
         <v>393347011</v>
       </c>
-      <c r="K6" s="319">
+      <c r="K6" s="335">
         <f t="shared" si="2"/>
         <v>306245559</v>
       </c>
-      <c r="L6" s="319">
+      <c r="L6" s="335">
         <f t="shared" si="2"/>
         <v>220355170</v>
       </c>
-      <c r="M6" s="319">
+      <c r="M6" s="335">
         <f t="shared" si="2"/>
         <v>174043110</v>
       </c>
-      <c r="N6" s="319">
+      <c r="N6" s="335">
         <f t="shared" si="2"/>
         <v>150686826</v>
       </c>
-      <c r="O6" s="319">
+      <c r="O6" s="335">
         <f t="shared" si="2"/>
         <v>105170552</v>
       </c>
-      <c r="P6" s="319">
+      <c r="P6" s="335">
         <f t="shared" si="2"/>
         <v>95075033</v>
       </c>
-      <c r="Q6" s="319" t="str">
+      <c r="Q6" s="335" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
@@ -10089,52 +10105,52 @@
       <c r="B7" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="C7" s="318">
+      <c r="C7" s="334">
         <f>C35</f>
         <v>-110806461</v>
       </c>
       <c r="E7" s="268"/>
-      <c r="G7" s="318">
+      <c r="G7" s="334">
         <f t="shared" ref="G7:Q7" si="3">G35</f>
         <v>-111039717</v>
       </c>
-      <c r="H7" s="318">
+      <c r="H7" s="334">
         <f t="shared" si="3"/>
         <v>-109258177</v>
       </c>
-      <c r="I7" s="318">
+      <c r="I7" s="334">
         <f t="shared" si="3"/>
         <v>-106760493</v>
       </c>
-      <c r="J7" s="318">
+      <c r="J7" s="334">
         <f t="shared" si="3"/>
         <v>-108867355</v>
       </c>
-      <c r="K7" s="318">
+      <c r="K7" s="334">
         <f t="shared" si="3"/>
         <v>-91320377</v>
       </c>
-      <c r="L7" s="318">
+      <c r="L7" s="334">
         <f t="shared" si="3"/>
         <v>-44144843</v>
       </c>
-      <c r="M7" s="318">
+      <c r="M7" s="334">
         <f t="shared" si="3"/>
         <v>-46758820</v>
       </c>
-      <c r="N7" s="318">
+      <c r="N7" s="334">
         <f t="shared" si="3"/>
         <v>-40616807</v>
       </c>
-      <c r="O7" s="318">
+      <c r="O7" s="334">
         <f t="shared" si="3"/>
         <v>-29266183</v>
       </c>
-      <c r="P7" s="318">
+      <c r="P7" s="334">
         <f t="shared" si="3"/>
         <v>-21316189</v>
       </c>
-      <c r="Q7" s="318" t="str">
+      <c r="Q7" s="334" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -10144,54 +10160,54 @@
       <c r="B8" s="29" t="s">
         <v>153</v>
       </c>
-      <c r="C8" s="320">
+      <c r="C8" s="336">
         <f>C6+C7</f>
         <v>174475161</v>
       </c>
       <c r="D8" s="59"/>
       <c r="E8" s="274"/>
       <c r="F8" s="59"/>
-      <c r="G8" s="319">
+      <c r="G8" s="335">
         <f>IF(G$4="","",G6+G7)</f>
         <v>174241905</v>
       </c>
-      <c r="H8" s="319">
+      <c r="H8" s="335">
         <f t="shared" ref="H8:Q8" si="4">IF(H$4="","",H6+H7)</f>
         <v>228612695</v>
       </c>
-      <c r="I8" s="319">
+      <c r="I8" s="335">
         <f t="shared" si="4"/>
         <v>447117434</v>
       </c>
-      <c r="J8" s="319">
+      <c r="J8" s="335">
         <f t="shared" si="4"/>
         <v>284479656</v>
       </c>
-      <c r="K8" s="319">
+      <c r="K8" s="335">
         <f t="shared" si="4"/>
         <v>214925182</v>
       </c>
-      <c r="L8" s="319">
+      <c r="L8" s="335">
         <f t="shared" si="4"/>
         <v>176210327</v>
       </c>
-      <c r="M8" s="319">
+      <c r="M8" s="335">
         <f t="shared" si="4"/>
         <v>127284290</v>
       </c>
-      <c r="N8" s="319">
+      <c r="N8" s="335">
         <f t="shared" si="4"/>
         <v>110070019</v>
       </c>
-      <c r="O8" s="319">
+      <c r="O8" s="335">
         <f t="shared" si="4"/>
         <v>75904369</v>
       </c>
-      <c r="P8" s="319">
+      <c r="P8" s="335">
         <f t="shared" si="4"/>
         <v>73758844</v>
       </c>
-      <c r="Q8" s="319" t="str">
+      <c r="Q8" s="335" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
@@ -10201,52 +10217,52 @@
       <c r="B9" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C9" s="318">
+      <c r="C9" s="334">
         <f>BS!$G$39*BS!D58</f>
         <v>61093655</v>
       </c>
       <c r="E9" s="268"/>
-      <c r="G9" s="318">
+      <c r="G9" s="334">
         <f>IF(Data!C61="","",-Data!C61)</f>
         <v>61093655</v>
       </c>
-      <c r="H9" s="318">
+      <c r="H9" s="334">
         <f>IF(Data!D61="","",-Data!D61)</f>
         <v>58833476</v>
       </c>
-      <c r="I9" s="318">
+      <c r="I9" s="334">
         <f>IF(Data!E61="","",-Data!E61)</f>
         <v>54349703</v>
       </c>
-      <c r="J9" s="318">
+      <c r="J9" s="334">
         <f>IF(Data!F61="","",-Data!F61)</f>
         <v>41876368</v>
       </c>
-      <c r="K9" s="318">
+      <c r="K9" s="334">
         <f>IF(Data!G61="","",-Data!G61)</f>
         <v>32578395</v>
       </c>
-      <c r="L9" s="318">
+      <c r="L9" s="334">
         <f>IF(Data!H61="","",-Data!H61)</f>
         <v>25986482</v>
       </c>
-      <c r="M9" s="318">
+      <c r="M9" s="334">
         <f>IF(Data!I61="","",-Data!I61)</f>
         <v>19020963</v>
       </c>
-      <c r="N9" s="318">
+      <c r="N9" s="334">
         <f>IF(Data!J61="","",-Data!J61)</f>
         <v>0</v>
       </c>
-      <c r="O9" s="318">
+      <c r="O9" s="334">
         <f>IF(Data!K61="","",-Data!K61)</f>
         <v>0</v>
       </c>
-      <c r="P9" s="318">
+      <c r="P9" s="334">
         <f>IF(Data!L61="","",-Data!L61)</f>
         <v>0</v>
       </c>
-      <c r="Q9" s="318" t="str">
+      <c r="Q9" s="334" t="str">
         <f>IF(Data!M61="","",-Data!M61)</f>
         <v/>
       </c>
@@ -10256,52 +10272,52 @@
       <c r="B10" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C10" s="318">
+      <c r="C10" s="334">
         <f>-C4*C78</f>
         <v>-61093655</v>
       </c>
       <c r="E10" s="268"/>
-      <c r="G10" s="318">
+      <c r="G10" s="334">
         <f>Data!C62</f>
         <v>-61093655</v>
       </c>
-      <c r="H10" s="318">
+      <c r="H10" s="334">
         <f>Data!D62</f>
         <v>-58833476</v>
       </c>
-      <c r="I10" s="318">
+      <c r="I10" s="334">
         <f>Data!E62</f>
         <v>-54349703</v>
       </c>
-      <c r="J10" s="318">
+      <c r="J10" s="334">
         <f>Data!F62</f>
         <v>-41876368</v>
       </c>
-      <c r="K10" s="318">
+      <c r="K10" s="334">
         <f>Data!G62</f>
         <v>-32578395</v>
       </c>
-      <c r="L10" s="318">
+      <c r="L10" s="334">
         <f>Data!H62</f>
         <v>-25986482</v>
       </c>
-      <c r="M10" s="318">
+      <c r="M10" s="334">
         <f>Data!I62</f>
         <v>-19020963</v>
       </c>
-      <c r="N10" s="318">
+      <c r="N10" s="334">
         <f>Data!J62</f>
         <v>0</v>
       </c>
-      <c r="O10" s="318">
+      <c r="O10" s="334">
         <f>Data!K62</f>
         <v>0</v>
       </c>
-      <c r="P10" s="318">
+      <c r="P10" s="334">
         <f>Data!L62</f>
         <v>0</v>
       </c>
-      <c r="Q10" s="318" t="str">
+      <c r="Q10" s="334" t="str">
         <f>Data!M62</f>
         <v/>
       </c>
@@ -10311,54 +10327,54 @@
       <c r="B11" s="31" t="s">
         <v>195</v>
       </c>
-      <c r="C11" s="321">
+      <c r="C11" s="337">
         <f>C63</f>
         <v>0</v>
       </c>
       <c r="D11" s="168"/>
       <c r="E11" s="267"/>
       <c r="F11" s="168"/>
-      <c r="G11" s="324">
+      <c r="G11" s="340">
         <f>G61</f>
         <v>0</v>
       </c>
-      <c r="H11" s="324">
+      <c r="H11" s="340">
         <f t="shared" ref="H11:Q11" si="5">H61</f>
         <v>0</v>
       </c>
-      <c r="I11" s="324">
+      <c r="I11" s="340">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="J11" s="324">
+      <c r="J11" s="340">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="K11" s="324">
+      <c r="K11" s="340">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="L11" s="324">
+      <c r="L11" s="340">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="M11" s="324">
+      <c r="M11" s="340">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N11" s="324">
+      <c r="N11" s="340">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O11" s="324">
+      <c r="O11" s="340">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="P11" s="324">
+      <c r="P11" s="340">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="Q11" s="324" t="str">
+      <c r="Q11" s="340" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -10368,52 +10384,52 @@
       <c r="B12" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C12" s="318">
+      <c r="C12" s="334">
         <f>C50</f>
         <v>-1836766.1869999999</v>
       </c>
       <c r="E12" s="268"/>
-      <c r="G12" s="318">
+      <c r="G12" s="334">
         <f>G50</f>
         <v>1556642.8639081065</v>
       </c>
-      <c r="H12" s="318">
+      <c r="H12" s="334">
         <f t="shared" ref="H12:Q12" si="6">H50</f>
         <v>-4876931.4294328652</v>
       </c>
-      <c r="I12" s="318">
+      <c r="I12" s="334">
         <f t="shared" si="6"/>
         <v>-4522710.3433301654</v>
       </c>
-      <c r="J12" s="318">
+      <c r="J12" s="334">
         <f t="shared" si="6"/>
         <v>451690.85756478301</v>
       </c>
-      <c r="K12" s="318">
+      <c r="K12" s="334">
         <f t="shared" si="6"/>
         <v>455699.92271862476</v>
       </c>
-      <c r="L12" s="318">
+      <c r="L12" s="334">
         <f t="shared" si="6"/>
         <v>-694923.58702304983</v>
       </c>
-      <c r="M12" s="318">
+      <c r="M12" s="334">
         <f t="shared" si="6"/>
         <v>-2414464.7603443339</v>
       </c>
-      <c r="N12" s="318">
+      <c r="N12" s="334">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="O12" s="318">
+      <c r="O12" s="334">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="P12" s="318">
+      <c r="P12" s="334">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="Q12" s="318" t="str">
+      <c r="Q12" s="334" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
@@ -10423,52 +10439,52 @@
       <c r="B13" s="70" t="s">
         <v>165</v>
       </c>
-      <c r="C13" s="319">
+      <c r="C13" s="335">
         <f>SUM(C8:C12)</f>
         <v>172638394.81299999</v>
       </c>
       <c r="E13" s="268"/>
-      <c r="G13" s="319">
+      <c r="G13" s="335">
         <f>IF(G$4="","",SUM(G8:G12))</f>
         <v>175798547.86390811</v>
       </c>
-      <c r="H13" s="319">
+      <c r="H13" s="335">
         <f t="shared" ref="H13:Q13" si="7">IF(H$4="","",SUM(H8:H12))</f>
         <v>223735763.57056713</v>
       </c>
-      <c r="I13" s="319">
+      <c r="I13" s="335">
         <f t="shared" si="7"/>
         <v>442594723.65666986</v>
       </c>
-      <c r="J13" s="319">
+      <c r="J13" s="335">
         <f t="shared" si="7"/>
         <v>284931346.85756481</v>
       </c>
-      <c r="K13" s="319">
+      <c r="K13" s="335">
         <f t="shared" si="7"/>
         <v>215380881.92271861</v>
       </c>
-      <c r="L13" s="319">
+      <c r="L13" s="335">
         <f t="shared" si="7"/>
         <v>175515403.41297695</v>
       </c>
-      <c r="M13" s="319">
+      <c r="M13" s="335">
         <f t="shared" si="7"/>
         <v>124869825.23965567</v>
       </c>
-      <c r="N13" s="319">
+      <c r="N13" s="335">
         <f t="shared" si="7"/>
         <v>110070019</v>
       </c>
-      <c r="O13" s="319">
+      <c r="O13" s="335">
         <f t="shared" si="7"/>
         <v>75904369</v>
       </c>
-      <c r="P13" s="319">
+      <c r="P13" s="335">
         <f t="shared" si="7"/>
         <v>73758844</v>
       </c>
-      <c r="Q13" s="319" t="str">
+      <c r="Q13" s="335" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -10478,52 +10494,52 @@
       <c r="B14" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C14" s="318">
+      <c r="C14" s="334">
         <f>-SUM(C8+C11,C12)*C43</f>
         <v>-43159598.703249998</v>
       </c>
       <c r="E14" s="268"/>
-      <c r="G14" s="318">
+      <c r="G14" s="334">
         <f>Data!C46</f>
         <v>-28257995</v>
       </c>
-      <c r="H14" s="318">
+      <c r="H14" s="334">
         <f>Data!D46</f>
         <v>-29716699</v>
       </c>
-      <c r="I14" s="318">
+      <c r="I14" s="334">
         <f>Data!E46</f>
         <v>-60986391</v>
       </c>
-      <c r="J14" s="318">
+      <c r="J14" s="334">
         <f>Data!F46</f>
         <v>-37814748</v>
       </c>
-      <c r="K14" s="318">
+      <c r="K14" s="334">
         <f>Data!G46</f>
         <v>-30587751</v>
       </c>
-      <c r="L14" s="318">
+      <c r="L14" s="334">
         <f>Data!H46</f>
         <v>-21993559</v>
       </c>
-      <c r="M14" s="318">
+      <c r="M14" s="334">
         <f>Data!I46</f>
         <v>-16485438</v>
       </c>
-      <c r="N14" s="318">
+      <c r="N14" s="334">
         <f>Data!J46</f>
         <v>-11657792</v>
       </c>
-      <c r="O14" s="318">
+      <c r="O14" s="334">
         <f>Data!K46</f>
         <v>-10793741</v>
       </c>
-      <c r="P14" s="318">
+      <c r="P14" s="334">
         <f>Data!L46</f>
         <v>-10094751</v>
       </c>
-      <c r="Q14" s="318" t="str">
+      <c r="Q14" s="334" t="str">
         <f>Data!M46</f>
         <v/>
       </c>
@@ -10533,54 +10549,54 @@
       <c r="B15" s="40" t="s">
         <v>244</v>
       </c>
-      <c r="C15" s="318">
+      <c r="C15" s="334">
         <f>-C4*C83</f>
         <v>0</v>
       </c>
       <c r="D15" s="60"/>
       <c r="E15" s="275"/>
       <c r="F15" s="60"/>
-      <c r="G15" s="323">
+      <c r="G15" s="339">
         <f>Data!C48</f>
         <v>0</v>
       </c>
-      <c r="H15" s="323">
+      <c r="H15" s="339">
         <f>Data!D48</f>
         <v>0</v>
       </c>
-      <c r="I15" s="323">
+      <c r="I15" s="339">
         <f>Data!E48</f>
         <v>0</v>
       </c>
-      <c r="J15" s="323">
+      <c r="J15" s="339">
         <f>Data!F48</f>
         <v>0</v>
       </c>
-      <c r="K15" s="323">
+      <c r="K15" s="339">
         <f>Data!G48</f>
         <v>0</v>
       </c>
-      <c r="L15" s="323">
+      <c r="L15" s="339">
         <f>Data!H48</f>
         <v>0</v>
       </c>
-      <c r="M15" s="323">
+      <c r="M15" s="339">
         <f>Data!I48</f>
         <v>-126598</v>
       </c>
-      <c r="N15" s="323">
+      <c r="N15" s="339">
         <f>Data!J48</f>
         <v>0</v>
       </c>
-      <c r="O15" s="323">
+      <c r="O15" s="339">
         <f>Data!K48</f>
         <v>0</v>
       </c>
-      <c r="P15" s="323">
+      <c r="P15" s="339">
         <f>Data!L48</f>
         <v>0</v>
       </c>
-      <c r="Q15" s="323" t="str">
+      <c r="Q15" s="339" t="str">
         <f>Data!M48</f>
         <v/>
       </c>
@@ -10590,54 +10606,54 @@
       <c r="B16" s="41" t="s">
         <v>155</v>
       </c>
-      <c r="C16" s="322">
+      <c r="C16" s="338">
         <f>SUM(C13:C15)</f>
         <v>129478796.10975</v>
       </c>
       <c r="D16" s="61"/>
       <c r="E16" s="276"/>
       <c r="F16" s="61"/>
-      <c r="G16" s="319">
+      <c r="G16" s="335">
         <f>IF(G$4="","",SUM(G13:G15))</f>
         <v>147540552.86390811</v>
       </c>
-      <c r="H16" s="319">
+      <c r="H16" s="335">
         <f t="shared" ref="H16:Q16" si="8">IF(H$4="","",SUM(H13:H15))</f>
         <v>194019064.57056713</v>
       </c>
-      <c r="I16" s="319">
+      <c r="I16" s="335">
         <f t="shared" si="8"/>
         <v>381608332.65666986</v>
       </c>
-      <c r="J16" s="319">
+      <c r="J16" s="335">
         <f t="shared" si="8"/>
         <v>247116598.85756481</v>
       </c>
-      <c r="K16" s="319">
+      <c r="K16" s="335">
         <f t="shared" si="8"/>
         <v>184793130.92271861</v>
       </c>
-      <c r="L16" s="319">
+      <c r="L16" s="335">
         <f t="shared" si="8"/>
         <v>153521844.41297695</v>
       </c>
-      <c r="M16" s="319">
+      <c r="M16" s="335">
         <f t="shared" si="8"/>
         <v>108257789.23965567</v>
       </c>
-      <c r="N16" s="319">
+      <c r="N16" s="335">
         <f t="shared" si="8"/>
         <v>98412227</v>
       </c>
-      <c r="O16" s="319">
+      <c r="O16" s="335">
         <f t="shared" si="8"/>
         <v>65110628</v>
       </c>
-      <c r="P16" s="319">
+      <c r="P16" s="335">
         <f t="shared" si="8"/>
         <v>63664093</v>
       </c>
-      <c r="Q16" s="319" t="str">
+      <c r="Q16" s="335" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
@@ -10647,7 +10663,7 @@
       <c r="B17" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="C17" s="318">
+      <c r="C17" s="334">
         <f>-C4*C85</f>
         <v>0</v>
       </c>
@@ -10656,24 +10672,24 @@
         <v>332</v>
       </c>
       <c r="F17" s="58"/>
-      <c r="G17" s="325"/>
-      <c r="H17" s="325"/>
-      <c r="I17" s="325"/>
-      <c r="J17" s="325"/>
-      <c r="K17" s="325"/>
-      <c r="L17" s="325"/>
-      <c r="M17" s="325"/>
-      <c r="N17" s="325"/>
-      <c r="O17" s="325"/>
-      <c r="P17" s="325"/>
-      <c r="Q17" s="325"/>
+      <c r="G17" s="341"/>
+      <c r="H17" s="341"/>
+      <c r="I17" s="341"/>
+      <c r="J17" s="341"/>
+      <c r="K17" s="341"/>
+      <c r="L17" s="341"/>
+      <c r="M17" s="341"/>
+      <c r="N17" s="341"/>
+      <c r="O17" s="341"/>
+      <c r="P17" s="341"/>
+      <c r="Q17" s="341"/>
     </row>
     <row r="18" spans="1:17" ht="15.75" customHeight="1">
       <c r="A18" s="10"/>
       <c r="B18" s="27" t="s">
         <v>99</v>
       </c>
-      <c r="C18" s="318">
+      <c r="C18" s="334">
         <v>0</v>
       </c>
       <c r="D18" s="58"/>
@@ -10681,71 +10697,71 @@
         <v>333</v>
       </c>
       <c r="F18" s="58"/>
-      <c r="G18" s="326"/>
-      <c r="H18" s="326"/>
-      <c r="I18" s="326"/>
-      <c r="J18" s="326"/>
-      <c r="K18" s="326"/>
-      <c r="L18" s="326"/>
-      <c r="M18" s="326"/>
-      <c r="N18" s="326"/>
-      <c r="O18" s="326"/>
-      <c r="P18" s="326"/>
-      <c r="Q18" s="326"/>
+      <c r="G18" s="342"/>
+      <c r="H18" s="342"/>
+      <c r="I18" s="342"/>
+      <c r="J18" s="342"/>
+      <c r="K18" s="342"/>
+      <c r="L18" s="342"/>
+      <c r="M18" s="342"/>
+      <c r="N18" s="342"/>
+      <c r="O18" s="342"/>
+      <c r="P18" s="342"/>
+      <c r="Q18" s="342"/>
     </row>
     <row r="19" spans="1:17" ht="15.75" customHeight="1">
       <c r="A19" s="10"/>
       <c r="B19" s="31" t="s">
         <v>66</v>
       </c>
-      <c r="C19" s="319">
+      <c r="C19" s="335">
         <f>C16+C17</f>
         <v>129478796.10975</v>
       </c>
       <c r="D19" s="27"/>
       <c r="E19" s="265"/>
       <c r="F19" s="27"/>
-      <c r="G19" s="324">
+      <c r="G19" s="340">
         <f>IF(G$4="","",G16+G17)</f>
         <v>147540552.86390811</v>
       </c>
-      <c r="H19" s="324">
+      <c r="H19" s="340">
         <f t="shared" ref="H19:Q19" si="9">IF(H$4="","",H16+H17)</f>
         <v>194019064.57056713</v>
       </c>
-      <c r="I19" s="324">
+      <c r="I19" s="340">
         <f t="shared" si="9"/>
         <v>381608332.65666986</v>
       </c>
-      <c r="J19" s="324">
+      <c r="J19" s="340">
         <f t="shared" si="9"/>
         <v>247116598.85756481</v>
       </c>
-      <c r="K19" s="324">
+      <c r="K19" s="340">
         <f t="shared" si="9"/>
         <v>184793130.92271861</v>
       </c>
-      <c r="L19" s="324">
+      <c r="L19" s="340">
         <f t="shared" si="9"/>
         <v>153521844.41297695</v>
       </c>
-      <c r="M19" s="324">
+      <c r="M19" s="340">
         <f t="shared" si="9"/>
         <v>108257789.23965567</v>
       </c>
-      <c r="N19" s="324">
+      <c r="N19" s="340">
         <f t="shared" si="9"/>
         <v>98412227</v>
       </c>
-      <c r="O19" s="324">
+      <c r="O19" s="340">
         <f t="shared" si="9"/>
         <v>65110628</v>
       </c>
-      <c r="P19" s="324">
+      <c r="P19" s="340">
         <f t="shared" si="9"/>
         <v>63664093</v>
       </c>
-      <c r="Q19" s="324" t="str">
+      <c r="Q19" s="340" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -10818,54 +10834,54 @@
       <c r="B23" s="27" t="s">
         <v>43</v>
       </c>
-      <c r="C23" s="327">
+      <c r="C23" s="343">
         <f>-C4*C28</f>
         <v>-1115025379</v>
       </c>
       <c r="D23" s="58"/>
       <c r="E23" s="267"/>
       <c r="F23" s="58"/>
-      <c r="G23" s="323">
+      <c r="G23" s="339">
         <f>Data!C37</f>
         <v>-1115025379</v>
       </c>
-      <c r="H23" s="323">
+      <c r="H23" s="339">
         <f>Data!D37</f>
         <v>-1033174066</v>
       </c>
-      <c r="I23" s="323">
+      <c r="I23" s="339">
         <f>Data!E37</f>
         <v>-1034288683</v>
       </c>
-      <c r="J23" s="323">
+      <c r="J23" s="339">
         <f>Data!F37</f>
         <v>-993330987</v>
       </c>
-      <c r="K23" s="323">
+      <c r="K23" s="339">
         <f>Data!G37</f>
         <v>-600104422</v>
       </c>
-      <c r="L23" s="323">
+      <c r="L23" s="339">
         <f>Data!H37</f>
         <v>-431395603</v>
       </c>
-      <c r="M23" s="323">
+      <c r="M23" s="339">
         <f>Data!I37</f>
         <v>-434340576</v>
       </c>
-      <c r="N23" s="323">
+      <c r="N23" s="339">
         <f>Data!J37</f>
         <v>-369324839</v>
       </c>
-      <c r="O23" s="323">
+      <c r="O23" s="339">
         <f>Data!K37</f>
         <v>-255166042</v>
       </c>
-      <c r="P23" s="323">
+      <c r="P23" s="339">
         <f>Data!L37</f>
         <v>-243249284</v>
       </c>
-      <c r="Q23" s="323" t="str">
+      <c r="Q23" s="339" t="str">
         <f>Data!M37</f>
         <v/>
       </c>
@@ -10875,54 +10891,54 @@
       <c r="B24" s="68" t="s">
         <v>62</v>
       </c>
-      <c r="C24" s="318">
+      <c r="C24" s="334">
         <f>-C4*C29</f>
         <v>-10699910</v>
       </c>
       <c r="D24" s="27"/>
       <c r="E24" s="265"/>
       <c r="F24" s="27"/>
-      <c r="G24" s="323">
+      <c r="G24" s="339">
         <f>Data!C40</f>
         <v>-10699910</v>
       </c>
-      <c r="H24" s="323">
+      <c r="H24" s="339">
         <f>Data!D40</f>
         <v>-8156496</v>
       </c>
-      <c r="I24" s="323">
+      <c r="I24" s="339">
         <f>Data!E40</f>
         <v>-8760304</v>
       </c>
-      <c r="J24" s="323">
+      <c r="J24" s="339">
         <f>Data!F40</f>
         <v>-6582094</v>
       </c>
-      <c r="K24" s="323">
+      <c r="K24" s="339">
         <f>Data!G40</f>
         <v>-6591833</v>
       </c>
-      <c r="L24" s="323">
+      <c r="L24" s="339">
         <f>Data!H40</f>
         <v>-28503017</v>
       </c>
-      <c r="M24" s="323">
+      <c r="M24" s="339">
         <f>Data!I40</f>
         <v>-27458819</v>
       </c>
-      <c r="N24" s="323">
+      <c r="N24" s="339">
         <f>Data!J40</f>
         <v>-20907812</v>
       </c>
-      <c r="O24" s="323">
+      <c r="O24" s="339">
         <f>Data!K40</f>
         <v>-15460659</v>
       </c>
-      <c r="P24" s="323">
+      <c r="P24" s="339">
         <f>Data!L40</f>
         <v>-11888598</v>
       </c>
-      <c r="Q24" s="323" t="str">
+      <c r="Q24" s="339" t="str">
         <f>Data!M40</f>
         <v/>
       </c>
@@ -10932,54 +10948,54 @@
       <c r="B25" s="70" t="s">
         <v>46</v>
       </c>
-      <c r="C25" s="319">
+      <c r="C25" s="335">
         <f>C23+C24</f>
         <v>-1125725289</v>
       </c>
       <c r="D25" s="9"/>
       <c r="E25" s="273"/>
       <c r="F25" s="9"/>
-      <c r="G25" s="319">
+      <c r="G25" s="335">
         <f t="shared" ref="G25:Q25" si="10">IF(G$4="","",G23+G24)</f>
         <v>-1125725289</v>
       </c>
-      <c r="H25" s="319">
+      <c r="H25" s="335">
         <f t="shared" si="10"/>
         <v>-1041330562</v>
       </c>
-      <c r="I25" s="319">
+      <c r="I25" s="335">
         <f t="shared" si="10"/>
         <v>-1043048987</v>
       </c>
-      <c r="J25" s="319">
+      <c r="J25" s="335">
         <f t="shared" si="10"/>
         <v>-999913081</v>
       </c>
-      <c r="K25" s="319">
+      <c r="K25" s="335">
         <f t="shared" si="10"/>
         <v>-606696255</v>
       </c>
-      <c r="L25" s="319">
+      <c r="L25" s="335">
         <f t="shared" si="10"/>
         <v>-459898620</v>
       </c>
-      <c r="M25" s="319">
+      <c r="M25" s="335">
         <f t="shared" si="10"/>
         <v>-461799395</v>
       </c>
-      <c r="N25" s="319">
+      <c r="N25" s="335">
         <f t="shared" si="10"/>
         <v>-390232651</v>
       </c>
-      <c r="O25" s="319">
+      <c r="O25" s="335">
         <f t="shared" si="10"/>
         <v>-270626701</v>
       </c>
-      <c r="P25" s="319">
+      <c r="P25" s="335">
         <f t="shared" si="10"/>
         <v>-255137882</v>
       </c>
-      <c r="Q25" s="319" t="str">
+      <c r="Q25" s="335" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
@@ -11185,54 +11201,54 @@
       <c r="B33" s="8" t="s">
         <v>175</v>
       </c>
-      <c r="C33" s="328">
+      <c r="C33" s="346">
         <f>G33</f>
         <v>-33090730</v>
       </c>
       <c r="E33" s="266" t="s">
         <v>334</v>
       </c>
-      <c r="G33" s="318">
+      <c r="G33" s="334">
         <f>Data!C41</f>
         <v>-33090730</v>
       </c>
-      <c r="H33" s="318">
+      <c r="H33" s="334">
         <f>Data!D41</f>
         <v>-30065930</v>
       </c>
-      <c r="I33" s="318">
+      <c r="I33" s="334">
         <f>Data!E41</f>
         <v>-32634216</v>
       </c>
-      <c r="J33" s="318">
+      <c r="J33" s="334">
         <f>Data!F41</f>
         <v>-29271942</v>
       </c>
-      <c r="K33" s="318">
+      <c r="K33" s="334">
         <f>Data!G41</f>
         <v>-21597140</v>
       </c>
-      <c r="L33" s="318">
+      <c r="L33" s="334">
         <f>Data!H41</f>
         <v>6016516</v>
       </c>
-      <c r="M33" s="318">
+      <c r="M33" s="334">
         <f>Data!I41</f>
         <v>6195744</v>
       </c>
-      <c r="N33" s="318">
+      <c r="N33" s="334">
         <f>Data!J41</f>
         <v>-40616807</v>
       </c>
-      <c r="O33" s="318">
+      <c r="O33" s="334">
         <f>Data!K41</f>
         <v>-29266183</v>
       </c>
-      <c r="P33" s="318">
+      <c r="P33" s="334">
         <f>Data!L41</f>
         <v>-21316189</v>
       </c>
-      <c r="Q33" s="318" t="str">
+      <c r="Q33" s="334" t="str">
         <f>Data!M41</f>
         <v/>
       </c>
@@ -11242,7 +11258,7 @@
       <c r="B34" s="27" t="s">
         <v>49</v>
       </c>
-      <c r="C34" s="328">
+      <c r="C34" s="346">
         <f>AVERAGE(G34:J34)</f>
         <v>-77715731</v>
       </c>
@@ -11251,47 +11267,47 @@
         <v>334</v>
       </c>
       <c r="F34" s="58"/>
-      <c r="G34" s="323">
+      <c r="G34" s="339">
         <f>Data!C42</f>
         <v>-77948987</v>
       </c>
-      <c r="H34" s="323">
+      <c r="H34" s="339">
         <f>Data!D42</f>
         <v>-79192247</v>
       </c>
-      <c r="I34" s="323">
+      <c r="I34" s="339">
         <f>Data!E42</f>
         <v>-74126277</v>
       </c>
-      <c r="J34" s="323">
+      <c r="J34" s="339">
         <f>Data!F42</f>
         <v>-79595413</v>
       </c>
-      <c r="K34" s="323">
+      <c r="K34" s="339">
         <f>Data!G42</f>
         <v>-69723237</v>
       </c>
-      <c r="L34" s="323">
+      <c r="L34" s="339">
         <f>Data!H42</f>
         <v>-50161359</v>
       </c>
-      <c r="M34" s="323">
+      <c r="M34" s="339">
         <f>Data!I42</f>
         <v>-52954564</v>
       </c>
-      <c r="N34" s="323">
+      <c r="N34" s="339">
         <f>Data!J42</f>
         <v>0</v>
       </c>
-      <c r="O34" s="323">
+      <c r="O34" s="339">
         <f>Data!K42</f>
         <v>0</v>
       </c>
-      <c r="P34" s="323">
+      <c r="P34" s="339">
         <f>Data!L42</f>
         <v>0</v>
       </c>
-      <c r="Q34" s="323" t="str">
+      <c r="Q34" s="339" t="str">
         <f>Data!M42</f>
         <v/>
       </c>
@@ -11301,54 +11317,54 @@
       <c r="B35" s="70" t="s">
         <v>45</v>
       </c>
-      <c r="C35" s="319">
+      <c r="C35" s="335">
         <f>C33+C34</f>
         <v>-110806461</v>
       </c>
       <c r="D35" s="58"/>
       <c r="E35" s="267"/>
       <c r="F35" s="58"/>
-      <c r="G35" s="319">
+      <c r="G35" s="335">
         <f t="shared" ref="G35:Q35" si="14">IF(G4="","",G33+G34)</f>
         <v>-111039717</v>
       </c>
-      <c r="H35" s="319">
+      <c r="H35" s="335">
         <f t="shared" si="14"/>
         <v>-109258177</v>
       </c>
-      <c r="I35" s="319">
+      <c r="I35" s="335">
         <f t="shared" si="14"/>
         <v>-106760493</v>
       </c>
-      <c r="J35" s="319">
+      <c r="J35" s="335">
         <f t="shared" si="14"/>
         <v>-108867355</v>
       </c>
-      <c r="K35" s="319">
+      <c r="K35" s="335">
         <f t="shared" si="14"/>
         <v>-91320377</v>
       </c>
-      <c r="L35" s="319">
+      <c r="L35" s="335">
         <f t="shared" si="14"/>
         <v>-44144843</v>
       </c>
-      <c r="M35" s="319">
+      <c r="M35" s="335">
         <f t="shared" si="14"/>
         <v>-46758820</v>
       </c>
-      <c r="N35" s="319">
+      <c r="N35" s="335">
         <f t="shared" si="14"/>
         <v>-40616807</v>
       </c>
-      <c r="O35" s="319">
+      <c r="O35" s="335">
         <f t="shared" si="14"/>
         <v>-29266183</v>
       </c>
-      <c r="P35" s="319">
+      <c r="P35" s="335">
         <f t="shared" si="14"/>
         <v>-21316189</v>
       </c>
-      <c r="Q35" s="319" t="str">
+      <c r="Q35" s="335" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
@@ -11642,52 +11658,52 @@
       <c r="B47" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C47" s="318">
+      <c r="C47" s="334">
         <f>-BS!G31*Normalized_FCF!C54</f>
         <v>-5219951</v>
       </c>
       <c r="E47" s="268"/>
-      <c r="G47" s="318">
+      <c r="G47" s="334">
         <f>Data!C51</f>
         <v>-5219951</v>
       </c>
-      <c r="H47" s="318">
+      <c r="H47" s="334">
         <f>Data!D51</f>
         <v>-8074436</v>
       </c>
-      <c r="I47" s="318">
+      <c r="I47" s="334">
         <f>Data!E51</f>
         <v>-4999986</v>
       </c>
-      <c r="J47" s="318">
+      <c r="J47" s="334">
         <f>Data!F51</f>
         <v>-32946</v>
       </c>
-      <c r="K47" s="318">
+      <c r="K47" s="334">
         <f>Data!G51</f>
         <v>0</v>
       </c>
-      <c r="L47" s="318">
+      <c r="L47" s="334">
         <f>Data!H51</f>
         <v>-1902780</v>
       </c>
-      <c r="M47" s="318">
+      <c r="M47" s="334">
         <f>Data!I51</f>
         <v>-3158441</v>
       </c>
-      <c r="N47" s="318">
+      <c r="N47" s="334">
         <f>Data!J51</f>
         <v>0</v>
       </c>
-      <c r="O47" s="318">
+      <c r="O47" s="334">
         <f>Data!K51</f>
         <v>0</v>
       </c>
-      <c r="P47" s="318">
+      <c r="P47" s="334">
         <f>Data!L51</f>
         <v>0</v>
       </c>
-      <c r="Q47" s="318" t="str">
+      <c r="Q47" s="334" t="str">
         <f>Data!M51</f>
         <v/>
       </c>
@@ -11697,52 +11713,52 @@
       <c r="B48" s="2" t="s">
         <v>346</v>
       </c>
-      <c r="C48" s="318">
+      <c r="C48" s="334">
         <f>BS!D75*C53</f>
         <v>3383184.8130000001</v>
       </c>
       <c r="E48" s="268"/>
-      <c r="G48" s="327">
+      <c r="G48" s="343">
         <f>IFERROR(IF(G$4="","",($C$48/$C$49)*G49),0)</f>
         <v>6776593.8639081065</v>
       </c>
-      <c r="H48" s="327">
+      <c r="H48" s="343">
         <f t="shared" ref="H48:Q48" si="19">IFERROR(IF(H$4="","",($C$48/$C$49)*H49),0)</f>
         <v>3197504.5705671343</v>
       </c>
-      <c r="I48" s="327">
+      <c r="I48" s="343">
         <f t="shared" si="19"/>
         <v>477275.65666983434</v>
       </c>
-      <c r="J48" s="327">
+      <c r="J48" s="343">
         <f t="shared" si="19"/>
         <v>484636.85756478301</v>
       </c>
-      <c r="K48" s="327">
+      <c r="K48" s="343">
         <f t="shared" si="19"/>
         <v>455699.92271862476</v>
       </c>
-      <c r="L48" s="327">
+      <c r="L48" s="343">
         <f t="shared" si="19"/>
         <v>1207856.4129769502</v>
       </c>
-      <c r="M48" s="327">
+      <c r="M48" s="343">
         <f t="shared" si="19"/>
         <v>743976.23965566582</v>
       </c>
-      <c r="N48" s="327">
+      <c r="N48" s="343">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="O48" s="327">
+      <c r="O48" s="343">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="P48" s="327">
+      <c r="P48" s="343">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="Q48" s="327" t="str">
+      <c r="Q48" s="343" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
@@ -11752,54 +11768,54 @@
       <c r="B49" s="287" t="s">
         <v>343</v>
       </c>
-      <c r="C49" s="329">
+      <c r="C49" s="348">
         <f>BS!$C$66*C53</f>
         <v>15188297.413799999</v>
       </c>
       <c r="D49" s="288"/>
       <c r="E49" s="289"/>
       <c r="F49" s="288"/>
-      <c r="G49" s="329">
+      <c r="G49" s="348">
         <f>Data!C52</f>
         <v>30422495</v>
       </c>
-      <c r="H49" s="329">
+      <c r="H49" s="348">
         <f>Data!D52</f>
         <v>14354714</v>
       </c>
-      <c r="I49" s="329">
+      <c r="I49" s="348">
         <f>Data!E52</f>
         <v>2142657</v>
       </c>
-      <c r="J49" s="329">
+      <c r="J49" s="348">
         <f>Data!F52</f>
         <v>2175704</v>
       </c>
-      <c r="K49" s="329">
+      <c r="K49" s="348">
         <f>Data!G52</f>
         <v>2045796</v>
       </c>
-      <c r="L49" s="329">
+      <c r="L49" s="348">
         <f>Data!H52</f>
         <v>5422489</v>
       </c>
-      <c r="M49" s="329">
+      <c r="M49" s="348">
         <f>Data!I52</f>
         <v>3339969</v>
       </c>
-      <c r="N49" s="329">
+      <c r="N49" s="348">
         <f>Data!J52</f>
         <v>0</v>
       </c>
-      <c r="O49" s="329">
+      <c r="O49" s="348">
         <f>Data!K52</f>
         <v>0</v>
       </c>
-      <c r="P49" s="329">
+      <c r="P49" s="348">
         <f>Data!L52</f>
         <v>0</v>
       </c>
-      <c r="Q49" s="329" t="str">
+      <c r="Q49" s="348" t="str">
         <f>Data!M52</f>
         <v/>
       </c>
@@ -11809,52 +11825,52 @@
       <c r="B50" s="70" t="s">
         <v>68</v>
       </c>
-      <c r="C50" s="319">
+      <c r="C50" s="335">
         <f>C47+C48</f>
         <v>-1836766.1869999999</v>
       </c>
       <c r="E50" s="268"/>
-      <c r="G50" s="319">
+      <c r="G50" s="335">
         <f>IF(G$4="","",(G47+G48))</f>
         <v>1556642.8639081065</v>
       </c>
-      <c r="H50" s="319">
+      <c r="H50" s="335">
         <f t="shared" ref="H50:Q50" si="20">IF(H$4="","",(H47+H48))</f>
         <v>-4876931.4294328652</v>
       </c>
-      <c r="I50" s="319">
+      <c r="I50" s="335">
         <f t="shared" si="20"/>
         <v>-4522710.3433301654</v>
       </c>
-      <c r="J50" s="319">
+      <c r="J50" s="335">
         <f t="shared" si="20"/>
         <v>451690.85756478301</v>
       </c>
-      <c r="K50" s="319">
+      <c r="K50" s="335">
         <f t="shared" si="20"/>
         <v>455699.92271862476</v>
       </c>
-      <c r="L50" s="319">
+      <c r="L50" s="335">
         <f t="shared" si="20"/>
         <v>-694923.58702304983</v>
       </c>
-      <c r="M50" s="319">
+      <c r="M50" s="335">
         <f t="shared" si="20"/>
         <v>-2414464.7603443339</v>
       </c>
-      <c r="N50" s="319">
+      <c r="N50" s="335">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="O50" s="319">
+      <c r="O50" s="335">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="P50" s="319">
+      <c r="P50" s="335">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="Q50" s="319" t="str">
+      <c r="Q50" s="335" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
@@ -12000,52 +12016,52 @@
       <c r="B58" s="40" t="s">
         <v>168</v>
       </c>
-      <c r="C58" s="318">
+      <c r="C58" s="334">
         <f>BS!$C67*C66</f>
         <v>0</v>
       </c>
       <c r="E58" s="268"/>
-      <c r="G58" s="318">
+      <c r="G58" s="334">
         <f>Data!C56</f>
         <v>0</v>
       </c>
-      <c r="H58" s="318">
+      <c r="H58" s="334">
         <f>Data!D56</f>
         <v>0</v>
       </c>
-      <c r="I58" s="318">
+      <c r="I58" s="334">
         <f>Data!E56</f>
         <v>0</v>
       </c>
-      <c r="J58" s="318">
+      <c r="J58" s="334">
         <f>Data!F56</f>
         <v>0</v>
       </c>
-      <c r="K58" s="318">
+      <c r="K58" s="334">
         <f>Data!G56</f>
         <v>0</v>
       </c>
-      <c r="L58" s="318">
+      <c r="L58" s="334">
         <f>Data!H56</f>
         <v>0</v>
       </c>
-      <c r="M58" s="318">
+      <c r="M58" s="334">
         <f>Data!I56</f>
         <v>0</v>
       </c>
-      <c r="N58" s="318">
+      <c r="N58" s="334">
         <f>Data!J56</f>
         <v>0</v>
       </c>
-      <c r="O58" s="318">
+      <c r="O58" s="334">
         <f>Data!K56</f>
         <v>0</v>
       </c>
-      <c r="P58" s="318">
+      <c r="P58" s="334">
         <f>Data!L56</f>
         <v>0</v>
       </c>
-      <c r="Q58" s="318" t="str">
+      <c r="Q58" s="334" t="str">
         <f>Data!M56</f>
         <v/>
       </c>
@@ -12055,52 +12071,52 @@
       <c r="B59" s="40" t="s">
         <v>160</v>
       </c>
-      <c r="C59" s="318">
+      <c r="C59" s="334">
         <f>BS!$C68*C67</f>
         <v>0</v>
       </c>
       <c r="E59" s="268"/>
-      <c r="G59" s="318">
+      <c r="G59" s="334">
         <f>Data!C55</f>
         <v>0</v>
       </c>
-      <c r="H59" s="318">
+      <c r="H59" s="334">
         <f>Data!D55</f>
         <v>0</v>
       </c>
-      <c r="I59" s="318">
+      <c r="I59" s="334">
         <f>Data!E55</f>
         <v>0</v>
       </c>
-      <c r="J59" s="318">
+      <c r="J59" s="334">
         <f>Data!F55</f>
         <v>0</v>
       </c>
-      <c r="K59" s="318">
+      <c r="K59" s="334">
         <f>Data!G55</f>
         <v>0</v>
       </c>
-      <c r="L59" s="318">
+      <c r="L59" s="334">
         <f>Data!H55</f>
         <v>0</v>
       </c>
-      <c r="M59" s="318">
+      <c r="M59" s="334">
         <f>Data!I55</f>
         <v>0</v>
       </c>
-      <c r="N59" s="318">
+      <c r="N59" s="334">
         <f>Data!J55</f>
         <v>0</v>
       </c>
-      <c r="O59" s="318">
+      <c r="O59" s="334">
         <f>Data!K55</f>
         <v>0</v>
       </c>
-      <c r="P59" s="318">
+      <c r="P59" s="334">
         <f>Data!L55</f>
         <v>0</v>
       </c>
-      <c r="Q59" s="318" t="str">
+      <c r="Q59" s="334" t="str">
         <f>Data!M55</f>
         <v/>
       </c>
@@ -12110,52 +12126,52 @@
       <c r="B60" s="40" t="s">
         <v>159</v>
       </c>
-      <c r="C60" s="318">
+      <c r="C60" s="334">
         <f>BS!$C69*C68</f>
         <v>0</v>
       </c>
       <c r="E60" s="268"/>
-      <c r="G60" s="318">
+      <c r="G60" s="334">
         <f>Data!C57</f>
         <v>0</v>
       </c>
-      <c r="H60" s="318">
+      <c r="H60" s="334">
         <f>Data!D57</f>
         <v>0</v>
       </c>
-      <c r="I60" s="318">
+      <c r="I60" s="334">
         <f>Data!E57</f>
         <v>0</v>
       </c>
-      <c r="J60" s="318">
+      <c r="J60" s="334">
         <f>Data!F57</f>
         <v>0</v>
       </c>
-      <c r="K60" s="318">
+      <c r="K60" s="334">
         <f>Data!G57</f>
         <v>0</v>
       </c>
-      <c r="L60" s="318">
+      <c r="L60" s="334">
         <f>Data!H57</f>
         <v>0</v>
       </c>
-      <c r="M60" s="318">
+      <c r="M60" s="334">
         <f>Data!I57</f>
         <v>0</v>
       </c>
-      <c r="N60" s="318">
+      <c r="N60" s="334">
         <f>Data!J57</f>
         <v>0</v>
       </c>
-      <c r="O60" s="318">
+      <c r="O60" s="334">
         <f>Data!K57</f>
         <v>0</v>
       </c>
-      <c r="P60" s="318">
+      <c r="P60" s="334">
         <f>Data!L57</f>
         <v>0</v>
       </c>
-      <c r="Q60" s="318" t="str">
+      <c r="Q60" s="334" t="str">
         <f>Data!M57</f>
         <v/>
       </c>
@@ -12165,52 +12181,52 @@
       <c r="B61" s="31" t="s">
         <v>195</v>
       </c>
-      <c r="C61" s="319">
+      <c r="C61" s="335">
         <f>SUM(C58:C60)</f>
         <v>0</v>
       </c>
       <c r="E61" s="268"/>
-      <c r="G61" s="319">
+      <c r="G61" s="335">
         <f t="shared" ref="G61:Q61" si="22">IF(G4="","",SUM(G58:G60))</f>
         <v>0</v>
       </c>
-      <c r="H61" s="319">
+      <c r="H61" s="335">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="I61" s="319">
+      <c r="I61" s="335">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="J61" s="319">
+      <c r="J61" s="335">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="K61" s="319">
+      <c r="K61" s="335">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="L61" s="319">
+      <c r="L61" s="335">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="M61" s="319">
+      <c r="M61" s="335">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="N61" s="319">
+      <c r="N61" s="335">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="O61" s="319">
+      <c r="O61" s="335">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="P61" s="319">
+      <c r="P61" s="335">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="Q61" s="319" t="str">
+      <c r="Q61" s="335" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
@@ -12220,53 +12236,53 @@
       <c r="B62" s="40" t="s">
         <v>161</v>
       </c>
-      <c r="C62" s="330">
+      <c r="C62" s="349">
         <v>0</v>
       </c>
       <c r="E62" s="266" t="s">
         <v>338</v>
       </c>
-      <c r="G62" s="318">
+      <c r="G62" s="334">
         <f>Data!C58</f>
         <v>20343730</v>
       </c>
-      <c r="H62" s="318">
+      <c r="H62" s="334">
         <f>Data!D58</f>
         <v>29902815</v>
       </c>
-      <c r="I62" s="318">
+      <c r="I62" s="334">
         <f>Data!E58</f>
         <v>38928126</v>
       </c>
-      <c r="J62" s="318">
+      <c r="J62" s="334">
         <f>Data!F58</f>
         <v>3581909</v>
       </c>
-      <c r="K62" s="318">
+      <c r="K62" s="334">
         <f>Data!G58</f>
         <v>-7731966</v>
       </c>
-      <c r="L62" s="318">
+      <c r="L62" s="334">
         <f>Data!H58</f>
         <v>-13016003</v>
       </c>
-      <c r="M62" s="318">
+      <c r="M62" s="334">
         <f>Data!I58</f>
         <v>-5234040</v>
       </c>
-      <c r="N62" s="318">
+      <c r="N62" s="334">
         <f>Data!J58</f>
         <v>-24806103</v>
       </c>
-      <c r="O62" s="318">
+      <c r="O62" s="334">
         <f>Data!K58</f>
         <v>-524529</v>
       </c>
-      <c r="P62" s="318">
+      <c r="P62" s="334">
         <f>Data!L58</f>
         <v>-6174489</v>
       </c>
-      <c r="Q62" s="318" t="str">
+      <c r="Q62" s="334" t="str">
         <f>Data!M58</f>
         <v/>
       </c>
@@ -12276,52 +12292,52 @@
       <c r="B63" s="31" t="s">
         <v>196</v>
       </c>
-      <c r="C63" s="319">
+      <c r="C63" s="335">
         <f>C61+C62</f>
         <v>0</v>
       </c>
       <c r="E63" s="268"/>
-      <c r="G63" s="319">
+      <c r="G63" s="335">
         <f t="shared" ref="G63:Q63" si="23">IF(G4="","",G61+G62)</f>
         <v>20343730</v>
       </c>
-      <c r="H63" s="319">
+      <c r="H63" s="335">
         <f t="shared" si="23"/>
         <v>29902815</v>
       </c>
-      <c r="I63" s="319">
+      <c r="I63" s="335">
         <f t="shared" si="23"/>
         <v>38928126</v>
       </c>
-      <c r="J63" s="319">
+      <c r="J63" s="335">
         <f t="shared" si="23"/>
         <v>3581909</v>
       </c>
-      <c r="K63" s="319">
+      <c r="K63" s="335">
         <f t="shared" si="23"/>
         <v>-7731966</v>
       </c>
-      <c r="L63" s="319">
+      <c r="L63" s="335">
         <f t="shared" si="23"/>
         <v>-13016003</v>
       </c>
-      <c r="M63" s="319">
+      <c r="M63" s="335">
         <f t="shared" si="23"/>
         <v>-5234040</v>
       </c>
-      <c r="N63" s="319">
+      <c r="N63" s="335">
         <f t="shared" si="23"/>
         <v>-24806103</v>
       </c>
-      <c r="O63" s="319">
+      <c r="O63" s="335">
         <f t="shared" si="23"/>
         <v>-524529</v>
       </c>
-      <c r="P63" s="319">
+      <c r="P63" s="335">
         <f t="shared" si="23"/>
         <v>-6174489</v>
       </c>
-      <c r="Q63" s="319" t="str">
+      <c r="Q63" s="335" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
@@ -13696,54 +13712,54 @@
       <c r="B101" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="C101" s="331">
+      <c r="C101" s="350">
         <f>BS!G32</f>
         <v>2813131398.21</v>
       </c>
       <c r="D101" s="26"/>
       <c r="E101" s="269"/>
       <c r="F101" s="26"/>
-      <c r="G101" s="323">
+      <c r="G101" s="339">
         <f t="shared" ref="G101:Q101" si="42">IF(G$4="","",G105+G104)</f>
         <v>2813131398.21</v>
       </c>
-      <c r="H101" s="323">
+      <c r="H101" s="339">
         <f t="shared" si="42"/>
         <v>2821719171</v>
       </c>
-      <c r="I101" s="323">
+      <c r="I101" s="339">
         <f t="shared" si="42"/>
         <v>2804541794</v>
       </c>
-      <c r="J101" s="323">
+      <c r="J101" s="339">
         <f t="shared" si="42"/>
         <v>2115221333</v>
       </c>
-      <c r="K101" s="323">
+      <c r="K101" s="339">
         <f t="shared" si="42"/>
         <v>1078793118</v>
       </c>
-      <c r="L101" s="323">
+      <c r="L101" s="339">
         <f t="shared" si="42"/>
         <v>976418045</v>
       </c>
-      <c r="M101" s="323">
+      <c r="M101" s="339">
         <f t="shared" si="42"/>
         <v>913519795</v>
       </c>
-      <c r="N101" s="323">
+      <c r="N101" s="339">
         <f t="shared" si="42"/>
         <v>632755333</v>
       </c>
-      <c r="O101" s="323">
+      <c r="O101" s="339">
         <f t="shared" si="42"/>
         <v>521915458</v>
       </c>
-      <c r="P101" s="323">
+      <c r="P101" s="339">
         <f t="shared" si="42"/>
         <v>463292481</v>
       </c>
-      <c r="Q101" s="323" t="str">
+      <c r="Q101" s="339" t="str">
         <f t="shared" si="42"/>
         <v/>
       </c>
@@ -13753,54 +13769,54 @@
       <c r="B102" s="93" t="s">
         <v>211</v>
       </c>
-      <c r="C102" s="332">
+      <c r="C102" s="351">
         <f>BS!C4</f>
         <v>435508276.29999995</v>
       </c>
       <c r="D102" s="89"/>
       <c r="E102" s="270"/>
       <c r="F102" s="89"/>
-      <c r="G102" s="333">
+      <c r="G102" s="352">
         <f>IF(G$4="","",Data!D77)</f>
         <v>286539091</v>
       </c>
-      <c r="H102" s="333">
+      <c r="H102" s="352">
         <f>IF(H$4="","",Data!E77)</f>
         <v>273013471</v>
       </c>
-      <c r="I102" s="333">
+      <c r="I102" s="352">
         <f>IF(I$4="","",Data!F77)</f>
         <v>232578044</v>
       </c>
-      <c r="J102" s="333">
+      <c r="J102" s="352">
         <f>IF(J$4="","",Data!G77)</f>
         <v>139788443</v>
       </c>
-      <c r="K102" s="333">
+      <c r="K102" s="352">
         <f>IF(K$4="","",Data!H77)</f>
         <v>109488661</v>
       </c>
-      <c r="L102" s="333">
+      <c r="L102" s="352">
         <f>IF(L$4="","",Data!I77)</f>
         <v>0</v>
       </c>
-      <c r="M102" s="333">
+      <c r="M102" s="352">
         <f>IF(M$4="","",Data!J77)</f>
         <v>0</v>
       </c>
-      <c r="N102" s="333">
+      <c r="N102" s="352">
         <f>IF(N$4="","",Data!K77)</f>
         <v>0</v>
       </c>
-      <c r="O102" s="333">
+      <c r="O102" s="352">
         <f>IF(O$4="","",Data!L77)</f>
         <v>0</v>
       </c>
-      <c r="P102" s="333">
+      <c r="P102" s="352">
         <f>IF(P$4="","",Data!M77)</f>
         <v>0</v>
       </c>
-      <c r="Q102" s="333" t="str">
+      <c r="Q102" s="352" t="str">
         <f>IF(Q$4="","",Data!N77)</f>
         <v/>
       </c>
@@ -13810,54 +13826,54 @@
       <c r="B103" s="93" t="s">
         <v>212</v>
       </c>
-      <c r="C103" s="332">
+      <c r="C103" s="351">
         <f>BS!C6+BS!C7</f>
         <v>149619822.47999999</v>
       </c>
       <c r="D103" s="89"/>
       <c r="E103" s="270"/>
       <c r="F103" s="89"/>
-      <c r="G103" s="333">
+      <c r="G103" s="352">
         <f>IF(G$4="","",Data!D78)</f>
         <v>175557090</v>
       </c>
-      <c r="H103" s="333">
+      <c r="H103" s="352">
         <f>IF(H$4="","",Data!E78)</f>
         <v>221536955</v>
       </c>
-      <c r="I103" s="333">
+      <c r="I103" s="352">
         <f>IF(I$4="","",Data!F78)</f>
         <v>134930930</v>
       </c>
-      <c r="J103" s="333">
+      <c r="J103" s="352">
         <f>IF(J$4="","",Data!G78)</f>
         <v>102812384</v>
       </c>
-      <c r="K103" s="333">
+      <c r="K103" s="352">
         <f>IF(K$4="","",Data!H78)</f>
         <v>54993674</v>
       </c>
-      <c r="L103" s="333">
+      <c r="L103" s="352">
         <f>IF(L$4="","",Data!I78)</f>
         <v>0</v>
       </c>
-      <c r="M103" s="333">
+      <c r="M103" s="352">
         <f>IF(M$4="","",Data!J78)</f>
         <v>0</v>
       </c>
-      <c r="N103" s="333">
+      <c r="N103" s="352">
         <f>IF(N$4="","",Data!K78)</f>
         <v>0</v>
       </c>
-      <c r="O103" s="333">
+      <c r="O103" s="352">
         <f>IF(O$4="","",Data!L78)</f>
         <v>0</v>
       </c>
-      <c r="P103" s="333">
+      <c r="P103" s="352">
         <f>IF(P$4="","",Data!M78)</f>
         <v>0</v>
       </c>
-      <c r="Q103" s="333" t="str">
+      <c r="Q103" s="352" t="str">
         <f>IF(Q$4="","",Data!N78)</f>
         <v/>
       </c>
@@ -13867,54 +13883,54 @@
       <c r="B104" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="C104" s="331">
+      <c r="C104" s="350">
         <f>BS!G30</f>
         <v>401550924.92000002</v>
       </c>
       <c r="D104" s="26"/>
       <c r="E104" s="269"/>
       <c r="F104" s="26"/>
-      <c r="G104" s="323">
+      <c r="G104" s="339">
         <f>Data!C79</f>
         <v>401550924.92000002</v>
       </c>
-      <c r="H104" s="323">
+      <c r="H104" s="339">
         <f>Data!D79</f>
         <v>375837168</v>
       </c>
-      <c r="I104" s="323">
+      <c r="I104" s="339">
         <f>Data!E79</f>
         <v>484715813</v>
       </c>
-      <c r="J104" s="323">
+      <c r="J104" s="339">
         <f>Data!F79</f>
         <v>120473425</v>
       </c>
-      <c r="K104" s="323">
+      <c r="K104" s="339">
         <f>Data!G79</f>
         <v>77386991</v>
       </c>
-      <c r="L104" s="323">
+      <c r="L104" s="339">
         <f>Data!H79</f>
         <v>107878390</v>
       </c>
-      <c r="M104" s="323">
+      <c r="M104" s="339">
         <f>Data!I79</f>
         <v>144733614</v>
       </c>
-      <c r="N104" s="323">
+      <c r="N104" s="339">
         <f>Data!J79</f>
         <v>117054123</v>
       </c>
-      <c r="O104" s="323">
+      <c r="O104" s="339">
         <f>Data!K79</f>
         <v>64103116</v>
       </c>
-      <c r="P104" s="323">
+      <c r="P104" s="339">
         <f>Data!L79</f>
         <v>30979762</v>
       </c>
-      <c r="Q104" s="323" t="str">
+      <c r="Q104" s="339" t="str">
         <f>Data!M79</f>
         <v/>
       </c>
@@ -13924,54 +13940,54 @@
       <c r="B105" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="C105" s="331">
+      <c r="C105" s="350">
         <f>BS!G27</f>
         <v>2411580473.29</v>
       </c>
       <c r="D105" s="26"/>
       <c r="E105" s="269"/>
       <c r="F105" s="26"/>
-      <c r="G105" s="323">
+      <c r="G105" s="339">
         <f>Data!C80</f>
         <v>2411580473.29</v>
       </c>
-      <c r="H105" s="323">
+      <c r="H105" s="339">
         <f>Data!D80</f>
         <v>2445882003</v>
       </c>
-      <c r="I105" s="323">
+      <c r="I105" s="339">
         <f>Data!E80</f>
         <v>2319825981</v>
       </c>
-      <c r="J105" s="323">
+      <c r="J105" s="339">
         <f>Data!F80</f>
         <v>1994747908</v>
       </c>
-      <c r="K105" s="323">
+      <c r="K105" s="339">
         <f>Data!G80</f>
         <v>1001406127</v>
       </c>
-      <c r="L105" s="323">
+      <c r="L105" s="339">
         <f>Data!H80</f>
         <v>868539655</v>
       </c>
-      <c r="M105" s="323">
+      <c r="M105" s="339">
         <f>Data!I80</f>
         <v>768786181</v>
       </c>
-      <c r="N105" s="323">
+      <c r="N105" s="339">
         <f>Data!J80</f>
         <v>515701210</v>
       </c>
-      <c r="O105" s="323">
+      <c r="O105" s="339">
         <f>Data!K80</f>
         <v>457812342</v>
       </c>
-      <c r="P105" s="323">
+      <c r="P105" s="339">
         <f>Data!L80</f>
         <v>432312719</v>
       </c>
-      <c r="Q105" s="323" t="str">
+      <c r="Q105" s="339" t="str">
         <f>Data!M80</f>
         <v/>
       </c>
@@ -15469,7 +15485,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:H94"/>
+  <dimension ref="A2:Q105"/>
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="6.1328125" customWidth="1"/>
@@ -15508,7 +15524,7 @@
       <c r="B4" s="100" t="s">
         <v>129</v>
       </c>
-      <c r="C4" s="114">
+      <c r="C4" s="344">
         <f>Normalized_FCF!C19</f>
         <v>129478796.10975</v>
       </c>
@@ -15540,7 +15556,7 @@
       <c r="B6" s="149" t="s">
         <v>229</v>
       </c>
-      <c r="C6" s="338">
+      <c r="C6" s="353">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
         <v>2157979935.1624999</v>
       </c>
@@ -15548,17 +15564,17 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="356" t="s">
+      <c r="E6" s="365" t="s">
         <v>250</v>
       </c>
-      <c r="F6" s="356"/>
+      <c r="F6" s="365"/>
       <c r="H6" s="120"/>
     </row>
     <row r="7" spans="2:8">
       <c r="B7" s="148" t="s">
         <v>225</v>
       </c>
-      <c r="C7" s="114">
+      <c r="C7" s="344">
         <f>BS!G31</f>
         <v>100067739.72</v>
       </c>
@@ -15566,15 +15582,15 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="356"/>
-      <c r="F7" s="356"/>
+      <c r="E7" s="365"/>
+      <c r="F7" s="365"/>
       <c r="H7" s="120"/>
     </row>
     <row r="8" spans="2:8">
       <c r="B8" s="148" t="s">
         <v>226</v>
       </c>
-      <c r="C8" s="114">
+      <c r="C8" s="344">
         <f>BS!D66</f>
         <v>787007506.71999991</v>
       </c>
@@ -15582,15 +15598,15 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="356"/>
-      <c r="F8" s="356"/>
+      <c r="E8" s="365"/>
+      <c r="F8" s="365"/>
       <c r="H8" s="120"/>
     </row>
     <row r="9" spans="2:8">
       <c r="B9" s="205" t="s">
         <v>191</v>
       </c>
-      <c r="C9" s="339">
+      <c r="C9" s="354">
         <f>BS!H42</f>
         <v>0</v>
       </c>
@@ -15598,15 +15614,15 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="356"/>
-      <c r="F9" s="356"/>
+      <c r="E9" s="365"/>
+      <c r="F9" s="365"/>
       <c r="H9" s="120"/>
     </row>
     <row r="10" spans="2:8" ht="13.15">
       <c r="B10" s="149" t="s">
         <v>228</v>
       </c>
-      <c r="C10" s="338">
+      <c r="C10" s="353">
         <f>C6-C7+C8+C9</f>
         <v>2844919702.1624999</v>
       </c>
@@ -15673,7 +15689,7 @@
       </c>
       <c r="H16" s="120"/>
     </row>
-    <row r="17" spans="2:8" ht="13.25" customHeight="1">
+    <row r="17" spans="2:17" ht="13.25" customHeight="1">
       <c r="B17" s="118" t="s">
         <v>135</v>
       </c>
@@ -15683,7 +15699,7 @@
       </c>
       <c r="H17" s="120"/>
     </row>
-    <row r="18" spans="2:8" ht="13.25" customHeight="1">
+    <row r="18" spans="2:17" ht="13.25" customHeight="1">
       <c r="B18" s="153" t="s">
         <v>107</v>
       </c>
@@ -15697,10 +15713,10 @@
       </c>
       <c r="H18" s="120"/>
     </row>
-    <row r="19" spans="2:8">
+    <row r="19" spans="2:17">
       <c r="H19" s="120"/>
     </row>
-    <row r="20" spans="2:8" ht="13.15">
+    <row r="20" spans="2:17" ht="13.15">
       <c r="B20" s="128" t="s">
         <v>108</v>
       </c>
@@ -15718,7 +15734,7 @@
       </c>
       <c r="H20" s="120"/>
     </row>
-    <row r="21" spans="2:8">
+    <row r="21" spans="2:17">
       <c r="B21" s="122">
         <v>1</v>
       </c>
@@ -15740,7 +15756,7 @@
       </c>
       <c r="H21" s="120"/>
     </row>
-    <row r="22" spans="2:8">
+    <row r="22" spans="2:17">
       <c r="B22" s="122">
         <v>2</v>
       </c>
@@ -15762,7 +15778,7 @@
       </c>
       <c r="H22" s="120"/>
     </row>
-    <row r="23" spans="2:8">
+    <row r="23" spans="2:17">
       <c r="B23" s="122">
         <v>3</v>
       </c>
@@ -15782,9 +15798,19 @@
         <f t="shared" si="1"/>
         <v>123174878.09029604</v>
       </c>
-      <c r="H23" s="120"/>
-    </row>
-    <row r="24" spans="2:8">
+      <c r="G23" s="344"/>
+      <c r="H23" s="345"/>
+      <c r="I23" s="344"/>
+      <c r="J23" s="344"/>
+      <c r="K23" s="344"/>
+      <c r="L23" s="344"/>
+      <c r="M23" s="344"/>
+      <c r="N23" s="344"/>
+      <c r="O23" s="344"/>
+      <c r="P23" s="344"/>
+      <c r="Q23" s="344"/>
+    </row>
+    <row r="24" spans="2:17">
       <c r="B24" s="122">
         <v>4</v>
       </c>
@@ -15804,9 +15830,19 @@
         <f t="shared" si="1"/>
         <v>121142529.39003712</v>
       </c>
-      <c r="H24" s="120"/>
-    </row>
-    <row r="25" spans="2:8">
+      <c r="G24" s="344"/>
+      <c r="H24" s="345"/>
+      <c r="I24" s="344"/>
+      <c r="J24" s="344"/>
+      <c r="K24" s="344"/>
+      <c r="L24" s="344"/>
+      <c r="M24" s="344"/>
+      <c r="N24" s="344"/>
+      <c r="O24" s="344"/>
+      <c r="P24" s="344"/>
+      <c r="Q24" s="344"/>
+    </row>
+    <row r="25" spans="2:17">
       <c r="B25" s="122">
         <v>5</v>
       </c>
@@ -15826,9 +15862,19 @@
         <f t="shared" si="1"/>
         <v>119143713.83633763</v>
       </c>
-      <c r="H25" s="120"/>
-    </row>
-    <row r="26" spans="2:8">
+      <c r="G25" s="344"/>
+      <c r="H25" s="345"/>
+      <c r="I25" s="344"/>
+      <c r="J25" s="344"/>
+      <c r="K25" s="344"/>
+      <c r="L25" s="344"/>
+      <c r="M25" s="344"/>
+      <c r="N25" s="344"/>
+      <c r="O25" s="344"/>
+      <c r="P25" s="344"/>
+      <c r="Q25" s="344"/>
+    </row>
+    <row r="26" spans="2:17">
       <c r="B26" s="122">
         <v>6</v>
       </c>
@@ -15850,7 +15896,7 @@
       </c>
       <c r="H26" s="120"/>
     </row>
-    <row r="27" spans="2:8">
+    <row r="27" spans="2:17">
       <c r="B27" s="122">
         <v>7</v>
       </c>
@@ -15872,7 +15918,7 @@
       </c>
       <c r="H27" s="120"/>
     </row>
-    <row r="28" spans="2:8">
+    <row r="28" spans="2:17">
       <c r="B28" s="122">
         <v>8</v>
       </c>
@@ -15894,7 +15940,7 @@
       </c>
       <c r="H28" s="120"/>
     </row>
-    <row r="29" spans="2:8">
+    <row r="29" spans="2:17">
       <c r="B29" s="122">
         <v>9</v>
       </c>
@@ -15916,7 +15962,7 @@
       </c>
       <c r="H29" s="120"/>
     </row>
-    <row r="30" spans="2:8">
+    <row r="30" spans="2:17">
       <c r="B30" s="122">
         <v>10</v>
       </c>
@@ -15938,7 +15984,7 @@
       </c>
       <c r="H30" s="120"/>
     </row>
-    <row r="31" spans="2:8">
+    <row r="31" spans="2:17">
       <c r="B31" s="122">
         <v>11</v>
       </c>
@@ -15960,7 +16006,7 @@
       </c>
       <c r="H31" s="120"/>
     </row>
-    <row r="32" spans="2:8">
+    <row r="32" spans="2:17">
       <c r="B32" s="122">
         <v>12</v>
       </c>
@@ -15982,11 +16028,11 @@
       </c>
       <c r="H32" s="120"/>
     </row>
-    <row r="33" spans="2:8">
+    <row r="33" spans="2:17">
       <c r="B33" s="122">
         <v>13</v>
       </c>
-      <c r="C33" s="123">
+      <c r="C33" s="347">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -16002,13 +16048,23 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H33" s="120"/>
-    </row>
-    <row r="34" spans="2:8">
+      <c r="G33" s="344"/>
+      <c r="H33" s="345"/>
+      <c r="I33" s="344"/>
+      <c r="J33" s="344"/>
+      <c r="K33" s="344"/>
+      <c r="L33" s="344"/>
+      <c r="M33" s="344"/>
+      <c r="N33" s="344"/>
+      <c r="O33" s="344"/>
+      <c r="P33" s="344"/>
+      <c r="Q33" s="344"/>
+    </row>
+    <row r="34" spans="2:17">
       <c r="B34" s="122">
         <v>14</v>
       </c>
-      <c r="C34" s="123">
+      <c r="C34" s="347">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -16024,13 +16080,23 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H34" s="120"/>
-    </row>
-    <row r="35" spans="2:8">
+      <c r="G34" s="344"/>
+      <c r="H34" s="345"/>
+      <c r="I34" s="344"/>
+      <c r="J34" s="344"/>
+      <c r="K34" s="344"/>
+      <c r="L34" s="344"/>
+      <c r="M34" s="344"/>
+      <c r="N34" s="344"/>
+      <c r="O34" s="344"/>
+      <c r="P34" s="344"/>
+      <c r="Q34" s="344"/>
+    </row>
+    <row r="35" spans="2:17">
       <c r="B35" s="122">
         <v>15</v>
       </c>
-      <c r="C35" s="123">
+      <c r="C35" s="347">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -16046,9 +16112,19 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H35" s="120"/>
-    </row>
-    <row r="36" spans="2:8">
+      <c r="G35" s="344"/>
+      <c r="H35" s="345"/>
+      <c r="I35" s="344"/>
+      <c r="J35" s="344"/>
+      <c r="K35" s="344"/>
+      <c r="L35" s="344"/>
+      <c r="M35" s="344"/>
+      <c r="N35" s="344"/>
+      <c r="O35" s="344"/>
+      <c r="P35" s="344"/>
+      <c r="Q35" s="344"/>
+    </row>
+    <row r="36" spans="2:17">
       <c r="B36" s="122">
         <v>16</v>
       </c>
@@ -16070,7 +16146,7 @@
       </c>
       <c r="H36" s="120"/>
     </row>
-    <row r="37" spans="2:8">
+    <row r="37" spans="2:17">
       <c r="B37" s="122">
         <v>17</v>
       </c>
@@ -16092,7 +16168,7 @@
       </c>
       <c r="H37" s="120"/>
     </row>
-    <row r="38" spans="2:8">
+    <row r="38" spans="2:17">
       <c r="B38" s="122">
         <v>18</v>
       </c>
@@ -16114,7 +16190,7 @@
       </c>
       <c r="H38" s="120"/>
     </row>
-    <row r="39" spans="2:8">
+    <row r="39" spans="2:17">
       <c r="B39" s="122">
         <v>19</v>
       </c>
@@ -16136,7 +16212,7 @@
       </c>
       <c r="H39" s="120"/>
     </row>
-    <row r="40" spans="2:8">
+    <row r="40" spans="2:17">
       <c r="B40" s="122">
         <v>20</v>
       </c>
@@ -16158,7 +16234,7 @@
       </c>
       <c r="H40" s="120"/>
     </row>
-    <row r="41" spans="2:8">
+    <row r="41" spans="2:17">
       <c r="B41" s="122">
         <v>21</v>
       </c>
@@ -16180,7 +16256,7 @@
       </c>
       <c r="H41" s="120"/>
     </row>
-    <row r="42" spans="2:8">
+    <row r="42" spans="2:17">
       <c r="B42" s="122">
         <v>22</v>
       </c>
@@ -16202,7 +16278,7 @@
       </c>
       <c r="H42" s="120"/>
     </row>
-    <row r="43" spans="2:8">
+    <row r="43" spans="2:17">
       <c r="B43" s="122">
         <v>23</v>
       </c>
@@ -16224,7 +16300,7 @@
       </c>
       <c r="H43" s="120"/>
     </row>
-    <row r="44" spans="2:8">
+    <row r="44" spans="2:17">
       <c r="B44" s="122">
         <v>24</v>
       </c>
@@ -16246,7 +16322,7 @@
       </c>
       <c r="H44" s="120"/>
     </row>
-    <row r="45" spans="2:8">
+    <row r="45" spans="2:17">
       <c r="B45" s="122">
         <v>25</v>
       </c>
@@ -16268,7 +16344,7 @@
       </c>
       <c r="H45" s="120"/>
     </row>
-    <row r="46" spans="2:8">
+    <row r="46" spans="2:17">
       <c r="B46" s="122">
         <v>26</v>
       </c>
@@ -16290,11 +16366,11 @@
       </c>
       <c r="H46" s="120"/>
     </row>
-    <row r="47" spans="2:8">
+    <row r="47" spans="2:17">
       <c r="B47" s="122">
         <v>27</v>
       </c>
-      <c r="C47" s="123">
+      <c r="C47" s="347">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -16310,13 +16386,23 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H47" s="120"/>
-    </row>
-    <row r="48" spans="2:8">
+      <c r="G47" s="344"/>
+      <c r="H47" s="345"/>
+      <c r="I47" s="344"/>
+      <c r="J47" s="344"/>
+      <c r="K47" s="344"/>
+      <c r="L47" s="344"/>
+      <c r="M47" s="344"/>
+      <c r="N47" s="344"/>
+      <c r="O47" s="344"/>
+      <c r="P47" s="344"/>
+      <c r="Q47" s="344"/>
+    </row>
+    <row r="48" spans="2:17">
       <c r="B48" s="122">
         <v>28</v>
       </c>
-      <c r="C48" s="123">
+      <c r="C48" s="347">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -16332,13 +16418,23 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H48" s="120"/>
-    </row>
-    <row r="49" spans="1:8">
+      <c r="G48" s="344"/>
+      <c r="H48" s="345"/>
+      <c r="I48" s="344"/>
+      <c r="J48" s="344"/>
+      <c r="K48" s="344"/>
+      <c r="L48" s="344"/>
+      <c r="M48" s="344"/>
+      <c r="N48" s="344"/>
+      <c r="O48" s="344"/>
+      <c r="P48" s="344"/>
+      <c r="Q48" s="344"/>
+    </row>
+    <row r="49" spans="1:17">
       <c r="B49" s="122">
         <v>29</v>
       </c>
-      <c r="C49" s="123">
+      <c r="C49" s="347">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -16354,13 +16450,23 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H49" s="120"/>
-    </row>
-    <row r="50" spans="1:8">
+      <c r="G49" s="344"/>
+      <c r="H49" s="345"/>
+      <c r="I49" s="344"/>
+      <c r="J49" s="344"/>
+      <c r="K49" s="344"/>
+      <c r="L49" s="344"/>
+      <c r="M49" s="344"/>
+      <c r="N49" s="344"/>
+      <c r="O49" s="344"/>
+      <c r="P49" s="344"/>
+      <c r="Q49" s="344"/>
+    </row>
+    <row r="50" spans="1:17">
       <c r="B50" s="122">
         <v>30</v>
       </c>
-      <c r="C50" s="123">
+      <c r="C50" s="347">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -16376,9 +16482,19 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H50" s="120"/>
-    </row>
-    <row r="51" spans="1:8">
+      <c r="G50" s="344"/>
+      <c r="H50" s="345"/>
+      <c r="I50" s="344"/>
+      <c r="J50" s="344"/>
+      <c r="K50" s="344"/>
+      <c r="L50" s="344"/>
+      <c r="M50" s="344"/>
+      <c r="N50" s="344"/>
+      <c r="O50" s="344"/>
+      <c r="P50" s="344"/>
+      <c r="Q50" s="344"/>
+    </row>
+    <row r="51" spans="1:17">
       <c r="B51" s="126" t="s">
         <v>132</v>
       </c>
@@ -16400,7 +16516,7 @@
       </c>
       <c r="H51" s="120"/>
     </row>
-    <row r="52" spans="1:8">
+    <row r="52" spans="1:17">
       <c r="C52" s="114"/>
       <c r="E52" s="127" t="s">
         <v>101</v>
@@ -16411,11 +16527,11 @@
       </c>
       <c r="H52" s="120"/>
     </row>
-    <row r="53" spans="1:8">
+    <row r="53" spans="1:17">
       <c r="C53" s="114"/>
       <c r="H53" s="120"/>
     </row>
-    <row r="54" spans="1:8" ht="13.15">
+    <row r="54" spans="1:17" ht="13.15">
       <c r="B54" s="119" t="s">
         <v>130</v>
       </c>
@@ -16425,7 +16541,7 @@
       <c r="F54" s="117"/>
       <c r="H54" s="120"/>
     </row>
-    <row r="55" spans="1:8" ht="13.15">
+    <row r="55" spans="1:17" ht="13.15">
       <c r="A55" s="133">
         <f>F52</f>
         <v>2297163804.1938334</v>
@@ -16452,7 +16568,7 @@
       </c>
       <c r="H55" s="120"/>
     </row>
-    <row r="56" spans="1:8" ht="13.15">
+    <row r="56" spans="1:17" ht="13.15">
       <c r="A56" s="143">
         <v>5</v>
       </c>
@@ -16474,7 +16590,7 @@
       </c>
       <c r="H56" s="120"/>
     </row>
-    <row r="57" spans="1:8" ht="13.15">
+    <row r="57" spans="1:17" ht="13.15">
       <c r="A57" s="143">
         <v>10</v>
       </c>
@@ -16495,14 +16611,14 @@
       </c>
       <c r="H57" s="120"/>
     </row>
-    <row r="58" spans="1:8" ht="13.15">
+    <row r="58" spans="1:17" ht="13.15">
       <c r="A58" s="143">
         <v>15</v>
       </c>
       <c r="B58" s="123">
         <v>2157979935.1624985</v>
       </c>
-      <c r="C58" s="123">
+      <c r="C58" s="347">
         <v>2365981354.4102435</v>
       </c>
       <c r="D58" s="123">
@@ -16514,16 +16630,26 @@
       <c r="F58" s="123">
         <v>3235296952.6150618</v>
       </c>
-      <c r="H58" s="120"/>
-    </row>
-    <row r="59" spans="1:8" ht="13.15">
+      <c r="G58" s="344"/>
+      <c r="H58" s="345"/>
+      <c r="I58" s="344"/>
+      <c r="J58" s="344"/>
+      <c r="K58" s="344"/>
+      <c r="L58" s="344"/>
+      <c r="M58" s="344"/>
+      <c r="N58" s="344"/>
+      <c r="O58" s="344"/>
+      <c r="P58" s="344"/>
+      <c r="Q58" s="344"/>
+    </row>
+    <row r="59" spans="1:17" ht="13.15">
       <c r="A59" s="144">
         <v>20</v>
       </c>
       <c r="B59" s="123">
         <v>2157979935.162499</v>
       </c>
-      <c r="C59" s="123">
+      <c r="C59" s="347">
         <v>2458269156.9786062</v>
       </c>
       <c r="D59" s="123">
@@ -16535,16 +16661,26 @@
       <c r="F59" s="123">
         <v>3896164894.664876</v>
       </c>
-      <c r="H59" s="120"/>
-    </row>
-    <row r="60" spans="1:8" ht="13.15">
+      <c r="G59" s="344"/>
+      <c r="H59" s="345"/>
+      <c r="I59" s="344"/>
+      <c r="J59" s="344"/>
+      <c r="K59" s="344"/>
+      <c r="L59" s="344"/>
+      <c r="M59" s="344"/>
+      <c r="N59" s="344"/>
+      <c r="O59" s="344"/>
+      <c r="P59" s="344"/>
+      <c r="Q59" s="344"/>
+    </row>
+    <row r="60" spans="1:17" ht="13.15">
       <c r="A60" s="144">
         <v>25</v>
       </c>
       <c r="B60" s="123">
         <v>2157979935.1624985</v>
       </c>
-      <c r="C60" s="123">
+      <c r="C60" s="347">
         <v>2552463867.5166478</v>
       </c>
       <c r="D60" s="123">
@@ -16556,16 +16692,26 @@
       <c r="F60" s="123">
         <v>4707976408.3152876</v>
       </c>
-      <c r="H60" s="120"/>
-    </row>
-    <row r="61" spans="1:8" ht="13.15">
+      <c r="G60" s="344"/>
+      <c r="H60" s="345"/>
+      <c r="I60" s="344"/>
+      <c r="J60" s="344"/>
+      <c r="K60" s="344"/>
+      <c r="L60" s="344"/>
+      <c r="M60" s="344"/>
+      <c r="N60" s="344"/>
+      <c r="O60" s="344"/>
+      <c r="P60" s="344"/>
+      <c r="Q60" s="344"/>
+    </row>
+    <row r="61" spans="1:17" ht="13.15">
       <c r="A61" s="144">
         <v>30</v>
       </c>
       <c r="B61" s="123">
         <v>2157979935.1624985</v>
       </c>
-      <c r="C61" s="123">
+      <c r="C61" s="347">
         <v>2643668791.6912336</v>
       </c>
       <c r="D61" s="123">
@@ -16577,26 +16723,56 @@
       <c r="F61" s="123">
         <v>5663732687.2271729</v>
       </c>
-      <c r="H61" s="120"/>
-    </row>
-    <row r="62" spans="1:8">
-      <c r="C62" s="114"/>
+      <c r="G61" s="344"/>
+      <c r="H61" s="345"/>
+      <c r="I61" s="344"/>
+      <c r="J61" s="344"/>
+      <c r="K61" s="344"/>
+      <c r="L61" s="344"/>
+      <c r="M61" s="344"/>
+      <c r="N61" s="344"/>
+      <c r="O61" s="344"/>
+      <c r="P61" s="344"/>
+      <c r="Q61" s="344"/>
+    </row>
+    <row r="62" spans="1:17">
+      <c r="C62" s="344"/>
       <c r="D62" s="114"/>
       <c r="E62" s="114"/>
       <c r="F62" s="114"/>
-      <c r="H62" s="120"/>
-    </row>
-    <row r="63" spans="1:8" ht="13.15">
+      <c r="G62" s="344"/>
+      <c r="H62" s="345"/>
+      <c r="I62" s="344"/>
+      <c r="J62" s="344"/>
+      <c r="K62" s="344"/>
+      <c r="L62" s="344"/>
+      <c r="M62" s="344"/>
+      <c r="N62" s="344"/>
+      <c r="O62" s="344"/>
+      <c r="P62" s="344"/>
+      <c r="Q62" s="344"/>
+    </row>
+    <row r="63" spans="1:17" ht="13.15">
       <c r="B63" s="119" t="s">
         <v>131</v>
       </c>
-      <c r="C63" s="114"/>
+      <c r="C63" s="344"/>
       <c r="D63" s="114"/>
       <c r="E63" s="114"/>
       <c r="F63" s="114"/>
-      <c r="H63" s="120"/>
-    </row>
-    <row r="64" spans="1:8" ht="13.15">
+      <c r="G63" s="344"/>
+      <c r="H63" s="345"/>
+      <c r="I63" s="344"/>
+      <c r="J63" s="344"/>
+      <c r="K63" s="344"/>
+      <c r="L63" s="344"/>
+      <c r="M63" s="344"/>
+      <c r="N63" s="344"/>
+      <c r="O63" s="344"/>
+      <c r="P63" s="344"/>
+      <c r="Q63" s="344"/>
+    </row>
+    <row r="64" spans="1:17" ht="13.15">
       <c r="B64" s="132">
         <f>B55</f>
         <v>0</v>
@@ -16968,6 +17144,76 @@
     </row>
     <row r="94" spans="3:3">
       <c r="C94" s="115"/>
+    </row>
+    <row r="101" spans="3:17">
+      <c r="C101" s="344"/>
+      <c r="G101" s="344"/>
+      <c r="H101" s="344"/>
+      <c r="I101" s="344"/>
+      <c r="J101" s="344"/>
+      <c r="K101" s="344"/>
+      <c r="L101" s="344"/>
+      <c r="M101" s="344"/>
+      <c r="N101" s="344"/>
+      <c r="O101" s="344"/>
+      <c r="P101" s="344"/>
+      <c r="Q101" s="344"/>
+    </row>
+    <row r="102" spans="3:17">
+      <c r="C102" s="344"/>
+      <c r="G102" s="344"/>
+      <c r="H102" s="344"/>
+      <c r="I102" s="344"/>
+      <c r="J102" s="344"/>
+      <c r="K102" s="344"/>
+      <c r="L102" s="344"/>
+      <c r="M102" s="344"/>
+      <c r="N102" s="344"/>
+      <c r="O102" s="344"/>
+      <c r="P102" s="344"/>
+      <c r="Q102" s="344"/>
+    </row>
+    <row r="103" spans="3:17">
+      <c r="C103" s="344"/>
+      <c r="G103" s="344"/>
+      <c r="H103" s="344"/>
+      <c r="I103" s="344"/>
+      <c r="J103" s="344"/>
+      <c r="K103" s="344"/>
+      <c r="L103" s="344"/>
+      <c r="M103" s="344"/>
+      <c r="N103" s="344"/>
+      <c r="O103" s="344"/>
+      <c r="P103" s="344"/>
+      <c r="Q103" s="344"/>
+    </row>
+    <row r="104" spans="3:17">
+      <c r="C104" s="344"/>
+      <c r="G104" s="344"/>
+      <c r="H104" s="344"/>
+      <c r="I104" s="344"/>
+      <c r="J104" s="344"/>
+      <c r="K104" s="344"/>
+      <c r="L104" s="344"/>
+      <c r="M104" s="344"/>
+      <c r="N104" s="344"/>
+      <c r="O104" s="344"/>
+      <c r="P104" s="344"/>
+      <c r="Q104" s="344"/>
+    </row>
+    <row r="105" spans="3:17">
+      <c r="C105" s="344"/>
+      <c r="G105" s="344"/>
+      <c r="H105" s="344"/>
+      <c r="I105" s="344"/>
+      <c r="J105" s="344"/>
+      <c r="K105" s="344"/>
+      <c r="L105" s="344"/>
+      <c r="M105" s="344"/>
+      <c r="N105" s="344"/>
+      <c r="O105" s="344"/>
+      <c r="P105" s="344"/>
+      <c r="Q105" s="344"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -17070,7 +17316,7 @@
       <c r="B6" s="149" t="s">
         <v>442</v>
       </c>
-      <c r="C6" s="338">
+      <c r="C6" s="325">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
         <v>1945702920.0000002</v>
       </c>
@@ -17078,8 +17324,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="356"/>
-      <c r="F6" s="356"/>
+      <c r="E6" s="365"/>
+      <c r="F6" s="365"/>
       <c r="H6" s="120"/>
     </row>
     <row r="7" spans="2:8" ht="13.15">
@@ -18536,7 +18782,7 @@
       <c r="B7" s="100" t="s">
         <v>276</v>
       </c>
-      <c r="C7" s="114">
+      <c r="C7" s="344">
         <f>Normalized_FCF!G8</f>
         <v>174241905</v>
       </c>
@@ -18544,11 +18790,11 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="358" t="str">
+      <c r="E7" s="367" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!C11&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 5-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 10-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 濮阳惠成(300481.SZ). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="358"/>
+      <c r="F7" s="367"/>
       <c r="H7" s="247">
         <v>4</v>
       </c>
@@ -18561,7 +18807,7 @@
       <c r="B8" s="100" t="s">
         <v>66</v>
       </c>
-      <c r="C8" s="114">
+      <c r="C8" s="344">
         <f>Normalized_FCF!G19</f>
         <v>147540552.86390811</v>
       </c>
@@ -18569,8 +18815,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="358"/>
-      <c r="F8" s="358"/>
+      <c r="E8" s="367"/>
+      <c r="F8" s="367"/>
       <c r="H8" s="247">
         <v>5</v>
       </c>
@@ -18583,7 +18829,7 @@
       <c r="B9" s="100" t="s">
         <v>57</v>
       </c>
-      <c r="C9" s="114">
+      <c r="C9" s="344">
         <f>Normalized_FCF!C19</f>
         <v>129478796.10975</v>
       </c>
@@ -18591,8 +18837,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="358"/>
-      <c r="F9" s="358"/>
+      <c r="E9" s="367"/>
+      <c r="F9" s="367"/>
       <c r="H9" s="247">
         <v>6</v>
       </c>
@@ -18602,8 +18848,8 @@
       </c>
     </row>
     <row r="10" spans="2:9">
-      <c r="E10" s="358"/>
-      <c r="F10" s="358"/>
+      <c r="E10" s="367"/>
+      <c r="F10" s="367"/>
       <c r="H10" s="247">
         <v>7</v>
       </c>
@@ -18616,8 +18862,8 @@
       <c r="B11" s="159" t="s">
         <v>448</v>
       </c>
-      <c r="E11" s="358"/>
-      <c r="F11" s="358"/>
+      <c r="E11" s="367"/>
+      <c r="F11" s="367"/>
       <c r="H11" s="247">
         <v>8</v>
       </c>
@@ -18635,8 +18881,8 @@
         <v>4.2279727191083527E-3</v>
       </c>
       <c r="D12" s="158"/>
-      <c r="E12" s="358"/>
-      <c r="F12" s="358"/>
+      <c r="E12" s="367"/>
+      <c r="F12" s="367"/>
       <c r="H12" s="247">
         <v>9</v>
       </c>
@@ -18653,8 +18899,8 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-0.15075343519689044</v>
       </c>
-      <c r="E13" s="358"/>
-      <c r="F13" s="358"/>
+      <c r="E13" s="367"/>
+      <c r="F13" s="367"/>
       <c r="H13" s="247">
         <v>10</v>
       </c>
@@ -18671,8 +18917,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-0.15795268346639479</v>
       </c>
-      <c r="E14" s="358"/>
-      <c r="F14" s="358"/>
+      <c r="E14" s="367"/>
+      <c r="F14" s="367"/>
     </row>
     <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
@@ -18698,21 +18944,21 @@
       <c r="C18" s="150">
         <v>5</v>
       </c>
-      <c r="E18" s="358" t="s">
+      <c r="E18" s="367" t="s">
         <v>331</v>
       </c>
-      <c r="F18" s="359"/>
+      <c r="F18" s="368"/>
     </row>
     <row r="19" spans="2:6">
-      <c r="E19" s="359"/>
-      <c r="F19" s="359"/>
+      <c r="E19" s="368"/>
+      <c r="F19" s="368"/>
     </row>
     <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="159" t="s">
         <v>304</v>
       </c>
-      <c r="E20" s="359"/>
-      <c r="F20" s="359"/>
+      <c r="E20" s="368"/>
+      <c r="F20" s="368"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
@@ -18726,8 +18972,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E21" s="359"/>
-      <c r="F21" s="359"/>
+      <c r="E21" s="368"/>
+      <c r="F21" s="368"/>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
@@ -18741,8 +18987,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E22" s="359"/>
-      <c r="F22" s="359"/>
+      <c r="E22" s="368"/>
+      <c r="F22" s="368"/>
     </row>
     <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="159" t="s">
@@ -18762,8 +19008,8 @@
         <v>5</v>
       </c>
       <c r="D25" s="163"/>
-      <c r="E25" s="357"/>
-      <c r="F25" s="357"/>
+      <c r="E25" s="366"/>
+      <c r="F25" s="366"/>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" s="118" t="s">
@@ -18773,8 +19019,8 @@
         <v>0.04</v>
       </c>
       <c r="D26" s="164"/>
-      <c r="E26" s="357"/>
-      <c r="F26" s="357"/>
+      <c r="E26" s="366"/>
+      <c r="F26" s="366"/>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
@@ -18788,8 +19034,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E27" s="357"/>
-      <c r="F27" s="357"/>
+      <c r="E27" s="366"/>
+      <c r="F27" s="366"/>
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
@@ -18799,8 +19045,8 @@
         <v>0.6</v>
       </c>
       <c r="D28" s="165"/>
-      <c r="E28" s="357"/>
-      <c r="F28" s="357"/>
+      <c r="E28" s="366"/>
+      <c r="F28" s="366"/>
     </row>
     <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="159" t="s">
@@ -18820,8 +19066,8 @@
         <v>5</v>
       </c>
       <c r="D31" s="163"/>
-      <c r="E31" s="357"/>
-      <c r="F31" s="357"/>
+      <c r="E31" s="366"/>
+      <c r="F31" s="366"/>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="118" t="s">
@@ -18831,8 +19077,8 @@
         <v>0.02</v>
       </c>
       <c r="D32" s="164"/>
-      <c r="E32" s="357"/>
-      <c r="F32" s="357"/>
+      <c r="E32" s="366"/>
+      <c r="F32" s="366"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
@@ -18846,8 +19092,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E33" s="357"/>
-      <c r="F33" s="357"/>
+      <c r="E33" s="366"/>
+      <c r="F33" s="366"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
@@ -18857,8 +19103,8 @@
         <v>0.2</v>
       </c>
       <c r="D34" s="165"/>
-      <c r="E34" s="357"/>
-      <c r="F34" s="357"/>
+      <c r="E34" s="366"/>
+      <c r="F34" s="366"/>
     </row>
     <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="159" t="s">
@@ -18878,8 +19124,8 @@
         <v>5</v>
       </c>
       <c r="D37" s="163"/>
-      <c r="E37" s="357"/>
-      <c r="F37" s="357"/>
+      <c r="E37" s="366"/>
+      <c r="F37" s="366"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="118" t="s">
@@ -18889,8 +19135,8 @@
         <v>0.06</v>
       </c>
       <c r="D38" s="164"/>
-      <c r="E38" s="357"/>
-      <c r="F38" s="357"/>
+      <c r="E38" s="366"/>
+      <c r="F38" s="366"/>
     </row>
     <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
@@ -18904,8 +19150,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E39" s="357"/>
-      <c r="F39" s="357"/>
+      <c r="E39" s="366"/>
+      <c r="F39" s="366"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
@@ -18916,8 +19162,8 @@
         <v>0.2</v>
       </c>
       <c r="D40" s="165"/>
-      <c r="E40" s="357"/>
-      <c r="F40" s="357"/>
+      <c r="E40" s="366"/>
+      <c r="F40" s="366"/>
     </row>
     <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
@@ -18979,8 +19225,8 @@
         <v>10</v>
       </c>
       <c r="D49" s="163"/>
-      <c r="E49" s="357"/>
-      <c r="F49" s="357"/>
+      <c r="E49" s="366"/>
+      <c r="F49" s="366"/>
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="118" t="s">
@@ -18990,8 +19236,8 @@
         <v>0</v>
       </c>
       <c r="D50" s="164"/>
-      <c r="E50" s="357"/>
-      <c r="F50" s="357"/>
+      <c r="E50" s="366"/>
+      <c r="F50" s="366"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
@@ -19005,8 +19251,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E51" s="357"/>
-      <c r="F51" s="357"/>
+      <c r="E51" s="366"/>
+      <c r="F51" s="366"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
@@ -19016,8 +19262,8 @@
         <v>0.05</v>
       </c>
       <c r="D52" s="165"/>
-      <c r="E52" s="357"/>
-      <c r="F52" s="357"/>
+      <c r="E52" s="366"/>
+      <c r="F52" s="366"/>
     </row>
     <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="159" t="s">
@@ -19037,8 +19283,8 @@
         <v>10</v>
       </c>
       <c r="D55" s="163"/>
-      <c r="E55" s="357"/>
-      <c r="F55" s="357"/>
+      <c r="E55" s="366"/>
+      <c r="F55" s="366"/>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="118" t="s">
@@ -19048,8 +19294,8 @@
         <v>0.08</v>
       </c>
       <c r="D56" s="164"/>
-      <c r="E56" s="357"/>
-      <c r="F56" s="357"/>
+      <c r="E56" s="366"/>
+      <c r="F56" s="366"/>
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
@@ -19063,8 +19309,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E57" s="357"/>
-      <c r="F57" s="357"/>
+      <c r="E57" s="366"/>
+      <c r="F57" s="366"/>
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
@@ -19074,8 +19320,8 @@
         <v>0.05</v>
       </c>
       <c r="D58" s="165"/>
-      <c r="E58" s="357"/>
-      <c r="F58" s="357"/>
+      <c r="E58" s="366"/>
+      <c r="F58" s="366"/>
     </row>
     <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
@@ -19259,7 +19505,7 @@
       </c>
       <c r="C80" s="167">
         <f>Thesis!F29</f>
-        <v>0.33699999999999997</v>
+        <v>0.33700000000000002</v>
       </c>
     </row>
     <row r="81" spans="2:8">
@@ -19268,7 +19514,7 @@
       </c>
       <c r="C81" s="116">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>0.69031028314322296</v>
+        <v>0.69031028314322285</v>
       </c>
       <c r="D81" s="116"/>
       <c r="E81" s="100"/>

--- a/financial_models/opportunities/300481.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/300481.SZ_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E554D39-EDF6-4748-AB19-1AE8C34F1C7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{822D022A-8691-4F10-8ABA-B52302F01655}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3895,29 +3895,29 @@
     <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4335,7 +4335,7 @@
         <v>95</v>
       </c>
       <c r="C12" s="50">
-        <v>13.47</v>
+        <v>13.48</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>3931.2927498600002</v>
+        <v>3934.2113042400001</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4393,13 +4393,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="357" t="s">
+      <c r="B18" s="359" t="s">
         <v>360</v>
       </c>
-      <c r="C18" s="357"/>
-      <c r="D18" s="357"/>
-      <c r="E18" s="357"/>
-      <c r="F18" s="357"/>
+      <c r="C18" s="359"/>
+      <c r="D18" s="359"/>
+      <c r="E18" s="359"/>
+      <c r="F18" s="359"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4482,7 +4482,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>-5.4450928827774248E-2</v>
+        <v>-5.4692532865156962E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4524,7 +4524,7 @@
         <v>425</v>
       </c>
       <c r="F29" s="302">
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="30" spans="2:6">
@@ -4599,22 +4599,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="357" t="s">
+      <c r="B36" s="359" t="s">
         <v>361</v>
       </c>
-      <c r="C36" s="357"/>
-      <c r="D36" s="357"/>
-      <c r="E36" s="357"/>
-      <c r="F36" s="357"/>
+      <c r="C36" s="359"/>
+      <c r="D36" s="359"/>
+      <c r="E36" s="359"/>
+      <c r="F36" s="359"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="359" t="s">
+      <c r="B37" s="362" t="s">
         <v>340</v>
       </c>
-      <c r="C37" s="359"/>
-      <c r="D37" s="359"/>
-      <c r="E37" s="359"/>
-      <c r="F37" s="359"/>
+      <c r="C37" s="362"/>
+      <c r="D37" s="362"/>
+      <c r="E37" s="362"/>
+      <c r="F37" s="362"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4626,13 +4626,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="358" t="s">
+      <c r="B40" s="360" t="s">
         <v>232</v>
       </c>
-      <c r="C40" s="358"/>
-      <c r="D40" s="358"/>
-      <c r="E40" s="358"/>
-      <c r="F40" s="358"/>
+      <c r="C40" s="360"/>
+      <c r="D40" s="360"/>
+      <c r="E40" s="360"/>
+      <c r="F40" s="360"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4652,13 +4652,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="358" t="s">
+      <c r="B43" s="360" t="s">
         <v>234</v>
       </c>
-      <c r="C43" s="358"/>
-      <c r="D43" s="358"/>
-      <c r="E43" s="358"/>
-      <c r="F43" s="358"/>
+      <c r="C43" s="360"/>
+      <c r="D43" s="360"/>
+      <c r="E43" s="360"/>
+      <c r="F43" s="360"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4687,13 +4687,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="358" t="s">
+      <c r="B47" s="360" t="s">
         <v>237</v>
       </c>
-      <c r="C47" s="358"/>
-      <c r="D47" s="358"/>
-      <c r="E47" s="358"/>
-      <c r="F47" s="358"/>
+      <c r="C47" s="360"/>
+      <c r="D47" s="360"/>
+      <c r="E47" s="360"/>
+      <c r="F47" s="360"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4709,13 +4709,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="358" t="s">
+      <c r="B50" s="360" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="358"/>
-      <c r="D50" s="358"/>
-      <c r="E50" s="358"/>
-      <c r="F50" s="358"/>
+      <c r="C50" s="360"/>
+      <c r="D50" s="360"/>
+      <c r="E50" s="360"/>
+      <c r="F50" s="360"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4779,13 +4779,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="358" t="s">
+      <c r="B58" s="360" t="s">
         <v>242</v>
       </c>
-      <c r="C58" s="358"/>
-      <c r="D58" s="358"/>
-      <c r="E58" s="358"/>
-      <c r="F58" s="358"/>
+      <c r="C58" s="360"/>
+      <c r="D58" s="360"/>
+      <c r="E58" s="360"/>
+      <c r="F58" s="360"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4801,7 +4801,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="358" t="s">
+      <c r="B61" s="360" t="s">
         <v>339</v>
       </c>
       <c r="C61" s="361"/>
@@ -4823,22 +4823,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="357" t="s">
+      <c r="B64" s="359" t="s">
         <v>344</v>
       </c>
-      <c r="C64" s="357"/>
-      <c r="D64" s="357"/>
-      <c r="E64" s="357"/>
-      <c r="F64" s="357"/>
+      <c r="C64" s="359"/>
+      <c r="D64" s="359"/>
+      <c r="E64" s="359"/>
+      <c r="F64" s="359"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="357" t="s">
+      <c r="B65" s="359" t="s">
         <v>362</v>
       </c>
-      <c r="C65" s="357"/>
-      <c r="D65" s="357"/>
-      <c r="E65" s="357"/>
-      <c r="F65" s="357"/>
+      <c r="C65" s="359"/>
+      <c r="D65" s="359"/>
+      <c r="E65" s="359"/>
+      <c r="F65" s="359"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4872,7 +4872,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>3.2935424642278541E-2</v>
+        <v>3.2910991834680409E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4882,7 +4882,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>2.9695619896065329E-2</v>
+        <v>2.967359050445104E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>449</v>
@@ -4973,22 +4973,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="357" t="s">
+      <c r="B80" s="359" t="s">
         <v>363</v>
       </c>
-      <c r="C80" s="357"/>
-      <c r="D80" s="357"/>
-      <c r="E80" s="357"/>
-      <c r="F80" s="357"/>
+      <c r="C80" s="359"/>
+      <c r="D80" s="359"/>
+      <c r="E80" s="359"/>
+      <c r="F80" s="359"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="359" t="s">
+      <c r="B81" s="362" t="s">
         <v>253</v>
       </c>
-      <c r="C81" s="359"/>
-      <c r="D81" s="359"/>
-      <c r="E81" s="359"/>
-      <c r="F81" s="359"/>
+      <c r="C81" s="362"/>
+      <c r="D81" s="362"/>
+      <c r="E81" s="362"/>
+      <c r="F81" s="362"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5032,22 +5032,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="357" t="s">
+      <c r="B89" s="359" t="s">
         <v>364</v>
       </c>
-      <c r="C89" s="357"/>
-      <c r="D89" s="357"/>
-      <c r="E89" s="357"/>
-      <c r="F89" s="357"/>
+      <c r="C89" s="359"/>
+      <c r="D89" s="359"/>
+      <c r="E89" s="359"/>
+      <c r="F89" s="359"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="357" t="s">
+      <c r="B90" s="359" t="s">
         <v>365</v>
       </c>
-      <c r="C90" s="357"/>
-      <c r="D90" s="357"/>
-      <c r="E90" s="357"/>
-      <c r="F90" s="357"/>
+      <c r="C90" s="359"/>
+      <c r="D90" s="359"/>
+      <c r="E90" s="359"/>
+      <c r="F90" s="359"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5084,13 +5084,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="357" t="s">
+      <c r="B97" s="359" t="s">
         <v>366</v>
       </c>
-      <c r="C97" s="357"/>
-      <c r="D97" s="357"/>
-      <c r="E97" s="357"/>
-      <c r="F97" s="357"/>
+      <c r="C97" s="359"/>
+      <c r="D97" s="359"/>
+      <c r="E97" s="359"/>
+      <c r="F97" s="359"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5103,13 +5103,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="357" t="s">
+      <c r="B101" s="359" t="s">
         <v>345</v>
       </c>
-      <c r="C101" s="357"/>
-      <c r="D101" s="357"/>
-      <c r="E101" s="357"/>
-      <c r="F101" s="357"/>
+      <c r="C101" s="359"/>
+      <c r="D101" s="359"/>
+      <c r="E101" s="359"/>
+      <c r="F101" s="359"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5231,13 +5231,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="357" t="s">
+      <c r="B116" s="359" t="s">
         <v>367</v>
       </c>
-      <c r="C116" s="357"/>
-      <c r="D116" s="357"/>
-      <c r="E116" s="357"/>
-      <c r="F116" s="357"/>
+      <c r="C116" s="359"/>
+      <c r="D116" s="359"/>
+      <c r="E116" s="359"/>
+      <c r="F116" s="359"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5276,13 +5276,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="358" t="s">
+      <c r="B123" s="360" t="s">
         <v>368</v>
       </c>
-      <c r="C123" s="358"/>
-      <c r="D123" s="358"/>
-      <c r="E123" s="358"/>
-      <c r="F123" s="358"/>
+      <c r="C123" s="360"/>
+      <c r="D123" s="360"/>
+      <c r="E123" s="360"/>
+      <c r="F123" s="360"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5425,13 +5425,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="362" t="s">
+      <c r="B134" s="363" t="s">
         <v>371</v>
       </c>
-      <c r="C134" s="362"/>
-      <c r="D134" s="362"/>
-      <c r="E134" s="362"/>
-      <c r="F134" s="362"/>
+      <c r="C134" s="363"/>
+      <c r="D134" s="363"/>
+      <c r="E134" s="363"/>
+      <c r="F134" s="363"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5444,22 +5444,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="360" t="s">
+      <c r="B138" s="364" t="s">
         <v>369</v>
       </c>
-      <c r="C138" s="360"/>
-      <c r="D138" s="360"/>
-      <c r="E138" s="360"/>
-      <c r="F138" s="360"/>
+      <c r="C138" s="364"/>
+      <c r="D138" s="364"/>
+      <c r="E138" s="364"/>
+      <c r="F138" s="364"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="357" t="s">
+      <c r="B139" s="359" t="s">
         <v>370</v>
       </c>
-      <c r="C139" s="357"/>
-      <c r="D139" s="357"/>
-      <c r="E139" s="357"/>
-      <c r="F139" s="357"/>
+      <c r="C139" s="359"/>
+      <c r="D139" s="359"/>
+      <c r="E139" s="359"/>
+      <c r="F139" s="359"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C142" s="224">
         <f>F29</f>
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="C146" s="297">
         <f>F29</f>
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="147" spans="2:4">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="C147" s="216">
         <f>Scenarios!C81</f>
-        <v>0.69031028314322285</v>
+        <v>0.69031028314322296</v>
       </c>
     </row>
     <row r="148" spans="2:4">
@@ -5792,13 +5792,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="364" t="s">
+      <c r="B179" s="358" t="s">
         <v>377</v>
       </c>
-      <c r="C179" s="357"/>
-      <c r="D179" s="357"/>
-      <c r="E179" s="357"/>
-      <c r="F179" s="357"/>
+      <c r="C179" s="359"/>
+      <c r="D179" s="359"/>
+      <c r="E179" s="359"/>
+      <c r="F179" s="359"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5835,13 +5835,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="358" t="s">
+      <c r="B188" s="360" t="s">
         <v>382</v>
       </c>
-      <c r="C188" s="358"/>
-      <c r="D188" s="358"/>
-      <c r="E188" s="358"/>
-      <c r="F188" s="358"/>
+      <c r="C188" s="360"/>
+      <c r="D188" s="360"/>
+      <c r="E188" s="360"/>
+      <c r="F188" s="360"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5849,22 +5849,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="363" t="s">
+      <c r="B191" s="357" t="s">
         <v>383</v>
       </c>
-      <c r="C191" s="363"/>
-      <c r="D191" s="363"/>
-      <c r="E191" s="363"/>
-      <c r="F191" s="363"/>
+      <c r="C191" s="357"/>
+      <c r="D191" s="357"/>
+      <c r="E191" s="357"/>
+      <c r="F191" s="357"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="363" t="s">
+      <c r="B192" s="357" t="s">
         <v>384</v>
       </c>
-      <c r="C192" s="363"/>
-      <c r="D192" s="363"/>
-      <c r="E192" s="363"/>
-      <c r="F192" s="363"/>
+      <c r="C192" s="357"/>
+      <c r="D192" s="357"/>
+      <c r="E192" s="357"/>
+      <c r="F192" s="357"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5888,17 +5888,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5915,6 +5904,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13484,32 +13484,32 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>2.9695619896065329E-2</v>
+        <v>2.967359050445104E-2</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>2.9695619896065329E-2</v>
+        <v>2.967359050445104E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>2.9695619896065329E-2</v>
+        <v>2.967359050445104E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>2.9695619896065329E-2</v>
+        <v>2.967359050445104E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
-        <v>2.9695619896065329E-2</v>
+        <v>2.967359050445104E-2</v>
       </c>
       <c r="K93" s="23">
         <f t="shared" si="39"/>
-        <v>1.4847809948032665E-2</v>
+        <v>1.483679525222552E-2</v>
       </c>
       <c r="L93" s="23">
         <f t="shared" si="39"/>
-        <v>1.4847809948032665E-2</v>
+        <v>1.483679525222552E-2</v>
       </c>
       <c r="M93" s="23">
         <f t="shared" si="39"/>
@@ -14683,50 +14683,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>3.2935424642278541E-2</v>
+        <v>3.2910991834680409E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>3.7529780215213498E-2</v>
+        <v>3.7501939131967796E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>4.9352484517332491E-2</v>
+        <v>4.9315872881933877E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>9.7069426506143447E-2</v>
+        <v>9.6997416545827317E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>6.2858864648623544E-2</v>
+        <v>6.2812233443394594E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>4.7005690667350941E-2</v>
+        <v>4.697081997694489E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>3.9051236878363767E-2</v>
+        <v>3.9022267118068249E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>2.7537452977398059E-2</v>
+        <v>2.7517024599818387E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>2.5033044665397821E-2</v>
+        <v>2.5014474157485804E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>1.6562141804961916E-2</v>
+        <v>1.654985534961699E-2</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>1.619418777761264E-2</v>
+        <v>1.6182174285196013E-2</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14740,43 +14740,43 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.8719389825858356E-2</v>
+        <v>4.8683247845275369E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.9796892258499844E-2</v>
+        <v>5.9752532546141907E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10739516664461972</v>
+        <v>0.10731549663969046</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.4200147650919151E-2</v>
+        <v>6.4152521428626194E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.5443387803251759E-2</v>
+        <v>4.5409676091231539E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.6812438861276289E-2</v>
+        <v>3.6785129930370301E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.6898617510427277E-2</v>
+        <v>2.6878663046398771E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.8723134776116899E-2</v>
+        <v>1.8709245210259243E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.6428717755069249E-2</v>
+        <v>1.6416530278989823E-2</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.4623587623192727E-2</v>
+        <v>1.4612739264421812E-2</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18726,7 +18726,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-13.47</v>
+        <v>-13.48</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18966,7 +18966,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>13.47</v>
+        <v>13.48</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19505,7 +19505,7 @@
       </c>
       <c r="C80" s="167">
         <f>Thesis!F29</f>
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="81" spans="2:8">
@@ -19514,7 +19514,7 @@
       </c>
       <c r="C81" s="116">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>0.69031028314322285</v>
+        <v>0.69031028314322296</v>
       </c>
       <c r="D81" s="116"/>
       <c r="E81" s="100"/>
@@ -19564,7 +19564,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>13.47</v>
+        <v>13.48</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19577,7 +19577,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>-5.4450928827774248E-2</v>
+        <v>-5.4692532865156962E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/300481.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/300481.SZ_Valuation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kamanl/PycharmProjects/Invest_Proc/financial_models/opportunities/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F503A437-39E5-4DFB-811C-1A095F6CE386}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0290A198-A1FF-6143-B7F3-3E3FC4E852E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="17120" windowHeight="10760" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -38,6 +38,17 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
     <ext uri="GoogleSheetsCustomDataVersion1">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId9" roundtripDataSignature="AMtx7mi73Cg0ax9bLfpeUuF69nNRn7idDQ=="/>
@@ -2499,7 +2510,7 @@
     <numFmt numFmtId="180" formatCode="0.000000000000000%"/>
     <numFmt numFmtId="181" formatCode="#,##0_);\(#,##0\);0;@"/>
   </numFmts>
-  <fonts count="59">
+  <fonts count="59" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -3891,30 +3902,30 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -3929,7 +3940,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="常规 2 2" xfId="1" xr:uid="{A35F4541-DCCE-4554-A311-39480A36979A}"/>
   </cellStyles>
   <dxfs count="8">
@@ -4218,16 +4229,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J197"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="2.73046875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="32.73046875" style="1" customWidth="1"/>
-    <col min="3" max="4" width="25.73046875" style="1" customWidth="1"/>
-    <col min="5" max="6" width="15.73046875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="32.6640625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="25.6640625" style="1" customWidth="1"/>
+    <col min="5" max="6" width="15.6640625" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B1" s="3" t="s">
         <v>41</v>
       </c>
@@ -4244,7 +4255,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="13.9">
+    <row r="2" spans="1:10" ht="16" x14ac:dyDescent="0.25">
       <c r="A2" s="222" t="s">
         <v>267</v>
       </c>
@@ -4258,7 +4269,7 @@
       <c r="I2" s="22"/>
       <c r="J2" s="22"/>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B4" s="45" t="s">
         <v>415</v>
       </c>
@@ -4267,7 +4278,7 @@
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
     </row>
-    <row r="5" spans="1:10" ht="12.4">
+    <row r="5" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="B5" s="4" t="s">
         <v>315</v>
       </c>
@@ -4275,7 +4286,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B6" s="4" t="s">
         <v>0</v>
       </c>
@@ -4284,7 +4295,7 @@
       </c>
       <c r="E6" s="48"/>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B7" s="2" t="s">
         <v>307</v>
       </c>
@@ -4294,7 +4305,7 @@
       <c r="D7" s="48"/>
       <c r="E7" s="48"/>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B8" s="1" t="s">
         <v>268</v>
       </c>
@@ -4304,17 +4315,17 @@
       </c>
       <c r="E8" s="48"/>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.15">
       <c r="E9" s="34"/>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B10" s="45" t="s">
         <v>418</v>
       </c>
       <c r="C10" s="46"/>
       <c r="E10" s="34"/>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B11" s="1" t="s">
         <v>417</v>
       </c>
@@ -4326,17 +4337,17 @@
       </c>
       <c r="E11" s="34"/>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B12" s="4" t="s">
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>13.46</v>
+        <v>13.53</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B13" s="1" t="s">
         <v>416</v>
       </c>
@@ -4346,13 +4357,13 @@
       <c r="D13" s="48"/>
       <c r="E13" s="5"/>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B14" s="4" t="s">
         <v>420</v>
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>3928.3741954799998</v>
+        <v>3948.8040761399998</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4360,7 +4371,7 @@
       </c>
       <c r="E14" s="5"/>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B15" s="4" t="s">
         <v>419</v>
       </c>
@@ -4374,7 +4385,7 @@
       </c>
       <c r="E15" s="5"/>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B16" s="4" t="s">
         <v>1</v>
       </c>
@@ -4384,27 +4395,27 @@
       <c r="D16" s="50"/>
       <c r="E16" s="5"/>
     </row>
-    <row r="17" spans="2:6">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.15">
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
     </row>
-    <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="358" t="s">
+    <row r="18" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B18" s="356" t="s">
         <v>359</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
-    </row>
-    <row r="20" spans="2:6">
+      <c r="C18" s="356"/>
+      <c r="D18" s="356"/>
+      <c r="E18" s="356"/>
+      <c r="F18" s="356"/>
+    </row>
+    <row r="20" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B20" s="45" t="s">
         <v>306</v>
       </c>
       <c r="C20" s="46"/>
       <c r="D20" s="5"/>
     </row>
-    <row r="21" spans="2:6">
+    <row r="21" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B21" s="2" t="s">
         <v>348</v>
       </c>
@@ -4419,7 +4430,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="22" spans="2:6">
+    <row r="22" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B22" s="2" t="s">
         <v>56</v>
       </c>
@@ -4432,7 +4443,7 @@
       </c>
       <c r="E22" s="313"/>
     </row>
-    <row r="23" spans="2:6">
+    <row r="23" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B23" s="1" t="s">
         <v>434</v>
       </c>
@@ -4440,7 +4451,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="24" spans="2:6">
+    <row r="24" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B24" s="1" t="s">
         <v>435</v>
       </c>
@@ -4448,7 +4459,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="25" spans="2:6">
+    <row r="25" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B25" s="4" t="s">
         <v>347</v>
       </c>
@@ -4464,7 +4475,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="2:6">
+    <row r="26" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B26" s="1" t="str">
         <f>"Expected Equity Value ("&amp;C13&amp;") :"</f>
         <v>Expected Equity Value (CNY) :</v>
@@ -4478,14 +4489,14 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>-5.4209080354837624E-2</v>
-      </c>
-    </row>
-    <row r="27" spans="2:6">
+        <v>-5.5896901541827249E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6" x14ac:dyDescent="0.15">
       <c r="D27" s="5"/>
       <c r="E27" s="5"/>
     </row>
-    <row r="28" spans="2:6">
+    <row r="28" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B28" s="45" t="s">
         <v>433</v>
       </c>
@@ -4504,7 +4515,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="2:6">
+    <row r="29" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B29" s="1" t="s">
         <v>425</v>
       </c>
@@ -4520,10 +4531,10 @@
         <v>424</v>
       </c>
       <c r="F29" s="302">
-        <v>0.33700000000000002</v>
-      </c>
-    </row>
-    <row r="30" spans="2:6">
+        <v>0.33699999999999997</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B30" s="1" t="s">
         <v>426</v>
       </c>
@@ -4542,7 +4553,7 @@
         <v>0.187</v>
       </c>
     </row>
-    <row r="31" spans="2:6">
+    <row r="31" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B31" s="1" t="s">
         <v>427</v>
       </c>
@@ -4561,7 +4572,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="32" spans="2:6">
+    <row r="32" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B32" s="1" t="s">
         <v>428</v>
       </c>
@@ -4580,11 +4591,11 @@
         <v>8.6999999999999994E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:6">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.15">
       <c r="D33" s="5"/>
       <c r="E33" s="5"/>
     </row>
-    <row r="34" spans="1:6" ht="13.9">
+    <row r="34" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A34" s="222" t="s">
         <v>354</v>
       </c>
@@ -4594,25 +4605,25 @@
       <c r="E34" s="36"/>
       <c r="F34" s="36"/>
     </row>
-    <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="358" t="s">
+    <row r="36" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B36" s="356" t="s">
         <v>360</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
-    </row>
-    <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="361" t="s">
+      <c r="C36" s="356"/>
+      <c r="D36" s="356"/>
+      <c r="E36" s="356"/>
+      <c r="F36" s="356"/>
+    </row>
+    <row r="37" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B37" s="358" t="s">
         <v>339</v>
       </c>
-      <c r="C37" s="361"/>
-      <c r="D37" s="361"/>
-      <c r="E37" s="361"/>
-      <c r="F37" s="361"/>
-    </row>
-    <row r="39" spans="1:6">
+      <c r="C37" s="358"/>
+      <c r="D37" s="358"/>
+      <c r="E37" s="358"/>
+      <c r="F37" s="358"/>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B39" s="210" t="s">
         <v>230</v>
       </c>
@@ -4621,16 +4632,16 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="359" t="s">
+    <row r="40" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B40" s="357" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
-    </row>
-    <row r="41" spans="1:6">
+      <c r="C40" s="357"/>
+      <c r="D40" s="357"/>
+      <c r="E40" s="357"/>
+      <c r="F40" s="357"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B41" s="47" t="s">
         <v>232</v>
       </c>
@@ -4643,20 +4654,20 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="42" spans="1:6">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B42" s="47"/>
       <c r="C42" s="76"/>
     </row>
-    <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="359" t="s">
+    <row r="43" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B43" s="357" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
-    </row>
-    <row r="44" spans="1:6">
+      <c r="C43" s="357"/>
+      <c r="D43" s="357"/>
+      <c r="E43" s="357"/>
+      <c r="F43" s="357"/>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B44" s="47" t="s">
         <v>234</v>
       </c>
@@ -4669,7 +4680,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="45" spans="1:6">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B45" s="52" t="s">
         <v>235</v>
       </c>
@@ -4682,16 +4693,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B47" s="357" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
-    </row>
-    <row r="48" spans="1:6">
+      <c r="C47" s="357"/>
+      <c r="D47" s="357"/>
+      <c r="E47" s="357"/>
+      <c r="F47" s="357"/>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B48" s="47" t="s">
         <v>237</v>
       </c>
@@ -4704,16 +4715,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+    <row r="50" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B50" s="357" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
-    </row>
-    <row r="51" spans="2:6">
+      <c r="C50" s="357"/>
+      <c r="D50" s="357"/>
+      <c r="E50" s="357"/>
+      <c r="F50" s="357"/>
+    </row>
+    <row r="51" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B51" s="47" t="s">
         <v>340</v>
       </c>
@@ -4728,7 +4739,7 @@
       <c r="E51" s="286"/>
       <c r="F51" s="286"/>
     </row>
-    <row r="52" spans="2:6">
+    <row r="52" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B52" s="47" t="s">
         <v>341</v>
       </c>
@@ -4743,7 +4754,7 @@
       <c r="E52" s="286"/>
       <c r="F52" s="286"/>
     </row>
-    <row r="53" spans="2:6">
+    <row r="53" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B53" s="47" t="s">
         <v>238</v>
       </c>
@@ -4756,12 +4767,12 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="55" spans="2:6">
+    <row r="55" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B55" s="1" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="56" spans="2:6">
+    <row r="56" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B56" s="47" t="s">
         <v>265</v>
       </c>
@@ -4774,16 +4785,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+    <row r="58" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B58" s="357" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
-    </row>
-    <row r="59" spans="2:6">
+      <c r="C58" s="357"/>
+      <c r="D58" s="357"/>
+      <c r="E58" s="357"/>
+      <c r="F58" s="357"/>
+    </row>
+    <row r="59" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B59" s="47" t="s">
         <v>239</v>
       </c>
@@ -4796,8 +4807,8 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+    <row r="61" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B61" s="357" t="s">
         <v>338</v>
       </c>
       <c r="C61" s="360"/>
@@ -4805,7 +4816,7 @@
       <c r="E61" s="360"/>
       <c r="F61" s="360"/>
     </row>
-    <row r="62" spans="2:6">
+    <row r="62" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B62" s="47" t="s">
         <v>242</v>
       </c>
@@ -4818,25 +4829,25 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="358" t="s">
+    <row r="64" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B64" s="356" t="s">
         <v>343</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
-    </row>
-    <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="C64" s="356"/>
+      <c r="D64" s="356"/>
+      <c r="E64" s="356"/>
+      <c r="F64" s="356"/>
+    </row>
+    <row r="65" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B65" s="356" t="s">
         <v>361</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
-    </row>
-    <row r="67" spans="1:6">
+      <c r="C65" s="356"/>
+      <c r="D65" s="356"/>
+      <c r="E65" s="356"/>
+      <c r="F65" s="356"/>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B67" s="47" t="s">
         <v>270</v>
       </c>
@@ -4849,7 +4860,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="68" spans="1:6">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B68" s="47" t="s">
         <v>248</v>
       </c>
@@ -4862,23 +4873,23 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="69" spans="1:6">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B69" s="227" t="s">
         <v>390</v>
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>3.2959893754197021E-2</v>
+        <v>3.2789369544086615E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
-    <row r="70" spans="1:6">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B70" s="227" t="s">
         <v>308</v>
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>2.9717682020802376E-2</v>
+        <v>2.9563932002956397E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>448</v>
@@ -4888,7 +4899,7 @@
         <v>0.90163160847623214</v>
       </c>
     </row>
-    <row r="72" spans="1:6">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B72" s="210" t="s">
         <v>450</v>
       </c>
@@ -4899,7 +4910,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="73" spans="1:6">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B73" s="47" t="s">
         <v>451</v>
       </c>
@@ -4912,7 +4923,7 @@
         <v>7.2897649409175577E-2</v>
       </c>
     </row>
-    <row r="74" spans="1:6">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B74" s="259" t="str">
         <f>Normalized_FCF!B117</f>
         <v>Pre-tax Profit/Sales</v>
@@ -4926,7 +4937,7 @@
         <v>0.12459084820450472</v>
       </c>
     </row>
-    <row r="75" spans="1:6">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B75" s="259" t="str">
         <f>Normalized_FCF!B118</f>
         <v>Sales/Total Assets</v>
@@ -4940,7 +4951,7 @@
         <v>0.50157874313934503</v>
       </c>
     </row>
-    <row r="76" spans="1:6">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B76" s="259" t="str">
         <f>Normalized_FCF!B119</f>
         <v>Total Assets/Equity</v>
@@ -4954,7 +4965,7 @@
         <v>1.1665094444773738</v>
       </c>
     </row>
-    <row r="78" spans="1:6" ht="13.9">
+    <row r="78" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A78" s="222" t="s">
         <v>355</v>
       </c>
@@ -4964,34 +4975,34 @@
       <c r="E78" s="36"/>
       <c r="F78" s="36"/>
     </row>
-    <row r="79" spans="1:6">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A79" s="209"/>
     </row>
-    <row r="80" spans="1:6" ht="24.6" customHeight="1">
+    <row r="80" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="356" t="s">
         <v>362</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
-    </row>
-    <row r="81" spans="1:6">
-      <c r="B81" s="361" t="s">
+      <c r="C80" s="356"/>
+      <c r="D80" s="356"/>
+      <c r="E80" s="356"/>
+      <c r="F80" s="356"/>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B81" s="358" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="361"/>
-      <c r="D81" s="361"/>
-      <c r="E81" s="361"/>
-      <c r="F81" s="361"/>
-    </row>
-    <row r="83" spans="1:6">
+      <c r="C81" s="358"/>
+      <c r="D81" s="358"/>
+      <c r="E81" s="358"/>
+      <c r="F81" s="358"/>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B83" s="210" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="84" spans="1:6">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B84" s="1" t="s">
         <v>431</v>
       </c>
@@ -5000,7 +5011,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="85" spans="1:6">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B85" s="1" t="s">
         <v>430</v>
       </c>
@@ -5009,7 +5020,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:6">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B86" s="80" t="s">
         <v>247</v>
       </c>
@@ -5018,34 +5029,34 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="87" spans="1:6">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.15">
       <c r="C87" s="121"/>
     </row>
-    <row r="88" spans="1:6">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B88" s="293" t="s">
         <v>356</v>
       </c>
       <c r="C88" s="121"/>
     </row>
-    <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="358" t="s">
+    <row r="89" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B89" s="356" t="s">
         <v>363</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
-    </row>
-    <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="C89" s="356"/>
+      <c r="D89" s="356"/>
+      <c r="E89" s="356"/>
+      <c r="F89" s="356"/>
+    </row>
+    <row r="90" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B90" s="356" t="s">
         <v>364</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
-    </row>
-    <row r="92" spans="1:6">
+      <c r="C90" s="356"/>
+      <c r="D90" s="356"/>
+      <c r="E90" s="356"/>
+      <c r="F90" s="356"/>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B92" s="47" t="s">
         <v>251</v>
       </c>
@@ -5053,7 +5064,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:6">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B93" s="47" t="s">
         <v>280</v>
       </c>
@@ -5066,7 +5077,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="95" spans="1:6" ht="13.9">
+    <row r="95" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A95" s="222" t="s">
         <v>357</v>
       </c>
@@ -5076,38 +5087,38 @@
       <c r="E95" s="36"/>
       <c r="F95" s="36"/>
     </row>
-    <row r="96" spans="1:6">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A96" s="209"/>
     </row>
-    <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+    <row r="97" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B97" s="356" t="s">
         <v>365</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
-    </row>
-    <row r="98" spans="2:6">
+      <c r="C97" s="356"/>
+      <c r="D97" s="356"/>
+      <c r="E97" s="356"/>
+      <c r="F97" s="356"/>
+    </row>
+    <row r="98" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B98" s="1" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="100" spans="2:6">
+    <row r="100" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B100" s="210" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="358" t="s">
+    <row r="101" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B101" s="356" t="s">
         <v>344</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
-    </row>
-    <row r="102" spans="2:6">
+      <c r="C101" s="356"/>
+      <c r="D101" s="356"/>
+      <c r="E101" s="356"/>
+      <c r="F101" s="356"/>
+    </row>
+    <row r="102" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B102" s="47" t="s">
         <v>255</v>
       </c>
@@ -5120,7 +5131,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="103" spans="2:6">
+    <row r="103" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B103" s="47" t="s">
         <v>281</v>
       </c>
@@ -5133,7 +5144,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="104" spans="2:6">
+    <row r="104" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B104" s="296" t="s">
         <v>404</v>
       </c>
@@ -5142,7 +5153,7 @@
         <v>4.1494671576720196E-2</v>
       </c>
     </row>
-    <row r="105" spans="2:6">
+    <row r="105" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B105" s="296" t="s">
         <v>406</v>
       </c>
@@ -5151,12 +5162,12 @@
         <v>0.57353573509526667</v>
       </c>
     </row>
-    <row r="107" spans="2:6">
+    <row r="107" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B107" s="1" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="108" spans="2:6">
+    <row r="108" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B108" s="47" t="s">
         <v>264</v>
       </c>
@@ -5169,7 +5180,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="109" spans="2:6">
+    <row r="109" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B109" s="47" t="s">
         <v>266</v>
       </c>
@@ -5182,7 +5193,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="110" spans="2:6">
+    <row r="110" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B110" s="47" t="s">
         <v>282</v>
       </c>
@@ -5195,12 +5206,12 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="112" spans="2:6">
+    <row r="112" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B112" s="1" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="113" spans="1:6">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B113" s="47" t="s">
         <v>257</v>
       </c>
@@ -5213,7 +5224,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="114" spans="1:6">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B114" s="47" t="s">
         <v>283</v>
       </c>
@@ -5226,16 +5237,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="358" t="s">
+    <row r="116" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B116" s="356" t="s">
         <v>366</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
-    </row>
-    <row r="118" spans="1:6">
+      <c r="C116" s="356"/>
+      <c r="D116" s="356"/>
+      <c r="E116" s="356"/>
+      <c r="F116" s="356"/>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B118" s="47" t="s">
         <v>449</v>
       </c>
@@ -5248,7 +5259,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="119" spans="1:6">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B119" s="296" t="s">
         <v>405</v>
       </c>
@@ -5261,7 +5272,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="121" spans="1:6" ht="13.9">
+    <row r="121" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A121" s="222" t="s">
         <v>358</v>
       </c>
@@ -5271,16 +5282,16 @@
       <c r="E121" s="36"/>
       <c r="F121" s="36"/>
     </row>
-    <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="359" t="s">
+    <row r="123" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B123" s="357" t="s">
         <v>367</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
-    </row>
-    <row r="125" spans="1:6" ht="12.4">
+      <c r="C123" s="357"/>
+      <c r="D123" s="357"/>
+      <c r="E123" s="357"/>
+      <c r="F123" s="357"/>
+    </row>
+    <row r="125" spans="1:6" ht="14" x14ac:dyDescent="0.2">
       <c r="B125" s="233" t="s">
         <v>117</v>
       </c>
@@ -5297,7 +5308,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="126" spans="1:6">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B126" s="228" t="str">
         <f>DCF!B74</f>
         <v>Snowball Scenario</v>
@@ -5319,7 +5330,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="127" spans="1:6">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B127" s="218" t="str">
         <f>DCF!B75</f>
         <v>Optimistic</v>
@@ -5341,7 +5352,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="128" spans="1:6">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B128" s="218" t="str">
         <f>DCF!B76</f>
         <v>Base</v>
@@ -5363,7 +5374,7 @@
         <v>0.53999999999999992</v>
       </c>
     </row>
-    <row r="129" spans="1:6">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B129" s="218" t="str">
         <f>DCF!B77</f>
         <v>Pessimistic</v>
@@ -5385,7 +5396,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="130" spans="1:6">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B130" s="218" t="str">
         <f>DCF!B78</f>
         <v>Devil's advocate</v>
@@ -5407,7 +5418,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="132" spans="1:6">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B132" s="211" t="s">
         <v>258</v>
       </c>
@@ -5420,16 +5431,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="362" t="s">
+    <row r="134" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B134" s="361" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="362"/>
-      <c r="D134" s="362"/>
-      <c r="E134" s="362"/>
-      <c r="F134" s="362"/>
-    </row>
-    <row r="136" spans="1:6" ht="13.9">
+      <c r="C134" s="361"/>
+      <c r="D134" s="361"/>
+      <c r="E134" s="361"/>
+      <c r="F134" s="361"/>
+    </row>
+    <row r="136" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A136" s="222" t="s">
         <v>402</v>
       </c>
@@ -5439,30 +5450,30 @@
       <c r="E136" s="36"/>
       <c r="F136" s="36"/>
     </row>
-    <row r="138" spans="1:6">
-      <c r="B138" s="363" t="s">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B138" s="359" t="s">
         <v>368</v>
       </c>
-      <c r="C138" s="363"/>
-      <c r="D138" s="363"/>
-      <c r="E138" s="363"/>
-      <c r="F138" s="363"/>
-    </row>
-    <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="C138" s="359"/>
+      <c r="D138" s="359"/>
+      <c r="E138" s="359"/>
+      <c r="F138" s="359"/>
+    </row>
+    <row r="139" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B139" s="356" t="s">
         <v>369</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
-    </row>
-    <row r="140" spans="1:6">
+      <c r="C139" s="356"/>
+      <c r="D139" s="356"/>
+      <c r="E139" s="356"/>
+      <c r="F139" s="356"/>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B140" s="210" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="141" spans="1:6">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B141" s="1" t="s">
         <v>263</v>
       </c>
@@ -5471,16 +5482,16 @@
         <v>3</v>
       </c>
     </row>
-    <row r="142" spans="1:6">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B142" s="1" t="s">
         <v>276</v>
       </c>
       <c r="C142" s="224">
         <f>F29</f>
-        <v>0.33700000000000002</v>
-      </c>
-    </row>
-    <row r="143" spans="1:6">
+        <v>0.33699999999999997</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B143" s="212" t="s">
         <v>261</v>
       </c>
@@ -5493,7 +5504,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="145" spans="2:4">
+    <row r="145" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B145" s="210" t="s">
         <v>408</v>
       </c>
@@ -5506,26 +5517,26 @@
         <v/>
       </c>
     </row>
-    <row r="146" spans="2:4">
+    <row r="146" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B146" s="1" t="s">
         <v>407</v>
       </c>
       <c r="C146" s="297">
         <f>F29</f>
-        <v>0.33700000000000002</v>
-      </c>
-    </row>
-    <row r="147" spans="2:4">
+        <v>0.33699999999999997</v>
+      </c>
+    </row>
+    <row r="147" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B147" s="212" t="str">
         <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="C147" s="216">
         <f>Scenarios!C81</f>
-        <v>0.69031028314322285</v>
-      </c>
-    </row>
-    <row r="148" spans="2:4">
+        <v>0.69031028314322296</v>
+      </c>
+    </row>
+    <row r="148" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B148" s="212" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5535,7 +5546,7 @@
         <v>4.2893376993526235</v>
       </c>
     </row>
-    <row r="149" spans="2:4">
+    <row r="149" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B149" s="80" t="s">
         <v>260</v>
       </c>
@@ -5548,7 +5559,7 @@
         <v/>
       </c>
     </row>
-    <row r="150" spans="2:4">
+    <row r="150" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B150" s="259" t="s">
         <v>416</v>
       </c>
@@ -5561,7 +5572,7 @@
         <v/>
       </c>
     </row>
-    <row r="151" spans="2:4">
+    <row r="151" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B151" s="214" t="s">
         <v>262</v>
       </c>
@@ -5570,12 +5581,12 @@
         <v>0.51424846499304677</v>
       </c>
     </row>
-    <row r="153" spans="2:4">
+    <row r="153" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B153" s="210" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="154" spans="2:4">
+    <row r="154" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B154" s="1" t="s">
         <v>410</v>
       </c>
@@ -5584,7 +5595,7 @@
         <v>0.187</v>
       </c>
     </row>
-    <row r="155" spans="2:4">
+    <row r="155" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B155" s="212" t="str">
         <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5594,7 +5605,7 @@
         <v>0.86005014536183588</v>
       </c>
     </row>
-    <row r="156" spans="2:4">
+    <row r="156" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B156" s="212" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5604,7 +5615,7 @@
         <v>6.1296023972810385</v>
       </c>
     </row>
-    <row r="157" spans="2:4">
+    <row r="157" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B157" s="80" t="s">
         <v>260</v>
       </c>
@@ -5617,7 +5628,7 @@
         <v/>
       </c>
     </row>
-    <row r="158" spans="2:4">
+    <row r="158" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B158" s="259" t="s">
         <v>416</v>
       </c>
@@ -5630,7 +5641,7 @@
         <v/>
       </c>
     </row>
-    <row r="159" spans="2:4">
+    <row r="159" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B159" s="214" t="s">
         <v>262</v>
       </c>
@@ -5639,12 +5650,12 @@
         <v>0.31817781825366975</v>
       </c>
     </row>
-    <row r="161" spans="2:4">
+    <row r="161" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B161" s="210" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="162" spans="2:4">
+    <row r="162" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B162" s="1" t="s">
         <v>409</v>
       </c>
@@ -5653,7 +5664,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="163" spans="2:4">
+    <row r="163" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B163" s="212" t="str">
         <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5663,7 +5674,7 @@
         <v>1.069204779784656</v>
       </c>
     </row>
-    <row r="164" spans="2:4">
+    <row r="164" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B164" s="212" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5673,7 +5684,7 @@
         <v>8.6072985209538491</v>
       </c>
     </row>
-    <row r="165" spans="2:4">
+    <row r="165" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B165" s="80" t="s">
         <v>401</v>
       </c>
@@ -5686,7 +5697,7 @@
         <v/>
       </c>
     </row>
-    <row r="166" spans="2:4">
+    <row r="166" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B166" s="259" t="s">
         <v>416</v>
       </c>
@@ -5699,7 +5710,7 @@
         <v/>
       </c>
     </row>
-    <row r="167" spans="2:4">
+    <row r="167" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B167" s="214" t="s">
         <v>262</v>
       </c>
@@ -5708,12 +5719,12 @@
         <v>5.6082608980383197E-2</v>
       </c>
     </row>
-    <row r="169" spans="2:4">
+    <row r="169" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B169" s="210" t="s">
         <v>432</v>
       </c>
     </row>
-    <row r="170" spans="2:4">
+    <row r="170" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B170" s="1" t="s">
         <v>423</v>
       </c>
@@ -5722,7 +5733,7 @@
         <v>8.6999999999999994E-2</v>
       </c>
     </row>
-    <row r="171" spans="2:4">
+    <row r="171" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B171" s="212" t="str">
         <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5732,7 +5743,7 @@
         <v>1.0179560233797402</v>
       </c>
     </row>
-    <row r="172" spans="2:4">
+    <row r="172" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B172" s="212" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5742,7 +5753,7 @@
         <v>7.981707879328158</v>
       </c>
     </row>
-    <row r="173" spans="2:4">
+    <row r="173" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B173" s="80" t="s">
         <v>401</v>
       </c>
@@ -5755,7 +5766,7 @@
         <v/>
       </c>
     </row>
-    <row r="174" spans="2:4">
+    <row r="174" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B174" s="259" t="s">
         <v>416</v>
       </c>
@@ -5768,7 +5779,7 @@
         <v/>
       </c>
     </row>
-    <row r="175" spans="2:4">
+    <row r="175" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B175" s="214" t="s">
         <v>262</v>
       </c>
@@ -5777,7 +5788,7 @@
         <v>0.11980238369313911</v>
       </c>
     </row>
-    <row r="177" spans="1:6" ht="13.9">
+    <row r="177" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A177" s="222" t="s">
         <v>374</v>
       </c>
@@ -5787,21 +5798,21 @@
       <c r="E177" s="36"/>
       <c r="F177" s="36"/>
     </row>
-    <row r="179" spans="1:6">
-      <c r="B179" s="357" t="s">
+    <row r="179" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B179" s="363" t="s">
         <v>376</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
-    </row>
-    <row r="181" spans="1:6">
+      <c r="C179" s="356"/>
+      <c r="D179" s="356"/>
+      <c r="E179" s="356"/>
+      <c r="F179" s="356"/>
+    </row>
+    <row r="181" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B181" s="210" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="182" spans="1:6">
+    <row r="182" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B182" s="360" t="s">
         <v>380</v>
       </c>
@@ -5810,80 +5821,91 @@
       <c r="E182" s="360"/>
       <c r="F182" s="360"/>
     </row>
-    <row r="183" spans="1:6">
+    <row r="183" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B183" s="214" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="184" spans="1:6">
+    <row r="184" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B184" s="214" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="185" spans="1:6">
+    <row r="185" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B185" s="214" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="187" spans="1:6">
+    <row r="187" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B187" s="1" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+    <row r="188" spans="1:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B188" s="357" t="s">
         <v>381</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
-    </row>
-    <row r="190" spans="1:6">
+      <c r="C188" s="357"/>
+      <c r="D188" s="357"/>
+      <c r="E188" s="357"/>
+      <c r="F188" s="357"/>
+    </row>
+    <row r="190" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B190" s="1" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="356" t="s">
+    <row r="191" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B191" s="362" t="s">
         <v>382</v>
       </c>
-      <c r="C191" s="356"/>
-      <c r="D191" s="356"/>
-      <c r="E191" s="356"/>
-      <c r="F191" s="356"/>
-    </row>
-    <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="356" t="s">
+      <c r="C191" s="362"/>
+      <c r="D191" s="362"/>
+      <c r="E191" s="362"/>
+      <c r="F191" s="362"/>
+    </row>
+    <row r="192" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B192" s="362" t="s">
         <v>383</v>
       </c>
-      <c r="C192" s="356"/>
-      <c r="D192" s="356"/>
-      <c r="E192" s="356"/>
-      <c r="F192" s="356"/>
-    </row>
-    <row r="194" spans="2:2">
+      <c r="C192" s="362"/>
+      <c r="D192" s="362"/>
+      <c r="E192" s="362"/>
+      <c r="F192" s="362"/>
+    </row>
+    <row r="194" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B194" s="1" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="195" spans="2:2">
+    <row r="195" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B195" s="214" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="196" spans="2:2">
+    <row r="196" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B196" s="214" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="197" spans="2:2">
+    <row r="197" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B197" s="214" t="s">
         <v>388</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5900,17 +5922,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -5941,15 +5952,15 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:M80"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="11.65"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="3" style="1" customWidth="1"/>
-    <col min="2" max="2" width="27.265625" style="1" customWidth="1"/>
-    <col min="3" max="13" width="20.73046875" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.86328125" style="1"/>
+    <col min="2" max="2" width="27.33203125" style="1" customWidth="1"/>
+    <col min="3" max="13" width="20.6640625" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:13">
+    <row r="1" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B1" s="90" t="str">
         <f>Thesis!C25</f>
         <v>CNY</v>
@@ -5998,7 +6009,7 @@
         <v>42004</v>
       </c>
     </row>
-    <row r="2" spans="2:13" ht="13.9">
+    <row r="2" spans="2:13" ht="16" x14ac:dyDescent="0.25">
       <c r="B2" s="36" t="s">
         <v>97</v>
       </c>
@@ -6014,7 +6025,7 @@
       <c r="L2" s="37"/>
       <c r="M2" s="37"/>
     </row>
-    <row r="3" spans="2:13">
+    <row r="3" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B3" s="16" t="s">
         <v>27</v>
       </c>
@@ -6022,7 +6033,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="2:13">
+    <row r="4" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B4" s="32" t="s">
         <v>2</v>
       </c>
@@ -6058,7 +6069,7 @@
       </c>
       <c r="M4" s="351"/>
     </row>
-    <row r="5" spans="2:13">
+    <row r="5" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B5" s="40" t="s">
         <v>43</v>
       </c>
@@ -6094,7 +6105,7 @@
       </c>
       <c r="M5" s="351"/>
     </row>
-    <row r="6" spans="2:13">
+    <row r="6" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B6" s="40" t="s">
         <v>54</v>
       </c>
@@ -6130,7 +6141,7 @@
       </c>
       <c r="M6" s="351"/>
     </row>
-    <row r="7" spans="2:13">
+    <row r="7" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B7" s="69" t="s">
         <v>61</v>
       </c>
@@ -6166,7 +6177,7 @@
       </c>
       <c r="M7" s="352"/>
     </row>
-    <row r="8" spans="2:13">
+    <row r="8" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B8" s="40" t="s">
         <v>49</v>
       </c>
@@ -6196,7 +6207,7 @@
       <c r="L8" s="351"/>
       <c r="M8" s="351"/>
     </row>
-    <row r="9" spans="2:13">
+    <row r="9" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B9" s="40" t="s">
         <v>159</v>
       </c>
@@ -6212,7 +6223,7 @@
       <c r="L9" s="351"/>
       <c r="M9" s="351"/>
     </row>
-    <row r="10" spans="2:13">
+    <row r="10" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B10" s="40" t="s">
         <v>167</v>
       </c>
@@ -6228,7 +6239,7 @@
       <c r="L10" s="351"/>
       <c r="M10" s="351"/>
     </row>
-    <row r="11" spans="2:13">
+    <row r="11" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B11" s="40" t="s">
         <v>158</v>
       </c>
@@ -6244,7 +6255,7 @@
       <c r="L11" s="351"/>
       <c r="M11" s="351"/>
     </row>
-    <row r="12" spans="2:13">
+    <row r="12" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B12" s="40" t="s">
         <v>39</v>
       </c>
@@ -6274,7 +6285,7 @@
       <c r="L12" s="351"/>
       <c r="M12" s="351"/>
     </row>
-    <row r="13" spans="2:13">
+    <row r="13" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B13" s="40" t="s">
         <v>67</v>
       </c>
@@ -6304,7 +6315,7 @@
       <c r="L13" s="351"/>
       <c r="M13" s="351"/>
     </row>
-    <row r="14" spans="2:13">
+    <row r="14" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B14" s="40" t="s">
         <v>50</v>
       </c>
@@ -6340,7 +6351,7 @@
       </c>
       <c r="M14" s="351"/>
     </row>
-    <row r="15" spans="2:13">
+    <row r="15" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B15" s="43" t="s">
         <v>42</v>
       </c>
@@ -6376,7 +6387,7 @@
       </c>
       <c r="M15" s="353"/>
     </row>
-    <row r="16" spans="2:13">
+    <row r="16" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B16" s="28" t="s">
         <v>44</v>
       </c>
@@ -6412,13 +6423,13 @@
       </c>
       <c r="M16" s="351"/>
     </row>
-    <row r="18" spans="2:13">
+    <row r="18" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B18" s="16" t="s">
         <v>51</v>
       </c>
       <c r="C18" s="9"/>
     </row>
-    <row r="19" spans="2:13">
+    <row r="19" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B19" s="27" t="s">
         <v>47</v>
       </c>
@@ -6448,7 +6459,7 @@
       <c r="L19" s="351"/>
       <c r="M19" s="351"/>
     </row>
-    <row r="20" spans="2:13">
+    <row r="20" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B20" s="27" t="s">
         <v>53</v>
       </c>
@@ -6464,7 +6475,7 @@
       <c r="L20" s="351"/>
       <c r="M20" s="351"/>
     </row>
-    <row r="21" spans="2:13">
+    <row r="21" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B21" s="27" t="s">
         <v>52</v>
       </c>
@@ -6480,7 +6491,7 @@
       <c r="L21" s="351"/>
       <c r="M21" s="351"/>
     </row>
-    <row r="22" spans="2:13">
+    <row r="22" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B22" s="27" t="s">
         <v>371</v>
       </c>
@@ -6516,7 +6527,7 @@
       </c>
       <c r="M22" s="351"/>
     </row>
-    <row r="23" spans="2:13">
+    <row r="23" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B23" s="27" t="s">
         <v>373</v>
       </c>
@@ -6552,7 +6563,7 @@
       </c>
       <c r="M23" s="351"/>
     </row>
-    <row r="24" spans="2:13">
+    <row r="24" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B24" s="27" t="s">
         <v>372</v>
       </c>
@@ -6588,7 +6599,7 @@
       </c>
       <c r="M24" s="351"/>
     </row>
-    <row r="25" spans="2:13">
+    <row r="25" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B25" s="24" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
         <v>Dividend per share (CNY)</v>
@@ -6623,7 +6634,7 @@
       <c r="L25" s="39"/>
       <c r="M25" s="39"/>
     </row>
-    <row r="27" spans="2:13">
+    <row r="27" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B27" s="16" t="s">
         <v>28</v>
       </c>
@@ -6631,7 +6642,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="28" spans="2:13">
+    <row r="28" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B28" s="26" t="s">
         <v>24</v>
       </c>
@@ -6668,7 +6679,7 @@
       </c>
       <c r="M28" s="351"/>
     </row>
-    <row r="29" spans="2:13">
+    <row r="29" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B29" s="26" t="s">
         <v>32</v>
       </c>
@@ -6705,7 +6716,7 @@
       </c>
       <c r="M29" s="351"/>
     </row>
-    <row r="30" spans="2:13">
+    <row r="30" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B30" s="29" t="s">
         <v>40</v>
       </c>
@@ -6742,7 +6753,7 @@
       </c>
       <c r="M30" s="353"/>
     </row>
-    <row r="31" spans="2:13">
+    <row r="31" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B31" s="29" t="s">
         <v>30</v>
       </c>
@@ -6779,7 +6790,7 @@
       </c>
       <c r="M31" s="353"/>
     </row>
-    <row r="32" spans="2:13">
+    <row r="32" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B32" s="26" t="s">
         <v>172</v>
       </c>
@@ -6816,7 +6827,7 @@
       </c>
       <c r="M32" s="351"/>
     </row>
-    <row r="34" spans="2:13" ht="13.9">
+    <row r="34" spans="2:13" ht="16" x14ac:dyDescent="0.25">
       <c r="B34" s="36" t="s">
         <v>81</v>
       </c>
@@ -6832,12 +6843,12 @@
       <c r="L34" s="37"/>
       <c r="M34" s="37"/>
     </row>
-    <row r="35" spans="2:13">
+    <row r="35" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B35" s="16" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="36" spans="2:13">
+    <row r="36" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B36" s="32" t="s">
         <v>2</v>
       </c>
@@ -6886,7 +6897,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="2:13">
+    <row r="37" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B37" s="40" t="s">
         <v>43</v>
       </c>
@@ -6935,7 +6946,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="2:13">
+    <row r="38" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B38" s="31" t="s">
         <v>58</v>
       </c>
@@ -6984,7 +6995,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="2:13">
+    <row r="39" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B39" s="40" t="s">
         <v>54</v>
       </c>
@@ -7033,7 +7044,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="2:13">
+    <row r="40" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B40" s="69" t="s">
         <v>61</v>
       </c>
@@ -7082,7 +7093,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="2:13">
+    <row r="41" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B41" s="69" t="s">
         <v>64</v>
       </c>
@@ -7131,7 +7142,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="2:13">
+    <row r="42" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B42" s="40" t="s">
         <v>49</v>
       </c>
@@ -7180,7 +7191,7 @@
         <v/>
       </c>
     </row>
-    <row r="43" spans="2:13">
+    <row r="43" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B43" s="43" t="s">
         <v>152</v>
       </c>
@@ -7229,7 +7240,7 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="2:13">
+    <row r="44" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B44" s="43" t="s">
         <v>168</v>
       </c>
@@ -7278,7 +7289,7 @@
         <v/>
       </c>
     </row>
-    <row r="45" spans="2:13">
+    <row r="45" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B45" s="40" t="s">
         <v>68</v>
       </c>
@@ -7327,7 +7338,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="2:13">
+    <row r="46" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B46" s="40" t="s">
         <v>50</v>
       </c>
@@ -7376,7 +7387,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="2:13">
+    <row r="47" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B47" s="43" t="s">
         <v>42</v>
       </c>
@@ -7425,7 +7436,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="2:13">
+    <row r="48" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B48" s="28" t="s">
         <v>44</v>
       </c>
@@ -7474,12 +7485,12 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="2:13">
+    <row r="50" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B50" s="16" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="51" spans="2:13">
+    <row r="51" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B51" s="40" t="s">
         <v>39</v>
       </c>
@@ -7528,7 +7539,7 @@
         <v/>
       </c>
     </row>
-    <row r="52" spans="2:13">
+    <row r="52" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B52" s="40" t="s">
         <v>67</v>
       </c>
@@ -7577,12 +7588,12 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="2:13">
+    <row r="54" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B54" s="174" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="55" spans="2:13">
+    <row r="55" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B55" s="40" t="s">
         <v>159</v>
       </c>
@@ -7631,7 +7642,7 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="2:13">
+    <row r="56" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B56" s="40" t="s">
         <v>167</v>
       </c>
@@ -7680,7 +7691,7 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="2:13">
+    <row r="57" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B57" s="40" t="s">
         <v>158</v>
       </c>
@@ -7729,7 +7740,7 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="2:13">
+    <row r="58" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B58" s="40" t="s">
         <v>160</v>
       </c>
@@ -7778,13 +7789,13 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="2:13">
+    <row r="60" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B60" s="16" t="s">
         <v>51</v>
       </c>
       <c r="C60" s="9"/>
     </row>
-    <row r="61" spans="2:13">
+    <row r="61" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B61" s="27" t="s">
         <v>47</v>
       </c>
@@ -7833,7 +7844,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="2:13">
+    <row r="62" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B62" s="27" t="s">
         <v>53</v>
       </c>
@@ -7882,7 +7893,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="2:13">
+    <row r="63" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B63" s="27" t="s">
         <v>52</v>
       </c>
@@ -7931,7 +7942,7 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="2:13">
+    <row r="64" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B64" s="27" t="s">
         <v>393</v>
       </c>
@@ -7980,7 +7991,7 @@
         <v/>
       </c>
     </row>
-    <row r="65" spans="2:13">
+    <row r="65" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B65" s="24" t="s">
         <v>36</v>
       </c>
@@ -8029,12 +8040,12 @@
         <v/>
       </c>
     </row>
-    <row r="67" spans="2:13">
+    <row r="67" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B67" s="91" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="68" spans="2:13">
+    <row r="68" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B68" s="1" t="str">
         <f>B36</f>
         <v>Sales</v>
@@ -8084,7 +8095,7 @@
         <v/>
       </c>
     </row>
-    <row r="69" spans="2:13">
+    <row r="69" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B69" s="31" t="s">
         <v>58</v>
       </c>
@@ -8133,7 +8144,7 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="2:13">
+    <row r="70" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B70" s="80" t="str">
         <f>B43</f>
         <v>Operating EBIT</v>
@@ -8183,7 +8194,7 @@
         <v/>
       </c>
     </row>
-    <row r="71" spans="2:13">
+    <row r="71" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B71" s="43" t="s">
         <v>168</v>
       </c>
@@ -8232,7 +8243,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="2:13">
+    <row r="72" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B72" s="80" t="str">
         <f>B47</f>
         <v>Reported Net Income</v>
@@ -8282,7 +8293,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="2:13" ht="13.9">
+    <row r="74" spans="2:13" ht="16" x14ac:dyDescent="0.25">
       <c r="B74" s="36" t="s">
         <v>82</v>
       </c>
@@ -8298,13 +8309,13 @@
       <c r="L74" s="37"/>
       <c r="M74" s="37"/>
     </row>
-    <row r="75" spans="2:13">
+    <row r="75" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B75" s="16" t="s">
         <v>28</v>
       </c>
       <c r="C75" s="9"/>
     </row>
-    <row r="76" spans="2:13">
+    <row r="76" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B76" s="26" t="s">
         <v>3</v>
       </c>
@@ -8353,7 +8364,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="2:13">
+    <row r="77" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B77" s="93" t="s">
         <v>85</v>
       </c>
@@ -8387,7 +8398,7 @@
       <c r="L77" s="355"/>
       <c r="M77" s="355"/>
     </row>
-    <row r="78" spans="2:13">
+    <row r="78" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B78" s="93" t="s">
         <v>86</v>
       </c>
@@ -8421,7 +8432,7 @@
       <c r="L78" s="355"/>
       <c r="M78" s="355"/>
     </row>
-    <row r="79" spans="2:13">
+    <row r="79" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B79" s="26" t="s">
         <v>40</v>
       </c>
@@ -8470,7 +8481,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="2:13">
+    <row r="80" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B80" s="26" t="s">
         <v>30</v>
       </c>
@@ -8551,18 +8562,18 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:H89"/>
-  <sheetFormatPr defaultColWidth="12.265625" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="2.265625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="2.33203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="34" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="18.73046875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="5.73046875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="25.265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="18.73046875" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="12.265625" style="1"/>
+    <col min="3" max="4" width="18.6640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="5.6640625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="25.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="18.6640625" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="12.33203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" ht="15" customHeight="1">
+    <row r="1" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B1" s="18" t="s">
         <v>37</v>
       </c>
@@ -8578,7 +8589,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="2:8" ht="15" customHeight="1">
+    <row r="2" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B2" s="79" t="s">
         <v>156</v>
       </c>
@@ -8589,7 +8600,7 @@
       <c r="G2" s="37"/>
       <c r="H2" s="37"/>
     </row>
-    <row r="3" spans="2:8" ht="15" customHeight="1">
+    <row r="3" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B3" s="16" t="s">
         <v>184</v>
       </c>
@@ -8609,7 +8620,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="2:8" ht="15" customHeight="1">
+    <row r="4" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B4" s="4" t="s">
         <v>24</v>
       </c>
@@ -8631,7 +8642,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="5" spans="2:8" ht="15" customHeight="1">
+    <row r="5" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B5" s="1" t="s">
         <v>33</v>
       </c>
@@ -8652,7 +8663,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="6" spans="2:8" ht="15" customHeight="1">
+    <row r="6" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B6" s="4" t="s">
         <v>10</v>
       </c>
@@ -8673,7 +8684,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="7" spans="2:8" ht="15" customHeight="1">
+    <row r="7" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B7" s="1" t="s">
         <v>69</v>
       </c>
@@ -8694,7 +8705,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="8" spans="2:8" ht="15" customHeight="1">
+    <row r="8" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B8" s="1" t="s">
         <v>173</v>
       </c>
@@ -8715,7 +8726,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="9" spans="2:8" ht="15" customHeight="1">
+    <row r="9" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B9" s="4" t="s">
         <v>25</v>
       </c>
@@ -8736,7 +8747,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="10" spans="2:8" ht="15" customHeight="1">
+    <row r="10" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B10" s="4" t="s">
         <v>11</v>
       </c>
@@ -8748,7 +8759,7 @@
       </c>
       <c r="H10" s="262"/>
     </row>
-    <row r="11" spans="2:8" ht="15" customHeight="1">
+    <row r="11" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B11" s="4" t="s">
         <v>12</v>
       </c>
@@ -8760,7 +8771,7 @@
       </c>
       <c r="H11" s="262"/>
     </row>
-    <row r="12" spans="2:8" ht="15" customHeight="1">
+    <row r="12" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B12" s="80" t="s">
         <v>72</v>
       </c>
@@ -8784,12 +8795,12 @@
         <v>911297844.82799995</v>
       </c>
     </row>
-    <row r="13" spans="2:8" ht="15" customHeight="1">
+    <row r="13" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F13" s="80"/>
       <c r="G13" s="81"/>
       <c r="H13" s="20"/>
     </row>
-    <row r="14" spans="2:8" ht="15" customHeight="1">
+    <row r="14" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B14" s="16" t="s">
         <v>183</v>
       </c>
@@ -8809,7 +8820,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="2:8" ht="15" customHeight="1">
+    <row r="15" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B15" s="4" t="s">
         <v>454</v>
       </c>
@@ -8829,7 +8840,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="16" spans="2:8" ht="15" customHeight="1">
+    <row r="16" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B16" s="1" t="s">
         <v>34</v>
       </c>
@@ -8849,7 +8860,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="17" spans="2:8" ht="15" customHeight="1">
+    <row r="17" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="1" t="s">
         <v>69</v>
       </c>
@@ -8869,7 +8880,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="18" spans="2:8" ht="15" customHeight="1">
+    <row r="18" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="4" t="s">
         <v>173</v>
       </c>
@@ -8889,7 +8900,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="19" spans="2:8" ht="15" customHeight="1">
+    <row r="19" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B19" s="4" t="s">
         <v>26</v>
       </c>
@@ -8910,7 +8921,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="20" spans="2:8" ht="15" customHeight="1">
+    <row r="20" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B20" s="4" t="s">
         <v>18</v>
       </c>
@@ -8930,7 +8941,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="21" spans="2:8" ht="15" customHeight="1">
+    <row r="21" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B21" s="4" t="s">
         <v>19</v>
       </c>
@@ -8950,7 +8961,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="22" spans="2:8" ht="15" customHeight="1">
+    <row r="22" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B22" s="4" t="s">
         <v>20</v>
       </c>
@@ -8962,7 +8973,7 @@
       </c>
       <c r="H22" s="262"/>
     </row>
-    <row r="23" spans="2:8" ht="15" customHeight="1">
+    <row r="23" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B23" s="4" t="s">
         <v>21</v>
       </c>
@@ -8975,7 +8986,7 @@
       </c>
       <c r="H23" s="262"/>
     </row>
-    <row r="24" spans="2:8" ht="15" customHeight="1">
+    <row r="24" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B24" s="80" t="s">
         <v>73</v>
       </c>
@@ -8999,7 +9010,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="2:8" ht="15" customHeight="1">
+    <row r="26" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B26" s="16" t="s">
         <v>200</v>
       </c>
@@ -9016,7 +9027,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="27" spans="2:8" ht="15" customHeight="1">
+    <row r="27" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B27" s="4" t="s">
         <v>5</v>
       </c>
@@ -9035,7 +9046,7 @@
         <v>955477434.55499983</v>
       </c>
     </row>
-    <row r="28" spans="2:8" ht="15" customHeight="1">
+    <row r="28" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B28" s="4" t="s">
         <v>6</v>
       </c>
@@ -9050,7 +9061,7 @@
       </c>
       <c r="H28" s="188"/>
     </row>
-    <row r="29" spans="2:8" ht="15" customHeight="1">
+    <row r="29" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B29" s="4" t="s">
         <v>7</v>
       </c>
@@ -9069,7 +9080,7 @@
         <v>955849140.38499987</v>
       </c>
     </row>
-    <row r="30" spans="2:8" ht="15" customHeight="1">
+    <row r="30" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B30" s="2" t="s">
         <v>8</v>
       </c>
@@ -9085,7 +9096,7 @@
       </c>
       <c r="H30" s="188"/>
     </row>
-    <row r="31" spans="2:8" ht="15" customHeight="1">
+    <row r="31" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B31" s="80" t="s">
         <v>203</v>
       </c>
@@ -9102,7 +9113,7 @@
       </c>
       <c r="H31" s="188"/>
     </row>
-    <row r="32" spans="2:8" ht="15" customHeight="1">
+    <row r="32" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B32" s="4" t="s">
         <v>9</v>
       </c>
@@ -9122,7 +9133,7 @@
         <v>1357028359.4749999</v>
       </c>
     </row>
-    <row r="33" spans="2:8" ht="15" customHeight="1">
+    <row r="33" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B33" s="83" t="s">
         <v>4</v>
       </c>
@@ -9133,7 +9144,7 @@
       <c r="G33" s="2"/>
       <c r="H33" s="195"/>
     </row>
-    <row r="34" spans="2:8" ht="15" customHeight="1">
+    <row r="34" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B34" s="83"/>
       <c r="C34" s="84"/>
       <c r="F34" s="196" t="s">
@@ -9146,7 +9157,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="35" spans="2:8" ht="15" customHeight="1">
+    <row r="35" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B35" s="16" t="s">
         <v>201</v>
       </c>
@@ -9165,7 +9176,7 @@
         <v>445730514.64700001</v>
       </c>
     </row>
-    <row r="36" spans="2:8" ht="15" customHeight="1">
+    <row r="36" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B36" s="4" t="s">
         <v>13</v>
       </c>
@@ -9181,7 +9192,7 @@
       </c>
       <c r="H36" s="195"/>
     </row>
-    <row r="37" spans="2:8" ht="15" customHeight="1">
+    <row r="37" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B37" s="4" t="s">
         <v>14</v>
       </c>
@@ -9197,7 +9208,7 @@
       </c>
       <c r="H37" s="195"/>
     </row>
-    <row r="38" spans="2:8" ht="15" customHeight="1">
+    <row r="38" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B38" s="4" t="s">
         <v>15</v>
       </c>
@@ -9213,7 +9224,7 @@
       </c>
       <c r="H38" s="195"/>
     </row>
-    <row r="39" spans="2:8" ht="15" customHeight="1">
+    <row r="39" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B39" s="2" t="s">
         <v>16</v>
       </c>
@@ -9232,7 +9243,7 @@
         <v>84395700.100000024</v>
       </c>
     </row>
-    <row r="40" spans="2:8" ht="15" customHeight="1">
+    <row r="40" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B40" s="80" t="s">
         <v>204</v>
       </c>
@@ -9252,7 +9263,7 @@
         <v>911297844.82799995</v>
       </c>
     </row>
-    <row r="41" spans="2:8" ht="15" customHeight="1">
+    <row r="41" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B41" s="4" t="s">
         <v>17</v>
       </c>
@@ -9272,7 +9283,7 @@
         <v>911297844.82799995</v>
       </c>
     </row>
-    <row r="42" spans="2:8" ht="15" customHeight="1">
+    <row r="42" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B42" s="83" t="s">
         <v>22</v>
       </c>
@@ -9291,7 +9302,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="2:8" ht="15" customHeight="1">
+    <row r="44" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B44" s="79" t="s">
         <v>96</v>
       </c>
@@ -9302,7 +9313,7 @@
       <c r="G44" s="37"/>
       <c r="H44" s="37"/>
     </row>
-    <row r="45" spans="2:8" ht="15" customHeight="1">
+    <row r="45" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B45" s="16" t="s">
         <v>271</v>
       </c>
@@ -9316,7 +9327,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="46" spans="2:8" ht="15" customHeight="1">
+    <row r="46" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B46" s="1" t="s">
         <v>273</v>
       </c>
@@ -9330,7 +9341,7 @@
       </c>
       <c r="F46" s="253"/>
     </row>
-    <row r="47" spans="2:8" ht="15" customHeight="1">
+    <row r="47" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B47" s="1" t="str">
         <f>"Equity per share ("&amp;Market_currency&amp;")"</f>
         <v>Equity per share (CNY)</v>
@@ -9345,10 +9356,10 @@
       </c>
       <c r="F47" s="253"/>
     </row>
-    <row r="48" spans="2:8" ht="15" customHeight="1">
+    <row r="48" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F48" s="253"/>
     </row>
-    <row r="49" spans="2:8" ht="15" customHeight="1">
+    <row r="49" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B49" s="157" t="s">
         <v>143</v>
       </c>
@@ -9361,7 +9372,7 @@
       <c r="E49" s="2"/>
       <c r="F49" s="253"/>
     </row>
-    <row r="50" spans="2:8" ht="15" customHeight="1">
+    <row r="50" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B50" s="8" t="s">
         <v>93</v>
       </c>
@@ -9375,7 +9386,7 @@
       </c>
       <c r="F50" s="253"/>
     </row>
-    <row r="51" spans="2:8" ht="15" customHeight="1">
+    <row r="51" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B51" s="1" t="s">
         <v>176</v>
       </c>
@@ -9386,10 +9397,10 @@
       </c>
       <c r="F51" s="253"/>
     </row>
-    <row r="52" spans="2:8" ht="15" customHeight="1">
+    <row r="52" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F52" s="253"/>
     </row>
-    <row r="53" spans="2:8" ht="15" customHeight="1">
+    <row r="53" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B53" s="157" t="s">
         <v>142</v>
       </c>
@@ -9401,7 +9412,7 @@
       </c>
       <c r="F53" s="253"/>
     </row>
-    <row r="54" spans="2:8" ht="15" customHeight="1">
+    <row r="54" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B54" s="1" t="s">
         <v>139</v>
       </c>
@@ -9415,7 +9426,7 @@
       </c>
       <c r="F54" s="253"/>
     </row>
-    <row r="55" spans="2:8" ht="15" customHeight="1">
+    <row r="55" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B55" s="1" t="s">
         <v>141</v>
       </c>
@@ -9429,10 +9440,10 @@
       </c>
       <c r="F55" s="253"/>
     </row>
-    <row r="56" spans="2:8" ht="15" customHeight="1">
+    <row r="56" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F56" s="253"/>
     </row>
-    <row r="57" spans="2:8" ht="15" customHeight="1">
+    <row r="57" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B57" s="157" t="s">
         <v>175</v>
       </c>
@@ -9444,7 +9455,7 @@
       </c>
       <c r="F57" s="253"/>
     </row>
-    <row r="58" spans="2:8" ht="15" customHeight="1">
+    <row r="58" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B58" s="2" t="s">
         <v>89</v>
       </c>
@@ -9455,7 +9466,7 @@
       </c>
       <c r="F58" s="5"/>
     </row>
-    <row r="59" spans="2:8" ht="15" customHeight="1">
+    <row r="59" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B59" s="1" t="s">
         <v>92</v>
       </c>
@@ -9466,10 +9477,10 @@
       </c>
       <c r="F59" s="253"/>
     </row>
-    <row r="60" spans="2:8" ht="15" customHeight="1">
+    <row r="60" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F60" s="253"/>
     </row>
-    <row r="61" spans="2:8" ht="15" customHeight="1">
+    <row r="61" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B61" s="157" t="s">
         <v>274</v>
       </c>
@@ -9481,7 +9492,7 @@
       </c>
       <c r="F61" s="253"/>
     </row>
-    <row r="62" spans="2:8" ht="15" customHeight="1">
+    <row r="62" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B62" s="1" t="s">
         <v>245</v>
       </c>
@@ -9497,7 +9508,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="64" spans="2:8" ht="15" customHeight="1">
+    <row r="64" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B64" s="79" t="s">
         <v>193</v>
       </c>
@@ -9508,7 +9519,7 @@
       <c r="G64" s="37"/>
       <c r="H64" s="37"/>
     </row>
-    <row r="65" spans="2:6" ht="15" customHeight="1">
+    <row r="65" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B65" s="16" t="s">
         <v>188</v>
       </c>
@@ -9522,7 +9533,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="66" spans="2:6" ht="15" customHeight="1">
+    <row r="66" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B66" s="105" t="s">
         <v>187</v>
       </c>
@@ -9538,7 +9549,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="67" spans="2:6" ht="15" customHeight="1">
+    <row r="67" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B67" s="105" t="s">
         <v>177</v>
       </c>
@@ -9548,7 +9559,7 @@
       </c>
       <c r="F67" s="253"/>
     </row>
-    <row r="68" spans="2:6" ht="15" customHeight="1">
+    <row r="68" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B68" s="105" t="s">
         <v>181</v>
       </c>
@@ -9558,7 +9569,7 @@
       </c>
       <c r="F68" s="253"/>
     </row>
-    <row r="69" spans="2:6" ht="15" customHeight="1">
+    <row r="69" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B69" s="105" t="s">
         <v>179</v>
       </c>
@@ -9568,7 +9579,7 @@
       </c>
       <c r="F69" s="253"/>
     </row>
-    <row r="70" spans="2:6" ht="15" customHeight="1">
+    <row r="70" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B70" s="80" t="s">
         <v>188</v>
       </c>
@@ -9578,10 +9589,10 @@
       </c>
       <c r="F70" s="253"/>
     </row>
-    <row r="71" spans="2:6" ht="15" customHeight="1">
+    <row r="71" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F71" s="253"/>
     </row>
-    <row r="72" spans="2:6" ht="15" customHeight="1">
+    <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B72" s="255" t="s">
         <v>318</v>
       </c>
@@ -9593,7 +9604,7 @@
       </c>
       <c r="F72" s="253"/>
     </row>
-    <row r="73" spans="2:6" ht="15" customHeight="1">
+    <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B73" s="105" t="s">
         <v>317</v>
       </c>
@@ -9609,7 +9620,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="74" spans="2:6" ht="15" customHeight="1">
+    <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B74" s="257" t="s">
         <v>321</v>
       </c>
@@ -9625,7 +9636,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="75" spans="2:6" ht="15" customHeight="1">
+    <row r="75" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B75" s="80" t="s">
         <v>320</v>
       </c>
@@ -9638,7 +9649,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="76" spans="2:6" ht="15" customHeight="1">
+    <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B76" s="259" t="s">
         <v>322</v>
       </c>
@@ -9651,10 +9662,10 @@
         <v>323</v>
       </c>
     </row>
-    <row r="77" spans="2:6" ht="15" customHeight="1">
+    <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F77" s="253"/>
     </row>
-    <row r="78" spans="2:6" ht="15" customHeight="1">
+    <row r="78" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B78" s="16" t="s">
         <v>189</v>
       </c>
@@ -9666,7 +9677,7 @@
       </c>
       <c r="F78" s="253"/>
     </row>
-    <row r="79" spans="2:6" ht="15" customHeight="1">
+    <row r="79" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B79" s="105" t="s">
         <v>178</v>
       </c>
@@ -9680,7 +9691,7 @@
       </c>
       <c r="F79" s="253"/>
     </row>
-    <row r="80" spans="2:6" ht="15" customHeight="1">
+    <row r="80" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B80" s="105" t="s">
         <v>182</v>
       </c>
@@ -9694,7 +9705,7 @@
       </c>
       <c r="F80" s="253"/>
     </row>
-    <row r="81" spans="2:8" ht="15" customHeight="1">
+    <row r="81" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B81" s="105" t="s">
         <v>180</v>
       </c>
@@ -9708,7 +9719,7 @@
       </c>
       <c r="F81" s="253"/>
     </row>
-    <row r="82" spans="2:8" ht="15" customHeight="1">
+    <row r="82" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B82" s="80" t="s">
         <v>189</v>
       </c>
@@ -9722,7 +9733,7 @@
       </c>
       <c r="F82" s="253"/>
     </row>
-    <row r="84" spans="2:8" ht="15" customHeight="1">
+    <row r="84" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B84" s="79" t="s">
         <v>288</v>
       </c>
@@ -9733,7 +9744,7 @@
       <c r="G84" s="37"/>
       <c r="H84" s="37"/>
     </row>
-    <row r="85" spans="2:8" ht="15" customHeight="1">
+    <row r="85" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B85" s="16" t="s">
         <v>289</v>
       </c>
@@ -9741,7 +9752,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="86" spans="2:8" ht="15" customHeight="1">
+    <row r="86" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B86" s="238" t="s">
         <v>286</v>
       </c>
@@ -9758,7 +9769,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="87" spans="2:8" ht="15" customHeight="1">
+    <row r="87" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B87" s="238" t="s">
         <v>287</v>
       </c>
@@ -9775,7 +9786,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="88" spans="2:8" ht="15" customHeight="1">
+    <row r="88" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B88" s="239" t="s">
         <v>189</v>
       </c>
@@ -9792,7 +9803,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="89" spans="2:8" ht="15" customHeight="1">
+    <row r="89" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B89" s="80" t="s">
         <v>291</v>
       </c>
@@ -9823,19 +9834,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q808"/>
-  <sheetFormatPr defaultColWidth="12.265625" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="1.265625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="26.265625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="20.73046875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="2.73046875" style="2" customWidth="1"/>
-    <col min="5" max="5" width="25.1328125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="2.73046875" style="2" customWidth="1"/>
-    <col min="7" max="17" width="20.73046875" style="2" customWidth="1"/>
-    <col min="18" max="16384" width="12.265625" style="2"/>
+    <col min="1" max="1" width="1.33203125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="26.33203125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="20.6640625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="2.6640625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="25.1640625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="2.6640625" style="2" customWidth="1"/>
+    <col min="7" max="17" width="20.6640625" style="2" customWidth="1"/>
+    <col min="18" max="16384" width="12.33203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15.75" customHeight="1">
+    <row r="1" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="3"/>
       <c r="B1" s="90" t="str">
         <f>Thesis!C25</f>
@@ -9892,7 +9903,7 @@
         <v>42004</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="15.75" customHeight="1">
+    <row r="2" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="54" t="s">
         <v>99</v>
@@ -9915,7 +9926,7 @@
       <c r="P2" s="37"/>
       <c r="Q2" s="37"/>
     </row>
-    <row r="3" spans="1:17" ht="15.75" customHeight="1">
+    <row r="3" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="10"/>
       <c r="B3" s="16" t="s">
         <v>66</v>
@@ -9929,7 +9940,7 @@
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
     </row>
-    <row r="4" spans="1:17" ht="15.75" customHeight="1">
+    <row r="4" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="10"/>
       <c r="B4" s="26" t="s">
         <v>2</v>
@@ -9986,7 +9997,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="15.75" customHeight="1">
+    <row r="5" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="10"/>
       <c r="B5" s="2" t="s">
         <v>46</v>
@@ -10041,7 +10052,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="15.75" customHeight="1">
+    <row r="6" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="10"/>
       <c r="B6" s="31" t="s">
         <v>48</v>
@@ -10096,7 +10107,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="15.75" customHeight="1">
+    <row r="7" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="10"/>
       <c r="B7" s="8" t="s">
         <v>45</v>
@@ -10151,7 +10162,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="15.75" customHeight="1">
+    <row r="8" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="10"/>
       <c r="B8" s="29" t="s">
         <v>152</v>
@@ -10208,7 +10219,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="15.75" customHeight="1">
+    <row r="9" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="10"/>
       <c r="B9" s="2" t="s">
         <v>65</v>
@@ -10263,7 +10274,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="15.75" customHeight="1">
+    <row r="10" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="10"/>
       <c r="B10" s="2" t="s">
         <v>80</v>
@@ -10318,7 +10329,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="15.75" customHeight="1">
+    <row r="11" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="10"/>
       <c r="B11" s="31" t="s">
         <v>194</v>
@@ -10375,7 +10386,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="15.75" customHeight="1">
+    <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="10"/>
       <c r="B12" s="2" t="s">
         <v>68</v>
@@ -10430,7 +10441,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="15.75" customHeight="1">
+    <row r="13" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="10"/>
       <c r="B13" s="70" t="s">
         <v>164</v>
@@ -10485,7 +10496,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="15.75" customHeight="1">
+    <row r="14" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="10"/>
       <c r="B14" s="2" t="s">
         <v>63</v>
@@ -10540,7 +10551,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="15.75" customHeight="1">
+    <row r="15" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="10"/>
       <c r="B15" s="40" t="s">
         <v>243</v>
@@ -10597,7 +10608,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="15.75" customHeight="1">
+    <row r="16" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="10"/>
       <c r="B16" s="41" t="s">
         <v>154</v>
@@ -10654,7 +10665,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="15.75" customHeight="1">
+    <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="10"/>
       <c r="B17" s="27" t="s">
         <v>52</v>
@@ -10680,7 +10691,7 @@
       <c r="P17" s="335"/>
       <c r="Q17" s="335"/>
     </row>
-    <row r="18" spans="1:17" ht="15.75" customHeight="1">
+    <row r="18" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="10"/>
       <c r="B18" s="27" t="s">
         <v>98</v>
@@ -10705,7 +10716,7 @@
       <c r="P18" s="336"/>
       <c r="Q18" s="336"/>
     </row>
-    <row r="19" spans="1:17" ht="15.75" customHeight="1">
+    <row r="19" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="10"/>
       <c r="B19" s="31" t="s">
         <v>66</v>
@@ -10762,7 +10773,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="15.75" customHeight="1">
+    <row r="20" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="10"/>
       <c r="B20" s="27"/>
       <c r="C20" s="62"/>
@@ -10781,7 +10792,7 @@
       <c r="P20" s="12"/>
       <c r="Q20" s="12"/>
     </row>
-    <row r="21" spans="1:17" ht="15.75" customHeight="1">
+    <row r="21" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="10"/>
       <c r="B21" s="54" t="s">
         <v>205</v>
@@ -10804,7 +10815,7 @@
       <c r="P21" s="37"/>
       <c r="Q21" s="37"/>
     </row>
-    <row r="22" spans="1:17" ht="15.75" customHeight="1">
+    <row r="22" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="10"/>
       <c r="B22" s="64" t="s">
         <v>46</v>
@@ -10825,7 +10836,7 @@
       <c r="P22" s="12"/>
       <c r="Q22" s="12"/>
     </row>
-    <row r="23" spans="1:17" ht="15.75" customHeight="1">
+    <row r="23" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="10"/>
       <c r="B23" s="27" t="s">
         <v>43</v>
@@ -10882,7 +10893,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="15.75" customHeight="1">
+    <row r="24" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="10"/>
       <c r="B24" s="68" t="s">
         <v>62</v>
@@ -10939,7 +10950,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="15.75" customHeight="1">
+    <row r="25" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="10"/>
       <c r="B25" s="70" t="s">
         <v>46</v>
@@ -10996,18 +11007,18 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="15.75" customHeight="1">
+    <row r="26" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="10"/>
       <c r="E26" s="268"/>
     </row>
-    <row r="27" spans="1:17" ht="15.75" customHeight="1">
+    <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="10"/>
       <c r="B27" s="64" t="s">
         <v>206</v>
       </c>
       <c r="E27" s="268"/>
     </row>
-    <row r="28" spans="1:17" ht="15.75" customHeight="1">
+    <row r="28" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="10"/>
       <c r="B28" s="26" t="s">
         <v>43</v>
@@ -11066,7 +11077,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:17" ht="15.75" customHeight="1">
+    <row r="29" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="10"/>
       <c r="B29" s="68" t="str">
         <f>B24</f>
@@ -11126,7 +11137,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:17" ht="15.75" customHeight="1">
+    <row r="30" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="10"/>
       <c r="B30" s="70" t="s">
         <v>46</v>
@@ -11181,18 +11192,18 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:17" ht="15.75" customHeight="1">
+    <row r="31" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="10"/>
       <c r="E31" s="268"/>
     </row>
-    <row r="32" spans="1:17" ht="15.75" customHeight="1">
+    <row r="32" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="10"/>
       <c r="B32" s="64" t="s">
         <v>45</v>
       </c>
       <c r="E32" s="268"/>
     </row>
-    <row r="33" spans="1:17" ht="15.75" customHeight="1">
+    <row r="33" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="10"/>
       <c r="B33" s="8" t="s">
         <v>174</v>
@@ -11249,7 +11260,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" spans="1:17" ht="15.75" customHeight="1">
+    <row r="34" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="10"/>
       <c r="B34" s="27" t="s">
         <v>49</v>
@@ -11308,7 +11319,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" spans="1:17" ht="15.75" customHeight="1">
+    <row r="35" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="10"/>
       <c r="B35" s="70" t="s">
         <v>45</v>
@@ -11365,18 +11376,18 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:17" ht="15.75" customHeight="1">
+    <row r="36" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="10"/>
       <c r="E36" s="268"/>
     </row>
-    <row r="37" spans="1:17" ht="15.75" customHeight="1">
+    <row r="37" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="10"/>
       <c r="B37" s="64" t="s">
         <v>207</v>
       </c>
       <c r="E37" s="268"/>
     </row>
-    <row r="38" spans="1:17" ht="15.75" customHeight="1">
+    <row r="38" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="10"/>
       <c r="B38" s="2" t="str">
         <f>B33</f>
@@ -11434,7 +11445,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:17" ht="15.75" customHeight="1">
+    <row r="39" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="10"/>
       <c r="B39" s="27" t="str">
         <f>B34</f>
@@ -11492,7 +11503,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="1:17" ht="15.75" customHeight="1">
+    <row r="40" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="10"/>
       <c r="B40" s="70" t="s">
         <v>45</v>
@@ -11547,18 +11558,18 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="1:17" ht="15.75" customHeight="1">
+    <row r="41" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="10"/>
       <c r="E41" s="268"/>
     </row>
-    <row r="42" spans="1:17" ht="15.75" customHeight="1">
+    <row r="42" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="10"/>
       <c r="B42" s="64" t="s">
         <v>208</v>
       </c>
       <c r="E42" s="268"/>
     </row>
-    <row r="43" spans="1:17" ht="15.75" customHeight="1">
+    <row r="43" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="10"/>
       <c r="B43" s="27" t="s">
         <v>171</v>
@@ -11616,10 +11627,10 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="1:17" ht="15.75" customHeight="1">
+    <row r="44" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="10"/>
     </row>
-    <row r="45" spans="1:17" ht="15.75" customHeight="1">
+    <row r="45" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="10"/>
       <c r="B45" s="54" t="s">
         <v>209</v>
@@ -11642,14 +11653,14 @@
       <c r="P45" s="37"/>
       <c r="Q45" s="37"/>
     </row>
-    <row r="46" spans="1:17" ht="15.75" customHeight="1">
+    <row r="46" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="10"/>
       <c r="B46" s="64" t="s">
         <v>60</v>
       </c>
       <c r="E46" s="268"/>
     </row>
-    <row r="47" spans="1:17" ht="15.75" customHeight="1">
+    <row r="47" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" s="10"/>
       <c r="B47" s="2" t="s">
         <v>39</v>
@@ -11704,7 +11715,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:17" ht="15.75" customHeight="1">
+    <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
         <v>345</v>
@@ -11759,7 +11770,7 @@
         <v/>
       </c>
     </row>
-    <row r="49" spans="1:17" ht="15.75" customHeight="1">
+    <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A49" s="10"/>
       <c r="B49" s="287" t="s">
         <v>342</v>
@@ -11816,7 +11827,7 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="1:17" ht="15.75" customHeight="1">
+    <row r="50" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="10"/>
       <c r="B50" s="70" t="s">
         <v>68</v>
@@ -11871,11 +11882,11 @@
         <v/>
       </c>
     </row>
-    <row r="51" spans="1:17" ht="15.75" customHeight="1">
+    <row r="51" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51" s="10"/>
       <c r="E51" s="268"/>
     </row>
-    <row r="52" spans="1:17" ht="15.75" customHeight="1">
+    <row r="52" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A52" s="10"/>
       <c r="B52" s="72" t="s">
         <v>155</v>
@@ -11885,7 +11896,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="53" spans="1:17" ht="15.75" customHeight="1">
+    <row r="53" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A53" s="10"/>
       <c r="B53" s="8" t="s">
         <v>88</v>
@@ -11911,7 +11922,7 @@
       <c r="P53" s="169"/>
       <c r="Q53" s="169"/>
     </row>
-    <row r="54" spans="1:17" ht="15.75" customHeight="1">
+    <row r="54" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A54" s="10"/>
       <c r="B54" s="8" t="s">
         <v>87</v>
@@ -11938,7 +11949,7 @@
       <c r="P54" s="169"/>
       <c r="Q54" s="169"/>
     </row>
-    <row r="55" spans="1:17" ht="15.75" customHeight="1">
+    <row r="55" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A55" s="10"/>
       <c r="B55" s="26" t="s">
         <v>90</v>
@@ -11993,11 +12004,11 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="1:17" ht="15.75" customHeight="1">
+    <row r="56" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A56" s="10"/>
       <c r="E56" s="268"/>
     </row>
-    <row r="57" spans="1:17" ht="15.75" customHeight="1">
+    <row r="57" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A57" s="10"/>
       <c r="B57" s="64" t="s">
         <v>168</v>
@@ -12007,7 +12018,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="58" spans="1:17" ht="15.75" customHeight="1">
+    <row r="58" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A58" s="10"/>
       <c r="B58" s="40" t="s">
         <v>167</v>
@@ -12062,7 +12073,7 @@
         <v/>
       </c>
     </row>
-    <row r="59" spans="1:17" ht="15.75" customHeight="1">
+    <row r="59" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A59" s="10"/>
       <c r="B59" s="40" t="s">
         <v>159</v>
@@ -12117,7 +12128,7 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="1:17" ht="15.75" customHeight="1">
+    <row r="60" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="10"/>
       <c r="B60" s="40" t="s">
         <v>158</v>
@@ -12172,7 +12183,7 @@
         <v/>
       </c>
     </row>
-    <row r="61" spans="1:17" ht="15.75" customHeight="1">
+    <row r="61" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A61" s="10"/>
       <c r="B61" s="31" t="s">
         <v>194</v>
@@ -12227,7 +12238,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="1:17" ht="15.75" customHeight="1">
+    <row r="62" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A62" s="10"/>
       <c r="B62" s="40" t="s">
         <v>160</v>
@@ -12283,7 +12294,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="1:17" ht="15.75" customHeight="1">
+    <row r="63" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A63" s="10"/>
       <c r="B63" s="31" t="s">
         <v>195</v>
@@ -12338,11 +12349,11 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="1:17" ht="15.75" customHeight="1">
+    <row r="64" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A64" s="10"/>
       <c r="E64" s="268"/>
     </row>
-    <row r="65" spans="1:17" ht="15.75" customHeight="1">
+    <row r="65" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A65" s="10"/>
       <c r="B65" s="96" t="s">
         <v>169</v>
@@ -12352,7 +12363,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="66" spans="1:17" ht="15.75" customHeight="1">
+    <row r="66" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A66" s="10"/>
       <c r="B66" s="40" t="s">
         <v>167</v>
@@ -12377,7 +12388,7 @@
       <c r="P66" s="175"/>
       <c r="Q66" s="175"/>
     </row>
-    <row r="67" spans="1:17" ht="15.75" customHeight="1">
+    <row r="67" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A67" s="10"/>
       <c r="B67" s="105" t="s">
         <v>157</v>
@@ -12402,7 +12413,7 @@
       <c r="P67" s="175"/>
       <c r="Q67" s="175"/>
     </row>
-    <row r="68" spans="1:17" ht="15.75" customHeight="1">
+    <row r="68" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A68" s="10"/>
       <c r="B68" s="105" t="s">
         <v>158</v>
@@ -12427,7 +12438,7 @@
       <c r="P68" s="175"/>
       <c r="Q68" s="175"/>
     </row>
-    <row r="69" spans="1:17" ht="15.75" customHeight="1">
+    <row r="69" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A69" s="10"/>
       <c r="B69" s="31" t="s">
         <v>194</v>
@@ -12454,10 +12465,10 @@
       <c r="P69" s="175"/>
       <c r="Q69" s="175"/>
     </row>
-    <row r="70" spans="1:17" ht="15.75" customHeight="1">
+    <row r="70" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A70" s="10"/>
     </row>
-    <row r="71" spans="1:17" ht="15.75" customHeight="1">
+    <row r="71" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="10"/>
       <c r="B71" s="54" t="s">
         <v>212</v>
@@ -12480,7 +12491,7 @@
       <c r="P71" s="37"/>
       <c r="Q71" s="37"/>
     </row>
-    <row r="72" spans="1:17" ht="15.75" customHeight="1">
+    <row r="72" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A72" s="10"/>
       <c r="B72" s="72" t="s">
         <v>216</v>
@@ -12501,7 +12512,7 @@
       <c r="P72" s="12"/>
       <c r="Q72" s="12"/>
     </row>
-    <row r="73" spans="1:17" ht="15.75" customHeight="1">
+    <row r="73" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A73" s="10"/>
       <c r="B73" s="2" t="s">
         <v>46</v>
@@ -12558,7 +12569,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="1:17" ht="15.75" customHeight="1">
+    <row r="74" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A74" s="10"/>
       <c r="B74" s="31" t="s">
         <v>48</v>
@@ -12615,7 +12626,7 @@
         <v/>
       </c>
     </row>
-    <row r="75" spans="1:17" ht="15.75" customHeight="1">
+    <row r="75" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A75" s="10"/>
       <c r="B75" s="8" t="s">
         <v>45</v>
@@ -12672,7 +12683,7 @@
         <v/>
       </c>
     </row>
-    <row r="76" spans="1:17" ht="15.75" customHeight="1">
+    <row r="76" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A76" s="10"/>
       <c r="B76" s="29" t="s">
         <v>152</v>
@@ -12729,7 +12740,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="1:17" ht="15.75" customHeight="1">
+    <row r="77" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A77" s="10"/>
       <c r="B77" s="2" t="s">
         <v>65</v>
@@ -12786,7 +12797,7 @@
         <v/>
       </c>
     </row>
-    <row r="78" spans="1:17" ht="15.75" customHeight="1">
+    <row r="78" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A78" s="10"/>
       <c r="B78" s="2" t="s">
         <v>80</v>
@@ -12845,7 +12856,7 @@
         <v/>
       </c>
     </row>
-    <row r="79" spans="1:17" ht="15.75" customHeight="1">
+    <row r="79" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A79" s="10"/>
       <c r="B79" s="31" t="s">
         <v>153</v>
@@ -12902,7 +12913,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="1:17" ht="15.75" customHeight="1">
+    <row r="80" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A80" s="10"/>
       <c r="B80" s="2" t="s">
         <v>68</v>
@@ -12959,7 +12970,7 @@
         <v/>
       </c>
     </row>
-    <row r="81" spans="1:17" ht="15.75" customHeight="1">
+    <row r="81" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A81" s="10"/>
       <c r="B81" s="70" t="s">
         <v>164</v>
@@ -13016,7 +13027,7 @@
         <v/>
       </c>
     </row>
-    <row r="82" spans="1:17" ht="15.75" customHeight="1">
+    <row r="82" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A82" s="10"/>
       <c r="B82" s="2" t="s">
         <v>63</v>
@@ -13073,7 +13084,7 @@
         <v/>
       </c>
     </row>
-    <row r="83" spans="1:17" ht="15.75" customHeight="1">
+    <row r="83" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A83" s="10"/>
       <c r="B83" s="40" t="str">
         <f>B15</f>
@@ -13131,7 +13142,7 @@
         <v/>
       </c>
     </row>
-    <row r="84" spans="1:17" ht="15.75" customHeight="1">
+    <row r="84" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A84" s="10"/>
       <c r="B84" s="41" t="s">
         <v>154</v>
@@ -13188,7 +13199,7 @@
         <v/>
       </c>
     </row>
-    <row r="85" spans="1:17" ht="15.75" customHeight="1">
+    <row r="85" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A85" s="10"/>
       <c r="B85" s="27" t="s">
         <v>52</v>
@@ -13214,7 +13225,7 @@
       <c r="P85" s="226"/>
       <c r="Q85" s="226"/>
     </row>
-    <row r="86" spans="1:17" ht="15.75" customHeight="1">
+    <row r="86" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A86" s="10"/>
       <c r="B86" s="8" t="s">
         <v>98</v>
@@ -13238,7 +13249,7 @@
       <c r="P86" s="169"/>
       <c r="Q86" s="169"/>
     </row>
-    <row r="87" spans="1:17" ht="15.75" customHeight="1">
+    <row r="87" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A87" s="10"/>
       <c r="B87" s="31" t="s">
         <v>140</v>
@@ -13295,18 +13306,18 @@
         <v/>
       </c>
     </row>
-    <row r="88" spans="1:17" ht="15.75" customHeight="1">
+    <row r="88" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A88" s="10"/>
       <c r="E88" s="268"/>
     </row>
-    <row r="89" spans="1:17" ht="15.75" customHeight="1">
+    <row r="89" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A89" s="10"/>
       <c r="B89" s="64" t="s">
         <v>214</v>
       </c>
       <c r="E89" s="268"/>
     </row>
-    <row r="90" spans="1:17" ht="15.75" customHeight="1">
+    <row r="90" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A90" s="10"/>
       <c r="B90" s="2" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
@@ -13362,7 +13373,7 @@
         <v/>
       </c>
     </row>
-    <row r="91" spans="1:17" ht="15.75" customHeight="1">
+    <row r="91" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A91" s="10"/>
       <c r="B91" s="2" t="str">
         <f>"Dividend ("&amp;Market_currency&amp;")"</f>
@@ -13418,7 +13429,7 @@
         <v/>
       </c>
     </row>
-    <row r="92" spans="1:17" ht="15.75" customHeight="1">
+    <row r="92" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A92" s="10"/>
       <c r="B92" s="2" t="s">
         <v>213</v>
@@ -13473,39 +13484,39 @@
         <v/>
       </c>
     </row>
-    <row r="93" spans="1:17" ht="15.75" customHeight="1">
+    <row r="93" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
         <v>309</v>
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>2.9717682020802376E-2</v>
+        <v>2.9563932002956397E-2</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>2.9717682020802376E-2</v>
+        <v>2.9563932002956397E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>2.9717682020802376E-2</v>
+        <v>2.9563932002956397E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>2.9717682020802376E-2</v>
+        <v>2.9563932002956397E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
-        <v>2.9717682020802376E-2</v>
+        <v>2.9563932002956397E-2</v>
       </c>
       <c r="K93" s="23">
         <f t="shared" si="39"/>
-        <v>1.4858841010401188E-2</v>
+        <v>1.4781966001478198E-2</v>
       </c>
       <c r="L93" s="23">
         <f t="shared" si="39"/>
-        <v>1.4858841010401188E-2</v>
+        <v>1.4781966001478198E-2</v>
       </c>
       <c r="M93" s="23">
         <f t="shared" si="39"/>
@@ -13528,11 +13539,11 @@
         <v/>
       </c>
     </row>
-    <row r="94" spans="1:17" ht="15.75" customHeight="1">
+    <row r="94" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A94" s="10"/>
       <c r="E94" s="268"/>
     </row>
-    <row r="95" spans="1:17" ht="15.75" customHeight="1">
+    <row r="95" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A95" s="10"/>
       <c r="B95" s="157" t="s">
         <v>84</v>
@@ -13553,7 +13564,7 @@
       <c r="P95" s="12"/>
       <c r="Q95" s="12"/>
     </row>
-    <row r="96" spans="1:17" ht="15.75" customHeight="1">
+    <row r="96" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A96" s="10"/>
       <c r="B96" s="27" t="s">
         <v>144</v>
@@ -13610,7 +13621,7 @@
         <v/>
       </c>
     </row>
-    <row r="97" spans="1:17" ht="15.75" customHeight="1">
+    <row r="97" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A97" s="10"/>
       <c r="B97" s="70" t="s">
         <v>164</v>
@@ -13667,10 +13678,10 @@
         <v/>
       </c>
     </row>
-    <row r="98" spans="1:17" ht="15.75" customHeight="1">
+    <row r="98" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A98" s="10"/>
     </row>
-    <row r="99" spans="1:17" ht="15.75" customHeight="1">
+    <row r="99" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="3"/>
       <c r="B99" s="54" t="s">
         <v>215</v>
@@ -13693,7 +13704,7 @@
       <c r="P99" s="37"/>
       <c r="Q99" s="37"/>
     </row>
-    <row r="100" spans="1:17" ht="15.75" customHeight="1">
+    <row r="100" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A100" s="10"/>
       <c r="B100" s="64" t="s">
         <v>28</v>
@@ -13703,7 +13714,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="101" spans="1:17" ht="15.75" customHeight="1">
+    <row r="101" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A101" s="10"/>
       <c r="B101" s="26" t="s">
         <v>3</v>
@@ -13760,7 +13771,7 @@
         <v/>
       </c>
     </row>
-    <row r="102" spans="1:17" ht="15.75" customHeight="1">
+    <row r="102" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A102" s="10"/>
       <c r="B102" s="93" t="s">
         <v>210</v>
@@ -13817,7 +13828,7 @@
         <v/>
       </c>
     </row>
-    <row r="103" spans="1:17" ht="15.75" customHeight="1">
+    <row r="103" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A103" s="10"/>
       <c r="B103" s="93" t="s">
         <v>211</v>
@@ -13874,7 +13885,7 @@
         <v/>
       </c>
     </row>
-    <row r="104" spans="1:17" ht="15.75" customHeight="1">
+    <row r="104" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A104" s="10"/>
       <c r="B104" s="26" t="s">
         <v>40</v>
@@ -13931,7 +13942,7 @@
         <v/>
       </c>
     </row>
-    <row r="105" spans="1:17" ht="15.75" customHeight="1">
+    <row r="105" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A105" s="10"/>
       <c r="B105" s="26" t="s">
         <v>30</v>
@@ -13988,11 +13999,11 @@
         <v/>
       </c>
     </row>
-    <row r="106" spans="1:17" ht="15.75" customHeight="1">
+    <row r="106" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A106" s="10"/>
       <c r="E106" s="268"/>
     </row>
-    <row r="107" spans="1:17" ht="15.75" customHeight="1">
+    <row r="107" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A107" s="10"/>
       <c r="B107" s="91" t="s">
         <v>220</v>
@@ -14015,7 +14026,7 @@
       <c r="P107" s="12"/>
       <c r="Q107" s="12"/>
     </row>
-    <row r="108" spans="1:17" ht="15.75" customHeight="1">
+    <row r="108" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A108" s="10"/>
       <c r="B108" s="26" t="s">
         <v>217</v>
@@ -14072,7 +14083,7 @@
         <v/>
       </c>
     </row>
-    <row r="109" spans="1:17" ht="15.75" customHeight="1">
+    <row r="109" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A109" s="10"/>
       <c r="B109" s="26" t="s">
         <v>218</v>
@@ -14129,7 +14140,7 @@
         <v/>
       </c>
     </row>
-    <row r="110" spans="1:17" ht="15.75" customHeight="1">
+    <row r="110" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A110" s="10"/>
       <c r="B110" s="26" t="s">
         <v>69</v>
@@ -14156,18 +14167,18 @@
       <c r="P110" s="204"/>
       <c r="Q110" s="204"/>
     </row>
-    <row r="111" spans="1:17" ht="15.75" customHeight="1">
+    <row r="111" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A111" s="10"/>
       <c r="E111" s="268"/>
     </row>
-    <row r="112" spans="1:17" ht="15.75" customHeight="1">
+    <row r="112" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A112" s="10"/>
       <c r="B112" s="64" t="s">
         <v>51</v>
       </c>
       <c r="E112" s="268"/>
     </row>
-    <row r="113" spans="1:17" ht="15.75" customHeight="1">
+    <row r="113" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
         <v>391</v>
@@ -14219,7 +14230,7 @@
         <v/>
       </c>
     </row>
-    <row r="114" spans="1:17" ht="15.75" customHeight="1">
+    <row r="114" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
         <v>392</v>
@@ -14271,11 +14282,11 @@
         <v/>
       </c>
     </row>
-    <row r="115" spans="1:17" ht="15.75" customHeight="1">
+    <row r="115" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A115" s="10"/>
       <c r="E115" s="268"/>
     </row>
-    <row r="116" spans="1:17" ht="15.75" customHeight="1">
+    <row r="116" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A116" s="10"/>
       <c r="B116" s="91" t="s">
         <v>38</v>
@@ -14329,7 +14340,7 @@
         <v/>
       </c>
     </row>
-    <row r="117" spans="1:17" ht="15.75" customHeight="1">
+    <row r="117" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A117" s="10"/>
       <c r="B117" s="7" t="s">
         <v>221</v>
@@ -14384,7 +14395,7 @@
         <v/>
       </c>
     </row>
-    <row r="118" spans="1:17" ht="15.75" customHeight="1">
+    <row r="118" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B118" s="7" t="s">
         <v>83</v>
       </c>
@@ -14438,7 +14449,7 @@
         <v/>
       </c>
     </row>
-    <row r="119" spans="1:17" ht="15.75" customHeight="1">
+    <row r="119" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B119" s="7" t="s">
         <v>91</v>
       </c>
@@ -14494,7 +14505,7 @@
         <v/>
       </c>
     </row>
-    <row r="120" spans="1:17" ht="15.75" customHeight="1">
+    <row r="120" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A120" s="10"/>
       <c r="B120" s="70" t="s">
         <v>222</v>
@@ -14551,7 +14562,7 @@
         <v/>
       </c>
     </row>
-    <row r="121" spans="1:17" ht="15.75" customHeight="1">
+    <row r="121" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A121" s="10"/>
       <c r="B121" s="27"/>
       <c r="C121" s="62"/>
@@ -14570,7 +14581,7 @@
       <c r="P121" s="12"/>
       <c r="Q121" s="12"/>
     </row>
-    <row r="122" spans="1:17" ht="15.75" customHeight="1">
+    <row r="122" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="10"/>
       <c r="B122" s="54" t="s">
         <v>223</v>
@@ -14593,7 +14604,7 @@
       <c r="P122" s="37"/>
       <c r="Q122" s="37"/>
     </row>
-    <row r="123" spans="1:17" ht="15.75" customHeight="1">
+    <row r="123" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A123" s="10"/>
       <c r="B123" s="178" t="s">
         <v>170</v>
@@ -14614,7 +14625,7 @@
       <c r="P123" s="12"/>
       <c r="Q123" s="12"/>
     </row>
-    <row r="124" spans="1:17" ht="15.75" customHeight="1">
+    <row r="124" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A124" s="10"/>
       <c r="B124" s="27" t="str">
         <f>"FCFE per share ("&amp;Market_currency&amp;")"</f>
@@ -14672,795 +14683,795 @@
         <v/>
       </c>
     </row>
-    <row r="125" spans="1:17" ht="15.75" customHeight="1">
+    <row r="125" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A125" s="10"/>
       <c r="B125" s="27" t="s">
         <v>269</v>
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>3.2959893754197021E-2</v>
+        <v>3.2789369544086615E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>3.7557662667082159E-2</v>
+        <v>3.7363351034658238E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>4.9389150553378051E-2</v>
+        <v>4.9133626492865387E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>9.7141543464914729E-2</v>
+        <v>9.6638963417424423E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>6.2905565142418962E-2</v>
+        <v>6.2580111368585309E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>4.7040613171561454E-2</v>
+        <v>4.6797239710954709E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>3.9080249684365527E-2</v>
+        <v>3.8878060661608281E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>2.7557911709179189E-2</v>
+        <v>2.7415335669294303E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>2.5051642766932291E-2</v>
+        <v>2.4922033380850604E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>1.6574446516555499E-2</v>
+        <v>1.6488695499840136E-2</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>1.6206219120686646E-2</v>
+        <v>1.6122373197667576E-2</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
         <v/>
       </c>
     </row>
-    <row r="126" spans="1:17" ht="15.75" customHeight="1">
+    <row r="126" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B126" s="2" t="s">
         <v>394</v>
       </c>
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.8755585509235665E-2</v>
+        <v>4.850333931665278E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.9841317884249103E-2</v>
+        <v>5.9531717569992086E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10747495502994261</v>
+        <v>0.10691891313400056</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.4247844640258622E-2</v>
+        <v>6.3915446330959427E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.5477149606968886E-2</v>
+        <v>4.5241865019201868E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.6839788370088535E-2</v>
+        <v>3.6649190795372627E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.691860162447663E-2</v>
+        <v>2.6779333175569509E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.8737044980259632E-2</v>
+        <v>1.8640105353606405E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.6440923340325618E-2</v>
+        <v>1.6355863130878258E-2</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.4634452101367462E-2</v>
+        <v>1.4558738010673027E-2</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
         <v/>
       </c>
     </row>
-    <row r="127" spans="1:17" ht="15.75" customHeight="1"/>
-    <row r="128" spans="1:17" ht="15.75" customHeight="1"/>
-    <row r="129" ht="15.75" customHeight="1"/>
-    <row r="130" ht="15.75" customHeight="1"/>
-    <row r="131" ht="15.75" customHeight="1"/>
-    <row r="132" ht="15.75" customHeight="1"/>
-    <row r="133" ht="15.75" customHeight="1"/>
-    <row r="134" ht="15.75" customHeight="1"/>
-    <row r="135" ht="15.75" customHeight="1"/>
-    <row r="136" ht="15.75" customHeight="1"/>
-    <row r="137" ht="15.75" customHeight="1"/>
-    <row r="138" ht="15.75" customHeight="1"/>
-    <row r="139" ht="15.75" customHeight="1"/>
-    <row r="140" ht="15.75" customHeight="1"/>
-    <row r="141" ht="15.75" customHeight="1"/>
-    <row r="142" ht="15.75" customHeight="1"/>
-    <row r="143" ht="15.75" customHeight="1"/>
-    <row r="144" ht="15.75" customHeight="1"/>
-    <row r="145" ht="15.75" customHeight="1"/>
-    <row r="146" ht="15.75" customHeight="1"/>
-    <row r="147" ht="15.75" customHeight="1"/>
-    <row r="148" ht="15.75" customHeight="1"/>
-    <row r="149" ht="15.75" customHeight="1"/>
-    <row r="150" ht="15.75" customHeight="1"/>
-    <row r="151" ht="15.75" customHeight="1"/>
-    <row r="152" ht="15.75" customHeight="1"/>
-    <row r="153" ht="15.75" customHeight="1"/>
-    <row r="154" ht="15.75" customHeight="1"/>
-    <row r="155" ht="15.75" customHeight="1"/>
-    <row r="156" ht="15.75" customHeight="1"/>
-    <row r="157" ht="15.75" customHeight="1"/>
-    <row r="158" ht="15.75" customHeight="1"/>
-    <row r="159" ht="15.75" customHeight="1"/>
-    <row r="160" ht="15.75" customHeight="1"/>
-    <row r="161" ht="15.75" customHeight="1"/>
-    <row r="162" ht="15.75" customHeight="1"/>
-    <row r="163" ht="15.75" customHeight="1"/>
-    <row r="164" ht="15.75" customHeight="1"/>
-    <row r="165" ht="15.75" customHeight="1"/>
-    <row r="166" ht="15.75" customHeight="1"/>
-    <row r="167" ht="15.75" customHeight="1"/>
-    <row r="168" ht="15.75" customHeight="1"/>
-    <row r="169" ht="15.75" customHeight="1"/>
-    <row r="170" ht="15.75" customHeight="1"/>
-    <row r="171" ht="15.75" customHeight="1"/>
-    <row r="172" ht="15.75" customHeight="1"/>
-    <row r="173" ht="15.75" customHeight="1"/>
-    <row r="174" ht="15.75" customHeight="1"/>
-    <row r="175" ht="15.75" customHeight="1"/>
-    <row r="176" ht="15.75" customHeight="1"/>
-    <row r="177" ht="15.75" customHeight="1"/>
-    <row r="178" ht="15.75" customHeight="1"/>
-    <row r="179" ht="15.75" customHeight="1"/>
-    <row r="180" ht="15.75" customHeight="1"/>
-    <row r="181" ht="15.75" customHeight="1"/>
-    <row r="182" ht="15.75" customHeight="1"/>
-    <row r="183" ht="15.75" customHeight="1"/>
-    <row r="184" ht="15.75" customHeight="1"/>
-    <row r="185" ht="15.75" customHeight="1"/>
-    <row r="186" ht="15.75" customHeight="1"/>
-    <row r="187" ht="15.75" customHeight="1"/>
-    <row r="188" ht="15.75" customHeight="1"/>
-    <row r="189" ht="15.75" customHeight="1"/>
-    <row r="190" ht="15.75" customHeight="1"/>
-    <row r="191" ht="15.75" customHeight="1"/>
-    <row r="192" ht="15.75" customHeight="1"/>
-    <row r="193" ht="15.75" customHeight="1"/>
-    <row r="194" ht="15.75" customHeight="1"/>
-    <row r="195" ht="15.75" customHeight="1"/>
-    <row r="196" ht="15.75" customHeight="1"/>
-    <row r="197" ht="15.75" customHeight="1"/>
-    <row r="198" ht="15.75" customHeight="1"/>
-    <row r="199" ht="15.75" customHeight="1"/>
-    <row r="200" ht="15.75" customHeight="1"/>
-    <row r="201" ht="15.75" customHeight="1"/>
-    <row r="202" ht="15.75" customHeight="1"/>
-    <row r="203" ht="15.75" customHeight="1"/>
-    <row r="204" ht="15.75" customHeight="1"/>
-    <row r="205" ht="15.75" customHeight="1"/>
-    <row r="206" ht="15.75" customHeight="1"/>
-    <row r="207" ht="15.75" customHeight="1"/>
-    <row r="208" ht="15.75" customHeight="1"/>
-    <row r="209" ht="15.75" customHeight="1"/>
-    <row r="210" ht="15.75" customHeight="1"/>
-    <row r="211" ht="15.75" customHeight="1"/>
-    <row r="212" ht="15.75" customHeight="1"/>
-    <row r="213" ht="15.75" customHeight="1"/>
-    <row r="214" ht="15.75" customHeight="1"/>
-    <row r="215" ht="15.75" customHeight="1"/>
-    <row r="216" ht="15.75" customHeight="1"/>
-    <row r="217" ht="15.75" customHeight="1"/>
-    <row r="218" ht="15.75" customHeight="1"/>
-    <row r="219" ht="15.75" customHeight="1"/>
-    <row r="220" ht="15.75" customHeight="1"/>
-    <row r="221" ht="15.75" customHeight="1"/>
-    <row r="222" ht="15.75" customHeight="1"/>
-    <row r="223" ht="15.75" customHeight="1"/>
-    <row r="224" ht="15.75" customHeight="1"/>
-    <row r="225" ht="15.75" customHeight="1"/>
-    <row r="226" ht="15.75" customHeight="1"/>
-    <row r="227" ht="15.75" customHeight="1"/>
-    <row r="228" ht="15.75" customHeight="1"/>
-    <row r="229" ht="15.75" customHeight="1"/>
-    <row r="230" ht="15.75" customHeight="1"/>
-    <row r="231" ht="15.75" customHeight="1"/>
-    <row r="232" ht="15.75" customHeight="1"/>
-    <row r="233" ht="15.75" customHeight="1"/>
-    <row r="234" ht="15.75" customHeight="1"/>
-    <row r="235" ht="15.75" customHeight="1"/>
-    <row r="236" ht="15.75" customHeight="1"/>
-    <row r="237" ht="15.75" customHeight="1"/>
-    <row r="238" ht="15.75" customHeight="1"/>
-    <row r="239" ht="15.75" customHeight="1"/>
-    <row r="240" ht="15.75" customHeight="1"/>
-    <row r="241" ht="15.75" customHeight="1"/>
-    <row r="242" ht="15.75" customHeight="1"/>
-    <row r="243" ht="15.75" customHeight="1"/>
-    <row r="244" ht="15.75" customHeight="1"/>
-    <row r="245" ht="15.75" customHeight="1"/>
-    <row r="246" ht="15.75" customHeight="1"/>
-    <row r="247" ht="15.75" customHeight="1"/>
-    <row r="248" ht="15.75" customHeight="1"/>
-    <row r="249" ht="15.75" customHeight="1"/>
-    <row r="250" ht="15.75" customHeight="1"/>
-    <row r="251" ht="15.75" customHeight="1"/>
-    <row r="252" ht="15.75" customHeight="1"/>
-    <row r="253" ht="15.75" customHeight="1"/>
-    <row r="254" ht="15.75" customHeight="1"/>
-    <row r="255" ht="15.75" customHeight="1"/>
-    <row r="256" ht="15.75" customHeight="1"/>
-    <row r="257" ht="15.75" customHeight="1"/>
-    <row r="258" ht="15.75" customHeight="1"/>
-    <row r="259" ht="15.75" customHeight="1"/>
-    <row r="260" ht="15.75" customHeight="1"/>
-    <row r="261" ht="15.75" customHeight="1"/>
-    <row r="262" ht="15.75" customHeight="1"/>
-    <row r="263" ht="15.75" customHeight="1"/>
-    <row r="264" ht="15.75" customHeight="1"/>
-    <row r="265" ht="15.75" customHeight="1"/>
-    <row r="266" ht="15.75" customHeight="1"/>
-    <row r="267" ht="15.75" customHeight="1"/>
-    <row r="268" ht="15.75" customHeight="1"/>
-    <row r="269" ht="15.75" customHeight="1"/>
-    <row r="270" ht="15.75" customHeight="1"/>
-    <row r="271" ht="15.75" customHeight="1"/>
-    <row r="272" ht="15.75" customHeight="1"/>
-    <row r="273" ht="15.75" customHeight="1"/>
-    <row r="274" ht="15.75" customHeight="1"/>
-    <row r="275" ht="15.75" customHeight="1"/>
-    <row r="276" ht="15.75" customHeight="1"/>
-    <row r="277" ht="15.75" customHeight="1"/>
-    <row r="278" ht="15.75" customHeight="1"/>
-    <row r="279" ht="15.75" customHeight="1"/>
-    <row r="280" ht="15.75" customHeight="1"/>
-    <row r="281" ht="15.75" customHeight="1"/>
-    <row r="282" ht="15.75" customHeight="1"/>
-    <row r="283" ht="15.75" customHeight="1"/>
-    <row r="284" ht="15.75" customHeight="1"/>
-    <row r="285" ht="15.75" customHeight="1"/>
-    <row r="286" ht="15.75" customHeight="1"/>
-    <row r="287" ht="15.75" customHeight="1"/>
-    <row r="288" ht="15.75" customHeight="1"/>
-    <row r="289" ht="15.75" customHeight="1"/>
-    <row r="290" ht="15.75" customHeight="1"/>
-    <row r="291" ht="15.75" customHeight="1"/>
-    <row r="292" ht="15.75" customHeight="1"/>
-    <row r="293" ht="15.75" customHeight="1"/>
-    <row r="294" ht="15.75" customHeight="1"/>
-    <row r="295" ht="15.75" customHeight="1"/>
-    <row r="296" ht="15.75" customHeight="1"/>
-    <row r="297" ht="15.75" customHeight="1"/>
-    <row r="298" ht="15.75" customHeight="1"/>
-    <row r="299" ht="15.75" customHeight="1"/>
-    <row r="300" ht="15.75" customHeight="1"/>
-    <row r="301" ht="15.75" customHeight="1"/>
-    <row r="302" ht="15.75" customHeight="1"/>
-    <row r="303" ht="15.75" customHeight="1"/>
-    <row r="304" ht="15.75" customHeight="1"/>
-    <row r="305" ht="15.75" customHeight="1"/>
-    <row r="306" ht="15.75" customHeight="1"/>
-    <row r="307" ht="15.75" customHeight="1"/>
-    <row r="308" ht="15.75" customHeight="1"/>
-    <row r="309" ht="15.75" customHeight="1"/>
-    <row r="310" ht="15.75" customHeight="1"/>
-    <row r="311" ht="15.75" customHeight="1"/>
-    <row r="312" ht="15.75" customHeight="1"/>
-    <row r="313" ht="15.75" customHeight="1"/>
-    <row r="314" ht="15.75" customHeight="1"/>
-    <row r="315" ht="15.75" customHeight="1"/>
-    <row r="316" ht="15.75" customHeight="1"/>
-    <row r="317" ht="15.75" customHeight="1"/>
-    <row r="318" ht="15.75" customHeight="1"/>
-    <row r="319" ht="15.75" customHeight="1"/>
-    <row r="320" ht="15.75" customHeight="1"/>
-    <row r="321" ht="15.75" customHeight="1"/>
-    <row r="322" ht="15.75" customHeight="1"/>
-    <row r="323" ht="15.75" customHeight="1"/>
-    <row r="324" ht="15.75" customHeight="1"/>
-    <row r="325" ht="15.75" customHeight="1"/>
-    <row r="326" ht="15.75" customHeight="1"/>
-    <row r="327" ht="15.75" customHeight="1"/>
-    <row r="328" ht="15.75" customHeight="1"/>
-    <row r="329" ht="15.75" customHeight="1"/>
-    <row r="330" ht="15.75" customHeight="1"/>
-    <row r="331" ht="15.75" customHeight="1"/>
-    <row r="332" ht="15.75" customHeight="1"/>
-    <row r="333" ht="15.75" customHeight="1"/>
-    <row r="334" ht="15.75" customHeight="1"/>
-    <row r="335" ht="15.75" customHeight="1"/>
-    <row r="336" ht="15.75" customHeight="1"/>
-    <row r="337" ht="15.75" customHeight="1"/>
-    <row r="338" ht="15.75" customHeight="1"/>
-    <row r="339" ht="15.75" customHeight="1"/>
-    <row r="340" ht="15.75" customHeight="1"/>
-    <row r="341" ht="15.75" customHeight="1"/>
-    <row r="342" ht="15.75" customHeight="1"/>
-    <row r="343" ht="15.75" customHeight="1"/>
-    <row r="344" ht="15.75" customHeight="1"/>
-    <row r="345" ht="15.75" customHeight="1"/>
-    <row r="346" ht="15.75" customHeight="1"/>
-    <row r="347" ht="15.75" customHeight="1"/>
-    <row r="348" ht="15.75" customHeight="1"/>
-    <row r="349" ht="15.75" customHeight="1"/>
-    <row r="350" ht="15.75" customHeight="1"/>
-    <row r="351" ht="15.75" customHeight="1"/>
-    <row r="352" ht="15.75" customHeight="1"/>
-    <row r="353" ht="15.75" customHeight="1"/>
-    <row r="354" ht="15.75" customHeight="1"/>
-    <row r="355" ht="15.75" customHeight="1"/>
-    <row r="356" ht="15.75" customHeight="1"/>
-    <row r="357" ht="15.75" customHeight="1"/>
-    <row r="358" ht="15.75" customHeight="1"/>
-    <row r="359" ht="15.75" customHeight="1"/>
-    <row r="360" ht="15.75" customHeight="1"/>
-    <row r="361" ht="15.75" customHeight="1"/>
-    <row r="362" ht="15.75" customHeight="1"/>
-    <row r="363" ht="15.75" customHeight="1"/>
-    <row r="364" ht="15.75" customHeight="1"/>
-    <row r="365" ht="15.75" customHeight="1"/>
-    <row r="366" ht="15.75" customHeight="1"/>
-    <row r="367" ht="15.75" customHeight="1"/>
-    <row r="368" ht="15.75" customHeight="1"/>
-    <row r="369" ht="15.75" customHeight="1"/>
-    <row r="370" ht="15.75" customHeight="1"/>
-    <row r="371" ht="15.75" customHeight="1"/>
-    <row r="372" ht="15.75" customHeight="1"/>
-    <row r="373" ht="15.75" customHeight="1"/>
-    <row r="374" ht="15.75" customHeight="1"/>
-    <row r="375" ht="15.75" customHeight="1"/>
-    <row r="376" ht="15.75" customHeight="1"/>
-    <row r="377" ht="15.75" customHeight="1"/>
-    <row r="378" ht="15.75" customHeight="1"/>
-    <row r="379" ht="15.75" customHeight="1"/>
-    <row r="380" ht="15.75" customHeight="1"/>
-    <row r="381" ht="15.75" customHeight="1"/>
-    <row r="382" ht="15.75" customHeight="1"/>
-    <row r="383" ht="15.75" customHeight="1"/>
-    <row r="384" ht="15.75" customHeight="1"/>
-    <row r="385" ht="15.75" customHeight="1"/>
-    <row r="386" ht="15.75" customHeight="1"/>
-    <row r="387" ht="15.75" customHeight="1"/>
-    <row r="388" ht="15.75" customHeight="1"/>
-    <row r="389" ht="15.75" customHeight="1"/>
-    <row r="390" ht="15.75" customHeight="1"/>
-    <row r="391" ht="15.75" customHeight="1"/>
-    <row r="392" ht="15.75" customHeight="1"/>
-    <row r="393" ht="15.75" customHeight="1"/>
-    <row r="394" ht="15.75" customHeight="1"/>
-    <row r="395" ht="15.75" customHeight="1"/>
-    <row r="396" ht="15.75" customHeight="1"/>
-    <row r="397" ht="15.75" customHeight="1"/>
-    <row r="398" ht="15.75" customHeight="1"/>
-    <row r="399" ht="15.75" customHeight="1"/>
-    <row r="400" ht="15.75" customHeight="1"/>
-    <row r="401" ht="15.75" customHeight="1"/>
-    <row r="402" ht="15.75" customHeight="1"/>
-    <row r="403" ht="15.75" customHeight="1"/>
-    <row r="404" ht="15.75" customHeight="1"/>
-    <row r="405" ht="15.75" customHeight="1"/>
-    <row r="406" ht="15.75" customHeight="1"/>
-    <row r="407" ht="15.75" customHeight="1"/>
-    <row r="408" ht="15.75" customHeight="1"/>
-    <row r="409" ht="15.75" customHeight="1"/>
-    <row r="410" ht="15.75" customHeight="1"/>
-    <row r="411" ht="15.75" customHeight="1"/>
-    <row r="412" ht="15.75" customHeight="1"/>
-    <row r="413" ht="15.75" customHeight="1"/>
-    <row r="414" ht="15.75" customHeight="1"/>
-    <row r="415" ht="15.75" customHeight="1"/>
-    <row r="416" ht="15.75" customHeight="1"/>
-    <row r="417" ht="15.75" customHeight="1"/>
-    <row r="418" ht="15.75" customHeight="1"/>
-    <row r="419" ht="15.75" customHeight="1"/>
-    <row r="420" ht="15.75" customHeight="1"/>
-    <row r="421" ht="15.75" customHeight="1"/>
-    <row r="422" ht="15.75" customHeight="1"/>
-    <row r="423" ht="15.75" customHeight="1"/>
-    <row r="424" ht="15.75" customHeight="1"/>
-    <row r="425" ht="15.75" customHeight="1"/>
-    <row r="426" ht="15.75" customHeight="1"/>
-    <row r="427" ht="15.75" customHeight="1"/>
-    <row r="428" ht="15.75" customHeight="1"/>
-    <row r="429" ht="15.75" customHeight="1"/>
-    <row r="430" ht="15.75" customHeight="1"/>
-    <row r="431" ht="15.75" customHeight="1"/>
-    <row r="432" ht="15.75" customHeight="1"/>
-    <row r="433" ht="15.75" customHeight="1"/>
-    <row r="434" ht="15.75" customHeight="1"/>
-    <row r="435" ht="15.75" customHeight="1"/>
-    <row r="436" ht="15.75" customHeight="1"/>
-    <row r="437" ht="15.75" customHeight="1"/>
-    <row r="438" ht="15.75" customHeight="1"/>
-    <row r="439" ht="15.75" customHeight="1"/>
-    <row r="440" ht="15.75" customHeight="1"/>
-    <row r="441" ht="15.75" customHeight="1"/>
-    <row r="442" ht="15.75" customHeight="1"/>
-    <row r="443" ht="15.75" customHeight="1"/>
-    <row r="444" ht="15.75" customHeight="1"/>
-    <row r="445" ht="15.75" customHeight="1"/>
-    <row r="446" ht="15.75" customHeight="1"/>
-    <row r="447" ht="15.75" customHeight="1"/>
-    <row r="448" ht="15.75" customHeight="1"/>
-    <row r="449" ht="15.75" customHeight="1"/>
-    <row r="450" ht="15.75" customHeight="1"/>
-    <row r="451" ht="15.75" customHeight="1"/>
-    <row r="452" ht="15.75" customHeight="1"/>
-    <row r="453" ht="15.75" customHeight="1"/>
-    <row r="454" ht="15.75" customHeight="1"/>
-    <row r="455" ht="15.75" customHeight="1"/>
-    <row r="456" ht="15.75" customHeight="1"/>
-    <row r="457" ht="15.75" customHeight="1"/>
-    <row r="458" ht="15.75" customHeight="1"/>
-    <row r="459" ht="15.75" customHeight="1"/>
-    <row r="460" ht="15.75" customHeight="1"/>
-    <row r="461" ht="15.75" customHeight="1"/>
-    <row r="462" ht="15.75" customHeight="1"/>
-    <row r="463" ht="15.75" customHeight="1"/>
-    <row r="464" ht="15.75" customHeight="1"/>
-    <row r="465" ht="15.75" customHeight="1"/>
-    <row r="466" ht="15.75" customHeight="1"/>
-    <row r="467" ht="15.75" customHeight="1"/>
-    <row r="468" ht="15.75" customHeight="1"/>
-    <row r="469" ht="15.75" customHeight="1"/>
-    <row r="470" ht="15.75" customHeight="1"/>
-    <row r="471" ht="15.75" customHeight="1"/>
-    <row r="472" ht="15.75" customHeight="1"/>
-    <row r="473" ht="15.75" customHeight="1"/>
-    <row r="474" ht="15.75" customHeight="1"/>
-    <row r="475" ht="15.75" customHeight="1"/>
-    <row r="476" ht="15.75" customHeight="1"/>
-    <row r="477" ht="15.75" customHeight="1"/>
-    <row r="478" ht="15.75" customHeight="1"/>
-    <row r="479" ht="15.75" customHeight="1"/>
-    <row r="480" ht="15.75" customHeight="1"/>
-    <row r="481" ht="15.75" customHeight="1"/>
-    <row r="482" ht="15.75" customHeight="1"/>
-    <row r="483" ht="15.75" customHeight="1"/>
-    <row r="484" ht="15.75" customHeight="1"/>
-    <row r="485" ht="15.75" customHeight="1"/>
-    <row r="486" ht="15.75" customHeight="1"/>
-    <row r="487" ht="15.75" customHeight="1"/>
-    <row r="488" ht="15.75" customHeight="1"/>
-    <row r="489" ht="15.75" customHeight="1"/>
-    <row r="490" ht="15.75" customHeight="1"/>
-    <row r="491" ht="15.75" customHeight="1"/>
-    <row r="492" ht="15.75" customHeight="1"/>
-    <row r="493" ht="15.75" customHeight="1"/>
-    <row r="494" ht="15.75" customHeight="1"/>
-    <row r="495" ht="15.75" customHeight="1"/>
-    <row r="496" ht="15.75" customHeight="1"/>
-    <row r="497" ht="15.75" customHeight="1"/>
-    <row r="498" ht="15.75" customHeight="1"/>
-    <row r="499" ht="15.75" customHeight="1"/>
-    <row r="500" ht="15.75" customHeight="1"/>
-    <row r="501" ht="15.75" customHeight="1"/>
-    <row r="502" ht="15.75" customHeight="1"/>
-    <row r="503" ht="15.75" customHeight="1"/>
-    <row r="504" ht="15.75" customHeight="1"/>
-    <row r="505" ht="15.75" customHeight="1"/>
-    <row r="506" ht="15.75" customHeight="1"/>
-    <row r="507" ht="15.75" customHeight="1"/>
-    <row r="508" ht="15.75" customHeight="1"/>
-    <row r="509" ht="15.75" customHeight="1"/>
-    <row r="510" ht="15.75" customHeight="1"/>
-    <row r="511" ht="15.75" customHeight="1"/>
-    <row r="512" ht="15.75" customHeight="1"/>
-    <row r="513" ht="15.75" customHeight="1"/>
-    <row r="514" ht="15.75" customHeight="1"/>
-    <row r="515" ht="15.75" customHeight="1"/>
-    <row r="516" ht="15.75" customHeight="1"/>
-    <row r="517" ht="15.75" customHeight="1"/>
-    <row r="518" ht="15.75" customHeight="1"/>
-    <row r="519" ht="15.75" customHeight="1"/>
-    <row r="520" ht="15.75" customHeight="1"/>
-    <row r="521" ht="15.75" customHeight="1"/>
-    <row r="522" ht="15.75" customHeight="1"/>
-    <row r="523" ht="15.75" customHeight="1"/>
-    <row r="524" ht="15.75" customHeight="1"/>
-    <row r="525" ht="15.75" customHeight="1"/>
-    <row r="526" ht="15.75" customHeight="1"/>
-    <row r="527" ht="15.75" customHeight="1"/>
-    <row r="528" ht="15.75" customHeight="1"/>
-    <row r="529" ht="15.75" customHeight="1"/>
-    <row r="530" ht="15.75" customHeight="1"/>
-    <row r="531" ht="15.75" customHeight="1"/>
-    <row r="532" ht="15.75" customHeight="1"/>
-    <row r="533" ht="15.75" customHeight="1"/>
-    <row r="534" ht="15.75" customHeight="1"/>
-    <row r="535" ht="15.75" customHeight="1"/>
-    <row r="536" ht="15.75" customHeight="1"/>
-    <row r="537" ht="15.75" customHeight="1"/>
-    <row r="538" ht="15.75" customHeight="1"/>
-    <row r="539" ht="15.75" customHeight="1"/>
-    <row r="540" ht="15.75" customHeight="1"/>
-    <row r="541" ht="15.75" customHeight="1"/>
-    <row r="542" ht="15.75" customHeight="1"/>
-    <row r="543" ht="15.75" customHeight="1"/>
-    <row r="544" ht="15.75" customHeight="1"/>
-    <row r="545" ht="15.75" customHeight="1"/>
-    <row r="546" ht="15.75" customHeight="1"/>
-    <row r="547" ht="15.75" customHeight="1"/>
-    <row r="548" ht="15.75" customHeight="1"/>
-    <row r="549" ht="15.75" customHeight="1"/>
-    <row r="550" ht="15.75" customHeight="1"/>
-    <row r="551" ht="15.75" customHeight="1"/>
-    <row r="552" ht="15.75" customHeight="1"/>
-    <row r="553" ht="15.75" customHeight="1"/>
-    <row r="554" ht="15.75" customHeight="1"/>
-    <row r="555" ht="15.75" customHeight="1"/>
-    <row r="556" ht="15.75" customHeight="1"/>
-    <row r="557" ht="15.75" customHeight="1"/>
-    <row r="558" ht="15.75" customHeight="1"/>
-    <row r="559" ht="15.75" customHeight="1"/>
-    <row r="560" ht="15.75" customHeight="1"/>
-    <row r="561" ht="15.75" customHeight="1"/>
-    <row r="562" ht="15.75" customHeight="1"/>
-    <row r="563" ht="15.75" customHeight="1"/>
-    <row r="564" ht="15.75" customHeight="1"/>
-    <row r="565" ht="15.75" customHeight="1"/>
-    <row r="566" ht="15.75" customHeight="1"/>
-    <row r="567" ht="15.75" customHeight="1"/>
-    <row r="568" ht="15.75" customHeight="1"/>
-    <row r="569" ht="15.75" customHeight="1"/>
-    <row r="570" ht="15.75" customHeight="1"/>
-    <row r="571" ht="15.75" customHeight="1"/>
-    <row r="572" ht="15.75" customHeight="1"/>
-    <row r="573" ht="15.75" customHeight="1"/>
-    <row r="574" ht="15.75" customHeight="1"/>
-    <row r="575" ht="15.75" customHeight="1"/>
-    <row r="576" ht="15.75" customHeight="1"/>
-    <row r="577" ht="15.75" customHeight="1"/>
-    <row r="578" ht="15.75" customHeight="1"/>
-    <row r="579" ht="15.75" customHeight="1"/>
-    <row r="580" ht="15.75" customHeight="1"/>
-    <row r="581" ht="15.75" customHeight="1"/>
-    <row r="582" ht="15.75" customHeight="1"/>
-    <row r="583" ht="15.75" customHeight="1"/>
-    <row r="584" ht="15.75" customHeight="1"/>
-    <row r="585" ht="15.75" customHeight="1"/>
-    <row r="586" ht="15.75" customHeight="1"/>
-    <row r="587" ht="15.75" customHeight="1"/>
-    <row r="588" ht="15.75" customHeight="1"/>
-    <row r="589" ht="15.75" customHeight="1"/>
-    <row r="590" ht="15.75" customHeight="1"/>
-    <row r="591" ht="15.75" customHeight="1"/>
-    <row r="592" ht="15.75" customHeight="1"/>
-    <row r="593" ht="15.75" customHeight="1"/>
-    <row r="594" ht="15.75" customHeight="1"/>
-    <row r="595" ht="15.75" customHeight="1"/>
-    <row r="596" ht="15.75" customHeight="1"/>
-    <row r="597" ht="15.75" customHeight="1"/>
-    <row r="598" ht="15.75" customHeight="1"/>
-    <row r="599" ht="15.75" customHeight="1"/>
-    <row r="600" ht="15.75" customHeight="1"/>
-    <row r="601" ht="15.75" customHeight="1"/>
-    <row r="602" ht="15.75" customHeight="1"/>
-    <row r="603" ht="15.75" customHeight="1"/>
-    <row r="604" ht="15.75" customHeight="1"/>
-    <row r="605" ht="15.75" customHeight="1"/>
-    <row r="606" ht="15.75" customHeight="1"/>
-    <row r="607" ht="15.75" customHeight="1"/>
-    <row r="608" ht="15.75" customHeight="1"/>
-    <row r="609" ht="15.75" customHeight="1"/>
-    <row r="610" ht="15.75" customHeight="1"/>
-    <row r="611" ht="15.75" customHeight="1"/>
-    <row r="612" ht="15.75" customHeight="1"/>
-    <row r="613" ht="15.75" customHeight="1"/>
-    <row r="614" ht="15.75" customHeight="1"/>
-    <row r="615" ht="15.75" customHeight="1"/>
-    <row r="616" ht="15.75" customHeight="1"/>
-    <row r="617" ht="15.75" customHeight="1"/>
-    <row r="618" ht="15.75" customHeight="1"/>
-    <row r="619" ht="15.75" customHeight="1"/>
-    <row r="620" ht="15.75" customHeight="1"/>
-    <row r="621" ht="15.75" customHeight="1"/>
-    <row r="622" ht="15.75" customHeight="1"/>
-    <row r="623" ht="15.75" customHeight="1"/>
-    <row r="624" ht="15.75" customHeight="1"/>
-    <row r="625" ht="15.75" customHeight="1"/>
-    <row r="626" ht="15.75" customHeight="1"/>
-    <row r="627" ht="15.75" customHeight="1"/>
-    <row r="628" ht="15.75" customHeight="1"/>
-    <row r="629" ht="15.75" customHeight="1"/>
-    <row r="630" ht="15.75" customHeight="1"/>
-    <row r="631" ht="15.75" customHeight="1"/>
-    <row r="632" ht="15.75" customHeight="1"/>
-    <row r="633" ht="15.75" customHeight="1"/>
-    <row r="634" ht="15.75" customHeight="1"/>
-    <row r="635" ht="15.75" customHeight="1"/>
-    <row r="636" ht="15.75" customHeight="1"/>
-    <row r="637" ht="15.75" customHeight="1"/>
-    <row r="638" ht="15.75" customHeight="1"/>
-    <row r="639" ht="15.75" customHeight="1"/>
-    <row r="640" ht="15.75" customHeight="1"/>
-    <row r="641" ht="15.75" customHeight="1"/>
-    <row r="642" ht="15.75" customHeight="1"/>
-    <row r="643" ht="15.75" customHeight="1"/>
-    <row r="644" ht="15.75" customHeight="1"/>
-    <row r="645" ht="15.75" customHeight="1"/>
-    <row r="646" ht="15.75" customHeight="1"/>
-    <row r="647" ht="15.75" customHeight="1"/>
-    <row r="648" ht="15.75" customHeight="1"/>
-    <row r="649" ht="15.75" customHeight="1"/>
-    <row r="650" ht="15.75" customHeight="1"/>
-    <row r="651" ht="15.75" customHeight="1"/>
-    <row r="652" ht="15.75" customHeight="1"/>
-    <row r="653" ht="15.75" customHeight="1"/>
-    <row r="654" ht="15.75" customHeight="1"/>
-    <row r="655" ht="15.75" customHeight="1"/>
-    <row r="656" ht="15.75" customHeight="1"/>
-    <row r="657" ht="15.75" customHeight="1"/>
-    <row r="658" ht="15.75" customHeight="1"/>
-    <row r="659" ht="15.75" customHeight="1"/>
-    <row r="660" ht="15.75" customHeight="1"/>
-    <row r="661" ht="15.75" customHeight="1"/>
-    <row r="662" ht="15.75" customHeight="1"/>
-    <row r="663" ht="15.75" customHeight="1"/>
-    <row r="664" ht="15.75" customHeight="1"/>
-    <row r="665" ht="15.75" customHeight="1"/>
-    <row r="666" ht="15.75" customHeight="1"/>
-    <row r="667" ht="15.75" customHeight="1"/>
-    <row r="668" ht="15.75" customHeight="1"/>
-    <row r="669" ht="15.75" customHeight="1"/>
-    <row r="670" ht="15.75" customHeight="1"/>
-    <row r="671" ht="15.75" customHeight="1"/>
-    <row r="672" ht="15.75" customHeight="1"/>
-    <row r="673" ht="15.75" customHeight="1"/>
-    <row r="674" ht="15.75" customHeight="1"/>
-    <row r="675" ht="15.75" customHeight="1"/>
-    <row r="676" ht="15.75" customHeight="1"/>
-    <row r="677" ht="15.75" customHeight="1"/>
-    <row r="678" ht="15.75" customHeight="1"/>
-    <row r="679" ht="15.75" customHeight="1"/>
-    <row r="680" ht="15.75" customHeight="1"/>
-    <row r="681" ht="15.75" customHeight="1"/>
-    <row r="682" ht="15.75" customHeight="1"/>
-    <row r="683" ht="15.75" customHeight="1"/>
-    <row r="684" ht="15.75" customHeight="1"/>
-    <row r="685" ht="15.75" customHeight="1"/>
-    <row r="686" ht="15.75" customHeight="1"/>
-    <row r="687" ht="15.75" customHeight="1"/>
-    <row r="688" ht="15.75" customHeight="1"/>
-    <row r="689" ht="15.75" customHeight="1"/>
-    <row r="690" ht="15.75" customHeight="1"/>
-    <row r="691" ht="15.75" customHeight="1"/>
-    <row r="692" ht="15.75" customHeight="1"/>
-    <row r="693" ht="15.75" customHeight="1"/>
-    <row r="694" ht="15.75" customHeight="1"/>
-    <row r="695" ht="15.75" customHeight="1"/>
-    <row r="696" ht="15.75" customHeight="1"/>
-    <row r="697" ht="15.75" customHeight="1"/>
-    <row r="698" ht="15.75" customHeight="1"/>
-    <row r="699" ht="15.75" customHeight="1"/>
-    <row r="700" ht="15.75" customHeight="1"/>
-    <row r="701" ht="15.75" customHeight="1"/>
-    <row r="702" ht="15.75" customHeight="1"/>
-    <row r="703" ht="15.75" customHeight="1"/>
-    <row r="704" ht="15.75" customHeight="1"/>
-    <row r="705" ht="15.75" customHeight="1"/>
-    <row r="706" ht="15.75" customHeight="1"/>
-    <row r="707" ht="15.75" customHeight="1"/>
-    <row r="708" ht="15.75" customHeight="1"/>
-    <row r="709" ht="15.75" customHeight="1"/>
-    <row r="710" ht="15.75" customHeight="1"/>
-    <row r="711" ht="15.75" customHeight="1"/>
-    <row r="712" ht="15.75" customHeight="1"/>
-    <row r="713" ht="15.75" customHeight="1"/>
-    <row r="714" ht="15.75" customHeight="1"/>
-    <row r="715" ht="15.75" customHeight="1"/>
-    <row r="716" ht="15.75" customHeight="1"/>
-    <row r="717" ht="15.75" customHeight="1"/>
-    <row r="718" ht="15.75" customHeight="1"/>
-    <row r="719" ht="15.75" customHeight="1"/>
-    <row r="720" ht="15.75" customHeight="1"/>
-    <row r="721" ht="15.75" customHeight="1"/>
-    <row r="722" ht="15.75" customHeight="1"/>
-    <row r="723" ht="15.75" customHeight="1"/>
-    <row r="724" ht="15.75" customHeight="1"/>
-    <row r="725" ht="15.75" customHeight="1"/>
-    <row r="726" ht="15.75" customHeight="1"/>
-    <row r="727" ht="15.75" customHeight="1"/>
-    <row r="728" ht="15.75" customHeight="1"/>
-    <row r="729" ht="15.75" customHeight="1"/>
-    <row r="730" ht="15.75" customHeight="1"/>
-    <row r="731" ht="15.75" customHeight="1"/>
-    <row r="732" ht="15.75" customHeight="1"/>
-    <row r="733" ht="15.75" customHeight="1"/>
-    <row r="734" ht="15.75" customHeight="1"/>
-    <row r="735" ht="15.75" customHeight="1"/>
-    <row r="736" ht="15.75" customHeight="1"/>
-    <row r="737" ht="15.75" customHeight="1"/>
-    <row r="738" ht="15.75" customHeight="1"/>
-    <row r="739" ht="15.75" customHeight="1"/>
-    <row r="740" ht="15.75" customHeight="1"/>
-    <row r="741" ht="15.75" customHeight="1"/>
-    <row r="742" ht="15.75" customHeight="1"/>
-    <row r="743" ht="15.75" customHeight="1"/>
-    <row r="744" ht="15.75" customHeight="1"/>
-    <row r="745" ht="15.75" customHeight="1"/>
-    <row r="746" ht="15.75" customHeight="1"/>
-    <row r="747" ht="15.75" customHeight="1"/>
-    <row r="748" ht="15.75" customHeight="1"/>
-    <row r="749" ht="15.75" customHeight="1"/>
-    <row r="750" ht="15.75" customHeight="1"/>
-    <row r="751" ht="15.75" customHeight="1"/>
-    <row r="752" ht="15.75" customHeight="1"/>
-    <row r="753" ht="15.75" customHeight="1"/>
-    <row r="754" ht="15.75" customHeight="1"/>
-    <row r="755" ht="15.75" customHeight="1"/>
-    <row r="756" ht="15.75" customHeight="1"/>
-    <row r="757" ht="15.75" customHeight="1"/>
-    <row r="758" ht="15.75" customHeight="1"/>
-    <row r="759" ht="15.75" customHeight="1"/>
-    <row r="760" ht="15.75" customHeight="1"/>
-    <row r="761" ht="15.75" customHeight="1"/>
-    <row r="762" ht="15.75" customHeight="1"/>
-    <row r="763" ht="15.75" customHeight="1"/>
-    <row r="764" ht="15.75" customHeight="1"/>
-    <row r="765" ht="15.75" customHeight="1"/>
-    <row r="766" ht="15.75" customHeight="1"/>
-    <row r="767" ht="15.75" customHeight="1"/>
-    <row r="768" ht="15.75" customHeight="1"/>
-    <row r="769" ht="15.75" customHeight="1"/>
-    <row r="770" ht="15.75" customHeight="1"/>
-    <row r="771" ht="15.75" customHeight="1"/>
-    <row r="772" ht="15.75" customHeight="1"/>
-    <row r="773" ht="15.75" customHeight="1"/>
-    <row r="774" ht="15.75" customHeight="1"/>
-    <row r="775" ht="15.75" customHeight="1"/>
-    <row r="776" ht="15.75" customHeight="1"/>
-    <row r="777" ht="15.75" customHeight="1"/>
-    <row r="778" ht="15.75" customHeight="1"/>
-    <row r="779" ht="15.75" customHeight="1"/>
-    <row r="780" ht="15.75" customHeight="1"/>
-    <row r="781" ht="15.75" customHeight="1"/>
-    <row r="782" ht="15.75" customHeight="1"/>
-    <row r="783" ht="15.75" customHeight="1"/>
-    <row r="784" ht="15.75" customHeight="1"/>
-    <row r="785" ht="15.75" customHeight="1"/>
-    <row r="786" ht="15.75" customHeight="1"/>
-    <row r="787" ht="15.75" customHeight="1"/>
-    <row r="788" ht="15.75" customHeight="1"/>
-    <row r="789" ht="15.75" customHeight="1"/>
-    <row r="790" ht="15.75" customHeight="1"/>
-    <row r="791" ht="15.75" customHeight="1"/>
-    <row r="792" ht="15.75" customHeight="1"/>
-    <row r="793" ht="15.75" customHeight="1"/>
-    <row r="794" ht="15.75" customHeight="1"/>
-    <row r="795" ht="15.75" customHeight="1"/>
-    <row r="796" ht="15.75" customHeight="1"/>
-    <row r="797" ht="15.75" customHeight="1"/>
-    <row r="798" ht="15.75" customHeight="1"/>
-    <row r="799" ht="15.75" customHeight="1"/>
-    <row r="800" ht="15.75" customHeight="1"/>
-    <row r="801" ht="15.75" customHeight="1"/>
-    <row r="802" ht="15.75" customHeight="1"/>
-    <row r="803" ht="15.75" customHeight="1"/>
-    <row r="804" ht="15.75" customHeight="1"/>
-    <row r="805" ht="15.75" customHeight="1"/>
-    <row r="806" ht="15.75" customHeight="1"/>
-    <row r="807" ht="15.75" customHeight="1"/>
-    <row r="808" ht="15.75" customHeight="1"/>
+    <row r="127" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="128" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="G4:Q13 G15:Q16 G23:Q24 G34:Q34">
@@ -15482,16 +15493,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:Q105"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="6.1328125" customWidth="1"/>
-    <col min="2" max="2" width="24.73046875" customWidth="1"/>
-    <col min="3" max="6" width="20.73046875" customWidth="1"/>
-    <col min="7" max="7" width="5.73046875" customWidth="1"/>
-    <col min="8" max="8" width="56.86328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.1640625" customWidth="1"/>
+    <col min="2" max="2" width="24.6640625" customWidth="1"/>
+    <col min="3" max="6" width="20.6640625" customWidth="1"/>
+    <col min="7" max="7" width="5.6640625" customWidth="1"/>
+    <col min="8" max="8" width="56.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="13.9">
+    <row r="2" spans="2:8" ht="16" x14ac:dyDescent="0.25">
       <c r="B2" s="36" t="s">
         <v>55</v>
       </c>
@@ -15503,7 +15514,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="2:8" ht="13.15">
+    <row r="3" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B3" s="109" t="s">
         <v>163</v>
       </c>
@@ -15516,7 +15527,7 @@
       </c>
       <c r="H3" s="120"/>
     </row>
-    <row r="4" spans="2:8">
+    <row r="4" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B4" s="100" t="s">
         <v>128</v>
       </c>
@@ -15537,7 +15548,7 @@
       </c>
       <c r="H4" s="120"/>
     </row>
-    <row r="5" spans="2:8">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B5" s="205" t="s">
         <v>123</v>
       </c>
@@ -15548,7 +15559,7 @@
       <c r="E5" s="148"/>
       <c r="H5" s="120"/>
     </row>
-    <row r="6" spans="2:8" ht="13.35" customHeight="1">
+    <row r="6" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B6" s="149" t="s">
         <v>228</v>
       </c>
@@ -15566,7 +15577,7 @@
       <c r="F6" s="364"/>
       <c r="H6" s="120"/>
     </row>
-    <row r="7" spans="2:8">
+    <row r="7" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B7" s="148" t="s">
         <v>224</v>
       </c>
@@ -15582,7 +15593,7 @@
       <c r="F7" s="364"/>
       <c r="H7" s="120"/>
     </row>
-    <row r="8" spans="2:8">
+    <row r="8" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B8" s="148" t="s">
         <v>225</v>
       </c>
@@ -15598,7 +15609,7 @@
       <c r="F8" s="364"/>
       <c r="H8" s="120"/>
     </row>
-    <row r="9" spans="2:8">
+    <row r="9" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B9" s="205" t="s">
         <v>190</v>
       </c>
@@ -15614,7 +15625,7 @@
       <c r="F9" s="364"/>
       <c r="H9" s="120"/>
     </row>
-    <row r="10" spans="2:8" ht="13.15">
+    <row r="10" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B10" s="149" t="s">
         <v>227</v>
       </c>
@@ -15628,7 +15639,7 @@
       </c>
       <c r="H10" s="120"/>
     </row>
-    <row r="11" spans="2:8" ht="13.15" thickBot="1">
+    <row r="11" spans="2:8" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B11" s="207" t="s">
         <v>166</v>
       </c>
@@ -15642,7 +15653,7 @@
       </c>
       <c r="H11" s="120"/>
     </row>
-    <row r="12" spans="2:8" ht="13.5" thickTop="1">
+    <row r="12" spans="2:8" ht="14" thickTop="1" x14ac:dyDescent="0.15">
       <c r="B12" s="149" t="s">
         <v>102</v>
       </c>
@@ -15656,10 +15667,10 @@
       </c>
       <c r="H12" s="120"/>
     </row>
-    <row r="13" spans="2:8">
+    <row r="13" spans="2:8" x14ac:dyDescent="0.15">
       <c r="H13" s="120"/>
     </row>
-    <row r="14" spans="2:8" ht="13.9">
+    <row r="14" spans="2:8" ht="16" x14ac:dyDescent="0.25">
       <c r="B14" s="36" t="s">
         <v>229</v>
       </c>
@@ -15669,13 +15680,13 @@
       <c r="F14" s="37"/>
       <c r="H14" s="120"/>
     </row>
-    <row r="15" spans="2:8" ht="13.15">
+    <row r="15" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B15" s="119" t="s">
         <v>135</v>
       </c>
       <c r="H15" s="120"/>
     </row>
-    <row r="16" spans="2:8" ht="13.35" customHeight="1">
+    <row r="16" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B16" s="152" t="s">
         <v>133</v>
       </c>
@@ -15685,7 +15696,7 @@
       </c>
       <c r="H16" s="120"/>
     </row>
-    <row r="17" spans="2:17" ht="13.35" customHeight="1">
+    <row r="17" spans="2:17" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="118" t="s">
         <v>134</v>
       </c>
@@ -15695,7 +15706,7 @@
       </c>
       <c r="H17" s="120"/>
     </row>
-    <row r="18" spans="2:17" ht="13.35" customHeight="1">
+    <row r="18" spans="2:17" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="153" t="s">
         <v>106</v>
       </c>
@@ -15709,10 +15720,10 @@
       </c>
       <c r="H18" s="120"/>
     </row>
-    <row r="19" spans="2:17">
+    <row r="19" spans="2:17" x14ac:dyDescent="0.15">
       <c r="H19" s="120"/>
     </row>
-    <row r="20" spans="2:17" ht="13.15">
+    <row r="20" spans="2:17" ht="14" x14ac:dyDescent="0.2">
       <c r="B20" s="128" t="s">
         <v>107</v>
       </c>
@@ -15730,7 +15741,7 @@
       </c>
       <c r="H20" s="120"/>
     </row>
-    <row r="21" spans="2:17">
+    <row r="21" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B21" s="122">
         <v>1</v>
       </c>
@@ -15752,7 +15763,7 @@
       </c>
       <c r="H21" s="120"/>
     </row>
-    <row r="22" spans="2:17">
+    <row r="22" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B22" s="122">
         <v>2</v>
       </c>
@@ -15774,7 +15785,7 @@
       </c>
       <c r="H22" s="120"/>
     </row>
-    <row r="23" spans="2:17">
+    <row r="23" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B23" s="122">
         <v>3</v>
       </c>
@@ -15806,7 +15817,7 @@
       <c r="P23" s="338"/>
       <c r="Q23" s="338"/>
     </row>
-    <row r="24" spans="2:17">
+    <row r="24" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B24" s="122">
         <v>4</v>
       </c>
@@ -15838,7 +15849,7 @@
       <c r="P24" s="338"/>
       <c r="Q24" s="338"/>
     </row>
-    <row r="25" spans="2:17">
+    <row r="25" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B25" s="122">
         <v>5</v>
       </c>
@@ -15870,7 +15881,7 @@
       <c r="P25" s="338"/>
       <c r="Q25" s="338"/>
     </row>
-    <row r="26" spans="2:17">
+    <row r="26" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B26" s="122">
         <v>6</v>
       </c>
@@ -15892,7 +15903,7 @@
       </c>
       <c r="H26" s="120"/>
     </row>
-    <row r="27" spans="2:17">
+    <row r="27" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B27" s="122">
         <v>7</v>
       </c>
@@ -15914,7 +15925,7 @@
       </c>
       <c r="H27" s="120"/>
     </row>
-    <row r="28" spans="2:17">
+    <row r="28" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B28" s="122">
         <v>8</v>
       </c>
@@ -15936,7 +15947,7 @@
       </c>
       <c r="H28" s="120"/>
     </row>
-    <row r="29" spans="2:17">
+    <row r="29" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B29" s="122">
         <v>9</v>
       </c>
@@ -15958,7 +15969,7 @@
       </c>
       <c r="H29" s="120"/>
     </row>
-    <row r="30" spans="2:17">
+    <row r="30" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B30" s="122">
         <v>10</v>
       </c>
@@ -15980,7 +15991,7 @@
       </c>
       <c r="H30" s="120"/>
     </row>
-    <row r="31" spans="2:17">
+    <row r="31" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B31" s="122">
         <v>11</v>
       </c>
@@ -16002,7 +16013,7 @@
       </c>
       <c r="H31" s="120"/>
     </row>
-    <row r="32" spans="2:17">
+    <row r="32" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B32" s="122">
         <v>12</v>
       </c>
@@ -16024,7 +16035,7 @@
       </c>
       <c r="H32" s="120"/>
     </row>
-    <row r="33" spans="2:17">
+    <row r="33" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B33" s="122">
         <v>13</v>
       </c>
@@ -16056,7 +16067,7 @@
       <c r="P33" s="338"/>
       <c r="Q33" s="338"/>
     </row>
-    <row r="34" spans="2:17">
+    <row r="34" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B34" s="122">
         <v>14</v>
       </c>
@@ -16088,7 +16099,7 @@
       <c r="P34" s="338"/>
       <c r="Q34" s="338"/>
     </row>
-    <row r="35" spans="2:17">
+    <row r="35" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B35" s="122">
         <v>15</v>
       </c>
@@ -16120,7 +16131,7 @@
       <c r="P35" s="338"/>
       <c r="Q35" s="338"/>
     </row>
-    <row r="36" spans="2:17">
+    <row r="36" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B36" s="122">
         <v>16</v>
       </c>
@@ -16142,7 +16153,7 @@
       </c>
       <c r="H36" s="120"/>
     </row>
-    <row r="37" spans="2:17">
+    <row r="37" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B37" s="122">
         <v>17</v>
       </c>
@@ -16164,7 +16175,7 @@
       </c>
       <c r="H37" s="120"/>
     </row>
-    <row r="38" spans="2:17">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B38" s="122">
         <v>18</v>
       </c>
@@ -16186,7 +16197,7 @@
       </c>
       <c r="H38" s="120"/>
     </row>
-    <row r="39" spans="2:17">
+    <row r="39" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B39" s="122">
         <v>19</v>
       </c>
@@ -16208,7 +16219,7 @@
       </c>
       <c r="H39" s="120"/>
     </row>
-    <row r="40" spans="2:17">
+    <row r="40" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B40" s="122">
         <v>20</v>
       </c>
@@ -16230,7 +16241,7 @@
       </c>
       <c r="H40" s="120"/>
     </row>
-    <row r="41" spans="2:17">
+    <row r="41" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B41" s="122">
         <v>21</v>
       </c>
@@ -16252,7 +16263,7 @@
       </c>
       <c r="H41" s="120"/>
     </row>
-    <row r="42" spans="2:17">
+    <row r="42" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B42" s="122">
         <v>22</v>
       </c>
@@ -16274,7 +16285,7 @@
       </c>
       <c r="H42" s="120"/>
     </row>
-    <row r="43" spans="2:17">
+    <row r="43" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B43" s="122">
         <v>23</v>
       </c>
@@ -16296,7 +16307,7 @@
       </c>
       <c r="H43" s="120"/>
     </row>
-    <row r="44" spans="2:17">
+    <row r="44" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B44" s="122">
         <v>24</v>
       </c>
@@ -16318,7 +16329,7 @@
       </c>
       <c r="H44" s="120"/>
     </row>
-    <row r="45" spans="2:17">
+    <row r="45" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B45" s="122">
         <v>25</v>
       </c>
@@ -16340,7 +16351,7 @@
       </c>
       <c r="H45" s="120"/>
     </row>
-    <row r="46" spans="2:17">
+    <row r="46" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B46" s="122">
         <v>26</v>
       </c>
@@ -16362,7 +16373,7 @@
       </c>
       <c r="H46" s="120"/>
     </row>
-    <row r="47" spans="2:17">
+    <row r="47" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B47" s="122">
         <v>27</v>
       </c>
@@ -16394,7 +16405,7 @@
       <c r="P47" s="338"/>
       <c r="Q47" s="338"/>
     </row>
-    <row r="48" spans="2:17">
+    <row r="48" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B48" s="122">
         <v>28</v>
       </c>
@@ -16426,7 +16437,7 @@
       <c r="P48" s="338"/>
       <c r="Q48" s="338"/>
     </row>
-    <row r="49" spans="1:17">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.15">
       <c r="B49" s="122">
         <v>29</v>
       </c>
@@ -16458,7 +16469,7 @@
       <c r="P49" s="338"/>
       <c r="Q49" s="338"/>
     </row>
-    <row r="50" spans="1:17">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.15">
       <c r="B50" s="122">
         <v>30</v>
       </c>
@@ -16490,7 +16501,7 @@
       <c r="P50" s="338"/>
       <c r="Q50" s="338"/>
     </row>
-    <row r="51" spans="1:17">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.15">
       <c r="B51" s="126" t="s">
         <v>131</v>
       </c>
@@ -16512,7 +16523,7 @@
       </c>
       <c r="H51" s="120"/>
     </row>
-    <row r="52" spans="1:17">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.15">
       <c r="C52" s="114"/>
       <c r="E52" s="127" t="s">
         <v>100</v>
@@ -16523,11 +16534,11 @@
       </c>
       <c r="H52" s="120"/>
     </row>
-    <row r="53" spans="1:17">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.15">
       <c r="C53" s="114"/>
       <c r="H53" s="120"/>
     </row>
-    <row r="54" spans="1:17" ht="13.15">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.15">
       <c r="B54" s="119" t="s">
         <v>129</v>
       </c>
@@ -16537,7 +16548,7 @@
       <c r="F54" s="117"/>
       <c r="H54" s="120"/>
     </row>
-    <row r="55" spans="1:17" ht="13.15">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A55" s="133">
         <f>F52</f>
         <v>2297163804.1938334</v>
@@ -16564,7 +16575,7 @@
       </c>
       <c r="H55" s="120"/>
     </row>
-    <row r="56" spans="1:17" ht="13.15">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A56" s="143">
         <v>5</v>
       </c>
@@ -16586,7 +16597,7 @@
       </c>
       <c r="H56" s="120"/>
     </row>
-    <row r="57" spans="1:17" ht="13.15">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A57" s="143">
         <v>10</v>
       </c>
@@ -16607,7 +16618,7 @@
       </c>
       <c r="H57" s="120"/>
     </row>
-    <row r="58" spans="1:17" ht="13.15">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A58" s="143">
         <v>15</v>
       </c>
@@ -16638,7 +16649,7 @@
       <c r="P58" s="338"/>
       <c r="Q58" s="338"/>
     </row>
-    <row r="59" spans="1:17" ht="13.15">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A59" s="144">
         <v>20</v>
       </c>
@@ -16669,7 +16680,7 @@
       <c r="P59" s="338"/>
       <c r="Q59" s="338"/>
     </row>
-    <row r="60" spans="1:17" ht="13.15">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A60" s="144">
         <v>25</v>
       </c>
@@ -16700,7 +16711,7 @@
       <c r="P60" s="338"/>
       <c r="Q60" s="338"/>
     </row>
-    <row r="61" spans="1:17" ht="13.15">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A61" s="144">
         <v>30</v>
       </c>
@@ -16731,7 +16742,7 @@
       <c r="P61" s="338"/>
       <c r="Q61" s="338"/>
     </row>
-    <row r="62" spans="1:17">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.15">
       <c r="C62" s="338"/>
       <c r="D62" s="114"/>
       <c r="E62" s="114"/>
@@ -16748,7 +16759,7 @@
       <c r="P62" s="338"/>
       <c r="Q62" s="338"/>
     </row>
-    <row r="63" spans="1:17" ht="13.15">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.15">
       <c r="B63" s="119" t="s">
         <v>130</v>
       </c>
@@ -16768,7 +16779,7 @@
       <c r="P63" s="338"/>
       <c r="Q63" s="338"/>
     </row>
-    <row r="64" spans="1:17" ht="13.15">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.15">
       <c r="B64" s="132">
         <f>B55</f>
         <v>0</v>
@@ -16791,7 +16802,7 @@
       </c>
       <c r="H64" s="120"/>
     </row>
-    <row r="65" spans="1:8" ht="13.15">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A65" s="143">
         <v>0</v>
       </c>
@@ -16817,7 +16828,7 @@
       </c>
       <c r="H65" s="120"/>
     </row>
-    <row r="66" spans="1:8" ht="13.15">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A66" s="143">
         <f t="shared" ref="A66:A71" si="3">A56</f>
         <v>5</v>
@@ -16844,7 +16855,7 @@
       </c>
       <c r="H66" s="120"/>
     </row>
-    <row r="67" spans="1:8" ht="13.15">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A67" s="143">
         <f t="shared" si="3"/>
         <v>10</v>
@@ -16871,7 +16882,7 @@
       </c>
       <c r="H67" s="120"/>
     </row>
-    <row r="68" spans="1:8" ht="13.15">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A68" s="143">
         <f t="shared" si="3"/>
         <v>15</v>
@@ -16898,7 +16909,7 @@
       </c>
       <c r="H68" s="120"/>
     </row>
-    <row r="69" spans="1:8" ht="13.15">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A69" s="144">
         <f t="shared" si="3"/>
         <v>20</v>
@@ -16925,7 +16936,7 @@
       </c>
       <c r="H69" s="120"/>
     </row>
-    <row r="70" spans="1:8" ht="13.15">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A70" s="144">
         <f t="shared" si="3"/>
         <v>25</v>
@@ -16951,7 +16962,7 @@
         <v>18.484891740531104</v>
       </c>
     </row>
-    <row r="71" spans="1:8" ht="13.15">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A71" s="144">
         <f t="shared" si="3"/>
         <v>30</v>
@@ -16977,7 +16988,7 @@
         <v>21.759650934539629</v>
       </c>
     </row>
-    <row r="73" spans="1:8" ht="13.15">
+    <row r="73" spans="1:8" ht="14" x14ac:dyDescent="0.2">
       <c r="B73" s="171" t="s">
         <v>117</v>
       </c>
@@ -16994,7 +17005,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="74" spans="1:8">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B74" s="127" t="str">
         <f>Scenarios!B54</f>
         <v>Snowball Scenario</v>
@@ -17016,7 +17027,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="75" spans="1:8">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B75" s="127" t="str">
         <f>Scenarios!B36</f>
         <v>Optimistic</v>
@@ -17039,7 +17050,7 @@
       </c>
       <c r="H75" s="120"/>
     </row>
-    <row r="76" spans="1:8">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B76" s="127" t="str">
         <f>Scenarios!B24</f>
         <v>Base</v>
@@ -17062,7 +17073,7 @@
       </c>
       <c r="H76" s="120"/>
     </row>
-    <row r="77" spans="1:8">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B77" s="127" t="str">
         <f>Scenarios!B30</f>
         <v>Pessimistic</v>
@@ -17085,7 +17096,7 @@
       </c>
       <c r="H77" s="120"/>
     </row>
-    <row r="78" spans="1:8">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B78" s="127" t="str">
         <f>Scenarios!B48</f>
         <v>Devil's advocate</v>
@@ -17107,14 +17118,14 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="79" spans="1:8">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B79" s="155"/>
       <c r="C79" s="155"/>
       <c r="D79" s="155"/>
       <c r="E79" s="155"/>
       <c r="F79" s="156"/>
     </row>
-    <row r="80" spans="1:8">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B80" s="155" t="s">
         <v>310</v>
       </c>
@@ -17122,26 +17133,26 @@
         <v>105</v>
       </c>
     </row>
-    <row r="81" spans="3:3">
+    <row r="81" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C81" s="155" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="82" spans="3:3">
+    <row r="82" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C82" s="155" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="92" spans="3:3">
+    <row r="92" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C92" s="115"/>
     </row>
-    <row r="93" spans="3:3">
+    <row r="93" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C93" s="115"/>
     </row>
-    <row r="94" spans="3:3">
+    <row r="94" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C94" s="115"/>
     </row>
-    <row r="101" spans="3:17">
+    <row r="101" spans="3:17" x14ac:dyDescent="0.15">
       <c r="C101" s="338"/>
       <c r="G101" s="338"/>
       <c r="H101" s="338"/>
@@ -17155,7 +17166,7 @@
       <c r="P101" s="338"/>
       <c r="Q101" s="338"/>
     </row>
-    <row r="102" spans="3:17">
+    <row r="102" spans="3:17" x14ac:dyDescent="0.15">
       <c r="C102" s="338"/>
       <c r="G102" s="338"/>
       <c r="H102" s="338"/>
@@ -17169,7 +17180,7 @@
       <c r="P102" s="338"/>
       <c r="Q102" s="338"/>
     </row>
-    <row r="103" spans="3:17">
+    <row r="103" spans="3:17" x14ac:dyDescent="0.15">
       <c r="C103" s="338"/>
       <c r="G103" s="338"/>
       <c r="H103" s="338"/>
@@ -17183,7 +17194,7 @@
       <c r="P103" s="338"/>
       <c r="Q103" s="338"/>
     </row>
-    <row r="104" spans="3:17">
+    <row r="104" spans="3:17" x14ac:dyDescent="0.15">
       <c r="C104" s="338"/>
       <c r="G104" s="338"/>
       <c r="H104" s="338"/>
@@ -17197,7 +17208,7 @@
       <c r="P104" s="338"/>
       <c r="Q104" s="338"/>
     </row>
-    <row r="105" spans="3:17">
+    <row r="105" spans="3:17" x14ac:dyDescent="0.15">
       <c r="C105" s="338"/>
       <c r="G105" s="338"/>
       <c r="H105" s="338"/>
@@ -17242,16 +17253,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:H89"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="6.1328125" customWidth="1"/>
-    <col min="2" max="2" width="24.73046875" customWidth="1"/>
-    <col min="3" max="6" width="20.73046875" customWidth="1"/>
-    <col min="7" max="7" width="5.73046875" customWidth="1"/>
-    <col min="8" max="8" width="56.86328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.1640625" customWidth="1"/>
+    <col min="2" max="2" width="24.6640625" customWidth="1"/>
+    <col min="3" max="6" width="20.6640625" customWidth="1"/>
+    <col min="7" max="7" width="5.6640625" customWidth="1"/>
+    <col min="8" max="8" width="56.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="13.9">
+    <row r="2" spans="2:8" ht="16" x14ac:dyDescent="0.25">
       <c r="B2" s="36" t="s">
         <v>443</v>
       </c>
@@ -17263,7 +17274,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="2:8" ht="13.15">
+    <row r="3" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B3" s="109" t="s">
         <v>442</v>
       </c>
@@ -17276,7 +17287,7 @@
       </c>
       <c r="H3" s="120"/>
     </row>
-    <row r="4" spans="2:8">
+    <row r="4" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B4" s="100" t="s">
         <v>440</v>
       </c>
@@ -17297,7 +17308,7 @@
       </c>
       <c r="H4" s="120"/>
     </row>
-    <row r="5" spans="2:8">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B5" s="205" t="s">
         <v>123</v>
       </c>
@@ -17308,7 +17319,7 @@
       <c r="E5" s="148"/>
       <c r="H5" s="120"/>
     </row>
-    <row r="6" spans="2:8" ht="13.35" customHeight="1">
+    <row r="6" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B6" s="149" t="s">
         <v>441</v>
       </c>
@@ -17324,7 +17335,7 @@
       <c r="F6" s="364"/>
       <c r="H6" s="120"/>
     </row>
-    <row r="7" spans="2:8" ht="13.15">
+    <row r="7" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B7" s="149" t="s">
         <v>444</v>
       </c>
@@ -17338,10 +17349,10 @@
       </c>
       <c r="H7" s="120"/>
     </row>
-    <row r="8" spans="2:8">
+    <row r="8" spans="2:8" x14ac:dyDescent="0.15">
       <c r="H8" s="120"/>
     </row>
-    <row r="9" spans="2:8" ht="13.9">
+    <row r="9" spans="2:8" ht="16" x14ac:dyDescent="0.25">
       <c r="B9" s="36" t="s">
         <v>229</v>
       </c>
@@ -17351,13 +17362,13 @@
       <c r="F9" s="37"/>
       <c r="H9" s="120"/>
     </row>
-    <row r="10" spans="2:8" ht="13.15">
+    <row r="10" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B10" s="119" t="s">
         <v>135</v>
       </c>
       <c r="H10" s="120"/>
     </row>
-    <row r="11" spans="2:8" ht="13.35" customHeight="1">
+    <row r="11" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B11" s="152" t="s">
         <v>133</v>
       </c>
@@ -17367,7 +17378,7 @@
       </c>
       <c r="H11" s="120"/>
     </row>
-    <row r="12" spans="2:8" ht="13.35" customHeight="1">
+    <row r="12" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B12" s="118" t="s">
         <v>134</v>
       </c>
@@ -17377,7 +17388,7 @@
       </c>
       <c r="H12" s="120"/>
     </row>
-    <row r="13" spans="2:8" ht="13.35" customHeight="1">
+    <row r="13" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B13" s="153" t="s">
         <v>106</v>
       </c>
@@ -17391,10 +17402,10 @@
       </c>
       <c r="H13" s="120"/>
     </row>
-    <row r="14" spans="2:8">
+    <row r="14" spans="2:8" x14ac:dyDescent="0.15">
       <c r="H14" s="120"/>
     </row>
-    <row r="15" spans="2:8" ht="13.15">
+    <row r="15" spans="2:8" ht="14" x14ac:dyDescent="0.2">
       <c r="B15" s="128" t="s">
         <v>107</v>
       </c>
@@ -17412,7 +17423,7 @@
       </c>
       <c r="H15" s="120"/>
     </row>
-    <row r="16" spans="2:8">
+    <row r="16" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B16" s="122">
         <v>1</v>
       </c>
@@ -17434,7 +17445,7 @@
       </c>
       <c r="H16" s="120"/>
     </row>
-    <row r="17" spans="2:8">
+    <row r="17" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B17" s="122">
         <v>2</v>
       </c>
@@ -17456,7 +17467,7 @@
       </c>
       <c r="H17" s="120"/>
     </row>
-    <row r="18" spans="2:8">
+    <row r="18" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B18" s="122">
         <v>3</v>
       </c>
@@ -17478,7 +17489,7 @@
       </c>
       <c r="H18" s="120"/>
     </row>
-    <row r="19" spans="2:8">
+    <row r="19" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B19" s="122">
         <v>4</v>
       </c>
@@ -17500,7 +17511,7 @@
       </c>
       <c r="H19" s="120"/>
     </row>
-    <row r="20" spans="2:8">
+    <row r="20" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B20" s="122">
         <v>5</v>
       </c>
@@ -17522,7 +17533,7 @@
       </c>
       <c r="H20" s="120"/>
     </row>
-    <row r="21" spans="2:8">
+    <row r="21" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B21" s="122">
         <v>6</v>
       </c>
@@ -17544,7 +17555,7 @@
       </c>
       <c r="H21" s="120"/>
     </row>
-    <row r="22" spans="2:8">
+    <row r="22" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B22" s="122">
         <v>7</v>
       </c>
@@ -17566,7 +17577,7 @@
       </c>
       <c r="H22" s="120"/>
     </row>
-    <row r="23" spans="2:8">
+    <row r="23" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B23" s="122">
         <v>8</v>
       </c>
@@ -17588,7 +17599,7 @@
       </c>
       <c r="H23" s="120"/>
     </row>
-    <row r="24" spans="2:8">
+    <row r="24" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B24" s="122">
         <v>9</v>
       </c>
@@ -17610,7 +17621,7 @@
       </c>
       <c r="H24" s="120"/>
     </row>
-    <row r="25" spans="2:8">
+    <row r="25" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B25" s="122">
         <v>10</v>
       </c>
@@ -17632,7 +17643,7 @@
       </c>
       <c r="H25" s="120"/>
     </row>
-    <row r="26" spans="2:8">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B26" s="122">
         <v>11</v>
       </c>
@@ -17654,7 +17665,7 @@
       </c>
       <c r="H26" s="120"/>
     </row>
-    <row r="27" spans="2:8">
+    <row r="27" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B27" s="122">
         <v>12</v>
       </c>
@@ -17676,7 +17687,7 @@
       </c>
       <c r="H27" s="120"/>
     </row>
-    <row r="28" spans="2:8">
+    <row r="28" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B28" s="122">
         <v>13</v>
       </c>
@@ -17698,7 +17709,7 @@
       </c>
       <c r="H28" s="120"/>
     </row>
-    <row r="29" spans="2:8">
+    <row r="29" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B29" s="122">
         <v>14</v>
       </c>
@@ -17720,7 +17731,7 @@
       </c>
       <c r="H29" s="120"/>
     </row>
-    <row r="30" spans="2:8">
+    <row r="30" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B30" s="122">
         <v>15</v>
       </c>
@@ -17742,7 +17753,7 @@
       </c>
       <c r="H30" s="120"/>
     </row>
-    <row r="31" spans="2:8">
+    <row r="31" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B31" s="122">
         <v>16</v>
       </c>
@@ -17764,7 +17775,7 @@
       </c>
       <c r="H31" s="120"/>
     </row>
-    <row r="32" spans="2:8">
+    <row r="32" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B32" s="122">
         <v>17</v>
       </c>
@@ -17786,7 +17797,7 @@
       </c>
       <c r="H32" s="120"/>
     </row>
-    <row r="33" spans="2:8">
+    <row r="33" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B33" s="122">
         <v>18</v>
       </c>
@@ -17808,7 +17819,7 @@
       </c>
       <c r="H33" s="120"/>
     </row>
-    <row r="34" spans="2:8">
+    <row r="34" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B34" s="122">
         <v>19</v>
       </c>
@@ -17830,7 +17841,7 @@
       </c>
       <c r="H34" s="120"/>
     </row>
-    <row r="35" spans="2:8">
+    <row r="35" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B35" s="122">
         <v>20</v>
       </c>
@@ -17852,7 +17863,7 @@
       </c>
       <c r="H35" s="120"/>
     </row>
-    <row r="36" spans="2:8">
+    <row r="36" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B36" s="122">
         <v>21</v>
       </c>
@@ -17874,7 +17885,7 @@
       </c>
       <c r="H36" s="120"/>
     </row>
-    <row r="37" spans="2:8">
+    <row r="37" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B37" s="122">
         <v>22</v>
       </c>
@@ -17896,7 +17907,7 @@
       </c>
       <c r="H37" s="120"/>
     </row>
-    <row r="38" spans="2:8">
+    <row r="38" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B38" s="122">
         <v>23</v>
       </c>
@@ -17918,7 +17929,7 @@
       </c>
       <c r="H38" s="120"/>
     </row>
-    <row r="39" spans="2:8">
+    <row r="39" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B39" s="122">
         <v>24</v>
       </c>
@@ -17940,7 +17951,7 @@
       </c>
       <c r="H39" s="120"/>
     </row>
-    <row r="40" spans="2:8">
+    <row r="40" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B40" s="122">
         <v>25</v>
       </c>
@@ -17962,7 +17973,7 @@
       </c>
       <c r="H40" s="120"/>
     </row>
-    <row r="41" spans="2:8">
+    <row r="41" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B41" s="122">
         <v>26</v>
       </c>
@@ -17984,7 +17995,7 @@
       </c>
       <c r="H41" s="120"/>
     </row>
-    <row r="42" spans="2:8">
+    <row r="42" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B42" s="122">
         <v>27</v>
       </c>
@@ -18006,7 +18017,7 @@
       </c>
       <c r="H42" s="120"/>
     </row>
-    <row r="43" spans="2:8">
+    <row r="43" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B43" s="122">
         <v>28</v>
       </c>
@@ -18028,7 +18039,7 @@
       </c>
       <c r="H43" s="120"/>
     </row>
-    <row r="44" spans="2:8">
+    <row r="44" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B44" s="122">
         <v>29</v>
       </c>
@@ -18050,7 +18061,7 @@
       </c>
       <c r="H44" s="120"/>
     </row>
-    <row r="45" spans="2:8">
+    <row r="45" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B45" s="122">
         <v>30</v>
       </c>
@@ -18072,7 +18083,7 @@
       </c>
       <c r="H45" s="120"/>
     </row>
-    <row r="46" spans="2:8">
+    <row r="46" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B46" s="126" t="s">
         <v>131</v>
       </c>
@@ -18094,7 +18105,7 @@
       </c>
       <c r="H46" s="120"/>
     </row>
-    <row r="47" spans="2:8">
+    <row r="47" spans="2:8" x14ac:dyDescent="0.15">
       <c r="C47" s="114"/>
       <c r="E47" s="127" t="s">
         <v>100</v>
@@ -18105,11 +18116,11 @@
       </c>
       <c r="H47" s="120"/>
     </row>
-    <row r="48" spans="2:8">
+    <row r="48" spans="2:8" x14ac:dyDescent="0.15">
       <c r="C48" s="114"/>
       <c r="H48" s="120"/>
     </row>
-    <row r="49" spans="1:8" ht="13.15">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B49" s="119" t="s">
         <v>129</v>
       </c>
@@ -18119,7 +18130,7 @@
       <c r="F49" s="117"/>
       <c r="H49" s="120"/>
     </row>
-    <row r="50" spans="1:8" ht="13.15">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A50" s="133">
         <f>F47</f>
         <v>2071195495.7086666</v>
@@ -18146,7 +18157,7 @@
       </c>
       <c r="H50" s="120"/>
     </row>
-    <row r="51" spans="1:8" ht="13.15">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A51" s="143">
         <v>5</v>
       </c>
@@ -18168,7 +18179,7 @@
       </c>
       <c r="H51" s="120"/>
     </row>
-    <row r="52" spans="1:8" ht="13.15">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A52" s="143">
         <v>10</v>
       </c>
@@ -18189,7 +18200,7 @@
       </c>
       <c r="H52" s="120"/>
     </row>
-    <row r="53" spans="1:8" ht="13.15">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A53" s="143">
         <v>15</v>
       </c>
@@ -18210,7 +18221,7 @@
       </c>
       <c r="H53" s="120"/>
     </row>
-    <row r="54" spans="1:8" ht="13.15">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A54" s="144">
         <v>20</v>
       </c>
@@ -18231,7 +18242,7 @@
       </c>
       <c r="H54" s="120"/>
     </row>
-    <row r="55" spans="1:8" ht="13.15">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A55" s="144">
         <v>25</v>
       </c>
@@ -18252,7 +18263,7 @@
       </c>
       <c r="H55" s="120"/>
     </row>
-    <row r="56" spans="1:8" ht="13.15">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A56" s="144">
         <v>30</v>
       </c>
@@ -18273,14 +18284,14 @@
       </c>
       <c r="H56" s="120"/>
     </row>
-    <row r="57" spans="1:8">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.15">
       <c r="C57" s="114"/>
       <c r="D57" s="114"/>
       <c r="E57" s="114"/>
       <c r="F57" s="114"/>
       <c r="H57" s="120"/>
     </row>
-    <row r="58" spans="1:8" ht="13.15">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B58" s="119" t="s">
         <v>130</v>
       </c>
@@ -18290,7 +18301,7 @@
       <c r="F58" s="114"/>
       <c r="H58" s="120"/>
     </row>
-    <row r="59" spans="1:8" ht="13.15">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B59" s="132">
         <f>B50</f>
         <v>0</v>
@@ -18313,7 +18324,7 @@
       </c>
       <c r="H59" s="120"/>
     </row>
-    <row r="60" spans="1:8" ht="13.15">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A60" s="143">
         <v>0</v>
       </c>
@@ -18339,7 +18350,7 @@
       </c>
       <c r="H60" s="120"/>
     </row>
-    <row r="61" spans="1:8" ht="13.15">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A61" s="143">
         <f t="shared" ref="A61:A66" si="3">A51</f>
         <v>5</v>
@@ -18366,7 +18377,7 @@
       </c>
       <c r="H61" s="120"/>
     </row>
-    <row r="62" spans="1:8" ht="13.15">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A62" s="143">
         <f t="shared" si="3"/>
         <v>10</v>
@@ -18393,7 +18404,7 @@
       </c>
       <c r="H62" s="120"/>
     </row>
-    <row r="63" spans="1:8" ht="13.15">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A63" s="143">
         <f t="shared" si="3"/>
         <v>15</v>
@@ -18420,7 +18431,7 @@
       </c>
       <c r="H63" s="120"/>
     </row>
-    <row r="64" spans="1:8" ht="13.15">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A64" s="144">
         <f t="shared" si="3"/>
         <v>20</v>
@@ -18447,7 +18458,7 @@
       </c>
       <c r="H64" s="120"/>
     </row>
-    <row r="65" spans="1:8" ht="13.15">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A65" s="144">
         <f t="shared" si="3"/>
         <v>25</v>
@@ -18473,7 +18484,7 @@
         <v>14.544393521622398</v>
       </c>
     </row>
-    <row r="66" spans="1:8" ht="13.15">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A66" s="144">
         <f t="shared" si="3"/>
         <v>30</v>
@@ -18499,7 +18510,7 @@
         <v>17.497019921088636</v>
       </c>
     </row>
-    <row r="68" spans="1:8" ht="13.15">
+    <row r="68" spans="1:8" ht="14" x14ac:dyDescent="0.2">
       <c r="B68" s="171" t="s">
         <v>117</v>
       </c>
@@ -18516,7 +18527,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="69" spans="1:8">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B69" s="127" t="str">
         <f>Scenarios!B54</f>
         <v>Snowball Scenario</v>
@@ -18538,7 +18549,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="70" spans="1:8">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B70" s="127" t="str">
         <f>Scenarios!B36</f>
         <v>Optimistic</v>
@@ -18561,7 +18572,7 @@
       </c>
       <c r="H70" s="120"/>
     </row>
-    <row r="71" spans="1:8">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B71" s="127" t="str">
         <f>Scenarios!B24</f>
         <v>Base</v>
@@ -18584,7 +18595,7 @@
       </c>
       <c r="H71" s="120"/>
     </row>
-    <row r="72" spans="1:8">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B72" s="127" t="str">
         <f>Scenarios!B30</f>
         <v>Pessimistic</v>
@@ -18607,7 +18618,7 @@
       </c>
       <c r="H72" s="120"/>
     </row>
-    <row r="73" spans="1:8">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B73" s="127" t="str">
         <f>Scenarios!B48</f>
         <v>Devil's advocate</v>
@@ -18629,14 +18640,14 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="74" spans="1:8">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B74" s="155"/>
       <c r="C74" s="155"/>
       <c r="D74" s="155"/>
       <c r="E74" s="155"/>
       <c r="F74" s="156"/>
     </row>
-    <row r="75" spans="1:8">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B75" s="155" t="s">
         <v>310</v>
       </c>
@@ -18644,23 +18655,23 @@
         <v>105</v>
       </c>
     </row>
-    <row r="76" spans="1:8">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.15">
       <c r="C76" s="155" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="77" spans="1:8">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.15">
       <c r="C77" s="155" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="87" spans="3:3">
+    <row r="87" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C87" s="115"/>
     </row>
-    <row r="88" spans="3:3">
+    <row r="88" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C88" s="115"/>
     </row>
-    <row r="89" spans="3:3">
+    <row r="89" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C89" s="115"/>
     </row>
   </sheetData>
@@ -18690,17 +18701,17 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
   <dimension ref="B2:I110"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="2.73046875" customWidth="1"/>
-    <col min="2" max="2" width="22.73046875" customWidth="1"/>
+    <col min="1" max="1" width="2.6640625" customWidth="1"/>
+    <col min="2" max="2" width="22.6640625" customWidth="1"/>
     <col min="3" max="3" width="14" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.73046875" customWidth="1"/>
-    <col min="5" max="6" width="42.73046875" customWidth="1"/>
-    <col min="8" max="9" width="15.73046875" customWidth="1"/>
+    <col min="4" max="4" width="10.6640625" customWidth="1"/>
+    <col min="5" max="6" width="42.6640625" customWidth="1"/>
+    <col min="8" max="9" width="15.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" ht="13.9">
+    <row r="2" spans="2:9" ht="16" x14ac:dyDescent="0.25">
       <c r="B2" s="36" t="s">
         <v>145</v>
       </c>
@@ -18713,7 +18724,7 @@
       </c>
       <c r="I2" s="249"/>
     </row>
-    <row r="3" spans="2:9" ht="13.15">
+    <row r="3" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B3" s="159" t="s">
         <v>148</v>
       </c>
@@ -18722,10 +18733,10 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-13.46</v>
-      </c>
-    </row>
-    <row r="4" spans="2:9">
+        <v>-13.53</v>
+      </c>
+    </row>
+    <row r="4" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B4" s="152" t="s">
         <v>146</v>
       </c>
@@ -18745,7 +18756,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="5" spans="2:9">
+    <row r="5" spans="2:9" x14ac:dyDescent="0.15">
       <c r="H5" s="247">
         <v>2</v>
       </c>
@@ -18754,7 +18765,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="6" spans="2:9" ht="13.15">
+    <row r="6" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B6" s="159" t="s">
         <v>95</v>
       </c>
@@ -18774,7 +18785,7 @@
         <v>10.651430255232372</v>
       </c>
     </row>
-    <row r="7" spans="2:9" ht="12.75" customHeight="1">
+    <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B7" s="100" t="s">
         <v>275</v>
       </c>
@@ -18799,7 +18810,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="2:9">
+    <row r="8" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B8" s="100" t="s">
         <v>66</v>
       </c>
@@ -18821,7 +18832,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="2:9">
+    <row r="9" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B9" s="100" t="s">
         <v>57</v>
       </c>
@@ -18843,7 +18854,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="2:9">
+    <row r="10" spans="2:9" x14ac:dyDescent="0.15">
       <c r="E10" s="366"/>
       <c r="F10" s="366"/>
       <c r="H10" s="247">
@@ -18854,7 +18865,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="2:9" ht="13.15">
+    <row r="11" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B11" s="159" t="s">
         <v>447</v>
       </c>
@@ -18868,7 +18879,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="2:9">
+    <row r="12" spans="2:9" ht="14" x14ac:dyDescent="0.15">
       <c r="B12" s="118" t="s">
         <v>144</v>
       </c>
@@ -18887,7 +18898,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="2:9">
+    <row r="13" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B13" s="148" t="s">
         <v>152</v>
       </c>
@@ -18905,7 +18916,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="2:9">
+    <row r="14" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B14" s="100" t="s">
         <v>66</v>
       </c>
@@ -18916,7 +18927,7 @@
       <c r="E14" s="366"/>
       <c r="F14" s="366"/>
     </row>
-    <row r="16" spans="2:9" ht="13.9">
+    <row r="16" spans="2:9" ht="16" x14ac:dyDescent="0.25">
       <c r="B16" s="36" t="s">
         <v>162</v>
       </c>
@@ -18925,7 +18936,7 @@
       <c r="E16" s="37"/>
       <c r="F16" s="37"/>
     </row>
-    <row r="17" spans="2:6" ht="13.15">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B17" s="109" t="s">
         <v>151</v>
       </c>
@@ -18933,7 +18944,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="18" spans="2:6">
+    <row r="18" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B18" s="152" t="s">
         <v>133</v>
       </c>
@@ -18945,24 +18956,24 @@
       </c>
       <c r="F18" s="367"/>
     </row>
-    <row r="19" spans="2:6">
+    <row r="19" spans="2:6" x14ac:dyDescent="0.15">
       <c r="E19" s="367"/>
       <c r="F19" s="367"/>
     </row>
-    <row r="20" spans="2:6" ht="13.15">
+    <row r="20" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B20" s="159" t="s">
         <v>303</v>
       </c>
       <c r="E20" s="367"/>
       <c r="F20" s="367"/>
     </row>
-    <row r="21" spans="2:6">
+    <row r="21" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B21" s="100" t="s">
         <v>277</v>
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>13.46</v>
+        <v>13.53</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -18971,7 +18982,7 @@
       <c r="E21" s="367"/>
       <c r="F21" s="367"/>
     </row>
-    <row r="22" spans="2:6">
+    <row r="22" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B22" s="100" t="s">
         <v>278</v>
       </c>
@@ -18986,7 +18997,7 @@
       <c r="E22" s="367"/>
       <c r="F22" s="367"/>
     </row>
-    <row r="24" spans="2:6" ht="13.15">
+    <row r="24" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B24" s="159" t="s">
         <v>115</v>
       </c>
@@ -18995,7 +19006,7 @@
       </c>
       <c r="F24" s="159"/>
     </row>
-    <row r="25" spans="2:6">
+    <row r="25" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B25" s="152" t="s">
         <v>133</v>
       </c>
@@ -19007,7 +19018,7 @@
       <c r="E25" s="365"/>
       <c r="F25" s="365"/>
     </row>
-    <row r="26" spans="2:6">
+    <row r="26" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B26" s="118" t="s">
         <v>134</v>
       </c>
@@ -19018,7 +19029,7 @@
       <c r="E26" s="365"/>
       <c r="F26" s="365"/>
     </row>
-    <row r="27" spans="2:6">
+    <row r="27" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B27" s="100" t="s">
         <v>113</v>
       </c>
@@ -19033,7 +19044,7 @@
       <c r="E27" s="365"/>
       <c r="F27" s="365"/>
     </row>
-    <row r="28" spans="2:6">
+    <row r="28" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B28" s="100" t="s">
         <v>147</v>
       </c>
@@ -19044,7 +19055,7 @@
       <c r="E28" s="365"/>
       <c r="F28" s="365"/>
     </row>
-    <row r="30" spans="2:6" ht="13.15">
+    <row r="30" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B30" s="159" t="s">
         <v>116</v>
       </c>
@@ -19053,7 +19064,7 @@
       </c>
       <c r="F30" s="159"/>
     </row>
-    <row r="31" spans="2:6">
+    <row r="31" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B31" s="152" t="s">
         <v>133</v>
       </c>
@@ -19065,7 +19076,7 @@
       <c r="E31" s="365"/>
       <c r="F31" s="365"/>
     </row>
-    <row r="32" spans="2:6">
+    <row r="32" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B32" s="118" t="s">
         <v>134</v>
       </c>
@@ -19076,7 +19087,7 @@
       <c r="E32" s="365"/>
       <c r="F32" s="365"/>
     </row>
-    <row r="33" spans="2:6">
+    <row r="33" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B33" s="100" t="s">
         <v>113</v>
       </c>
@@ -19091,7 +19102,7 @@
       <c r="E33" s="365"/>
       <c r="F33" s="365"/>
     </row>
-    <row r="34" spans="2:6">
+    <row r="34" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B34" s="100" t="s">
         <v>147</v>
       </c>
@@ -19102,7 +19113,7 @@
       <c r="E34" s="365"/>
       <c r="F34" s="365"/>
     </row>
-    <row r="36" spans="2:6" ht="13.15">
+    <row r="36" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B36" s="159" t="s">
         <v>114</v>
       </c>
@@ -19111,7 +19122,7 @@
       </c>
       <c r="F36" s="159"/>
     </row>
-    <row r="37" spans="2:6">
+    <row r="37" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B37" s="152" t="s">
         <v>133</v>
       </c>
@@ -19123,7 +19134,7 @@
       <c r="E37" s="365"/>
       <c r="F37" s="365"/>
     </row>
-    <row r="38" spans="2:6">
+    <row r="38" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B38" s="118" t="s">
         <v>134</v>
       </c>
@@ -19134,7 +19145,7 @@
       <c r="E38" s="365"/>
       <c r="F38" s="365"/>
     </row>
-    <row r="39" spans="2:6">
+    <row r="39" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B39" s="100" t="s">
         <v>113</v>
       </c>
@@ -19149,7 +19160,7 @@
       <c r="E39" s="365"/>
       <c r="F39" s="365"/>
     </row>
-    <row r="40" spans="2:6">
+    <row r="40" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B40" s="100" t="s">
         <v>147</v>
       </c>
@@ -19161,7 +19172,7 @@
       <c r="E40" s="365"/>
       <c r="F40" s="365"/>
     </row>
-    <row r="42" spans="2:6" ht="13.15">
+    <row r="42" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B42" s="100" t="s">
         <v>120</v>
       </c>
@@ -19174,7 +19185,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="44" spans="2:6" ht="13.9">
+    <row r="44" spans="2:6" ht="16" x14ac:dyDescent="0.25">
       <c r="B44" s="36" t="s">
         <v>161</v>
       </c>
@@ -19183,12 +19194,12 @@
       <c r="E44" s="37"/>
       <c r="F44" s="37"/>
     </row>
-    <row r="45" spans="2:6" ht="13.15">
+    <row r="45" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B45" s="109" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="46" spans="2:6">
+    <row r="46" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B46" s="152" t="s">
         <v>133</v>
       </c>
@@ -19198,12 +19209,12 @@
       <c r="E46" s="100"/>
       <c r="F46" s="100"/>
     </row>
-    <row r="47" spans="2:6" ht="13.15">
+    <row r="47" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B47" s="159"/>
       <c r="E47" s="159"/>
       <c r="F47" s="159"/>
     </row>
-    <row r="48" spans="2:6" ht="13.15">
+    <row r="48" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B48" s="159" t="s">
         <v>165</v>
       </c>
@@ -19212,7 +19223,7 @@
       </c>
       <c r="F48" s="159"/>
     </row>
-    <row r="49" spans="2:6" ht="12.75" customHeight="1">
+    <row r="49" spans="2:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B49" s="152" t="s">
         <v>133</v>
       </c>
@@ -19224,7 +19235,7 @@
       <c r="E49" s="365"/>
       <c r="F49" s="365"/>
     </row>
-    <row r="50" spans="2:6">
+    <row r="50" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B50" s="118" t="s">
         <v>134</v>
       </c>
@@ -19235,7 +19246,7 @@
       <c r="E50" s="365"/>
       <c r="F50" s="365"/>
     </row>
-    <row r="51" spans="2:6">
+    <row r="51" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B51" s="100" t="s">
         <v>113</v>
       </c>
@@ -19250,7 +19261,7 @@
       <c r="E51" s="365"/>
       <c r="F51" s="365"/>
     </row>
-    <row r="52" spans="2:6">
+    <row r="52" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B52" s="100" t="s">
         <v>147</v>
       </c>
@@ -19261,7 +19272,7 @@
       <c r="E52" s="365"/>
       <c r="F52" s="365"/>
     </row>
-    <row r="54" spans="2:6" ht="13.15">
+    <row r="54" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B54" s="159" t="s">
         <v>316</v>
       </c>
@@ -19270,7 +19281,7 @@
       </c>
       <c r="F54" s="159"/>
     </row>
-    <row r="55" spans="2:6">
+    <row r="55" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B55" s="152" t="s">
         <v>133</v>
       </c>
@@ -19282,7 +19293,7 @@
       <c r="E55" s="365"/>
       <c r="F55" s="365"/>
     </row>
-    <row r="56" spans="2:6">
+    <row r="56" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B56" s="118" t="s">
         <v>134</v>
       </c>
@@ -19293,7 +19304,7 @@
       <c r="E56" s="365"/>
       <c r="F56" s="365"/>
     </row>
-    <row r="57" spans="2:6">
+    <row r="57" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B57" s="100" t="s">
         <v>113</v>
       </c>
@@ -19308,7 +19319,7 @@
       <c r="E57" s="365"/>
       <c r="F57" s="365"/>
     </row>
-    <row r="58" spans="2:6">
+    <row r="58" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B58" s="100" t="s">
         <v>147</v>
       </c>
@@ -19319,7 +19330,7 @@
       <c r="E58" s="365"/>
       <c r="F58" s="365"/>
     </row>
-    <row r="60" spans="2:6" ht="13.15">
+    <row r="60" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B60" s="100" t="s">
         <v>120</v>
       </c>
@@ -19339,7 +19350,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="62" spans="2:6" ht="13.9">
+    <row r="62" spans="2:6" ht="16" x14ac:dyDescent="0.25">
       <c r="B62" s="36" t="s">
         <v>349</v>
       </c>
@@ -19348,7 +19359,7 @@
       <c r="E62" s="37"/>
       <c r="F62" s="37"/>
     </row>
-    <row r="63" spans="2:6" ht="13.15">
+    <row r="63" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B63" s="109" t="s">
         <v>304</v>
       </c>
@@ -19356,7 +19367,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="64" spans="2:6">
+    <row r="64" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B64" s="152" t="s">
         <v>133</v>
       </c>
@@ -19369,7 +19380,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="65" spans="2:6">
+    <row r="65" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B65" s="118" t="s">
         <v>134</v>
       </c>
@@ -19381,7 +19392,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="66" spans="2:6">
+    <row r="66" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B66" s="100" t="s">
         <v>102</v>
       </c>
@@ -19397,7 +19408,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="68" spans="2:6" ht="13.15">
+    <row r="68" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B68" s="109" t="s">
         <v>350</v>
       </c>
@@ -19405,7 +19416,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="69" spans="2:6">
+    <row r="69" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B69" s="100" t="s">
         <v>305</v>
       </c>
@@ -19415,7 +19426,7 @@
       </c>
       <c r="E69" s="134"/>
     </row>
-    <row r="70" spans="2:6">
+    <row r="70" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B70" s="100" t="s">
         <v>293</v>
       </c>
@@ -19427,7 +19438,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="71" spans="2:6">
+    <row r="71" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B71" s="100" t="s">
         <v>292</v>
       </c>
@@ -19437,7 +19448,7 @@
       </c>
       <c r="E71" s="251"/>
     </row>
-    <row r="72" spans="2:6">
+    <row r="72" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B72" s="100" t="s">
         <v>284</v>
       </c>
@@ -19453,7 +19464,7 @@
         <v>0.22959710481590032</v>
       </c>
     </row>
-    <row r="74" spans="2:6" ht="13.9">
+    <row r="74" spans="2:6" ht="16" x14ac:dyDescent="0.25">
       <c r="B74" s="36" t="s">
         <v>127</v>
       </c>
@@ -19462,12 +19473,12 @@
       <c r="E74" s="37"/>
       <c r="F74" s="37"/>
     </row>
-    <row r="75" spans="2:6" ht="13.15">
+    <row r="75" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B75" s="109" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="76" spans="2:6">
+    <row r="76" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B76" s="246" t="s">
         <v>297</v>
       </c>
@@ -19477,7 +19488,7 @@
       </c>
       <c r="D76" s="134"/>
     </row>
-    <row r="77" spans="2:6">
+    <row r="77" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B77" s="100" t="s">
         <v>111</v>
       </c>
@@ -19490,33 +19501,33 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="79" spans="2:6" ht="13.15">
+    <row r="79" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B79" s="109" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="80" spans="2:6">
+    <row r="80" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B80" s="148" t="s">
         <v>299</v>
       </c>
       <c r="C80" s="167">
         <f>Thesis!F29</f>
-        <v>0.33700000000000002</v>
-      </c>
-    </row>
-    <row r="81" spans="2:8">
+        <v>0.33699999999999997</v>
+      </c>
+    </row>
+    <row r="81" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B81" s="100" t="s">
         <v>121</v>
       </c>
       <c r="C81" s="116">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>0.69031028314322285</v>
+        <v>0.69031028314322296</v>
       </c>
       <c r="D81" s="116"/>
       <c r="E81" s="100"/>
       <c r="F81" s="100"/>
     </row>
-    <row r="82" spans="2:8">
+    <row r="82" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B82" s="100" t="s">
         <v>122</v>
       </c>
@@ -19526,7 +19537,7 @@
       </c>
       <c r="D82" s="116"/>
     </row>
-    <row r="83" spans="2:8" ht="13.15">
+    <row r="83" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B83" s="110" t="s">
         <v>101</v>
       </c>
@@ -19546,45 +19557,45 @@
         <v>0.51424846499304677</v>
       </c>
     </row>
-    <row r="84" spans="2:8">
+    <row r="84" spans="2:8" x14ac:dyDescent="0.15">
       <c r="E84" s="120"/>
     </row>
-    <row r="85" spans="2:8" ht="13.15">
+    <row r="85" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B85" s="109" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="86" spans="2:8">
+    <row r="86" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B86" s="148" t="s">
         <v>300</v>
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>13.46</v>
+        <v>13.53</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="87" spans="2:8" ht="13.15">
+    <row r="87" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B87" s="100" t="s">
         <v>298</v>
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>-5.4209080354837624E-2</v>
-      </c>
-    </row>
-    <row r="88" spans="2:8">
+        <v>-5.5896901541827249E-2</v>
+      </c>
+    </row>
+    <row r="88" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B88" s="100"/>
     </row>
-    <row r="89" spans="2:8" ht="13.15">
+    <row r="89" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B89" s="109" t="s">
         <v>412</v>
       </c>
     </row>
-    <row r="90" spans="2:8">
+    <row r="90" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B90" s="148" t="s">
         <v>413</v>
       </c>
@@ -19593,7 +19604,7 @@
         <v>0.187</v>
       </c>
     </row>
-    <row r="91" spans="2:8">
+    <row r="91" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B91" s="100" t="s">
         <v>121</v>
       </c>
@@ -19605,7 +19616,7 @@
       <c r="E91" s="100"/>
       <c r="F91" s="100"/>
     </row>
-    <row r="92" spans="2:8">
+    <row r="92" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B92" s="100" t="s">
         <v>122</v>
       </c>
@@ -19615,7 +19626,7 @@
       </c>
       <c r="D92" s="116"/>
     </row>
-    <row r="93" spans="2:8" ht="13.15">
+    <row r="93" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B93" s="110" t="s">
         <v>101</v>
       </c>
@@ -19635,14 +19646,14 @@
         <v>0.31817781825366975</v>
       </c>
     </row>
-    <row r="95" spans="2:8" ht="13.15">
+    <row r="95" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B95" s="109" t="s">
         <v>397</v>
       </c>
       <c r="G95" s="2"/>
       <c r="H95" s="281"/>
     </row>
-    <row r="96" spans="2:8">
+    <row r="96" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B96" s="148" t="s">
         <v>403</v>
       </c>
@@ -19653,7 +19664,7 @@
       <c r="G96" s="2"/>
       <c r="H96" s="281"/>
     </row>
-    <row r="97" spans="2:8">
+    <row r="97" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B97" s="100" t="s">
         <v>121</v>
       </c>
@@ -19665,7 +19676,7 @@
       <c r="G97" s="2"/>
       <c r="H97" s="281"/>
     </row>
-    <row r="98" spans="2:8">
+    <row r="98" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B98" s="100" t="s">
         <v>122</v>
       </c>
@@ -19677,7 +19688,7 @@
       <c r="G98" s="2"/>
       <c r="H98" s="281"/>
     </row>
-    <row r="99" spans="2:8" ht="13.15">
+    <row r="99" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B99" s="110" t="s">
         <v>398</v>
       </c>
@@ -19696,15 +19707,15 @@
         <v>5.6082608980383197E-2</v>
       </c>
     </row>
-    <row r="100" spans="2:8">
+    <row r="100" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B100" s="100"/>
     </row>
-    <row r="101" spans="2:8" ht="13.15">
+    <row r="101" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B101" s="109" t="s">
         <v>422</v>
       </c>
     </row>
-    <row r="102" spans="2:8">
+    <row r="102" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B102" s="148" t="s">
         <v>421</v>
       </c>
@@ -19713,7 +19724,7 @@
         <v>8.6999999999999994E-2</v>
       </c>
     </row>
-    <row r="103" spans="2:8">
+    <row r="103" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B103" s="100" t="s">
         <v>121</v>
       </c>
@@ -19723,7 +19734,7 @@
       </c>
       <c r="D103" s="116"/>
     </row>
-    <row r="104" spans="2:8">
+    <row r="104" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B104" s="100" t="s">
         <v>122</v>
       </c>
@@ -19733,7 +19744,7 @@
       </c>
       <c r="D104" s="116"/>
     </row>
-    <row r="105" spans="2:8" ht="13.15">
+    <row r="105" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B105" s="110" t="s">
         <v>398</v>
       </c>
@@ -19752,16 +19763,16 @@
         <v>0.11980238369313911</v>
       </c>
     </row>
-    <row r="106" spans="2:8">
+    <row r="106" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B106" s="100"/>
     </row>
-    <row r="107" spans="2:8" ht="14.65">
+    <row r="107" spans="2:8" ht="16" x14ac:dyDescent="0.25">
       <c r="E107" s="285" t="s">
         <v>324</v>
       </c>
       <c r="F107" s="282"/>
     </row>
-    <row r="108" spans="2:8" ht="13.9">
+    <row r="108" spans="2:8" ht="16" x14ac:dyDescent="0.25">
       <c r="E108" s="278" t="s">
         <v>325</v>
       </c>
@@ -19769,7 +19780,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="109" spans="2:8" ht="13.9">
+    <row r="109" spans="2:8" ht="16" x14ac:dyDescent="0.25">
       <c r="E109" s="279" t="s">
         <v>325</v>
       </c>
@@ -19777,7 +19788,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="110" spans="2:8" ht="13.9">
+    <row r="110" spans="2:8" ht="16" x14ac:dyDescent="0.25">
       <c r="E110" s="280" t="s">
         <v>325</v>
       </c>

--- a/financial_models/opportunities/300481.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/300481.SZ_Valuation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kamanl/PycharmProjects/Invest_Proc/financial_models/opportunities/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0290A198-A1FF-6143-B7F3-3E3FC4E852E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C84597E4-7B5D-4ED1-9163-5B20FE4C1426}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="17120" windowHeight="10760" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -38,17 +38,6 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
     <ext uri="GoogleSheetsCustomDataVersion1">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId9" roundtripDataSignature="AMtx7mi73Cg0ax9bLfpeUuF69nNRn7idDQ=="/>
@@ -2510,7 +2499,7 @@
     <numFmt numFmtId="180" formatCode="0.000000000000000%"/>
     <numFmt numFmtId="181" formatCode="#,##0_);\(#,##0\);0;@"/>
   </numFmts>
-  <fonts count="59" x14ac:knownFonts="1">
+  <fonts count="59">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -3902,29 +3891,29 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -3940,7 +3929,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="常规 2 2" xfId="1" xr:uid="{A35F4541-DCCE-4554-A311-39480A36979A}"/>
   </cellStyles>
   <dxfs count="8">
@@ -4229,7 +4218,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J197"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="32.6640625" style="1" customWidth="1"/>
@@ -4238,7 +4227,7 @@
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:10">
       <c r="B1" s="3" t="s">
         <v>41</v>
       </c>
@@ -4255,7 +4244,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="13.9">
       <c r="A2" s="222" t="s">
         <v>267</v>
       </c>
@@ -4269,7 +4258,7 @@
       <c r="I2" s="22"/>
       <c r="J2" s="22"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:10">
       <c r="B4" s="45" t="s">
         <v>415</v>
       </c>
@@ -4278,7 +4267,7 @@
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
     </row>
-    <row r="5" spans="1:10" ht="14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" ht="12.4">
       <c r="B5" s="4" t="s">
         <v>315</v>
       </c>
@@ -4286,7 +4275,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:10">
       <c r="B6" s="4" t="s">
         <v>0</v>
       </c>
@@ -4295,7 +4284,7 @@
       </c>
       <c r="E6" s="48"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:10">
       <c r="B7" s="2" t="s">
         <v>307</v>
       </c>
@@ -4305,7 +4294,7 @@
       <c r="D7" s="48"/>
       <c r="E7" s="48"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:10">
       <c r="B8" s="1" t="s">
         <v>268</v>
       </c>
@@ -4315,17 +4304,17 @@
       </c>
       <c r="E8" s="48"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:10">
       <c r="E9" s="34"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:10">
       <c r="B10" s="45" t="s">
         <v>418</v>
       </c>
       <c r="C10" s="46"/>
       <c r="E10" s="34"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:10">
       <c r="B11" s="1" t="s">
         <v>417</v>
       </c>
@@ -4337,17 +4326,17 @@
       </c>
       <c r="E11" s="34"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:10">
       <c r="B12" s="4" t="s">
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>13.53</v>
+        <v>13.39</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:10">
       <c r="B13" s="1" t="s">
         <v>416</v>
       </c>
@@ -4357,13 +4346,13 @@
       <c r="D13" s="48"/>
       <c r="E13" s="5"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:10">
       <c r="B14" s="4" t="s">
         <v>420</v>
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>3948.8040761399998</v>
+        <v>3907.9443148200003</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4371,7 +4360,7 @@
       </c>
       <c r="E14" s="5"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:10">
       <c r="B15" s="4" t="s">
         <v>419</v>
       </c>
@@ -4385,7 +4374,7 @@
       </c>
       <c r="E15" s="5"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:10">
       <c r="B16" s="4" t="s">
         <v>1</v>
       </c>
@@ -4395,27 +4384,27 @@
       <c r="D16" s="50"/>
       <c r="E16" s="5"/>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:6">
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
     </row>
-    <row r="18" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B18" s="356" t="s">
+    <row r="18" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B18" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C18" s="356"/>
-      <c r="D18" s="356"/>
-      <c r="E18" s="356"/>
-      <c r="F18" s="356"/>
-    </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
+    </row>
+    <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
         <v>306</v>
       </c>
       <c r="C20" s="46"/>
       <c r="D20" s="5"/>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:6">
       <c r="B21" s="2" t="s">
         <v>348</v>
       </c>
@@ -4430,7 +4419,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:6">
       <c r="B22" s="2" t="s">
         <v>56</v>
       </c>
@@ -4443,7 +4432,7 @@
       </c>
       <c r="E22" s="313"/>
     </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:6">
       <c r="B23" s="1" t="s">
         <v>434</v>
       </c>
@@ -4451,7 +4440,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:6">
       <c r="B24" s="1" t="s">
         <v>435</v>
       </c>
@@ -4459,7 +4448,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:6">
       <c r="B25" s="4" t="s">
         <v>347</v>
       </c>
@@ -4475,7 +4464,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:6">
       <c r="B26" s="1" t="str">
         <f>"Expected Equity Value ("&amp;C13&amp;") :"</f>
         <v>Expected Equity Value (CNY) :</v>
@@ -4489,14 +4478,14 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>-5.5896901541827249E-2</v>
-      </c>
-    </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.15">
+        <v>-5.2509260474737696E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6">
       <c r="D27" s="5"/>
       <c r="E27" s="5"/>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:6">
       <c r="B28" s="45" t="s">
         <v>433</v>
       </c>
@@ -4515,7 +4504,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:6">
       <c r="B29" s="1" t="s">
         <v>425</v>
       </c>
@@ -4534,7 +4523,7 @@
         <v>0.33699999999999997</v>
       </c>
     </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:6">
       <c r="B30" s="1" t="s">
         <v>426</v>
       </c>
@@ -4553,7 +4542,7 @@
         <v>0.187</v>
       </c>
     </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:6">
       <c r="B31" s="1" t="s">
         <v>427</v>
       </c>
@@ -4572,7 +4561,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:6">
       <c r="B32" s="1" t="s">
         <v>428</v>
       </c>
@@ -4591,11 +4580,11 @@
         <v>8.6999999999999994E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:6">
       <c r="D33" s="5"/>
       <c r="E33" s="5"/>
     </row>
-    <row r="34" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" ht="13.9">
       <c r="A34" s="222" t="s">
         <v>354</v>
       </c>
@@ -4605,25 +4594,25 @@
       <c r="E34" s="36"/>
       <c r="F34" s="36"/>
     </row>
-    <row r="36" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B36" s="356" t="s">
+    <row r="36" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B36" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C36" s="356"/>
-      <c r="D36" s="356"/>
-      <c r="E36" s="356"/>
-      <c r="F36" s="356"/>
-    </row>
-    <row r="37" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B37" s="358" t="s">
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
+    </row>
+    <row r="37" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B37" s="361" t="s">
         <v>339</v>
       </c>
-      <c r="C37" s="358"/>
-      <c r="D37" s="358"/>
-      <c r="E37" s="358"/>
-      <c r="F37" s="358"/>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C37" s="361"/>
+      <c r="D37" s="361"/>
+      <c r="E37" s="361"/>
+      <c r="F37" s="361"/>
+    </row>
+    <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
         <v>230</v>
       </c>
@@ -4632,16 +4621,16 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B40" s="357" t="s">
+    <row r="40" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B40" s="359" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="357"/>
-      <c r="D40" s="357"/>
-      <c r="E40" s="357"/>
-      <c r="F40" s="357"/>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
+    </row>
+    <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
         <v>232</v>
       </c>
@@ -4654,20 +4643,20 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:6">
       <c r="B42" s="47"/>
       <c r="C42" s="76"/>
     </row>
-    <row r="43" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B43" s="357" t="s">
+    <row r="43" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B43" s="359" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="357"/>
-      <c r="D43" s="357"/>
-      <c r="E43" s="357"/>
-      <c r="F43" s="357"/>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
+    </row>
+    <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
         <v>234</v>
       </c>
@@ -4680,7 +4669,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:6">
       <c r="B45" s="52" t="s">
         <v>235</v>
       </c>
@@ -4693,16 +4682,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B47" s="357" t="s">
+    <row r="47" spans="1:6">
+      <c r="B47" s="359" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="357"/>
-      <c r="D47" s="357"/>
-      <c r="E47" s="357"/>
-      <c r="F47" s="357"/>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
+    </row>
+    <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
         <v>237</v>
       </c>
@@ -4715,16 +4704,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="50" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B50" s="357" t="s">
+    <row r="50" spans="2:6">
+      <c r="B50" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="357"/>
-      <c r="D50" s="357"/>
-      <c r="E50" s="357"/>
-      <c r="F50" s="357"/>
-    </row>
-    <row r="51" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
+    </row>
+    <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
         <v>340</v>
       </c>
@@ -4739,7 +4728,7 @@
       <c r="E51" s="286"/>
       <c r="F51" s="286"/>
     </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:6">
       <c r="B52" s="47" t="s">
         <v>341</v>
       </c>
@@ -4754,7 +4743,7 @@
       <c r="E52" s="286"/>
       <c r="F52" s="286"/>
     </row>
-    <row r="53" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
         <v>238</v>
       </c>
@@ -4767,12 +4756,12 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:6">
       <c r="B55" s="1" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="56" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:6">
       <c r="B56" s="47" t="s">
         <v>265</v>
       </c>
@@ -4785,16 +4774,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="58" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B58" s="357" t="s">
+    <row r="58" spans="2:6">
+      <c r="B58" s="359" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="357"/>
-      <c r="D58" s="357"/>
-      <c r="E58" s="357"/>
-      <c r="F58" s="357"/>
-    </row>
-    <row r="59" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
+    </row>
+    <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
         <v>239</v>
       </c>
@@ -4807,8 +4796,8 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="61" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B61" s="357" t="s">
+    <row r="61" spans="2:6">
+      <c r="B61" s="359" t="s">
         <v>338</v>
       </c>
       <c r="C61" s="360"/>
@@ -4816,7 +4805,7 @@
       <c r="E61" s="360"/>
       <c r="F61" s="360"/>
     </row>
-    <row r="62" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
         <v>242</v>
       </c>
@@ -4829,25 +4818,25 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="64" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B64" s="356" t="s">
+    <row r="64" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B64" s="358" t="s">
         <v>343</v>
       </c>
-      <c r="C64" s="356"/>
-      <c r="D64" s="356"/>
-      <c r="E64" s="356"/>
-      <c r="F64" s="356"/>
-    </row>
-    <row r="65" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B65" s="356" t="s">
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
+    </row>
+    <row r="65" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B65" s="358" t="s">
         <v>361</v>
       </c>
-      <c r="C65" s="356"/>
-      <c r="D65" s="356"/>
-      <c r="E65" s="356"/>
-      <c r="F65" s="356"/>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
+    </row>
+    <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
         <v>270</v>
       </c>
@@ -4860,7 +4849,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:6">
       <c r="B68" s="47" t="s">
         <v>248</v>
       </c>
@@ -4873,23 +4862,23 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:6">
       <c r="B69" s="227" t="s">
         <v>390</v>
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>3.2789369544086615E-2</v>
+        <v>3.3132200891074826E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:6">
       <c r="B70" s="227" t="s">
         <v>308</v>
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>2.9563932002956397E-2</v>
+        <v>2.9873039581777446E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>448</v>
@@ -4899,7 +4888,7 @@
         <v>0.90163160847623214</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:6">
       <c r="B72" s="210" t="s">
         <v>450</v>
       </c>
@@ -4910,7 +4899,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:6">
       <c r="B73" s="47" t="s">
         <v>451</v>
       </c>
@@ -4923,7 +4912,7 @@
         <v>7.2897649409175577E-2</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:6">
       <c r="B74" s="259" t="str">
         <f>Normalized_FCF!B117</f>
         <v>Pre-tax Profit/Sales</v>
@@ -4937,7 +4926,7 @@
         <v>0.12459084820450472</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:6">
       <c r="B75" s="259" t="str">
         <f>Normalized_FCF!B118</f>
         <v>Sales/Total Assets</v>
@@ -4951,7 +4940,7 @@
         <v>0.50157874313934503</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:6">
       <c r="B76" s="259" t="str">
         <f>Normalized_FCF!B119</f>
         <v>Total Assets/Equity</v>
@@ -4965,7 +4954,7 @@
         <v>1.1665094444773738</v>
       </c>
     </row>
-    <row r="78" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:6" ht="13.9">
       <c r="A78" s="222" t="s">
         <v>355</v>
       </c>
@@ -4975,34 +4964,34 @@
       <c r="E78" s="36"/>
       <c r="F78" s="36"/>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:6">
       <c r="A79" s="209"/>
     </row>
-    <row r="80" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="356" t="s">
+      <c r="B80" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C80" s="356"/>
-      <c r="D80" s="356"/>
-      <c r="E80" s="356"/>
-      <c r="F80" s="356"/>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B81" s="358" t="s">
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
+    </row>
+    <row r="81" spans="1:6">
+      <c r="B81" s="361" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="358"/>
-      <c r="D81" s="358"/>
-      <c r="E81" s="358"/>
-      <c r="F81" s="358"/>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C81" s="361"/>
+      <c r="D81" s="361"/>
+      <c r="E81" s="361"/>
+      <c r="F81" s="361"/>
+    </row>
+    <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:6">
       <c r="B84" s="1" t="s">
         <v>431</v>
       </c>
@@ -5011,7 +5000,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:6">
       <c r="B85" s="1" t="s">
         <v>430</v>
       </c>
@@ -5020,7 +5009,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:6">
       <c r="B86" s="80" t="s">
         <v>247</v>
       </c>
@@ -5029,34 +5018,34 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:6">
       <c r="C87" s="121"/>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:6">
       <c r="B88" s="293" t="s">
         <v>356</v>
       </c>
       <c r="C88" s="121"/>
     </row>
-    <row r="89" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B89" s="356" t="s">
+    <row r="89" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B89" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C89" s="356"/>
-      <c r="D89" s="356"/>
-      <c r="E89" s="356"/>
-      <c r="F89" s="356"/>
-    </row>
-    <row r="90" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B90" s="356" t="s">
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
+    </row>
+    <row r="90" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B90" s="358" t="s">
         <v>364</v>
       </c>
-      <c r="C90" s="356"/>
-      <c r="D90" s="356"/>
-      <c r="E90" s="356"/>
-      <c r="F90" s="356"/>
-    </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
+    </row>
+    <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
         <v>251</v>
       </c>
@@ -5064,7 +5053,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:6">
       <c r="B93" s="47" t="s">
         <v>280</v>
       </c>
@@ -5077,7 +5066,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="95" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:6" ht="13.9">
       <c r="A95" s="222" t="s">
         <v>357</v>
       </c>
@@ -5087,38 +5076,38 @@
       <c r="E95" s="36"/>
       <c r="F95" s="36"/>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:6">
       <c r="A96" s="209"/>
     </row>
-    <row r="97" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B97" s="356" t="s">
+    <row r="97" spans="2:6">
+      <c r="B97" s="358" t="s">
         <v>365</v>
       </c>
-      <c r="C97" s="356"/>
-      <c r="D97" s="356"/>
-      <c r="E97" s="356"/>
-      <c r="F97" s="356"/>
-    </row>
-    <row r="98" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
+    </row>
+    <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="100" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="100" spans="2:6">
       <c r="B100" s="210" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="101" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B101" s="356" t="s">
+    <row r="101" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B101" s="358" t="s">
         <v>344</v>
       </c>
-      <c r="C101" s="356"/>
-      <c r="D101" s="356"/>
-      <c r="E101" s="356"/>
-      <c r="F101" s="356"/>
-    </row>
-    <row r="102" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
+    </row>
+    <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
         <v>255</v>
       </c>
@@ -5131,7 +5120,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="103" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="103" spans="2:6">
       <c r="B103" s="47" t="s">
         <v>281</v>
       </c>
@@ -5144,7 +5133,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="104" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="104" spans="2:6">
       <c r="B104" s="296" t="s">
         <v>404</v>
       </c>
@@ -5153,7 +5142,7 @@
         <v>4.1494671576720196E-2</v>
       </c>
     </row>
-    <row r="105" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="105" spans="2:6">
       <c r="B105" s="296" t="s">
         <v>406</v>
       </c>
@@ -5162,12 +5151,12 @@
         <v>0.57353573509526667</v>
       </c>
     </row>
-    <row r="107" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="107" spans="2:6">
       <c r="B107" s="1" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="108" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="108" spans="2:6">
       <c r="B108" s="47" t="s">
         <v>264</v>
       </c>
@@ -5180,7 +5169,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="109" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="109" spans="2:6">
       <c r="B109" s="47" t="s">
         <v>266</v>
       </c>
@@ -5193,7 +5182,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="110" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="110" spans="2:6">
       <c r="B110" s="47" t="s">
         <v>282</v>
       </c>
@@ -5206,12 +5195,12 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="112" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="112" spans="2:6">
       <c r="B112" s="1" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:6">
       <c r="B113" s="47" t="s">
         <v>257</v>
       </c>
@@ -5224,7 +5213,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:6">
       <c r="B114" s="47" t="s">
         <v>283</v>
       </c>
@@ -5237,16 +5226,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="116" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B116" s="356" t="s">
+    <row r="116" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B116" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C116" s="356"/>
-      <c r="D116" s="356"/>
-      <c r="E116" s="356"/>
-      <c r="F116" s="356"/>
-    </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
+    </row>
+    <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
         <v>449</v>
       </c>
@@ -5259,7 +5248,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="119" spans="1:6">
       <c r="B119" s="296" t="s">
         <v>405</v>
       </c>
@@ -5272,7 +5261,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="121" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="222" t="s">
         <v>358</v>
       </c>
@@ -5282,16 +5271,16 @@
       <c r="E121" s="36"/>
       <c r="F121" s="36"/>
     </row>
-    <row r="123" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B123" s="357" t="s">
+    <row r="123" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B123" s="359" t="s">
         <v>367</v>
       </c>
-      <c r="C123" s="357"/>
-      <c r="D123" s="357"/>
-      <c r="E123" s="357"/>
-      <c r="F123" s="357"/>
-    </row>
-    <row r="125" spans="1:6" ht="14" x14ac:dyDescent="0.2">
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
+    </row>
+    <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
         <v>117</v>
       </c>
@@ -5308,7 +5297,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="126" spans="1:6">
       <c r="B126" s="228" t="str">
         <f>DCF!B74</f>
         <v>Snowball Scenario</v>
@@ -5330,7 +5319,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="127" spans="1:6">
       <c r="B127" s="218" t="str">
         <f>DCF!B75</f>
         <v>Optimistic</v>
@@ -5352,7 +5341,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="128" spans="1:6">
       <c r="B128" s="218" t="str">
         <f>DCF!B76</f>
         <v>Base</v>
@@ -5374,7 +5363,7 @@
         <v>0.53999999999999992</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="129" spans="1:6">
       <c r="B129" s="218" t="str">
         <f>DCF!B77</f>
         <v>Pessimistic</v>
@@ -5396,7 +5385,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="130" spans="1:6">
       <c r="B130" s="218" t="str">
         <f>DCF!B78</f>
         <v>Devil's advocate</v>
@@ -5418,7 +5407,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="132" spans="1:6">
       <c r="B132" s="211" t="s">
         <v>258</v>
       </c>
@@ -5431,16 +5420,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="134" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B134" s="361" t="s">
+    <row r="134" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B134" s="362" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="361"/>
-      <c r="D134" s="361"/>
-      <c r="E134" s="361"/>
-      <c r="F134" s="361"/>
-    </row>
-    <row r="136" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+      <c r="C134" s="362"/>
+      <c r="D134" s="362"/>
+      <c r="E134" s="362"/>
+      <c r="F134" s="362"/>
+    </row>
+    <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
         <v>402</v>
       </c>
@@ -5450,30 +5439,30 @@
       <c r="E136" s="36"/>
       <c r="F136" s="36"/>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B138" s="359" t="s">
+    <row r="138" spans="1:6">
+      <c r="B138" s="363" t="s">
         <v>368</v>
       </c>
-      <c r="C138" s="359"/>
-      <c r="D138" s="359"/>
-      <c r="E138" s="359"/>
-      <c r="F138" s="359"/>
-    </row>
-    <row r="139" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B139" s="356" t="s">
+      <c r="C138" s="363"/>
+      <c r="D138" s="363"/>
+      <c r="E138" s="363"/>
+      <c r="F138" s="363"/>
+    </row>
+    <row r="139" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B139" s="358" t="s">
         <v>369</v>
       </c>
-      <c r="C139" s="356"/>
-      <c r="D139" s="356"/>
-      <c r="E139" s="356"/>
-      <c r="F139" s="356"/>
-    </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
+    </row>
+    <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="141" spans="1:6">
       <c r="B141" s="1" t="s">
         <v>263</v>
       </c>
@@ -5482,7 +5471,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="142" spans="1:6">
       <c r="B142" s="1" t="s">
         <v>276</v>
       </c>
@@ -5491,7 +5480,7 @@
         <v>0.33699999999999997</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="143" spans="1:6">
       <c r="B143" s="212" t="s">
         <v>261</v>
       </c>
@@ -5504,7 +5493,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="145" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="145" spans="2:4">
       <c r="B145" s="210" t="s">
         <v>408</v>
       </c>
@@ -5517,7 +5506,7 @@
         <v/>
       </c>
     </row>
-    <row r="146" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="146" spans="2:4">
       <c r="B146" s="1" t="s">
         <v>407</v>
       </c>
@@ -5526,7 +5515,7 @@
         <v>0.33699999999999997</v>
       </c>
     </row>
-    <row r="147" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="147" spans="2:4">
       <c r="B147" s="212" t="str">
         <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5536,7 +5525,7 @@
         <v>0.69031028314322296</v>
       </c>
     </row>
-    <row r="148" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="148" spans="2:4">
       <c r="B148" s="212" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5546,7 +5535,7 @@
         <v>4.2893376993526235</v>
       </c>
     </row>
-    <row r="149" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="149" spans="2:4">
       <c r="B149" s="80" t="s">
         <v>260</v>
       </c>
@@ -5559,7 +5548,7 @@
         <v/>
       </c>
     </row>
-    <row r="150" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="150" spans="2:4">
       <c r="B150" s="259" t="s">
         <v>416</v>
       </c>
@@ -5572,7 +5561,7 @@
         <v/>
       </c>
     </row>
-    <row r="151" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="151" spans="2:4">
       <c r="B151" s="214" t="s">
         <v>262</v>
       </c>
@@ -5581,12 +5570,12 @@
         <v>0.51424846499304677</v>
       </c>
     </row>
-    <row r="153" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="153" spans="2:4">
       <c r="B153" s="210" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="154" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="154" spans="2:4">
       <c r="B154" s="1" t="s">
         <v>410</v>
       </c>
@@ -5595,7 +5584,7 @@
         <v>0.187</v>
       </c>
     </row>
-    <row r="155" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="155" spans="2:4">
       <c r="B155" s="212" t="str">
         <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5605,7 +5594,7 @@
         <v>0.86005014536183588</v>
       </c>
     </row>
-    <row r="156" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="156" spans="2:4">
       <c r="B156" s="212" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5615,7 +5604,7 @@
         <v>6.1296023972810385</v>
       </c>
     </row>
-    <row r="157" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="157" spans="2:4">
       <c r="B157" s="80" t="s">
         <v>260</v>
       </c>
@@ -5628,7 +5617,7 @@
         <v/>
       </c>
     </row>
-    <row r="158" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="158" spans="2:4">
       <c r="B158" s="259" t="s">
         <v>416</v>
       </c>
@@ -5641,7 +5630,7 @@
         <v/>
       </c>
     </row>
-    <row r="159" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="159" spans="2:4">
       <c r="B159" s="214" t="s">
         <v>262</v>
       </c>
@@ -5650,12 +5639,12 @@
         <v>0.31817781825366975</v>
       </c>
     </row>
-    <row r="161" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="161" spans="2:4">
       <c r="B161" s="210" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="162" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="162" spans="2:4">
       <c r="B162" s="1" t="s">
         <v>409</v>
       </c>
@@ -5664,7 +5653,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="163" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="163" spans="2:4">
       <c r="B163" s="212" t="str">
         <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5674,7 +5663,7 @@
         <v>1.069204779784656</v>
       </c>
     </row>
-    <row r="164" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="164" spans="2:4">
       <c r="B164" s="212" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5684,7 +5673,7 @@
         <v>8.6072985209538491</v>
       </c>
     </row>
-    <row r="165" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="165" spans="2:4">
       <c r="B165" s="80" t="s">
         <v>401</v>
       </c>
@@ -5697,7 +5686,7 @@
         <v/>
       </c>
     </row>
-    <row r="166" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="166" spans="2:4">
       <c r="B166" s="259" t="s">
         <v>416</v>
       </c>
@@ -5710,7 +5699,7 @@
         <v/>
       </c>
     </row>
-    <row r="167" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="167" spans="2:4">
       <c r="B167" s="214" t="s">
         <v>262</v>
       </c>
@@ -5719,12 +5708,12 @@
         <v>5.6082608980383197E-2</v>
       </c>
     </row>
-    <row r="169" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="169" spans="2:4">
       <c r="B169" s="210" t="s">
         <v>432</v>
       </c>
     </row>
-    <row r="170" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="170" spans="2:4">
       <c r="B170" s="1" t="s">
         <v>423</v>
       </c>
@@ -5733,7 +5722,7 @@
         <v>8.6999999999999994E-2</v>
       </c>
     </row>
-    <row r="171" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="171" spans="2:4">
       <c r="B171" s="212" t="str">
         <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5743,7 +5732,7 @@
         <v>1.0179560233797402</v>
       </c>
     </row>
-    <row r="172" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="172" spans="2:4">
       <c r="B172" s="212" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5753,7 +5742,7 @@
         <v>7.981707879328158</v>
       </c>
     </row>
-    <row r="173" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="173" spans="2:4">
       <c r="B173" s="80" t="s">
         <v>401</v>
       </c>
@@ -5766,7 +5755,7 @@
         <v/>
       </c>
     </row>
-    <row r="174" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="174" spans="2:4">
       <c r="B174" s="259" t="s">
         <v>416</v>
       </c>
@@ -5779,7 +5768,7 @@
         <v/>
       </c>
     </row>
-    <row r="175" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="175" spans="2:4">
       <c r="B175" s="214" t="s">
         <v>262</v>
       </c>
@@ -5788,7 +5777,7 @@
         <v>0.11980238369313911</v>
       </c>
     </row>
-    <row r="177" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:6" ht="13.9">
       <c r="A177" s="222" t="s">
         <v>374</v>
       </c>
@@ -5798,21 +5787,21 @@
       <c r="E177" s="36"/>
       <c r="F177" s="36"/>
     </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B179" s="363" t="s">
+    <row r="179" spans="1:6">
+      <c r="B179" s="357" t="s">
         <v>376</v>
       </c>
-      <c r="C179" s="356"/>
-      <c r="D179" s="356"/>
-      <c r="E179" s="356"/>
-      <c r="F179" s="356"/>
-    </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
+    </row>
+    <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="182" spans="1:6">
       <c r="B182" s="360" t="s">
         <v>380</v>
       </c>
@@ -5821,91 +5810,80 @@
       <c r="E182" s="360"/>
       <c r="F182" s="360"/>
     </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="184" spans="1:6">
       <c r="B184" s="214" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="185" spans="1:6">
       <c r="B185" s="214" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="187" spans="1:6">
       <c r="B187" s="1" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="188" spans="1:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B188" s="357" t="s">
+    <row r="188" spans="1:6" ht="46.5" customHeight="1">
+      <c r="B188" s="359" t="s">
         <v>381</v>
       </c>
-      <c r="C188" s="357"/>
-      <c r="D188" s="357"/>
-      <c r="E188" s="357"/>
-      <c r="F188" s="357"/>
-    </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
+    </row>
+    <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="191" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B191" s="362" t="s">
+    <row r="191" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B191" s="356" t="s">
         <v>382</v>
       </c>
-      <c r="C191" s="362"/>
-      <c r="D191" s="362"/>
-      <c r="E191" s="362"/>
-      <c r="F191" s="362"/>
-    </row>
-    <row r="192" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B192" s="362" t="s">
+      <c r="C191" s="356"/>
+      <c r="D191" s="356"/>
+      <c r="E191" s="356"/>
+      <c r="F191" s="356"/>
+    </row>
+    <row r="192" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B192" s="356" t="s">
         <v>383</v>
       </c>
-      <c r="C192" s="362"/>
-      <c r="D192" s="362"/>
-      <c r="E192" s="362"/>
-      <c r="F192" s="362"/>
-    </row>
-    <row r="194" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="C192" s="356"/>
+      <c r="D192" s="356"/>
+      <c r="E192" s="356"/>
+      <c r="F192" s="356"/>
+    </row>
+    <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="195" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="195" spans="2:2">
       <c r="B195" s="214" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="196" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="196" spans="2:2">
       <c r="B196" s="214" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="197" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="197" spans="2:2">
       <c r="B197" s="214" t="s">
         <v>388</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5922,6 +5900,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -5952,15 +5941,15 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:M80"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="3" style="1" customWidth="1"/>
     <col min="2" max="2" width="27.33203125" style="1" customWidth="1"/>
     <col min="3" max="13" width="20.6640625" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.83203125" style="1"/>
+    <col min="14" max="16384" width="8.796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="1" spans="2:13">
       <c r="B1" s="90" t="str">
         <f>Thesis!C25</f>
         <v>CNY</v>
@@ -6009,7 +5998,7 @@
         <v>42004</v>
       </c>
     </row>
-    <row r="2" spans="2:13" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:13" ht="13.9">
       <c r="B2" s="36" t="s">
         <v>97</v>
       </c>
@@ -6025,7 +6014,7 @@
       <c r="L2" s="37"/>
       <c r="M2" s="37"/>
     </row>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:13">
       <c r="B3" s="16" t="s">
         <v>27</v>
       </c>
@@ -6033,7 +6022,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:13">
       <c r="B4" s="32" t="s">
         <v>2</v>
       </c>
@@ -6069,7 +6058,7 @@
       </c>
       <c r="M4" s="351"/>
     </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:13">
       <c r="B5" s="40" t="s">
         <v>43</v>
       </c>
@@ -6105,7 +6094,7 @@
       </c>
       <c r="M5" s="351"/>
     </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:13">
       <c r="B6" s="40" t="s">
         <v>54</v>
       </c>
@@ -6141,7 +6130,7 @@
       </c>
       <c r="M6" s="351"/>
     </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:13">
       <c r="B7" s="69" t="s">
         <v>61</v>
       </c>
@@ -6177,7 +6166,7 @@
       </c>
       <c r="M7" s="352"/>
     </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:13">
       <c r="B8" s="40" t="s">
         <v>49</v>
       </c>
@@ -6207,7 +6196,7 @@
       <c r="L8" s="351"/>
       <c r="M8" s="351"/>
     </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:13">
       <c r="B9" s="40" t="s">
         <v>159</v>
       </c>
@@ -6223,7 +6212,7 @@
       <c r="L9" s="351"/>
       <c r="M9" s="351"/>
     </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:13">
       <c r="B10" s="40" t="s">
         <v>167</v>
       </c>
@@ -6239,7 +6228,7 @@
       <c r="L10" s="351"/>
       <c r="M10" s="351"/>
     </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:13">
       <c r="B11" s="40" t="s">
         <v>158</v>
       </c>
@@ -6255,7 +6244,7 @@
       <c r="L11" s="351"/>
       <c r="M11" s="351"/>
     </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:13">
       <c r="B12" s="40" t="s">
         <v>39</v>
       </c>
@@ -6285,7 +6274,7 @@
       <c r="L12" s="351"/>
       <c r="M12" s="351"/>
     </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:13">
       <c r="B13" s="40" t="s">
         <v>67</v>
       </c>
@@ -6315,7 +6304,7 @@
       <c r="L13" s="351"/>
       <c r="M13" s="351"/>
     </row>
-    <row r="14" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:13">
       <c r="B14" s="40" t="s">
         <v>50</v>
       </c>
@@ -6351,7 +6340,7 @@
       </c>
       <c r="M14" s="351"/>
     </row>
-    <row r="15" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:13">
       <c r="B15" s="43" t="s">
         <v>42</v>
       </c>
@@ -6387,7 +6376,7 @@
       </c>
       <c r="M15" s="353"/>
     </row>
-    <row r="16" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:13">
       <c r="B16" s="28" t="s">
         <v>44</v>
       </c>
@@ -6423,13 +6412,13 @@
       </c>
       <c r="M16" s="351"/>
     </row>
-    <row r="18" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:13">
       <c r="B18" s="16" t="s">
         <v>51</v>
       </c>
       <c r="C18" s="9"/>
     </row>
-    <row r="19" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:13">
       <c r="B19" s="27" t="s">
         <v>47</v>
       </c>
@@ -6459,7 +6448,7 @@
       <c r="L19" s="351"/>
       <c r="M19" s="351"/>
     </row>
-    <row r="20" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:13">
       <c r="B20" s="27" t="s">
         <v>53</v>
       </c>
@@ -6475,7 +6464,7 @@
       <c r="L20" s="351"/>
       <c r="M20" s="351"/>
     </row>
-    <row r="21" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:13">
       <c r="B21" s="27" t="s">
         <v>52</v>
       </c>
@@ -6491,7 +6480,7 @@
       <c r="L21" s="351"/>
       <c r="M21" s="351"/>
     </row>
-    <row r="22" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:13">
       <c r="B22" s="27" t="s">
         <v>371</v>
       </c>
@@ -6527,7 +6516,7 @@
       </c>
       <c r="M22" s="351"/>
     </row>
-    <row r="23" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:13">
       <c r="B23" s="27" t="s">
         <v>373</v>
       </c>
@@ -6563,7 +6552,7 @@
       </c>
       <c r="M23" s="351"/>
     </row>
-    <row r="24" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:13">
       <c r="B24" s="27" t="s">
         <v>372</v>
       </c>
@@ -6599,7 +6588,7 @@
       </c>
       <c r="M24" s="351"/>
     </row>
-    <row r="25" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:13">
       <c r="B25" s="24" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
         <v>Dividend per share (CNY)</v>
@@ -6634,7 +6623,7 @@
       <c r="L25" s="39"/>
       <c r="M25" s="39"/>
     </row>
-    <row r="27" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:13">
       <c r="B27" s="16" t="s">
         <v>28</v>
       </c>
@@ -6642,7 +6631,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="28" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:13">
       <c r="B28" s="26" t="s">
         <v>24</v>
       </c>
@@ -6679,7 +6668,7 @@
       </c>
       <c r="M28" s="351"/>
     </row>
-    <row r="29" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:13">
       <c r="B29" s="26" t="s">
         <v>32</v>
       </c>
@@ -6716,7 +6705,7 @@
       </c>
       <c r="M29" s="351"/>
     </row>
-    <row r="30" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:13">
       <c r="B30" s="29" t="s">
         <v>40</v>
       </c>
@@ -6753,7 +6742,7 @@
       </c>
       <c r="M30" s="353"/>
     </row>
-    <row r="31" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:13">
       <c r="B31" s="29" t="s">
         <v>30</v>
       </c>
@@ -6790,7 +6779,7 @@
       </c>
       <c r="M31" s="353"/>
     </row>
-    <row r="32" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:13">
       <c r="B32" s="26" t="s">
         <v>172</v>
       </c>
@@ -6827,7 +6816,7 @@
       </c>
       <c r="M32" s="351"/>
     </row>
-    <row r="34" spans="2:13" ht="16" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:13" ht="13.9">
       <c r="B34" s="36" t="s">
         <v>81</v>
       </c>
@@ -6843,12 +6832,12 @@
       <c r="L34" s="37"/>
       <c r="M34" s="37"/>
     </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:13">
       <c r="B35" s="16" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="36" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:13">
       <c r="B36" s="32" t="s">
         <v>2</v>
       </c>
@@ -6897,7 +6886,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:13">
       <c r="B37" s="40" t="s">
         <v>43</v>
       </c>
@@ -6946,7 +6935,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:13">
       <c r="B38" s="31" t="s">
         <v>58</v>
       </c>
@@ -6995,7 +6984,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:13">
       <c r="B39" s="40" t="s">
         <v>54</v>
       </c>
@@ -7044,7 +7033,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:13">
       <c r="B40" s="69" t="s">
         <v>61</v>
       </c>
@@ -7093,7 +7082,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:13">
       <c r="B41" s="69" t="s">
         <v>64</v>
       </c>
@@ -7142,7 +7131,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:13">
       <c r="B42" s="40" t="s">
         <v>49</v>
       </c>
@@ -7191,7 +7180,7 @@
         <v/>
       </c>
     </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="43" spans="2:13">
       <c r="B43" s="43" t="s">
         <v>152</v>
       </c>
@@ -7240,7 +7229,7 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:13">
       <c r="B44" s="43" t="s">
         <v>168</v>
       </c>
@@ -7289,7 +7278,7 @@
         <v/>
       </c>
     </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:13">
       <c r="B45" s="40" t="s">
         <v>68</v>
       </c>
@@ -7338,7 +7327,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:13">
       <c r="B46" s="40" t="s">
         <v>50</v>
       </c>
@@ -7387,7 +7376,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:13">
       <c r="B47" s="43" t="s">
         <v>42</v>
       </c>
@@ -7436,7 +7425,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:13">
       <c r="B48" s="28" t="s">
         <v>44</v>
       </c>
@@ -7485,12 +7474,12 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:13">
       <c r="B50" s="16" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="51" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:13">
       <c r="B51" s="40" t="s">
         <v>39</v>
       </c>
@@ -7539,7 +7528,7 @@
         <v/>
       </c>
     </row>
-    <row r="52" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:13">
       <c r="B52" s="40" t="s">
         <v>67</v>
       </c>
@@ -7588,12 +7577,12 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="54" spans="2:13">
       <c r="B54" s="174" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="55" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:13">
       <c r="B55" s="40" t="s">
         <v>159</v>
       </c>
@@ -7642,7 +7631,7 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:13">
       <c r="B56" s="40" t="s">
         <v>167</v>
       </c>
@@ -7691,7 +7680,7 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:13">
       <c r="B57" s="40" t="s">
         <v>158</v>
       </c>
@@ -7740,7 +7729,7 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:13">
       <c r="B58" s="40" t="s">
         <v>160</v>
       </c>
@@ -7789,13 +7778,13 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:13">
       <c r="B60" s="16" t="s">
         <v>51</v>
       </c>
       <c r="C60" s="9"/>
     </row>
-    <row r="61" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="61" spans="2:13">
       <c r="B61" s="27" t="s">
         <v>47</v>
       </c>
@@ -7844,7 +7833,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:13">
       <c r="B62" s="27" t="s">
         <v>53</v>
       </c>
@@ -7893,7 +7882,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="63" spans="2:13">
       <c r="B63" s="27" t="s">
         <v>52</v>
       </c>
@@ -7942,7 +7931,7 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:13">
       <c r="B64" s="27" t="s">
         <v>393</v>
       </c>
@@ -7991,7 +7980,7 @@
         <v/>
       </c>
     </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="65" spans="2:13">
       <c r="B65" s="24" t="s">
         <v>36</v>
       </c>
@@ -8040,12 +8029,12 @@
         <v/>
       </c>
     </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="67" spans="2:13">
       <c r="B67" s="91" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="68" spans="2:13">
       <c r="B68" s="1" t="str">
         <f>B36</f>
         <v>Sales</v>
@@ -8095,7 +8084,7 @@
         <v/>
       </c>
     </row>
-    <row r="69" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="69" spans="2:13">
       <c r="B69" s="31" t="s">
         <v>58</v>
       </c>
@@ -8144,7 +8133,7 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="70" spans="2:13">
       <c r="B70" s="80" t="str">
         <f>B43</f>
         <v>Operating EBIT</v>
@@ -8194,7 +8183,7 @@
         <v/>
       </c>
     </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="71" spans="2:13">
       <c r="B71" s="43" t="s">
         <v>168</v>
       </c>
@@ -8243,7 +8232,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="72" spans="2:13">
       <c r="B72" s="80" t="str">
         <f>B47</f>
         <v>Reported Net Income</v>
@@ -8293,7 +8282,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="2:13" ht="16" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:13" ht="13.9">
       <c r="B74" s="36" t="s">
         <v>82</v>
       </c>
@@ -8309,13 +8298,13 @@
       <c r="L74" s="37"/>
       <c r="M74" s="37"/>
     </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="75" spans="2:13">
       <c r="B75" s="16" t="s">
         <v>28</v>
       </c>
       <c r="C75" s="9"/>
     </row>
-    <row r="76" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="76" spans="2:13">
       <c r="B76" s="26" t="s">
         <v>3</v>
       </c>
@@ -8364,7 +8353,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="77" spans="2:13">
       <c r="B77" s="93" t="s">
         <v>85</v>
       </c>
@@ -8398,7 +8387,7 @@
       <c r="L77" s="355"/>
       <c r="M77" s="355"/>
     </row>
-    <row r="78" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="78" spans="2:13">
       <c r="B78" s="93" t="s">
         <v>86</v>
       </c>
@@ -8432,7 +8421,7 @@
       <c r="L78" s="355"/>
       <c r="M78" s="355"/>
     </row>
-    <row r="79" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="79" spans="2:13">
       <c r="B79" s="26" t="s">
         <v>40</v>
       </c>
@@ -8481,7 +8470,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="80" spans="2:13">
       <c r="B80" s="26" t="s">
         <v>30</v>
       </c>
@@ -8562,7 +8551,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:H89"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="2.33203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="34" style="1" bestFit="1" customWidth="1"/>
@@ -8573,7 +8562,7 @@
     <col min="9" max="16384" width="12.33203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="2:8" ht="15" customHeight="1">
       <c r="B1" s="18" t="s">
         <v>37</v>
       </c>
@@ -8589,7 +8578,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="2:8" ht="15" customHeight="1">
       <c r="B2" s="79" t="s">
         <v>156</v>
       </c>
@@ -8600,7 +8589,7 @@
       <c r="G2" s="37"/>
       <c r="H2" s="37"/>
     </row>
-    <row r="3" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:8" ht="15" customHeight="1">
       <c r="B3" s="16" t="s">
         <v>184</v>
       </c>
@@ -8620,7 +8609,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:8" ht="15" customHeight="1">
       <c r="B4" s="4" t="s">
         <v>24</v>
       </c>
@@ -8642,7 +8631,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="5" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:8" ht="15" customHeight="1">
       <c r="B5" s="1" t="s">
         <v>33</v>
       </c>
@@ -8663,7 +8652,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="6" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:8" ht="15" customHeight="1">
       <c r="B6" s="4" t="s">
         <v>10</v>
       </c>
@@ -8684,7 +8673,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="7" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:8" ht="15" customHeight="1">
       <c r="B7" s="1" t="s">
         <v>69</v>
       </c>
@@ -8705,7 +8694,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="8" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:8" ht="15" customHeight="1">
       <c r="B8" s="1" t="s">
         <v>173</v>
       </c>
@@ -8726,7 +8715,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="9" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:8" ht="15" customHeight="1">
       <c r="B9" s="4" t="s">
         <v>25</v>
       </c>
@@ -8747,7 +8736,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="10" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:8" ht="15" customHeight="1">
       <c r="B10" s="4" t="s">
         <v>11</v>
       </c>
@@ -8759,7 +8748,7 @@
       </c>
       <c r="H10" s="262"/>
     </row>
-    <row r="11" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:8" ht="15" customHeight="1">
       <c r="B11" s="4" t="s">
         <v>12</v>
       </c>
@@ -8771,7 +8760,7 @@
       </c>
       <c r="H11" s="262"/>
     </row>
-    <row r="12" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:8" ht="15" customHeight="1">
       <c r="B12" s="80" t="s">
         <v>72</v>
       </c>
@@ -8795,12 +8784,12 @@
         <v>911297844.82799995</v>
       </c>
     </row>
-    <row r="13" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:8" ht="15" customHeight="1">
       <c r="F13" s="80"/>
       <c r="G13" s="81"/>
       <c r="H13" s="20"/>
     </row>
-    <row r="14" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:8" ht="15" customHeight="1">
       <c r="B14" s="16" t="s">
         <v>183</v>
       </c>
@@ -8820,7 +8809,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:8" ht="15" customHeight="1">
       <c r="B15" s="4" t="s">
         <v>454</v>
       </c>
@@ -8840,7 +8829,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="16" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:8" ht="15" customHeight="1">
       <c r="B16" s="1" t="s">
         <v>34</v>
       </c>
@@ -8860,7 +8849,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="17" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:8" ht="15" customHeight="1">
       <c r="B17" s="1" t="s">
         <v>69</v>
       </c>
@@ -8880,7 +8869,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="18" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:8" ht="15" customHeight="1">
       <c r="B18" s="4" t="s">
         <v>173</v>
       </c>
@@ -8900,7 +8889,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="19" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:8" ht="15" customHeight="1">
       <c r="B19" s="4" t="s">
         <v>26</v>
       </c>
@@ -8921,7 +8910,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="20" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:8" ht="15" customHeight="1">
       <c r="B20" s="4" t="s">
         <v>18</v>
       </c>
@@ -8941,7 +8930,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="21" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:8" ht="15" customHeight="1">
       <c r="B21" s="4" t="s">
         <v>19</v>
       </c>
@@ -8961,7 +8950,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="22" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:8" ht="15" customHeight="1">
       <c r="B22" s="4" t="s">
         <v>20</v>
       </c>
@@ -8973,7 +8962,7 @@
       </c>
       <c r="H22" s="262"/>
     </row>
-    <row r="23" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:8" ht="15" customHeight="1">
       <c r="B23" s="4" t="s">
         <v>21</v>
       </c>
@@ -8986,7 +8975,7 @@
       </c>
       <c r="H23" s="262"/>
     </row>
-    <row r="24" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:8" ht="15" customHeight="1">
       <c r="B24" s="80" t="s">
         <v>73</v>
       </c>
@@ -9010,7 +8999,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:8" ht="15" customHeight="1">
       <c r="B26" s="16" t="s">
         <v>200</v>
       </c>
@@ -9027,7 +9016,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="27" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:8" ht="15" customHeight="1">
       <c r="B27" s="4" t="s">
         <v>5</v>
       </c>
@@ -9046,7 +9035,7 @@
         <v>955477434.55499983</v>
       </c>
     </row>
-    <row r="28" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:8" ht="15" customHeight="1">
       <c r="B28" s="4" t="s">
         <v>6</v>
       </c>
@@ -9061,7 +9050,7 @@
       </c>
       <c r="H28" s="188"/>
     </row>
-    <row r="29" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:8" ht="15" customHeight="1">
       <c r="B29" s="4" t="s">
         <v>7</v>
       </c>
@@ -9080,7 +9069,7 @@
         <v>955849140.38499987</v>
       </c>
     </row>
-    <row r="30" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:8" ht="15" customHeight="1">
       <c r="B30" s="2" t="s">
         <v>8</v>
       </c>
@@ -9096,7 +9085,7 @@
       </c>
       <c r="H30" s="188"/>
     </row>
-    <row r="31" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:8" ht="15" customHeight="1">
       <c r="B31" s="80" t="s">
         <v>203</v>
       </c>
@@ -9113,7 +9102,7 @@
       </c>
       <c r="H31" s="188"/>
     </row>
-    <row r="32" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:8" ht="15" customHeight="1">
       <c r="B32" s="4" t="s">
         <v>9</v>
       </c>
@@ -9133,7 +9122,7 @@
         <v>1357028359.4749999</v>
       </c>
     </row>
-    <row r="33" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:8" ht="15" customHeight="1">
       <c r="B33" s="83" t="s">
         <v>4</v>
       </c>
@@ -9144,7 +9133,7 @@
       <c r="G33" s="2"/>
       <c r="H33" s="195"/>
     </row>
-    <row r="34" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:8" ht="15" customHeight="1">
       <c r="B34" s="83"/>
       <c r="C34" s="84"/>
       <c r="F34" s="196" t="s">
@@ -9157,7 +9146,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="35" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:8" ht="15" customHeight="1">
       <c r="B35" s="16" t="s">
         <v>201</v>
       </c>
@@ -9176,7 +9165,7 @@
         <v>445730514.64700001</v>
       </c>
     </row>
-    <row r="36" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:8" ht="15" customHeight="1">
       <c r="B36" s="4" t="s">
         <v>13</v>
       </c>
@@ -9192,7 +9181,7 @@
       </c>
       <c r="H36" s="195"/>
     </row>
-    <row r="37" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:8" ht="15" customHeight="1">
       <c r="B37" s="4" t="s">
         <v>14</v>
       </c>
@@ -9208,7 +9197,7 @@
       </c>
       <c r="H37" s="195"/>
     </row>
-    <row r="38" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:8" ht="15" customHeight="1">
       <c r="B38" s="4" t="s">
         <v>15</v>
       </c>
@@ -9224,7 +9213,7 @@
       </c>
       <c r="H38" s="195"/>
     </row>
-    <row r="39" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:8" ht="15" customHeight="1">
       <c r="B39" s="2" t="s">
         <v>16</v>
       </c>
@@ -9243,7 +9232,7 @@
         <v>84395700.100000024</v>
       </c>
     </row>
-    <row r="40" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:8" ht="15" customHeight="1">
       <c r="B40" s="80" t="s">
         <v>204</v>
       </c>
@@ -9263,7 +9252,7 @@
         <v>911297844.82799995</v>
       </c>
     </row>
-    <row r="41" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:8" ht="15" customHeight="1">
       <c r="B41" s="4" t="s">
         <v>17</v>
       </c>
@@ -9283,7 +9272,7 @@
         <v>911297844.82799995</v>
       </c>
     </row>
-    <row r="42" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:8" ht="15" customHeight="1">
       <c r="B42" s="83" t="s">
         <v>22</v>
       </c>
@@ -9302,7 +9291,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:8" ht="15" customHeight="1">
       <c r="B44" s="79" t="s">
         <v>96</v>
       </c>
@@ -9313,7 +9302,7 @@
       <c r="G44" s="37"/>
       <c r="H44" s="37"/>
     </row>
-    <row r="45" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:8" ht="15" customHeight="1">
       <c r="B45" s="16" t="s">
         <v>271</v>
       </c>
@@ -9327,7 +9316,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="46" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:8" ht="15" customHeight="1">
       <c r="B46" s="1" t="s">
         <v>273</v>
       </c>
@@ -9341,7 +9330,7 @@
       </c>
       <c r="F46" s="253"/>
     </row>
-    <row r="47" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:8" ht="15" customHeight="1">
       <c r="B47" s="1" t="str">
         <f>"Equity per share ("&amp;Market_currency&amp;")"</f>
         <v>Equity per share (CNY)</v>
@@ -9356,10 +9345,10 @@
       </c>
       <c r="F47" s="253"/>
     </row>
-    <row r="48" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:8" ht="15" customHeight="1">
       <c r="F48" s="253"/>
     </row>
-    <row r="49" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="2:8" ht="15" customHeight="1">
       <c r="B49" s="157" t="s">
         <v>143</v>
       </c>
@@ -9372,7 +9361,7 @@
       <c r="E49" s="2"/>
       <c r="F49" s="253"/>
     </row>
-    <row r="50" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:8" ht="15" customHeight="1">
       <c r="B50" s="8" t="s">
         <v>93</v>
       </c>
@@ -9386,7 +9375,7 @@
       </c>
       <c r="F50" s="253"/>
     </row>
-    <row r="51" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:8" ht="15" customHeight="1">
       <c r="B51" s="1" t="s">
         <v>176</v>
       </c>
@@ -9397,10 +9386,10 @@
       </c>
       <c r="F51" s="253"/>
     </row>
-    <row r="52" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:8" ht="15" customHeight="1">
       <c r="F52" s="253"/>
     </row>
-    <row r="53" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="2:8" ht="15" customHeight="1">
       <c r="B53" s="157" t="s">
         <v>142</v>
       </c>
@@ -9412,7 +9401,7 @@
       </c>
       <c r="F53" s="253"/>
     </row>
-    <row r="54" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="2:8" ht="15" customHeight="1">
       <c r="B54" s="1" t="s">
         <v>139</v>
       </c>
@@ -9426,7 +9415,7 @@
       </c>
       <c r="F54" s="253"/>
     </row>
-    <row r="55" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:8" ht="15" customHeight="1">
       <c r="B55" s="1" t="s">
         <v>141</v>
       </c>
@@ -9440,10 +9429,10 @@
       </c>
       <c r="F55" s="253"/>
     </row>
-    <row r="56" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:8" ht="15" customHeight="1">
       <c r="F56" s="253"/>
     </row>
-    <row r="57" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:8" ht="15" customHeight="1">
       <c r="B57" s="157" t="s">
         <v>175</v>
       </c>
@@ -9455,7 +9444,7 @@
       </c>
       <c r="F57" s="253"/>
     </row>
-    <row r="58" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:8" ht="15" customHeight="1">
       <c r="B58" s="2" t="s">
         <v>89</v>
       </c>
@@ -9466,7 +9455,7 @@
       </c>
       <c r="F58" s="5"/>
     </row>
-    <row r="59" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="2:8" ht="15" customHeight="1">
       <c r="B59" s="1" t="s">
         <v>92</v>
       </c>
@@ -9477,10 +9466,10 @@
       </c>
       <c r="F59" s="253"/>
     </row>
-    <row r="60" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:8" ht="15" customHeight="1">
       <c r="F60" s="253"/>
     </row>
-    <row r="61" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="61" spans="2:8" ht="15" customHeight="1">
       <c r="B61" s="157" t="s">
         <v>274</v>
       </c>
@@ -9492,7 +9481,7 @@
       </c>
       <c r="F61" s="253"/>
     </row>
-    <row r="62" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:8" ht="15" customHeight="1">
       <c r="B62" s="1" t="s">
         <v>245</v>
       </c>
@@ -9508,7 +9497,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="64" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:8" ht="15" customHeight="1">
       <c r="B64" s="79" t="s">
         <v>193</v>
       </c>
@@ -9519,7 +9508,7 @@
       <c r="G64" s="37"/>
       <c r="H64" s="37"/>
     </row>
-    <row r="65" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="2:6" ht="15" customHeight="1">
       <c r="B65" s="16" t="s">
         <v>188</v>
       </c>
@@ -9533,7 +9522,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="66" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="66" spans="2:6" ht="15" customHeight="1">
       <c r="B66" s="105" t="s">
         <v>187</v>
       </c>
@@ -9549,7 +9538,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="67" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="67" spans="2:6" ht="15" customHeight="1">
       <c r="B67" s="105" t="s">
         <v>177</v>
       </c>
@@ -9559,7 +9548,7 @@
       </c>
       <c r="F67" s="253"/>
     </row>
-    <row r="68" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="68" spans="2:6" ht="15" customHeight="1">
       <c r="B68" s="105" t="s">
         <v>181</v>
       </c>
@@ -9569,7 +9558,7 @@
       </c>
       <c r="F68" s="253"/>
     </row>
-    <row r="69" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="69" spans="2:6" ht="15" customHeight="1">
       <c r="B69" s="105" t="s">
         <v>179</v>
       </c>
@@ -9579,7 +9568,7 @@
       </c>
       <c r="F69" s="253"/>
     </row>
-    <row r="70" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="70" spans="2:6" ht="15" customHeight="1">
       <c r="B70" s="80" t="s">
         <v>188</v>
       </c>
@@ -9589,10 +9578,10 @@
       </c>
       <c r="F70" s="253"/>
     </row>
-    <row r="71" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="71" spans="2:6" ht="15" customHeight="1">
       <c r="F71" s="253"/>
     </row>
-    <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="72" spans="2:6" ht="15" customHeight="1">
       <c r="B72" s="255" t="s">
         <v>318</v>
       </c>
@@ -9604,7 +9593,7 @@
       </c>
       <c r="F72" s="253"/>
     </row>
-    <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="73" spans="2:6" ht="15" customHeight="1">
       <c r="B73" s="105" t="s">
         <v>317</v>
       </c>
@@ -9620,7 +9609,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="74" spans="2:6" ht="15" customHeight="1">
       <c r="B74" s="257" t="s">
         <v>321</v>
       </c>
@@ -9636,7 +9625,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="75" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="75" spans="2:6" ht="15" customHeight="1">
       <c r="B75" s="80" t="s">
         <v>320</v>
       </c>
@@ -9649,7 +9638,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="76" spans="2:6" ht="15" customHeight="1">
       <c r="B76" s="259" t="s">
         <v>322</v>
       </c>
@@ -9662,10 +9651,10 @@
         <v>323</v>
       </c>
     </row>
-    <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="77" spans="2:6" ht="15" customHeight="1">
       <c r="F77" s="253"/>
     </row>
-    <row r="78" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="78" spans="2:6" ht="15" customHeight="1">
       <c r="B78" s="16" t="s">
         <v>189</v>
       </c>
@@ -9677,7 +9666,7 @@
       </c>
       <c r="F78" s="253"/>
     </row>
-    <row r="79" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="79" spans="2:6" ht="15" customHeight="1">
       <c r="B79" s="105" t="s">
         <v>178</v>
       </c>
@@ -9691,7 +9680,7 @@
       </c>
       <c r="F79" s="253"/>
     </row>
-    <row r="80" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="2:6" ht="15" customHeight="1">
       <c r="B80" s="105" t="s">
         <v>182</v>
       </c>
@@ -9705,7 +9694,7 @@
       </c>
       <c r="F80" s="253"/>
     </row>
-    <row r="81" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="81" spans="2:8" ht="15" customHeight="1">
       <c r="B81" s="105" t="s">
         <v>180</v>
       </c>
@@ -9719,7 +9708,7 @@
       </c>
       <c r="F81" s="253"/>
     </row>
-    <row r="82" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="82" spans="2:8" ht="15" customHeight="1">
       <c r="B82" s="80" t="s">
         <v>189</v>
       </c>
@@ -9733,7 +9722,7 @@
       </c>
       <c r="F82" s="253"/>
     </row>
-    <row r="84" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="84" spans="2:8" ht="15" customHeight="1">
       <c r="B84" s="79" t="s">
         <v>288</v>
       </c>
@@ -9744,7 +9733,7 @@
       <c r="G84" s="37"/>
       <c r="H84" s="37"/>
     </row>
-    <row r="85" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="85" spans="2:8" ht="15" customHeight="1">
       <c r="B85" s="16" t="s">
         <v>289</v>
       </c>
@@ -9752,7 +9741,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="86" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="86" spans="2:8" ht="15" customHeight="1">
       <c r="B86" s="238" t="s">
         <v>286</v>
       </c>
@@ -9769,7 +9758,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="87" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="87" spans="2:8" ht="15" customHeight="1">
       <c r="B87" s="238" t="s">
         <v>287</v>
       </c>
@@ -9786,7 +9775,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="88" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="88" spans="2:8" ht="15" customHeight="1">
       <c r="B88" s="239" t="s">
         <v>189</v>
       </c>
@@ -9803,7 +9792,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="89" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="89" spans="2:8" ht="15" customHeight="1">
       <c r="B89" s="80" t="s">
         <v>291</v>
       </c>
@@ -9834,19 +9823,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q808"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="1.33203125" style="2" customWidth="1"/>
     <col min="2" max="2" width="26.33203125" style="2" customWidth="1"/>
     <col min="3" max="3" width="20.6640625" style="2" customWidth="1"/>
     <col min="4" max="4" width="2.6640625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="25.1640625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="25.1328125" style="2" customWidth="1"/>
     <col min="6" max="6" width="2.6640625" style="2" customWidth="1"/>
     <col min="7" max="17" width="20.6640625" style="2" customWidth="1"/>
     <col min="18" max="16384" width="12.33203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:17" ht="15.75" customHeight="1">
       <c r="A1" s="3"/>
       <c r="B1" s="90" t="str">
         <f>Thesis!C25</f>
@@ -9903,7 +9892,7 @@
         <v>42004</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" ht="15.75" customHeight="1">
       <c r="A2" s="3"/>
       <c r="B2" s="54" t="s">
         <v>99</v>
@@ -9926,7 +9915,7 @@
       <c r="P2" s="37"/>
       <c r="Q2" s="37"/>
     </row>
-    <row r="3" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:17" ht="15.75" customHeight="1">
       <c r="A3" s="10"/>
       <c r="B3" s="16" t="s">
         <v>66</v>
@@ -9940,7 +9929,7 @@
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
     </row>
-    <row r="4" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:17" ht="15.75" customHeight="1">
       <c r="A4" s="10"/>
       <c r="B4" s="26" t="s">
         <v>2</v>
@@ -9997,7 +9986,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:17" ht="15.75" customHeight="1">
       <c r="A5" s="10"/>
       <c r="B5" s="2" t="s">
         <v>46</v>
@@ -10052,7 +10041,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:17" ht="15.75" customHeight="1">
       <c r="A6" s="10"/>
       <c r="B6" s="31" t="s">
         <v>48</v>
@@ -10107,7 +10096,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:17" ht="15.75" customHeight="1">
       <c r="A7" s="10"/>
       <c r="B7" s="8" t="s">
         <v>45</v>
@@ -10162,7 +10151,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:17" ht="15.75" customHeight="1">
       <c r="A8" s="10"/>
       <c r="B8" s="29" t="s">
         <v>152</v>
@@ -10219,7 +10208,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:17" ht="15.75" customHeight="1">
       <c r="A9" s="10"/>
       <c r="B9" s="2" t="s">
         <v>65</v>
@@ -10274,7 +10263,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:17" ht="15.75" customHeight="1">
       <c r="A10" s="10"/>
       <c r="B10" s="2" t="s">
         <v>80</v>
@@ -10329,7 +10318,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:17" ht="15.75" customHeight="1">
       <c r="A11" s="10"/>
       <c r="B11" s="31" t="s">
         <v>194</v>
@@ -10386,7 +10375,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:17" ht="15.75" customHeight="1">
       <c r="A12" s="10"/>
       <c r="B12" s="2" t="s">
         <v>68</v>
@@ -10441,7 +10430,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:17" ht="15.75" customHeight="1">
       <c r="A13" s="10"/>
       <c r="B13" s="70" t="s">
         <v>164</v>
@@ -10496,7 +10485,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:17" ht="15.75" customHeight="1">
       <c r="A14" s="10"/>
       <c r="B14" s="2" t="s">
         <v>63</v>
@@ -10551,7 +10540,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:17" ht="15.75" customHeight="1">
       <c r="A15" s="10"/>
       <c r="B15" s="40" t="s">
         <v>243</v>
@@ -10608,7 +10597,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:17" ht="15.75" customHeight="1">
       <c r="A16" s="10"/>
       <c r="B16" s="41" t="s">
         <v>154</v>
@@ -10665,7 +10654,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:17" ht="15.75" customHeight="1">
       <c r="A17" s="10"/>
       <c r="B17" s="27" t="s">
         <v>52</v>
@@ -10691,7 +10680,7 @@
       <c r="P17" s="335"/>
       <c r="Q17" s="335"/>
     </row>
-    <row r="18" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:17" ht="15.75" customHeight="1">
       <c r="A18" s="10"/>
       <c r="B18" s="27" t="s">
         <v>98</v>
@@ -10716,7 +10705,7 @@
       <c r="P18" s="336"/>
       <c r="Q18" s="336"/>
     </row>
-    <row r="19" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:17" ht="15.75" customHeight="1">
       <c r="A19" s="10"/>
       <c r="B19" s="31" t="s">
         <v>66</v>
@@ -10773,7 +10762,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:17" ht="15.75" customHeight="1">
       <c r="A20" s="10"/>
       <c r="B20" s="27"/>
       <c r="C20" s="62"/>
@@ -10792,7 +10781,7 @@
       <c r="P20" s="12"/>
       <c r="Q20" s="12"/>
     </row>
-    <row r="21" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:17" ht="15.75" customHeight="1">
       <c r="A21" s="10"/>
       <c r="B21" s="54" t="s">
         <v>205</v>
@@ -10815,7 +10804,7 @@
       <c r="P21" s="37"/>
       <c r="Q21" s="37"/>
     </row>
-    <row r="22" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:17" ht="15.75" customHeight="1">
       <c r="A22" s="10"/>
       <c r="B22" s="64" t="s">
         <v>46</v>
@@ -10836,7 +10825,7 @@
       <c r="P22" s="12"/>
       <c r="Q22" s="12"/>
     </row>
-    <row r="23" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:17" ht="15.75" customHeight="1">
       <c r="A23" s="10"/>
       <c r="B23" s="27" t="s">
         <v>43</v>
@@ -10893,7 +10882,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:17" ht="15.75" customHeight="1">
       <c r="A24" s="10"/>
       <c r="B24" s="68" t="s">
         <v>62</v>
@@ -10950,7 +10939,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:17" ht="15.75" customHeight="1">
       <c r="A25" s="10"/>
       <c r="B25" s="70" t="s">
         <v>46</v>
@@ -11007,18 +10996,18 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:17" ht="15.75" customHeight="1">
       <c r="A26" s="10"/>
       <c r="E26" s="268"/>
     </row>
-    <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:17" ht="15.75" customHeight="1">
       <c r="A27" s="10"/>
       <c r="B27" s="64" t="s">
         <v>206</v>
       </c>
       <c r="E27" s="268"/>
     </row>
-    <row r="28" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:17" ht="15.75" customHeight="1">
       <c r="A28" s="10"/>
       <c r="B28" s="26" t="s">
         <v>43</v>
@@ -11077,7 +11066,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:17" ht="15.75" customHeight="1">
       <c r="A29" s="10"/>
       <c r="B29" s="68" t="str">
         <f>B24</f>
@@ -11137,7 +11126,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:17" ht="15.75" customHeight="1">
       <c r="A30" s="10"/>
       <c r="B30" s="70" t="s">
         <v>46</v>
@@ -11192,18 +11181,18 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:17" ht="15.75" customHeight="1">
       <c r="A31" s="10"/>
       <c r="E31" s="268"/>
     </row>
-    <row r="32" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:17" ht="15.75" customHeight="1">
       <c r="A32" s="10"/>
       <c r="B32" s="64" t="s">
         <v>45</v>
       </c>
       <c r="E32" s="268"/>
     </row>
-    <row r="33" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:17" ht="15.75" customHeight="1">
       <c r="A33" s="10"/>
       <c r="B33" s="8" t="s">
         <v>174</v>
@@ -11260,7 +11249,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:17" ht="15.75" customHeight="1">
       <c r="A34" s="10"/>
       <c r="B34" s="27" t="s">
         <v>49</v>
@@ -11319,7 +11308,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:17" ht="15.75" customHeight="1">
       <c r="A35" s="10"/>
       <c r="B35" s="70" t="s">
         <v>45</v>
@@ -11376,18 +11365,18 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:17" ht="15.75" customHeight="1">
       <c r="A36" s="10"/>
       <c r="E36" s="268"/>
     </row>
-    <row r="37" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:17" ht="15.75" customHeight="1">
       <c r="A37" s="10"/>
       <c r="B37" s="64" t="s">
         <v>207</v>
       </c>
       <c r="E37" s="268"/>
     </row>
-    <row r="38" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:17" ht="15.75" customHeight="1">
       <c r="A38" s="10"/>
       <c r="B38" s="2" t="str">
         <f>B33</f>
@@ -11445,7 +11434,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:17" ht="15.75" customHeight="1">
       <c r="A39" s="10"/>
       <c r="B39" s="27" t="str">
         <f>B34</f>
@@ -11503,7 +11492,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:17" ht="15.75" customHeight="1">
       <c r="A40" s="10"/>
       <c r="B40" s="70" t="s">
         <v>45</v>
@@ -11558,18 +11547,18 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:17" ht="15.75" customHeight="1">
       <c r="A41" s="10"/>
       <c r="E41" s="268"/>
     </row>
-    <row r="42" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:17" ht="15.75" customHeight="1">
       <c r="A42" s="10"/>
       <c r="B42" s="64" t="s">
         <v>208</v>
       </c>
       <c r="E42" s="268"/>
     </row>
-    <row r="43" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:17" ht="15.75" customHeight="1">
       <c r="A43" s="10"/>
       <c r="B43" s="27" t="s">
         <v>171</v>
@@ -11627,10 +11616,10 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:17" ht="15.75" customHeight="1">
       <c r="A44" s="10"/>
     </row>
-    <row r="45" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:17" ht="15.75" customHeight="1">
       <c r="A45" s="10"/>
       <c r="B45" s="54" t="s">
         <v>209</v>
@@ -11653,14 +11642,14 @@
       <c r="P45" s="37"/>
       <c r="Q45" s="37"/>
     </row>
-    <row r="46" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:17" ht="15.75" customHeight="1">
       <c r="A46" s="10"/>
       <c r="B46" s="64" t="s">
         <v>60</v>
       </c>
       <c r="E46" s="268"/>
     </row>
-    <row r="47" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:17" ht="15.75" customHeight="1">
       <c r="A47" s="10"/>
       <c r="B47" s="2" t="s">
         <v>39</v>
@@ -11715,7 +11704,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:17" ht="15.75" customHeight="1">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
         <v>345</v>
@@ -11770,7 +11759,7 @@
         <v/>
       </c>
     </row>
-    <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:17" ht="15.75" customHeight="1">
       <c r="A49" s="10"/>
       <c r="B49" s="287" t="s">
         <v>342</v>
@@ -11827,7 +11816,7 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:17" ht="15.75" customHeight="1">
       <c r="A50" s="10"/>
       <c r="B50" s="70" t="s">
         <v>68</v>
@@ -11882,11 +11871,11 @@
         <v/>
       </c>
     </row>
-    <row r="51" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:17" ht="15.75" customHeight="1">
       <c r="A51" s="10"/>
       <c r="E51" s="268"/>
     </row>
-    <row r="52" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:17" ht="15.75" customHeight="1">
       <c r="A52" s="10"/>
       <c r="B52" s="72" t="s">
         <v>155</v>
@@ -11896,7 +11885,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="53" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:17" ht="15.75" customHeight="1">
       <c r="A53" s="10"/>
       <c r="B53" s="8" t="s">
         <v>88</v>
@@ -11922,7 +11911,7 @@
       <c r="P53" s="169"/>
       <c r="Q53" s="169"/>
     </row>
-    <row r="54" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:17" ht="15.75" customHeight="1">
       <c r="A54" s="10"/>
       <c r="B54" s="8" t="s">
         <v>87</v>
@@ -11949,7 +11938,7 @@
       <c r="P54" s="169"/>
       <c r="Q54" s="169"/>
     </row>
-    <row r="55" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:17" ht="15.75" customHeight="1">
       <c r="A55" s="10"/>
       <c r="B55" s="26" t="s">
         <v>90</v>
@@ -12004,11 +11993,11 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:17" ht="15.75" customHeight="1">
       <c r="A56" s="10"/>
       <c r="E56" s="268"/>
     </row>
-    <row r="57" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:17" ht="15.75" customHeight="1">
       <c r="A57" s="10"/>
       <c r="B57" s="64" t="s">
         <v>168</v>
@@ -12018,7 +12007,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="58" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:17" ht="15.75" customHeight="1">
       <c r="A58" s="10"/>
       <c r="B58" s="40" t="s">
         <v>167</v>
@@ -12073,7 +12062,7 @@
         <v/>
       </c>
     </row>
-    <row r="59" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:17" ht="15.75" customHeight="1">
       <c r="A59" s="10"/>
       <c r="B59" s="40" t="s">
         <v>159</v>
@@ -12128,7 +12117,7 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:17" ht="15.75" customHeight="1">
       <c r="A60" s="10"/>
       <c r="B60" s="40" t="s">
         <v>158</v>
@@ -12183,7 +12172,7 @@
         <v/>
       </c>
     </row>
-    <row r="61" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:17" ht="15.75" customHeight="1">
       <c r="A61" s="10"/>
       <c r="B61" s="31" t="s">
         <v>194</v>
@@ -12238,7 +12227,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:17" ht="15.75" customHeight="1">
       <c r="A62" s="10"/>
       <c r="B62" s="40" t="s">
         <v>160</v>
@@ -12294,7 +12283,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:17" ht="15.75" customHeight="1">
       <c r="A63" s="10"/>
       <c r="B63" s="31" t="s">
         <v>195</v>
@@ -12349,11 +12338,11 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:17" ht="15.75" customHeight="1">
       <c r="A64" s="10"/>
       <c r="E64" s="268"/>
     </row>
-    <row r="65" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:17" ht="15.75" customHeight="1">
       <c r="A65" s="10"/>
       <c r="B65" s="96" t="s">
         <v>169</v>
@@ -12363,7 +12352,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="66" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:17" ht="15.75" customHeight="1">
       <c r="A66" s="10"/>
       <c r="B66" s="40" t="s">
         <v>167</v>
@@ -12388,7 +12377,7 @@
       <c r="P66" s="175"/>
       <c r="Q66" s="175"/>
     </row>
-    <row r="67" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:17" ht="15.75" customHeight="1">
       <c r="A67" s="10"/>
       <c r="B67" s="105" t="s">
         <v>157</v>
@@ -12413,7 +12402,7 @@
       <c r="P67" s="175"/>
       <c r="Q67" s="175"/>
     </row>
-    <row r="68" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:17" ht="15.75" customHeight="1">
       <c r="A68" s="10"/>
       <c r="B68" s="105" t="s">
         <v>158</v>
@@ -12438,7 +12427,7 @@
       <c r="P68" s="175"/>
       <c r="Q68" s="175"/>
     </row>
-    <row r="69" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:17" ht="15.75" customHeight="1">
       <c r="A69" s="10"/>
       <c r="B69" s="31" t="s">
         <v>194</v>
@@ -12465,10 +12454,10 @@
       <c r="P69" s="175"/>
       <c r="Q69" s="175"/>
     </row>
-    <row r="70" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:17" ht="15.75" customHeight="1">
       <c r="A70" s="10"/>
     </row>
-    <row r="71" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:17" ht="15.75" customHeight="1">
       <c r="A71" s="10"/>
       <c r="B71" s="54" t="s">
         <v>212</v>
@@ -12491,7 +12480,7 @@
       <c r="P71" s="37"/>
       <c r="Q71" s="37"/>
     </row>
-    <row r="72" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:17" ht="15.75" customHeight="1">
       <c r="A72" s="10"/>
       <c r="B72" s="72" t="s">
         <v>216</v>
@@ -12512,7 +12501,7 @@
       <c r="P72" s="12"/>
       <c r="Q72" s="12"/>
     </row>
-    <row r="73" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:17" ht="15.75" customHeight="1">
       <c r="A73" s="10"/>
       <c r="B73" s="2" t="s">
         <v>46</v>
@@ -12569,7 +12558,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:17" ht="15.75" customHeight="1">
       <c r="A74" s="10"/>
       <c r="B74" s="31" t="s">
         <v>48</v>
@@ -12626,7 +12615,7 @@
         <v/>
       </c>
     </row>
-    <row r="75" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:17" ht="15.75" customHeight="1">
       <c r="A75" s="10"/>
       <c r="B75" s="8" t="s">
         <v>45</v>
@@ -12683,7 +12672,7 @@
         <v/>
       </c>
     </row>
-    <row r="76" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:17" ht="15.75" customHeight="1">
       <c r="A76" s="10"/>
       <c r="B76" s="29" t="s">
         <v>152</v>
@@ -12740,7 +12729,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:17" ht="15.75" customHeight="1">
       <c r="A77" s="10"/>
       <c r="B77" s="2" t="s">
         <v>65</v>
@@ -12797,7 +12786,7 @@
         <v/>
       </c>
     </row>
-    <row r="78" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:17" ht="15.75" customHeight="1">
       <c r="A78" s="10"/>
       <c r="B78" s="2" t="s">
         <v>80</v>
@@ -12856,7 +12845,7 @@
         <v/>
       </c>
     </row>
-    <row r="79" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:17" ht="15.75" customHeight="1">
       <c r="A79" s="10"/>
       <c r="B79" s="31" t="s">
         <v>153</v>
@@ -12913,7 +12902,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:17" ht="15.75" customHeight="1">
       <c r="A80" s="10"/>
       <c r="B80" s="2" t="s">
         <v>68</v>
@@ -12970,7 +12959,7 @@
         <v/>
       </c>
     </row>
-    <row r="81" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:17" ht="15.75" customHeight="1">
       <c r="A81" s="10"/>
       <c r="B81" s="70" t="s">
         <v>164</v>
@@ -13027,7 +13016,7 @@
         <v/>
       </c>
     </row>
-    <row r="82" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:17" ht="15.75" customHeight="1">
       <c r="A82" s="10"/>
       <c r="B82" s="2" t="s">
         <v>63</v>
@@ -13084,7 +13073,7 @@
         <v/>
       </c>
     </row>
-    <row r="83" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:17" ht="15.75" customHeight="1">
       <c r="A83" s="10"/>
       <c r="B83" s="40" t="str">
         <f>B15</f>
@@ -13142,7 +13131,7 @@
         <v/>
       </c>
     </row>
-    <row r="84" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:17" ht="15.75" customHeight="1">
       <c r="A84" s="10"/>
       <c r="B84" s="41" t="s">
         <v>154</v>
@@ -13199,7 +13188,7 @@
         <v/>
       </c>
     </row>
-    <row r="85" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:17" ht="15.75" customHeight="1">
       <c r="A85" s="10"/>
       <c r="B85" s="27" t="s">
         <v>52</v>
@@ -13225,7 +13214,7 @@
       <c r="P85" s="226"/>
       <c r="Q85" s="226"/>
     </row>
-    <row r="86" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:17" ht="15.75" customHeight="1">
       <c r="A86" s="10"/>
       <c r="B86" s="8" t="s">
         <v>98</v>
@@ -13249,7 +13238,7 @@
       <c r="P86" s="169"/>
       <c r="Q86" s="169"/>
     </row>
-    <row r="87" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:17" ht="15.75" customHeight="1">
       <c r="A87" s="10"/>
       <c r="B87" s="31" t="s">
         <v>140</v>
@@ -13306,18 +13295,18 @@
         <v/>
       </c>
     </row>
-    <row r="88" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:17" ht="15.75" customHeight="1">
       <c r="A88" s="10"/>
       <c r="E88" s="268"/>
     </row>
-    <row r="89" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:17" ht="15.75" customHeight="1">
       <c r="A89" s="10"/>
       <c r="B89" s="64" t="s">
         <v>214</v>
       </c>
       <c r="E89" s="268"/>
     </row>
-    <row r="90" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:17" ht="15.75" customHeight="1">
       <c r="A90" s="10"/>
       <c r="B90" s="2" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
@@ -13373,7 +13362,7 @@
         <v/>
       </c>
     </row>
-    <row r="91" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:17" ht="15.75" customHeight="1">
       <c r="A91" s="10"/>
       <c r="B91" s="2" t="str">
         <f>"Dividend ("&amp;Market_currency&amp;")"</f>
@@ -13429,7 +13418,7 @@
         <v/>
       </c>
     </row>
-    <row r="92" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:17" ht="15.75" customHeight="1">
       <c r="A92" s="10"/>
       <c r="B92" s="2" t="s">
         <v>213</v>
@@ -13484,39 +13473,39 @@
         <v/>
       </c>
     </row>
-    <row r="93" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:17" ht="15.75" customHeight="1">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
         <v>309</v>
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>2.9563932002956397E-2</v>
+        <v>2.9873039581777446E-2</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>2.9563932002956397E-2</v>
+        <v>2.9873039581777446E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>2.9563932002956397E-2</v>
+        <v>2.9873039581777446E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>2.9563932002956397E-2</v>
+        <v>2.9873039581777446E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
-        <v>2.9563932002956397E-2</v>
+        <v>2.9873039581777446E-2</v>
       </c>
       <c r="K93" s="23">
         <f t="shared" si="39"/>
-        <v>1.4781966001478198E-2</v>
+        <v>1.4936519790888723E-2</v>
       </c>
       <c r="L93" s="23">
         <f t="shared" si="39"/>
-        <v>1.4781966001478198E-2</v>
+        <v>1.4936519790888723E-2</v>
       </c>
       <c r="M93" s="23">
         <f t="shared" si="39"/>
@@ -13539,11 +13528,11 @@
         <v/>
       </c>
     </row>
-    <row r="94" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:17" ht="15.75" customHeight="1">
       <c r="A94" s="10"/>
       <c r="E94" s="268"/>
     </row>
-    <row r="95" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:17" ht="15.75" customHeight="1">
       <c r="A95" s="10"/>
       <c r="B95" s="157" t="s">
         <v>84</v>
@@ -13564,7 +13553,7 @@
       <c r="P95" s="12"/>
       <c r="Q95" s="12"/>
     </row>
-    <row r="96" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:17" ht="15.75" customHeight="1">
       <c r="A96" s="10"/>
       <c r="B96" s="27" t="s">
         <v>144</v>
@@ -13621,7 +13610,7 @@
         <v/>
       </c>
     </row>
-    <row r="97" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="97" spans="1:17" ht="15.75" customHeight="1">
       <c r="A97" s="10"/>
       <c r="B97" s="70" t="s">
         <v>164</v>
@@ -13678,10 +13667,10 @@
         <v/>
       </c>
     </row>
-    <row r="98" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="98" spans="1:17" ht="15.75" customHeight="1">
       <c r="A98" s="10"/>
     </row>
-    <row r="99" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:17" ht="15.75" customHeight="1">
       <c r="A99" s="3"/>
       <c r="B99" s="54" t="s">
         <v>215</v>
@@ -13704,7 +13693,7 @@
       <c r="P99" s="37"/>
       <c r="Q99" s="37"/>
     </row>
-    <row r="100" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="100" spans="1:17" ht="15.75" customHeight="1">
       <c r="A100" s="10"/>
       <c r="B100" s="64" t="s">
         <v>28</v>
@@ -13714,7 +13703,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="101" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="101" spans="1:17" ht="15.75" customHeight="1">
       <c r="A101" s="10"/>
       <c r="B101" s="26" t="s">
         <v>3</v>
@@ -13771,7 +13760,7 @@
         <v/>
       </c>
     </row>
-    <row r="102" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="102" spans="1:17" ht="15.75" customHeight="1">
       <c r="A102" s="10"/>
       <c r="B102" s="93" t="s">
         <v>210</v>
@@ -13828,7 +13817,7 @@
         <v/>
       </c>
     </row>
-    <row r="103" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="103" spans="1:17" ht="15.75" customHeight="1">
       <c r="A103" s="10"/>
       <c r="B103" s="93" t="s">
         <v>211</v>
@@ -13885,7 +13874,7 @@
         <v/>
       </c>
     </row>
-    <row r="104" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="104" spans="1:17" ht="15.75" customHeight="1">
       <c r="A104" s="10"/>
       <c r="B104" s="26" t="s">
         <v>40</v>
@@ -13942,7 +13931,7 @@
         <v/>
       </c>
     </row>
-    <row r="105" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="105" spans="1:17" ht="15.75" customHeight="1">
       <c r="A105" s="10"/>
       <c r="B105" s="26" t="s">
         <v>30</v>
@@ -13999,11 +13988,11 @@
         <v/>
       </c>
     </row>
-    <row r="106" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="106" spans="1:17" ht="15.75" customHeight="1">
       <c r="A106" s="10"/>
       <c r="E106" s="268"/>
     </row>
-    <row r="107" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="107" spans="1:17" ht="15.75" customHeight="1">
       <c r="A107" s="10"/>
       <c r="B107" s="91" t="s">
         <v>220</v>
@@ -14026,7 +14015,7 @@
       <c r="P107" s="12"/>
       <c r="Q107" s="12"/>
     </row>
-    <row r="108" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="108" spans="1:17" ht="15.75" customHeight="1">
       <c r="A108" s="10"/>
       <c r="B108" s="26" t="s">
         <v>217</v>
@@ -14083,7 +14072,7 @@
         <v/>
       </c>
     </row>
-    <row r="109" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="109" spans="1:17" ht="15.75" customHeight="1">
       <c r="A109" s="10"/>
       <c r="B109" s="26" t="s">
         <v>218</v>
@@ -14140,7 +14129,7 @@
         <v/>
       </c>
     </row>
-    <row r="110" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="110" spans="1:17" ht="15.75" customHeight="1">
       <c r="A110" s="10"/>
       <c r="B110" s="26" t="s">
         <v>69</v>
@@ -14167,18 +14156,18 @@
       <c r="P110" s="204"/>
       <c r="Q110" s="204"/>
     </row>
-    <row r="111" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="111" spans="1:17" ht="15.75" customHeight="1">
       <c r="A111" s="10"/>
       <c r="E111" s="268"/>
     </row>
-    <row r="112" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="112" spans="1:17" ht="15.75" customHeight="1">
       <c r="A112" s="10"/>
       <c r="B112" s="64" t="s">
         <v>51</v>
       </c>
       <c r="E112" s="268"/>
     </row>
-    <row r="113" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:17" ht="15.75" customHeight="1">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
         <v>391</v>
@@ -14230,7 +14219,7 @@
         <v/>
       </c>
     </row>
-    <row r="114" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:17" ht="15.75" customHeight="1">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
         <v>392</v>
@@ -14282,11 +14271,11 @@
         <v/>
       </c>
     </row>
-    <row r="115" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="115" spans="1:17" ht="15.75" customHeight="1">
       <c r="A115" s="10"/>
       <c r="E115" s="268"/>
     </row>
-    <row r="116" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="116" spans="1:17" ht="15.75" customHeight="1">
       <c r="A116" s="10"/>
       <c r="B116" s="91" t="s">
         <v>38</v>
@@ -14340,7 +14329,7 @@
         <v/>
       </c>
     </row>
-    <row r="117" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="117" spans="1:17" ht="15.75" customHeight="1">
       <c r="A117" s="10"/>
       <c r="B117" s="7" t="s">
         <v>221</v>
@@ -14395,7 +14384,7 @@
         <v/>
       </c>
     </row>
-    <row r="118" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="118" spans="1:17" ht="15.75" customHeight="1">
       <c r="B118" s="7" t="s">
         <v>83</v>
       </c>
@@ -14449,7 +14438,7 @@
         <v/>
       </c>
     </row>
-    <row r="119" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="119" spans="1:17" ht="15.75" customHeight="1">
       <c r="B119" s="7" t="s">
         <v>91</v>
       </c>
@@ -14505,7 +14494,7 @@
         <v/>
       </c>
     </row>
-    <row r="120" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="120" spans="1:17" ht="15.75" customHeight="1">
       <c r="A120" s="10"/>
       <c r="B120" s="70" t="s">
         <v>222</v>
@@ -14562,7 +14551,7 @@
         <v/>
       </c>
     </row>
-    <row r="121" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="121" spans="1:17" ht="15.75" customHeight="1">
       <c r="A121" s="10"/>
       <c r="B121" s="27"/>
       <c r="C121" s="62"/>
@@ -14581,7 +14570,7 @@
       <c r="P121" s="12"/>
       <c r="Q121" s="12"/>
     </row>
-    <row r="122" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:17" ht="15.75" customHeight="1">
       <c r="A122" s="10"/>
       <c r="B122" s="54" t="s">
         <v>223</v>
@@ -14604,7 +14593,7 @@
       <c r="P122" s="37"/>
       <c r="Q122" s="37"/>
     </row>
-    <row r="123" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="123" spans="1:17" ht="15.75" customHeight="1">
       <c r="A123" s="10"/>
       <c r="B123" s="178" t="s">
         <v>170</v>
@@ -14625,7 +14614,7 @@
       <c r="P123" s="12"/>
       <c r="Q123" s="12"/>
     </row>
-    <row r="124" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="124" spans="1:17" ht="15.75" customHeight="1">
       <c r="A124" s="10"/>
       <c r="B124" s="27" t="str">
         <f>"FCFE per share ("&amp;Market_currency&amp;")"</f>
@@ -14683,795 +14672,795 @@
         <v/>
       </c>
     </row>
-    <row r="125" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="125" spans="1:17" ht="15.75" customHeight="1">
       <c r="A125" s="10"/>
       <c r="B125" s="27" t="s">
         <v>269</v>
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>3.2789369544086615E-2</v>
+        <v>3.3132200891074826E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>3.7363351034658238E-2</v>
+        <v>3.7754005937186398E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>4.9133626492865387E-2</v>
+        <v>4.9647346262021552E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>9.6638963417424423E-2</v>
+        <v>9.7649378270183149E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>6.2580111368585309E-2</v>
+        <v>6.323442171896633E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>4.6797239710954709E-2</v>
+        <v>4.7286531238925851E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>3.8878060661608281E-2</v>
+        <v>3.9284552707360712E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>2.7415335669294303E-2</v>
+        <v>2.7701978461953089E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>2.4922033380850604E-2</v>
+        <v>2.5182607292226187E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>1.6488695499840136E-2</v>
+        <v>1.6661094108501643E-2</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>1.6122373197667576E-2</v>
+        <v>1.6290941700107711E-2</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
         <v/>
       </c>
     </row>
-    <row r="126" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="126" spans="1:17" ht="15.75" customHeight="1">
       <c r="B126" s="2" t="s">
         <v>394</v>
       </c>
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.850333931665278E-2</v>
+        <v>4.9010469077991933E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.9531717569992086E-2</v>
+        <v>6.0154155244360928E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10691891313400056</v>
+        <v>0.10803681065743298</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.3915446330959427E-2</v>
+        <v>6.4583718361305525E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.5241865019201868E-2</v>
+        <v>4.5714894227767082E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.6649190795372627E-2</v>
+        <v>3.7032378749917223E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.6779333175569509E-2</v>
+        <v>2.7059326203544093E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.8640105353606405E-2</v>
+        <v>1.8834998165369276E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.6355863130878258E-2</v>
+        <v>1.6526872902224255E-2</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.4558738010673027E-2</v>
+        <v>1.4710957825571773E-2</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
         <v/>
       </c>
     </row>
-    <row r="127" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="128" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="127" spans="1:17" ht="15.75" customHeight="1"/>
+    <row r="128" spans="1:17" ht="15.75" customHeight="1"/>
+    <row r="129" ht="15.75" customHeight="1"/>
+    <row r="130" ht="15.75" customHeight="1"/>
+    <row r="131" ht="15.75" customHeight="1"/>
+    <row r="132" ht="15.75" customHeight="1"/>
+    <row r="133" ht="15.75" customHeight="1"/>
+    <row r="134" ht="15.75" customHeight="1"/>
+    <row r="135" ht="15.75" customHeight="1"/>
+    <row r="136" ht="15.75" customHeight="1"/>
+    <row r="137" ht="15.75" customHeight="1"/>
+    <row r="138" ht="15.75" customHeight="1"/>
+    <row r="139" ht="15.75" customHeight="1"/>
+    <row r="140" ht="15.75" customHeight="1"/>
+    <row r="141" ht="15.75" customHeight="1"/>
+    <row r="142" ht="15.75" customHeight="1"/>
+    <row r="143" ht="15.75" customHeight="1"/>
+    <row r="144" ht="15.75" customHeight="1"/>
+    <row r="145" ht="15.75" customHeight="1"/>
+    <row r="146" ht="15.75" customHeight="1"/>
+    <row r="147" ht="15.75" customHeight="1"/>
+    <row r="148" ht="15.75" customHeight="1"/>
+    <row r="149" ht="15.75" customHeight="1"/>
+    <row r="150" ht="15.75" customHeight="1"/>
+    <row r="151" ht="15.75" customHeight="1"/>
+    <row r="152" ht="15.75" customHeight="1"/>
+    <row r="153" ht="15.75" customHeight="1"/>
+    <row r="154" ht="15.75" customHeight="1"/>
+    <row r="155" ht="15.75" customHeight="1"/>
+    <row r="156" ht="15.75" customHeight="1"/>
+    <row r="157" ht="15.75" customHeight="1"/>
+    <row r="158" ht="15.75" customHeight="1"/>
+    <row r="159" ht="15.75" customHeight="1"/>
+    <row r="160" ht="15.75" customHeight="1"/>
+    <row r="161" ht="15.75" customHeight="1"/>
+    <row r="162" ht="15.75" customHeight="1"/>
+    <row r="163" ht="15.75" customHeight="1"/>
+    <row r="164" ht="15.75" customHeight="1"/>
+    <row r="165" ht="15.75" customHeight="1"/>
+    <row r="166" ht="15.75" customHeight="1"/>
+    <row r="167" ht="15.75" customHeight="1"/>
+    <row r="168" ht="15.75" customHeight="1"/>
+    <row r="169" ht="15.75" customHeight="1"/>
+    <row r="170" ht="15.75" customHeight="1"/>
+    <row r="171" ht="15.75" customHeight="1"/>
+    <row r="172" ht="15.75" customHeight="1"/>
+    <row r="173" ht="15.75" customHeight="1"/>
+    <row r="174" ht="15.75" customHeight="1"/>
+    <row r="175" ht="15.75" customHeight="1"/>
+    <row r="176" ht="15.75" customHeight="1"/>
+    <row r="177" ht="15.75" customHeight="1"/>
+    <row r="178" ht="15.75" customHeight="1"/>
+    <row r="179" ht="15.75" customHeight="1"/>
+    <row r="180" ht="15.75" customHeight="1"/>
+    <row r="181" ht="15.75" customHeight="1"/>
+    <row r="182" ht="15.75" customHeight="1"/>
+    <row r="183" ht="15.75" customHeight="1"/>
+    <row r="184" ht="15.75" customHeight="1"/>
+    <row r="185" ht="15.75" customHeight="1"/>
+    <row r="186" ht="15.75" customHeight="1"/>
+    <row r="187" ht="15.75" customHeight="1"/>
+    <row r="188" ht="15.75" customHeight="1"/>
+    <row r="189" ht="15.75" customHeight="1"/>
+    <row r="190" ht="15.75" customHeight="1"/>
+    <row r="191" ht="15.75" customHeight="1"/>
+    <row r="192" ht="15.75" customHeight="1"/>
+    <row r="193" ht="15.75" customHeight="1"/>
+    <row r="194" ht="15.75" customHeight="1"/>
+    <row r="195" ht="15.75" customHeight="1"/>
+    <row r="196" ht="15.75" customHeight="1"/>
+    <row r="197" ht="15.75" customHeight="1"/>
+    <row r="198" ht="15.75" customHeight="1"/>
+    <row r="199" ht="15.75" customHeight="1"/>
+    <row r="200" ht="15.75" customHeight="1"/>
+    <row r="201" ht="15.75" customHeight="1"/>
+    <row r="202" ht="15.75" customHeight="1"/>
+    <row r="203" ht="15.75" customHeight="1"/>
+    <row r="204" ht="15.75" customHeight="1"/>
+    <row r="205" ht="15.75" customHeight="1"/>
+    <row r="206" ht="15.75" customHeight="1"/>
+    <row r="207" ht="15.75" customHeight="1"/>
+    <row r="208" ht="15.75" customHeight="1"/>
+    <row r="209" ht="15.75" customHeight="1"/>
+    <row r="210" ht="15.75" customHeight="1"/>
+    <row r="211" ht="15.75" customHeight="1"/>
+    <row r="212" ht="15.75" customHeight="1"/>
+    <row r="213" ht="15.75" customHeight="1"/>
+    <row r="214" ht="15.75" customHeight="1"/>
+    <row r="215" ht="15.75" customHeight="1"/>
+    <row r="216" ht="15.75" customHeight="1"/>
+    <row r="217" ht="15.75" customHeight="1"/>
+    <row r="218" ht="15.75" customHeight="1"/>
+    <row r="219" ht="15.75" customHeight="1"/>
+    <row r="220" ht="15.75" customHeight="1"/>
+    <row r="221" ht="15.75" customHeight="1"/>
+    <row r="222" ht="15.75" customHeight="1"/>
+    <row r="223" ht="15.75" customHeight="1"/>
+    <row r="224" ht="15.75" customHeight="1"/>
+    <row r="225" ht="15.75" customHeight="1"/>
+    <row r="226" ht="15.75" customHeight="1"/>
+    <row r="227" ht="15.75" customHeight="1"/>
+    <row r="228" ht="15.75" customHeight="1"/>
+    <row r="229" ht="15.75" customHeight="1"/>
+    <row r="230" ht="15.75" customHeight="1"/>
+    <row r="231" ht="15.75" customHeight="1"/>
+    <row r="232" ht="15.75" customHeight="1"/>
+    <row r="233" ht="15.75" customHeight="1"/>
+    <row r="234" ht="15.75" customHeight="1"/>
+    <row r="235" ht="15.75" customHeight="1"/>
+    <row r="236" ht="15.75" customHeight="1"/>
+    <row r="237" ht="15.75" customHeight="1"/>
+    <row r="238" ht="15.75" customHeight="1"/>
+    <row r="239" ht="15.75" customHeight="1"/>
+    <row r="240" ht="15.75" customHeight="1"/>
+    <row r="241" ht="15.75" customHeight="1"/>
+    <row r="242" ht="15.75" customHeight="1"/>
+    <row r="243" ht="15.75" customHeight="1"/>
+    <row r="244" ht="15.75" customHeight="1"/>
+    <row r="245" ht="15.75" customHeight="1"/>
+    <row r="246" ht="15.75" customHeight="1"/>
+    <row r="247" ht="15.75" customHeight="1"/>
+    <row r="248" ht="15.75" customHeight="1"/>
+    <row r="249" ht="15.75" customHeight="1"/>
+    <row r="250" ht="15.75" customHeight="1"/>
+    <row r="251" ht="15.75" customHeight="1"/>
+    <row r="252" ht="15.75" customHeight="1"/>
+    <row r="253" ht="15.75" customHeight="1"/>
+    <row r="254" ht="15.75" customHeight="1"/>
+    <row r="255" ht="15.75" customHeight="1"/>
+    <row r="256" ht="15.75" customHeight="1"/>
+    <row r="257" ht="15.75" customHeight="1"/>
+    <row r="258" ht="15.75" customHeight="1"/>
+    <row r="259" ht="15.75" customHeight="1"/>
+    <row r="260" ht="15.75" customHeight="1"/>
+    <row r="261" ht="15.75" customHeight="1"/>
+    <row r="262" ht="15.75" customHeight="1"/>
+    <row r="263" ht="15.75" customHeight="1"/>
+    <row r="264" ht="15.75" customHeight="1"/>
+    <row r="265" ht="15.75" customHeight="1"/>
+    <row r="266" ht="15.75" customHeight="1"/>
+    <row r="267" ht="15.75" customHeight="1"/>
+    <row r="268" ht="15.75" customHeight="1"/>
+    <row r="269" ht="15.75" customHeight="1"/>
+    <row r="270" ht="15.75" customHeight="1"/>
+    <row r="271" ht="15.75" customHeight="1"/>
+    <row r="272" ht="15.75" customHeight="1"/>
+    <row r="273" ht="15.75" customHeight="1"/>
+    <row r="274" ht="15.75" customHeight="1"/>
+    <row r="275" ht="15.75" customHeight="1"/>
+    <row r="276" ht="15.75" customHeight="1"/>
+    <row r="277" ht="15.75" customHeight="1"/>
+    <row r="278" ht="15.75" customHeight="1"/>
+    <row r="279" ht="15.75" customHeight="1"/>
+    <row r="280" ht="15.75" customHeight="1"/>
+    <row r="281" ht="15.75" customHeight="1"/>
+    <row r="282" ht="15.75" customHeight="1"/>
+    <row r="283" ht="15.75" customHeight="1"/>
+    <row r="284" ht="15.75" customHeight="1"/>
+    <row r="285" ht="15.75" customHeight="1"/>
+    <row r="286" ht="15.75" customHeight="1"/>
+    <row r="287" ht="15.75" customHeight="1"/>
+    <row r="288" ht="15.75" customHeight="1"/>
+    <row r="289" ht="15.75" customHeight="1"/>
+    <row r="290" ht="15.75" customHeight="1"/>
+    <row r="291" ht="15.75" customHeight="1"/>
+    <row r="292" ht="15.75" customHeight="1"/>
+    <row r="293" ht="15.75" customHeight="1"/>
+    <row r="294" ht="15.75" customHeight="1"/>
+    <row r="295" ht="15.75" customHeight="1"/>
+    <row r="296" ht="15.75" customHeight="1"/>
+    <row r="297" ht="15.75" customHeight="1"/>
+    <row r="298" ht="15.75" customHeight="1"/>
+    <row r="299" ht="15.75" customHeight="1"/>
+    <row r="300" ht="15.75" customHeight="1"/>
+    <row r="301" ht="15.75" customHeight="1"/>
+    <row r="302" ht="15.75" customHeight="1"/>
+    <row r="303" ht="15.75" customHeight="1"/>
+    <row r="304" ht="15.75" customHeight="1"/>
+    <row r="305" ht="15.75" customHeight="1"/>
+    <row r="306" ht="15.75" customHeight="1"/>
+    <row r="307" ht="15.75" customHeight="1"/>
+    <row r="308" ht="15.75" customHeight="1"/>
+    <row r="309" ht="15.75" customHeight="1"/>
+    <row r="310" ht="15.75" customHeight="1"/>
+    <row r="311" ht="15.75" customHeight="1"/>
+    <row r="312" ht="15.75" customHeight="1"/>
+    <row r="313" ht="15.75" customHeight="1"/>
+    <row r="314" ht="15.75" customHeight="1"/>
+    <row r="315" ht="15.75" customHeight="1"/>
+    <row r="316" ht="15.75" customHeight="1"/>
+    <row r="317" ht="15.75" customHeight="1"/>
+    <row r="318" ht="15.75" customHeight="1"/>
+    <row r="319" ht="15.75" customHeight="1"/>
+    <row r="320" ht="15.75" customHeight="1"/>
+    <row r="321" ht="15.75" customHeight="1"/>
+    <row r="322" ht="15.75" customHeight="1"/>
+    <row r="323" ht="15.75" customHeight="1"/>
+    <row r="324" ht="15.75" customHeight="1"/>
+    <row r="325" ht="15.75" customHeight="1"/>
+    <row r="326" ht="15.75" customHeight="1"/>
+    <row r="327" ht="15.75" customHeight="1"/>
+    <row r="328" ht="15.75" customHeight="1"/>
+    <row r="329" ht="15.75" customHeight="1"/>
+    <row r="330" ht="15.75" customHeight="1"/>
+    <row r="331" ht="15.75" customHeight="1"/>
+    <row r="332" ht="15.75" customHeight="1"/>
+    <row r="333" ht="15.75" customHeight="1"/>
+    <row r="334" ht="15.75" customHeight="1"/>
+    <row r="335" ht="15.75" customHeight="1"/>
+    <row r="336" ht="15.75" customHeight="1"/>
+    <row r="337" ht="15.75" customHeight="1"/>
+    <row r="338" ht="15.75" customHeight="1"/>
+    <row r="339" ht="15.75" customHeight="1"/>
+    <row r="340" ht="15.75" customHeight="1"/>
+    <row r="341" ht="15.75" customHeight="1"/>
+    <row r="342" ht="15.75" customHeight="1"/>
+    <row r="343" ht="15.75" customHeight="1"/>
+    <row r="344" ht="15.75" customHeight="1"/>
+    <row r="345" ht="15.75" customHeight="1"/>
+    <row r="346" ht="15.75" customHeight="1"/>
+    <row r="347" ht="15.75" customHeight="1"/>
+    <row r="348" ht="15.75" customHeight="1"/>
+    <row r="349" ht="15.75" customHeight="1"/>
+    <row r="350" ht="15.75" customHeight="1"/>
+    <row r="351" ht="15.75" customHeight="1"/>
+    <row r="352" ht="15.75" customHeight="1"/>
+    <row r="353" ht="15.75" customHeight="1"/>
+    <row r="354" ht="15.75" customHeight="1"/>
+    <row r="355" ht="15.75" customHeight="1"/>
+    <row r="356" ht="15.75" customHeight="1"/>
+    <row r="357" ht="15.75" customHeight="1"/>
+    <row r="358" ht="15.75" customHeight="1"/>
+    <row r="359" ht="15.75" customHeight="1"/>
+    <row r="360" ht="15.75" customHeight="1"/>
+    <row r="361" ht="15.75" customHeight="1"/>
+    <row r="362" ht="15.75" customHeight="1"/>
+    <row r="363" ht="15.75" customHeight="1"/>
+    <row r="364" ht="15.75" customHeight="1"/>
+    <row r="365" ht="15.75" customHeight="1"/>
+    <row r="366" ht="15.75" customHeight="1"/>
+    <row r="367" ht="15.75" customHeight="1"/>
+    <row r="368" ht="15.75" customHeight="1"/>
+    <row r="369" ht="15.75" customHeight="1"/>
+    <row r="370" ht="15.75" customHeight="1"/>
+    <row r="371" ht="15.75" customHeight="1"/>
+    <row r="372" ht="15.75" customHeight="1"/>
+    <row r="373" ht="15.75" customHeight="1"/>
+    <row r="374" ht="15.75" customHeight="1"/>
+    <row r="375" ht="15.75" customHeight="1"/>
+    <row r="376" ht="15.75" customHeight="1"/>
+    <row r="377" ht="15.75" customHeight="1"/>
+    <row r="378" ht="15.75" customHeight="1"/>
+    <row r="379" ht="15.75" customHeight="1"/>
+    <row r="380" ht="15.75" customHeight="1"/>
+    <row r="381" ht="15.75" customHeight="1"/>
+    <row r="382" ht="15.75" customHeight="1"/>
+    <row r="383" ht="15.75" customHeight="1"/>
+    <row r="384" ht="15.75" customHeight="1"/>
+    <row r="385" ht="15.75" customHeight="1"/>
+    <row r="386" ht="15.75" customHeight="1"/>
+    <row r="387" ht="15.75" customHeight="1"/>
+    <row r="388" ht="15.75" customHeight="1"/>
+    <row r="389" ht="15.75" customHeight="1"/>
+    <row r="390" ht="15.75" customHeight="1"/>
+    <row r="391" ht="15.75" customHeight="1"/>
+    <row r="392" ht="15.75" customHeight="1"/>
+    <row r="393" ht="15.75" customHeight="1"/>
+    <row r="394" ht="15.75" customHeight="1"/>
+    <row r="395" ht="15.75" customHeight="1"/>
+    <row r="396" ht="15.75" customHeight="1"/>
+    <row r="397" ht="15.75" customHeight="1"/>
+    <row r="398" ht="15.75" customHeight="1"/>
+    <row r="399" ht="15.75" customHeight="1"/>
+    <row r="400" ht="15.75" customHeight="1"/>
+    <row r="401" ht="15.75" customHeight="1"/>
+    <row r="402" ht="15.75" customHeight="1"/>
+    <row r="403" ht="15.75" customHeight="1"/>
+    <row r="404" ht="15.75" customHeight="1"/>
+    <row r="405" ht="15.75" customHeight="1"/>
+    <row r="406" ht="15.75" customHeight="1"/>
+    <row r="407" ht="15.75" customHeight="1"/>
+    <row r="408" ht="15.75" customHeight="1"/>
+    <row r="409" ht="15.75" customHeight="1"/>
+    <row r="410" ht="15.75" customHeight="1"/>
+    <row r="411" ht="15.75" customHeight="1"/>
+    <row r="412" ht="15.75" customHeight="1"/>
+    <row r="413" ht="15.75" customHeight="1"/>
+    <row r="414" ht="15.75" customHeight="1"/>
+    <row r="415" ht="15.75" customHeight="1"/>
+    <row r="416" ht="15.75" customHeight="1"/>
+    <row r="417" ht="15.75" customHeight="1"/>
+    <row r="418" ht="15.75" customHeight="1"/>
+    <row r="419" ht="15.75" customHeight="1"/>
+    <row r="420" ht="15.75" customHeight="1"/>
+    <row r="421" ht="15.75" customHeight="1"/>
+    <row r="422" ht="15.75" customHeight="1"/>
+    <row r="423" ht="15.75" customHeight="1"/>
+    <row r="424" ht="15.75" customHeight="1"/>
+    <row r="425" ht="15.75" customHeight="1"/>
+    <row r="426" ht="15.75" customHeight="1"/>
+    <row r="427" ht="15.75" customHeight="1"/>
+    <row r="428" ht="15.75" customHeight="1"/>
+    <row r="429" ht="15.75" customHeight="1"/>
+    <row r="430" ht="15.75" customHeight="1"/>
+    <row r="431" ht="15.75" customHeight="1"/>
+    <row r="432" ht="15.75" customHeight="1"/>
+    <row r="433" ht="15.75" customHeight="1"/>
+    <row r="434" ht="15.75" customHeight="1"/>
+    <row r="435" ht="15.75" customHeight="1"/>
+    <row r="436" ht="15.75" customHeight="1"/>
+    <row r="437" ht="15.75" customHeight="1"/>
+    <row r="438" ht="15.75" customHeight="1"/>
+    <row r="439" ht="15.75" customHeight="1"/>
+    <row r="440" ht="15.75" customHeight="1"/>
+    <row r="441" ht="15.75" customHeight="1"/>
+    <row r="442" ht="15.75" customHeight="1"/>
+    <row r="443" ht="15.75" customHeight="1"/>
+    <row r="444" ht="15.75" customHeight="1"/>
+    <row r="445" ht="15.75" customHeight="1"/>
+    <row r="446" ht="15.75" customHeight="1"/>
+    <row r="447" ht="15.75" customHeight="1"/>
+    <row r="448" ht="15.75" customHeight="1"/>
+    <row r="449" ht="15.75" customHeight="1"/>
+    <row r="450" ht="15.75" customHeight="1"/>
+    <row r="451" ht="15.75" customHeight="1"/>
+    <row r="452" ht="15.75" customHeight="1"/>
+    <row r="453" ht="15.75" customHeight="1"/>
+    <row r="454" ht="15.75" customHeight="1"/>
+    <row r="455" ht="15.75" customHeight="1"/>
+    <row r="456" ht="15.75" customHeight="1"/>
+    <row r="457" ht="15.75" customHeight="1"/>
+    <row r="458" ht="15.75" customHeight="1"/>
+    <row r="459" ht="15.75" customHeight="1"/>
+    <row r="460" ht="15.75" customHeight="1"/>
+    <row r="461" ht="15.75" customHeight="1"/>
+    <row r="462" ht="15.75" customHeight="1"/>
+    <row r="463" ht="15.75" customHeight="1"/>
+    <row r="464" ht="15.75" customHeight="1"/>
+    <row r="465" ht="15.75" customHeight="1"/>
+    <row r="466" ht="15.75" customHeight="1"/>
+    <row r="467" ht="15.75" customHeight="1"/>
+    <row r="468" ht="15.75" customHeight="1"/>
+    <row r="469" ht="15.75" customHeight="1"/>
+    <row r="470" ht="15.75" customHeight="1"/>
+    <row r="471" ht="15.75" customHeight="1"/>
+    <row r="472" ht="15.75" customHeight="1"/>
+    <row r="473" ht="15.75" customHeight="1"/>
+    <row r="474" ht="15.75" customHeight="1"/>
+    <row r="475" ht="15.75" customHeight="1"/>
+    <row r="476" ht="15.75" customHeight="1"/>
+    <row r="477" ht="15.75" customHeight="1"/>
+    <row r="478" ht="15.75" customHeight="1"/>
+    <row r="479" ht="15.75" customHeight="1"/>
+    <row r="480" ht="15.75" customHeight="1"/>
+    <row r="481" ht="15.75" customHeight="1"/>
+    <row r="482" ht="15.75" customHeight="1"/>
+    <row r="483" ht="15.75" customHeight="1"/>
+    <row r="484" ht="15.75" customHeight="1"/>
+    <row r="485" ht="15.75" customHeight="1"/>
+    <row r="486" ht="15.75" customHeight="1"/>
+    <row r="487" ht="15.75" customHeight="1"/>
+    <row r="488" ht="15.75" customHeight="1"/>
+    <row r="489" ht="15.75" customHeight="1"/>
+    <row r="490" ht="15.75" customHeight="1"/>
+    <row r="491" ht="15.75" customHeight="1"/>
+    <row r="492" ht="15.75" customHeight="1"/>
+    <row r="493" ht="15.75" customHeight="1"/>
+    <row r="494" ht="15.75" customHeight="1"/>
+    <row r="495" ht="15.75" customHeight="1"/>
+    <row r="496" ht="15.75" customHeight="1"/>
+    <row r="497" ht="15.75" customHeight="1"/>
+    <row r="498" ht="15.75" customHeight="1"/>
+    <row r="499" ht="15.75" customHeight="1"/>
+    <row r="500" ht="15.75" customHeight="1"/>
+    <row r="501" ht="15.75" customHeight="1"/>
+    <row r="502" ht="15.75" customHeight="1"/>
+    <row r="503" ht="15.75" customHeight="1"/>
+    <row r="504" ht="15.75" customHeight="1"/>
+    <row r="505" ht="15.75" customHeight="1"/>
+    <row r="506" ht="15.75" customHeight="1"/>
+    <row r="507" ht="15.75" customHeight="1"/>
+    <row r="508" ht="15.75" customHeight="1"/>
+    <row r="509" ht="15.75" customHeight="1"/>
+    <row r="510" ht="15.75" customHeight="1"/>
+    <row r="511" ht="15.75" customHeight="1"/>
+    <row r="512" ht="15.75" customHeight="1"/>
+    <row r="513" ht="15.75" customHeight="1"/>
+    <row r="514" ht="15.75" customHeight="1"/>
+    <row r="515" ht="15.75" customHeight="1"/>
+    <row r="516" ht="15.75" customHeight="1"/>
+    <row r="517" ht="15.75" customHeight="1"/>
+    <row r="518" ht="15.75" customHeight="1"/>
+    <row r="519" ht="15.75" customHeight="1"/>
+    <row r="520" ht="15.75" customHeight="1"/>
+    <row r="521" ht="15.75" customHeight="1"/>
+    <row r="522" ht="15.75" customHeight="1"/>
+    <row r="523" ht="15.75" customHeight="1"/>
+    <row r="524" ht="15.75" customHeight="1"/>
+    <row r="525" ht="15.75" customHeight="1"/>
+    <row r="526" ht="15.75" customHeight="1"/>
+    <row r="527" ht="15.75" customHeight="1"/>
+    <row r="528" ht="15.75" customHeight="1"/>
+    <row r="529" ht="15.75" customHeight="1"/>
+    <row r="530" ht="15.75" customHeight="1"/>
+    <row r="531" ht="15.75" customHeight="1"/>
+    <row r="532" ht="15.75" customHeight="1"/>
+    <row r="533" ht="15.75" customHeight="1"/>
+    <row r="534" ht="15.75" customHeight="1"/>
+    <row r="535" ht="15.75" customHeight="1"/>
+    <row r="536" ht="15.75" customHeight="1"/>
+    <row r="537" ht="15.75" customHeight="1"/>
+    <row r="538" ht="15.75" customHeight="1"/>
+    <row r="539" ht="15.75" customHeight="1"/>
+    <row r="540" ht="15.75" customHeight="1"/>
+    <row r="541" ht="15.75" customHeight="1"/>
+    <row r="542" ht="15.75" customHeight="1"/>
+    <row r="543" ht="15.75" customHeight="1"/>
+    <row r="544" ht="15.75" customHeight="1"/>
+    <row r="545" ht="15.75" customHeight="1"/>
+    <row r="546" ht="15.75" customHeight="1"/>
+    <row r="547" ht="15.75" customHeight="1"/>
+    <row r="548" ht="15.75" customHeight="1"/>
+    <row r="549" ht="15.75" customHeight="1"/>
+    <row r="550" ht="15.75" customHeight="1"/>
+    <row r="551" ht="15.75" customHeight="1"/>
+    <row r="552" ht="15.75" customHeight="1"/>
+    <row r="553" ht="15.75" customHeight="1"/>
+    <row r="554" ht="15.75" customHeight="1"/>
+    <row r="555" ht="15.75" customHeight="1"/>
+    <row r="556" ht="15.75" customHeight="1"/>
+    <row r="557" ht="15.75" customHeight="1"/>
+    <row r="558" ht="15.75" customHeight="1"/>
+    <row r="559" ht="15.75" customHeight="1"/>
+    <row r="560" ht="15.75" customHeight="1"/>
+    <row r="561" ht="15.75" customHeight="1"/>
+    <row r="562" ht="15.75" customHeight="1"/>
+    <row r="563" ht="15.75" customHeight="1"/>
+    <row r="564" ht="15.75" customHeight="1"/>
+    <row r="565" ht="15.75" customHeight="1"/>
+    <row r="566" ht="15.75" customHeight="1"/>
+    <row r="567" ht="15.75" customHeight="1"/>
+    <row r="568" ht="15.75" customHeight="1"/>
+    <row r="569" ht="15.75" customHeight="1"/>
+    <row r="570" ht="15.75" customHeight="1"/>
+    <row r="571" ht="15.75" customHeight="1"/>
+    <row r="572" ht="15.75" customHeight="1"/>
+    <row r="573" ht="15.75" customHeight="1"/>
+    <row r="574" ht="15.75" customHeight="1"/>
+    <row r="575" ht="15.75" customHeight="1"/>
+    <row r="576" ht="15.75" customHeight="1"/>
+    <row r="577" ht="15.75" customHeight="1"/>
+    <row r="578" ht="15.75" customHeight="1"/>
+    <row r="579" ht="15.75" customHeight="1"/>
+    <row r="580" ht="15.75" customHeight="1"/>
+    <row r="581" ht="15.75" customHeight="1"/>
+    <row r="582" ht="15.75" customHeight="1"/>
+    <row r="583" ht="15.75" customHeight="1"/>
+    <row r="584" ht="15.75" customHeight="1"/>
+    <row r="585" ht="15.75" customHeight="1"/>
+    <row r="586" ht="15.75" customHeight="1"/>
+    <row r="587" ht="15.75" customHeight="1"/>
+    <row r="588" ht="15.75" customHeight="1"/>
+    <row r="589" ht="15.75" customHeight="1"/>
+    <row r="590" ht="15.75" customHeight="1"/>
+    <row r="591" ht="15.75" customHeight="1"/>
+    <row r="592" ht="15.75" customHeight="1"/>
+    <row r="593" ht="15.75" customHeight="1"/>
+    <row r="594" ht="15.75" customHeight="1"/>
+    <row r="595" ht="15.75" customHeight="1"/>
+    <row r="596" ht="15.75" customHeight="1"/>
+    <row r="597" ht="15.75" customHeight="1"/>
+    <row r="598" ht="15.75" customHeight="1"/>
+    <row r="599" ht="15.75" customHeight="1"/>
+    <row r="600" ht="15.75" customHeight="1"/>
+    <row r="601" ht="15.75" customHeight="1"/>
+    <row r="602" ht="15.75" customHeight="1"/>
+    <row r="603" ht="15.75" customHeight="1"/>
+    <row r="604" ht="15.75" customHeight="1"/>
+    <row r="605" ht="15.75" customHeight="1"/>
+    <row r="606" ht="15.75" customHeight="1"/>
+    <row r="607" ht="15.75" customHeight="1"/>
+    <row r="608" ht="15.75" customHeight="1"/>
+    <row r="609" ht="15.75" customHeight="1"/>
+    <row r="610" ht="15.75" customHeight="1"/>
+    <row r="611" ht="15.75" customHeight="1"/>
+    <row r="612" ht="15.75" customHeight="1"/>
+    <row r="613" ht="15.75" customHeight="1"/>
+    <row r="614" ht="15.75" customHeight="1"/>
+    <row r="615" ht="15.75" customHeight="1"/>
+    <row r="616" ht="15.75" customHeight="1"/>
+    <row r="617" ht="15.75" customHeight="1"/>
+    <row r="618" ht="15.75" customHeight="1"/>
+    <row r="619" ht="15.75" customHeight="1"/>
+    <row r="620" ht="15.75" customHeight="1"/>
+    <row r="621" ht="15.75" customHeight="1"/>
+    <row r="622" ht="15.75" customHeight="1"/>
+    <row r="623" ht="15.75" customHeight="1"/>
+    <row r="624" ht="15.75" customHeight="1"/>
+    <row r="625" ht="15.75" customHeight="1"/>
+    <row r="626" ht="15.75" customHeight="1"/>
+    <row r="627" ht="15.75" customHeight="1"/>
+    <row r="628" ht="15.75" customHeight="1"/>
+    <row r="629" ht="15.75" customHeight="1"/>
+    <row r="630" ht="15.75" customHeight="1"/>
+    <row r="631" ht="15.75" customHeight="1"/>
+    <row r="632" ht="15.75" customHeight="1"/>
+    <row r="633" ht="15.75" customHeight="1"/>
+    <row r="634" ht="15.75" customHeight="1"/>
+    <row r="635" ht="15.75" customHeight="1"/>
+    <row r="636" ht="15.75" customHeight="1"/>
+    <row r="637" ht="15.75" customHeight="1"/>
+    <row r="638" ht="15.75" customHeight="1"/>
+    <row r="639" ht="15.75" customHeight="1"/>
+    <row r="640" ht="15.75" customHeight="1"/>
+    <row r="641" ht="15.75" customHeight="1"/>
+    <row r="642" ht="15.75" customHeight="1"/>
+    <row r="643" ht="15.75" customHeight="1"/>
+    <row r="644" ht="15.75" customHeight="1"/>
+    <row r="645" ht="15.75" customHeight="1"/>
+    <row r="646" ht="15.75" customHeight="1"/>
+    <row r="647" ht="15.75" customHeight="1"/>
+    <row r="648" ht="15.75" customHeight="1"/>
+    <row r="649" ht="15.75" customHeight="1"/>
+    <row r="650" ht="15.75" customHeight="1"/>
+    <row r="651" ht="15.75" customHeight="1"/>
+    <row r="652" ht="15.75" customHeight="1"/>
+    <row r="653" ht="15.75" customHeight="1"/>
+    <row r="654" ht="15.75" customHeight="1"/>
+    <row r="655" ht="15.75" customHeight="1"/>
+    <row r="656" ht="15.75" customHeight="1"/>
+    <row r="657" ht="15.75" customHeight="1"/>
+    <row r="658" ht="15.75" customHeight="1"/>
+    <row r="659" ht="15.75" customHeight="1"/>
+    <row r="660" ht="15.75" customHeight="1"/>
+    <row r="661" ht="15.75" customHeight="1"/>
+    <row r="662" ht="15.75" customHeight="1"/>
+    <row r="663" ht="15.75" customHeight="1"/>
+    <row r="664" ht="15.75" customHeight="1"/>
+    <row r="665" ht="15.75" customHeight="1"/>
+    <row r="666" ht="15.75" customHeight="1"/>
+    <row r="667" ht="15.75" customHeight="1"/>
+    <row r="668" ht="15.75" customHeight="1"/>
+    <row r="669" ht="15.75" customHeight="1"/>
+    <row r="670" ht="15.75" customHeight="1"/>
+    <row r="671" ht="15.75" customHeight="1"/>
+    <row r="672" ht="15.75" customHeight="1"/>
+    <row r="673" ht="15.75" customHeight="1"/>
+    <row r="674" ht="15.75" customHeight="1"/>
+    <row r="675" ht="15.75" customHeight="1"/>
+    <row r="676" ht="15.75" customHeight="1"/>
+    <row r="677" ht="15.75" customHeight="1"/>
+    <row r="678" ht="15.75" customHeight="1"/>
+    <row r="679" ht="15.75" customHeight="1"/>
+    <row r="680" ht="15.75" customHeight="1"/>
+    <row r="681" ht="15.75" customHeight="1"/>
+    <row r="682" ht="15.75" customHeight="1"/>
+    <row r="683" ht="15.75" customHeight="1"/>
+    <row r="684" ht="15.75" customHeight="1"/>
+    <row r="685" ht="15.75" customHeight="1"/>
+    <row r="686" ht="15.75" customHeight="1"/>
+    <row r="687" ht="15.75" customHeight="1"/>
+    <row r="688" ht="15.75" customHeight="1"/>
+    <row r="689" ht="15.75" customHeight="1"/>
+    <row r="690" ht="15.75" customHeight="1"/>
+    <row r="691" ht="15.75" customHeight="1"/>
+    <row r="692" ht="15.75" customHeight="1"/>
+    <row r="693" ht="15.75" customHeight="1"/>
+    <row r="694" ht="15.75" customHeight="1"/>
+    <row r="695" ht="15.75" customHeight="1"/>
+    <row r="696" ht="15.75" customHeight="1"/>
+    <row r="697" ht="15.75" customHeight="1"/>
+    <row r="698" ht="15.75" customHeight="1"/>
+    <row r="699" ht="15.75" customHeight="1"/>
+    <row r="700" ht="15.75" customHeight="1"/>
+    <row r="701" ht="15.75" customHeight="1"/>
+    <row r="702" ht="15.75" customHeight="1"/>
+    <row r="703" ht="15.75" customHeight="1"/>
+    <row r="704" ht="15.75" customHeight="1"/>
+    <row r="705" ht="15.75" customHeight="1"/>
+    <row r="706" ht="15.75" customHeight="1"/>
+    <row r="707" ht="15.75" customHeight="1"/>
+    <row r="708" ht="15.75" customHeight="1"/>
+    <row r="709" ht="15.75" customHeight="1"/>
+    <row r="710" ht="15.75" customHeight="1"/>
+    <row r="711" ht="15.75" customHeight="1"/>
+    <row r="712" ht="15.75" customHeight="1"/>
+    <row r="713" ht="15.75" customHeight="1"/>
+    <row r="714" ht="15.75" customHeight="1"/>
+    <row r="715" ht="15.75" customHeight="1"/>
+    <row r="716" ht="15.75" customHeight="1"/>
+    <row r="717" ht="15.75" customHeight="1"/>
+    <row r="718" ht="15.75" customHeight="1"/>
+    <row r="719" ht="15.75" customHeight="1"/>
+    <row r="720" ht="15.75" customHeight="1"/>
+    <row r="721" ht="15.75" customHeight="1"/>
+    <row r="722" ht="15.75" customHeight="1"/>
+    <row r="723" ht="15.75" customHeight="1"/>
+    <row r="724" ht="15.75" customHeight="1"/>
+    <row r="725" ht="15.75" customHeight="1"/>
+    <row r="726" ht="15.75" customHeight="1"/>
+    <row r="727" ht="15.75" customHeight="1"/>
+    <row r="728" ht="15.75" customHeight="1"/>
+    <row r="729" ht="15.75" customHeight="1"/>
+    <row r="730" ht="15.75" customHeight="1"/>
+    <row r="731" ht="15.75" customHeight="1"/>
+    <row r="732" ht="15.75" customHeight="1"/>
+    <row r="733" ht="15.75" customHeight="1"/>
+    <row r="734" ht="15.75" customHeight="1"/>
+    <row r="735" ht="15.75" customHeight="1"/>
+    <row r="736" ht="15.75" customHeight="1"/>
+    <row r="737" ht="15.75" customHeight="1"/>
+    <row r="738" ht="15.75" customHeight="1"/>
+    <row r="739" ht="15.75" customHeight="1"/>
+    <row r="740" ht="15.75" customHeight="1"/>
+    <row r="741" ht="15.75" customHeight="1"/>
+    <row r="742" ht="15.75" customHeight="1"/>
+    <row r="743" ht="15.75" customHeight="1"/>
+    <row r="744" ht="15.75" customHeight="1"/>
+    <row r="745" ht="15.75" customHeight="1"/>
+    <row r="746" ht="15.75" customHeight="1"/>
+    <row r="747" ht="15.75" customHeight="1"/>
+    <row r="748" ht="15.75" customHeight="1"/>
+    <row r="749" ht="15.75" customHeight="1"/>
+    <row r="750" ht="15.75" customHeight="1"/>
+    <row r="751" ht="15.75" customHeight="1"/>
+    <row r="752" ht="15.75" customHeight="1"/>
+    <row r="753" ht="15.75" customHeight="1"/>
+    <row r="754" ht="15.75" customHeight="1"/>
+    <row r="755" ht="15.75" customHeight="1"/>
+    <row r="756" ht="15.75" customHeight="1"/>
+    <row r="757" ht="15.75" customHeight="1"/>
+    <row r="758" ht="15.75" customHeight="1"/>
+    <row r="759" ht="15.75" customHeight="1"/>
+    <row r="760" ht="15.75" customHeight="1"/>
+    <row r="761" ht="15.75" customHeight="1"/>
+    <row r="762" ht="15.75" customHeight="1"/>
+    <row r="763" ht="15.75" customHeight="1"/>
+    <row r="764" ht="15.75" customHeight="1"/>
+    <row r="765" ht="15.75" customHeight="1"/>
+    <row r="766" ht="15.75" customHeight="1"/>
+    <row r="767" ht="15.75" customHeight="1"/>
+    <row r="768" ht="15.75" customHeight="1"/>
+    <row r="769" ht="15.75" customHeight="1"/>
+    <row r="770" ht="15.75" customHeight="1"/>
+    <row r="771" ht="15.75" customHeight="1"/>
+    <row r="772" ht="15.75" customHeight="1"/>
+    <row r="773" ht="15.75" customHeight="1"/>
+    <row r="774" ht="15.75" customHeight="1"/>
+    <row r="775" ht="15.75" customHeight="1"/>
+    <row r="776" ht="15.75" customHeight="1"/>
+    <row r="777" ht="15.75" customHeight="1"/>
+    <row r="778" ht="15.75" customHeight="1"/>
+    <row r="779" ht="15.75" customHeight="1"/>
+    <row r="780" ht="15.75" customHeight="1"/>
+    <row r="781" ht="15.75" customHeight="1"/>
+    <row r="782" ht="15.75" customHeight="1"/>
+    <row r="783" ht="15.75" customHeight="1"/>
+    <row r="784" ht="15.75" customHeight="1"/>
+    <row r="785" ht="15.75" customHeight="1"/>
+    <row r="786" ht="15.75" customHeight="1"/>
+    <row r="787" ht="15.75" customHeight="1"/>
+    <row r="788" ht="15.75" customHeight="1"/>
+    <row r="789" ht="15.75" customHeight="1"/>
+    <row r="790" ht="15.75" customHeight="1"/>
+    <row r="791" ht="15.75" customHeight="1"/>
+    <row r="792" ht="15.75" customHeight="1"/>
+    <row r="793" ht="15.75" customHeight="1"/>
+    <row r="794" ht="15.75" customHeight="1"/>
+    <row r="795" ht="15.75" customHeight="1"/>
+    <row r="796" ht="15.75" customHeight="1"/>
+    <row r="797" ht="15.75" customHeight="1"/>
+    <row r="798" ht="15.75" customHeight="1"/>
+    <row r="799" ht="15.75" customHeight="1"/>
+    <row r="800" ht="15.75" customHeight="1"/>
+    <row r="801" ht="15.75" customHeight="1"/>
+    <row r="802" ht="15.75" customHeight="1"/>
+    <row r="803" ht="15.75" customHeight="1"/>
+    <row r="804" ht="15.75" customHeight="1"/>
+    <row r="805" ht="15.75" customHeight="1"/>
+    <row r="806" ht="15.75" customHeight="1"/>
+    <row r="807" ht="15.75" customHeight="1"/>
+    <row r="808" ht="15.75" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="G4:Q13 G15:Q16 G23:Q24 G34:Q34">
@@ -15493,16 +15482,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:Q105"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="6.1640625" customWidth="1"/>
+    <col min="1" max="1" width="6.1328125" customWidth="1"/>
     <col min="2" max="2" width="24.6640625" customWidth="1"/>
     <col min="3" max="6" width="20.6640625" customWidth="1"/>
     <col min="7" max="7" width="5.6640625" customWidth="1"/>
-    <col min="8" max="8" width="56.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="56.796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:8" ht="13.9">
       <c r="B2" s="36" t="s">
         <v>55</v>
       </c>
@@ -15514,7 +15503,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:8" ht="13.15">
       <c r="B3" s="109" t="s">
         <v>163</v>
       </c>
@@ -15527,7 +15516,7 @@
       </c>
       <c r="H3" s="120"/>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:8">
       <c r="B4" s="100" t="s">
         <v>128</v>
       </c>
@@ -15548,7 +15537,7 @@
       </c>
       <c r="H4" s="120"/>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:8">
       <c r="B5" s="205" t="s">
         <v>123</v>
       </c>
@@ -15559,7 +15548,7 @@
       <c r="E5" s="148"/>
       <c r="H5" s="120"/>
     </row>
-    <row r="6" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:8" ht="13.25" customHeight="1">
       <c r="B6" s="149" t="s">
         <v>228</v>
       </c>
@@ -15577,7 +15566,7 @@
       <c r="F6" s="364"/>
       <c r="H6" s="120"/>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:8">
       <c r="B7" s="148" t="s">
         <v>224</v>
       </c>
@@ -15593,7 +15582,7 @@
       <c r="F7" s="364"/>
       <c r="H7" s="120"/>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:8">
       <c r="B8" s="148" t="s">
         <v>225</v>
       </c>
@@ -15609,7 +15598,7 @@
       <c r="F8" s="364"/>
       <c r="H8" s="120"/>
     </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:8">
       <c r="B9" s="205" t="s">
         <v>190</v>
       </c>
@@ -15625,7 +15614,7 @@
       <c r="F9" s="364"/>
       <c r="H9" s="120"/>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:8" ht="13.15">
       <c r="B10" s="149" t="s">
         <v>227</v>
       </c>
@@ -15639,7 +15628,7 @@
       </c>
       <c r="H10" s="120"/>
     </row>
-    <row r="11" spans="2:8" ht="14" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:8" ht="13.15" thickBot="1">
       <c r="B11" s="207" t="s">
         <v>166</v>
       </c>
@@ -15653,7 +15642,7 @@
       </c>
       <c r="H11" s="120"/>
     </row>
-    <row r="12" spans="2:8" ht="14" thickTop="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:8" ht="13.5" thickTop="1">
       <c r="B12" s="149" t="s">
         <v>102</v>
       </c>
@@ -15667,10 +15656,10 @@
       </c>
       <c r="H12" s="120"/>
     </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:8">
       <c r="H13" s="120"/>
     </row>
-    <row r="14" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:8" ht="13.9">
       <c r="B14" s="36" t="s">
         <v>229</v>
       </c>
@@ -15680,13 +15669,13 @@
       <c r="F14" s="37"/>
       <c r="H14" s="120"/>
     </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:8" ht="13.15">
       <c r="B15" s="119" t="s">
         <v>135</v>
       </c>
       <c r="H15" s="120"/>
     </row>
-    <row r="16" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:8" ht="13.25" customHeight="1">
       <c r="B16" s="152" t="s">
         <v>133</v>
       </c>
@@ -15696,7 +15685,7 @@
       </c>
       <c r="H16" s="120"/>
     </row>
-    <row r="17" spans="2:17" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:17" ht="13.25" customHeight="1">
       <c r="B17" s="118" t="s">
         <v>134</v>
       </c>
@@ -15706,7 +15695,7 @@
       </c>
       <c r="H17" s="120"/>
     </row>
-    <row r="18" spans="2:17" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:17" ht="13.25" customHeight="1">
       <c r="B18" s="153" t="s">
         <v>106</v>
       </c>
@@ -15720,10 +15709,10 @@
       </c>
       <c r="H18" s="120"/>
     </row>
-    <row r="19" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:17">
       <c r="H19" s="120"/>
     </row>
-    <row r="20" spans="2:17" ht="14" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:17" ht="13.15">
       <c r="B20" s="128" t="s">
         <v>107</v>
       </c>
@@ -15741,7 +15730,7 @@
       </c>
       <c r="H20" s="120"/>
     </row>
-    <row r="21" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:17">
       <c r="B21" s="122">
         <v>1</v>
       </c>
@@ -15763,7 +15752,7 @@
       </c>
       <c r="H21" s="120"/>
     </row>
-    <row r="22" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:17">
       <c r="B22" s="122">
         <v>2</v>
       </c>
@@ -15785,7 +15774,7 @@
       </c>
       <c r="H22" s="120"/>
     </row>
-    <row r="23" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:17">
       <c r="B23" s="122">
         <v>3</v>
       </c>
@@ -15817,7 +15806,7 @@
       <c r="P23" s="338"/>
       <c r="Q23" s="338"/>
     </row>
-    <row r="24" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:17">
       <c r="B24" s="122">
         <v>4</v>
       </c>
@@ -15849,7 +15838,7 @@
       <c r="P24" s="338"/>
       <c r="Q24" s="338"/>
     </row>
-    <row r="25" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:17">
       <c r="B25" s="122">
         <v>5</v>
       </c>
@@ -15881,7 +15870,7 @@
       <c r="P25" s="338"/>
       <c r="Q25" s="338"/>
     </row>
-    <row r="26" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:17">
       <c r="B26" s="122">
         <v>6</v>
       </c>
@@ -15903,7 +15892,7 @@
       </c>
       <c r="H26" s="120"/>
     </row>
-    <row r="27" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:17">
       <c r="B27" s="122">
         <v>7</v>
       </c>
@@ -15925,7 +15914,7 @@
       </c>
       <c r="H27" s="120"/>
     </row>
-    <row r="28" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:17">
       <c r="B28" s="122">
         <v>8</v>
       </c>
@@ -15947,7 +15936,7 @@
       </c>
       <c r="H28" s="120"/>
     </row>
-    <row r="29" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:17">
       <c r="B29" s="122">
         <v>9</v>
       </c>
@@ -15969,7 +15958,7 @@
       </c>
       <c r="H29" s="120"/>
     </row>
-    <row r="30" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:17">
       <c r="B30" s="122">
         <v>10</v>
       </c>
@@ -15991,7 +15980,7 @@
       </c>
       <c r="H30" s="120"/>
     </row>
-    <row r="31" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:17">
       <c r="B31" s="122">
         <v>11</v>
       </c>
@@ -16013,7 +16002,7 @@
       </c>
       <c r="H31" s="120"/>
     </row>
-    <row r="32" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:17">
       <c r="B32" s="122">
         <v>12</v>
       </c>
@@ -16035,7 +16024,7 @@
       </c>
       <c r="H32" s="120"/>
     </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:17">
       <c r="B33" s="122">
         <v>13</v>
       </c>
@@ -16067,7 +16056,7 @@
       <c r="P33" s="338"/>
       <c r="Q33" s="338"/>
     </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:17">
       <c r="B34" s="122">
         <v>14</v>
       </c>
@@ -16099,7 +16088,7 @@
       <c r="P34" s="338"/>
       <c r="Q34" s="338"/>
     </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:17">
       <c r="B35" s="122">
         <v>15</v>
       </c>
@@ -16131,7 +16120,7 @@
       <c r="P35" s="338"/>
       <c r="Q35" s="338"/>
     </row>
-    <row r="36" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:17">
       <c r="B36" s="122">
         <v>16</v>
       </c>
@@ -16153,7 +16142,7 @@
       </c>
       <c r="H36" s="120"/>
     </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:17">
       <c r="B37" s="122">
         <v>17</v>
       </c>
@@ -16175,7 +16164,7 @@
       </c>
       <c r="H37" s="120"/>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:17">
       <c r="B38" s="122">
         <v>18</v>
       </c>
@@ -16197,7 +16186,7 @@
       </c>
       <c r="H38" s="120"/>
     </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:17">
       <c r="B39" s="122">
         <v>19</v>
       </c>
@@ -16219,7 +16208,7 @@
       </c>
       <c r="H39" s="120"/>
     </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:17">
       <c r="B40" s="122">
         <v>20</v>
       </c>
@@ -16241,7 +16230,7 @@
       </c>
       <c r="H40" s="120"/>
     </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:17">
       <c r="B41" s="122">
         <v>21</v>
       </c>
@@ -16263,7 +16252,7 @@
       </c>
       <c r="H41" s="120"/>
     </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:17">
       <c r="B42" s="122">
         <v>22</v>
       </c>
@@ -16285,7 +16274,7 @@
       </c>
       <c r="H42" s="120"/>
     </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="43" spans="2:17">
       <c r="B43" s="122">
         <v>23</v>
       </c>
@@ -16307,7 +16296,7 @@
       </c>
       <c r="H43" s="120"/>
     </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:17">
       <c r="B44" s="122">
         <v>24</v>
       </c>
@@ -16329,7 +16318,7 @@
       </c>
       <c r="H44" s="120"/>
     </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:17">
       <c r="B45" s="122">
         <v>25</v>
       </c>
@@ -16351,7 +16340,7 @@
       </c>
       <c r="H45" s="120"/>
     </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:17">
       <c r="B46" s="122">
         <v>26</v>
       </c>
@@ -16373,7 +16362,7 @@
       </c>
       <c r="H46" s="120"/>
     </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:17">
       <c r="B47" s="122">
         <v>27</v>
       </c>
@@ -16405,7 +16394,7 @@
       <c r="P47" s="338"/>
       <c r="Q47" s="338"/>
     </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:17">
       <c r="B48" s="122">
         <v>28</v>
       </c>
@@ -16437,7 +16426,7 @@
       <c r="P48" s="338"/>
       <c r="Q48" s="338"/>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:17">
       <c r="B49" s="122">
         <v>29</v>
       </c>
@@ -16469,7 +16458,7 @@
       <c r="P49" s="338"/>
       <c r="Q49" s="338"/>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:17">
       <c r="B50" s="122">
         <v>30</v>
       </c>
@@ -16501,7 +16490,7 @@
       <c r="P50" s="338"/>
       <c r="Q50" s="338"/>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:17">
       <c r="B51" s="126" t="s">
         <v>131</v>
       </c>
@@ -16523,7 +16512,7 @@
       </c>
       <c r="H51" s="120"/>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:17">
       <c r="C52" s="114"/>
       <c r="E52" s="127" t="s">
         <v>100</v>
@@ -16534,11 +16523,11 @@
       </c>
       <c r="H52" s="120"/>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:17">
       <c r="C53" s="114"/>
       <c r="H53" s="120"/>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:17" ht="13.15">
       <c r="B54" s="119" t="s">
         <v>129</v>
       </c>
@@ -16548,7 +16537,7 @@
       <c r="F54" s="117"/>
       <c r="H54" s="120"/>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:17" ht="13.15">
       <c r="A55" s="133">
         <f>F52</f>
         <v>2297163804.1938334</v>
@@ -16575,7 +16564,7 @@
       </c>
       <c r="H55" s="120"/>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:17" ht="13.15">
       <c r="A56" s="143">
         <v>5</v>
       </c>
@@ -16597,7 +16586,7 @@
       </c>
       <c r="H56" s="120"/>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:17" ht="13.15">
       <c r="A57" s="143">
         <v>10</v>
       </c>
@@ -16618,7 +16607,7 @@
       </c>
       <c r="H57" s="120"/>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:17" ht="13.15">
       <c r="A58" s="143">
         <v>15</v>
       </c>
@@ -16649,7 +16638,7 @@
       <c r="P58" s="338"/>
       <c r="Q58" s="338"/>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:17" ht="13.15">
       <c r="A59" s="144">
         <v>20</v>
       </c>
@@ -16680,7 +16669,7 @@
       <c r="P59" s="338"/>
       <c r="Q59" s="338"/>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:17" ht="13.15">
       <c r="A60" s="144">
         <v>25</v>
       </c>
@@ -16711,7 +16700,7 @@
       <c r="P60" s="338"/>
       <c r="Q60" s="338"/>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:17" ht="13.15">
       <c r="A61" s="144">
         <v>30</v>
       </c>
@@ -16742,7 +16731,7 @@
       <c r="P61" s="338"/>
       <c r="Q61" s="338"/>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:17">
       <c r="C62" s="338"/>
       <c r="D62" s="114"/>
       <c r="E62" s="114"/>
@@ -16759,7 +16748,7 @@
       <c r="P62" s="338"/>
       <c r="Q62" s="338"/>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:17" ht="13.15">
       <c r="B63" s="119" t="s">
         <v>130</v>
       </c>
@@ -16779,7 +16768,7 @@
       <c r="P63" s="338"/>
       <c r="Q63" s="338"/>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:17" ht="13.15">
       <c r="B64" s="132">
         <f>B55</f>
         <v>0</v>
@@ -16802,7 +16791,7 @@
       </c>
       <c r="H64" s="120"/>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:8" ht="13.15">
       <c r="A65" s="143">
         <v>0</v>
       </c>
@@ -16828,7 +16817,7 @@
       </c>
       <c r="H65" s="120"/>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:8" ht="13.15">
       <c r="A66" s="143">
         <f t="shared" ref="A66:A71" si="3">A56</f>
         <v>5</v>
@@ -16855,7 +16844,7 @@
       </c>
       <c r="H66" s="120"/>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:8" ht="13.15">
       <c r="A67" s="143">
         <f t="shared" si="3"/>
         <v>10</v>
@@ -16882,7 +16871,7 @@
       </c>
       <c r="H67" s="120"/>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:8" ht="13.15">
       <c r="A68" s="143">
         <f t="shared" si="3"/>
         <v>15</v>
@@ -16909,7 +16898,7 @@
       </c>
       <c r="H68" s="120"/>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:8" ht="13.15">
       <c r="A69" s="144">
         <f t="shared" si="3"/>
         <v>20</v>
@@ -16936,7 +16925,7 @@
       </c>
       <c r="H69" s="120"/>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:8" ht="13.15">
       <c r="A70" s="144">
         <f t="shared" si="3"/>
         <v>25</v>
@@ -16962,7 +16951,7 @@
         <v>18.484891740531104</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:8" ht="13.15">
       <c r="A71" s="144">
         <f t="shared" si="3"/>
         <v>30</v>
@@ -16988,7 +16977,7 @@
         <v>21.759650934539629</v>
       </c>
     </row>
-    <row r="73" spans="1:8" ht="14" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:8" ht="13.15">
       <c r="B73" s="171" t="s">
         <v>117</v>
       </c>
@@ -17005,7 +16994,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:8">
       <c r="B74" s="127" t="str">
         <f>Scenarios!B54</f>
         <v>Snowball Scenario</v>
@@ -17027,7 +17016,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:8">
       <c r="B75" s="127" t="str">
         <f>Scenarios!B36</f>
         <v>Optimistic</v>
@@ -17050,7 +17039,7 @@
       </c>
       <c r="H75" s="120"/>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:8">
       <c r="B76" s="127" t="str">
         <f>Scenarios!B24</f>
         <v>Base</v>
@@ -17073,7 +17062,7 @@
       </c>
       <c r="H76" s="120"/>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:8">
       <c r="B77" s="127" t="str">
         <f>Scenarios!B30</f>
         <v>Pessimistic</v>
@@ -17096,7 +17085,7 @@
       </c>
       <c r="H77" s="120"/>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:8">
       <c r="B78" s="127" t="str">
         <f>Scenarios!B48</f>
         <v>Devil's advocate</v>
@@ -17118,14 +17107,14 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:8">
       <c r="B79" s="155"/>
       <c r="C79" s="155"/>
       <c r="D79" s="155"/>
       <c r="E79" s="155"/>
       <c r="F79" s="156"/>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:8">
       <c r="B80" s="155" t="s">
         <v>310</v>
       </c>
@@ -17133,26 +17122,26 @@
         <v>105</v>
       </c>
     </row>
-    <row r="81" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="81" spans="3:3">
       <c r="C81" s="155" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="82" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="82" spans="3:3">
       <c r="C82" s="155" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="92" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="92" spans="3:3">
       <c r="C92" s="115"/>
     </row>
-    <row r="93" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="93" spans="3:3">
       <c r="C93" s="115"/>
     </row>
-    <row r="94" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="94" spans="3:3">
       <c r="C94" s="115"/>
     </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.15">
+    <row r="101" spans="3:17">
       <c r="C101" s="338"/>
       <c r="G101" s="338"/>
       <c r="H101" s="338"/>
@@ -17166,7 +17155,7 @@
       <c r="P101" s="338"/>
       <c r="Q101" s="338"/>
     </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.15">
+    <row r="102" spans="3:17">
       <c r="C102" s="338"/>
       <c r="G102" s="338"/>
       <c r="H102" s="338"/>
@@ -17180,7 +17169,7 @@
       <c r="P102" s="338"/>
       <c r="Q102" s="338"/>
     </row>
-    <row r="103" spans="3:17" x14ac:dyDescent="0.15">
+    <row r="103" spans="3:17">
       <c r="C103" s="338"/>
       <c r="G103" s="338"/>
       <c r="H103" s="338"/>
@@ -17194,7 +17183,7 @@
       <c r="P103" s="338"/>
       <c r="Q103" s="338"/>
     </row>
-    <row r="104" spans="3:17" x14ac:dyDescent="0.15">
+    <row r="104" spans="3:17">
       <c r="C104" s="338"/>
       <c r="G104" s="338"/>
       <c r="H104" s="338"/>
@@ -17208,7 +17197,7 @@
       <c r="P104" s="338"/>
       <c r="Q104" s="338"/>
     </row>
-    <row r="105" spans="3:17" x14ac:dyDescent="0.15">
+    <row r="105" spans="3:17">
       <c r="C105" s="338"/>
       <c r="G105" s="338"/>
       <c r="H105" s="338"/>
@@ -17253,16 +17242,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:H89"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="6.1640625" customWidth="1"/>
+    <col min="1" max="1" width="6.1328125" customWidth="1"/>
     <col min="2" max="2" width="24.6640625" customWidth="1"/>
     <col min="3" max="6" width="20.6640625" customWidth="1"/>
     <col min="7" max="7" width="5.6640625" customWidth="1"/>
-    <col min="8" max="8" width="56.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="56.796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:8" ht="13.9">
       <c r="B2" s="36" t="s">
         <v>443</v>
       </c>
@@ -17274,7 +17263,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:8" ht="13.15">
       <c r="B3" s="109" t="s">
         <v>442</v>
       </c>
@@ -17287,7 +17276,7 @@
       </c>
       <c r="H3" s="120"/>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:8">
       <c r="B4" s="100" t="s">
         <v>440</v>
       </c>
@@ -17308,7 +17297,7 @@
       </c>
       <c r="H4" s="120"/>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:8">
       <c r="B5" s="205" t="s">
         <v>123</v>
       </c>
@@ -17319,7 +17308,7 @@
       <c r="E5" s="148"/>
       <c r="H5" s="120"/>
     </row>
-    <row r="6" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:8" ht="13.25" customHeight="1">
       <c r="B6" s="149" t="s">
         <v>441</v>
       </c>
@@ -17335,7 +17324,7 @@
       <c r="F6" s="364"/>
       <c r="H6" s="120"/>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:8" ht="13.15">
       <c r="B7" s="149" t="s">
         <v>444</v>
       </c>
@@ -17349,10 +17338,10 @@
       </c>
       <c r="H7" s="120"/>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:8">
       <c r="H8" s="120"/>
     </row>
-    <row r="9" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:8" ht="13.9">
       <c r="B9" s="36" t="s">
         <v>229</v>
       </c>
@@ -17362,13 +17351,13 @@
       <c r="F9" s="37"/>
       <c r="H9" s="120"/>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:8" ht="13.15">
       <c r="B10" s="119" t="s">
         <v>135</v>
       </c>
       <c r="H10" s="120"/>
     </row>
-    <row r="11" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:8" ht="13.25" customHeight="1">
       <c r="B11" s="152" t="s">
         <v>133</v>
       </c>
@@ -17378,7 +17367,7 @@
       </c>
       <c r="H11" s="120"/>
     </row>
-    <row r="12" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:8" ht="13.25" customHeight="1">
       <c r="B12" s="118" t="s">
         <v>134</v>
       </c>
@@ -17388,7 +17377,7 @@
       </c>
       <c r="H12" s="120"/>
     </row>
-    <row r="13" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:8" ht="13.25" customHeight="1">
       <c r="B13" s="153" t="s">
         <v>106</v>
       </c>
@@ -17402,10 +17391,10 @@
       </c>
       <c r="H13" s="120"/>
     </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:8">
       <c r="H14" s="120"/>
     </row>
-    <row r="15" spans="2:8" ht="14" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:8" ht="13.15">
       <c r="B15" s="128" t="s">
         <v>107</v>
       </c>
@@ -17423,7 +17412,7 @@
       </c>
       <c r="H15" s="120"/>
     </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:8">
       <c r="B16" s="122">
         <v>1</v>
       </c>
@@ -17445,7 +17434,7 @@
       </c>
       <c r="H16" s="120"/>
     </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:8">
       <c r="B17" s="122">
         <v>2</v>
       </c>
@@ -17467,7 +17456,7 @@
       </c>
       <c r="H17" s="120"/>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:8">
       <c r="B18" s="122">
         <v>3</v>
       </c>
@@ -17489,7 +17478,7 @@
       </c>
       <c r="H18" s="120"/>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:8">
       <c r="B19" s="122">
         <v>4</v>
       </c>
@@ -17511,7 +17500,7 @@
       </c>
       <c r="H19" s="120"/>
     </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:8">
       <c r="B20" s="122">
         <v>5</v>
       </c>
@@ -17533,7 +17522,7 @@
       </c>
       <c r="H20" s="120"/>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:8">
       <c r="B21" s="122">
         <v>6</v>
       </c>
@@ -17555,7 +17544,7 @@
       </c>
       <c r="H21" s="120"/>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:8">
       <c r="B22" s="122">
         <v>7</v>
       </c>
@@ -17577,7 +17566,7 @@
       </c>
       <c r="H22" s="120"/>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:8">
       <c r="B23" s="122">
         <v>8</v>
       </c>
@@ -17599,7 +17588,7 @@
       </c>
       <c r="H23" s="120"/>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:8">
       <c r="B24" s="122">
         <v>9</v>
       </c>
@@ -17621,7 +17610,7 @@
       </c>
       <c r="H24" s="120"/>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:8">
       <c r="B25" s="122">
         <v>10</v>
       </c>
@@ -17643,7 +17632,7 @@
       </c>
       <c r="H25" s="120"/>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:8">
       <c r="B26" s="122">
         <v>11</v>
       </c>
@@ -17665,7 +17654,7 @@
       </c>
       <c r="H26" s="120"/>
     </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:8">
       <c r="B27" s="122">
         <v>12</v>
       </c>
@@ -17687,7 +17676,7 @@
       </c>
       <c r="H27" s="120"/>
     </row>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:8">
       <c r="B28" s="122">
         <v>13</v>
       </c>
@@ -17709,7 +17698,7 @@
       </c>
       <c r="H28" s="120"/>
     </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:8">
       <c r="B29" s="122">
         <v>14</v>
       </c>
@@ -17731,7 +17720,7 @@
       </c>
       <c r="H29" s="120"/>
     </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:8">
       <c r="B30" s="122">
         <v>15</v>
       </c>
@@ -17753,7 +17742,7 @@
       </c>
       <c r="H30" s="120"/>
     </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:8">
       <c r="B31" s="122">
         <v>16</v>
       </c>
@@ -17775,7 +17764,7 @@
       </c>
       <c r="H31" s="120"/>
     </row>
-    <row r="32" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:8">
       <c r="B32" s="122">
         <v>17</v>
       </c>
@@ -17797,7 +17786,7 @@
       </c>
       <c r="H32" s="120"/>
     </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:8">
       <c r="B33" s="122">
         <v>18</v>
       </c>
@@ -17819,7 +17808,7 @@
       </c>
       <c r="H33" s="120"/>
     </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:8">
       <c r="B34" s="122">
         <v>19</v>
       </c>
@@ -17841,7 +17830,7 @@
       </c>
       <c r="H34" s="120"/>
     </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:8">
       <c r="B35" s="122">
         <v>20</v>
       </c>
@@ -17863,7 +17852,7 @@
       </c>
       <c r="H35" s="120"/>
     </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:8">
       <c r="B36" s="122">
         <v>21</v>
       </c>
@@ -17885,7 +17874,7 @@
       </c>
       <c r="H36" s="120"/>
     </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:8">
       <c r="B37" s="122">
         <v>22</v>
       </c>
@@ -17907,7 +17896,7 @@
       </c>
       <c r="H37" s="120"/>
     </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:8">
       <c r="B38" s="122">
         <v>23</v>
       </c>
@@ -17929,7 +17918,7 @@
       </c>
       <c r="H38" s="120"/>
     </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:8">
       <c r="B39" s="122">
         <v>24</v>
       </c>
@@ -17951,7 +17940,7 @@
       </c>
       <c r="H39" s="120"/>
     </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:8">
       <c r="B40" s="122">
         <v>25</v>
       </c>
@@ -17973,7 +17962,7 @@
       </c>
       <c r="H40" s="120"/>
     </row>
-    <row r="41" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:8">
       <c r="B41" s="122">
         <v>26</v>
       </c>
@@ -17995,7 +17984,7 @@
       </c>
       <c r="H41" s="120"/>
     </row>
-    <row r="42" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:8">
       <c r="B42" s="122">
         <v>27</v>
       </c>
@@ -18017,7 +18006,7 @@
       </c>
       <c r="H42" s="120"/>
     </row>
-    <row r="43" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="43" spans="2:8">
       <c r="B43" s="122">
         <v>28</v>
       </c>
@@ -18039,7 +18028,7 @@
       </c>
       <c r="H43" s="120"/>
     </row>
-    <row r="44" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:8">
       <c r="B44" s="122">
         <v>29</v>
       </c>
@@ -18061,7 +18050,7 @@
       </c>
       <c r="H44" s="120"/>
     </row>
-    <row r="45" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:8">
       <c r="B45" s="122">
         <v>30</v>
       </c>
@@ -18083,7 +18072,7 @@
       </c>
       <c r="H45" s="120"/>
     </row>
-    <row r="46" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:8">
       <c r="B46" s="126" t="s">
         <v>131</v>
       </c>
@@ -18105,7 +18094,7 @@
       </c>
       <c r="H46" s="120"/>
     </row>
-    <row r="47" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:8">
       <c r="C47" s="114"/>
       <c r="E47" s="127" t="s">
         <v>100</v>
@@ -18116,11 +18105,11 @@
       </c>
       <c r="H47" s="120"/>
     </row>
-    <row r="48" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:8">
       <c r="C48" s="114"/>
       <c r="H48" s="120"/>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:8" ht="13.15">
       <c r="B49" s="119" t="s">
         <v>129</v>
       </c>
@@ -18130,7 +18119,7 @@
       <c r="F49" s="117"/>
       <c r="H49" s="120"/>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:8" ht="13.15">
       <c r="A50" s="133">
         <f>F47</f>
         <v>2071195495.7086666</v>
@@ -18157,7 +18146,7 @@
       </c>
       <c r="H50" s="120"/>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:8" ht="13.15">
       <c r="A51" s="143">
         <v>5</v>
       </c>
@@ -18179,7 +18168,7 @@
       </c>
       <c r="H51" s="120"/>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:8" ht="13.15">
       <c r="A52" s="143">
         <v>10</v>
       </c>
@@ -18200,7 +18189,7 @@
       </c>
       <c r="H52" s="120"/>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:8" ht="13.15">
       <c r="A53" s="143">
         <v>15</v>
       </c>
@@ -18221,7 +18210,7 @@
       </c>
       <c r="H53" s="120"/>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:8" ht="13.15">
       <c r="A54" s="144">
         <v>20</v>
       </c>
@@ -18242,7 +18231,7 @@
       </c>
       <c r="H54" s="120"/>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:8" ht="13.15">
       <c r="A55" s="144">
         <v>25</v>
       </c>
@@ -18263,7 +18252,7 @@
       </c>
       <c r="H55" s="120"/>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:8" ht="13.15">
       <c r="A56" s="144">
         <v>30</v>
       </c>
@@ -18284,14 +18273,14 @@
       </c>
       <c r="H56" s="120"/>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:8">
       <c r="C57" s="114"/>
       <c r="D57" s="114"/>
       <c r="E57" s="114"/>
       <c r="F57" s="114"/>
       <c r="H57" s="120"/>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:8" ht="13.15">
       <c r="B58" s="119" t="s">
         <v>130</v>
       </c>
@@ -18301,7 +18290,7 @@
       <c r="F58" s="114"/>
       <c r="H58" s="120"/>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:8" ht="13.15">
       <c r="B59" s="132">
         <f>B50</f>
         <v>0</v>
@@ -18324,7 +18313,7 @@
       </c>
       <c r="H59" s="120"/>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:8" ht="13.15">
       <c r="A60" s="143">
         <v>0</v>
       </c>
@@ -18350,7 +18339,7 @@
       </c>
       <c r="H60" s="120"/>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:8" ht="13.15">
       <c r="A61" s="143">
         <f t="shared" ref="A61:A66" si="3">A51</f>
         <v>5</v>
@@ -18377,7 +18366,7 @@
       </c>
       <c r="H61" s="120"/>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:8" ht="13.15">
       <c r="A62" s="143">
         <f t="shared" si="3"/>
         <v>10</v>
@@ -18404,7 +18393,7 @@
       </c>
       <c r="H62" s="120"/>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:8" ht="13.15">
       <c r="A63" s="143">
         <f t="shared" si="3"/>
         <v>15</v>
@@ -18431,7 +18420,7 @@
       </c>
       <c r="H63" s="120"/>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:8" ht="13.15">
       <c r="A64" s="144">
         <f t="shared" si="3"/>
         <v>20</v>
@@ -18458,7 +18447,7 @@
       </c>
       <c r="H64" s="120"/>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:8" ht="13.15">
       <c r="A65" s="144">
         <f t="shared" si="3"/>
         <v>25</v>
@@ -18484,7 +18473,7 @@
         <v>14.544393521622398</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:8" ht="13.15">
       <c r="A66" s="144">
         <f t="shared" si="3"/>
         <v>30</v>
@@ -18510,7 +18499,7 @@
         <v>17.497019921088636</v>
       </c>
     </row>
-    <row r="68" spans="1:8" ht="14" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:8" ht="13.15">
       <c r="B68" s="171" t="s">
         <v>117</v>
       </c>
@@ -18527,7 +18516,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:8">
       <c r="B69" s="127" t="str">
         <f>Scenarios!B54</f>
         <v>Snowball Scenario</v>
@@ -18549,7 +18538,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:8">
       <c r="B70" s="127" t="str">
         <f>Scenarios!B36</f>
         <v>Optimistic</v>
@@ -18572,7 +18561,7 @@
       </c>
       <c r="H70" s="120"/>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:8">
       <c r="B71" s="127" t="str">
         <f>Scenarios!B24</f>
         <v>Base</v>
@@ -18595,7 +18584,7 @@
       </c>
       <c r="H71" s="120"/>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:8">
       <c r="B72" s="127" t="str">
         <f>Scenarios!B30</f>
         <v>Pessimistic</v>
@@ -18618,7 +18607,7 @@
       </c>
       <c r="H72" s="120"/>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:8">
       <c r="B73" s="127" t="str">
         <f>Scenarios!B48</f>
         <v>Devil's advocate</v>
@@ -18640,14 +18629,14 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:8">
       <c r="B74" s="155"/>
       <c r="C74" s="155"/>
       <c r="D74" s="155"/>
       <c r="E74" s="155"/>
       <c r="F74" s="156"/>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:8">
       <c r="B75" s="155" t="s">
         <v>310</v>
       </c>
@@ -18655,23 +18644,23 @@
         <v>105</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:8">
       <c r="C76" s="155" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:8">
       <c r="C77" s="155" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="87" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="87" spans="3:3">
       <c r="C87" s="115"/>
     </row>
-    <row r="88" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="88" spans="3:3">
       <c r="C88" s="115"/>
     </row>
-    <row r="89" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="89" spans="3:3">
       <c r="C89" s="115"/>
     </row>
   </sheetData>
@@ -18701,7 +18690,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
   <dimension ref="B2:I110"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="2.6640625" customWidth="1"/>
     <col min="2" max="2" width="22.6640625" customWidth="1"/>
@@ -18711,7 +18700,7 @@
     <col min="8" max="9" width="15.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:9" ht="13.9">
       <c r="B2" s="36" t="s">
         <v>145</v>
       </c>
@@ -18724,7 +18713,7 @@
       </c>
       <c r="I2" s="249"/>
     </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:9" ht="13.15">
       <c r="B3" s="159" t="s">
         <v>148</v>
       </c>
@@ -18733,10 +18722,10 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-13.53</v>
-      </c>
-    </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.15">
+        <v>-13.39</v>
+      </c>
+    </row>
+    <row r="4" spans="2:9">
       <c r="B4" s="152" t="s">
         <v>146</v>
       </c>
@@ -18756,7 +18745,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:9">
       <c r="H5" s="247">
         <v>2</v>
       </c>
@@ -18765,7 +18754,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:9" ht="13.15">
       <c r="B6" s="159" t="s">
         <v>95</v>
       </c>
@@ -18785,7 +18774,7 @@
         <v>10.651430255232372</v>
       </c>
     </row>
-    <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:9" ht="12.75" customHeight="1">
       <c r="B7" s="100" t="s">
         <v>275</v>
       </c>
@@ -18810,7 +18799,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:9">
       <c r="B8" s="100" t="s">
         <v>66</v>
       </c>
@@ -18832,7 +18821,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:9">
       <c r="B9" s="100" t="s">
         <v>57</v>
       </c>
@@ -18854,7 +18843,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:9">
       <c r="E10" s="366"/>
       <c r="F10" s="366"/>
       <c r="H10" s="247">
@@ -18865,7 +18854,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:9" ht="13.15">
       <c r="B11" s="159" t="s">
         <v>447</v>
       </c>
@@ -18879,7 +18868,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="2:9" ht="14" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:9">
       <c r="B12" s="118" t="s">
         <v>144</v>
       </c>
@@ -18898,7 +18887,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:9">
       <c r="B13" s="148" t="s">
         <v>152</v>
       </c>
@@ -18916,7 +18905,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:9">
       <c r="B14" s="100" t="s">
         <v>66</v>
       </c>
@@ -18927,7 +18916,7 @@
       <c r="E14" s="366"/>
       <c r="F14" s="366"/>
     </row>
-    <row r="16" spans="2:9" ht="16" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
         <v>162</v>
       </c>
@@ -18936,7 +18925,7 @@
       <c r="E16" s="37"/>
       <c r="F16" s="37"/>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:6" ht="13.15">
       <c r="B17" s="109" t="s">
         <v>151</v>
       </c>
@@ -18944,7 +18933,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:6">
       <c r="B18" s="152" t="s">
         <v>133</v>
       </c>
@@ -18956,24 +18945,24 @@
       </c>
       <c r="F18" s="367"/>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:6">
       <c r="E19" s="367"/>
       <c r="F19" s="367"/>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="159" t="s">
         <v>303</v>
       </c>
       <c r="E20" s="367"/>
       <c r="F20" s="367"/>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
         <v>277</v>
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>13.53</v>
+        <v>13.39</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -18982,7 +18971,7 @@
       <c r="E21" s="367"/>
       <c r="F21" s="367"/>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
         <v>278</v>
       </c>
@@ -18997,7 +18986,7 @@
       <c r="E22" s="367"/>
       <c r="F22" s="367"/>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="159" t="s">
         <v>115</v>
       </c>
@@ -19006,7 +18995,7 @@
       </c>
       <c r="F24" s="159"/>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:6">
       <c r="B25" s="152" t="s">
         <v>133</v>
       </c>
@@ -19018,7 +19007,7 @@
       <c r="E25" s="365"/>
       <c r="F25" s="365"/>
     </row>
-    <row r="26" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:6">
       <c r="B26" s="118" t="s">
         <v>134</v>
       </c>
@@ -19029,7 +19018,7 @@
       <c r="E26" s="365"/>
       <c r="F26" s="365"/>
     </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
         <v>113</v>
       </c>
@@ -19044,7 +19033,7 @@
       <c r="E27" s="365"/>
       <c r="F27" s="365"/>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
         <v>147</v>
       </c>
@@ -19055,7 +19044,7 @@
       <c r="E28" s="365"/>
       <c r="F28" s="365"/>
     </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="159" t="s">
         <v>116</v>
       </c>
@@ -19064,7 +19053,7 @@
       </c>
       <c r="F30" s="159"/>
     </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:6">
       <c r="B31" s="152" t="s">
         <v>133</v>
       </c>
@@ -19076,7 +19065,7 @@
       <c r="E31" s="365"/>
       <c r="F31" s="365"/>
     </row>
-    <row r="32" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:6">
       <c r="B32" s="118" t="s">
         <v>134</v>
       </c>
@@ -19087,7 +19076,7 @@
       <c r="E32" s="365"/>
       <c r="F32" s="365"/>
     </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
         <v>113</v>
       </c>
@@ -19102,7 +19091,7 @@
       <c r="E33" s="365"/>
       <c r="F33" s="365"/>
     </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
         <v>147</v>
       </c>
@@ -19113,7 +19102,7 @@
       <c r="E34" s="365"/>
       <c r="F34" s="365"/>
     </row>
-    <row r="36" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="159" t="s">
         <v>114</v>
       </c>
@@ -19122,7 +19111,7 @@
       </c>
       <c r="F36" s="159"/>
     </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:6">
       <c r="B37" s="152" t="s">
         <v>133</v>
       </c>
@@ -19134,7 +19123,7 @@
       <c r="E37" s="365"/>
       <c r="F37" s="365"/>
     </row>
-    <row r="38" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:6">
       <c r="B38" s="118" t="s">
         <v>134</v>
       </c>
@@ -19145,7 +19134,7 @@
       <c r="E38" s="365"/>
       <c r="F38" s="365"/>
     </row>
-    <row r="39" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
         <v>113</v>
       </c>
@@ -19160,7 +19149,7 @@
       <c r="E39" s="365"/>
       <c r="F39" s="365"/>
     </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
         <v>147</v>
       </c>
@@ -19172,7 +19161,7 @@
       <c r="E40" s="365"/>
       <c r="F40" s="365"/>
     </row>
-    <row r="42" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
         <v>120</v>
       </c>
@@ -19185,7 +19174,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="44" spans="2:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:6" ht="13.9">
       <c r="B44" s="36" t="s">
         <v>161</v>
       </c>
@@ -19194,12 +19183,12 @@
       <c r="E44" s="37"/>
       <c r="F44" s="37"/>
     </row>
-    <row r="45" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:6" ht="13.15">
       <c r="B45" s="109" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="46" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:6">
       <c r="B46" s="152" t="s">
         <v>133</v>
       </c>
@@ -19209,12 +19198,12 @@
       <c r="E46" s="100"/>
       <c r="F46" s="100"/>
     </row>
-    <row r="47" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:6" ht="13.15">
       <c r="B47" s="159"/>
       <c r="E47" s="159"/>
       <c r="F47" s="159"/>
     </row>
-    <row r="48" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:6" ht="13.15">
       <c r="B48" s="159" t="s">
         <v>165</v>
       </c>
@@ -19223,7 +19212,7 @@
       </c>
       <c r="F48" s="159"/>
     </row>
-    <row r="49" spans="2:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="2:6" ht="12.75" customHeight="1">
       <c r="B49" s="152" t="s">
         <v>133</v>
       </c>
@@ -19235,7 +19224,7 @@
       <c r="E49" s="365"/>
       <c r="F49" s="365"/>
     </row>
-    <row r="50" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:6">
       <c r="B50" s="118" t="s">
         <v>134</v>
       </c>
@@ -19246,7 +19235,7 @@
       <c r="E50" s="365"/>
       <c r="F50" s="365"/>
     </row>
-    <row r="51" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
         <v>113</v>
       </c>
@@ -19261,7 +19250,7 @@
       <c r="E51" s="365"/>
       <c r="F51" s="365"/>
     </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
         <v>147</v>
       </c>
@@ -19272,7 +19261,7 @@
       <c r="E52" s="365"/>
       <c r="F52" s="365"/>
     </row>
-    <row r="54" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="159" t="s">
         <v>316</v>
       </c>
@@ -19281,7 +19270,7 @@
       </c>
       <c r="F54" s="159"/>
     </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:6">
       <c r="B55" s="152" t="s">
         <v>133</v>
       </c>
@@ -19293,7 +19282,7 @@
       <c r="E55" s="365"/>
       <c r="F55" s="365"/>
     </row>
-    <row r="56" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:6">
       <c r="B56" s="118" t="s">
         <v>134</v>
       </c>
@@ -19304,7 +19293,7 @@
       <c r="E56" s="365"/>
       <c r="F56" s="365"/>
     </row>
-    <row r="57" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
         <v>113</v>
       </c>
@@ -19319,7 +19308,7 @@
       <c r="E57" s="365"/>
       <c r="F57" s="365"/>
     </row>
-    <row r="58" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
         <v>147</v>
       </c>
@@ -19330,7 +19319,7 @@
       <c r="E58" s="365"/>
       <c r="F58" s="365"/>
     </row>
-    <row r="60" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
         <v>120</v>
       </c>
@@ -19350,7 +19339,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="62" spans="2:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:6" ht="13.9">
       <c r="B62" s="36" t="s">
         <v>349</v>
       </c>
@@ -19359,7 +19348,7 @@
       <c r="E62" s="37"/>
       <c r="F62" s="37"/>
     </row>
-    <row r="63" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="63" spans="2:6" ht="13.15">
       <c r="B63" s="109" t="s">
         <v>304</v>
       </c>
@@ -19367,7 +19356,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="64" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:6">
       <c r="B64" s="152" t="s">
         <v>133</v>
       </c>
@@ -19380,7 +19369,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="65" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="65" spans="2:6">
       <c r="B65" s="118" t="s">
         <v>134</v>
       </c>
@@ -19392,7 +19381,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="66" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="66" spans="2:6">
       <c r="B66" s="100" t="s">
         <v>102</v>
       </c>
@@ -19408,7 +19397,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="68" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="68" spans="2:6" ht="13.15">
       <c r="B68" s="109" t="s">
         <v>350</v>
       </c>
@@ -19416,7 +19405,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="69" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="69" spans="2:6">
       <c r="B69" s="100" t="s">
         <v>305</v>
       </c>
@@ -19426,7 +19415,7 @@
       </c>
       <c r="E69" s="134"/>
     </row>
-    <row r="70" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="70" spans="2:6">
       <c r="B70" s="100" t="s">
         <v>293</v>
       </c>
@@ -19438,7 +19427,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="71" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="71" spans="2:6">
       <c r="B71" s="100" t="s">
         <v>292</v>
       </c>
@@ -19448,7 +19437,7 @@
       </c>
       <c r="E71" s="251"/>
     </row>
-    <row r="72" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="72" spans="2:6">
       <c r="B72" s="100" t="s">
         <v>284</v>
       </c>
@@ -19464,7 +19453,7 @@
         <v>0.22959710481590032</v>
       </c>
     </row>
-    <row r="74" spans="2:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:6" ht="13.9">
       <c r="B74" s="36" t="s">
         <v>127</v>
       </c>
@@ -19473,12 +19462,12 @@
       <c r="E74" s="37"/>
       <c r="F74" s="37"/>
     </row>
-    <row r="75" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="75" spans="2:6" ht="13.15">
       <c r="B75" s="109" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="76" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="76" spans="2:6">
       <c r="B76" s="246" t="s">
         <v>297</v>
       </c>
@@ -19488,7 +19477,7 @@
       </c>
       <c r="D76" s="134"/>
     </row>
-    <row r="77" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="77" spans="2:6">
       <c r="B77" s="100" t="s">
         <v>111</v>
       </c>
@@ -19501,12 +19490,12 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="79" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="79" spans="2:6" ht="13.15">
       <c r="B79" s="109" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="80" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="80" spans="2:6">
       <c r="B80" s="148" t="s">
         <v>299</v>
       </c>
@@ -19515,7 +19504,7 @@
         <v>0.33699999999999997</v>
       </c>
     </row>
-    <row r="81" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="81" spans="2:8">
       <c r="B81" s="100" t="s">
         <v>121</v>
       </c>
@@ -19527,7 +19516,7 @@
       <c r="E81" s="100"/>
       <c r="F81" s="100"/>
     </row>
-    <row r="82" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="82" spans="2:8">
       <c r="B82" s="100" t="s">
         <v>122</v>
       </c>
@@ -19537,7 +19526,7 @@
       </c>
       <c r="D82" s="116"/>
     </row>
-    <row r="83" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="83" spans="2:8" ht="13.15">
       <c r="B83" s="110" t="s">
         <v>101</v>
       </c>
@@ -19557,45 +19546,45 @@
         <v>0.51424846499304677</v>
       </c>
     </row>
-    <row r="84" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="84" spans="2:8">
       <c r="E84" s="120"/>
     </row>
-    <row r="85" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="85" spans="2:8" ht="13.15">
       <c r="B85" s="109" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="86" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="86" spans="2:8">
       <c r="B86" s="148" t="s">
         <v>300</v>
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>13.53</v>
+        <v>13.39</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="87" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="87" spans="2:8" ht="13.15">
       <c r="B87" s="100" t="s">
         <v>298</v>
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>-5.5896901541827249E-2</v>
-      </c>
-    </row>
-    <row r="88" spans="2:8" x14ac:dyDescent="0.15">
+        <v>-5.2509260474737696E-2</v>
+      </c>
+    </row>
+    <row r="88" spans="2:8">
       <c r="B88" s="100"/>
     </row>
-    <row r="89" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="89" spans="2:8" ht="13.15">
       <c r="B89" s="109" t="s">
         <v>412</v>
       </c>
     </row>
-    <row r="90" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="90" spans="2:8">
       <c r="B90" s="148" t="s">
         <v>413</v>
       </c>
@@ -19604,7 +19593,7 @@
         <v>0.187</v>
       </c>
     </row>
-    <row r="91" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="91" spans="2:8">
       <c r="B91" s="100" t="s">
         <v>121</v>
       </c>
@@ -19616,7 +19605,7 @@
       <c r="E91" s="100"/>
       <c r="F91" s="100"/>
     </row>
-    <row r="92" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="92" spans="2:8">
       <c r="B92" s="100" t="s">
         <v>122</v>
       </c>
@@ -19626,7 +19615,7 @@
       </c>
       <c r="D92" s="116"/>
     </row>
-    <row r="93" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="93" spans="2:8" ht="13.15">
       <c r="B93" s="110" t="s">
         <v>101</v>
       </c>
@@ -19646,14 +19635,14 @@
         <v>0.31817781825366975</v>
       </c>
     </row>
-    <row r="95" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="95" spans="2:8" ht="13.15">
       <c r="B95" s="109" t="s">
         <v>397</v>
       </c>
       <c r="G95" s="2"/>
       <c r="H95" s="281"/>
     </row>
-    <row r="96" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="96" spans="2:8">
       <c r="B96" s="148" t="s">
         <v>403</v>
       </c>
@@ -19664,7 +19653,7 @@
       <c r="G96" s="2"/>
       <c r="H96" s="281"/>
     </row>
-    <row r="97" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="97" spans="2:8">
       <c r="B97" s="100" t="s">
         <v>121</v>
       </c>
@@ -19676,7 +19665,7 @@
       <c r="G97" s="2"/>
       <c r="H97" s="281"/>
     </row>
-    <row r="98" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="98" spans="2:8">
       <c r="B98" s="100" t="s">
         <v>122</v>
       </c>
@@ -19688,7 +19677,7 @@
       <c r="G98" s="2"/>
       <c r="H98" s="281"/>
     </row>
-    <row r="99" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="99" spans="2:8" ht="13.15">
       <c r="B99" s="110" t="s">
         <v>398</v>
       </c>
@@ -19707,15 +19696,15 @@
         <v>5.6082608980383197E-2</v>
       </c>
     </row>
-    <row r="100" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="100" spans="2:8">
       <c r="B100" s="100"/>
     </row>
-    <row r="101" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="101" spans="2:8" ht="13.15">
       <c r="B101" s="109" t="s">
         <v>422</v>
       </c>
     </row>
-    <row r="102" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="102" spans="2:8">
       <c r="B102" s="148" t="s">
         <v>421</v>
       </c>
@@ -19724,7 +19713,7 @@
         <v>8.6999999999999994E-2</v>
       </c>
     </row>
-    <row r="103" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="103" spans="2:8">
       <c r="B103" s="100" t="s">
         <v>121</v>
       </c>
@@ -19734,7 +19723,7 @@
       </c>
       <c r="D103" s="116"/>
     </row>
-    <row r="104" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="104" spans="2:8">
       <c r="B104" s="100" t="s">
         <v>122</v>
       </c>
@@ -19744,7 +19733,7 @@
       </c>
       <c r="D104" s="116"/>
     </row>
-    <row r="105" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="105" spans="2:8" ht="13.15">
       <c r="B105" s="110" t="s">
         <v>398</v>
       </c>
@@ -19763,16 +19752,16 @@
         <v>0.11980238369313911</v>
       </c>
     </row>
-    <row r="106" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="106" spans="2:8">
       <c r="B106" s="100"/>
     </row>
-    <row r="107" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="107" spans="2:8" ht="14.65">
       <c r="E107" s="285" t="s">
         <v>324</v>
       </c>
       <c r="F107" s="282"/>
     </row>
-    <row r="108" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="108" spans="2:8" ht="13.9">
       <c r="E108" s="278" t="s">
         <v>325</v>
       </c>
@@ -19780,7 +19769,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="109" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="109" spans="2:8" ht="13.9">
       <c r="E109" s="279" t="s">
         <v>325</v>
       </c>
@@ -19788,7 +19777,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="110" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="110" spans="2:8" ht="13.9">
       <c r="E110" s="280" t="s">
         <v>325</v>
       </c>

--- a/financial_models/opportunities/300481.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/300481.SZ_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C84597E4-7B5D-4ED1-9163-5B20FE4C1426}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5D81A4F-5492-4CC0-853B-10A1515066D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3891,29 +3891,29 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4331,7 +4331,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>13.39</v>
+        <v>13.67</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4352,7 +4352,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>3907.9443148200003</v>
+        <v>3989.6638374600002</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4389,13 +4389,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="358" t="s">
+      <c r="B18" s="356" t="s">
         <v>359</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+      <c r="C18" s="356"/>
+      <c r="D18" s="356"/>
+      <c r="E18" s="356"/>
+      <c r="F18" s="356"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4478,7 +4478,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>-5.2509260474737696E-2</v>
+        <v>-5.9237132741926435E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4595,22 +4595,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="358" t="s">
+      <c r="B36" s="356" t="s">
         <v>360</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
+      <c r="C36" s="356"/>
+      <c r="D36" s="356"/>
+      <c r="E36" s="356"/>
+      <c r="F36" s="356"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="361" t="s">
+      <c r="B37" s="358" t="s">
         <v>339</v>
       </c>
-      <c r="C37" s="361"/>
-      <c r="D37" s="361"/>
-      <c r="E37" s="361"/>
-      <c r="F37" s="361"/>
+      <c r="C37" s="358"/>
+      <c r="D37" s="358"/>
+      <c r="E37" s="358"/>
+      <c r="F37" s="358"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4622,13 +4622,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="359" t="s">
+      <c r="B40" s="357" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+      <c r="C40" s="357"/>
+      <c r="D40" s="357"/>
+      <c r="E40" s="357"/>
+      <c r="F40" s="357"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4648,13 +4648,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="359" t="s">
+      <c r="B43" s="357" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+      <c r="C43" s="357"/>
+      <c r="D43" s="357"/>
+      <c r="E43" s="357"/>
+      <c r="F43" s="357"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4683,13 +4683,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+      <c r="B47" s="357" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="C47" s="357"/>
+      <c r="D47" s="357"/>
+      <c r="E47" s="357"/>
+      <c r="F47" s="357"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4705,13 +4705,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+      <c r="B50" s="357" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="C50" s="357"/>
+      <c r="D50" s="357"/>
+      <c r="E50" s="357"/>
+      <c r="F50" s="357"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4775,13 +4775,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+      <c r="B58" s="357" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="C58" s="357"/>
+      <c r="D58" s="357"/>
+      <c r="E58" s="357"/>
+      <c r="F58" s="357"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4797,7 +4797,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+      <c r="B61" s="357" t="s">
         <v>338</v>
       </c>
       <c r="C61" s="360"/>
@@ -4819,22 +4819,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="358" t="s">
+      <c r="B64" s="356" t="s">
         <v>343</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
+      <c r="C64" s="356"/>
+      <c r="D64" s="356"/>
+      <c r="E64" s="356"/>
+      <c r="F64" s="356"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="B65" s="356" t="s">
         <v>361</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+      <c r="C65" s="356"/>
+      <c r="D65" s="356"/>
+      <c r="E65" s="356"/>
+      <c r="F65" s="356"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>3.3132200891074826E-2</v>
+        <v>3.2453560346122304E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4878,7 +4878,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>2.9873039581777446E-2</v>
+        <v>2.9261155815654721E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>448</v>
@@ -4969,22 +4969,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="356" t="s">
         <v>362</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="C80" s="356"/>
+      <c r="D80" s="356"/>
+      <c r="E80" s="356"/>
+      <c r="F80" s="356"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="361" t="s">
+      <c r="B81" s="358" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="361"/>
-      <c r="D81" s="361"/>
-      <c r="E81" s="361"/>
-      <c r="F81" s="361"/>
+      <c r="C81" s="358"/>
+      <c r="D81" s="358"/>
+      <c r="E81" s="358"/>
+      <c r="F81" s="358"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5028,22 +5028,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="358" t="s">
+      <c r="B89" s="356" t="s">
         <v>363</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
+      <c r="C89" s="356"/>
+      <c r="D89" s="356"/>
+      <c r="E89" s="356"/>
+      <c r="F89" s="356"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="B90" s="356" t="s">
         <v>364</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+      <c r="C90" s="356"/>
+      <c r="D90" s="356"/>
+      <c r="E90" s="356"/>
+      <c r="F90" s="356"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5080,13 +5080,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+      <c r="B97" s="356" t="s">
         <v>365</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="C97" s="356"/>
+      <c r="D97" s="356"/>
+      <c r="E97" s="356"/>
+      <c r="F97" s="356"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5099,13 +5099,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="358" t="s">
+      <c r="B101" s="356" t="s">
         <v>344</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+      <c r="C101" s="356"/>
+      <c r="D101" s="356"/>
+      <c r="E101" s="356"/>
+      <c r="F101" s="356"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5227,13 +5227,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="358" t="s">
+      <c r="B116" s="356" t="s">
         <v>366</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+      <c r="C116" s="356"/>
+      <c r="D116" s="356"/>
+      <c r="E116" s="356"/>
+      <c r="F116" s="356"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5272,13 +5272,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="359" t="s">
+      <c r="B123" s="357" t="s">
         <v>367</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+      <c r="C123" s="357"/>
+      <c r="D123" s="357"/>
+      <c r="E123" s="357"/>
+      <c r="F123" s="357"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5421,13 +5421,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="362" t="s">
+      <c r="B134" s="361" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="362"/>
-      <c r="D134" s="362"/>
-      <c r="E134" s="362"/>
-      <c r="F134" s="362"/>
+      <c r="C134" s="361"/>
+      <c r="D134" s="361"/>
+      <c r="E134" s="361"/>
+      <c r="F134" s="361"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5440,22 +5440,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="363" t="s">
+      <c r="B138" s="359" t="s">
         <v>368</v>
       </c>
-      <c r="C138" s="363"/>
-      <c r="D138" s="363"/>
-      <c r="E138" s="363"/>
-      <c r="F138" s="363"/>
+      <c r="C138" s="359"/>
+      <c r="D138" s="359"/>
+      <c r="E138" s="359"/>
+      <c r="F138" s="359"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="B139" s="356" t="s">
         <v>369</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="C139" s="356"/>
+      <c r="D139" s="356"/>
+      <c r="E139" s="356"/>
+      <c r="F139" s="356"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5788,13 +5788,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="357" t="s">
+      <c r="B179" s="363" t="s">
         <v>376</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="C179" s="356"/>
+      <c r="D179" s="356"/>
+      <c r="E179" s="356"/>
+      <c r="F179" s="356"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5831,13 +5831,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+      <c r="B188" s="357" t="s">
         <v>381</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="C188" s="357"/>
+      <c r="D188" s="357"/>
+      <c r="E188" s="357"/>
+      <c r="F188" s="357"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5845,22 +5845,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="356" t="s">
+      <c r="B191" s="362" t="s">
         <v>382</v>
       </c>
-      <c r="C191" s="356"/>
-      <c r="D191" s="356"/>
-      <c r="E191" s="356"/>
-      <c r="F191" s="356"/>
+      <c r="C191" s="362"/>
+      <c r="D191" s="362"/>
+      <c r="E191" s="362"/>
+      <c r="F191" s="362"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="356" t="s">
+      <c r="B192" s="362" t="s">
         <v>383</v>
       </c>
-      <c r="C192" s="356"/>
-      <c r="D192" s="356"/>
-      <c r="E192" s="356"/>
-      <c r="F192" s="356"/>
+      <c r="C192" s="362"/>
+      <c r="D192" s="362"/>
+      <c r="E192" s="362"/>
+      <c r="F192" s="362"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5884,6 +5884,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5900,17 +5911,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13480,32 +13480,32 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>2.9873039581777446E-2</v>
+        <v>2.9261155815654721E-2</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>2.9873039581777446E-2</v>
+        <v>2.9261155815654721E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>2.9873039581777446E-2</v>
+        <v>2.9261155815654721E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>2.9873039581777446E-2</v>
+        <v>2.9261155815654721E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
-        <v>2.9873039581777446E-2</v>
+        <v>2.9261155815654721E-2</v>
       </c>
       <c r="K93" s="23">
         <f t="shared" si="39"/>
-        <v>1.4936519790888723E-2</v>
+        <v>1.4630577907827361E-2</v>
       </c>
       <c r="L93" s="23">
         <f t="shared" si="39"/>
-        <v>1.4936519790888723E-2</v>
+        <v>1.4630577907827361E-2</v>
       </c>
       <c r="M93" s="23">
         <f t="shared" si="39"/>
@@ -14679,50 +14679,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>3.3132200891074826E-2</v>
+        <v>3.2453560346122304E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>3.7754005937186398E-2</v>
+        <v>3.6980697841911186E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>4.9647346262021552E-2</v>
+        <v>4.8630429147656813E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>9.7649378270183149E-2</v>
+        <v>9.5649244699177197E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>6.323442171896633E-2</v>
+        <v>6.193920313218429E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>4.7286531238925851E-2</v>
+        <v>4.631797024793103E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>3.9284552707360712E-2</v>
+        <v>3.8479894714817851E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>2.7701978461953089E-2</v>
+        <v>2.7134564126229107E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>2.5182607292226187E-2</v>
+        <v>2.4666796755150596E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>1.6661094108501643E-2</v>
+        <v>1.6319828098963939E-2</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>1.6290941700107711E-2</v>
+        <v>1.5957257451678294E-2</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14736,43 +14736,43 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.9010469077991933E-2</v>
+        <v>4.8006596997389323E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.0154155244360928E-2</v>
+        <v>5.8922029167665903E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10803681065743298</v>
+        <v>0.1058239132921015</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.4583718361305525E-2</v>
+        <v>6.326086238901836E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.5714894227767082E-2</v>
+        <v>4.4778524777600671E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.7032378749917223E-2</v>
+        <v>3.6273851606539259E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.7059326203544093E-2</v>
+        <v>2.6505075191328123E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.8834998165369276E-2</v>
+        <v>1.8449204494096171E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.6526872902224255E-2</v>
+        <v>1.6188356120028002E-2</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.4710957825571773E-2</v>
+        <v>1.4409636085179667E-2</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18722,7 +18722,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-13.39</v>
+        <v>-13.67</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18962,7 +18962,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>13.39</v>
+        <v>13.67</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19560,7 +19560,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>13.39</v>
+        <v>13.67</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19573,7 +19573,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>-5.2509260474737696E-2</v>
+        <v>-5.9237132741926435E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/300481.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/300481.SZ_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5D81A4F-5492-4CC0-853B-10A1515066D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48C666EE-CD3E-46DA-985E-B46AFF6315C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3891,29 +3891,29 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4331,7 +4331,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>13.67</v>
+        <v>13.31</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4352,7 +4352,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>3989.6638374600002</v>
+        <v>3884.5958797800004</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4389,13 +4389,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="356" t="s">
+      <c r="B18" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C18" s="356"/>
-      <c r="D18" s="356"/>
-      <c r="E18" s="356"/>
-      <c r="F18" s="356"/>
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4478,7 +4478,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>-5.9237132741926435E-2</v>
+        <v>-5.0551725042324858E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4595,22 +4595,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="356" t="s">
+      <c r="B36" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C36" s="356"/>
-      <c r="D36" s="356"/>
-      <c r="E36" s="356"/>
-      <c r="F36" s="356"/>
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="358" t="s">
+      <c r="B37" s="361" t="s">
         <v>339</v>
       </c>
-      <c r="C37" s="358"/>
-      <c r="D37" s="358"/>
-      <c r="E37" s="358"/>
-      <c r="F37" s="358"/>
+      <c r="C37" s="361"/>
+      <c r="D37" s="361"/>
+      <c r="E37" s="361"/>
+      <c r="F37" s="361"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4622,13 +4622,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="357" t="s">
+      <c r="B40" s="359" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="357"/>
-      <c r="D40" s="357"/>
-      <c r="E40" s="357"/>
-      <c r="F40" s="357"/>
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4648,13 +4648,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="357" t="s">
+      <c r="B43" s="359" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="357"/>
-      <c r="D43" s="357"/>
-      <c r="E43" s="357"/>
-      <c r="F43" s="357"/>
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4683,13 +4683,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="357" t="s">
+      <c r="B47" s="359" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="357"/>
-      <c r="D47" s="357"/>
-      <c r="E47" s="357"/>
-      <c r="F47" s="357"/>
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4705,13 +4705,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="357" t="s">
+      <c r="B50" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="357"/>
-      <c r="D50" s="357"/>
-      <c r="E50" s="357"/>
-      <c r="F50" s="357"/>
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4775,13 +4775,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="357" t="s">
+      <c r="B58" s="359" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="357"/>
-      <c r="D58" s="357"/>
-      <c r="E58" s="357"/>
-      <c r="F58" s="357"/>
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4797,7 +4797,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="357" t="s">
+      <c r="B61" s="359" t="s">
         <v>338</v>
       </c>
       <c r="C61" s="360"/>
@@ -4819,22 +4819,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="356" t="s">
+      <c r="B64" s="358" t="s">
         <v>343</v>
       </c>
-      <c r="C64" s="356"/>
-      <c r="D64" s="356"/>
-      <c r="E64" s="356"/>
-      <c r="F64" s="356"/>
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="356" t="s">
+      <c r="B65" s="358" t="s">
         <v>361</v>
       </c>
-      <c r="C65" s="356"/>
-      <c r="D65" s="356"/>
-      <c r="E65" s="356"/>
-      <c r="F65" s="356"/>
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>3.2453560346122304E-2</v>
+        <v>3.3331342594402097E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4878,7 +4878,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>2.9261155815654721E-2</v>
+        <v>3.005259203606311E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>448</v>
@@ -4969,22 +4969,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="356" t="s">
+      <c r="B80" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C80" s="356"/>
-      <c r="D80" s="356"/>
-      <c r="E80" s="356"/>
-      <c r="F80" s="356"/>
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="358" t="s">
+      <c r="B81" s="361" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="358"/>
-      <c r="D81" s="358"/>
-      <c r="E81" s="358"/>
-      <c r="F81" s="358"/>
+      <c r="C81" s="361"/>
+      <c r="D81" s="361"/>
+      <c r="E81" s="361"/>
+      <c r="F81" s="361"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5028,22 +5028,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="356" t="s">
+      <c r="B89" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C89" s="356"/>
-      <c r="D89" s="356"/>
-      <c r="E89" s="356"/>
-      <c r="F89" s="356"/>
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="356" t="s">
+      <c r="B90" s="358" t="s">
         <v>364</v>
       </c>
-      <c r="C90" s="356"/>
-      <c r="D90" s="356"/>
-      <c r="E90" s="356"/>
-      <c r="F90" s="356"/>
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5080,13 +5080,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="356" t="s">
+      <c r="B97" s="358" t="s">
         <v>365</v>
       </c>
-      <c r="C97" s="356"/>
-      <c r="D97" s="356"/>
-      <c r="E97" s="356"/>
-      <c r="F97" s="356"/>
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5099,13 +5099,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="356" t="s">
+      <c r="B101" s="358" t="s">
         <v>344</v>
       </c>
-      <c r="C101" s="356"/>
-      <c r="D101" s="356"/>
-      <c r="E101" s="356"/>
-      <c r="F101" s="356"/>
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5227,13 +5227,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="356" t="s">
+      <c r="B116" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C116" s="356"/>
-      <c r="D116" s="356"/>
-      <c r="E116" s="356"/>
-      <c r="F116" s="356"/>
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5272,13 +5272,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="357" t="s">
+      <c r="B123" s="359" t="s">
         <v>367</v>
       </c>
-      <c r="C123" s="357"/>
-      <c r="D123" s="357"/>
-      <c r="E123" s="357"/>
-      <c r="F123" s="357"/>
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5421,13 +5421,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="361" t="s">
+      <c r="B134" s="362" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="361"/>
-      <c r="D134" s="361"/>
-      <c r="E134" s="361"/>
-      <c r="F134" s="361"/>
+      <c r="C134" s="362"/>
+      <c r="D134" s="362"/>
+      <c r="E134" s="362"/>
+      <c r="F134" s="362"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5440,22 +5440,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="359" t="s">
+      <c r="B138" s="363" t="s">
         <v>368</v>
       </c>
-      <c r="C138" s="359"/>
-      <c r="D138" s="359"/>
-      <c r="E138" s="359"/>
-      <c r="F138" s="359"/>
+      <c r="C138" s="363"/>
+      <c r="D138" s="363"/>
+      <c r="E138" s="363"/>
+      <c r="F138" s="363"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="356" t="s">
+      <c r="B139" s="358" t="s">
         <v>369</v>
       </c>
-      <c r="C139" s="356"/>
-      <c r="D139" s="356"/>
-      <c r="E139" s="356"/>
-      <c r="F139" s="356"/>
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5788,13 +5788,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="363" t="s">
+      <c r="B179" s="357" t="s">
         <v>376</v>
       </c>
-      <c r="C179" s="356"/>
-      <c r="D179" s="356"/>
-      <c r="E179" s="356"/>
-      <c r="F179" s="356"/>
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5831,13 +5831,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="357" t="s">
+      <c r="B188" s="359" t="s">
         <v>381</v>
       </c>
-      <c r="C188" s="357"/>
-      <c r="D188" s="357"/>
-      <c r="E188" s="357"/>
-      <c r="F188" s="357"/>
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5845,22 +5845,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="362" t="s">
+      <c r="B191" s="356" t="s">
         <v>382</v>
       </c>
-      <c r="C191" s="362"/>
-      <c r="D191" s="362"/>
-      <c r="E191" s="362"/>
-      <c r="F191" s="362"/>
+      <c r="C191" s="356"/>
+      <c r="D191" s="356"/>
+      <c r="E191" s="356"/>
+      <c r="F191" s="356"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="362" t="s">
+      <c r="B192" s="356" t="s">
         <v>383</v>
       </c>
-      <c r="C192" s="362"/>
-      <c r="D192" s="362"/>
-      <c r="E192" s="362"/>
-      <c r="F192" s="362"/>
+      <c r="C192" s="356"/>
+      <c r="D192" s="356"/>
+      <c r="E192" s="356"/>
+      <c r="F192" s="356"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5884,17 +5884,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5911,6 +5900,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13480,32 +13480,32 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>2.9261155815654721E-2</v>
+        <v>3.005259203606311E-2</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>2.9261155815654721E-2</v>
+        <v>3.005259203606311E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>2.9261155815654721E-2</v>
+        <v>3.005259203606311E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>2.9261155815654721E-2</v>
+        <v>3.005259203606311E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
-        <v>2.9261155815654721E-2</v>
+        <v>3.005259203606311E-2</v>
       </c>
       <c r="K93" s="23">
         <f t="shared" si="39"/>
-        <v>1.4630577907827361E-2</v>
+        <v>1.5026296018031555E-2</v>
       </c>
       <c r="L93" s="23">
         <f t="shared" si="39"/>
-        <v>1.4630577907827361E-2</v>
+        <v>1.5026296018031555E-2</v>
       </c>
       <c r="M93" s="23">
         <f t="shared" si="39"/>
@@ -14679,50 +14679,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>3.2453560346122304E-2</v>
+        <v>3.3331342594402097E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>3.6980697841911186E-2</v>
+        <v>3.7980927084817873E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>4.8630429147656813E-2</v>
+        <v>4.9945752550598695E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>9.5649244699177197E-2</v>
+        <v>9.8236301655728941E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>6.193920313218429E-2</v>
+        <v>6.361449337467763E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>4.631797024793103E-2</v>
+        <v>4.7570747805350651E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>3.8479894714817851E-2</v>
+        <v>3.9520673234527424E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>2.7134564126229107E-2</v>
+        <v>2.7868481713414866E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>2.4666796755150596E-2</v>
+        <v>2.5333967816897719E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>1.6319828098963939E-2</v>
+        <v>1.6761235921325095E-2</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>1.5957257451678294E-2</v>
+        <v>1.6388858705067035E-2</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14736,43 +14736,43 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.8006596997389323E-2</v>
+        <v>4.930504740453133E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.8922029167665903E-2</v>
+        <v>6.0515712901727491E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1058239132921015</v>
+        <v>0.10868616789654602</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.326086238901836E-2</v>
+        <v>6.4971899989322388E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.4778524777600671E-2</v>
+        <v>4.5989664441006849E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.6273851606539259E-2</v>
+        <v>3.7254962544056469E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.6505075191328123E-2</v>
+        <v>2.7221966781777265E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.8449204494096171E-2</v>
+        <v>1.8948206268542045E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.6188356120028002E-2</v>
+        <v>1.662620797601674E-2</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.4409636085179667E-2</v>
+        <v>1.47993783083701E-2</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18722,7 +18722,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-13.67</v>
+        <v>-13.31</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18962,7 +18962,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>13.67</v>
+        <v>13.31</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19560,7 +19560,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>13.67</v>
+        <v>13.31</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19573,7 +19573,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>-5.9237132741926435E-2</v>
+        <v>-5.0551725042324858E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/300481.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/300481.SZ_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48C666EE-CD3E-46DA-985E-B46AFF6315C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD1F2FD5-5B6E-4F09-B242-9E811FAEA46A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3891,29 +3891,29 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4389,13 +4389,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="358" t="s">
+      <c r="B18" s="356" t="s">
         <v>359</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+      <c r="C18" s="356"/>
+      <c r="D18" s="356"/>
+      <c r="E18" s="356"/>
+      <c r="F18" s="356"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4595,22 +4595,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="358" t="s">
+      <c r="B36" s="356" t="s">
         <v>360</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
+      <c r="C36" s="356"/>
+      <c r="D36" s="356"/>
+      <c r="E36" s="356"/>
+      <c r="F36" s="356"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="361" t="s">
+      <c r="B37" s="358" t="s">
         <v>339</v>
       </c>
-      <c r="C37" s="361"/>
-      <c r="D37" s="361"/>
-      <c r="E37" s="361"/>
-      <c r="F37" s="361"/>
+      <c r="C37" s="358"/>
+      <c r="D37" s="358"/>
+      <c r="E37" s="358"/>
+      <c r="F37" s="358"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4622,13 +4622,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="359" t="s">
+      <c r="B40" s="357" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+      <c r="C40" s="357"/>
+      <c r="D40" s="357"/>
+      <c r="E40" s="357"/>
+      <c r="F40" s="357"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4648,13 +4648,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="359" t="s">
+      <c r="B43" s="357" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+      <c r="C43" s="357"/>
+      <c r="D43" s="357"/>
+      <c r="E43" s="357"/>
+      <c r="F43" s="357"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4683,13 +4683,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+      <c r="B47" s="357" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="C47" s="357"/>
+      <c r="D47" s="357"/>
+      <c r="E47" s="357"/>
+      <c r="F47" s="357"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4705,13 +4705,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+      <c r="B50" s="357" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="C50" s="357"/>
+      <c r="D50" s="357"/>
+      <c r="E50" s="357"/>
+      <c r="F50" s="357"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4775,13 +4775,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+      <c r="B58" s="357" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="C58" s="357"/>
+      <c r="D58" s="357"/>
+      <c r="E58" s="357"/>
+      <c r="F58" s="357"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4797,7 +4797,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+      <c r="B61" s="357" t="s">
         <v>338</v>
       </c>
       <c r="C61" s="360"/>
@@ -4819,22 +4819,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="358" t="s">
+      <c r="B64" s="356" t="s">
         <v>343</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
+      <c r="C64" s="356"/>
+      <c r="D64" s="356"/>
+      <c r="E64" s="356"/>
+      <c r="F64" s="356"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="B65" s="356" t="s">
         <v>361</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+      <c r="C65" s="356"/>
+      <c r="D65" s="356"/>
+      <c r="E65" s="356"/>
+      <c r="F65" s="356"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4969,22 +4969,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="356" t="s">
         <v>362</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="C80" s="356"/>
+      <c r="D80" s="356"/>
+      <c r="E80" s="356"/>
+      <c r="F80" s="356"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="361" t="s">
+      <c r="B81" s="358" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="361"/>
-      <c r="D81" s="361"/>
-      <c r="E81" s="361"/>
-      <c r="F81" s="361"/>
+      <c r="C81" s="358"/>
+      <c r="D81" s="358"/>
+      <c r="E81" s="358"/>
+      <c r="F81" s="358"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5028,22 +5028,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="358" t="s">
+      <c r="B89" s="356" t="s">
         <v>363</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
+      <c r="C89" s="356"/>
+      <c r="D89" s="356"/>
+      <c r="E89" s="356"/>
+      <c r="F89" s="356"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="B90" s="356" t="s">
         <v>364</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+      <c r="C90" s="356"/>
+      <c r="D90" s="356"/>
+      <c r="E90" s="356"/>
+      <c r="F90" s="356"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5080,13 +5080,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+      <c r="B97" s="356" t="s">
         <v>365</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="C97" s="356"/>
+      <c r="D97" s="356"/>
+      <c r="E97" s="356"/>
+      <c r="F97" s="356"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5099,13 +5099,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="358" t="s">
+      <c r="B101" s="356" t="s">
         <v>344</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+      <c r="C101" s="356"/>
+      <c r="D101" s="356"/>
+      <c r="E101" s="356"/>
+      <c r="F101" s="356"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5227,13 +5227,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="358" t="s">
+      <c r="B116" s="356" t="s">
         <v>366</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+      <c r="C116" s="356"/>
+      <c r="D116" s="356"/>
+      <c r="E116" s="356"/>
+      <c r="F116" s="356"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5272,13 +5272,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="359" t="s">
+      <c r="B123" s="357" t="s">
         <v>367</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+      <c r="C123" s="357"/>
+      <c r="D123" s="357"/>
+      <c r="E123" s="357"/>
+      <c r="F123" s="357"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5421,13 +5421,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="362" t="s">
+      <c r="B134" s="361" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="362"/>
-      <c r="D134" s="362"/>
-      <c r="E134" s="362"/>
-      <c r="F134" s="362"/>
+      <c r="C134" s="361"/>
+      <c r="D134" s="361"/>
+      <c r="E134" s="361"/>
+      <c r="F134" s="361"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5440,22 +5440,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="363" t="s">
+      <c r="B138" s="359" t="s">
         <v>368</v>
       </c>
-      <c r="C138" s="363"/>
-      <c r="D138" s="363"/>
-      <c r="E138" s="363"/>
-      <c r="F138" s="363"/>
+      <c r="C138" s="359"/>
+      <c r="D138" s="359"/>
+      <c r="E138" s="359"/>
+      <c r="F138" s="359"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="B139" s="356" t="s">
         <v>369</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="C139" s="356"/>
+      <c r="D139" s="356"/>
+      <c r="E139" s="356"/>
+      <c r="F139" s="356"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5788,13 +5788,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="357" t="s">
+      <c r="B179" s="363" t="s">
         <v>376</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="C179" s="356"/>
+      <c r="D179" s="356"/>
+      <c r="E179" s="356"/>
+      <c r="F179" s="356"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5831,13 +5831,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+      <c r="B188" s="357" t="s">
         <v>381</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="C188" s="357"/>
+      <c r="D188" s="357"/>
+      <c r="E188" s="357"/>
+      <c r="F188" s="357"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5845,22 +5845,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="356" t="s">
+      <c r="B191" s="362" t="s">
         <v>382</v>
       </c>
-      <c r="C191" s="356"/>
-      <c r="D191" s="356"/>
-      <c r="E191" s="356"/>
-      <c r="F191" s="356"/>
+      <c r="C191" s="362"/>
+      <c r="D191" s="362"/>
+      <c r="E191" s="362"/>
+      <c r="F191" s="362"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="356" t="s">
+      <c r="B192" s="362" t="s">
         <v>383</v>
       </c>
-      <c r="C192" s="356"/>
-      <c r="D192" s="356"/>
-      <c r="E192" s="356"/>
-      <c r="F192" s="356"/>
+      <c r="C192" s="362"/>
+      <c r="D192" s="362"/>
+      <c r="E192" s="362"/>
+      <c r="F192" s="362"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5884,6 +5884,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5900,17 +5911,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">

--- a/financial_models/opportunities/300481.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/300481.SZ_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD1F2FD5-5B6E-4F09-B242-9E811FAEA46A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64D222EB-A403-4F94-996C-045E3FC8813D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1837" yWindow="1837" windowWidth="12691" windowHeight="7643" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3891,29 +3891,29 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4331,7 +4331,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>13.31</v>
+        <v>13.26</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4352,7 +4352,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>3884.5958797800004</v>
+        <v>3870.0031078800002</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4389,13 +4389,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="356" t="s">
+      <c r="B18" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C18" s="356"/>
-      <c r="D18" s="356"/>
-      <c r="E18" s="356"/>
-      <c r="F18" s="356"/>
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4478,7 +4478,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>-5.0551725042324858E-2</v>
+        <v>-4.9320107050515705E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4595,22 +4595,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="356" t="s">
+      <c r="B36" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C36" s="356"/>
-      <c r="D36" s="356"/>
-      <c r="E36" s="356"/>
-      <c r="F36" s="356"/>
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="358" t="s">
+      <c r="B37" s="361" t="s">
         <v>339</v>
       </c>
-      <c r="C37" s="358"/>
-      <c r="D37" s="358"/>
-      <c r="E37" s="358"/>
-      <c r="F37" s="358"/>
+      <c r="C37" s="361"/>
+      <c r="D37" s="361"/>
+      <c r="E37" s="361"/>
+      <c r="F37" s="361"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4622,13 +4622,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="357" t="s">
+      <c r="B40" s="359" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="357"/>
-      <c r="D40" s="357"/>
-      <c r="E40" s="357"/>
-      <c r="F40" s="357"/>
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4648,13 +4648,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="357" t="s">
+      <c r="B43" s="359" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="357"/>
-      <c r="D43" s="357"/>
-      <c r="E43" s="357"/>
-      <c r="F43" s="357"/>
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4683,13 +4683,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="357" t="s">
+      <c r="B47" s="359" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="357"/>
-      <c r="D47" s="357"/>
-      <c r="E47" s="357"/>
-      <c r="F47" s="357"/>
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4705,13 +4705,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="357" t="s">
+      <c r="B50" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="357"/>
-      <c r="D50" s="357"/>
-      <c r="E50" s="357"/>
-      <c r="F50" s="357"/>
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4775,13 +4775,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="357" t="s">
+      <c r="B58" s="359" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="357"/>
-      <c r="D58" s="357"/>
-      <c r="E58" s="357"/>
-      <c r="F58" s="357"/>
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4797,7 +4797,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="357" t="s">
+      <c r="B61" s="359" t="s">
         <v>338</v>
       </c>
       <c r="C61" s="360"/>
@@ -4819,22 +4819,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="356" t="s">
+      <c r="B64" s="358" t="s">
         <v>343</v>
       </c>
-      <c r="C64" s="356"/>
-      <c r="D64" s="356"/>
-      <c r="E64" s="356"/>
-      <c r="F64" s="356"/>
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="356" t="s">
+      <c r="B65" s="358" t="s">
         <v>361</v>
       </c>
-      <c r="C65" s="356"/>
-      <c r="D65" s="356"/>
-      <c r="E65" s="356"/>
-      <c r="F65" s="356"/>
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>3.3331342594402097E-2</v>
+        <v>3.345702639000693E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4878,7 +4878,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>3.005259203606311E-2</v>
+        <v>3.0165912518853699E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>448</v>
@@ -4969,22 +4969,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="356" t="s">
+      <c r="B80" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C80" s="356"/>
-      <c r="D80" s="356"/>
-      <c r="E80" s="356"/>
-      <c r="F80" s="356"/>
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="358" t="s">
+      <c r="B81" s="361" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="358"/>
-      <c r="D81" s="358"/>
-      <c r="E81" s="358"/>
-      <c r="F81" s="358"/>
+      <c r="C81" s="361"/>
+      <c r="D81" s="361"/>
+      <c r="E81" s="361"/>
+      <c r="F81" s="361"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5028,22 +5028,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="356" t="s">
+      <c r="B89" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C89" s="356"/>
-      <c r="D89" s="356"/>
-      <c r="E89" s="356"/>
-      <c r="F89" s="356"/>
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="356" t="s">
+      <c r="B90" s="358" t="s">
         <v>364</v>
       </c>
-      <c r="C90" s="356"/>
-      <c r="D90" s="356"/>
-      <c r="E90" s="356"/>
-      <c r="F90" s="356"/>
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5080,13 +5080,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="356" t="s">
+      <c r="B97" s="358" t="s">
         <v>365</v>
       </c>
-      <c r="C97" s="356"/>
-      <c r="D97" s="356"/>
-      <c r="E97" s="356"/>
-      <c r="F97" s="356"/>
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5099,13 +5099,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="356" t="s">
+      <c r="B101" s="358" t="s">
         <v>344</v>
       </c>
-      <c r="C101" s="356"/>
-      <c r="D101" s="356"/>
-      <c r="E101" s="356"/>
-      <c r="F101" s="356"/>
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5227,13 +5227,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="356" t="s">
+      <c r="B116" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C116" s="356"/>
-      <c r="D116" s="356"/>
-      <c r="E116" s="356"/>
-      <c r="F116" s="356"/>
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5272,13 +5272,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="357" t="s">
+      <c r="B123" s="359" t="s">
         <v>367</v>
       </c>
-      <c r="C123" s="357"/>
-      <c r="D123" s="357"/>
-      <c r="E123" s="357"/>
-      <c r="F123" s="357"/>
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5421,13 +5421,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="361" t="s">
+      <c r="B134" s="362" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="361"/>
-      <c r="D134" s="361"/>
-      <c r="E134" s="361"/>
-      <c r="F134" s="361"/>
+      <c r="C134" s="362"/>
+      <c r="D134" s="362"/>
+      <c r="E134" s="362"/>
+      <c r="F134" s="362"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5440,22 +5440,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="359" t="s">
+      <c r="B138" s="363" t="s">
         <v>368</v>
       </c>
-      <c r="C138" s="359"/>
-      <c r="D138" s="359"/>
-      <c r="E138" s="359"/>
-      <c r="F138" s="359"/>
+      <c r="C138" s="363"/>
+      <c r="D138" s="363"/>
+      <c r="E138" s="363"/>
+      <c r="F138" s="363"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="356" t="s">
+      <c r="B139" s="358" t="s">
         <v>369</v>
       </c>
-      <c r="C139" s="356"/>
-      <c r="D139" s="356"/>
-      <c r="E139" s="356"/>
-      <c r="F139" s="356"/>
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5788,13 +5788,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="363" t="s">
+      <c r="B179" s="357" t="s">
         <v>376</v>
       </c>
-      <c r="C179" s="356"/>
-      <c r="D179" s="356"/>
-      <c r="E179" s="356"/>
-      <c r="F179" s="356"/>
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5831,13 +5831,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="357" t="s">
+      <c r="B188" s="359" t="s">
         <v>381</v>
       </c>
-      <c r="C188" s="357"/>
-      <c r="D188" s="357"/>
-      <c r="E188" s="357"/>
-      <c r="F188" s="357"/>
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5845,22 +5845,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="362" t="s">
+      <c r="B191" s="356" t="s">
         <v>382</v>
       </c>
-      <c r="C191" s="362"/>
-      <c r="D191" s="362"/>
-      <c r="E191" s="362"/>
-      <c r="F191" s="362"/>
+      <c r="C191" s="356"/>
+      <c r="D191" s="356"/>
+      <c r="E191" s="356"/>
+      <c r="F191" s="356"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="362" t="s">
+      <c r="B192" s="356" t="s">
         <v>383</v>
       </c>
-      <c r="C192" s="362"/>
-      <c r="D192" s="362"/>
-      <c r="E192" s="362"/>
-      <c r="F192" s="362"/>
+      <c r="C192" s="356"/>
+      <c r="D192" s="356"/>
+      <c r="E192" s="356"/>
+      <c r="F192" s="356"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5884,17 +5884,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5911,6 +5900,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13480,32 +13480,32 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>3.005259203606311E-2</v>
+        <v>3.0165912518853699E-2</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>3.005259203606311E-2</v>
+        <v>3.0165912518853699E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>3.005259203606311E-2</v>
+        <v>3.0165912518853699E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>3.005259203606311E-2</v>
+        <v>3.0165912518853699E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
-        <v>3.005259203606311E-2</v>
+        <v>3.0165912518853699E-2</v>
       </c>
       <c r="K93" s="23">
         <f t="shared" si="39"/>
-        <v>1.5026296018031555E-2</v>
+        <v>1.508295625942685E-2</v>
       </c>
       <c r="L93" s="23">
         <f t="shared" si="39"/>
-        <v>1.5026296018031555E-2</v>
+        <v>1.508295625942685E-2</v>
       </c>
       <c r="M93" s="23">
         <f t="shared" si="39"/>
@@ -14679,50 +14679,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>3.3331342594402097E-2</v>
+        <v>3.345702639000693E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>3.7980927084817873E-2</v>
+        <v>3.8124143250296068E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>4.9945752550598695E-2</v>
+        <v>5.0134084950864903E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>9.8236301655728941E-2</v>
+        <v>9.8606725115969254E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>6.361449337467763E-2</v>
+        <v>6.385436702993659E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>4.7570747805350651E-2</v>
+        <v>4.7750124682444738E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>3.9520673234527424E-2</v>
+        <v>3.9669695380962294E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>2.7868481713414866E-2</v>
+        <v>2.7973566486089885E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>2.5333967816897719E-2</v>
+        <v>2.5429495599012721E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>1.6761235921325095E-2</v>
+        <v>1.6824438168388918E-2</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>1.6388858705067035E-2</v>
+        <v>1.6450656814814651E-2</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14736,43 +14736,43 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.930504740453133E-2</v>
+        <v>4.9490963872874209E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.0515712901727491E-2</v>
+        <v>6.0743901864403683E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10868616789654602</v>
+        <v>0.1090959950756431</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.4971899989322388E-2</v>
+        <v>6.5216892070730101E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.5989664441006849E-2</v>
+        <v>4.6163079465294209E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.7254962544056469E-2</v>
+        <v>3.7395441286681118E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.7221966781777265E-2</v>
+        <v>2.7324613715343546E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.8948206268542045E-2</v>
+        <v>1.9019655010127801E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.662620797601674E-2</v>
+        <v>1.6688901067932339E-2</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.47993783083701E-2</v>
+        <v>1.4855182902293065E-2</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18722,7 +18722,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-13.31</v>
+        <v>-13.26</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18962,7 +18962,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>13.31</v>
+        <v>13.26</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19560,7 +19560,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>13.31</v>
+        <v>13.26</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19573,7 +19573,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>-5.0551725042324858E-2</v>
+        <v>-4.9320107050515705E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/300481.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/300481.SZ_Valuation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64D222EB-A403-4F94-996C-045E3FC8813D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{059D7CC3-80A2-4AE1-84AE-C7098CD69371}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1837" yWindow="1837" windowWidth="12691" windowHeight="7643" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3891,29 +3891,29 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4331,7 +4331,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>13.26</v>
+        <v>13.38</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4352,7 +4352,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>3870.0031078800002</v>
+        <v>3905.0257604399999</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4389,13 +4389,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="358" t="s">
+      <c r="B18" s="356" t="s">
         <v>359</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+      <c r="C18" s="356"/>
+      <c r="D18" s="356"/>
+      <c r="E18" s="356"/>
+      <c r="F18" s="356"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4478,7 +4478,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>-4.9320107050515705E-2</v>
+        <v>-5.2265440895660209E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4595,22 +4595,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="358" t="s">
+      <c r="B36" s="356" t="s">
         <v>360</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
+      <c r="C36" s="356"/>
+      <c r="D36" s="356"/>
+      <c r="E36" s="356"/>
+      <c r="F36" s="356"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="361" t="s">
+      <c r="B37" s="358" t="s">
         <v>339</v>
       </c>
-      <c r="C37" s="361"/>
-      <c r="D37" s="361"/>
-      <c r="E37" s="361"/>
-      <c r="F37" s="361"/>
+      <c r="C37" s="358"/>
+      <c r="D37" s="358"/>
+      <c r="E37" s="358"/>
+      <c r="F37" s="358"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4622,13 +4622,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="359" t="s">
+      <c r="B40" s="357" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+      <c r="C40" s="357"/>
+      <c r="D40" s="357"/>
+      <c r="E40" s="357"/>
+      <c r="F40" s="357"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4648,13 +4648,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="359" t="s">
+      <c r="B43" s="357" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+      <c r="C43" s="357"/>
+      <c r="D43" s="357"/>
+      <c r="E43" s="357"/>
+      <c r="F43" s="357"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4683,13 +4683,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+      <c r="B47" s="357" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="C47" s="357"/>
+      <c r="D47" s="357"/>
+      <c r="E47" s="357"/>
+      <c r="F47" s="357"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4705,13 +4705,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+      <c r="B50" s="357" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="C50" s="357"/>
+      <c r="D50" s="357"/>
+      <c r="E50" s="357"/>
+      <c r="F50" s="357"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4775,13 +4775,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+      <c r="B58" s="357" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="C58" s="357"/>
+      <c r="D58" s="357"/>
+      <c r="E58" s="357"/>
+      <c r="F58" s="357"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4797,7 +4797,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+      <c r="B61" s="357" t="s">
         <v>338</v>
       </c>
       <c r="C61" s="360"/>
@@ -4819,22 +4819,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="358" t="s">
+      <c r="B64" s="356" t="s">
         <v>343</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
+      <c r="C64" s="356"/>
+      <c r="D64" s="356"/>
+      <c r="E64" s="356"/>
+      <c r="F64" s="356"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="B65" s="356" t="s">
         <v>361</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+      <c r="C65" s="356"/>
+      <c r="D65" s="356"/>
+      <c r="E65" s="356"/>
+      <c r="F65" s="356"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>3.345702639000693E-2</v>
+        <v>3.3156963373056195E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4878,7 +4878,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>3.0165912518853699E-2</v>
+        <v>2.9895366218236172E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>448</v>
@@ -4969,22 +4969,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="356" t="s">
         <v>362</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="C80" s="356"/>
+      <c r="D80" s="356"/>
+      <c r="E80" s="356"/>
+      <c r="F80" s="356"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="361" t="s">
+      <c r="B81" s="358" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="361"/>
-      <c r="D81" s="361"/>
-      <c r="E81" s="361"/>
-      <c r="F81" s="361"/>
+      <c r="C81" s="358"/>
+      <c r="D81" s="358"/>
+      <c r="E81" s="358"/>
+      <c r="F81" s="358"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5028,22 +5028,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="358" t="s">
+      <c r="B89" s="356" t="s">
         <v>363</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
+      <c r="C89" s="356"/>
+      <c r="D89" s="356"/>
+      <c r="E89" s="356"/>
+      <c r="F89" s="356"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="B90" s="356" t="s">
         <v>364</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+      <c r="C90" s="356"/>
+      <c r="D90" s="356"/>
+      <c r="E90" s="356"/>
+      <c r="F90" s="356"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5080,13 +5080,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+      <c r="B97" s="356" t="s">
         <v>365</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="C97" s="356"/>
+      <c r="D97" s="356"/>
+      <c r="E97" s="356"/>
+      <c r="F97" s="356"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5099,13 +5099,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="358" t="s">
+      <c r="B101" s="356" t="s">
         <v>344</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+      <c r="C101" s="356"/>
+      <c r="D101" s="356"/>
+      <c r="E101" s="356"/>
+      <c r="F101" s="356"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5227,13 +5227,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="358" t="s">
+      <c r="B116" s="356" t="s">
         <v>366</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+      <c r="C116" s="356"/>
+      <c r="D116" s="356"/>
+      <c r="E116" s="356"/>
+      <c r="F116" s="356"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5272,13 +5272,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="359" t="s">
+      <c r="B123" s="357" t="s">
         <v>367</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+      <c r="C123" s="357"/>
+      <c r="D123" s="357"/>
+      <c r="E123" s="357"/>
+      <c r="F123" s="357"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5421,13 +5421,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="362" t="s">
+      <c r="B134" s="361" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="362"/>
-      <c r="D134" s="362"/>
-      <c r="E134" s="362"/>
-      <c r="F134" s="362"/>
+      <c r="C134" s="361"/>
+      <c r="D134" s="361"/>
+      <c r="E134" s="361"/>
+      <c r="F134" s="361"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5440,22 +5440,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="363" t="s">
+      <c r="B138" s="359" t="s">
         <v>368</v>
       </c>
-      <c r="C138" s="363"/>
-      <c r="D138" s="363"/>
-      <c r="E138" s="363"/>
-      <c r="F138" s="363"/>
+      <c r="C138" s="359"/>
+      <c r="D138" s="359"/>
+      <c r="E138" s="359"/>
+      <c r="F138" s="359"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="B139" s="356" t="s">
         <v>369</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="C139" s="356"/>
+      <c r="D139" s="356"/>
+      <c r="E139" s="356"/>
+      <c r="F139" s="356"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5788,13 +5788,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="357" t="s">
+      <c r="B179" s="363" t="s">
         <v>376</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="C179" s="356"/>
+      <c r="D179" s="356"/>
+      <c r="E179" s="356"/>
+      <c r="F179" s="356"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5831,13 +5831,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+      <c r="B188" s="357" t="s">
         <v>381</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="C188" s="357"/>
+      <c r="D188" s="357"/>
+      <c r="E188" s="357"/>
+      <c r="F188" s="357"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5845,22 +5845,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="356" t="s">
+      <c r="B191" s="362" t="s">
         <v>382</v>
       </c>
-      <c r="C191" s="356"/>
-      <c r="D191" s="356"/>
-      <c r="E191" s="356"/>
-      <c r="F191" s="356"/>
+      <c r="C191" s="362"/>
+      <c r="D191" s="362"/>
+      <c r="E191" s="362"/>
+      <c r="F191" s="362"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="356" t="s">
+      <c r="B192" s="362" t="s">
         <v>383</v>
       </c>
-      <c r="C192" s="356"/>
-      <c r="D192" s="356"/>
-      <c r="E192" s="356"/>
-      <c r="F192" s="356"/>
+      <c r="C192" s="362"/>
+      <c r="D192" s="362"/>
+      <c r="E192" s="362"/>
+      <c r="F192" s="362"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5884,6 +5884,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5900,17 +5911,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13480,32 +13480,32 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>3.0165912518853699E-2</v>
+        <v>2.9895366218236172E-2</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>3.0165912518853699E-2</v>
+        <v>2.9895366218236172E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>3.0165912518853699E-2</v>
+        <v>2.9895366218236172E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>3.0165912518853699E-2</v>
+        <v>2.9895366218236172E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
-        <v>3.0165912518853699E-2</v>
+        <v>2.9895366218236172E-2</v>
       </c>
       <c r="K93" s="23">
         <f t="shared" si="39"/>
-        <v>1.508295625942685E-2</v>
+        <v>1.4947683109118086E-2</v>
       </c>
       <c r="L93" s="23">
         <f t="shared" si="39"/>
-        <v>1.508295625942685E-2</v>
+        <v>1.4947683109118086E-2</v>
       </c>
       <c r="M93" s="23">
         <f t="shared" si="39"/>
@@ -14679,50 +14679,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>3.345702639000693E-2</v>
+        <v>3.3156963373056195E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>3.8124143250296068E-2</v>
+        <v>3.7782222683028839E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>5.0134084950864903E-2</v>
+        <v>4.9684451901978219E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>9.8606725115969254E-2</v>
+        <v>9.7722359868292391E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>6.385436702993659E-2</v>
+        <v>6.3281682123838501E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>4.7750124682444738E-2</v>
+        <v>4.7321872443140296E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>3.9669695380962294E-2</v>
+        <v>3.931391335960837E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>2.7973566486089885E-2</v>
+        <v>2.7722682481730335E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>2.5429495599012721E-2</v>
+        <v>2.5201428373909464E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>1.6824438168388918E-2</v>
+        <v>1.6673546346250897E-2</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>1.6450656814814651E-2</v>
+        <v>1.6303117291811827E-2</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14736,43 +14736,43 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.9490963872874209E-2</v>
+        <v>4.9047098726032287E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.0743901864403683E-2</v>
+        <v>6.0199113506875401E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1090959950756431</v>
+        <v>0.10811755565792433</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.5216892070730101E-2</v>
+        <v>6.4631987209109204E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.6163079465294209E-2</v>
+        <v>4.5749060815381257E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.7395441286681118E-2</v>
+        <v>3.7060056163033754E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.7324613715343546E-2</v>
+        <v>2.7079549915205937E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.9019655010127801E-2</v>
+        <v>1.8849075144566116E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.6688901067932339E-2</v>
+        <v>1.6539224825170614E-2</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.4855182902293065E-2</v>
+        <v>1.4721952562362185E-2</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18722,7 +18722,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-13.26</v>
+        <v>-13.38</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18962,7 +18962,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>13.26</v>
+        <v>13.38</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19560,7 +19560,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>13.26</v>
+        <v>13.38</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19573,7 +19573,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>-4.9320107050515705E-2</v>
+        <v>-5.2265440895660209E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/300481.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/300481.SZ_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{059D7CC3-80A2-4AE1-84AE-C7098CD69371}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{167ABB71-F6D1-46FF-99D2-26B25B4A8751}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3891,29 +3891,29 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4331,7 +4331,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>13.38</v>
+        <v>13.56</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4352,7 +4352,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>3905.0257604399999</v>
+        <v>3957.55973928</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4389,13 +4389,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="356" t="s">
+      <c r="B18" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C18" s="356"/>
-      <c r="D18" s="356"/>
-      <c r="E18" s="356"/>
-      <c r="F18" s="356"/>
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4478,7 +4478,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>-5.2265440895660209E-2</v>
+        <v>-5.661661689545272E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4595,22 +4595,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="356" t="s">
+      <c r="B36" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C36" s="356"/>
-      <c r="D36" s="356"/>
-      <c r="E36" s="356"/>
-      <c r="F36" s="356"/>
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="358" t="s">
+      <c r="B37" s="361" t="s">
         <v>339</v>
       </c>
-      <c r="C37" s="358"/>
-      <c r="D37" s="358"/>
-      <c r="E37" s="358"/>
-      <c r="F37" s="358"/>
+      <c r="C37" s="361"/>
+      <c r="D37" s="361"/>
+      <c r="E37" s="361"/>
+      <c r="F37" s="361"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4622,13 +4622,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="357" t="s">
+      <c r="B40" s="359" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="357"/>
-      <c r="D40" s="357"/>
-      <c r="E40" s="357"/>
-      <c r="F40" s="357"/>
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4648,13 +4648,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="357" t="s">
+      <c r="B43" s="359" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="357"/>
-      <c r="D43" s="357"/>
-      <c r="E43" s="357"/>
-      <c r="F43" s="357"/>
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4683,13 +4683,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="357" t="s">
+      <c r="B47" s="359" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="357"/>
-      <c r="D47" s="357"/>
-      <c r="E47" s="357"/>
-      <c r="F47" s="357"/>
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4705,13 +4705,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="357" t="s">
+      <c r="B50" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="357"/>
-      <c r="D50" s="357"/>
-      <c r="E50" s="357"/>
-      <c r="F50" s="357"/>
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4775,13 +4775,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="357" t="s">
+      <c r="B58" s="359" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="357"/>
-      <c r="D58" s="357"/>
-      <c r="E58" s="357"/>
-      <c r="F58" s="357"/>
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4797,7 +4797,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="357" t="s">
+      <c r="B61" s="359" t="s">
         <v>338</v>
       </c>
       <c r="C61" s="360"/>
@@ -4819,22 +4819,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="356" t="s">
+      <c r="B64" s="358" t="s">
         <v>343</v>
       </c>
-      <c r="C64" s="356"/>
-      <c r="D64" s="356"/>
-      <c r="E64" s="356"/>
-      <c r="F64" s="356"/>
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="356" t="s">
+      <c r="B65" s="358" t="s">
         <v>361</v>
       </c>
-      <c r="C65" s="356"/>
-      <c r="D65" s="356"/>
-      <c r="E65" s="356"/>
-      <c r="F65" s="356"/>
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>3.3156963373056195E-2</v>
+        <v>3.271682669111297E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4878,7 +4878,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>2.9895366218236172E-2</v>
+        <v>2.9498525073746312E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>448</v>
@@ -4969,22 +4969,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="356" t="s">
+      <c r="B80" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C80" s="356"/>
-      <c r="D80" s="356"/>
-      <c r="E80" s="356"/>
-      <c r="F80" s="356"/>
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="358" t="s">
+      <c r="B81" s="361" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="358"/>
-      <c r="D81" s="358"/>
-      <c r="E81" s="358"/>
-      <c r="F81" s="358"/>
+      <c r="C81" s="361"/>
+      <c r="D81" s="361"/>
+      <c r="E81" s="361"/>
+      <c r="F81" s="361"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5028,22 +5028,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="356" t="s">
+      <c r="B89" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C89" s="356"/>
-      <c r="D89" s="356"/>
-      <c r="E89" s="356"/>
-      <c r="F89" s="356"/>
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="356" t="s">
+      <c r="B90" s="358" t="s">
         <v>364</v>
       </c>
-      <c r="C90" s="356"/>
-      <c r="D90" s="356"/>
-      <c r="E90" s="356"/>
-      <c r="F90" s="356"/>
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5080,13 +5080,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="356" t="s">
+      <c r="B97" s="358" t="s">
         <v>365</v>
       </c>
-      <c r="C97" s="356"/>
-      <c r="D97" s="356"/>
-      <c r="E97" s="356"/>
-      <c r="F97" s="356"/>
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5099,13 +5099,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="356" t="s">
+      <c r="B101" s="358" t="s">
         <v>344</v>
       </c>
-      <c r="C101" s="356"/>
-      <c r="D101" s="356"/>
-      <c r="E101" s="356"/>
-      <c r="F101" s="356"/>
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5227,13 +5227,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="356" t="s">
+      <c r="B116" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C116" s="356"/>
-      <c r="D116" s="356"/>
-      <c r="E116" s="356"/>
-      <c r="F116" s="356"/>
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5272,13 +5272,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="357" t="s">
+      <c r="B123" s="359" t="s">
         <v>367</v>
       </c>
-      <c r="C123" s="357"/>
-      <c r="D123" s="357"/>
-      <c r="E123" s="357"/>
-      <c r="F123" s="357"/>
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5421,13 +5421,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="361" t="s">
+      <c r="B134" s="362" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="361"/>
-      <c r="D134" s="361"/>
-      <c r="E134" s="361"/>
-      <c r="F134" s="361"/>
+      <c r="C134" s="362"/>
+      <c r="D134" s="362"/>
+      <c r="E134" s="362"/>
+      <c r="F134" s="362"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5440,22 +5440,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="359" t="s">
+      <c r="B138" s="363" t="s">
         <v>368</v>
       </c>
-      <c r="C138" s="359"/>
-      <c r="D138" s="359"/>
-      <c r="E138" s="359"/>
-      <c r="F138" s="359"/>
+      <c r="C138" s="363"/>
+      <c r="D138" s="363"/>
+      <c r="E138" s="363"/>
+      <c r="F138" s="363"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="356" t="s">
+      <c r="B139" s="358" t="s">
         <v>369</v>
       </c>
-      <c r="C139" s="356"/>
-      <c r="D139" s="356"/>
-      <c r="E139" s="356"/>
-      <c r="F139" s="356"/>
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5788,13 +5788,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="363" t="s">
+      <c r="B179" s="357" t="s">
         <v>376</v>
       </c>
-      <c r="C179" s="356"/>
-      <c r="D179" s="356"/>
-      <c r="E179" s="356"/>
-      <c r="F179" s="356"/>
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5831,13 +5831,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="357" t="s">
+      <c r="B188" s="359" t="s">
         <v>381</v>
       </c>
-      <c r="C188" s="357"/>
-      <c r="D188" s="357"/>
-      <c r="E188" s="357"/>
-      <c r="F188" s="357"/>
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5845,22 +5845,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="362" t="s">
+      <c r="B191" s="356" t="s">
         <v>382</v>
       </c>
-      <c r="C191" s="362"/>
-      <c r="D191" s="362"/>
-      <c r="E191" s="362"/>
-      <c r="F191" s="362"/>
+      <c r="C191" s="356"/>
+      <c r="D191" s="356"/>
+      <c r="E191" s="356"/>
+      <c r="F191" s="356"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="362" t="s">
+      <c r="B192" s="356" t="s">
         <v>383</v>
       </c>
-      <c r="C192" s="362"/>
-      <c r="D192" s="362"/>
-      <c r="E192" s="362"/>
-      <c r="F192" s="362"/>
+      <c r="C192" s="356"/>
+      <c r="D192" s="356"/>
+      <c r="E192" s="356"/>
+      <c r="F192" s="356"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5884,17 +5884,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5911,6 +5900,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13480,32 +13480,32 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>2.9895366218236172E-2</v>
+        <v>2.9498525073746312E-2</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>2.9895366218236172E-2</v>
+        <v>2.9498525073746312E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>2.9895366218236172E-2</v>
+        <v>2.9498525073746312E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>2.9895366218236172E-2</v>
+        <v>2.9498525073746312E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
-        <v>2.9895366218236172E-2</v>
+        <v>2.9498525073746312E-2</v>
       </c>
       <c r="K93" s="23">
         <f t="shared" si="39"/>
-        <v>1.4947683109118086E-2</v>
+        <v>1.4749262536873156E-2</v>
       </c>
       <c r="L93" s="23">
         <f t="shared" si="39"/>
-        <v>1.4947683109118086E-2</v>
+        <v>1.4749262536873156E-2</v>
       </c>
       <c r="M93" s="23">
         <f t="shared" si="39"/>
@@ -14679,50 +14679,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>3.3156963373056195E-2</v>
+        <v>3.271682669111297E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>3.7782222683028839E-2</v>
+        <v>3.7280688753608099E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>4.9684451901978219E-2</v>
+        <v>4.9024923779385589E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>9.7722359868292391E-2</v>
+        <v>9.6425160401014176E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>6.3281682123838501E-2</v>
+        <v>6.2441659794761004E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>4.7321872443140296E-2</v>
+        <v>4.6693705994780024E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>3.931391335960837E-2</v>
+        <v>3.8792047253064892E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>2.7722682481730335E-2</v>
+        <v>2.7354682271795862E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>2.5201428373909464E-2</v>
+        <v>2.4866896138857571E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>1.6673546346250897E-2</v>
+        <v>1.6452216085017481E-2</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>1.6303117291811827E-2</v>
+        <v>1.6086704230416096E-2</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14736,43 +14736,43 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.9047098726032287E-2</v>
+        <v>4.8396031043828322E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.0199113506875401E-2</v>
+        <v>5.9400010230235459E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10811755565792433</v>
+        <v>0.10668236686600498</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.4631987209109204E-2</v>
+        <v>6.3774040476244909E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.5749060815381257E-2</v>
+        <v>4.5141772397477964E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.7060056163033754E-2</v>
+        <v>3.6568108514851892E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.7079549915205937E-2</v>
+        <v>2.6720086863234176E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.8849075144566116E-2</v>
+        <v>1.8598866182470104E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.6539224825170614E-2</v>
+        <v>1.6319677592978081E-2</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.4721952562362185E-2</v>
+        <v>1.452652841330428E-2</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18722,7 +18722,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-13.38</v>
+        <v>-13.56</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18962,7 +18962,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>13.38</v>
+        <v>13.56</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19560,7 +19560,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>13.38</v>
+        <v>13.56</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19573,7 +19573,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>-5.2265440895660209E-2</v>
+        <v>-5.661661689545272E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/300481.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/300481.SZ_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{167ABB71-F6D1-46FF-99D2-26B25B4A8751}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF31A930-A489-4E24-B67C-D907F600B2E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3891,29 +3891,29 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4331,7 +4331,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>13.56</v>
+        <v>13.6</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4352,7 +4352,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>3957.55973928</v>
+        <v>3969.2339567999998</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4389,13 +4389,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="358" t="s">
+      <c r="B18" s="356" t="s">
         <v>359</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+      <c r="C18" s="356"/>
+      <c r="D18" s="356"/>
+      <c r="E18" s="356"/>
+      <c r="F18" s="356"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4478,7 +4478,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>-5.661661689545272E-2</v>
+        <v>-5.7572870899340045E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4595,22 +4595,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="358" t="s">
+      <c r="B36" s="356" t="s">
         <v>360</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
+      <c r="C36" s="356"/>
+      <c r="D36" s="356"/>
+      <c r="E36" s="356"/>
+      <c r="F36" s="356"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="361" t="s">
+      <c r="B37" s="358" t="s">
         <v>339</v>
       </c>
-      <c r="C37" s="361"/>
-      <c r="D37" s="361"/>
-      <c r="E37" s="361"/>
-      <c r="F37" s="361"/>
+      <c r="C37" s="358"/>
+      <c r="D37" s="358"/>
+      <c r="E37" s="358"/>
+      <c r="F37" s="358"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4622,13 +4622,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="359" t="s">
+      <c r="B40" s="357" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+      <c r="C40" s="357"/>
+      <c r="D40" s="357"/>
+      <c r="E40" s="357"/>
+      <c r="F40" s="357"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4648,13 +4648,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="359" t="s">
+      <c r="B43" s="357" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+      <c r="C43" s="357"/>
+      <c r="D43" s="357"/>
+      <c r="E43" s="357"/>
+      <c r="F43" s="357"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4683,13 +4683,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+      <c r="B47" s="357" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="C47" s="357"/>
+      <c r="D47" s="357"/>
+      <c r="E47" s="357"/>
+      <c r="F47" s="357"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4705,13 +4705,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+      <c r="B50" s="357" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="C50" s="357"/>
+      <c r="D50" s="357"/>
+      <c r="E50" s="357"/>
+      <c r="F50" s="357"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4775,13 +4775,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+      <c r="B58" s="357" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="C58" s="357"/>
+      <c r="D58" s="357"/>
+      <c r="E58" s="357"/>
+      <c r="F58" s="357"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4797,7 +4797,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+      <c r="B61" s="357" t="s">
         <v>338</v>
       </c>
       <c r="C61" s="360"/>
@@ -4819,22 +4819,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="358" t="s">
+      <c r="B64" s="356" t="s">
         <v>343</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
+      <c r="C64" s="356"/>
+      <c r="D64" s="356"/>
+      <c r="E64" s="356"/>
+      <c r="F64" s="356"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="B65" s="356" t="s">
         <v>361</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+      <c r="C65" s="356"/>
+      <c r="D65" s="356"/>
+      <c r="E65" s="356"/>
+      <c r="F65" s="356"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>3.271682669111297E-2</v>
+        <v>3.2620600730256757E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4878,7 +4878,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>2.9498525073746312E-2</v>
+        <v>2.9411764705882356E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>448</v>
@@ -4969,22 +4969,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="356" t="s">
         <v>362</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="C80" s="356"/>
+      <c r="D80" s="356"/>
+      <c r="E80" s="356"/>
+      <c r="F80" s="356"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="361" t="s">
+      <c r="B81" s="358" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="361"/>
-      <c r="D81" s="361"/>
-      <c r="E81" s="361"/>
-      <c r="F81" s="361"/>
+      <c r="C81" s="358"/>
+      <c r="D81" s="358"/>
+      <c r="E81" s="358"/>
+      <c r="F81" s="358"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5028,22 +5028,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="358" t="s">
+      <c r="B89" s="356" t="s">
         <v>363</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
+      <c r="C89" s="356"/>
+      <c r="D89" s="356"/>
+      <c r="E89" s="356"/>
+      <c r="F89" s="356"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="B90" s="356" t="s">
         <v>364</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+      <c r="C90" s="356"/>
+      <c r="D90" s="356"/>
+      <c r="E90" s="356"/>
+      <c r="F90" s="356"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5080,13 +5080,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+      <c r="B97" s="356" t="s">
         <v>365</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="C97" s="356"/>
+      <c r="D97" s="356"/>
+      <c r="E97" s="356"/>
+      <c r="F97" s="356"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5099,13 +5099,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="358" t="s">
+      <c r="B101" s="356" t="s">
         <v>344</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+      <c r="C101" s="356"/>
+      <c r="D101" s="356"/>
+      <c r="E101" s="356"/>
+      <c r="F101" s="356"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5227,13 +5227,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="358" t="s">
+      <c r="B116" s="356" t="s">
         <v>366</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+      <c r="C116" s="356"/>
+      <c r="D116" s="356"/>
+      <c r="E116" s="356"/>
+      <c r="F116" s="356"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5272,13 +5272,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="359" t="s">
+      <c r="B123" s="357" t="s">
         <v>367</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+      <c r="C123" s="357"/>
+      <c r="D123" s="357"/>
+      <c r="E123" s="357"/>
+      <c r="F123" s="357"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5421,13 +5421,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="362" t="s">
+      <c r="B134" s="361" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="362"/>
-      <c r="D134" s="362"/>
-      <c r="E134" s="362"/>
-      <c r="F134" s="362"/>
+      <c r="C134" s="361"/>
+      <c r="D134" s="361"/>
+      <c r="E134" s="361"/>
+      <c r="F134" s="361"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5440,22 +5440,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="363" t="s">
+      <c r="B138" s="359" t="s">
         <v>368</v>
       </c>
-      <c r="C138" s="363"/>
-      <c r="D138" s="363"/>
-      <c r="E138" s="363"/>
-      <c r="F138" s="363"/>
+      <c r="C138" s="359"/>
+      <c r="D138" s="359"/>
+      <c r="E138" s="359"/>
+      <c r="F138" s="359"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="B139" s="356" t="s">
         <v>369</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="C139" s="356"/>
+      <c r="D139" s="356"/>
+      <c r="E139" s="356"/>
+      <c r="F139" s="356"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5788,13 +5788,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="357" t="s">
+      <c r="B179" s="363" t="s">
         <v>376</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="C179" s="356"/>
+      <c r="D179" s="356"/>
+      <c r="E179" s="356"/>
+      <c r="F179" s="356"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5831,13 +5831,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+      <c r="B188" s="357" t="s">
         <v>381</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="C188" s="357"/>
+      <c r="D188" s="357"/>
+      <c r="E188" s="357"/>
+      <c r="F188" s="357"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5845,22 +5845,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="356" t="s">
+      <c r="B191" s="362" t="s">
         <v>382</v>
       </c>
-      <c r="C191" s="356"/>
-      <c r="D191" s="356"/>
-      <c r="E191" s="356"/>
-      <c r="F191" s="356"/>
+      <c r="C191" s="362"/>
+      <c r="D191" s="362"/>
+      <c r="E191" s="362"/>
+      <c r="F191" s="362"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="356" t="s">
+      <c r="B192" s="362" t="s">
         <v>383</v>
       </c>
-      <c r="C192" s="356"/>
-      <c r="D192" s="356"/>
-      <c r="E192" s="356"/>
-      <c r="F192" s="356"/>
+      <c r="C192" s="362"/>
+      <c r="D192" s="362"/>
+      <c r="E192" s="362"/>
+      <c r="F192" s="362"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5884,6 +5884,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5900,17 +5911,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13480,32 +13480,32 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>2.9498525073746312E-2</v>
+        <v>2.9411764705882356E-2</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>2.9498525073746312E-2</v>
+        <v>2.9411764705882356E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>2.9498525073746312E-2</v>
+        <v>2.9411764705882356E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>2.9498525073746312E-2</v>
+        <v>2.9411764705882356E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
-        <v>2.9498525073746312E-2</v>
+        <v>2.9411764705882356E-2</v>
       </c>
       <c r="K93" s="23">
         <f t="shared" si="39"/>
-        <v>1.4749262536873156E-2</v>
+        <v>1.4705882352941178E-2</v>
       </c>
       <c r="L93" s="23">
         <f t="shared" si="39"/>
-        <v>1.4749262536873156E-2</v>
+        <v>1.4705882352941178E-2</v>
       </c>
       <c r="M93" s="23">
         <f t="shared" si="39"/>
@@ -14679,50 +14679,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>3.271682669111297E-2</v>
+        <v>3.2620600730256757E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>3.7280688753608099E-2</v>
+        <v>3.7171039669038668E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>4.9024923779385589E-2</v>
+        <v>4.8880732827093286E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>9.6425160401014176E-2</v>
+        <v>9.6141556988070032E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>6.2441659794761004E-2</v>
+        <v>6.2258007854188176E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>4.6693705994780024E-2</v>
+        <v>4.6556371565383614E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>3.8792047253064892E-2</v>
+        <v>3.8677952996438239E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>2.7354682271795862E-2</v>
+        <v>2.7274227323937639E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>2.4866896138857571E-2</v>
+        <v>2.4793758209037401E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>1.6452216085017481E-2</v>
+        <v>1.6403827214179195E-2</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>1.6086704230416096E-2</v>
+        <v>1.6039390394444283E-2</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14736,43 +14736,43 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.8396031043828322E-2</v>
+        <v>4.8253689776052357E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.9400010230235459E-2</v>
+        <v>5.9225304317793603E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10668236686600498</v>
+        <v>0.10636859519875204</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.3774040476244909E-2</v>
+        <v>6.3586469768961845E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.5141772397477964E-2</v>
+        <v>4.5009002478661859E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.6568108514851892E-2</v>
+        <v>3.6460555254514096E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.6720086863234176E-2</v>
+        <v>2.6641498372459962E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.8598866182470104E-2</v>
+        <v>1.8544163634874607E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.6319677592978081E-2</v>
+        <v>1.6271678541234031E-2</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.452652841330428E-2</v>
+        <v>1.4483803329735739E-2</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18722,7 +18722,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-13.56</v>
+        <v>-13.6</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18962,7 +18962,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>13.56</v>
+        <v>13.6</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19560,7 +19560,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>13.56</v>
+        <v>13.6</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19573,7 +19573,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>-5.661661689545272E-2</v>
+        <v>-5.7572870899340045E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/300481.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/300481.SZ_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF31A930-A489-4E24-B67C-D907F600B2E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45125F39-C868-44A5-B1BC-A9C02540215A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3891,29 +3891,29 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4331,7 +4331,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>13.6</v>
+        <v>14.06</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4352,7 +4352,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>3969.2339567999998</v>
+        <v>4103.4874582800003</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4389,13 +4389,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="356" t="s">
+      <c r="B18" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C18" s="356"/>
-      <c r="D18" s="356"/>
-      <c r="E18" s="356"/>
-      <c r="F18" s="356"/>
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4478,7 +4478,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>-5.7572870899340045E-2</v>
+        <v>-6.8301555261349622E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4595,22 +4595,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="356" t="s">
+      <c r="B36" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C36" s="356"/>
-      <c r="D36" s="356"/>
-      <c r="E36" s="356"/>
-      <c r="F36" s="356"/>
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="358" t="s">
+      <c r="B37" s="361" t="s">
         <v>339</v>
       </c>
-      <c r="C37" s="358"/>
-      <c r="D37" s="358"/>
-      <c r="E37" s="358"/>
-      <c r="F37" s="358"/>
+      <c r="C37" s="361"/>
+      <c r="D37" s="361"/>
+      <c r="E37" s="361"/>
+      <c r="F37" s="361"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4622,13 +4622,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="357" t="s">
+      <c r="B40" s="359" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="357"/>
-      <c r="D40" s="357"/>
-      <c r="E40" s="357"/>
-      <c r="F40" s="357"/>
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4648,13 +4648,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="357" t="s">
+      <c r="B43" s="359" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="357"/>
-      <c r="D43" s="357"/>
-      <c r="E43" s="357"/>
-      <c r="F43" s="357"/>
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4683,13 +4683,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="357" t="s">
+      <c r="B47" s="359" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="357"/>
-      <c r="D47" s="357"/>
-      <c r="E47" s="357"/>
-      <c r="F47" s="357"/>
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4705,13 +4705,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="357" t="s">
+      <c r="B50" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="357"/>
-      <c r="D50" s="357"/>
-      <c r="E50" s="357"/>
-      <c r="F50" s="357"/>
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4775,13 +4775,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="357" t="s">
+      <c r="B58" s="359" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="357"/>
-      <c r="D58" s="357"/>
-      <c r="E58" s="357"/>
-      <c r="F58" s="357"/>
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4797,7 +4797,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="357" t="s">
+      <c r="B61" s="359" t="s">
         <v>338</v>
       </c>
       <c r="C61" s="360"/>
@@ -4819,22 +4819,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="356" t="s">
+      <c r="B64" s="358" t="s">
         <v>343</v>
       </c>
-      <c r="C64" s="356"/>
-      <c r="D64" s="356"/>
-      <c r="E64" s="356"/>
-      <c r="F64" s="356"/>
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="356" t="s">
+      <c r="B65" s="358" t="s">
         <v>361</v>
       </c>
-      <c r="C65" s="356"/>
-      <c r="D65" s="356"/>
-      <c r="E65" s="356"/>
-      <c r="F65" s="356"/>
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>3.2620600730256757E-2</v>
+        <v>3.1553354902666565E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4878,7 +4878,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>2.9411764705882356E-2</v>
+        <v>2.8449502133712661E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>448</v>
@@ -4969,22 +4969,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="356" t="s">
+      <c r="B80" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C80" s="356"/>
-      <c r="D80" s="356"/>
-      <c r="E80" s="356"/>
-      <c r="F80" s="356"/>
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="358" t="s">
+      <c r="B81" s="361" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="358"/>
-      <c r="D81" s="358"/>
-      <c r="E81" s="358"/>
-      <c r="F81" s="358"/>
+      <c r="C81" s="361"/>
+      <c r="D81" s="361"/>
+      <c r="E81" s="361"/>
+      <c r="F81" s="361"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5028,22 +5028,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="356" t="s">
+      <c r="B89" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C89" s="356"/>
-      <c r="D89" s="356"/>
-      <c r="E89" s="356"/>
-      <c r="F89" s="356"/>
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="356" t="s">
+      <c r="B90" s="358" t="s">
         <v>364</v>
       </c>
-      <c r="C90" s="356"/>
-      <c r="D90" s="356"/>
-      <c r="E90" s="356"/>
-      <c r="F90" s="356"/>
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5080,13 +5080,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="356" t="s">
+      <c r="B97" s="358" t="s">
         <v>365</v>
       </c>
-      <c r="C97" s="356"/>
-      <c r="D97" s="356"/>
-      <c r="E97" s="356"/>
-      <c r="F97" s="356"/>
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5099,13 +5099,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="356" t="s">
+      <c r="B101" s="358" t="s">
         <v>344</v>
       </c>
-      <c r="C101" s="356"/>
-      <c r="D101" s="356"/>
-      <c r="E101" s="356"/>
-      <c r="F101" s="356"/>
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5227,13 +5227,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="356" t="s">
+      <c r="B116" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C116" s="356"/>
-      <c r="D116" s="356"/>
-      <c r="E116" s="356"/>
-      <c r="F116" s="356"/>
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5272,13 +5272,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="357" t="s">
+      <c r="B123" s="359" t="s">
         <v>367</v>
       </c>
-      <c r="C123" s="357"/>
-      <c r="D123" s="357"/>
-      <c r="E123" s="357"/>
-      <c r="F123" s="357"/>
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5421,13 +5421,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="361" t="s">
+      <c r="B134" s="362" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="361"/>
-      <c r="D134" s="361"/>
-      <c r="E134" s="361"/>
-      <c r="F134" s="361"/>
+      <c r="C134" s="362"/>
+      <c r="D134" s="362"/>
+      <c r="E134" s="362"/>
+      <c r="F134" s="362"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5440,22 +5440,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="359" t="s">
+      <c r="B138" s="363" t="s">
         <v>368</v>
       </c>
-      <c r="C138" s="359"/>
-      <c r="D138" s="359"/>
-      <c r="E138" s="359"/>
-      <c r="F138" s="359"/>
+      <c r="C138" s="363"/>
+      <c r="D138" s="363"/>
+      <c r="E138" s="363"/>
+      <c r="F138" s="363"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="356" t="s">
+      <c r="B139" s="358" t="s">
         <v>369</v>
       </c>
-      <c r="C139" s="356"/>
-      <c r="D139" s="356"/>
-      <c r="E139" s="356"/>
-      <c r="F139" s="356"/>
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5788,13 +5788,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="363" t="s">
+      <c r="B179" s="357" t="s">
         <v>376</v>
       </c>
-      <c r="C179" s="356"/>
-      <c r="D179" s="356"/>
-      <c r="E179" s="356"/>
-      <c r="F179" s="356"/>
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5831,13 +5831,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="357" t="s">
+      <c r="B188" s="359" t="s">
         <v>381</v>
       </c>
-      <c r="C188" s="357"/>
-      <c r="D188" s="357"/>
-      <c r="E188" s="357"/>
-      <c r="F188" s="357"/>
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5845,22 +5845,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="362" t="s">
+      <c r="B191" s="356" t="s">
         <v>382</v>
       </c>
-      <c r="C191" s="362"/>
-      <c r="D191" s="362"/>
-      <c r="E191" s="362"/>
-      <c r="F191" s="362"/>
+      <c r="C191" s="356"/>
+      <c r="D191" s="356"/>
+      <c r="E191" s="356"/>
+      <c r="F191" s="356"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="362" t="s">
+      <c r="B192" s="356" t="s">
         <v>383</v>
       </c>
-      <c r="C192" s="362"/>
-      <c r="D192" s="362"/>
-      <c r="E192" s="362"/>
-      <c r="F192" s="362"/>
+      <c r="C192" s="356"/>
+      <c r="D192" s="356"/>
+      <c r="E192" s="356"/>
+      <c r="F192" s="356"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5884,17 +5884,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5911,6 +5900,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13480,32 +13480,32 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>2.9411764705882356E-2</v>
+        <v>2.8449502133712661E-2</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>2.9411764705882356E-2</v>
+        <v>2.8449502133712661E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>2.9411764705882356E-2</v>
+        <v>2.8449502133712661E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>2.9411764705882356E-2</v>
+        <v>2.8449502133712661E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
-        <v>2.9411764705882356E-2</v>
+        <v>2.8449502133712661E-2</v>
       </c>
       <c r="K93" s="23">
         <f t="shared" si="39"/>
-        <v>1.4705882352941178E-2</v>
+        <v>1.422475106685633E-2</v>
       </c>
       <c r="L93" s="23">
         <f t="shared" si="39"/>
-        <v>1.4705882352941178E-2</v>
+        <v>1.422475106685633E-2</v>
       </c>
       <c r="M93" s="23">
         <f t="shared" si="39"/>
@@ -14679,50 +14679,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>3.2620600730256757E-2</v>
+        <v>3.1553354902666565E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>3.7171039669038668E-2</v>
+        <v>3.5954917460805536E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>4.8880732827093286E-2</v>
+        <v>4.7281505437302175E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>9.6141556988070032E-2</v>
+        <v>9.2996100642798882E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>6.2258007854188176E-2</v>
+        <v>6.0221117127806485E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>4.6556371565383614E-2</v>
+        <v>4.5033190134368219E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>3.8677952996438239E-2</v>
+        <v>3.7412529214193455E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>2.7274227323937639E-2</v>
+        <v>2.6381898407222749E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>2.4793758209037401E-2</v>
+        <v>2.3982582620406021E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>1.6403827214179195E-2</v>
+        <v>1.586714438924872E-2</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>1.6039390394444283E-2</v>
+        <v>1.5514630822506561E-2</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14736,43 +14736,43 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.8253689776052357E-2</v>
+        <v>4.6674977308272546E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.9225304317793603E-2</v>
+        <v>5.7287634333000916E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10636859519875204</v>
+        <v>0.10288854158627507</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.3586469768961845E-2</v>
+        <v>6.1506115850489401E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.5009002478661859E-2</v>
+        <v>4.353644620980094E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.6460555254514096E-2</v>
+        <v>3.5267677913327994E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.6641498372459962E-2</v>
+        <v>2.5769870402948463E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.8544163634874607E-2</v>
+        <v>1.7937455578541581E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.6271678541234031E-2</v>
+        <v>1.5739319214849418E-2</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.4483803329735739E-2</v>
+        <v>1.4009937786942107E-2</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18722,7 +18722,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-13.6</v>
+        <v>-14.06</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18962,7 +18962,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>13.6</v>
+        <v>14.06</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19560,7 +19560,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>13.6</v>
+        <v>14.06</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19573,7 +19573,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>-5.7572870899340045E-2</v>
+        <v>-6.8301555261349622E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/300481.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/300481.SZ_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45125F39-C868-44A5-B1BC-A9C02540215A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CA40430-D100-4AEF-BFE2-4B79854C63C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -25,6 +25,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">DCF!$B$73:$H$73</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">DDM!$B$68:$H$68</definedName>
     <definedName name="Common_Shares">Thesis!$C$6</definedName>
+    <definedName name="dividend_tax_rate">Normalized_FCF!$C$93</definedName>
     <definedName name="Equity_Cost">Thesis!$C$86</definedName>
     <definedName name="Exchange_Rate">Thesis!$C$16</definedName>
     <definedName name="Market_currency">Thesis!$C$13</definedName>
@@ -47,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="685" uniqueCount="465">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="686" uniqueCount="465">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -465,10 +466,6 @@
   <si>
     <t>PV of FCFE</t>
     <phoneticPr fontId="28" type="noConversion"/>
-  </si>
-  <si>
-    <t>Annual Dividend per share</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>HGP</t>
@@ -1497,14 +1494,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Dividend/Market Cap =</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Dividend Yield</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Note of the formulas:</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2445,6 +2434,18 @@
     <t>LT AR and Prepayments</t>
   </si>
   <si>
+    <t>Dividend after tax Yield</t>
+  </si>
+  <si>
+    <t>Dividend tax rate</t>
+  </si>
+  <si>
+    <t>After tax Dividend/Market Cap =</t>
+  </si>
+  <si>
+    <t>After-tax Dividend per share</t>
+  </si>
+  <si>
     <t>CN</t>
   </si>
   <si>
@@ -2467,9 +2468,6 @@
   </si>
   <si>
     <t>Latest Asset Value</t>
-  </si>
-  <si>
-    <t>Notes</t>
   </si>
   <si>
     <t>Historical Average or D&amp;A</t>
@@ -3146,7 +3144,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="368">
+  <cellXfs count="370">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3891,6 +3889,10 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -4220,10 +4222,10 @@
   <dimension ref="A1:J197"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
   <cols>
-    <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="32.6640625" style="1" customWidth="1"/>
-    <col min="3" max="4" width="25.6640625" style="1" customWidth="1"/>
-    <col min="5" max="6" width="15.6640625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="2.73046875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="32.73046875" style="1" customWidth="1"/>
+    <col min="3" max="4" width="25.73046875" style="1" customWidth="1"/>
+    <col min="5" max="6" width="15.73046875" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -4235,18 +4237,18 @@
         <v>45797</v>
       </c>
       <c r="D1" s="316" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="E1" s="292" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="F1" s="254" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9">
       <c r="A2" s="222" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B2" s="36"/>
       <c r="C2" s="36"/>
@@ -4260,7 +4262,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="B4" s="45" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="C4" s="46"/>
       <c r="D4" s="5"/>
@@ -4269,10 +4271,10 @@
     </row>
     <row r="5" spans="1:10" ht="12.4">
       <c r="B5" s="4" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="C5" s="294" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -4286,7 +4288,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="B7" s="2" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C7" s="250">
         <v>6</v>
@@ -4296,7 +4298,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="B8" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C8" s="33">
         <f>EOMONTH(EDATE(BS!C1,C7+2),0)</f>
@@ -4309,20 +4311,20 @@
     </row>
     <row r="10" spans="1:10">
       <c r="B10" s="45" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="C10" s="46"/>
       <c r="E10" s="34"/>
     </row>
     <row r="11" spans="1:10">
       <c r="B11" s="1" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="C11" s="49" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D11" s="49" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="E11" s="34"/>
     </row>
@@ -4338,17 +4340,17 @@
     </row>
     <row r="13" spans="1:10">
       <c r="B13" s="1" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="C13" s="48" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="D13" s="48"/>
       <c r="E13" s="5"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="4" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
@@ -4362,7 +4364,7 @@
     </row>
     <row r="15" spans="1:10">
       <c r="B15" s="4" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="C15" s="32" t="str">
         <f>IF(C25=C13,C13,C25&amp;"/"&amp;C13)</f>
@@ -4388,35 +4390,35 @@
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
     </row>
-    <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="358" t="s">
-        <v>359</v>
-      </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+    <row r="18" spans="2:6" ht="24.6" customHeight="1">
+      <c r="B18" s="360" t="s">
+        <v>356</v>
+      </c>
+      <c r="C18" s="360"/>
+      <c r="D18" s="360"/>
+      <c r="E18" s="360"/>
+      <c r="F18" s="360"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C20" s="46"/>
       <c r="D20" s="5"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="2" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="C21" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
         <v xml:space="preserve">Low Growth </v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="E21" s="308" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="22" spans="2:6">
@@ -4424,7 +4426,7 @@
         <v>56</v>
       </c>
       <c r="C22" s="48" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D22" s="1" t="str">
         <f>IF(valuation_method="DDM","DDM Terminal Value","")</f>
@@ -4434,26 +4436,26 @@
     </row>
     <row r="23" spans="2:6">
       <c r="B23" s="1" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="C23" s="262" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="24" spans="2:6">
       <c r="B24" s="1" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="C24" s="262" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="25" spans="2:6">
       <c r="B25" s="4" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="C25" s="48" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="D25" s="32" t="str">
         <f>IF(D11="","",Market_currency&amp;"/"&amp;D13&amp;":")</f>
@@ -4474,11 +4476,11 @@
         <v>10.251430255232371</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>-6.8301555261349622E-2</v>
+        <v>-7.1459666738491467E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4487,7 +4489,7 @@
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="45" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="C28" s="309" t="str">
         <f>C145&amp;" ("&amp;Market_currency&amp;")"</f>
@@ -4498,7 +4500,7 @@
         <v/>
       </c>
       <c r="E28" s="305" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="F28" s="303">
         <v>3</v>
@@ -4506,37 +4508,37 @@
     </row>
     <row r="29" spans="2:6">
       <c r="B29" s="1" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="C29" s="310">
         <f>C149</f>
-        <v>4.9796479824958464</v>
+        <v>4.9106169541815241</v>
       </c>
       <c r="D29" s="310" t="str">
         <f>D149</f>
         <v/>
       </c>
       <c r="E29" s="306" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="F29" s="302">
-        <v>0.33699999999999997</v>
+        <v>0.33700000000000002</v>
       </c>
     </row>
     <row r="30" spans="2:6">
       <c r="B30" s="1" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="C30" s="311">
         <f>C157</f>
-        <v>6.9896525426428742</v>
+        <v>6.9036475281066911</v>
       </c>
       <c r="D30" s="311" t="str">
         <f>D157</f>
         <v/>
       </c>
       <c r="E30" s="307" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="F30" s="312">
         <v>0.187</v>
@@ -4544,18 +4546,18 @@
     </row>
     <row r="31" spans="2:6">
       <c r="B31" s="1" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="C31" s="311">
         <f>C165</f>
-        <v>9.6765033007385046</v>
+        <v>9.5695828227600401</v>
       </c>
       <c r="D31" s="311" t="str">
         <f>D165</f>
         <v/>
       </c>
       <c r="E31" s="307" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="F31" s="312">
         <v>0.06</v>
@@ -4563,18 +4565,18 @@
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="1" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="C32" s="311">
         <f>C173</f>
-        <v>8.9996639027078977</v>
+        <v>8.8978683003699235</v>
       </c>
       <c r="D32" s="311" t="str">
         <f>D173</f>
         <v/>
       </c>
       <c r="E32" s="307" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="F32" s="312">
         <v>8.6999999999999994E-2</v>
@@ -4586,7 +4588,7 @@
     </row>
     <row r="34" spans="1:6" ht="13.9">
       <c r="A34" s="222" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="B34" s="36"/>
       <c r="C34" s="36"/>
@@ -4594,45 +4596,45 @@
       <c r="E34" s="36"/>
       <c r="F34" s="36"/>
     </row>
-    <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="358" t="s">
-        <v>360</v>
-      </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
-    </row>
-    <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="361" t="s">
-        <v>339</v>
-      </c>
-      <c r="C37" s="361"/>
-      <c r="D37" s="361"/>
-      <c r="E37" s="361"/>
-      <c r="F37" s="361"/>
+    <row r="36" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B36" s="360" t="s">
+        <v>357</v>
+      </c>
+      <c r="C36" s="360"/>
+      <c r="D36" s="360"/>
+      <c r="E36" s="360"/>
+      <c r="F36" s="360"/>
+    </row>
+    <row r="37" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B37" s="363" t="s">
+        <v>336</v>
+      </c>
+      <c r="C37" s="363"/>
+      <c r="D37" s="363"/>
+      <c r="E37" s="363"/>
+      <c r="F37" s="363"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C39" s="108">
         <f>scaling_factor</f>
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="359" t="s">
-        <v>231</v>
-      </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+    <row r="40" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B40" s="361" t="s">
+        <v>230</v>
+      </c>
+      <c r="C40" s="361"/>
+      <c r="D40" s="361"/>
+      <c r="E40" s="361"/>
+      <c r="F40" s="361"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C41" s="349">
         <f>Normalized_FCF!C8</f>
@@ -4647,18 +4649,18 @@
       <c r="B42" s="47"/>
       <c r="C42" s="76"/>
     </row>
-    <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="359" t="s">
-        <v>233</v>
-      </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+    <row r="43" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B43" s="361" t="s">
+        <v>232</v>
+      </c>
+      <c r="C43" s="361"/>
+      <c r="D43" s="361"/>
+      <c r="E43" s="361"/>
+      <c r="F43" s="361"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C44" s="349">
         <f>Normalized_FCF!C9</f>
@@ -4671,7 +4673,7 @@
     </row>
     <row r="45" spans="1:6">
       <c r="B45" s="52" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C45" s="349">
         <f>Normalized_FCF!C10</f>
@@ -4683,17 +4685,17 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
-        <v>236</v>
-      </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="B47" s="361" t="s">
+        <v>235</v>
+      </c>
+      <c r="C47" s="361"/>
+      <c r="D47" s="361"/>
+      <c r="E47" s="361"/>
+      <c r="F47" s="361"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C48" s="349">
         <f>Normalized_FCF!C11</f>
@@ -4705,17 +4707,17 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
-        <v>240</v>
-      </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="B50" s="361" t="s">
+        <v>239</v>
+      </c>
+      <c r="C50" s="361"/>
+      <c r="D50" s="361"/>
+      <c r="E50" s="361"/>
+      <c r="F50" s="361"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="C51" s="350">
         <f>Normalized_FCF!C48</f>
@@ -4730,7 +4732,7 @@
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="47" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="C52" s="350">
         <f>Normalized_FCF!C47</f>
@@ -4745,7 +4747,7 @@
     </row>
     <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C53" s="349">
         <f>Normalized_FCF!C12</f>
@@ -4758,12 +4760,12 @@
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="47" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C56" s="349">
         <f>Normalized_FCF!C15</f>
@@ -4775,17 +4777,17 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
-        <v>241</v>
-      </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="B58" s="361" t="s">
+        <v>240</v>
+      </c>
+      <c r="C58" s="361"/>
+      <c r="D58" s="361"/>
+      <c r="E58" s="361"/>
+      <c r="F58" s="361"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C59" s="349">
         <f>Normalized_FCF!C14</f>
@@ -4797,17 +4799,17 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
-        <v>338</v>
-      </c>
-      <c r="C61" s="360"/>
-      <c r="D61" s="360"/>
-      <c r="E61" s="360"/>
-      <c r="F61" s="360"/>
+      <c r="B61" s="361" t="s">
+        <v>335</v>
+      </c>
+      <c r="C61" s="362"/>
+      <c r="D61" s="362"/>
+      <c r="E61" s="362"/>
+      <c r="F61" s="362"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C62" s="349">
         <f>Normalized_FCF!C17</f>
@@ -4818,27 +4820,27 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="358" t="s">
-        <v>343</v>
-      </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
-    </row>
-    <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="358" t="s">
-        <v>361</v>
-      </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+    <row r="64" spans="2:6" ht="24.6" customHeight="1">
+      <c r="B64" s="360" t="s">
+        <v>340</v>
+      </c>
+      <c r="C64" s="360"/>
+      <c r="D64" s="360"/>
+      <c r="E64" s="360"/>
+      <c r="F64" s="360"/>
+    </row>
+    <row r="65" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B65" s="360" t="s">
+        <v>358</v>
+      </c>
+      <c r="C65" s="360"/>
+      <c r="D65" s="360"/>
+      <c r="E65" s="360"/>
+      <c r="F65" s="360"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C67" s="349">
         <f>Normalized_FCF!G19</f>
@@ -4851,7 +4853,7 @@
     </row>
     <row r="68" spans="1:6">
       <c r="B68" s="47" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C68" s="349">
         <f>Normalized_FCF!C19</f>
@@ -4864,24 +4866,24 @@
     </row>
     <row r="69" spans="1:6">
       <c r="B69" s="227" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="C69" s="92">
-        <f>Normalized_FCF!C125</f>
+        <f>Normalized_FCF!C126</f>
         <v>3.1553354902666565E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
     <row r="70" spans="1:6">
       <c r="B70" s="227" t="s">
-        <v>308</v>
+        <v>454</v>
       </c>
       <c r="C70" s="92">
-        <f>Normalized_FCF!C93</f>
-        <v>2.8449502133712661E-2</v>
+        <f>Normalized_FCF!C94</f>
+        <v>2.5604551920341397E-2</v>
       </c>
       <c r="E70" s="47" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="F70" s="315">
         <f>Normalized_FCF!C92</f>
@@ -4890,73 +4892,73 @@
     </row>
     <row r="72" spans="1:6">
       <c r="B72" s="210" t="s">
+        <v>447</v>
+      </c>
+      <c r="C72" s="323" t="s">
+        <v>449</v>
+      </c>
+      <c r="D72" s="323" t="s">
         <v>450</v>
-      </c>
-      <c r="C72" s="323" t="s">
-        <v>452</v>
-      </c>
-      <c r="D72" s="323" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="73" spans="1:6">
       <c r="B73" s="47" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="C73" s="92">
-        <f>Normalized_FCF!C120</f>
+        <f>Normalized_FCF!C121</f>
         <v>7.1587241945726146E-2</v>
       </c>
       <c r="D73" s="92">
-        <f>Normalized_FCF!G120</f>
+        <f>Normalized_FCF!G121</f>
         <v>7.2897649409175577E-2</v>
       </c>
     </row>
     <row r="74" spans="1:6">
       <c r="B74" s="259" t="str">
-        <f>Normalized_FCF!B117</f>
+        <f>Normalized_FCF!B118</f>
         <v>Pre-tax Profit/Sales</v>
       </c>
       <c r="C74" s="322">
-        <f>Normalized_FCF!C117</f>
+        <f>Normalized_FCF!C118</f>
         <v>0.12235120428336442</v>
       </c>
       <c r="D74" s="322">
-        <f>Normalized_FCF!G117</f>
+        <f>Normalized_FCF!G118</f>
         <v>0.12459084820450472</v>
       </c>
     </row>
     <row r="75" spans="1:6">
       <c r="B75" s="259" t="str">
-        <f>Normalized_FCF!B118</f>
+        <f>Normalized_FCF!B119</f>
         <v>Sales/Total Assets</v>
       </c>
       <c r="C75" s="324">
-        <f>Normalized_FCF!C118</f>
+        <f>Normalized_FCF!C119</f>
         <v>0.50157874313934503</v>
       </c>
       <c r="D75" s="324">
-        <f>Normalized_FCF!G118</f>
+        <f>Normalized_FCF!G119</f>
         <v>0.50157874313934503</v>
       </c>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="259" t="str">
-        <f>Normalized_FCF!B119</f>
+        <f>Normalized_FCF!B120</f>
         <v>Total Assets/Equity</v>
       </c>
       <c r="C76" s="324">
-        <f>Normalized_FCF!C119</f>
+        <f>Normalized_FCF!C120</f>
         <v>1.1665094444773738</v>
       </c>
       <c r="D76" s="324">
-        <f>Normalized_FCF!G119</f>
+        <f>Normalized_FCF!G120</f>
         <v>1.1665094444773738</v>
       </c>
     </row>
     <row r="78" spans="1:6" ht="13.9">
       <c r="A78" s="222" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="B78" s="36"/>
       <c r="C78" s="36"/>
@@ -4967,33 +4969,33 @@
     <row r="79" spans="1:6">
       <c r="A79" s="209"/>
     </row>
-    <row r="80" spans="1:6" ht="24.5" customHeight="1">
+    <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
-        <v>362</v>
-      </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="B80" s="360" t="s">
+        <v>359</v>
+      </c>
+      <c r="C80" s="360"/>
+      <c r="D80" s="360"/>
+      <c r="E80" s="360"/>
+      <c r="F80" s="360"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="361" t="s">
-        <v>252</v>
-      </c>
-      <c r="C81" s="361"/>
-      <c r="D81" s="361"/>
-      <c r="E81" s="361"/>
-      <c r="F81" s="361"/>
+      <c r="B81" s="363" t="s">
+        <v>251</v>
+      </c>
+      <c r="C81" s="363"/>
+      <c r="D81" s="363"/>
+      <c r="E81" s="363"/>
+      <c r="F81" s="363"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="84" spans="1:6">
       <c r="B84" s="1" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="C84" s="92">
         <f>F31</f>
@@ -5002,7 +5004,7 @@
     </row>
     <row r="85" spans="1:6">
       <c r="B85" s="1" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="C85" s="92">
         <f>IF(C23="Y",1%,0)+IF(C24="Y",1%,0)</f>
@@ -5011,7 +5013,7 @@
     </row>
     <row r="86" spans="1:6">
       <c r="B86" s="80" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C86" s="236">
         <f>F31+C85</f>
@@ -5023,31 +5025,31 @@
     </row>
     <row r="88" spans="1:6">
       <c r="B88" s="293" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="C88" s="121"/>
     </row>
-    <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="358" t="s">
-        <v>363</v>
-      </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
-    </row>
-    <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="358" t="s">
-        <v>364</v>
-      </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+    <row r="89" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B89" s="360" t="s">
+        <v>360</v>
+      </c>
+      <c r="C89" s="360"/>
+      <c r="D89" s="360"/>
+      <c r="E89" s="360"/>
+      <c r="F89" s="360"/>
+    </row>
+    <row r="90" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B90" s="360" t="s">
+        <v>361</v>
+      </c>
+      <c r="C90" s="360"/>
+      <c r="D90" s="360"/>
+      <c r="E90" s="360"/>
+      <c r="F90" s="360"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C92" s="236">
         <v>0</v>
@@ -5055,7 +5057,7 @@
     </row>
     <row r="93" spans="1:6">
       <c r="B93" s="47" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C93" s="223">
         <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
@@ -5068,7 +5070,7 @@
     </row>
     <row r="95" spans="1:6" ht="13.9">
       <c r="A95" s="222" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="B95" s="36"/>
       <c r="C95" s="36"/>
@@ -5080,36 +5082,36 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
-        <v>365</v>
-      </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="B97" s="360" t="s">
+        <v>362</v>
+      </c>
+      <c r="C97" s="360"/>
+      <c r="D97" s="360"/>
+      <c r="E97" s="360"/>
+      <c r="F97" s="360"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="210" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="358" t="s">
-        <v>344</v>
-      </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+        <v>229</v>
+      </c>
+    </row>
+    <row r="101" spans="2:6" ht="24.6" customHeight="1">
+      <c r="B101" s="360" t="s">
+        <v>341</v>
+      </c>
+      <c r="C101" s="360"/>
+      <c r="D101" s="360"/>
+      <c r="E101" s="360"/>
+      <c r="F101" s="360"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C102" s="349">
         <f>DCF!C7</f>
@@ -5122,7 +5124,7 @@
     </row>
     <row r="103" spans="2:6">
       <c r="B103" s="47" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C103" s="223">
         <f>C102*scaling_factor*Exchange_Rate/Common_Shares</f>
@@ -5135,7 +5137,7 @@
     </row>
     <row r="104" spans="2:6">
       <c r="B104" s="296" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="C104" s="325">
         <f>IF(BS!G31/BS!G27&gt;300%,"nm",BS!G31/BS!G27)</f>
@@ -5144,7 +5146,7 @@
     </row>
     <row r="105" spans="2:6">
       <c r="B105" s="296" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="C105" s="326">
         <f>IF(BS!C50&gt;30,"nm",BS!C50)</f>
@@ -5153,12 +5155,12 @@
     </row>
     <row r="107" spans="2:6">
       <c r="B107" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="108" spans="2:6">
       <c r="B108" s="47" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C108" s="349">
         <f>BS!C66</f>
@@ -5171,7 +5173,7 @@
     </row>
     <row r="109" spans="2:6">
       <c r="B109" s="47" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C109" s="349">
         <f>DCF!C8</f>
@@ -5184,7 +5186,7 @@
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="47" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C110" s="223">
         <f>C109*scaling_factor*Exchange_Rate/Common_Shares</f>
@@ -5197,12 +5199,12 @@
     </row>
     <row r="112" spans="2:6">
       <c r="B112" s="1" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="113" spans="1:6">
       <c r="B113" s="47" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C113" s="349">
         <f>DCF!C9</f>
@@ -5215,7 +5217,7 @@
     </row>
     <row r="114" spans="1:6">
       <c r="B114" s="47" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C114" s="223">
         <f>C113*scaling_factor*Exchange_Rate/Common_Shares</f>
@@ -5226,18 +5228,18 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="358" t="s">
-        <v>366</v>
-      </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+    <row r="116" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B116" s="360" t="s">
+        <v>363</v>
+      </c>
+      <c r="C116" s="360"/>
+      <c r="D116" s="360"/>
+      <c r="E116" s="360"/>
+      <c r="F116" s="360"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="C118" s="223">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
@@ -5250,7 +5252,7 @@
     </row>
     <row r="119" spans="1:6">
       <c r="B119" s="296" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="C119" s="223">
         <f>BS!D47</f>
@@ -5263,7 +5265,7 @@
     </row>
     <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="222" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="B121" s="36"/>
       <c r="C121" s="36"/>
@@ -5271,30 +5273,30 @@
       <c r="E121" s="36"/>
       <c r="F121" s="36"/>
     </row>
-    <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="359" t="s">
-        <v>367</v>
-      </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+    <row r="123" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B123" s="361" t="s">
+        <v>364</v>
+      </c>
+      <c r="C123" s="361"/>
+      <c r="D123" s="361"/>
+      <c r="E123" s="361"/>
+      <c r="F123" s="361"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C125" s="233" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D125" s="233" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E125" s="233" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="F125" s="233" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="126" spans="1:6">
@@ -5409,7 +5411,7 @@
     </row>
     <row r="132" spans="1:6">
       <c r="B132" s="211" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C132" s="217">
         <f>Scenarios!C60</f>
@@ -5420,18 +5422,18 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="362" t="s">
-        <v>370</v>
-      </c>
-      <c r="C134" s="362"/>
-      <c r="D134" s="362"/>
-      <c r="E134" s="362"/>
-      <c r="F134" s="362"/>
+    <row r="134" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B134" s="364" t="s">
+        <v>367</v>
+      </c>
+      <c r="C134" s="364"/>
+      <c r="D134" s="364"/>
+      <c r="E134" s="364"/>
+      <c r="F134" s="364"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="B136" s="36"/>
       <c r="C136" s="36"/>
@@ -5440,31 +5442,31 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="363" t="s">
-        <v>368</v>
-      </c>
-      <c r="C138" s="363"/>
-      <c r="D138" s="363"/>
-      <c r="E138" s="363"/>
-      <c r="F138" s="363"/>
-    </row>
-    <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="358" t="s">
-        <v>369</v>
-      </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="B138" s="365" t="s">
+        <v>365</v>
+      </c>
+      <c r="C138" s="365"/>
+      <c r="D138" s="365"/>
+      <c r="E138" s="365"/>
+      <c r="F138" s="365"/>
+    </row>
+    <row r="139" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B139" s="360" t="s">
+        <v>366</v>
+      </c>
+      <c r="C139" s="360"/>
+      <c r="D139" s="360"/>
+      <c r="E139" s="360"/>
+      <c r="F139" s="360"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="141" spans="1:6">
       <c r="B141" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C141" s="225">
         <f>F28</f>
@@ -5473,20 +5475,20 @@
     </row>
     <row r="142" spans="1:6">
       <c r="B142" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C142" s="224">
         <f>F29</f>
-        <v>0.33699999999999997</v>
+        <v>0.33700000000000002</v>
       </c>
     </row>
     <row r="143" spans="1:6">
       <c r="B143" s="212" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C143" s="213">
         <f>Scenarios!C77</f>
-        <v>0.4</v>
+        <v>0.36000000000000004</v>
       </c>
       <c r="D143" s="212" t="str">
         <f>Market_currency</f>
@@ -5495,7 +5497,7 @@
     </row>
     <row r="145" spans="2:4">
       <c r="B145" s="210" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="C145" s="241" t="str">
         <f>C11</f>
@@ -5508,11 +5510,11 @@
     </row>
     <row r="146" spans="2:4">
       <c r="B146" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="C146" s="297">
         <f>F29</f>
-        <v>0.33699999999999997</v>
+        <v>0.33700000000000002</v>
       </c>
     </row>
     <row r="147" spans="2:4">
@@ -5522,7 +5524,7 @@
       </c>
       <c r="C147" s="216">
         <f>Scenarios!C81</f>
-        <v>0.69031028314322296</v>
+        <v>0.62127925482890056</v>
       </c>
     </row>
     <row r="148" spans="2:4">
@@ -5537,11 +5539,11 @@
     </row>
     <row r="149" spans="2:4">
       <c r="B149" s="80" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C149" s="215">
         <f>Scenarios!C83</f>
-        <v>4.9796479824958464</v>
+        <v>4.9106169541815241</v>
       </c>
       <c r="D149" s="300" t="str">
         <f>IF($D$11="","",C149*$E$25)</f>
@@ -5550,7 +5552,7 @@
     </row>
     <row r="150" spans="2:4">
       <c r="B150" s="259" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="C150" s="298" t="str">
         <f>Market_currency</f>
@@ -5563,21 +5565,21 @@
     </row>
     <row r="151" spans="2:4">
       <c r="B151" s="214" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C151" s="92">
         <f>Scenarios!F83</f>
-        <v>0.51424846499304677</v>
+        <v>0.52098225984855873</v>
       </c>
     </row>
     <row r="153" spans="2:4">
       <c r="B153" s="210" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
     </row>
     <row r="154" spans="2:4">
       <c r="B154" s="1" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="C154" s="297">
         <f>Scenarios!C90</f>
@@ -5591,7 +5593,7 @@
       </c>
       <c r="C155" s="216">
         <f>Scenarios!C91</f>
-        <v>0.86005014536183588</v>
+        <v>0.77404513082565229</v>
       </c>
     </row>
     <row r="156" spans="2:4">
@@ -5606,11 +5608,11 @@
     </row>
     <row r="157" spans="2:4">
       <c r="B157" s="80" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C157" s="215">
         <f>Scenarios!C93</f>
-        <v>6.9896525426428742</v>
+        <v>6.9036475281066911</v>
       </c>
       <c r="D157" s="300" t="str">
         <f>IF($D$11="","",C157*$E$25)</f>
@@ -5619,7 +5621,7 @@
     </row>
     <row r="158" spans="2:4">
       <c r="B158" s="259" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="C158" s="298" t="str">
         <f>Market_currency</f>
@@ -5632,21 +5634,21 @@
     </row>
     <row r="159" spans="2:4">
       <c r="B159" s="214" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C159" s="92">
         <f>Scenarios!F93</f>
-        <v>0.31817781825366975</v>
+        <v>0.32656738072396863</v>
       </c>
     </row>
     <row r="161" spans="2:4">
       <c r="B161" s="210" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
     </row>
     <row r="162" spans="2:4">
       <c r="B162" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="C162" s="92">
         <f>Scenarios!C96</f>
@@ -5660,7 +5662,7 @@
       </c>
       <c r="C163" s="216">
         <f>Scenarios!C97</f>
-        <v>1.069204779784656</v>
+        <v>0.9622843018061904</v>
       </c>
     </row>
     <row r="164" spans="2:4">
@@ -5675,11 +5677,11 @@
     </row>
     <row r="165" spans="2:4">
       <c r="B165" s="80" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="C165" s="215">
         <f>Scenarios!C99</f>
-        <v>9.6765033007385046</v>
+        <v>9.5695828227600401</v>
       </c>
       <c r="D165" s="300" t="str">
         <f>IF($D$11="","",C165*$E$25)</f>
@@ -5688,7 +5690,7 @@
     </row>
     <row r="166" spans="2:4">
       <c r="B166" s="259" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="C166" s="298" t="str">
         <f>Market_currency</f>
@@ -5701,21 +5703,21 @@
     </row>
     <row r="167" spans="2:4">
       <c r="B167" s="214" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C167" s="92">
         <f>Scenarios!F99</f>
-        <v>5.6082608980383197E-2</v>
+        <v>6.6512419779114595E-2</v>
       </c>
     </row>
     <row r="169" spans="2:4">
       <c r="B169" s="210" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
     </row>
     <row r="170" spans="2:4">
       <c r="B170" s="1" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="C170" s="92">
         <f>F32</f>
@@ -5729,7 +5731,7 @@
       </c>
       <c r="C171" s="216">
         <f>Scenarios!C103</f>
-        <v>1.0179560233797402</v>
+        <v>0.91616042104176609</v>
       </c>
     </row>
     <row r="172" spans="2:4">
@@ -5744,11 +5746,11 @@
     </row>
     <row r="173" spans="2:4">
       <c r="B173" s="80" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="C173" s="215">
         <f>Scenarios!C105</f>
-        <v>8.9996639027078977</v>
+        <v>8.8978683003699235</v>
       </c>
       <c r="D173" s="300" t="str">
         <f>IF($D$11="","",C173*$E$25)</f>
@@ -5757,7 +5759,7 @@
     </row>
     <row r="174" spans="2:4">
       <c r="B174" s="259" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="C174" s="298" t="str">
         <f>Market_currency</f>
@@ -5770,16 +5772,16 @@
     </row>
     <row r="175" spans="2:4">
       <c r="B175" s="214" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C175" s="92">
         <f>Scenarios!F105</f>
-        <v>0.11980238369313911</v>
+        <v>0.12975833843734319</v>
       </c>
     </row>
     <row r="177" spans="1:6" ht="13.9">
       <c r="A177" s="222" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="B177" s="36"/>
       <c r="C177" s="36"/>
@@ -5788,98 +5790,98 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="357" t="s">
-        <v>376</v>
-      </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="B179" s="359" t="s">
+        <v>373</v>
+      </c>
+      <c r="C179" s="360"/>
+      <c r="D179" s="360"/>
+      <c r="E179" s="360"/>
+      <c r="F179" s="360"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="360" t="s">
-        <v>380</v>
-      </c>
-      <c r="C182" s="360"/>
-      <c r="D182" s="360"/>
-      <c r="E182" s="360"/>
-      <c r="F182" s="360"/>
+      <c r="B182" s="362" t="s">
+        <v>377</v>
+      </c>
+      <c r="C182" s="362"/>
+      <c r="D182" s="362"/>
+      <c r="E182" s="362"/>
+      <c r="F182" s="362"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
     </row>
     <row r="184" spans="1:6">
       <c r="B184" s="214" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
     </row>
     <row r="185" spans="1:6">
       <c r="B185" s="214" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
     </row>
     <row r="187" spans="1:6">
       <c r="B187" s="1" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
-        <v>381</v>
-      </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="B188" s="361" t="s">
+        <v>378</v>
+      </c>
+      <c r="C188" s="361"/>
+      <c r="D188" s="361"/>
+      <c r="E188" s="361"/>
+      <c r="F188" s="361"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="356" t="s">
         <v>382</v>
       </c>
-      <c r="C191" s="356"/>
-      <c r="D191" s="356"/>
-      <c r="E191" s="356"/>
-      <c r="F191" s="356"/>
-    </row>
-    <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="356" t="s">
-        <v>383</v>
-      </c>
-      <c r="C192" s="356"/>
-      <c r="D192" s="356"/>
-      <c r="E192" s="356"/>
-      <c r="F192" s="356"/>
+    </row>
+    <row r="191" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B191" s="358" t="s">
+        <v>379</v>
+      </c>
+      <c r="C191" s="358"/>
+      <c r="D191" s="358"/>
+      <c r="E191" s="358"/>
+      <c r="F191" s="358"/>
+    </row>
+    <row r="192" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B192" s="358" t="s">
+        <v>380</v>
+      </c>
+      <c r="C192" s="358"/>
+      <c r="D192" s="358"/>
+      <c r="E192" s="358"/>
+      <c r="F192" s="358"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
     </row>
     <row r="195" spans="2:2">
       <c r="B195" s="214" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
     </row>
     <row r="196" spans="2:2">
       <c r="B196" s="214" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
     </row>
     <row r="197" spans="2:2">
       <c r="B197" s="214" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
   </sheetData>
@@ -5917,7 +5919,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F1" xr:uid="{45F807FD-9E0F-415A-9BBD-D5FB6470B56D}">
       <formula1>"Y, N"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C23:C25" xr:uid="{342D2C68-3352-49DC-9D77-964DC8D8A160}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C23:C24" xr:uid="{342D2C68-3352-49DC-9D77-964DC8D8A160}">
       <formula1>"Y,N"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="C25:D25" xr:uid="{00000000-0002-0000-0000-000001000000}">
@@ -5941,12 +5943,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:M80"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="11.65"/>
+  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="3" style="1" customWidth="1"/>
-    <col min="2" max="2" width="27.33203125" style="1" customWidth="1"/>
-    <col min="3" max="13" width="20.6640625" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.796875" style="1"/>
+    <col min="2" max="2" width="27.265625" style="1" customWidth="1"/>
+    <col min="3" max="13" width="20.73046875" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="8.86328125" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:13">
@@ -6198,7 +6200,7 @@
     </row>
     <row r="9" spans="2:13">
       <c r="B9" s="40" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C9" s="351"/>
       <c r="D9" s="351"/>
@@ -6214,7 +6216,7 @@
     </row>
     <row r="10" spans="2:13">
       <c r="B10" s="40" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C10" s="351"/>
       <c r="D10" s="351"/>
@@ -6230,7 +6232,7 @@
     </row>
     <row r="11" spans="2:13">
       <c r="B11" s="40" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C11" s="351"/>
       <c r="D11" s="351"/>
@@ -6482,7 +6484,7 @@
     </row>
     <row r="22" spans="2:13">
       <c r="B22" s="27" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="C22" s="351">
         <v>246703905</v>
@@ -6518,7 +6520,7 @@
     </row>
     <row r="23" spans="2:13">
       <c r="B23" s="27" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="C23" s="351">
         <v>12280558</v>
@@ -6554,7 +6556,7 @@
     </row>
     <row r="24" spans="2:13">
       <c r="B24" s="27" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="C24" s="351">
         <v>-205377752</v>
@@ -6628,7 +6630,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -6781,7 +6783,7 @@
     </row>
     <row r="32" spans="2:13">
       <c r="B32" s="26" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C32" s="333">
         <f>BS!G28</f>
@@ -7182,7 +7184,7 @@
     </row>
     <row r="43" spans="2:13">
       <c r="B43" s="43" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C43" s="334">
         <f>IF(C$4="","",C38+C39+C42)</f>
@@ -7231,7 +7233,7 @@
     </row>
     <row r="44" spans="2:13">
       <c r="B44" s="43" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C44" s="354">
         <f t="shared" ref="C44:M44" si="18">IF(C$4="","",C47-C46-C45-C43)</f>
@@ -7579,12 +7581,12 @@
     </row>
     <row r="54" spans="2:13">
       <c r="B54" s="174" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="55" spans="2:13">
       <c r="B55" s="40" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C55" s="349">
         <f t="shared" ref="C55:M55" si="25">IF(C$4="","",C9)</f>
@@ -7633,7 +7635,7 @@
     </row>
     <row r="56" spans="2:13">
       <c r="B56" s="40" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C56" s="349">
         <f t="shared" ref="C56:M56" si="26">IF(C$4="","",C10)</f>
@@ -7682,7 +7684,7 @@
     </row>
     <row r="57" spans="2:13">
       <c r="B57" s="40" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C57" s="349">
         <f t="shared" ref="C57:M57" si="27">IF(C$4="","",C11)</f>
@@ -7731,7 +7733,7 @@
     </row>
     <row r="58" spans="2:13">
       <c r="B58" s="40" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C58" s="349">
         <f>IF(C$4="","",C44-C55-C56-C57)</f>
@@ -7933,7 +7935,7 @@
     </row>
     <row r="64" spans="2:13">
       <c r="B64" s="27" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="C64" s="333">
         <f>IF(C$4="","",C22+C23+C24)</f>
@@ -8185,7 +8187,7 @@
     </row>
     <row r="71" spans="2:13">
       <c r="B71" s="43" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C71" s="101">
         <f>IF(D$36="","",C44/D44-1)</f>
@@ -8551,15 +8553,15 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:H89"/>
-  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.265625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="2.33203125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="2.265625" style="1" customWidth="1"/>
     <col min="2" max="2" width="34" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="18.6640625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="5.6640625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="25.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="18.6640625" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="12.33203125" style="1"/>
+    <col min="3" max="4" width="18.73046875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="5.73046875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="25.265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="18.73046875" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="12.265625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:8" ht="15" customHeight="1">
@@ -8580,7 +8582,7 @@
     </row>
     <row r="2" spans="2:8" ht="15" customHeight="1">
       <c r="B2" s="79" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
@@ -8591,19 +8593,19 @@
     </row>
     <row r="3" spans="2:8" ht="15" customHeight="1">
       <c r="B3" s="16" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C3" s="182" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D3" s="183" t="s">
         <v>35</v>
       </c>
       <c r="F3" s="16" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G3" s="182" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H3" s="183" t="s">
         <v>35</v>
@@ -8664,7 +8666,7 @@
       </c>
       <c r="E6" s="25"/>
       <c r="F6" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G6" s="19">
         <v>0</v>
@@ -8685,7 +8687,7 @@
       </c>
       <c r="E7" s="25"/>
       <c r="F7" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G7" s="19">
         <v>0</v>
@@ -8696,7 +8698,7 @@
     </row>
     <row r="8" spans="2:8" ht="15" customHeight="1">
       <c r="B8" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C8" s="19">
         <v>0</v>
@@ -8706,7 +8708,7 @@
       </c>
       <c r="E8" s="25"/>
       <c r="F8" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G8" s="19">
         <v>0</v>
@@ -8727,7 +8729,7 @@
       </c>
       <c r="E9" s="25"/>
       <c r="F9" s="4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G9" s="19">
         <v>0</v>
@@ -8791,19 +8793,19 @@
     </row>
     <row r="14" spans="2:8" ht="15" customHeight="1">
       <c r="B14" s="16" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C14" s="182" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D14" s="183" t="s">
         <v>35</v>
       </c>
       <c r="F14" s="16" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G14" s="182" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H14" s="183" t="s">
         <v>35</v>
@@ -8811,7 +8813,7 @@
     </row>
     <row r="15" spans="2:8" ht="15" customHeight="1">
       <c r="B15" s="4" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="C15" s="19">
         <v>0</v>
@@ -8840,7 +8842,7 @@
         <v>0.5</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G16" s="19">
         <v>0</v>
@@ -8860,7 +8862,7 @@
         <v>0.6</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G17" s="19">
         <v>0</v>
@@ -8871,7 +8873,7 @@
     </row>
     <row r="18" spans="2:8" ht="15" customHeight="1">
       <c r="B18" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C18" s="19">
         <v>0</v>
@@ -8880,7 +8882,7 @@
         <v>0.6</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G18" s="19">
         <v>0</v>
@@ -8901,7 +8903,7 @@
         <v>0.1</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G19" s="19">
         <v>0</v>
@@ -8921,7 +8923,7 @@
         <v>0.05</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G20" s="19">
         <v>0</v>
@@ -8941,7 +8943,7 @@
         <v>0.05</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G21" s="19">
         <v>0</v>
@@ -9001,16 +9003,16 @@
     </row>
     <row r="26" spans="2:8" ht="15" customHeight="1">
       <c r="B26" s="16" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C26" s="182" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F26" s="184" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G26" s="185" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H26" s="186" t="s">
         <v>35</v>
@@ -9043,7 +9045,7 @@
         <v>0</v>
       </c>
       <c r="F28" s="189" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="G28" s="12">
         <v>-371705.83</v>
@@ -9087,7 +9089,7 @@
     </row>
     <row r="31" spans="2:8" ht="15" customHeight="1">
       <c r="B31" s="80" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C31" s="81">
         <f>SUM(C27:C30)</f>
@@ -9137,10 +9139,10 @@
       <c r="B34" s="83"/>
       <c r="C34" s="84"/>
       <c r="F34" s="196" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G34" s="197" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H34" s="198" t="s">
         <v>35</v>
@@ -9148,10 +9150,10 @@
     </row>
     <row r="35" spans="2:8" ht="15" customHeight="1">
       <c r="B35" s="16" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C35" s="182" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F35" s="199" t="s">
         <v>31</v>
@@ -9173,7 +9175,7 @@
         <v>0</v>
       </c>
       <c r="F36" s="190" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G36" s="191">
         <f>C4+C15</f>
@@ -9189,7 +9191,7 @@
         <v>0</v>
       </c>
       <c r="F37" s="190" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G37" s="191">
         <f>C6</f>
@@ -9205,7 +9207,7 @@
         <v>0</v>
       </c>
       <c r="F38" s="190" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G38" s="191">
         <f>C7+C17</f>
@@ -9234,14 +9236,14 @@
     </row>
     <row r="40" spans="2:8" ht="15" customHeight="1">
       <c r="B40" s="80" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C40" s="81">
         <f>SUM(C36:C39)</f>
         <v>0</v>
       </c>
       <c r="F40" s="199" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G40" s="193">
         <f>G12+G24</f>
@@ -9261,7 +9263,7 @@
         <v>20422655.370000001</v>
       </c>
       <c r="F41" s="190" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G41" s="191">
         <f>C70</f>
@@ -9280,7 +9282,7 @@
         <v>20422655.370000001</v>
       </c>
       <c r="F42" s="201" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G42" s="202">
         <f>C82</f>
@@ -9304,13 +9306,13 @@
     </row>
     <row r="45" spans="2:8" ht="15" customHeight="1">
       <c r="B45" s="16" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C45" s="234" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D45" s="182" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="F45" s="256" t="s">
         <v>59</v>
@@ -9318,7 +9320,7 @@
     </row>
     <row r="46" spans="2:8" ht="15" customHeight="1">
       <c r="B46" s="1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C46" s="76">
         <f>G29</f>
@@ -9350,7 +9352,7 @@
     </row>
     <row r="49" spans="2:8" ht="15" customHeight="1">
       <c r="B49" s="157" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C49" s="235" t="s">
         <v>57</v>
@@ -9377,7 +9379,7 @@
     </row>
     <row r="51" spans="2:8" ht="15" customHeight="1">
       <c r="B51" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C51" s="181"/>
       <c r="D51" s="92">
@@ -9391,7 +9393,7 @@
     </row>
     <row r="53" spans="2:8" ht="15" customHeight="1">
       <c r="B53" s="157" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C53" s="235" t="s">
         <v>57</v>
@@ -9403,7 +9405,7 @@
     </row>
     <row r="54" spans="2:8" ht="15" customHeight="1">
       <c r="B54" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C54" s="92">
         <f>Normalized_FCF!C8/G35</f>
@@ -9417,7 +9419,7 @@
     </row>
     <row r="55" spans="2:8" ht="15" customHeight="1">
       <c r="B55" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C55" s="92">
         <f>Normalized_FCF!C11/G40</f>
@@ -9434,7 +9436,7 @@
     </row>
     <row r="57" spans="2:8" ht="15" customHeight="1">
       <c r="B57" s="157" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C57" s="235" t="s">
         <v>57</v>
@@ -9471,10 +9473,10 @@
     </row>
     <row r="61" spans="2:8" ht="15" customHeight="1">
       <c r="B61" s="157" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C61" s="235" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D61" s="197" t="s">
         <v>95</v>
@@ -9483,7 +9485,7 @@
     </row>
     <row r="62" spans="2:8" ht="15" customHeight="1">
       <c r="B62" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C62" s="92">
         <f>IF(G28&lt;=0,0,G28/G29)</f>
@@ -9494,12 +9496,12 @@
         <v>-1.5410995011336286E-4</v>
       </c>
       <c r="F62" s="253" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="64" spans="2:8" ht="15" customHeight="1">
       <c r="B64" s="79" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C64" s="37"/>
       <c r="D64" s="37"/>
@@ -9510,13 +9512,13 @@
     </row>
     <row r="65" spans="2:6" ht="15" customHeight="1">
       <c r="B65" s="16" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C65" s="234" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D65" s="183" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F65" s="256" t="s">
         <v>59</v>
@@ -9524,7 +9526,7 @@
     </row>
     <row r="66" spans="2:6" ht="15" customHeight="1">
       <c r="B66" s="105" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C66" s="20">
         <f>G4+G5+G15</f>
@@ -9535,12 +9537,12 @@
         <v>787007506.71999991</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="67" spans="2:6" ht="15" customHeight="1">
       <c r="B67" s="105" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C67" s="20">
         <f>G6+G16</f>
@@ -9550,7 +9552,7 @@
     </row>
     <row r="68" spans="2:6" ht="15" customHeight="1">
       <c r="B68" s="105" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C68" s="20">
         <f>G18</f>
@@ -9560,7 +9562,7 @@
     </row>
     <row r="69" spans="2:6" ht="15" customHeight="1">
       <c r="B69" s="105" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C69" s="20">
         <f>G8+G20</f>
@@ -9570,7 +9572,7 @@
     </row>
     <row r="70" spans="2:6" ht="15" customHeight="1">
       <c r="B70" s="80" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C70" s="81">
         <f>SUM(C66:C69)</f>
@@ -9583,7 +9585,7 @@
     </row>
     <row r="72" spans="2:6" ht="15" customHeight="1">
       <c r="B72" s="255" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="C72" s="234" t="s">
         <v>95</v>
@@ -9595,7 +9597,7 @@
     </row>
     <row r="73" spans="2:6" ht="15" customHeight="1">
       <c r="B73" s="105" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="C73" s="349">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
@@ -9606,12 +9608,12 @@
         <v>-112772827.10000001</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="15" customHeight="1">
       <c r="B74" s="257" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="C74" s="258">
         <f>-$C$66/C73</f>
@@ -9622,12 +9624,12 @@
         <v>8.978698033544287</v>
       </c>
       <c r="F74" s="253" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
     </row>
     <row r="75" spans="2:6" ht="15" customHeight="1">
       <c r="B75" s="80" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="C75" s="320"/>
       <c r="D75" s="321">
@@ -9635,12 +9637,12 @@
         <v>225545654.20000002</v>
       </c>
       <c r="F75" s="253" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
     </row>
     <row r="76" spans="2:6" ht="15" customHeight="1">
       <c r="B76" s="259" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="C76" s="260"/>
       <c r="D76" s="290">
@@ -9648,7 +9650,7 @@
         <v>2</v>
       </c>
       <c r="F76" s="253" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="15" customHeight="1">
@@ -9656,10 +9658,10 @@
     </row>
     <row r="78" spans="2:6" ht="15" customHeight="1">
       <c r="B78" s="16" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C78" s="234" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D78" s="183" t="s">
         <v>35</v>
@@ -9668,7 +9670,7 @@
     </row>
     <row r="79" spans="2:6" ht="15" customHeight="1">
       <c r="B79" s="105" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C79" s="20">
         <f>G7+G17</f>
@@ -9682,7 +9684,7 @@
     </row>
     <row r="80" spans="2:6" ht="15" customHeight="1">
       <c r="B80" s="105" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C80" s="20">
         <f>G19</f>
@@ -9696,7 +9698,7 @@
     </row>
     <row r="81" spans="2:8" ht="15" customHeight="1">
       <c r="B81" s="105" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C81" s="20">
         <f>G9+G21</f>
@@ -9710,7 +9712,7 @@
     </row>
     <row r="82" spans="2:8" ht="15" customHeight="1">
       <c r="B82" s="80" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C82" s="81">
         <f>SUM(C79:C81)</f>
@@ -9724,7 +9726,7 @@
     </row>
     <row r="84" spans="2:8" ht="15" customHeight="1">
       <c r="B84" s="79" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C84" s="37"/>
       <c r="D84" s="37"/>
@@ -9735,15 +9737,15 @@
     </row>
     <row r="85" spans="2:8" ht="15" customHeight="1">
       <c r="B85" s="16" t="s">
+        <v>288</v>
+      </c>
+      <c r="D85" s="241" t="s">
         <v>289</v>
-      </c>
-      <c r="D85" s="241" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="86" spans="2:8" ht="15" customHeight="1">
       <c r="B86" s="238" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C86" s="76">
         <f>-DCF!C7*Exchange_Rate</f>
@@ -9760,7 +9762,7 @@
     </row>
     <row r="87" spans="2:8" ht="15" customHeight="1">
       <c r="B87" s="238" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C87" s="76">
         <f>DCF!C8*Exchange_Rate</f>
@@ -9777,7 +9779,7 @@
     </row>
     <row r="88" spans="2:8" ht="15" customHeight="1">
       <c r="B88" s="239" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C88" s="76">
         <f>DCF!C9*Exchange_Rate</f>
@@ -9794,7 +9796,7 @@
     </row>
     <row r="89" spans="2:8" ht="15" customHeight="1">
       <c r="B89" s="80" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C89" s="180">
         <f>SUM(C86:C88)</f>
@@ -9822,17 +9824,17 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q808"/>
-  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
+  <dimension ref="A1:Q809"/>
+  <sheetFormatPr defaultColWidth="12.265625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="1.33203125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="26.33203125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="20.6640625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="2.6640625" style="2" customWidth="1"/>
+    <col min="1" max="1" width="1.265625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="26.265625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="20.73046875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="2.73046875" style="2" customWidth="1"/>
     <col min="5" max="5" width="25.1328125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="2.6640625" style="2" customWidth="1"/>
-    <col min="7" max="17" width="20.6640625" style="2" customWidth="1"/>
-    <col min="18" max="16384" width="12.33203125" style="2"/>
+    <col min="6" max="6" width="2.73046875" style="2" customWidth="1"/>
+    <col min="7" max="17" width="20.73046875" style="2" customWidth="1"/>
+    <col min="18" max="16384" width="12.265625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="15.75" customHeight="1">
@@ -10154,7 +10156,7 @@
     <row r="8" spans="1:17" ht="15.75" customHeight="1">
       <c r="A8" s="10"/>
       <c r="B8" s="29" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C8" s="330">
         <f>C6+C7</f>
@@ -10321,7 +10323,7 @@
     <row r="11" spans="1:17" ht="15.75" customHeight="1">
       <c r="A11" s="10"/>
       <c r="B11" s="31" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C11" s="331">
         <f>C63</f>
@@ -10433,7 +10435,7 @@
     <row r="13" spans="1:17" ht="15.75" customHeight="1">
       <c r="A13" s="10"/>
       <c r="B13" s="70" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C13" s="329">
         <f>SUM(C8:C12)</f>
@@ -10543,7 +10545,7 @@
     <row r="15" spans="1:17" ht="15.75" customHeight="1">
       <c r="A15" s="10"/>
       <c r="B15" s="40" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C15" s="328">
         <f>-C4*C83</f>
@@ -10600,7 +10602,7 @@
     <row r="16" spans="1:17" ht="15.75" customHeight="1">
       <c r="A16" s="10"/>
       <c r="B16" s="41" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C16" s="332">
         <f>SUM(C13:C15)</f>
@@ -10665,7 +10667,7 @@
       </c>
       <c r="D17" s="58"/>
       <c r="E17" s="267" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="F17" s="58"/>
       <c r="G17" s="335"/>
@@ -10690,7 +10692,7 @@
       </c>
       <c r="D18" s="58"/>
       <c r="E18" s="267" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="F18" s="58"/>
       <c r="G18" s="336"/>
@@ -10784,7 +10786,7 @@
     <row r="21" spans="1:17" ht="15.75" customHeight="1">
       <c r="A21" s="10"/>
       <c r="B21" s="54" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C21" s="54"/>
       <c r="D21" s="56"/>
@@ -11003,7 +11005,7 @@
     <row r="27" spans="1:17" ht="15.75" customHeight="1">
       <c r="A27" s="10"/>
       <c r="B27" s="64" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E27" s="268"/>
     </row>
@@ -11018,7 +11020,7 @@
       </c>
       <c r="D28" s="26"/>
       <c r="E28" s="266" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="F28" s="26"/>
       <c r="G28" s="13">
@@ -11078,7 +11080,7 @@
       </c>
       <c r="D29" s="26"/>
       <c r="E29" s="266" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="F29" s="26"/>
       <c r="G29" s="13">
@@ -11195,14 +11197,14 @@
     <row r="33" spans="1:17" ht="15.75" customHeight="1">
       <c r="A33" s="10"/>
       <c r="B33" s="8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C33" s="340">
         <f>G33</f>
         <v>-33090730</v>
       </c>
       <c r="E33" s="266" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="G33" s="328">
         <f>Data!C41</f>
@@ -11260,7 +11262,7 @@
       </c>
       <c r="D34" s="58"/>
       <c r="E34" s="266" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="F34" s="58"/>
       <c r="G34" s="333">
@@ -11372,7 +11374,7 @@
     <row r="37" spans="1:17" ht="15.75" customHeight="1">
       <c r="A37" s="10"/>
       <c r="B37" s="64" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E37" s="268"/>
     </row>
@@ -11554,21 +11556,21 @@
     <row r="42" spans="1:17" ht="15.75" customHeight="1">
       <c r="A42" s="10"/>
       <c r="B42" s="64" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E42" s="268"/>
     </row>
     <row r="43" spans="1:17" ht="15.75" customHeight="1">
       <c r="A43" s="10"/>
       <c r="B43" s="27" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C43" s="263">
         <v>0.25</v>
       </c>
       <c r="D43" s="27"/>
       <c r="E43" s="265" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="F43" s="27"/>
       <c r="G43" s="6">
@@ -11622,7 +11624,7 @@
     <row r="45" spans="1:17" ht="15.75" customHeight="1">
       <c r="A45" s="10"/>
       <c r="B45" s="54" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C45" s="54"/>
       <c r="D45" s="56"/>
@@ -11707,7 +11709,7 @@
     <row r="48" spans="1:17" ht="15.75" customHeight="1">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="C48" s="328">
         <f>BS!D75*C53</f>
@@ -11762,7 +11764,7 @@
     <row r="49" spans="1:17" ht="15.75" customHeight="1">
       <c r="A49" s="10"/>
       <c r="B49" s="287" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="C49" s="342">
         <f>BS!$C$66*C53</f>
@@ -11878,11 +11880,11 @@
     <row r="52" spans="1:17" ht="15.75" customHeight="1">
       <c r="A52" s="10"/>
       <c r="B52" s="72" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E52" s="268"/>
       <c r="G52" s="97" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="53" spans="1:17" ht="15.75" customHeight="1">
@@ -11894,7 +11896,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
       <c r="E53" s="265" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="G53" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G49/BS!$C$66)</f>
@@ -11921,7 +11923,7 @@
         <v>5.216417413450098E-2</v>
       </c>
       <c r="E54" s="265" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="G54" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
@@ -12000,17 +12002,17 @@
     <row r="57" spans="1:17" ht="15.75" customHeight="1">
       <c r="A57" s="10"/>
       <c r="B57" s="64" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E57" s="268"/>
       <c r="G57" s="97" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="58" spans="1:17" ht="15.75" customHeight="1">
       <c r="A58" s="10"/>
       <c r="B58" s="40" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C58" s="328">
         <f>BS!$C67*C66</f>
@@ -12065,7 +12067,7 @@
     <row r="59" spans="1:17" ht="15.75" customHeight="1">
       <c r="A59" s="10"/>
       <c r="B59" s="40" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C59" s="328">
         <f>BS!$C68*C67</f>
@@ -12120,7 +12122,7 @@
     <row r="60" spans="1:17" ht="15.75" customHeight="1">
       <c r="A60" s="10"/>
       <c r="B60" s="40" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C60" s="328">
         <f>BS!$C69*C68</f>
@@ -12175,7 +12177,7 @@
     <row r="61" spans="1:17" ht="15.75" customHeight="1">
       <c r="A61" s="10"/>
       <c r="B61" s="31" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C61" s="329">
         <f>SUM(C58:C60)</f>
@@ -12230,13 +12232,13 @@
     <row r="62" spans="1:17" ht="15.75" customHeight="1">
       <c r="A62" s="10"/>
       <c r="B62" s="40" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C62" s="343">
         <v>0</v>
       </c>
       <c r="E62" s="266" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="G62" s="328">
         <f>Data!C58</f>
@@ -12286,7 +12288,7 @@
     <row r="63" spans="1:17" ht="15.75" customHeight="1">
       <c r="A63" s="10"/>
       <c r="B63" s="31" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C63" s="329">
         <f>C61+C62</f>
@@ -12345,17 +12347,17 @@
     <row r="65" spans="1:17" ht="15.75" customHeight="1">
       <c r="A65" s="10"/>
       <c r="B65" s="96" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E65" s="268"/>
       <c r="G65" s="97" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="66" spans="1:17" ht="15.75" customHeight="1">
       <c r="A66" s="10"/>
       <c r="B66" s="40" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C66" s="176">
         <f>G66</f>
@@ -12380,7 +12382,7 @@
     <row r="67" spans="1:17" ht="15.75" customHeight="1">
       <c r="A67" s="10"/>
       <c r="B67" s="105" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C67" s="176">
         <f>G67</f>
@@ -12405,7 +12407,7 @@
     <row r="68" spans="1:17" ht="15.75" customHeight="1">
       <c r="A68" s="10"/>
       <c r="B68" s="105" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C68" s="176">
         <f>G68</f>
@@ -12430,7 +12432,7 @@
     <row r="69" spans="1:17" ht="15.75" customHeight="1">
       <c r="A69" s="10"/>
       <c r="B69" s="31" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C69" s="71">
         <f>C61/BS!C70</f>
@@ -12460,12 +12462,12 @@
     <row r="71" spans="1:17" ht="15.75" customHeight="1">
       <c r="A71" s="10"/>
       <c r="B71" s="54" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C71" s="54"/>
       <c r="D71" s="56"/>
       <c r="E71" s="66" t="s">
-        <v>463</v>
+        <v>59</v>
       </c>
       <c r="F71" s="56"/>
       <c r="G71" s="37"/>
@@ -12483,7 +12485,7 @@
     <row r="72" spans="1:17" ht="15.75" customHeight="1">
       <c r="A72" s="10"/>
       <c r="B72" s="72" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C72" s="62"/>
       <c r="D72" s="27"/>
@@ -12675,7 +12677,7 @@
     <row r="76" spans="1:17" ht="15.75" customHeight="1">
       <c r="A76" s="10"/>
       <c r="B76" s="29" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C76" s="78">
         <f>ABS(C8/C$4)</f>
@@ -12848,7 +12850,7 @@
     <row r="79" spans="1:17" ht="15.75" customHeight="1">
       <c r="A79" s="10"/>
       <c r="B79" s="31" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C79" s="78">
         <f>ABS(C11/C$4)</f>
@@ -12962,7 +12964,7 @@
     <row r="81" spans="1:17" ht="15.75" customHeight="1">
       <c r="A81" s="10"/>
       <c r="B81" s="70" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C81" s="78">
         <f>C13/C4</f>
@@ -13134,7 +13136,7 @@
     <row r="84" spans="1:17" ht="15.75" customHeight="1">
       <c r="A84" s="10"/>
       <c r="B84" s="41" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C84" s="78">
         <f>ABS(C16/C$4)</f>
@@ -13241,7 +13243,7 @@
     <row r="87" spans="1:17" ht="15.75" customHeight="1">
       <c r="A87" s="10"/>
       <c r="B87" s="31" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C87" s="78">
         <f>ABS(C19/C$4)</f>
@@ -13302,7 +13304,7 @@
     <row r="89" spans="1:17" ht="15.75" customHeight="1">
       <c r="A89" s="10"/>
       <c r="B89" s="64" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E89" s="268"/>
     </row>
@@ -13421,7 +13423,7 @@
     <row r="92" spans="1:17" ht="15.75" customHeight="1">
       <c r="A92" s="10"/>
       <c r="B92" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*scaling_factor/Common_Shares)</f>
@@ -13476,1310 +13478,1330 @@
     <row r="93" spans="1:17" ht="15.75" customHeight="1">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="C93" s="23">
-        <f>C90/Market_Price</f>
-        <v>2.8449502133712661E-2</v>
+        <v>453</v>
+      </c>
+      <c r="C93" s="356">
+        <v>0.1</v>
       </c>
       <c r="E93" s="268"/>
-      <c r="G93" s="23">
-        <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>2.8449502133712661E-2</v>
-      </c>
-      <c r="H93" s="23">
+      <c r="G93" s="357"/>
+      <c r="H93" s="357"/>
+      <c r="I93" s="357"/>
+      <c r="J93" s="357"/>
+      <c r="K93" s="357"/>
+      <c r="L93" s="357"/>
+      <c r="M93" s="357"/>
+      <c r="N93" s="357"/>
+      <c r="O93" s="357"/>
+      <c r="P93" s="357"/>
+      <c r="Q93" s="357"/>
+    </row>
+    <row r="94" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A94" s="10"/>
+      <c r="B94" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="C94" s="23">
+        <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
+        <v>2.5604551920341397E-2</v>
+      </c>
+      <c r="E94" s="268"/>
+      <c r="G94" s="23">
+        <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
+        <v>2.5604551920341397E-2</v>
+      </c>
+      <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>2.8449502133712661E-2</v>
-      </c>
-      <c r="I93" s="23">
+        <v>2.5604551920341397E-2</v>
+      </c>
+      <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>2.8449502133712661E-2</v>
-      </c>
-      <c r="J93" s="23">
+        <v>2.5604551920341397E-2</v>
+      </c>
+      <c r="J94" s="23">
         <f t="shared" si="39"/>
-        <v>2.8449502133712661E-2</v>
-      </c>
-      <c r="K93" s="23">
+        <v>2.5604551920341397E-2</v>
+      </c>
+      <c r="K94" s="23">
         <f t="shared" si="39"/>
-        <v>1.422475106685633E-2</v>
-      </c>
-      <c r="L93" s="23">
+        <v>1.2802275960170698E-2</v>
+      </c>
+      <c r="L94" s="23">
         <f t="shared" si="39"/>
-        <v>1.422475106685633E-2</v>
-      </c>
-      <c r="M93" s="23">
+        <v>1.2802275960170698E-2</v>
+      </c>
+      <c r="M94" s="23">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="N93" s="23">
+      <c r="N94" s="23">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="O93" s="23">
+      <c r="O94" s="23">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="P93" s="23">
+      <c r="P94" s="23">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="Q93" s="23" t="str">
+      <c r="Q94" s="23" t="str">
         <f t="shared" si="39"/>
         <v/>
       </c>
     </row>
-    <row r="94" spans="1:17" ht="15.75" customHeight="1">
-      <c r="A94" s="10"/>
-      <c r="E94" s="268"/>
-    </row>
     <row r="95" spans="1:17" ht="15.75" customHeight="1">
       <c r="A95" s="10"/>
-      <c r="B95" s="157" t="s">
-        <v>84</v>
-      </c>
-      <c r="C95" s="62"/>
-      <c r="D95" s="27"/>
-      <c r="E95" s="265"/>
-      <c r="F95" s="27"/>
-      <c r="G95" s="12"/>
-      <c r="H95" s="12"/>
-      <c r="I95" s="12"/>
-      <c r="J95" s="12"/>
-      <c r="K95" s="12"/>
-      <c r="L95" s="12"/>
-      <c r="M95" s="12"/>
-      <c r="N95" s="12"/>
-      <c r="O95" s="12"/>
-      <c r="P95" s="12"/>
-      <c r="Q95" s="12"/>
+      <c r="E95" s="268"/>
     </row>
     <row r="96" spans="1:17" ht="15.75" customHeight="1">
       <c r="A96" s="10"/>
-      <c r="B96" s="27" t="s">
-        <v>144</v>
-      </c>
-      <c r="C96" s="77">
-        <f>C4/G4-1</f>
-        <v>0</v>
-      </c>
+      <c r="B96" s="157" t="s">
+        <v>84</v>
+      </c>
+      <c r="C96" s="62"/>
       <c r="D96" s="27"/>
       <c r="E96" s="265"/>
       <c r="F96" s="27"/>
-      <c r="G96" s="6">
-        <f t="shared" ref="G96:Q96" si="40">IF(H4="","",G4/H4-1)</f>
-        <v>2.3060791713184869E-2</v>
-      </c>
-      <c r="H96" s="6">
-        <f t="shared" si="40"/>
-        <v>-0.13634029089949951</v>
-      </c>
-      <c r="I96" s="6">
-        <f t="shared" si="40"/>
-        <v>0.14618004432154508</v>
-      </c>
-      <c r="J96" s="6">
-        <f t="shared" si="40"/>
-        <v>0.52612145772523466</v>
-      </c>
-      <c r="K96" s="6">
-        <f t="shared" si="40"/>
-        <v>0.34206060652745496</v>
-      </c>
-      <c r="L96" s="6">
-        <f t="shared" si="40"/>
-        <v>6.9846360774512783E-2</v>
-      </c>
-      <c r="M96" s="6">
-        <f t="shared" si="40"/>
-        <v>0.17548458141395407</v>
-      </c>
-      <c r="N96" s="6">
-        <f t="shared" si="40"/>
-        <v>0.43939178022677039</v>
-      </c>
-      <c r="O96" s="6">
-        <f t="shared" si="40"/>
-        <v>7.3053667937974298E-2</v>
-      </c>
-      <c r="P96" s="6" t="str">
-        <f t="shared" si="40"/>
-        <v/>
-      </c>
-      <c r="Q96" s="6" t="str">
-        <f t="shared" si="40"/>
-        <v/>
-      </c>
+      <c r="G96" s="12"/>
+      <c r="H96" s="12"/>
+      <c r="I96" s="12"/>
+      <c r="J96" s="12"/>
+      <c r="K96" s="12"/>
+      <c r="L96" s="12"/>
+      <c r="M96" s="12"/>
+      <c r="N96" s="12"/>
+      <c r="O96" s="12"/>
+      <c r="P96" s="12"/>
+      <c r="Q96" s="12"/>
     </row>
     <row r="97" spans="1:17" ht="15.75" customHeight="1">
       <c r="A97" s="10"/>
-      <c r="B97" s="70" t="s">
-        <v>164</v>
+      <c r="B97" s="27" t="s">
+        <v>143</v>
       </c>
       <c r="C97" s="77">
-        <f>C13/G13-1</f>
-        <v>-1.7975990639891415E-2</v>
+        <f>C4/G4-1</f>
+        <v>0</v>
       </c>
       <c r="D97" s="27"/>
       <c r="E97" s="265"/>
       <c r="F97" s="27"/>
       <c r="G97" s="6">
-        <f t="shared" ref="G97:Q97" si="41">IF(H5="","",G13/H13-1)</f>
+        <f t="shared" ref="G97:Q97" si="40">IF(H4="","",G4/H4-1)</f>
+        <v>2.3060791713184869E-2</v>
+      </c>
+      <c r="H97" s="6">
+        <f t="shared" si="40"/>
+        <v>-0.13634029089949951</v>
+      </c>
+      <c r="I97" s="6">
+        <f t="shared" si="40"/>
+        <v>0.14618004432154508</v>
+      </c>
+      <c r="J97" s="6">
+        <f t="shared" si="40"/>
+        <v>0.52612145772523466</v>
+      </c>
+      <c r="K97" s="6">
+        <f t="shared" si="40"/>
+        <v>0.34206060652745496</v>
+      </c>
+      <c r="L97" s="6">
+        <f t="shared" si="40"/>
+        <v>6.9846360774512783E-2</v>
+      </c>
+      <c r="M97" s="6">
+        <f t="shared" si="40"/>
+        <v>0.17548458141395407</v>
+      </c>
+      <c r="N97" s="6">
+        <f t="shared" si="40"/>
+        <v>0.43939178022677039</v>
+      </c>
+      <c r="O97" s="6">
+        <f t="shared" si="40"/>
+        <v>7.3053667937974298E-2</v>
+      </c>
+      <c r="P97" s="6" t="str">
+        <f t="shared" si="40"/>
+        <v/>
+      </c>
+      <c r="Q97" s="6" t="str">
+        <f t="shared" si="40"/>
+        <v/>
+      </c>
+    </row>
+    <row r="98" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A98" s="10"/>
+      <c r="B98" s="70" t="s">
+        <v>163</v>
+      </c>
+      <c r="C98" s="77">
+        <f>C13/G13-1</f>
+        <v>-1.7975990639891415E-2</v>
+      </c>
+      <c r="D98" s="27"/>
+      <c r="E98" s="265"/>
+      <c r="F98" s="27"/>
+      <c r="G98" s="6">
+        <f t="shared" ref="G98:Q98" si="41">IF(H5="","",G13/H13-1)</f>
         <v>-0.21425817196873598</v>
       </c>
-      <c r="H97" s="6">
+      <c r="H98" s="6">
         <f t="shared" si="41"/>
         <v>-0.4944906669422392</v>
       </c>
-      <c r="I97" s="6">
+      <c r="I98" s="6">
         <f t="shared" si="41"/>
         <v>0.553338123509169</v>
       </c>
-      <c r="J97" s="6">
+      <c r="J98" s="6">
         <f t="shared" si="41"/>
         <v>0.32291847035802257</v>
       </c>
-      <c r="K97" s="6">
+      <c r="K98" s="6">
         <f t="shared" si="41"/>
         <v>0.2271337884569633</v>
       </c>
-      <c r="L97" s="6">
+      <c r="L98" s="6">
         <f t="shared" si="41"/>
         <v>0.4055870029137949</v>
       </c>
-      <c r="M97" s="6">
+      <c r="M98" s="6">
         <f t="shared" si="41"/>
         <v>0.13445810561416982</v>
       </c>
-      <c r="N97" s="6">
+      <c r="N98" s="6">
         <f t="shared" si="41"/>
         <v>0.4501144064579472</v>
       </c>
-      <c r="O97" s="6">
+      <c r="O98" s="6">
         <f t="shared" si="41"/>
         <v>2.908837616815152E-2</v>
       </c>
-      <c r="P97" s="6" t="str">
+      <c r="P98" s="6" t="str">
         <f t="shared" si="41"/>
         <v/>
       </c>
-      <c r="Q97" s="6" t="str">
+      <c r="Q98" s="6" t="str">
         <f t="shared" si="41"/>
         <v/>
       </c>
     </row>
-    <row r="98" spans="1:17" ht="15.75" customHeight="1">
-      <c r="A98" s="10"/>
-    </row>
     <row r="99" spans="1:17" ht="15.75" customHeight="1">
-      <c r="A99" s="3"/>
-      <c r="B99" s="54" t="s">
-        <v>215</v>
-      </c>
-      <c r="C99" s="54"/>
-      <c r="D99" s="56"/>
-      <c r="E99" s="66" t="s">
+      <c r="A99" s="10"/>
+    </row>
+    <row r="100" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A100" s="3"/>
+      <c r="B100" s="54" t="s">
+        <v>214</v>
+      </c>
+      <c r="C100" s="54"/>
+      <c r="D100" s="56"/>
+      <c r="E100" s="66" t="s">
         <v>59</v>
       </c>
-      <c r="F99" s="56"/>
-      <c r="G99" s="37"/>
-      <c r="H99" s="37"/>
-      <c r="I99" s="37"/>
-      <c r="J99" s="37"/>
-      <c r="K99" s="37"/>
-      <c r="L99" s="37"/>
-      <c r="M99" s="37"/>
-      <c r="N99" s="37"/>
-      <c r="O99" s="37"/>
-      <c r="P99" s="37"/>
-      <c r="Q99" s="37"/>
-    </row>
-    <row r="100" spans="1:17" ht="15.75" customHeight="1">
-      <c r="A100" s="10"/>
-      <c r="B100" s="64" t="s">
-        <v>28</v>
-      </c>
-      <c r="E100" s="268"/>
-      <c r="G100" s="97" t="s">
-        <v>219</v>
-      </c>
+      <c r="F100" s="56"/>
+      <c r="G100" s="37"/>
+      <c r="H100" s="37"/>
+      <c r="I100" s="37"/>
+      <c r="J100" s="37"/>
+      <c r="K100" s="37"/>
+      <c r="L100" s="37"/>
+      <c r="M100" s="37"/>
+      <c r="N100" s="37"/>
+      <c r="O100" s="37"/>
+      <c r="P100" s="37"/>
+      <c r="Q100" s="37"/>
     </row>
     <row r="101" spans="1:17" ht="15.75" customHeight="1">
       <c r="A101" s="10"/>
-      <c r="B101" s="26" t="s">
+      <c r="B101" s="64" t="s">
+        <v>28</v>
+      </c>
+      <c r="E101" s="268"/>
+      <c r="G101" s="97" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="102" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A102" s="10"/>
+      <c r="B102" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="C101" s="344">
+      <c r="C102" s="344">
         <f>BS!G32</f>
         <v>2813131398.21</v>
       </c>
-      <c r="D101" s="26"/>
-      <c r="E101" s="269"/>
-      <c r="F101" s="26"/>
-      <c r="G101" s="333">
-        <f t="shared" ref="G101:Q101" si="42">IF(G$4="","",G105+G104)</f>
+      <c r="D102" s="26"/>
+      <c r="E102" s="269"/>
+      <c r="F102" s="26"/>
+      <c r="G102" s="333">
+        <f t="shared" ref="G102:Q102" si="42">IF(G$4="","",G106+G105)</f>
         <v>2813131398.21</v>
       </c>
-      <c r="H101" s="333">
+      <c r="H102" s="333">
         <f t="shared" si="42"/>
         <v>2821719171</v>
       </c>
-      <c r="I101" s="333">
+      <c r="I102" s="333">
         <f t="shared" si="42"/>
         <v>2804541794</v>
       </c>
-      <c r="J101" s="333">
+      <c r="J102" s="333">
         <f t="shared" si="42"/>
         <v>2115221333</v>
       </c>
-      <c r="K101" s="333">
+      <c r="K102" s="333">
         <f t="shared" si="42"/>
         <v>1078793118</v>
       </c>
-      <c r="L101" s="333">
+      <c r="L102" s="333">
         <f t="shared" si="42"/>
         <v>976418045</v>
       </c>
-      <c r="M101" s="333">
+      <c r="M102" s="333">
         <f t="shared" si="42"/>
         <v>913519795</v>
       </c>
-      <c r="N101" s="333">
+      <c r="N102" s="333">
         <f t="shared" si="42"/>
         <v>632755333</v>
       </c>
-      <c r="O101" s="333">
+      <c r="O102" s="333">
         <f t="shared" si="42"/>
         <v>521915458</v>
       </c>
-      <c r="P101" s="333">
+      <c r="P102" s="333">
         <f t="shared" si="42"/>
         <v>463292481</v>
       </c>
-      <c r="Q101" s="333" t="str">
+      <c r="Q102" s="333" t="str">
         <f t="shared" si="42"/>
-        <v/>
-      </c>
-    </row>
-    <row r="102" spans="1:17" ht="15.75" customHeight="1">
-      <c r="A102" s="10"/>
-      <c r="B102" s="93" t="s">
-        <v>210</v>
-      </c>
-      <c r="C102" s="345">
-        <f>BS!C4</f>
-        <v>435508276.29999995</v>
-      </c>
-      <c r="D102" s="89"/>
-      <c r="E102" s="270"/>
-      <c r="F102" s="89"/>
-      <c r="G102" s="346">
-        <f>IF(G$4="","",Data!D77)</f>
-        <v>286539091</v>
-      </c>
-      <c r="H102" s="346">
-        <f>IF(H$4="","",Data!E77)</f>
-        <v>273013471</v>
-      </c>
-      <c r="I102" s="346">
-        <f>IF(I$4="","",Data!F77)</f>
-        <v>232578044</v>
-      </c>
-      <c r="J102" s="346">
-        <f>IF(J$4="","",Data!G77)</f>
-        <v>139788443</v>
-      </c>
-      <c r="K102" s="346">
-        <f>IF(K$4="","",Data!H77)</f>
-        <v>109488661</v>
-      </c>
-      <c r="L102" s="346">
-        <f>IF(L$4="","",Data!I77)</f>
-        <v>0</v>
-      </c>
-      <c r="M102" s="346">
-        <f>IF(M$4="","",Data!J77)</f>
-        <v>0</v>
-      </c>
-      <c r="N102" s="346">
-        <f>IF(N$4="","",Data!K77)</f>
-        <v>0</v>
-      </c>
-      <c r="O102" s="346">
-        <f>IF(O$4="","",Data!L77)</f>
-        <v>0</v>
-      </c>
-      <c r="P102" s="346">
-        <f>IF(P$4="","",Data!M77)</f>
-        <v>0</v>
-      </c>
-      <c r="Q102" s="346" t="str">
-        <f>IF(Q$4="","",Data!N77)</f>
         <v/>
       </c>
     </row>
     <row r="103" spans="1:17" ht="15.75" customHeight="1">
       <c r="A103" s="10"/>
       <c r="B103" s="93" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C103" s="345">
-        <f>BS!C6+BS!C7</f>
-        <v>149619822.47999999</v>
+        <f>BS!C4</f>
+        <v>435508276.29999995</v>
       </c>
       <c r="D103" s="89"/>
       <c r="E103" s="270"/>
       <c r="F103" s="89"/>
       <c r="G103" s="346">
+        <f>IF(G$4="","",Data!D77)</f>
+        <v>286539091</v>
+      </c>
+      <c r="H103" s="346">
+        <f>IF(H$4="","",Data!E77)</f>
+        <v>273013471</v>
+      </c>
+      <c r="I103" s="346">
+        <f>IF(I$4="","",Data!F77)</f>
+        <v>232578044</v>
+      </c>
+      <c r="J103" s="346">
+        <f>IF(J$4="","",Data!G77)</f>
+        <v>139788443</v>
+      </c>
+      <c r="K103" s="346">
+        <f>IF(K$4="","",Data!H77)</f>
+        <v>109488661</v>
+      </c>
+      <c r="L103" s="346">
+        <f>IF(L$4="","",Data!I77)</f>
+        <v>0</v>
+      </c>
+      <c r="M103" s="346">
+        <f>IF(M$4="","",Data!J77)</f>
+        <v>0</v>
+      </c>
+      <c r="N103" s="346">
+        <f>IF(N$4="","",Data!K77)</f>
+        <v>0</v>
+      </c>
+      <c r="O103" s="346">
+        <f>IF(O$4="","",Data!L77)</f>
+        <v>0</v>
+      </c>
+      <c r="P103" s="346">
+        <f>IF(P$4="","",Data!M77)</f>
+        <v>0</v>
+      </c>
+      <c r="Q103" s="346" t="str">
+        <f>IF(Q$4="","",Data!N77)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="104" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A104" s="10"/>
+      <c r="B104" s="93" t="s">
+        <v>210</v>
+      </c>
+      <c r="C104" s="345">
+        <f>BS!C6+BS!C7</f>
+        <v>149619822.47999999</v>
+      </c>
+      <c r="D104" s="89"/>
+      <c r="E104" s="270"/>
+      <c r="F104" s="89"/>
+      <c r="G104" s="346">
         <f>IF(G$4="","",Data!D78)</f>
         <v>175557090</v>
       </c>
-      <c r="H103" s="346">
+      <c r="H104" s="346">
         <f>IF(H$4="","",Data!E78)</f>
         <v>221536955</v>
       </c>
-      <c r="I103" s="346">
+      <c r="I104" s="346">
         <f>IF(I$4="","",Data!F78)</f>
         <v>134930930</v>
       </c>
-      <c r="J103" s="346">
+      <c r="J104" s="346">
         <f>IF(J$4="","",Data!G78)</f>
         <v>102812384</v>
       </c>
-      <c r="K103" s="346">
+      <c r="K104" s="346">
         <f>IF(K$4="","",Data!H78)</f>
         <v>54993674</v>
       </c>
-      <c r="L103" s="346">
+      <c r="L104" s="346">
         <f>IF(L$4="","",Data!I78)</f>
         <v>0</v>
       </c>
-      <c r="M103" s="346">
+      <c r="M104" s="346">
         <f>IF(M$4="","",Data!J78)</f>
         <v>0</v>
       </c>
-      <c r="N103" s="346">
+      <c r="N104" s="346">
         <f>IF(N$4="","",Data!K78)</f>
         <v>0</v>
       </c>
-      <c r="O103" s="346">
+      <c r="O104" s="346">
         <f>IF(O$4="","",Data!L78)</f>
         <v>0</v>
       </c>
-      <c r="P103" s="346">
+      <c r="P104" s="346">
         <f>IF(P$4="","",Data!M78)</f>
         <v>0</v>
       </c>
-      <c r="Q103" s="346" t="str">
+      <c r="Q104" s="346" t="str">
         <f>IF(Q$4="","",Data!N78)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="104" spans="1:17" ht="15.75" customHeight="1">
-      <c r="A104" s="10"/>
-      <c r="B104" s="26" t="s">
-        <v>40</v>
-      </c>
-      <c r="C104" s="344">
-        <f>BS!G30</f>
-        <v>401550924.92000002</v>
-      </c>
-      <c r="D104" s="26"/>
-      <c r="E104" s="269"/>
-      <c r="F104" s="26"/>
-      <c r="G104" s="333">
-        <f>Data!C79</f>
-        <v>401550924.92000002</v>
-      </c>
-      <c r="H104" s="333">
-        <f>Data!D79</f>
-        <v>375837168</v>
-      </c>
-      <c r="I104" s="333">
-        <f>Data!E79</f>
-        <v>484715813</v>
-      </c>
-      <c r="J104" s="333">
-        <f>Data!F79</f>
-        <v>120473425</v>
-      </c>
-      <c r="K104" s="333">
-        <f>Data!G79</f>
-        <v>77386991</v>
-      </c>
-      <c r="L104" s="333">
-        <f>Data!H79</f>
-        <v>107878390</v>
-      </c>
-      <c r="M104" s="333">
-        <f>Data!I79</f>
-        <v>144733614</v>
-      </c>
-      <c r="N104" s="333">
-        <f>Data!J79</f>
-        <v>117054123</v>
-      </c>
-      <c r="O104" s="333">
-        <f>Data!K79</f>
-        <v>64103116</v>
-      </c>
-      <c r="P104" s="333">
-        <f>Data!L79</f>
-        <v>30979762</v>
-      </c>
-      <c r="Q104" s="333" t="str">
-        <f>Data!M79</f>
         <v/>
       </c>
     </row>
     <row r="105" spans="1:17" ht="15.75" customHeight="1">
       <c r="A105" s="10"/>
       <c r="B105" s="26" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="C105" s="344">
-        <f>BS!G27</f>
-        <v>2411580473.29</v>
+        <f>BS!G30</f>
+        <v>401550924.92000002</v>
       </c>
       <c r="D105" s="26"/>
       <c r="E105" s="269"/>
       <c r="F105" s="26"/>
       <c r="G105" s="333">
+        <f>Data!C79</f>
+        <v>401550924.92000002</v>
+      </c>
+      <c r="H105" s="333">
+        <f>Data!D79</f>
+        <v>375837168</v>
+      </c>
+      <c r="I105" s="333">
+        <f>Data!E79</f>
+        <v>484715813</v>
+      </c>
+      <c r="J105" s="333">
+        <f>Data!F79</f>
+        <v>120473425</v>
+      </c>
+      <c r="K105" s="333">
+        <f>Data!G79</f>
+        <v>77386991</v>
+      </c>
+      <c r="L105" s="333">
+        <f>Data!H79</f>
+        <v>107878390</v>
+      </c>
+      <c r="M105" s="333">
+        <f>Data!I79</f>
+        <v>144733614</v>
+      </c>
+      <c r="N105" s="333">
+        <f>Data!J79</f>
+        <v>117054123</v>
+      </c>
+      <c r="O105" s="333">
+        <f>Data!K79</f>
+        <v>64103116</v>
+      </c>
+      <c r="P105" s="333">
+        <f>Data!L79</f>
+        <v>30979762</v>
+      </c>
+      <c r="Q105" s="333" t="str">
+        <f>Data!M79</f>
+        <v/>
+      </c>
+    </row>
+    <row r="106" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A106" s="10"/>
+      <c r="B106" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="C106" s="344">
+        <f>BS!G27</f>
+        <v>2411580473.29</v>
+      </c>
+      <c r="D106" s="26"/>
+      <c r="E106" s="269"/>
+      <c r="F106" s="26"/>
+      <c r="G106" s="333">
         <f>Data!C80</f>
         <v>2411580473.29</v>
       </c>
-      <c r="H105" s="333">
+      <c r="H106" s="333">
         <f>Data!D80</f>
         <v>2445882003</v>
       </c>
-      <c r="I105" s="333">
+      <c r="I106" s="333">
         <f>Data!E80</f>
         <v>2319825981</v>
       </c>
-      <c r="J105" s="333">
+      <c r="J106" s="333">
         <f>Data!F80</f>
         <v>1994747908</v>
       </c>
-      <c r="K105" s="333">
+      <c r="K106" s="333">
         <f>Data!G80</f>
         <v>1001406127</v>
       </c>
-      <c r="L105" s="333">
+      <c r="L106" s="333">
         <f>Data!H80</f>
         <v>868539655</v>
       </c>
-      <c r="M105" s="333">
+      <c r="M106" s="333">
         <f>Data!I80</f>
         <v>768786181</v>
       </c>
-      <c r="N105" s="333">
+      <c r="N106" s="333">
         <f>Data!J80</f>
         <v>515701210</v>
       </c>
-      <c r="O105" s="333">
+      <c r="O106" s="333">
         <f>Data!K80</f>
         <v>457812342</v>
       </c>
-      <c r="P105" s="333">
+      <c r="P106" s="333">
         <f>Data!L80</f>
         <v>432312719</v>
       </c>
-      <c r="Q105" s="333" t="str">
+      <c r="Q106" s="333" t="str">
         <f>Data!M80</f>
         <v/>
       </c>
     </row>
-    <row r="106" spans="1:17" ht="15.75" customHeight="1">
-      <c r="A106" s="10"/>
-      <c r="E106" s="268"/>
-    </row>
     <row r="107" spans="1:17" ht="15.75" customHeight="1">
       <c r="A107" s="10"/>
-      <c r="B107" s="91" t="s">
-        <v>220</v>
-      </c>
-      <c r="C107" s="26"/>
-      <c r="D107" s="26"/>
-      <c r="E107" s="269"/>
-      <c r="F107" s="26"/>
-      <c r="G107" s="97" t="s">
-        <v>219</v>
-      </c>
-      <c r="H107" s="12"/>
-      <c r="I107" s="12"/>
-      <c r="J107" s="12"/>
-      <c r="K107" s="12"/>
-      <c r="L107" s="12"/>
-      <c r="M107" s="12"/>
-      <c r="N107" s="12"/>
-      <c r="O107" s="12"/>
-      <c r="P107" s="12"/>
-      <c r="Q107" s="12"/>
+      <c r="E107" s="268"/>
     </row>
     <row r="108" spans="1:17" ht="15.75" customHeight="1">
       <c r="A108" s="10"/>
-      <c r="B108" s="26" t="s">
-        <v>217</v>
-      </c>
-      <c r="C108" s="94">
-        <f>C102/C$4</f>
-        <v>0.30865070390856503</v>
-      </c>
+      <c r="B108" s="91" t="s">
+        <v>219</v>
+      </c>
+      <c r="C108" s="26"/>
       <c r="D108" s="26"/>
       <c r="E108" s="269"/>
       <c r="F108" s="26"/>
-      <c r="G108" s="94">
-        <f t="shared" ref="G108:Q108" si="43">IF(G$4="","",G102/G$4)</f>
-        <v>0.20307419387260534</v>
-      </c>
-      <c r="H108" s="94">
-        <f t="shared" si="43"/>
-        <v>0.19795039670760667</v>
-      </c>
-      <c r="I108" s="94">
-        <f t="shared" si="43"/>
-        <v>0.14564100708744146</v>
-      </c>
-      <c r="J108" s="94">
-        <f t="shared" si="43"/>
-        <v>0.100331907733994</v>
-      </c>
-      <c r="K108" s="94">
-        <f t="shared" si="43"/>
-        <v>0.11992950626314505</v>
-      </c>
-      <c r="L108" s="94">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="M108" s="94">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="N108" s="94">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="O108" s="94">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="P108" s="94">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="Q108" s="94" t="str">
-        <f t="shared" si="43"/>
-        <v/>
-      </c>
+      <c r="G108" s="97" t="s">
+        <v>218</v>
+      </c>
+      <c r="H108" s="12"/>
+      <c r="I108" s="12"/>
+      <c r="J108" s="12"/>
+      <c r="K108" s="12"/>
+      <c r="L108" s="12"/>
+      <c r="M108" s="12"/>
+      <c r="N108" s="12"/>
+      <c r="O108" s="12"/>
+      <c r="P108" s="12"/>
+      <c r="Q108" s="12"/>
     </row>
     <row r="109" spans="1:17" ht="15.75" customHeight="1">
       <c r="A109" s="10"/>
       <c r="B109" s="26" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C109" s="94">
         <f>C103/C$4</f>
-        <v>0.10603762555206932</v>
+        <v>0.30865070390856503</v>
       </c>
       <c r="D109" s="26"/>
       <c r="E109" s="269"/>
       <c r="F109" s="26"/>
       <c r="G109" s="94">
-        <f t="shared" ref="G109:Q109" si="44">IF(G$4="","",G103/G$4)</f>
-        <v>0.12441972369616551</v>
+        <f t="shared" ref="G109:Q109" si="43">IF(G$4="","",G103/G$4)</f>
+        <v>0.20307419387260534</v>
       </c>
       <c r="H109" s="94">
-        <f t="shared" si="44"/>
-        <v>0.16062697553720787</v>
+        <f t="shared" si="43"/>
+        <v>0.19795039670760667</v>
       </c>
       <c r="I109" s="94">
-        <f t="shared" si="44"/>
-        <v>8.4494117305608893E-2</v>
+        <f t="shared" si="43"/>
+        <v>0.14564100708744146</v>
       </c>
       <c r="J109" s="94">
-        <f t="shared" si="44"/>
-        <v>7.3792671296867951E-2</v>
+        <f t="shared" si="43"/>
+        <v>0.100331907733994</v>
       </c>
       <c r="K109" s="94">
-        <f t="shared" si="44"/>
-        <v>6.0237874042649554E-2</v>
+        <f t="shared" si="43"/>
+        <v>0.11992950626314505</v>
       </c>
       <c r="L109" s="94">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="M109" s="94">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="N109" s="94">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="O109" s="94">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="P109" s="94">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="Q109" s="94" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
     </row>
     <row r="110" spans="1:17" ht="15.75" customHeight="1">
       <c r="A110" s="10"/>
       <c r="B110" s="26" t="s">
-        <v>69</v>
+        <v>217</v>
       </c>
       <c r="C110" s="94">
-        <f>BS!$G$38/C$4</f>
-        <v>0</v>
+        <f>C104/C$4</f>
+        <v>0.10603762555206932</v>
       </c>
       <c r="D110" s="26"/>
       <c r="E110" s="269"/>
       <c r="F110" s="26"/>
       <c r="G110" s="94">
-        <f>BS!$G$38/G$4</f>
-        <v>0</v>
-      </c>
-      <c r="H110" s="204"/>
-      <c r="I110" s="204"/>
-      <c r="J110" s="204"/>
-      <c r="K110" s="204"/>
-      <c r="L110" s="204"/>
-      <c r="M110" s="204"/>
-      <c r="N110" s="204"/>
-      <c r="O110" s="204"/>
-      <c r="P110" s="204"/>
-      <c r="Q110" s="204"/>
+        <f t="shared" ref="G110:Q110" si="44">IF(G$4="","",G104/G$4)</f>
+        <v>0.12441972369616551</v>
+      </c>
+      <c r="H110" s="94">
+        <f t="shared" si="44"/>
+        <v>0.16062697553720787</v>
+      </c>
+      <c r="I110" s="94">
+        <f t="shared" si="44"/>
+        <v>8.4494117305608893E-2</v>
+      </c>
+      <c r="J110" s="94">
+        <f t="shared" si="44"/>
+        <v>7.3792671296867951E-2</v>
+      </c>
+      <c r="K110" s="94">
+        <f t="shared" si="44"/>
+        <v>6.0237874042649554E-2</v>
+      </c>
+      <c r="L110" s="94">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="M110" s="94">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="N110" s="94">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="O110" s="94">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="P110" s="94">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="Q110" s="94" t="str">
+        <f t="shared" si="44"/>
+        <v/>
+      </c>
     </row>
     <row r="111" spans="1:17" ht="15.75" customHeight="1">
       <c r="A111" s="10"/>
-      <c r="E111" s="268"/>
+      <c r="B111" s="26" t="s">
+        <v>69</v>
+      </c>
+      <c r="C111" s="94">
+        <f>BS!$G$38/C$4</f>
+        <v>0</v>
+      </c>
+      <c r="D111" s="26"/>
+      <c r="E111" s="269"/>
+      <c r="F111" s="26"/>
+      <c r="G111" s="94">
+        <f>BS!$G$38/G$4</f>
+        <v>0</v>
+      </c>
+      <c r="H111" s="204"/>
+      <c r="I111" s="204"/>
+      <c r="J111" s="204"/>
+      <c r="K111" s="204"/>
+      <c r="L111" s="204"/>
+      <c r="M111" s="204"/>
+      <c r="N111" s="204"/>
+      <c r="O111" s="204"/>
+      <c r="P111" s="204"/>
+      <c r="Q111" s="204"/>
     </row>
     <row r="112" spans="1:17" ht="15.75" customHeight="1">
       <c r="A112" s="10"/>
-      <c r="B112" s="64" t="s">
-        <v>51</v>
-      </c>
       <c r="E112" s="268"/>
     </row>
     <row r="113" spans="1:17" ht="15.75" customHeight="1">
       <c r="A113" s="10"/>
-      <c r="B113" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="C113" s="169"/>
+      <c r="B113" s="64" t="s">
+        <v>51</v>
+      </c>
       <c r="E113" s="268"/>
-      <c r="G113" s="295">
-        <f>IF(G$4="","",Data!C$22/Data!C15)</f>
-        <v>1.2880680206520347</v>
-      </c>
-      <c r="H113" s="295">
-        <f>IF(H$4="","",Data!D$22/Data!D15)</f>
-        <v>1.4762961966387407</v>
-      </c>
-      <c r="I113" s="295">
-        <f>IF(I$4="","",Data!E$22/Data!E15)</f>
-        <v>0.67983408599071948</v>
-      </c>
-      <c r="J113" s="295">
-        <f>IF(J$4="","",Data!F$22/Data!F15)</f>
-        <v>0.34179947012470702</v>
-      </c>
-      <c r="K113" s="295">
-        <f>IF(K$4="","",Data!G$22/Data!G15)</f>
-        <v>0.3261494079238545</v>
-      </c>
-      <c r="L113" s="295">
-        <f>IF(L$4="","",Data!H$22/Data!H15)</f>
-        <v>0.96883995833236425</v>
-      </c>
-      <c r="M113" s="295">
-        <f>IF(M$4="","",Data!I$22/Data!I15)</f>
-        <v>0.64186063555485706</v>
-      </c>
-      <c r="N113" s="295">
-        <f>IF(N$4="","",Data!J$22/Data!J15)</f>
-        <v>0.57060193795831449</v>
-      </c>
-      <c r="O113" s="295">
-        <f>IF(O$4="","",Data!K$22/Data!K15)</f>
-        <v>0.89694138362498099</v>
-      </c>
-      <c r="P113" s="295">
-        <f>IF(P$4="","",Data!L$22/Data!L15)</f>
-        <v>1.0465515121655735</v>
-      </c>
-      <c r="Q113" s="295" t="str">
-        <f>IF(Q$4="","",Data!M$22/Data!M15)</f>
-        <v/>
-      </c>
     </row>
     <row r="114" spans="1:17" ht="15.75" customHeight="1">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="C114" s="169"/>
       <c r="E114" s="268"/>
       <c r="G114" s="295">
+        <f>IF(G$4="","",Data!C$22/Data!C15)</f>
+        <v>1.2880680206520347</v>
+      </c>
+      <c r="H114" s="295">
+        <f>IF(H$4="","",Data!D$22/Data!D15)</f>
+        <v>1.4762961966387407</v>
+      </c>
+      <c r="I114" s="295">
+        <f>IF(I$4="","",Data!E$22/Data!E15)</f>
+        <v>0.67983408599071948</v>
+      </c>
+      <c r="J114" s="295">
+        <f>IF(J$4="","",Data!F$22/Data!F15)</f>
+        <v>0.34179947012470702</v>
+      </c>
+      <c r="K114" s="295">
+        <f>IF(K$4="","",Data!G$22/Data!G15)</f>
+        <v>0.3261494079238545</v>
+      </c>
+      <c r="L114" s="295">
+        <f>IF(L$4="","",Data!H$22/Data!H15)</f>
+        <v>0.96883995833236425</v>
+      </c>
+      <c r="M114" s="295">
+        <f>IF(M$4="","",Data!I$22/Data!I15)</f>
+        <v>0.64186063555485706</v>
+      </c>
+      <c r="N114" s="295">
+        <f>IF(N$4="","",Data!J$22/Data!J15)</f>
+        <v>0.57060193795831449</v>
+      </c>
+      <c r="O114" s="295">
+        <f>IF(O$4="","",Data!K$22/Data!K15)</f>
+        <v>0.89694138362498099</v>
+      </c>
+      <c r="P114" s="295">
+        <f>IF(P$4="","",Data!L$22/Data!L15)</f>
+        <v>1.0465515121655735</v>
+      </c>
+      <c r="Q114" s="295" t="str">
+        <f>IF(Q$4="","",Data!M$22/Data!M15)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="115" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A115" s="10"/>
+      <c r="B115" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="C115" s="169"/>
+      <c r="E115" s="268"/>
+      <c r="G115" s="295">
         <f>IF(G$4="","",Data!C$22/G19)</f>
         <v>1.6721091266857355</v>
       </c>
-      <c r="H114" s="295">
+      <c r="H115" s="295">
         <f>IF(H$4="","",Data!D$22/H19)</f>
         <v>1.7887230090926192</v>
       </c>
-      <c r="I114" s="295">
+      <c r="I115" s="295">
         <f>IF(I$4="","",Data!E$22/I19)</f>
         <v>0.75215129607307663</v>
       </c>
-      <c r="J114" s="295">
+      <c r="J115" s="295">
         <f>IF(J$4="","",Data!F$22/J19)</f>
         <v>0.34909279020031797</v>
       </c>
-      <c r="K114" s="295">
+      <c r="K115" s="295">
         <f>IF(K$4="","",Data!G$22/K19)</f>
         <v>0.3153093554346863</v>
       </c>
-      <c r="L114" s="295">
+      <c r="L115" s="295">
         <f>IF(L$4="","",Data!H$22/L19)</f>
         <v>0.9132965965600931</v>
       </c>
-      <c r="M114" s="295">
+      <c r="M115" s="295">
         <f>IF(M$4="","",Data!I$22/M19)</f>
         <v>0.62697024830003711</v>
       </c>
-      <c r="N114" s="295">
+      <c r="N115" s="295">
         <f>IF(N$4="","",Data!J$22/N19)</f>
         <v>0.42677417512358501</v>
       </c>
-      <c r="O114" s="295">
+      <c r="O115" s="295">
         <f>IF(O$4="","",Data!K$22/O19)</f>
         <v>0.88971565440898526</v>
       </c>
-      <c r="P114" s="295">
+      <c r="P115" s="295">
         <f>IF(P$4="","",Data!L$22/P19)</f>
         <v>0.94505127089456842</v>
       </c>
-      <c r="Q114" s="295" t="str">
+      <c r="Q115" s="295" t="str">
         <f>IF(Q$4="","",Data!M$22/Q19)</f>
         <v/>
       </c>
     </row>
-    <row r="115" spans="1:17" ht="15.75" customHeight="1">
-      <c r="A115" s="10"/>
-      <c r="E115" s="268"/>
-    </row>
     <row r="116" spans="1:17" ht="15.75" customHeight="1">
       <c r="A116" s="10"/>
-      <c r="B116" s="91" t="s">
-        <v>38</v>
-      </c>
-      <c r="C116" s="55"/>
-      <c r="D116" s="55"/>
-      <c r="E116" s="271"/>
-      <c r="F116" s="55"/>
-      <c r="G116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*G118*(1/#REF!)=G120,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="H116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*H118*(1/#REF!)=H120,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="I116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*I118*(1/#REF!)=I120,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="J116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*J118*(1/#REF!)=J120,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="K116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*K118*(1/#REF!)=K120,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="L116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*L118*(1/#REF!)=L120,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="M116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*M118*(1/#REF!)=M120,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="N116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*N118*(1/#REF!)=N120,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="O116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*O118*(1/#REF!)=O120,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="P116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*P118*(1/#REF!)=P120,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="Q116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*Q118*(1/#REF!)=Q120,"","Error"),"")</f>
-        <v/>
-      </c>
+      <c r="E116" s="268"/>
     </row>
     <row r="117" spans="1:17" ht="15.75" customHeight="1">
       <c r="A117" s="10"/>
-      <c r="B117" s="7" t="s">
-        <v>221</v>
-      </c>
-      <c r="C117" s="23">
+      <c r="B117" s="91" t="s">
+        <v>38</v>
+      </c>
+      <c r="C117" s="55"/>
+      <c r="D117" s="55"/>
+      <c r="E117" s="271"/>
+      <c r="F117" s="55"/>
+      <c r="G117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*G119*(1/#REF!)=G121,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="H117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*H119*(1/#REF!)=H121,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="I117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*I119*(1/#REF!)=I121,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="J117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*J119*(1/#REF!)=J121,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="K117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*K119*(1/#REF!)=K121,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="L117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*L119*(1/#REF!)=L121,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="M117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*M119*(1/#REF!)=M121,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="N117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*N119*(1/#REF!)=N121,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="O117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*O119*(1/#REF!)=O121,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="P117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*P119*(1/#REF!)=P121,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="Q117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*Q119*(1/#REF!)=Q121,"","Error"),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="118" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A118" s="10"/>
+      <c r="B118" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="C118" s="23">
         <f>IF(valuation_method="DDM",C13/(C4+C12),C81)</f>
         <v>0.12235120428336442</v>
       </c>
-      <c r="E117" s="268"/>
-      <c r="G117" s="23">
-        <f t="shared" ref="G117:Q117" si="45">IF(G4="","",IF(valuation_method="DDM",G13/(G4+G12),G81))</f>
+      <c r="E118" s="268"/>
+      <c r="G118" s="23">
+        <f t="shared" ref="G118:Q118" si="45">IF(G4="","",IF(valuation_method="DDM",G13/(G4+G12),G81))</f>
         <v>0.12459084820450472</v>
       </c>
-      <c r="H117" s="23">
+      <c r="H118" s="23">
         <f t="shared" si="45"/>
         <v>0.16222123763436222</v>
       </c>
-      <c r="I117" s="23">
+      <c r="I118" s="23">
         <f t="shared" si="45"/>
         <v>0.27715402613389095</v>
       </c>
-      <c r="J117" s="23">
+      <c r="J118" s="23">
         <f t="shared" si="45"/>
         <v>0.20450693197459704</v>
       </c>
-      <c r="K117" s="23">
+      <c r="K118" s="23">
         <f t="shared" si="45"/>
         <v>0.23591961570808129</v>
       </c>
-      <c r="L117" s="23">
+      <c r="L118" s="23">
         <f t="shared" si="45"/>
         <v>0.25801459101459318</v>
       </c>
-      <c r="M117" s="23">
+      <c r="M118" s="23">
         <f t="shared" si="45"/>
         <v>0.19638483469999488</v>
       </c>
-      <c r="N117" s="23">
+      <c r="N118" s="23">
         <f t="shared" si="45"/>
         <v>0.20348688424099767</v>
       </c>
-      <c r="O117" s="23">
+      <c r="O118" s="23">
         <f t="shared" si="45"/>
         <v>0.20198223481958236</v>
       </c>
-      <c r="P117" s="23">
+      <c r="P118" s="23">
         <f t="shared" si="45"/>
         <v>0.21061143333334809</v>
       </c>
-      <c r="Q117" s="23" t="str">
+      <c r="Q118" s="23" t="str">
         <f t="shared" si="45"/>
         <v/>
       </c>
     </row>
-    <row r="118" spans="1:17" ht="15.75" customHeight="1">
-      <c r="B118" s="7" t="s">
+    <row r="119" spans="1:17" ht="15.75" customHeight="1">
+      <c r="B119" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="C118" s="42">
-        <f>IF(valuation_method="DDM",(C4+C12)/C101,C4/C101)</f>
+      <c r="C119" s="42">
+        <f>IF(valuation_method="DDM",(C4+C12)/C102,C4/C102)</f>
         <v>0.50157874313934503</v>
       </c>
-      <c r="E118" s="268"/>
-      <c r="G118" s="42">
-        <f t="shared" ref="G118:Q118" si="46">IF(G4="","",IF(valuation_method="DDM",(G4+G12)/G101,G4/G101))</f>
+      <c r="E119" s="268"/>
+      <c r="G119" s="42">
+        <f t="shared" ref="G119:Q119" si="46">IF(G4="","",IF(valuation_method="DDM",(G4+G12)/G102,G4/G102))</f>
         <v>0.50157874313934503</v>
       </c>
-      <c r="H118" s="42">
+      <c r="H119" s="42">
         <f t="shared" si="46"/>
         <v>0.48878054491553796</v>
       </c>
-      <c r="I118" s="42">
+      <c r="I119" s="42">
         <f t="shared" si="46"/>
         <v>0.5694074224233151</v>
       </c>
-      <c r="J118" s="42">
+      <c r="J119" s="42">
         <f t="shared" si="46"/>
         <v>0.65868288592946034</v>
       </c>
-      <c r="K118" s="42">
+      <c r="K119" s="42">
         <f t="shared" si="46"/>
         <v>0.84626217832435224</v>
       </c>
-      <c r="L118" s="42">
+      <c r="L119" s="42">
         <f t="shared" si="46"/>
         <v>0.69668293563747075</v>
       </c>
-      <c r="M118" s="42">
+      <c r="M119" s="42">
         <f t="shared" si="46"/>
         <v>0.69603582591223434</v>
       </c>
-      <c r="N118" s="42">
+      <c r="N119" s="42">
         <f t="shared" si="46"/>
         <v>0.85486356066792724</v>
       </c>
-      <c r="O118" s="42">
+      <c r="O119" s="42">
         <f t="shared" si="46"/>
         <v>0.72003472447447614</v>
       </c>
-      <c r="P118" s="42">
+      <c r="P119" s="42">
         <f t="shared" si="46"/>
         <v>0.75592186224148972</v>
       </c>
-      <c r="Q118" s="42" t="str">
+      <c r="Q119" s="42" t="str">
         <f t="shared" si="46"/>
         <v/>
       </c>
     </row>
-    <row r="119" spans="1:17" ht="15.75" customHeight="1">
-      <c r="B119" s="7" t="s">
+    <row r="120" spans="1:17" ht="15.75" customHeight="1">
+      <c r="B120" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="C119" s="15">
-        <f>C101/C105</f>
+      <c r="C120" s="15">
+        <f>C102/C106</f>
         <v>1.1665094444773738</v>
       </c>
-      <c r="D119" s="11"/>
-      <c r="E119" s="272"/>
-      <c r="F119" s="11"/>
-      <c r="G119" s="15">
-        <f t="shared" ref="G119:Q119" si="47">IF(G$4="","",G101/G105)</f>
+      <c r="D120" s="11"/>
+      <c r="E120" s="272"/>
+      <c r="F120" s="11"/>
+      <c r="G120" s="15">
+        <f t="shared" ref="G120:Q120" si="47">IF(G$4="","",G102/G106)</f>
         <v>1.1665094444773738</v>
       </c>
-      <c r="H119" s="15">
+      <c r="H120" s="15">
         <f t="shared" si="47"/>
         <v>1.15366120178284</v>
       </c>
-      <c r="I119" s="15">
+      <c r="I120" s="15">
         <f t="shared" si="47"/>
         <v>1.2089449023202401</v>
       </c>
-      <c r="J119" s="15">
+      <c r="J120" s="15">
         <f t="shared" si="47"/>
         <v>1.0603953133710968</v>
       </c>
-      <c r="K119" s="15">
+      <c r="K120" s="15">
         <f t="shared" si="47"/>
         <v>1.0772783278566858</v>
       </c>
-      <c r="L119" s="15">
+      <c r="L120" s="15">
         <f t="shared" si="47"/>
         <v>1.1242066374044832</v>
       </c>
-      <c r="M119" s="15">
+      <c r="M120" s="15">
         <f t="shared" si="47"/>
         <v>1.1882625072835433</v>
       </c>
-      <c r="N119" s="15">
+      <c r="N120" s="15">
         <f t="shared" si="47"/>
         <v>1.2269805087329542</v>
       </c>
-      <c r="O119" s="15">
+      <c r="O120" s="15">
         <f t="shared" si="47"/>
         <v>1.1400205064807973</v>
       </c>
-      <c r="P119" s="15">
+      <c r="P120" s="15">
         <f t="shared" si="47"/>
         <v>1.0716605379357345</v>
       </c>
-      <c r="Q119" s="15" t="str">
+      <c r="Q120" s="15" t="str">
         <f t="shared" si="47"/>
         <v/>
       </c>
     </row>
-    <row r="120" spans="1:17" ht="15.75" customHeight="1">
-      <c r="A120" s="10"/>
-      <c r="B120" s="70" t="s">
-        <v>222</v>
-      </c>
-      <c r="C120" s="102">
-        <f>C13/C105</f>
+    <row r="121" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A121" s="10"/>
+      <c r="B121" s="70" t="s">
+        <v>221</v>
+      </c>
+      <c r="C121" s="102">
+        <f>C13/C106</f>
         <v>7.1587241945726146E-2</v>
       </c>
-      <c r="D120" s="103"/>
-      <c r="E120" s="271"/>
-      <c r="F120" s="103"/>
-      <c r="G120" s="102">
-        <f>IF(G$4="","",G13/G105)</f>
+      <c r="D121" s="103"/>
+      <c r="E121" s="271"/>
+      <c r="F121" s="103"/>
+      <c r="G121" s="102">
+        <f t="shared" ref="G121:Q121" si="48">IF(G$4="","",G13/G106)</f>
         <v>7.2897649409175577E-2</v>
       </c>
-      <c r="H120" s="102">
-        <f t="shared" ref="H120:Q120" si="48">IF(H$4="","",H13/H105)</f>
+      <c r="H121" s="102">
+        <f t="shared" si="48"/>
         <v>9.1474471497866097E-2</v>
       </c>
-      <c r="I120" s="102">
+      <c r="I121" s="102">
         <f t="shared" si="48"/>
         <v>0.1907878984379173</v>
       </c>
-      <c r="J120" s="102">
+      <c r="J121" s="102">
         <f t="shared" si="48"/>
         <v>0.1428407798874427</v>
       </c>
-      <c r="K120" s="102">
+      <c r="K121" s="102">
         <f t="shared" si="48"/>
         <v>0.21507845430100769</v>
       </c>
-      <c r="L120" s="102">
+      <c r="L121" s="102">
         <f t="shared" si="48"/>
         <v>0.20208104765576529</v>
       </c>
-      <c r="M120" s="102">
+      <c r="M121" s="102">
         <f t="shared" si="48"/>
         <v>0.16242464852480962</v>
       </c>
-      <c r="N120" s="102">
+      <c r="N121" s="102">
         <f t="shared" si="48"/>
         <v>0.21343758142432903</v>
       </c>
-      <c r="O120" s="102">
+      <c r="O121" s="102">
         <f t="shared" si="48"/>
         <v>0.16579799633274195</v>
       </c>
-      <c r="P120" s="102">
+      <c r="P121" s="102">
         <f t="shared" si="48"/>
         <v>0.17061455922604951</v>
       </c>
-      <c r="Q120" s="102" t="str">
+      <c r="Q121" s="102" t="str">
         <f t="shared" si="48"/>
         <v/>
       </c>
     </row>
-    <row r="121" spans="1:17" ht="15.75" customHeight="1">
-      <c r="A121" s="10"/>
-      <c r="B121" s="27"/>
-      <c r="C121" s="62"/>
-      <c r="D121" s="27"/>
-      <c r="E121" s="67"/>
-      <c r="F121" s="27"/>
-      <c r="G121" s="12"/>
-      <c r="H121" s="12"/>
-      <c r="I121" s="12"/>
-      <c r="J121" s="12"/>
-      <c r="K121" s="12"/>
-      <c r="L121" s="12"/>
-      <c r="M121" s="12"/>
-      <c r="N121" s="12"/>
-      <c r="O121" s="12"/>
-      <c r="P121" s="12"/>
-      <c r="Q121" s="12"/>
-    </row>
     <row r="122" spans="1:17" ht="15.75" customHeight="1">
       <c r="A122" s="10"/>
-      <c r="B122" s="54" t="s">
-        <v>223</v>
-      </c>
-      <c r="C122" s="54"/>
-      <c r="D122" s="56"/>
-      <c r="E122" s="66" t="s">
-        <v>59</v>
-      </c>
-      <c r="F122" s="56"/>
-      <c r="G122" s="37"/>
-      <c r="H122" s="37"/>
-      <c r="I122" s="37"/>
-      <c r="J122" s="37"/>
-      <c r="K122" s="37"/>
-      <c r="L122" s="37"/>
-      <c r="M122" s="37"/>
-      <c r="N122" s="37"/>
-      <c r="O122" s="37"/>
-      <c r="P122" s="37"/>
-      <c r="Q122" s="37"/>
+      <c r="B122" s="27"/>
+      <c r="C122" s="62"/>
+      <c r="D122" s="27"/>
+      <c r="E122" s="67"/>
+      <c r="F122" s="27"/>
+      <c r="G122" s="12"/>
+      <c r="H122" s="12"/>
+      <c r="I122" s="12"/>
+      <c r="J122" s="12"/>
+      <c r="K122" s="12"/>
+      <c r="L122" s="12"/>
+      <c r="M122" s="12"/>
+      <c r="N122" s="12"/>
+      <c r="O122" s="12"/>
+      <c r="P122" s="12"/>
+      <c r="Q122" s="12"/>
     </row>
     <row r="123" spans="1:17" ht="15.75" customHeight="1">
       <c r="A123" s="10"/>
-      <c r="B123" s="178" t="s">
-        <v>170</v>
-      </c>
-      <c r="C123" s="179"/>
-      <c r="D123" s="27"/>
-      <c r="E123" s="265"/>
-      <c r="F123" s="27"/>
-      <c r="G123" s="12"/>
-      <c r="H123" s="12"/>
-      <c r="I123" s="12"/>
-      <c r="J123" s="12"/>
-      <c r="K123" s="12"/>
-      <c r="L123" s="12"/>
-      <c r="M123" s="12"/>
-      <c r="N123" s="12"/>
-      <c r="O123" s="12"/>
-      <c r="P123" s="12"/>
-      <c r="Q123" s="12"/>
+      <c r="B123" s="54" t="s">
+        <v>222</v>
+      </c>
+      <c r="C123" s="54"/>
+      <c r="D123" s="56"/>
+      <c r="E123" s="66" t="s">
+        <v>59</v>
+      </c>
+      <c r="F123" s="56"/>
+      <c r="G123" s="37"/>
+      <c r="H123" s="37"/>
+      <c r="I123" s="37"/>
+      <c r="J123" s="37"/>
+      <c r="K123" s="37"/>
+      <c r="L123" s="37"/>
+      <c r="M123" s="37"/>
+      <c r="N123" s="37"/>
+      <c r="O123" s="37"/>
+      <c r="P123" s="37"/>
+      <c r="Q123" s="37"/>
     </row>
     <row r="124" spans="1:17" ht="15.75" customHeight="1">
       <c r="A124" s="10"/>
-      <c r="B124" s="27" t="str">
-        <f>"FCFE per share ("&amp;Market_currency&amp;")"</f>
-        <v>FCFE per share (CNY)</v>
-      </c>
-      <c r="C124" s="177">
-        <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>0.44364016993149191</v>
-      </c>
+      <c r="B124" s="178" t="s">
+        <v>169</v>
+      </c>
+      <c r="C124" s="179"/>
       <c r="D124" s="27"/>
       <c r="E124" s="265"/>
       <c r="F124" s="27"/>
-      <c r="G124" s="177">
-        <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>0.50552613949892589</v>
-      </c>
-      <c r="H124" s="177">
-        <f t="shared" si="49"/>
-        <v>0.66477796644846865</v>
-      </c>
-      <c r="I124" s="177">
-        <f t="shared" si="49"/>
-        <v>1.3075251750377523</v>
-      </c>
-      <c r="J124" s="177">
-        <f t="shared" si="49"/>
-        <v>0.84670890681695921</v>
-      </c>
-      <c r="K124" s="177">
-        <f t="shared" si="49"/>
-        <v>0.63316665328921717</v>
-      </c>
-      <c r="L124" s="177">
-        <f t="shared" si="49"/>
-        <v>0.52602016075156</v>
-      </c>
-      <c r="M124" s="177">
-        <f t="shared" si="49"/>
-        <v>0.37092949160555189</v>
-      </c>
-      <c r="N124" s="177">
-        <f t="shared" si="49"/>
-        <v>0.33719511164290866</v>
-      </c>
-      <c r="O124" s="177">
-        <f t="shared" si="49"/>
-        <v>0.22309205011283703</v>
-      </c>
-      <c r="P124" s="177">
-        <f t="shared" si="49"/>
-        <v>0.21813570936444227</v>
-      </c>
-      <c r="Q124" s="177" t="str">
-        <f t="shared" si="49"/>
-        <v/>
-      </c>
+      <c r="G124" s="12"/>
+      <c r="H124" s="12"/>
+      <c r="I124" s="12"/>
+      <c r="J124" s="12"/>
+      <c r="K124" s="12"/>
+      <c r="L124" s="12"/>
+      <c r="M124" s="12"/>
+      <c r="N124" s="12"/>
+      <c r="O124" s="12"/>
+      <c r="P124" s="12"/>
+      <c r="Q124" s="12"/>
     </row>
     <row r="125" spans="1:17" ht="15.75" customHeight="1">
       <c r="A125" s="10"/>
-      <c r="B125" s="27" t="s">
-        <v>269</v>
-      </c>
-      <c r="C125" s="77">
-        <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>3.1553354902666565E-2</v>
+      <c r="B125" s="27" t="str">
+        <f>"FCFE per share ("&amp;Market_currency&amp;")"</f>
+        <v>FCFE per share (CNY)</v>
+      </c>
+      <c r="C125" s="177">
+        <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
+        <v>0.44364016993149191</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
-      <c r="G125" s="77">
-        <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
+      <c r="G125" s="177">
+        <f t="shared" ref="G125:Q125" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
+        <v>0.50552613949892589</v>
+      </c>
+      <c r="H125" s="177">
+        <f t="shared" si="49"/>
+        <v>0.66477796644846865</v>
+      </c>
+      <c r="I125" s="177">
+        <f t="shared" si="49"/>
+        <v>1.3075251750377523</v>
+      </c>
+      <c r="J125" s="177">
+        <f t="shared" si="49"/>
+        <v>0.84670890681695921</v>
+      </c>
+      <c r="K125" s="177">
+        <f t="shared" si="49"/>
+        <v>0.63316665328921717</v>
+      </c>
+      <c r="L125" s="177">
+        <f t="shared" si="49"/>
+        <v>0.52602016075156</v>
+      </c>
+      <c r="M125" s="177">
+        <f t="shared" si="49"/>
+        <v>0.37092949160555189</v>
+      </c>
+      <c r="N125" s="177">
+        <f t="shared" si="49"/>
+        <v>0.33719511164290866</v>
+      </c>
+      <c r="O125" s="177">
+        <f t="shared" si="49"/>
+        <v>0.22309205011283703</v>
+      </c>
+      <c r="P125" s="177">
+        <f t="shared" si="49"/>
+        <v>0.21813570936444227</v>
+      </c>
+      <c r="Q125" s="177" t="str">
+        <f t="shared" si="49"/>
+        <v/>
+      </c>
+    </row>
+    <row r="126" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A126" s="10"/>
+      <c r="B126" s="27" t="s">
+        <v>268</v>
+      </c>
+      <c r="C126" s="77">
+        <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
+        <v>3.1553354902666565E-2</v>
+      </c>
+      <c r="D126" s="27"/>
+      <c r="E126" s="265"/>
+      <c r="F126" s="27"/>
+      <c r="G126" s="77">
+        <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
         <v>3.5954917460805536E-2</v>
       </c>
-      <c r="H125" s="77">
-        <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
+      <c r="H126" s="77">
+        <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
         <v>4.7281505437302175E-2</v>
       </c>
-      <c r="I125" s="77">
-        <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
+      <c r="I126" s="77">
+        <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
         <v>9.2996100642798882E-2</v>
       </c>
-      <c r="J125" s="77">
-        <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
+      <c r="J126" s="77">
+        <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
         <v>6.0221117127806485E-2</v>
       </c>
-      <c r="K125" s="77">
-        <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
+      <c r="K126" s="77">
+        <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
         <v>4.5033190134368219E-2</v>
       </c>
-      <c r="L125" s="77">
-        <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
+      <c r="L126" s="77">
+        <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
         <v>3.7412529214193455E-2</v>
       </c>
-      <c r="M125" s="77">
-        <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
+      <c r="M126" s="77">
+        <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
         <v>2.6381898407222749E-2</v>
       </c>
-      <c r="N125" s="77">
-        <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
+      <c r="N126" s="77">
+        <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
         <v>2.3982582620406021E-2</v>
       </c>
-      <c r="O125" s="77">
-        <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
+      <c r="O126" s="77">
+        <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
         <v>1.586714438924872E-2</v>
       </c>
-      <c r="P125" s="77">
-        <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
+      <c r="P126" s="77">
+        <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
         <v>1.5514630822506561E-2</v>
       </c>
-      <c r="Q125" s="77" t="str">
-        <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
+      <c r="Q126" s="77" t="str">
+        <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
         <v/>
       </c>
     </row>
-    <row r="126" spans="1:17" ht="15.75" customHeight="1">
-      <c r="B126" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="C126" s="169"/>
-      <c r="G126" s="23">
+    <row r="127" spans="1:17" ht="15.75" customHeight="1">
+      <c r="B127" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C127" s="169"/>
+      <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
         <v>4.6674977308272546E-2</v>
       </c>
-      <c r="H126" s="23">
+      <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
         <v>5.7287634333000916E-2</v>
       </c>
-      <c r="I126" s="23">
+      <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
         <v>0.10288854158627507</v>
       </c>
-      <c r="J126" s="23">
+      <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
         <v>6.1506115850489401E-2</v>
       </c>
-      <c r="K126" s="23">
+      <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
         <v>4.353644620980094E-2</v>
       </c>
-      <c r="L126" s="23">
+      <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
         <v>3.5267677913327994E-2</v>
       </c>
-      <c r="M126" s="23">
+      <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
         <v>2.5769870402948463E-2</v>
       </c>
-      <c r="N126" s="23">
+      <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
         <v>1.7937455578541581E-2</v>
       </c>
-      <c r="O126" s="23">
+      <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
         <v>1.5739319214849418E-2</v>
       </c>
-      <c r="P126" s="23">
+      <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
         <v>1.4009937786942107E-2</v>
       </c>
-      <c r="Q126" s="23" t="str">
+      <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
         <v/>
       </c>
     </row>
-    <row r="127" spans="1:17" ht="15.75" customHeight="1"/>
     <row r="128" spans="1:17" ht="15.75" customHeight="1"/>
     <row r="129" ht="15.75" customHeight="1"/>
     <row r="130" ht="15.75" customHeight="1"/>
@@ -15461,6 +15483,7 @@
     <row r="806" ht="15.75" customHeight="1"/>
     <row r="807" ht="15.75" customHeight="1"/>
     <row r="808" ht="15.75" customHeight="1"/>
+    <row r="809" ht="15.75" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="G4:Q13 G15:Q16 G23:Q24 G34:Q34">
@@ -15482,13 +15505,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:Q105"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="6.1328125" customWidth="1"/>
-    <col min="2" max="2" width="24.6640625" customWidth="1"/>
-    <col min="3" max="6" width="20.6640625" customWidth="1"/>
-    <col min="7" max="7" width="5.6640625" customWidth="1"/>
-    <col min="8" max="8" width="56.796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.73046875" customWidth="1"/>
+    <col min="3" max="6" width="20.73046875" customWidth="1"/>
+    <col min="7" max="7" width="5.73046875" customWidth="1"/>
+    <col min="8" max="8" width="56.86328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="13.9">
@@ -15505,20 +15528,20 @@
     </row>
     <row r="3" spans="2:8" ht="13.15">
       <c r="B3" s="109" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C3" s="107">
         <f>scaling_factor</f>
         <v>1</v>
       </c>
       <c r="E3" s="109" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H3" s="120"/>
     </row>
     <row r="4" spans="2:8">
       <c r="B4" s="100" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C4" s="338">
         <f>Normalized_FCF!C19</f>
@@ -15529,7 +15552,7 @@
         <v>CNY</v>
       </c>
       <c r="E4" s="100" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F4" s="134">
         <f>Terminal_Growth</f>
@@ -15539,7 +15562,7 @@
     </row>
     <row r="5" spans="2:8">
       <c r="B5" s="205" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C5" s="206">
         <f>Equity_Cost</f>
@@ -15548,9 +15571,9 @@
       <c r="E5" s="148"/>
       <c r="H5" s="120"/>
     </row>
-    <row r="6" spans="2:8" ht="13.25" customHeight="1">
+    <row r="6" spans="2:8" ht="13.35" customHeight="1">
       <c r="B6" s="149" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C6" s="347">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
@@ -15560,15 +15583,15 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="364" t="s">
-        <v>249</v>
-      </c>
-      <c r="F6" s="364"/>
+      <c r="E6" s="366" t="s">
+        <v>248</v>
+      </c>
+      <c r="F6" s="366"/>
       <c r="H6" s="120"/>
     </row>
     <row r="7" spans="2:8">
       <c r="B7" s="148" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C7" s="338">
         <f>BS!G31</f>
@@ -15578,13 +15601,13 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="364"/>
-      <c r="F7" s="364"/>
+      <c r="E7" s="366"/>
+      <c r="F7" s="366"/>
       <c r="H7" s="120"/>
     </row>
     <row r="8" spans="2:8">
       <c r="B8" s="148" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C8" s="338">
         <f>BS!D66</f>
@@ -15594,13 +15617,13 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="364"/>
-      <c r="F8" s="364"/>
+      <c r="E8" s="366"/>
+      <c r="F8" s="366"/>
       <c r="H8" s="120"/>
     </row>
     <row r="9" spans="2:8">
       <c r="B9" s="205" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C9" s="348">
         <f>BS!H42</f>
@@ -15610,13 +15633,13 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="364"/>
-      <c r="F9" s="364"/>
+      <c r="E9" s="366"/>
+      <c r="F9" s="366"/>
       <c r="H9" s="120"/>
     </row>
     <row r="10" spans="2:8" ht="13.15">
       <c r="B10" s="149" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C10" s="347">
         <f>C6-C7+C8+C9</f>
@@ -15630,7 +15653,7 @@
     </row>
     <row r="11" spans="2:8" ht="13.15" thickBot="1">
       <c r="B11" s="207" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C11" s="208">
         <f>Exchange_Rate</f>
@@ -15661,7 +15684,7 @@
     </row>
     <row r="14" spans="2:8" ht="13.9">
       <c r="B14" s="36" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C14" s="37"/>
       <c r="D14" s="37"/>
@@ -15671,13 +15694,13 @@
     </row>
     <row r="15" spans="2:8" ht="13.15">
       <c r="B15" s="119" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H15" s="120"/>
     </row>
-    <row r="16" spans="2:8" ht="13.25" customHeight="1">
+    <row r="16" spans="2:8" ht="13.35" customHeight="1">
       <c r="B16" s="152" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C16" s="161">
         <f>Scenarios!C65</f>
@@ -15685,9 +15708,9 @@
       </c>
       <c r="H16" s="120"/>
     </row>
-    <row r="17" spans="2:17" ht="13.25" customHeight="1">
+    <row r="17" spans="2:17" ht="13.35" customHeight="1">
       <c r="B17" s="118" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C17" s="162">
         <f>Scenarios!C64</f>
@@ -15695,7 +15718,7 @@
       </c>
       <c r="H17" s="120"/>
     </row>
-    <row r="18" spans="2:17" ht="13.25" customHeight="1">
+    <row r="18" spans="2:17" ht="13.35" customHeight="1">
       <c r="B18" s="153" t="s">
         <v>106</v>
       </c>
@@ -15720,7 +15743,7 @@
         <v>108</v>
       </c>
       <c r="D20" s="128" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E20" s="128" t="s">
         <v>109</v>
@@ -16492,7 +16515,7 @@
     </row>
     <row r="51" spans="1:17">
       <c r="B51" s="126" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C51" s="123">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
@@ -16529,7 +16552,7 @@
     </row>
     <row r="54" spans="1:17" ht="13.15">
       <c r="B54" s="119" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C54" s="136"/>
       <c r="D54" s="136"/>
@@ -16750,7 +16773,7 @@
     </row>
     <row r="63" spans="1:17" ht="13.15">
       <c r="B63" s="119" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C63" s="338"/>
       <c r="D63" s="114"/>
@@ -16979,19 +17002,19 @@
     </row>
     <row r="73" spans="1:8" ht="13.15">
       <c r="B73" s="171" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C73" s="171" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D73" s="171" t="s">
+        <v>111</v>
+      </c>
+      <c r="E73" s="172" t="s">
         <v>112</v>
       </c>
-      <c r="E73" s="172" t="s">
-        <v>113</v>
-      </c>
       <c r="F73" s="172" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="74" spans="1:8">
@@ -17116,7 +17139,7 @@
     </row>
     <row r="80" spans="1:8">
       <c r="B80" s="155" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="C80" s="155" t="s">
         <v>105</v>
@@ -17242,18 +17265,18 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:H89"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="6.1328125" customWidth="1"/>
-    <col min="2" max="2" width="24.6640625" customWidth="1"/>
-    <col min="3" max="6" width="20.6640625" customWidth="1"/>
-    <col min="7" max="7" width="5.6640625" customWidth="1"/>
-    <col min="8" max="8" width="56.796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.73046875" customWidth="1"/>
+    <col min="3" max="6" width="20.73046875" customWidth="1"/>
+    <col min="7" max="7" width="5.73046875" customWidth="1"/>
+    <col min="8" max="8" width="56.86328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="13.9">
       <c r="B2" s="36" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
@@ -17265,31 +17288,31 @@
     </row>
     <row r="3" spans="2:8" ht="13.15">
       <c r="B3" s="109" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="C3" s="107">
         <f>scaling_factor</f>
         <v>1</v>
       </c>
       <c r="E3" s="109" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H3" s="120"/>
     </row>
     <row r="4" spans="2:8">
       <c r="B4" s="100" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="C4" s="114">
-        <f>Normalized_FCF!C91</f>
-        <v>116742175.2</v>
+        <f>Normalized_FCF!C91*(1-dividend_tax_rate)</f>
+        <v>105067957.68000001</v>
       </c>
       <c r="D4" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
       <c r="E4" s="100" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F4" s="134">
         <f>Thesis!E22</f>
@@ -17299,7 +17322,7 @@
     </row>
     <row r="5" spans="2:8">
       <c r="B5" s="205" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C5" s="206">
         <f>Equity_Cost</f>
@@ -17308,29 +17331,29 @@
       <c r="E5" s="148"/>
       <c r="H5" s="120"/>
     </row>
-    <row r="6" spans="2:8" ht="13.25" customHeight="1">
+    <row r="6" spans="2:8" ht="13.35" customHeight="1">
       <c r="B6" s="149" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="C6" s="319">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>1945702920.0000002</v>
+        <v>1751132628.0000002</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="364"/>
-      <c r="F6" s="364"/>
+      <c r="E6" s="366"/>
+      <c r="F6" s="366"/>
       <c r="H6" s="120"/>
     </row>
     <row r="7" spans="2:8" ht="13.15">
       <c r="B7" s="149" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="C7" s="111">
         <f>(C6*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>6.6666666666666679</v>
+        <v>6.0000000000000009</v>
       </c>
       <c r="D7" t="str">
         <f>Market_currency</f>
@@ -17343,7 +17366,7 @@
     </row>
     <row r="9" spans="2:8" ht="13.9">
       <c r="B9" s="36" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C9" s="37"/>
       <c r="D9" s="37"/>
@@ -17353,13 +17376,13 @@
     </row>
     <row r="10" spans="2:8" ht="13.15">
       <c r="B10" s="119" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H10" s="120"/>
     </row>
-    <row r="11" spans="2:8" ht="13.25" customHeight="1">
+    <row r="11" spans="2:8" ht="13.35" customHeight="1">
       <c r="B11" s="152" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C11" s="161">
         <f>Scenarios!C65</f>
@@ -17367,9 +17390,9 @@
       </c>
       <c r="H11" s="120"/>
     </row>
-    <row r="12" spans="2:8" ht="13.25" customHeight="1">
+    <row r="12" spans="2:8" ht="13.35" customHeight="1">
       <c r="B12" s="118" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C12" s="162">
         <f>Scenarios!C64</f>
@@ -17377,13 +17400,13 @@
       </c>
       <c r="H12" s="120"/>
     </row>
-    <row r="13" spans="2:8" ht="13.25" customHeight="1">
+    <row r="13" spans="2:8" ht="13.35" customHeight="1">
       <c r="B13" s="153" t="s">
         <v>106</v>
       </c>
       <c r="C13" s="140">
         <f>F47/Common_Shares*scaling_factor</f>
-        <v>7.0966486350296014</v>
+        <v>6.3869837715266424</v>
       </c>
       <c r="D13" t="str">
         <f>Market_currency</f>
@@ -17399,16 +17422,16 @@
         <v>107</v>
       </c>
       <c r="C15" s="128" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="D15" s="128" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E15" s="128" t="s">
         <v>109</v>
       </c>
       <c r="F15" s="129" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="H15" s="120"/>
     </row>
@@ -17418,7 +17441,7 @@
       </c>
       <c r="C16" s="123">
         <f>C4*(1+D16)</f>
-        <v>121704922.02676882</v>
+        <v>109534429.82409194</v>
       </c>
       <c r="D16" s="138">
         <f>IF($C$12&lt;B16,0,DDM!$C$11)</f>
@@ -17430,7 +17453,7 @@
       </c>
       <c r="F16" s="125">
         <f t="shared" ref="F16:F46" si="1">C16*E16</f>
-        <v>114815964.17619699</v>
+        <v>103334367.75857729</v>
       </c>
       <c r="H16" s="120"/>
     </row>
@@ -17440,7 +17463,7 @@
       </c>
       <c r="C17" s="123">
         <f t="shared" ref="C17:C45" si="2">IF(ROW()-ROW($C$16)&lt;$C$12, $C$16*(1+D17)^(ROW()-ROW($C$16)), 0)</f>
-        <v>126878636.79228307</v>
+        <v>114190773.11305477</v>
       </c>
       <c r="D17" s="138">
         <f>IF($C$12&lt;B17,0,DDM!$C$11)</f>
@@ -17452,7 +17475,7 @@
       </c>
       <c r="F17" s="125">
         <f t="shared" si="1"/>
-        <v>112921535.05899169</v>
+        <v>101629381.55309252</v>
       </c>
       <c r="H17" s="120"/>
     </row>
@@ -17462,7 +17485,7 @@
       </c>
       <c r="C18" s="123">
         <f t="shared" si="2"/>
-        <v>132272287.81040849</v>
+        <v>119045059.02936764</v>
       </c>
       <c r="D18" s="138">
         <f>IF($C$12&lt;B18,0,DDM!$C$11)</f>
@@ -17474,7 +17497,7 @@
       </c>
       <c r="F18" s="125">
         <f t="shared" si="1"/>
-        <v>111058363.45641743</v>
+        <v>99952527.110775679</v>
       </c>
       <c r="H18" s="120"/>
     </row>
@@ -17484,7 +17507,7 @@
       </c>
       <c r="C19" s="123">
         <f t="shared" si="2"/>
-        <v>137895224.64087245</v>
+        <v>124105702.1767852</v>
       </c>
       <c r="D19" s="138">
         <f>IF($C$12&lt;B19,0,DDM!$C$11)</f>
@@ -17496,7 +17519,7 @@
       </c>
       <c r="F19" s="125">
         <f t="shared" si="1"/>
-        <v>109225933.62881839</v>
+        <v>98303340.265936553</v>
       </c>
       <c r="H19" s="120"/>
     </row>
@@ -17506,7 +17529,7 @@
       </c>
       <c r="C20" s="123">
         <f t="shared" si="2"/>
-        <v>143757194.29614627</v>
+        <v>129381474.86653166</v>
       </c>
       <c r="D20" s="138">
         <f>IF($C$12&lt;B20,0,DDM!$C$11)</f>
@@ -17518,7 +17541,7 @@
       </c>
       <c r="F20" s="125">
         <f t="shared" si="1"/>
-        <v>107423738.34608901</v>
+        <v>96681364.511480108</v>
       </c>
       <c r="H20" s="120"/>
     </row>
@@ -18074,11 +18097,11 @@
     </row>
     <row r="46" spans="2:8">
       <c r="B46" s="126" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C46" s="123">
         <f>C$16*(1+F4)^$C$12/Equity_Cost</f>
-        <v>2028415367.1128137</v>
+        <v>1825573830.4015324</v>
       </c>
       <c r="D46" s="139">
         <f>Terminal_Growth</f>
@@ -18090,7 +18113,7 @@
       </c>
       <c r="F46" s="125">
         <f t="shared" si="1"/>
-        <v>1515749961.0421531</v>
+        <v>1364174964.937938</v>
       </c>
       <c r="H46" s="120"/>
     </row>
@@ -18101,7 +18124,7 @@
       </c>
       <c r="F47" s="137">
         <f>SUM(F16:F46)</f>
-        <v>2071195495.7086666</v>
+        <v>1864075946.1378002</v>
       </c>
       <c r="H47" s="120"/>
     </row>
@@ -18111,7 +18134,7 @@
     </row>
     <row r="49" spans="1:8" ht="13.15">
       <c r="B49" s="119" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C49" s="136"/>
       <c r="D49" s="136"/>
@@ -18122,7 +18145,7 @@
     <row r="50" spans="1:8" ht="13.15">
       <c r="A50" s="133">
         <f>F47</f>
-        <v>2071195495.7086666</v>
+        <v>1864075946.1378002</v>
       </c>
       <c r="B50" s="131">
         <f>C73</f>
@@ -18152,19 +18175,19 @@
       </c>
       <c r="B51" s="123">
         <f t="dataTable" ref="B51:F56" dt2D="1" dtr="1" r1="C11" r2="C12"/>
-        <v>1945702919.9999995</v>
+        <v>1751132627.9999995</v>
       </c>
       <c r="C51" s="123">
-        <v>2003883773.6356356</v>
+        <v>1803495396.2720721</v>
       </c>
       <c r="D51" s="123">
-        <v>2063590270.2103729</v>
+        <v>1857231243.1893353</v>
       </c>
       <c r="E51" s="123">
-        <v>2124889829.4757133</v>
+        <v>1912400846.5281417</v>
       </c>
       <c r="F51" s="123">
-        <v>2187851968.2101088</v>
+        <v>1969066771.3890979</v>
       </c>
       <c r="H51" s="120"/>
     </row>
@@ -18173,19 +18196,19 @@
         <v>10</v>
       </c>
       <c r="B52" s="123">
-        <v>1945702919.9999993</v>
+        <v>1751132627.9999995</v>
       </c>
       <c r="C52" s="123">
-        <v>2058791246.2930689</v>
+        <v>1852912121.6637621</v>
       </c>
       <c r="D52" s="123">
-        <v>2182808719.5917172</v>
+        <v>1964527847.6325455</v>
       </c>
       <c r="E52" s="123">
-        <v>2319080320.8338833</v>
+        <v>2087172288.750495</v>
       </c>
       <c r="F52" s="123">
-        <v>2469080412.3095703</v>
+        <v>2222172371.0786138</v>
       </c>
       <c r="H52" s="120"/>
     </row>
@@ -18194,19 +18217,19 @@
         <v>15</v>
       </c>
       <c r="B53" s="123">
-        <v>1945702919.9999986</v>
+        <v>1751132627.999999</v>
       </c>
       <c r="C53" s="123">
-        <v>2133243574.2016823</v>
+        <v>1919919216.7815142</v>
       </c>
       <c r="D53" s="123">
-        <v>2353068442.898922</v>
+        <v>2117761598.6090295</v>
       </c>
       <c r="E53" s="123">
-        <v>2611718905.9123459</v>
+        <v>2350547015.3211112</v>
       </c>
       <c r="F53" s="123">
-        <v>2917045995.2845707</v>
+        <v>2625341395.756114</v>
       </c>
       <c r="H53" s="120"/>
     </row>
@@ -18215,19 +18238,19 @@
         <v>20</v>
       </c>
       <c r="B54" s="123">
-        <v>1945702919.9999986</v>
+        <v>1751132627.999999</v>
       </c>
       <c r="C54" s="123">
-        <v>2216453174.074132</v>
+        <v>1994807856.6667194</v>
       </c>
       <c r="D54" s="123">
-        <v>2554094940.2883377</v>
+        <v>2298685446.2595038</v>
       </c>
       <c r="E54" s="123">
-        <v>2977923633.6263809</v>
+        <v>2680131270.2637429</v>
       </c>
       <c r="F54" s="123">
-        <v>3512905420.8653216</v>
+        <v>3161614878.7787895</v>
       </c>
       <c r="H54" s="120"/>
     </row>
@@ -18236,19 +18259,19 @@
         <v>25</v>
       </c>
       <c r="B55" s="123">
-        <v>1945702919.9999983</v>
+        <v>1751132627.999999</v>
       </c>
       <c r="C55" s="123">
-        <v>2301382102.4465003</v>
+        <v>2071243892.2018504</v>
       </c>
       <c r="D55" s="123">
-        <v>2771407847.0964856</v>
+        <v>2494267062.386837</v>
       </c>
       <c r="E55" s="123">
-        <v>3399101262.6710753</v>
+        <v>3059191136.4039683</v>
       </c>
       <c r="F55" s="123">
-        <v>4244860341.6974673</v>
+        <v>3820374307.5277209</v>
       </c>
       <c r="H55" s="120"/>
     </row>
@@ -18257,19 +18280,19 @@
         <v>30</v>
       </c>
       <c r="B56" s="123">
-        <v>1945702919.9999981</v>
+        <v>1751132627.9999988</v>
       </c>
       <c r="C56" s="123">
-        <v>2383615344.930985</v>
+        <v>2145253810.4378872</v>
       </c>
       <c r="D56" s="123">
-        <v>2994795653.7633381</v>
+        <v>2695316088.3870044</v>
       </c>
       <c r="E56" s="123">
-        <v>3861357841.521266</v>
+        <v>3475222057.3691401</v>
       </c>
       <c r="F56" s="123">
-        <v>5106600412.7640495</v>
+        <v>4595940371.4876442</v>
       </c>
       <c r="H56" s="120"/>
     </row>
@@ -18282,7 +18305,7 @@
     </row>
     <row r="58" spans="1:8" ht="13.15">
       <c r="B58" s="119" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C58" s="114"/>
       <c r="D58" s="114"/>
@@ -18319,23 +18342,23 @@
       </c>
       <c r="B60" s="124">
         <f>C7</f>
-        <v>6.6666666666666679</v>
+        <v>6.0000000000000009</v>
       </c>
       <c r="C60" s="124">
         <f>C7</f>
-        <v>6.6666666666666679</v>
+        <v>6.0000000000000009</v>
       </c>
       <c r="D60" s="124">
         <f>C7</f>
-        <v>6.6666666666666679</v>
+        <v>6.0000000000000009</v>
       </c>
       <c r="E60" s="141">
         <f>C7</f>
-        <v>6.6666666666666679</v>
+        <v>6.0000000000000009</v>
       </c>
       <c r="F60" s="124">
         <f>C7</f>
-        <v>6.6666666666666679</v>
+        <v>6.0000000000000009</v>
       </c>
       <c r="H60" s="120"/>
     </row>
@@ -18346,23 +18369,23 @@
       </c>
       <c r="B61" s="124">
         <f t="shared" ref="B61:F66" si="4">B51/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>6.6666666666666652</v>
+        <v>5.9999999999999982</v>
       </c>
       <c r="C61" s="124">
         <f t="shared" si="4"/>
-        <v>6.8660148577928348</v>
+        <v>6.1794133720135518</v>
       </c>
       <c r="D61" s="124">
         <f t="shared" si="4"/>
-        <v>7.07059044145812</v>
+        <v>6.3635313973123067</v>
       </c>
       <c r="E61" s="124">
         <f t="shared" si="4"/>
-        <v>7.2806244215868041</v>
+        <v>6.5525619794281225</v>
       </c>
       <c r="F61" s="124">
         <f t="shared" si="4"/>
-        <v>7.4963549872595099</v>
+        <v>6.7467194885335591</v>
       </c>
       <c r="H61" s="120"/>
     </row>
@@ -18373,23 +18396,23 @@
       </c>
       <c r="B62" s="124">
         <f t="shared" si="4"/>
-        <v>6.6666666666666643</v>
+        <v>5.9999999999999982</v>
       </c>
       <c r="C62" s="124">
         <f t="shared" si="4"/>
-        <v>7.0541472874425892</v>
+        <v>6.3487325586983312</v>
       </c>
       <c r="D62" s="124">
         <f t="shared" si="4"/>
-        <v>7.4790750330021849</v>
+        <v>6.7311675297019669</v>
       </c>
       <c r="E62" s="124">
         <f t="shared" si="4"/>
-        <v>7.9459897568668341</v>
+        <v>7.15139078118015</v>
       </c>
       <c r="F62" s="124">
         <f t="shared" si="4"/>
-        <v>8.4599431459268217</v>
+        <v>7.6139488313341408</v>
       </c>
       <c r="H62" s="120"/>
     </row>
@@ -18400,23 +18423,23 @@
       </c>
       <c r="B63" s="124">
         <f t="shared" si="4"/>
-        <v>6.6666666666666616</v>
+        <v>5.9999999999999964</v>
       </c>
       <c r="C63" s="124">
         <f t="shared" si="4"/>
-        <v>7.3092473068865083</v>
+        <v>6.5783225761978574</v>
       </c>
       <c r="D63" s="124">
         <f t="shared" si="4"/>
-        <v>8.0624450893353643</v>
+        <v>7.2562005804018277</v>
       </c>
       <c r="E63" s="124">
         <f t="shared" si="4"/>
-        <v>8.9486730958644873</v>
+        <v>8.0538057862780388</v>
       </c>
       <c r="F63" s="124">
         <f t="shared" si="4"/>
-        <v>9.9948317402417928</v>
+        <v>8.9953485662176149</v>
       </c>
       <c r="H63" s="120"/>
     </row>
@@ -18427,23 +18450,23 @@
       </c>
       <c r="B64" s="124">
         <f t="shared" si="4"/>
-        <v>6.6666666666666616</v>
+        <v>5.9999999999999964</v>
       </c>
       <c r="C64" s="124">
         <f t="shared" si="4"/>
-        <v>7.5943528387301527</v>
+        <v>6.8349175548571397</v>
       </c>
       <c r="D64" s="124">
         <f t="shared" si="4"/>
-        <v>8.7512330001140413</v>
+        <v>7.8761097001026377</v>
       </c>
       <c r="E64" s="124">
         <f t="shared" si="4"/>
-        <v>10.203420069994998</v>
+        <v>9.1830780629954987</v>
       </c>
       <c r="F64" s="124">
         <f t="shared" si="4"/>
-        <v>12.036456969718419</v>
+        <v>10.832811272746577</v>
       </c>
       <c r="H64" s="120"/>
     </row>
@@ -18454,23 +18477,23 @@
       </c>
       <c r="B65" s="124">
         <f t="shared" si="4"/>
-        <v>6.6666666666666607</v>
+        <v>5.9999999999999964</v>
       </c>
       <c r="C65" s="124">
         <f t="shared" si="4"/>
-        <v>7.8853493983774952</v>
+        <v>7.0968144585397459</v>
       </c>
       <c r="D65" s="124">
         <f t="shared" si="4"/>
-        <v>9.4958239123044397</v>
+        <v>8.5462415210739948</v>
       </c>
       <c r="E65" s="124">
         <f t="shared" si="4"/>
-        <v>11.646523655560857</v>
+        <v>10.481871290004774</v>
       </c>
       <c r="F65" s="124">
         <f t="shared" si="4"/>
-        <v>14.544393521622398</v>
+        <v>13.089954169460158</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="13.15">
@@ -18480,40 +18503,40 @@
       </c>
       <c r="B66" s="124">
         <f t="shared" si="4"/>
-        <v>6.6666666666666599</v>
+        <v>5.9999999999999956</v>
       </c>
       <c r="C66" s="124">
         <f t="shared" si="4"/>
-        <v>8.1671095843380694</v>
+        <v>7.3503986259042646</v>
       </c>
       <c r="D66" s="124">
         <f t="shared" si="4"/>
-        <v>10.261229580938418</v>
+        <v>9.235106622844576</v>
       </c>
       <c r="E66" s="124">
         <f t="shared" si="4"/>
-        <v>13.230378258435143</v>
+        <v>11.907340432591631</v>
       </c>
       <c r="F66" s="124">
         <f t="shared" si="4"/>
-        <v>17.497019921088636</v>
+        <v>15.747317928979772</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="13.15">
       <c r="B68" s="171" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C68" s="171" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D68" s="171" t="s">
+        <v>111</v>
+      </c>
+      <c r="E68" s="172" t="s">
         <v>112</v>
       </c>
-      <c r="E68" s="172" t="s">
-        <v>113</v>
-      </c>
       <c r="F68" s="172" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="69" spans="1:8">
@@ -18531,7 +18554,7 @@
       </c>
       <c r="E69" s="135">
         <f>INDEX(B$60:F$66, MATCH(D69, A$60:A$66, 0), MATCH(C69, B$59:F$59, 0))</f>
-        <v>8.4599431459268217</v>
+        <v>7.6139488313341408</v>
       </c>
       <c r="F69" s="142">
         <f>Scenarios!C58</f>
@@ -18553,7 +18576,7 @@
       </c>
       <c r="E70" s="135">
         <f>INDEX(B$60:F$66, MATCH(D70, A$60:A$66, 0), MATCH(C70, B$59:F$59, 0))</f>
-        <v>7.2806244215868041</v>
+        <v>6.5525619794281225</v>
       </c>
       <c r="F70" s="142">
         <f>Scenarios!C40*(1-F$69-F$73)</f>
@@ -18576,7 +18599,7 @@
       </c>
       <c r="E71" s="135">
         <f>INDEX(B$60:F$66, MATCH(D71, A$60:A$66, 0), MATCH(C71, B$59:F$59, 0))</f>
-        <v>7.07059044145812</v>
+        <v>6.3635313973123067</v>
       </c>
       <c r="F71" s="142">
         <f>Scenarios!C28*(1-F$69-F$73)</f>
@@ -18599,7 +18622,7 @@
       </c>
       <c r="E72" s="135">
         <f>INDEX(B$60:F$66, MATCH(D72, A$60:A$66, 0), MATCH(C72, B$59:F$59, 0))</f>
-        <v>6.8660148577928348</v>
+        <v>6.1794133720135518</v>
       </c>
       <c r="F72" s="142">
         <f>Scenarios!C34*(1-F$69-F$73)</f>
@@ -18622,7 +18645,7 @@
       </c>
       <c r="E73" s="135">
         <f>INDEX(B$60:F$66, MATCH(D73, A$60:A$66, 0), MATCH(C73, B$59:F$59, 0))</f>
-        <v>6.6666666666666643</v>
+        <v>5.9999999999999982</v>
       </c>
       <c r="F73" s="142">
         <f>Scenarios!C52</f>
@@ -18638,7 +18661,7 @@
     </row>
     <row r="75" spans="1:8">
       <c r="B75" s="155" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="C75" s="155" t="s">
         <v>105</v>
@@ -18690,32 +18713,32 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
   <dimension ref="B2:I110"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="2.6640625" customWidth="1"/>
-    <col min="2" max="2" width="22.6640625" customWidth="1"/>
+    <col min="1" max="1" width="2.73046875" customWidth="1"/>
+    <col min="2" max="2" width="22.73046875" customWidth="1"/>
     <col min="3" max="3" width="14" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.6640625" customWidth="1"/>
-    <col min="5" max="6" width="42.6640625" customWidth="1"/>
-    <col min="8" max="9" width="15.6640625" customWidth="1"/>
+    <col min="4" max="4" width="10.73046875" customWidth="1"/>
+    <col min="5" max="6" width="42.73046875" customWidth="1"/>
+    <col min="8" max="9" width="15.73046875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:9" ht="13.9">
       <c r="B2" s="36" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
       <c r="H2" s="248" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="I2" s="249"/>
     </row>
     <row r="3" spans="2:9" ht="13.15">
       <c r="B3" s="159" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H3" s="247">
         <v>0</v>
@@ -18727,14 +18750,14 @@
     </row>
     <row r="4" spans="2:9">
       <c r="B4" s="152" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C4" s="120">
         <v>3</v>
       </c>
       <c r="D4" s="120"/>
       <c r="E4" s="155" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F4" s="155"/>
       <c r="H4" s="247">
@@ -18742,7 +18765,7 @@
       </c>
       <c r="I4" s="124">
         <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
-        <v>0.4</v>
+        <v>0.36000000000000004</v>
       </c>
     </row>
     <row r="5" spans="2:9">
@@ -18751,7 +18774,7 @@
       </c>
       <c r="I5" s="124">
         <f t="shared" si="0"/>
-        <v>0.4</v>
+        <v>0.36000000000000004</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="13.15">
@@ -18763,7 +18786,7 @@
         <v>1</v>
       </c>
       <c r="E6" s="100" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F6" s="100"/>
       <c r="H6" s="247">
@@ -18771,12 +18794,12 @@
       </c>
       <c r="I6" s="124">
         <f t="shared" si="0"/>
-        <v>10.651430255232372</v>
+        <v>10.611430255232371</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
       <c r="B7" s="100" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C7" s="338">
         <f>Normalized_FCF!G8</f>
@@ -18786,11 +18809,11 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="366" t="str">
+      <c r="E7" s="368" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!C11&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 5-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 10-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 濮阳惠成(300481.SZ). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="366"/>
+      <c r="F7" s="368"/>
       <c r="H7" s="247">
         <v>4</v>
       </c>
@@ -18811,8 +18834,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="366"/>
-      <c r="F8" s="366"/>
+      <c r="E8" s="368"/>
+      <c r="F8" s="368"/>
       <c r="H8" s="247">
         <v>5</v>
       </c>
@@ -18833,8 +18856,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="366"/>
-      <c r="F9" s="366"/>
+      <c r="E9" s="368"/>
+      <c r="F9" s="368"/>
       <c r="H9" s="247">
         <v>6</v>
       </c>
@@ -18844,8 +18867,8 @@
       </c>
     </row>
     <row r="10" spans="2:9">
-      <c r="E10" s="366"/>
-      <c r="F10" s="366"/>
+      <c r="E10" s="368"/>
+      <c r="F10" s="368"/>
       <c r="H10" s="247">
         <v>7</v>
       </c>
@@ -18856,10 +18879,10 @@
     </row>
     <row r="11" spans="2:9" ht="13.15">
       <c r="B11" s="159" t="s">
-        <v>447</v>
-      </c>
-      <c r="E11" s="366"/>
-      <c r="F11" s="366"/>
+        <v>444</v>
+      </c>
+      <c r="E11" s="368"/>
+      <c r="F11" s="368"/>
       <c r="H11" s="247">
         <v>8</v>
       </c>
@@ -18870,15 +18893,15 @@
     </row>
     <row r="12" spans="2:9">
       <c r="B12" s="118" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C12" s="158">
         <f ca="1">(Normalized_FCF!G4/OFFSET(Normalized_FCF!G4, 0, $C$4))^(1/$C$4) - 1</f>
         <v>4.2279727191083527E-3</v>
       </c>
       <c r="D12" s="158"/>
-      <c r="E12" s="366"/>
-      <c r="F12" s="366"/>
+      <c r="E12" s="368"/>
+      <c r="F12" s="368"/>
       <c r="H12" s="247">
         <v>9</v>
       </c>
@@ -18889,14 +18912,14 @@
     </row>
     <row r="13" spans="2:9">
       <c r="B13" s="148" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C13" s="158">
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-0.15075343519689044</v>
       </c>
-      <c r="E13" s="366"/>
-      <c r="F13" s="366"/>
+      <c r="E13" s="368"/>
+      <c r="F13" s="368"/>
       <c r="H13" s="247">
         <v>10</v>
       </c>
@@ -18913,12 +18936,12 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-0.15795268346639479</v>
       </c>
-      <c r="E14" s="366"/>
-      <c r="F14" s="366"/>
+      <c r="E14" s="368"/>
+      <c r="F14" s="368"/>
     </row>
     <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C16" s="37"/>
       <c r="D16" s="37"/>
@@ -18927,38 +18950,38 @@
     </row>
     <row r="17" spans="2:6" ht="13.15">
       <c r="B17" s="109" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E17" s="159" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
     </row>
     <row r="18" spans="2:6">
       <c r="B18" s="152" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C18" s="150">
         <v>5</v>
       </c>
-      <c r="E18" s="366" t="s">
-        <v>330</v>
-      </c>
-      <c r="F18" s="367"/>
+      <c r="E18" s="368" t="s">
+        <v>327</v>
+      </c>
+      <c r="F18" s="369"/>
     </row>
     <row r="19" spans="2:6">
-      <c r="E19" s="367"/>
-      <c r="F19" s="367"/>
+      <c r="E19" s="369"/>
+      <c r="F19" s="369"/>
     </row>
     <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="159" t="s">
-        <v>303</v>
-      </c>
-      <c r="E20" s="367"/>
-      <c r="F20" s="367"/>
+        <v>302</v>
+      </c>
+      <c r="E20" s="369"/>
+      <c r="F20" s="369"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
@@ -18968,12 +18991,12 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E21" s="367"/>
-      <c r="F21" s="367"/>
+      <c r="E21" s="369"/>
+      <c r="F21" s="369"/>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C22" s="160">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
@@ -18983,44 +19006,44 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E22" s="367"/>
-      <c r="F22" s="367"/>
+      <c r="E22" s="369"/>
+      <c r="F22" s="369"/>
     </row>
     <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="159" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E24" s="159" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F24" s="159"/>
     </row>
     <row r="25" spans="2:6">
       <c r="B25" s="152" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C25" s="166">
         <f>C18</f>
         <v>5</v>
       </c>
       <c r="D25" s="163"/>
-      <c r="E25" s="365"/>
-      <c r="F25" s="365"/>
+      <c r="E25" s="367"/>
+      <c r="F25" s="367"/>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" s="118" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C26" s="164">
         <v>0.04</v>
       </c>
       <c r="D26" s="164"/>
-      <c r="E26" s="365"/>
-      <c r="F26" s="365"/>
+      <c r="E26" s="367"/>
+      <c r="F26" s="367"/>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C27" s="160">
         <f>IF(valuation_method="DCF",DCF!E76,DDM!E71)</f>
@@ -19030,55 +19053,55 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E27" s="365"/>
-      <c r="F27" s="365"/>
+      <c r="E27" s="367"/>
+      <c r="F27" s="367"/>
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C28" s="165">
         <v>0.6</v>
       </c>
       <c r="D28" s="165"/>
-      <c r="E28" s="365"/>
-      <c r="F28" s="365"/>
+      <c r="E28" s="367"/>
+      <c r="F28" s="367"/>
     </row>
     <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="159" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E30" s="159" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F30" s="159"/>
     </row>
     <row r="31" spans="2:6">
       <c r="B31" s="152" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C31" s="166">
         <f>C18</f>
         <v>5</v>
       </c>
       <c r="D31" s="163"/>
-      <c r="E31" s="365"/>
-      <c r="F31" s="365"/>
+      <c r="E31" s="367"/>
+      <c r="F31" s="367"/>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="118" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C32" s="164">
         <v>0.02</v>
       </c>
       <c r="D32" s="164"/>
-      <c r="E32" s="365"/>
-      <c r="F32" s="365"/>
+      <c r="E32" s="367"/>
+      <c r="F32" s="367"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C33" s="160">
         <f>IF(valuation_method="DCF",DCF!E77,DDM!E72)</f>
@@ -19088,55 +19111,55 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E33" s="365"/>
-      <c r="F33" s="365"/>
+      <c r="E33" s="367"/>
+      <c r="F33" s="367"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C34" s="165">
         <v>0.2</v>
       </c>
       <c r="D34" s="165"/>
-      <c r="E34" s="365"/>
-      <c r="F34" s="365"/>
+      <c r="E34" s="367"/>
+      <c r="F34" s="367"/>
     </row>
     <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="159" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E36" s="159" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F36" s="159"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="152" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C37" s="166">
         <f>C18</f>
         <v>5</v>
       </c>
       <c r="D37" s="163"/>
-      <c r="E37" s="365"/>
-      <c r="F37" s="365"/>
+      <c r="E37" s="367"/>
+      <c r="F37" s="367"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="118" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C38" s="164">
         <v>0.06</v>
       </c>
       <c r="D38" s="164"/>
-      <c r="E38" s="365"/>
-      <c r="F38" s="365"/>
+      <c r="E38" s="367"/>
+      <c r="F38" s="367"/>
     </row>
     <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C39" s="160">
         <f>IF(valuation_method="DCF",DCF!E75,DDM!E70)</f>
@@ -19146,24 +19169,24 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E39" s="365"/>
-      <c r="F39" s="365"/>
+      <c r="E39" s="367"/>
+      <c r="F39" s="367"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C40" s="167">
         <f>1-C28-C34</f>
         <v>0.2</v>
       </c>
       <c r="D40" s="165"/>
-      <c r="E40" s="365"/>
-      <c r="F40" s="365"/>
+      <c r="E40" s="367"/>
+      <c r="F40" s="367"/>
     </row>
     <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C42" s="154">
         <f>C27*C28+C33*C34+C39*C40</f>
@@ -19176,7 +19199,7 @@
     </row>
     <row r="44" spans="2:6" ht="13.9">
       <c r="B44" s="36" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C44" s="37"/>
       <c r="D44" s="37"/>
@@ -19185,12 +19208,12 @@
     </row>
     <row r="45" spans="2:6" ht="13.15">
       <c r="B45" s="109" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="46" spans="2:6">
       <c r="B46" s="152" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C46" s="150">
         <v>10</v>
@@ -19205,39 +19228,39 @@
     </row>
     <row r="48" spans="2:6" ht="13.15">
       <c r="B48" s="159" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E48" s="159" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F48" s="159"/>
     </row>
     <row r="49" spans="2:6" ht="12.75" customHeight="1">
       <c r="B49" s="152" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C49" s="166">
         <f>C46</f>
         <v>10</v>
       </c>
       <c r="D49" s="163"/>
-      <c r="E49" s="365"/>
-      <c r="F49" s="365"/>
+      <c r="E49" s="367"/>
+      <c r="F49" s="367"/>
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="118" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C50" s="164">
         <v>0</v>
       </c>
       <c r="D50" s="164"/>
-      <c r="E50" s="365"/>
-      <c r="F50" s="365"/>
+      <c r="E50" s="367"/>
+      <c r="F50" s="367"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C51" s="160">
         <f>IF(valuation_method="DCF",DCF!E78,DDM!E73)</f>
@@ -19247,55 +19270,55 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E51" s="365"/>
-      <c r="F51" s="365"/>
+      <c r="E51" s="367"/>
+      <c r="F51" s="367"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C52" s="165">
         <v>0.05</v>
       </c>
       <c r="D52" s="165"/>
-      <c r="E52" s="365"/>
-      <c r="F52" s="365"/>
+      <c r="E52" s="367"/>
+      <c r="F52" s="367"/>
     </row>
     <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="159" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="E54" s="159" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F54" s="159"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="152" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C55" s="166">
         <f>C46</f>
         <v>10</v>
       </c>
       <c r="D55" s="163"/>
-      <c r="E55" s="365"/>
-      <c r="F55" s="365"/>
+      <c r="E55" s="367"/>
+      <c r="F55" s="367"/>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="118" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C56" s="164">
         <v>0.08</v>
       </c>
       <c r="D56" s="164"/>
-      <c r="E56" s="365"/>
-      <c r="F56" s="365"/>
+      <c r="E56" s="367"/>
+      <c r="F56" s="367"/>
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C57" s="160">
         <f>IF(valuation_method="DCF",DCF!E74,DDM!E69)</f>
@@ -19305,23 +19328,23 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E57" s="365"/>
-      <c r="F57" s="365"/>
+      <c r="E57" s="367"/>
+      <c r="F57" s="367"/>
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C58" s="165">
         <v>0.05</v>
       </c>
       <c r="D58" s="165"/>
-      <c r="E58" s="365"/>
-      <c r="F58" s="365"/>
+      <c r="E58" s="367"/>
+      <c r="F58" s="367"/>
     </row>
     <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C60" s="154">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
@@ -19332,7 +19355,7 @@
         <v>CNY</v>
       </c>
       <c r="E60" s="100" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F60" s="277">
         <f>Thesis!F28</f>
@@ -19341,7 +19364,7 @@
     </row>
     <row r="62" spans="2:6" ht="13.9">
       <c r="B62" s="36" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="C62" s="37"/>
       <c r="D62" s="37"/>
@@ -19350,15 +19373,15 @@
     </row>
     <row r="63" spans="2:6" ht="13.15">
       <c r="B63" s="109" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E63" s="252" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
     </row>
     <row r="64" spans="2:6">
       <c r="B64" s="152" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C64" s="166">
         <f>C18</f>
@@ -19366,19 +19389,19 @@
       </c>
       <c r="D64" s="150"/>
       <c r="E64" s="251" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
     </row>
     <row r="65" spans="2:6">
       <c r="B65" s="118" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C65" s="151">
         <v>4.25103165866728E-2</v>
       </c>
       <c r="D65" s="151"/>
       <c r="E65" s="251" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
     </row>
     <row r="66" spans="2:6">
@@ -19394,20 +19417,20 @@
         <v>CNY</v>
       </c>
       <c r="E66" s="251" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
     </row>
     <row r="68" spans="2:6" ht="13.15">
       <c r="B68" s="109" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="E68" s="252" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
     </row>
     <row r="69" spans="2:6">
       <c r="B69" s="100" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C69" s="244" t="str">
         <f>IF(C60&lt;C22,"Y","N")</f>
@@ -19417,19 +19440,19 @@
     </row>
     <row r="70" spans="2:6">
       <c r="B70" s="100" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C70" s="244" t="str">
         <f>IF(C69="Y","N",IF(C65&gt;8%,"N","Y"))</f>
         <v>Y</v>
       </c>
       <c r="E70" s="251" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="71" spans="2:6">
       <c r="B71" s="100" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C71" s="244" t="str">
         <f>IF(C65&gt;8%,"Y","N")</f>
@@ -19439,14 +19462,14 @@
     </row>
     <row r="72" spans="2:6">
       <c r="B72" s="100" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C72" s="243" t="str">
         <f>IF(F72&gt;50%,"Y","N")</f>
         <v>N</v>
       </c>
       <c r="E72" s="134" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="F72" s="291">
         <f>BS!D89/C60</f>
@@ -19455,7 +19478,7 @@
     </row>
     <row r="74" spans="2:6" ht="13.9">
       <c r="B74" s="36" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C74" s="37"/>
       <c r="D74" s="37"/>
@@ -19464,12 +19487,12 @@
     </row>
     <row r="75" spans="2:6" ht="13.15">
       <c r="B75" s="109" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="76" spans="2:6">
       <c r="B76" s="246" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C76" s="245">
         <f>F60</f>
@@ -19479,11 +19502,11 @@
     </row>
     <row r="77" spans="2:6">
       <c r="B77" s="100" t="s">
-        <v>111</v>
+        <v>455</v>
       </c>
       <c r="C77" s="173">
-        <f>Normalized_FCF!C90</f>
-        <v>0.4</v>
+        <f>Normalized_FCF!C90*(1-dividend_tax_rate)</f>
+        <v>0.36000000000000004</v>
       </c>
       <c r="D77" t="str">
         <f>Market_currency</f>
@@ -19492,25 +19515,25 @@
     </row>
     <row r="79" spans="2:6" ht="13.15">
       <c r="B79" s="109" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="80" spans="2:6">
       <c r="B80" s="148" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C80" s="167">
         <f>Thesis!F29</f>
-        <v>0.33699999999999997</v>
+        <v>0.33700000000000002</v>
       </c>
     </row>
     <row r="81" spans="2:8">
       <c r="B81" s="100" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C81" s="116">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>0.69031028314322296</v>
+        <v>0.62127925482890056</v>
       </c>
       <c r="D81" s="116"/>
       <c r="E81" s="100"/>
@@ -19518,7 +19541,7 @@
     </row>
     <row r="82" spans="2:8">
       <c r="B82" s="100" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C82" s="116">
         <f>C60/(1+C80)^C76</f>
@@ -19532,18 +19555,18 @@
       </c>
       <c r="C83" s="111">
         <f>C81+C82</f>
-        <v>4.9796479824958464</v>
+        <v>4.9106169541815241</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
       <c r="E83" s="146" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F83" s="291">
         <f>(1-C83/C60)</f>
-        <v>0.51424846499304677</v>
+        <v>0.52098225984855873</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -19551,12 +19574,12 @@
     </row>
     <row r="85" spans="2:8" ht="13.15">
       <c r="B85" s="109" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="86" spans="2:8">
       <c r="B86" s="148" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
@@ -19569,11 +19592,11 @@
     </row>
     <row r="87" spans="2:8" ht="13.15">
       <c r="B87" s="100" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>-6.8301555261349622E-2</v>
+        <v>-7.1459666738491467E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -19581,12 +19604,12 @@
     </row>
     <row r="89" spans="2:8" ht="13.15">
       <c r="B89" s="109" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="90" spans="2:8">
       <c r="B90" s="148" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="C90" s="167">
         <f>Thesis!F30</f>
@@ -19595,11 +19618,11 @@
     </row>
     <row r="91" spans="2:8">
       <c r="B91" s="100" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C91" s="116">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>0.86005014536183588</v>
+        <v>0.77404513082565229</v>
       </c>
       <c r="D91" s="116"/>
       <c r="E91" s="100"/>
@@ -19607,7 +19630,7 @@
     </row>
     <row r="92" spans="2:8">
       <c r="B92" s="100" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C92" s="116">
         <f>C60/(1+C90)^C76</f>
@@ -19621,30 +19644,30 @@
       </c>
       <c r="C93" s="111">
         <f>C91+C92</f>
-        <v>6.9896525426428742</v>
+        <v>6.9036475281066911</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
       <c r="E93" s="146" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F93" s="291">
         <f>(1-C93/C60)</f>
-        <v>0.31817781825366975</v>
+        <v>0.32656738072396863</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
       <c r="B95" s="109" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="G95" s="2"/>
       <c r="H95" s="281"/>
     </row>
     <row r="96" spans="2:8">
       <c r="B96" s="148" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="C96" s="134">
         <f>Thesis!F31</f>
@@ -19655,11 +19678,11 @@
     </row>
     <row r="97" spans="2:8">
       <c r="B97" s="100" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C97" s="116">
         <f>PV(C96, C76, -C77, 0)</f>
-        <v>1.069204779784656</v>
+        <v>0.9622843018061904</v>
       </c>
       <c r="D97" s="116"/>
       <c r="G97" s="2"/>
@@ -19667,7 +19690,7 @@
     </row>
     <row r="98" spans="2:8">
       <c r="B98" s="100" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C98" s="116">
         <f>C60/(1+C96)^C76</f>
@@ -19679,21 +19702,21 @@
     </row>
     <row r="99" spans="2:8" ht="13.15">
       <c r="B99" s="110" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="C99" s="111">
         <f>C97+C98</f>
-        <v>9.6765033007385046</v>
+        <v>9.5695828227600401</v>
       </c>
       <c r="D99" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="E99" s="146" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F99" s="291">
         <f>(1-C99/C60)</f>
-        <v>5.6082608980383197E-2</v>
+        <v>6.6512419779114595E-2</v>
       </c>
     </row>
     <row r="100" spans="2:8">
@@ -19701,12 +19724,12 @@
     </row>
     <row r="101" spans="2:8" ht="13.15">
       <c r="B101" s="109" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
     </row>
     <row r="102" spans="2:8">
       <c r="B102" s="148" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="C102" s="134">
         <f>Thesis!F32</f>
@@ -19715,17 +19738,17 @@
     </row>
     <row r="103" spans="2:8">
       <c r="B103" s="100" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C103" s="116">
         <f>PV(C102, C76, -C77, 0)</f>
-        <v>1.0179560233797402</v>
+        <v>0.91616042104176609</v>
       </c>
       <c r="D103" s="116"/>
     </row>
     <row r="104" spans="2:8">
       <c r="B104" s="100" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C104" s="116">
         <f>C60/(1+C102)^C76</f>
@@ -19735,21 +19758,21 @@
     </row>
     <row r="105" spans="2:8" ht="13.15">
       <c r="B105" s="110" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="C105" s="111">
         <f>C103+C104</f>
-        <v>8.9996639027078977</v>
+        <v>8.8978683003699235</v>
       </c>
       <c r="D105" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="E105" s="146" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F105" s="291">
         <f>(1-C105/C66)</f>
-        <v>0.11980238369313911</v>
+        <v>0.12975833843734319</v>
       </c>
     </row>
     <row r="106" spans="2:8">
@@ -19757,32 +19780,32 @@
     </row>
     <row r="107" spans="2:8" ht="14.65">
       <c r="E107" s="285" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="F107" s="282"/>
     </row>
     <row r="108" spans="2:8" ht="13.9">
       <c r="E108" s="278" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="F108" s="283" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
     </row>
     <row r="109" spans="2:8" ht="13.9">
       <c r="E109" s="279" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="F109" s="283" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
     </row>
     <row r="110" spans="2:8" ht="13.9">
       <c r="E110" s="280" t="s">
+        <v>322</v>
+      </c>
+      <c r="F110" s="284" t="s">
         <v>325</v>
-      </c>
-      <c r="F110" s="284" t="s">
-        <v>328</v>
       </c>
     </row>
   </sheetData>

--- a/financial_models/opportunities/300481.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/300481.SZ_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CA40430-D100-4AEF-BFE2-4B79854C63C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F961917-7890-4DD5-985A-991A3B613F22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3893,29 +3893,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4333,7 +4333,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>14.06</v>
+        <v>14.15</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>4103.4874582800003</v>
+        <v>4129.7544477000001</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4391,13 +4391,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="360" t="s">
+      <c r="B18" s="358" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="360"/>
-      <c r="D18" s="360"/>
-      <c r="E18" s="360"/>
-      <c r="F18" s="360"/>
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4480,7 +4480,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>-7.1459666738491467E-2</v>
+        <v>-7.3489748596123561E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4522,7 +4522,7 @@
         <v>421</v>
       </c>
       <c r="F29" s="302">
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="30" spans="2:6">
@@ -4597,22 +4597,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="360" t="s">
+      <c r="B36" s="358" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="360"/>
-      <c r="D36" s="360"/>
-      <c r="E36" s="360"/>
-      <c r="F36" s="360"/>
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="363" t="s">
+      <c r="B37" s="360" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="363"/>
-      <c r="D37" s="363"/>
-      <c r="E37" s="363"/>
-      <c r="F37" s="363"/>
+      <c r="C37" s="360"/>
+      <c r="D37" s="360"/>
+      <c r="E37" s="360"/>
+      <c r="F37" s="360"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4624,13 +4624,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="361" t="s">
+      <c r="B40" s="359" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="361"/>
-      <c r="D40" s="361"/>
-      <c r="E40" s="361"/>
-      <c r="F40" s="361"/>
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4650,13 +4650,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="361" t="s">
+      <c r="B43" s="359" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="361"/>
-      <c r="D43" s="361"/>
-      <c r="E43" s="361"/>
-      <c r="F43" s="361"/>
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4685,13 +4685,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="361" t="s">
+      <c r="B47" s="359" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="361"/>
-      <c r="D47" s="361"/>
-      <c r="E47" s="361"/>
-      <c r="F47" s="361"/>
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4707,13 +4707,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="361" t="s">
+      <c r="B50" s="359" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="361"/>
-      <c r="D50" s="361"/>
-      <c r="E50" s="361"/>
-      <c r="F50" s="361"/>
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4777,13 +4777,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="361" t="s">
+      <c r="B58" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="361"/>
-      <c r="D58" s="361"/>
-      <c r="E58" s="361"/>
-      <c r="F58" s="361"/>
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4799,7 +4799,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="361" t="s">
+      <c r="B61" s="359" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4821,22 +4821,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="360" t="s">
+      <c r="B64" s="358" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="360"/>
-      <c r="D64" s="360"/>
-      <c r="E64" s="360"/>
-      <c r="F64" s="360"/>
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="360" t="s">
+      <c r="B65" s="358" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="360"/>
-      <c r="D65" s="360"/>
-      <c r="E65" s="360"/>
-      <c r="F65" s="360"/>
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4870,7 +4870,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>3.1553354902666565E-2</v>
+        <v>3.1352662185971159E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>2.5604551920341397E-2</v>
+        <v>2.5441696113074206E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>445</v>
@@ -4971,22 +4971,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="360" t="s">
+      <c r="B80" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="360"/>
-      <c r="D80" s="360"/>
-      <c r="E80" s="360"/>
-      <c r="F80" s="360"/>
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="363" t="s">
+      <c r="B81" s="360" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="363"/>
-      <c r="D81" s="363"/>
-      <c r="E81" s="363"/>
-      <c r="F81" s="363"/>
+      <c r="C81" s="360"/>
+      <c r="D81" s="360"/>
+      <c r="E81" s="360"/>
+      <c r="F81" s="360"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5030,22 +5030,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="360" t="s">
+      <c r="B89" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="360"/>
-      <c r="D89" s="360"/>
-      <c r="E89" s="360"/>
-      <c r="F89" s="360"/>
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="360" t="s">
+      <c r="B90" s="358" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="360"/>
-      <c r="D90" s="360"/>
-      <c r="E90" s="360"/>
-      <c r="F90" s="360"/>
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5082,13 +5082,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="360" t="s">
+      <c r="B97" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="360"/>
-      <c r="D97" s="360"/>
-      <c r="E97" s="360"/>
-      <c r="F97" s="360"/>
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5101,13 +5101,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="360" t="s">
+      <c r="B101" s="358" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="360"/>
-      <c r="D101" s="360"/>
-      <c r="E101" s="360"/>
-      <c r="F101" s="360"/>
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5229,13 +5229,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="360" t="s">
+      <c r="B116" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="360"/>
-      <c r="D116" s="360"/>
-      <c r="E116" s="360"/>
-      <c r="F116" s="360"/>
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5274,13 +5274,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="361" t="s">
+      <c r="B123" s="359" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="361"/>
-      <c r="D123" s="361"/>
-      <c r="E123" s="361"/>
-      <c r="F123" s="361"/>
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5423,13 +5423,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="364" t="s">
+      <c r="B134" s="363" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="364"/>
-      <c r="D134" s="364"/>
-      <c r="E134" s="364"/>
-      <c r="F134" s="364"/>
+      <c r="C134" s="363"/>
+      <c r="D134" s="363"/>
+      <c r="E134" s="363"/>
+      <c r="F134" s="363"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5442,22 +5442,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="365" t="s">
+      <c r="B138" s="361" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="365"/>
-      <c r="D138" s="365"/>
-      <c r="E138" s="365"/>
-      <c r="F138" s="365"/>
+      <c r="C138" s="361"/>
+      <c r="D138" s="361"/>
+      <c r="E138" s="361"/>
+      <c r="F138" s="361"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="360" t="s">
+      <c r="B139" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="360"/>
-      <c r="D139" s="360"/>
-      <c r="E139" s="360"/>
-      <c r="F139" s="360"/>
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5479,7 +5479,7 @@
       </c>
       <c r="C142" s="224">
         <f>F29</f>
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -5514,7 +5514,7 @@
       </c>
       <c r="C146" s="297">
         <f>F29</f>
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="147" spans="2:4">
@@ -5524,7 +5524,7 @@
       </c>
       <c r="C147" s="216">
         <f>Scenarios!C81</f>
-        <v>0.62127925482890056</v>
+        <v>0.62127925482890078</v>
       </c>
     </row>
     <row r="148" spans="2:4">
@@ -5790,13 +5790,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="359" t="s">
+      <c r="B179" s="365" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="360"/>
-      <c r="D179" s="360"/>
-      <c r="E179" s="360"/>
-      <c r="F179" s="360"/>
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5833,13 +5833,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="361" t="s">
+      <c r="B188" s="359" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="361"/>
-      <c r="D188" s="361"/>
-      <c r="E188" s="361"/>
-      <c r="F188" s="361"/>
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5847,22 +5847,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="358" t="s">
+      <c r="B191" s="364" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="358"/>
-      <c r="D191" s="358"/>
-      <c r="E191" s="358"/>
-      <c r="F191" s="358"/>
+      <c r="C191" s="364"/>
+      <c r="D191" s="364"/>
+      <c r="E191" s="364"/>
+      <c r="F191" s="364"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="358" t="s">
+      <c r="B192" s="364" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="358"/>
-      <c r="D192" s="358"/>
-      <c r="E192" s="358"/>
-      <c r="F192" s="358"/>
+      <c r="C192" s="364"/>
+      <c r="D192" s="364"/>
+      <c r="E192" s="364"/>
+      <c r="F192" s="364"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5886,6 +5886,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5902,17 +5913,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13503,32 +13503,32 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>2.5604551920341397E-2</v>
+        <v>2.5441696113074206E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>2.5604551920341397E-2</v>
+        <v>2.5441696113074206E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>2.5604551920341397E-2</v>
+        <v>2.5441696113074206E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>2.5604551920341397E-2</v>
+        <v>2.5441696113074206E-2</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
-        <v>2.5604551920341397E-2</v>
+        <v>2.5441696113074206E-2</v>
       </c>
       <c r="K94" s="23">
         <f t="shared" si="39"/>
-        <v>1.2802275960170698E-2</v>
+        <v>1.2720848056537103E-2</v>
       </c>
       <c r="L94" s="23">
         <f t="shared" si="39"/>
-        <v>1.2802275960170698E-2</v>
+        <v>1.2720848056537103E-2</v>
       </c>
       <c r="M94" s="23">
         <f t="shared" si="39"/>
@@ -14702,50 +14702,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>3.1553354902666565E-2</v>
+        <v>3.1352662185971159E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>3.5954917460805536E-2</v>
+        <v>3.5726228939853416E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>4.7281505437302175E-2</v>
+        <v>4.6980775014026054E-2</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>9.2996100642798882E-2</v>
+        <v>9.2404606009735143E-2</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>6.0221117127806485E-2</v>
+        <v>5.983808528741761E-2</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>4.5033190134368219E-2</v>
+        <v>4.4746759949767997E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>3.7412529214193455E-2</v>
+        <v>3.7174569664421203E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>2.6381898407222749E-2</v>
+        <v>2.6214098346682112E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>2.3982582620406021E-2</v>
+        <v>2.3830043225647253E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>1.586714438924872E-2</v>
+        <v>1.5766222622815337E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>1.5514630822506561E-2</v>
+        <v>1.5415951191833374E-2</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14759,43 +14759,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.6674977308272546E-2</v>
+        <v>4.6378104661082123E-2</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.7287634333000916E-2</v>
+        <v>5.6923260687066629E-2</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10288854158627507</v>
+        <v>0.10223412683413621</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.1506115850489401E-2</v>
+        <v>6.1114910873348478E-2</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.353644620980094E-2</v>
+        <v>4.32595359512227E-2</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.5267677913327994E-2</v>
+        <v>3.5043360527306826E-2</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.5769870402948463E-2</v>
+        <v>2.5605963100032183E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.7937455578541581E-2</v>
+        <v>1.7823365755073824E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.5739319214849418E-2</v>
+        <v>1.5639210470726698E-2</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.4009937786942107E-2</v>
+        <v>1.3920828642007494E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18745,7 +18745,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-14.06</v>
+        <v>-14.15</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18985,7 +18985,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>14.06</v>
+        <v>14.15</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19524,7 +19524,7 @@
       </c>
       <c r="C80" s="167">
         <f>Thesis!F29</f>
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="81" spans="2:8">
@@ -19533,7 +19533,7 @@
       </c>
       <c r="C81" s="116">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>0.62127925482890056</v>
+        <v>0.62127925482890078</v>
       </c>
       <c r="D81" s="116"/>
       <c r="E81" s="100"/>
@@ -19583,7 +19583,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>14.06</v>
+        <v>14.15</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19596,7 +19596,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>-7.1459666738491467E-2</v>
+        <v>-7.3489748596123561E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/300481.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/300481.SZ_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F961917-7890-4DD5-985A-991A3B613F22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DDD7C0B-3306-429C-9EEC-6EE8DA5FEF28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1470" yWindow="1470" windowWidth="12690" windowHeight="7643" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3893,29 +3893,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4333,7 +4333,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>14.15</v>
+        <v>13.82</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>4129.7544477000001</v>
+        <v>4033.4421531599996</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4391,13 +4391,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="358" t="s">
+      <c r="B18" s="360" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+      <c r="C18" s="360"/>
+      <c r="D18" s="360"/>
+      <c r="E18" s="360"/>
+      <c r="F18" s="360"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4480,7 +4480,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>-7.3489748596123561E-2</v>
+        <v>-6.5958680292173444E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4597,22 +4597,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="358" t="s">
+      <c r="B36" s="360" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
+      <c r="C36" s="360"/>
+      <c r="D36" s="360"/>
+      <c r="E36" s="360"/>
+      <c r="F36" s="360"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="360" t="s">
+      <c r="B37" s="363" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="360"/>
-      <c r="D37" s="360"/>
-      <c r="E37" s="360"/>
-      <c r="F37" s="360"/>
+      <c r="C37" s="363"/>
+      <c r="D37" s="363"/>
+      <c r="E37" s="363"/>
+      <c r="F37" s="363"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4624,13 +4624,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="359" t="s">
+      <c r="B40" s="361" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+      <c r="C40" s="361"/>
+      <c r="D40" s="361"/>
+      <c r="E40" s="361"/>
+      <c r="F40" s="361"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4650,13 +4650,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="359" t="s">
+      <c r="B43" s="361" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+      <c r="C43" s="361"/>
+      <c r="D43" s="361"/>
+      <c r="E43" s="361"/>
+      <c r="F43" s="361"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4685,13 +4685,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+      <c r="B47" s="361" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="C47" s="361"/>
+      <c r="D47" s="361"/>
+      <c r="E47" s="361"/>
+      <c r="F47" s="361"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4707,13 +4707,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+      <c r="B50" s="361" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="C50" s="361"/>
+      <c r="D50" s="361"/>
+      <c r="E50" s="361"/>
+      <c r="F50" s="361"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4777,13 +4777,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+      <c r="B58" s="361" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="C58" s="361"/>
+      <c r="D58" s="361"/>
+      <c r="E58" s="361"/>
+      <c r="F58" s="361"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4799,7 +4799,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+      <c r="B61" s="361" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4821,22 +4821,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="358" t="s">
+      <c r="B64" s="360" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
+      <c r="C64" s="360"/>
+      <c r="D64" s="360"/>
+      <c r="E64" s="360"/>
+      <c r="F64" s="360"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="B65" s="360" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+      <c r="C65" s="360"/>
+      <c r="D65" s="360"/>
+      <c r="E65" s="360"/>
+      <c r="F65" s="360"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4870,7 +4870,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>3.1352662185971159E-2</v>
+        <v>3.2101314756258464E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>2.5441696113074206E-2</v>
+        <v>2.6049204052098412E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>445</v>
@@ -4971,22 +4971,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="360" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="C80" s="360"/>
+      <c r="D80" s="360"/>
+      <c r="E80" s="360"/>
+      <c r="F80" s="360"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="360" t="s">
+      <c r="B81" s="363" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="360"/>
-      <c r="D81" s="360"/>
-      <c r="E81" s="360"/>
-      <c r="F81" s="360"/>
+      <c r="C81" s="363"/>
+      <c r="D81" s="363"/>
+      <c r="E81" s="363"/>
+      <c r="F81" s="363"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5030,22 +5030,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="358" t="s">
+      <c r="B89" s="360" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
+      <c r="C89" s="360"/>
+      <c r="D89" s="360"/>
+      <c r="E89" s="360"/>
+      <c r="F89" s="360"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="B90" s="360" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+      <c r="C90" s="360"/>
+      <c r="D90" s="360"/>
+      <c r="E90" s="360"/>
+      <c r="F90" s="360"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5082,13 +5082,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+      <c r="B97" s="360" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="C97" s="360"/>
+      <c r="D97" s="360"/>
+      <c r="E97" s="360"/>
+      <c r="F97" s="360"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5101,13 +5101,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="358" t="s">
+      <c r="B101" s="360" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+      <c r="C101" s="360"/>
+      <c r="D101" s="360"/>
+      <c r="E101" s="360"/>
+      <c r="F101" s="360"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5229,13 +5229,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="358" t="s">
+      <c r="B116" s="360" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+      <c r="C116" s="360"/>
+      <c r="D116" s="360"/>
+      <c r="E116" s="360"/>
+      <c r="F116" s="360"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5274,13 +5274,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="359" t="s">
+      <c r="B123" s="361" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+      <c r="C123" s="361"/>
+      <c r="D123" s="361"/>
+      <c r="E123" s="361"/>
+      <c r="F123" s="361"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5423,13 +5423,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="363" t="s">
+      <c r="B134" s="364" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="363"/>
-      <c r="D134" s="363"/>
-      <c r="E134" s="363"/>
-      <c r="F134" s="363"/>
+      <c r="C134" s="364"/>
+      <c r="D134" s="364"/>
+      <c r="E134" s="364"/>
+      <c r="F134" s="364"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5442,22 +5442,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="361" t="s">
+      <c r="B138" s="365" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="361"/>
-      <c r="D138" s="361"/>
-      <c r="E138" s="361"/>
-      <c r="F138" s="361"/>
+      <c r="C138" s="365"/>
+      <c r="D138" s="365"/>
+      <c r="E138" s="365"/>
+      <c r="F138" s="365"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="B139" s="360" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="C139" s="360"/>
+      <c r="D139" s="360"/>
+      <c r="E139" s="360"/>
+      <c r="F139" s="360"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5790,13 +5790,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="365" t="s">
+      <c r="B179" s="359" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="C179" s="360"/>
+      <c r="D179" s="360"/>
+      <c r="E179" s="360"/>
+      <c r="F179" s="360"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5833,13 +5833,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+      <c r="B188" s="361" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="C188" s="361"/>
+      <c r="D188" s="361"/>
+      <c r="E188" s="361"/>
+      <c r="F188" s="361"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5847,22 +5847,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="364" t="s">
+      <c r="B191" s="358" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="364"/>
-      <c r="D191" s="364"/>
-      <c r="E191" s="364"/>
-      <c r="F191" s="364"/>
+      <c r="C191" s="358"/>
+      <c r="D191" s="358"/>
+      <c r="E191" s="358"/>
+      <c r="F191" s="358"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="364" t="s">
+      <c r="B192" s="358" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="364"/>
-      <c r="D192" s="364"/>
-      <c r="E192" s="364"/>
-      <c r="F192" s="364"/>
+      <c r="C192" s="358"/>
+      <c r="D192" s="358"/>
+      <c r="E192" s="358"/>
+      <c r="F192" s="358"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5886,17 +5886,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5913,6 +5902,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13503,32 +13503,32 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>2.5441696113074206E-2</v>
+        <v>2.6049204052098412E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>2.5441696113074206E-2</v>
+        <v>2.6049204052098412E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>2.5441696113074206E-2</v>
+        <v>2.6049204052098412E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>2.5441696113074206E-2</v>
+        <v>2.6049204052098412E-2</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
-        <v>2.5441696113074206E-2</v>
+        <v>2.6049204052098412E-2</v>
       </c>
       <c r="K94" s="23">
         <f t="shared" si="39"/>
-        <v>1.2720848056537103E-2</v>
+        <v>1.3024602026049206E-2</v>
       </c>
       <c r="L94" s="23">
         <f t="shared" si="39"/>
-        <v>1.2720848056537103E-2</v>
+        <v>1.3024602026049206E-2</v>
       </c>
       <c r="M94" s="23">
         <f t="shared" si="39"/>
@@ -14702,50 +14702,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>3.1352662185971159E-2</v>
+        <v>3.2101314756258464E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>3.5726228939853416E-2</v>
+        <v>3.6579315448547457E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>4.6980775014026054E-2</v>
+        <v>4.8102602492653301E-2</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>9.2404606009735143E-2</v>
+        <v>9.4611083577261376E-2</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>5.983808528741761E-2</v>
+        <v>6.1266925240011517E-2</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>4.4746759949767997E-2</v>
+        <v>4.5815242640319623E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>3.7174569664421203E-2</v>
+        <v>3.8062240285930533E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>2.6214098346682112E-2</v>
+        <v>2.6840050043817069E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>2.3830043225647253E-2</v>
+        <v>2.4399067412656197E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>1.5766222622815337E-2</v>
+        <v>1.6142695377195156E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>1.5415951191833374E-2</v>
+        <v>1.5784060011898859E-2</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14759,43 +14759,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.6378104661082123E-2</v>
+        <v>4.7485541313626055E-2</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.6923260687066629E-2</v>
+        <v>5.8282499183935813E-2</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10223412683413621</v>
+        <v>0.10467531799587754</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.1114910873348478E-2</v>
+        <v>6.2574239425317008E-2</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.32595359512227E-2</v>
+        <v>4.4292506057149149E-2</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.5043360527306826E-2</v>
+        <v>3.5880141205599979E-2</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.5605963100032183E-2</v>
+        <v>2.621739347796349E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.7823365755073824E-2</v>
+        <v>1.8248959872235501E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.5639210470726698E-2</v>
+        <v>1.6012650373428569E-2</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.3920828642007494E-2</v>
+        <v>1.4253236272388281E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18745,7 +18745,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-14.15</v>
+        <v>-13.82</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18985,7 +18985,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>14.15</v>
+        <v>13.82</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19583,7 +19583,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>14.15</v>
+        <v>13.82</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19596,7 +19596,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>-7.3489748596123561E-2</v>
+        <v>-6.5958680292173444E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/300481.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/300481.SZ_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DDD7C0B-3306-429C-9EEC-6EE8DA5FEF28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFAD3967-F56D-4CA2-83F5-FF69B48DEE57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1470" yWindow="1470" windowWidth="12690" windowHeight="7643" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3893,29 +3893,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4333,7 +4333,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>13.82</v>
+        <v>13.8</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>4033.4421531599996</v>
+        <v>4027.6050444000002</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4391,13 +4391,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="360" t="s">
+      <c r="B18" s="358" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="360"/>
-      <c r="D18" s="360"/>
-      <c r="E18" s="360"/>
-      <c r="F18" s="360"/>
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4480,7 +4480,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>-6.5958680292173444E-2</v>
+        <v>-6.5494409358920036E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4597,22 +4597,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="360" t="s">
+      <c r="B36" s="358" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="360"/>
-      <c r="D36" s="360"/>
-      <c r="E36" s="360"/>
-      <c r="F36" s="360"/>
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="363" t="s">
+      <c r="B37" s="360" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="363"/>
-      <c r="D37" s="363"/>
-      <c r="E37" s="363"/>
-      <c r="F37" s="363"/>
+      <c r="C37" s="360"/>
+      <c r="D37" s="360"/>
+      <c r="E37" s="360"/>
+      <c r="F37" s="360"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4624,13 +4624,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="361" t="s">
+      <c r="B40" s="359" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="361"/>
-      <c r="D40" s="361"/>
-      <c r="E40" s="361"/>
-      <c r="F40" s="361"/>
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4650,13 +4650,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="361" t="s">
+      <c r="B43" s="359" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="361"/>
-      <c r="D43" s="361"/>
-      <c r="E43" s="361"/>
-      <c r="F43" s="361"/>
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4685,13 +4685,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="361" t="s">
+      <c r="B47" s="359" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="361"/>
-      <c r="D47" s="361"/>
-      <c r="E47" s="361"/>
-      <c r="F47" s="361"/>
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4707,13 +4707,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="361" t="s">
+      <c r="B50" s="359" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="361"/>
-      <c r="D50" s="361"/>
-      <c r="E50" s="361"/>
-      <c r="F50" s="361"/>
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4777,13 +4777,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="361" t="s">
+      <c r="B58" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="361"/>
-      <c r="D58" s="361"/>
-      <c r="E58" s="361"/>
-      <c r="F58" s="361"/>
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4799,7 +4799,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="361" t="s">
+      <c r="B61" s="359" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4821,22 +4821,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="360" t="s">
+      <c r="B64" s="358" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="360"/>
-      <c r="D64" s="360"/>
-      <c r="E64" s="360"/>
-      <c r="F64" s="360"/>
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="360" t="s">
+      <c r="B65" s="358" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="360"/>
-      <c r="D65" s="360"/>
-      <c r="E65" s="360"/>
-      <c r="F65" s="360"/>
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4870,7 +4870,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>3.2101314756258464E-2</v>
+        <v>3.2147838400832747E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>2.6049204052098412E-2</v>
+        <v>2.6086956521739132E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>445</v>
@@ -4971,22 +4971,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="360" t="s">
+      <c r="B80" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="360"/>
-      <c r="D80" s="360"/>
-      <c r="E80" s="360"/>
-      <c r="F80" s="360"/>
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="363" t="s">
+      <c r="B81" s="360" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="363"/>
-      <c r="D81" s="363"/>
-      <c r="E81" s="363"/>
-      <c r="F81" s="363"/>
+      <c r="C81" s="360"/>
+      <c r="D81" s="360"/>
+      <c r="E81" s="360"/>
+      <c r="F81" s="360"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5030,22 +5030,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="360" t="s">
+      <c r="B89" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="360"/>
-      <c r="D89" s="360"/>
-      <c r="E89" s="360"/>
-      <c r="F89" s="360"/>
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="360" t="s">
+      <c r="B90" s="358" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="360"/>
-      <c r="D90" s="360"/>
-      <c r="E90" s="360"/>
-      <c r="F90" s="360"/>
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5082,13 +5082,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="360" t="s">
+      <c r="B97" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="360"/>
-      <c r="D97" s="360"/>
-      <c r="E97" s="360"/>
-      <c r="F97" s="360"/>
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5101,13 +5101,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="360" t="s">
+      <c r="B101" s="358" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="360"/>
-      <c r="D101" s="360"/>
-      <c r="E101" s="360"/>
-      <c r="F101" s="360"/>
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5229,13 +5229,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="360" t="s">
+      <c r="B116" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="360"/>
-      <c r="D116" s="360"/>
-      <c r="E116" s="360"/>
-      <c r="F116" s="360"/>
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5274,13 +5274,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="361" t="s">
+      <c r="B123" s="359" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="361"/>
-      <c r="D123" s="361"/>
-      <c r="E123" s="361"/>
-      <c r="F123" s="361"/>
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5423,13 +5423,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="364" t="s">
+      <c r="B134" s="363" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="364"/>
-      <c r="D134" s="364"/>
-      <c r="E134" s="364"/>
-      <c r="F134" s="364"/>
+      <c r="C134" s="363"/>
+      <c r="D134" s="363"/>
+      <c r="E134" s="363"/>
+      <c r="F134" s="363"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5442,22 +5442,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="365" t="s">
+      <c r="B138" s="361" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="365"/>
-      <c r="D138" s="365"/>
-      <c r="E138" s="365"/>
-      <c r="F138" s="365"/>
+      <c r="C138" s="361"/>
+      <c r="D138" s="361"/>
+      <c r="E138" s="361"/>
+      <c r="F138" s="361"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="360" t="s">
+      <c r="B139" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="360"/>
-      <c r="D139" s="360"/>
-      <c r="E139" s="360"/>
-      <c r="F139" s="360"/>
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5790,13 +5790,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="359" t="s">
+      <c r="B179" s="365" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="360"/>
-      <c r="D179" s="360"/>
-      <c r="E179" s="360"/>
-      <c r="F179" s="360"/>
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5833,13 +5833,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="361" t="s">
+      <c r="B188" s="359" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="361"/>
-      <c r="D188" s="361"/>
-      <c r="E188" s="361"/>
-      <c r="F188" s="361"/>
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5847,22 +5847,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="358" t="s">
+      <c r="B191" s="364" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="358"/>
-      <c r="D191" s="358"/>
-      <c r="E191" s="358"/>
-      <c r="F191" s="358"/>
+      <c r="C191" s="364"/>
+      <c r="D191" s="364"/>
+      <c r="E191" s="364"/>
+      <c r="F191" s="364"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="358" t="s">
+      <c r="B192" s="364" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="358"/>
-      <c r="D192" s="358"/>
-      <c r="E192" s="358"/>
-      <c r="F192" s="358"/>
+      <c r="C192" s="364"/>
+      <c r="D192" s="364"/>
+      <c r="E192" s="364"/>
+      <c r="F192" s="364"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5886,6 +5886,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5902,17 +5913,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13503,32 +13503,32 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>2.6049204052098412E-2</v>
+        <v>2.6086956521739132E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>2.6049204052098412E-2</v>
+        <v>2.6086956521739132E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>2.6049204052098412E-2</v>
+        <v>2.6086956521739132E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>2.6049204052098412E-2</v>
+        <v>2.6086956521739132E-2</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
-        <v>2.6049204052098412E-2</v>
+        <v>2.6086956521739132E-2</v>
       </c>
       <c r="K94" s="23">
         <f t="shared" si="39"/>
-        <v>1.3024602026049206E-2</v>
+        <v>1.3043478260869566E-2</v>
       </c>
       <c r="L94" s="23">
         <f t="shared" si="39"/>
-        <v>1.3024602026049206E-2</v>
+        <v>1.3043478260869566E-2</v>
       </c>
       <c r="M94" s="23">
         <f t="shared" si="39"/>
@@ -14702,50 +14702,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>3.2101314756258464E-2</v>
+        <v>3.2147838400832747E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>3.6579315448547457E-2</v>
+        <v>3.6632328949197525E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>4.8102602492653301E-2</v>
+        <v>4.8172316409309322E-2</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>9.4611083577261376E-2</v>
+        <v>9.4748201089692188E-2</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>6.1266925240011517E-2</v>
+        <v>6.1355717885286896E-2</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>4.5815242640319623E-2</v>
+        <v>4.5881641542696895E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>3.8062240285930533E-2</v>
+        <v>3.8117402953011595E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>2.6840050043817069E-2</v>
+        <v>2.6878948667068976E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>2.4399067412656197E-2</v>
+        <v>2.4434428379920915E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>1.6142695377195156E-2</v>
+        <v>1.616609058788674E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>1.5784060011898859E-2</v>
+        <v>1.5806935461191468E-2</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14759,43 +14759,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.7485541313626055E-2</v>
+        <v>4.755436093871826E-2</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.8282499183935813E-2</v>
+        <v>5.8366966574057454E-2</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10467531799587754</v>
+        <v>0.10482702135529186</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.2574239425317008E-2</v>
+        <v>6.2664926728831963E-2</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.4292506057149149E-2</v>
+        <v>4.4356698094913133E-2</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.5880141205599979E-2</v>
+        <v>3.5932141410245769E-2</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.621739347796349E-2</v>
+        <v>2.6255389700395322E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.8248959872235501E-2</v>
+        <v>1.8275407640166278E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.6012650373428569E-2</v>
+        <v>1.6035857113100203E-2</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.4253236272388281E-2</v>
+        <v>1.4273893136551162E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18745,7 +18745,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-13.82</v>
+        <v>-13.8</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18985,7 +18985,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>13.82</v>
+        <v>13.8</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19583,7 +19583,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>13.82</v>
+        <v>13.8</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19596,7 +19596,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>-6.5958680292173444E-2</v>
+        <v>-6.5494409358920036E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/300481.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/300481.SZ_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFAD3967-F56D-4CA2-83F5-FF69B48DEE57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{769B58DA-BD30-426E-9542-279E31A9FFBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1470" yWindow="1470" windowWidth="12690" windowHeight="7643" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3893,29 +3893,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4333,7 +4333,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>13.8</v>
+        <v>13.87</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>4027.6050444000002</v>
+        <v>4048.0349250599998</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4391,13 +4391,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="358" t="s">
+      <c r="B18" s="360" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+      <c r="C18" s="360"/>
+      <c r="D18" s="360"/>
+      <c r="E18" s="360"/>
+      <c r="F18" s="360"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4480,7 +4480,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>-6.5494409358920036E-2</v>
+        <v>-6.7115373860151983E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4597,22 +4597,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="358" t="s">
+      <c r="B36" s="360" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
+      <c r="C36" s="360"/>
+      <c r="D36" s="360"/>
+      <c r="E36" s="360"/>
+      <c r="F36" s="360"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="360" t="s">
+      <c r="B37" s="363" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="360"/>
-      <c r="D37" s="360"/>
-      <c r="E37" s="360"/>
-      <c r="F37" s="360"/>
+      <c r="C37" s="363"/>
+      <c r="D37" s="363"/>
+      <c r="E37" s="363"/>
+      <c r="F37" s="363"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4624,13 +4624,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="359" t="s">
+      <c r="B40" s="361" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+      <c r="C40" s="361"/>
+      <c r="D40" s="361"/>
+      <c r="E40" s="361"/>
+      <c r="F40" s="361"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4650,13 +4650,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="359" t="s">
+      <c r="B43" s="361" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+      <c r="C43" s="361"/>
+      <c r="D43" s="361"/>
+      <c r="E43" s="361"/>
+      <c r="F43" s="361"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4685,13 +4685,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+      <c r="B47" s="361" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="C47" s="361"/>
+      <c r="D47" s="361"/>
+      <c r="E47" s="361"/>
+      <c r="F47" s="361"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4707,13 +4707,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+      <c r="B50" s="361" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="C50" s="361"/>
+      <c r="D50" s="361"/>
+      <c r="E50" s="361"/>
+      <c r="F50" s="361"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4777,13 +4777,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+      <c r="B58" s="361" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="C58" s="361"/>
+      <c r="D58" s="361"/>
+      <c r="E58" s="361"/>
+      <c r="F58" s="361"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4799,7 +4799,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+      <c r="B61" s="361" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4821,22 +4821,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="358" t="s">
+      <c r="B64" s="360" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
+      <c r="C64" s="360"/>
+      <c r="D64" s="360"/>
+      <c r="E64" s="360"/>
+      <c r="F64" s="360"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="B65" s="360" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+      <c r="C65" s="360"/>
+      <c r="D65" s="360"/>
+      <c r="E65" s="360"/>
+      <c r="F65" s="360"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4870,7 +4870,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>3.2147838400832747E-2</v>
+        <v>3.1985592641059261E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>2.6086956521739132E-2</v>
+        <v>2.5955299206921419E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>445</v>
@@ -4971,22 +4971,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="360" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="C80" s="360"/>
+      <c r="D80" s="360"/>
+      <c r="E80" s="360"/>
+      <c r="F80" s="360"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="360" t="s">
+      <c r="B81" s="363" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="360"/>
-      <c r="D81" s="360"/>
-      <c r="E81" s="360"/>
-      <c r="F81" s="360"/>
+      <c r="C81" s="363"/>
+      <c r="D81" s="363"/>
+      <c r="E81" s="363"/>
+      <c r="F81" s="363"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5030,22 +5030,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="358" t="s">
+      <c r="B89" s="360" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
+      <c r="C89" s="360"/>
+      <c r="D89" s="360"/>
+      <c r="E89" s="360"/>
+      <c r="F89" s="360"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="B90" s="360" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+      <c r="C90" s="360"/>
+      <c r="D90" s="360"/>
+      <c r="E90" s="360"/>
+      <c r="F90" s="360"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5082,13 +5082,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+      <c r="B97" s="360" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="C97" s="360"/>
+      <c r="D97" s="360"/>
+      <c r="E97" s="360"/>
+      <c r="F97" s="360"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5101,13 +5101,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="358" t="s">
+      <c r="B101" s="360" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+      <c r="C101" s="360"/>
+      <c r="D101" s="360"/>
+      <c r="E101" s="360"/>
+      <c r="F101" s="360"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5229,13 +5229,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="358" t="s">
+      <c r="B116" s="360" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+      <c r="C116" s="360"/>
+      <c r="D116" s="360"/>
+      <c r="E116" s="360"/>
+      <c r="F116" s="360"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5274,13 +5274,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="359" t="s">
+      <c r="B123" s="361" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+      <c r="C123" s="361"/>
+      <c r="D123" s="361"/>
+      <c r="E123" s="361"/>
+      <c r="F123" s="361"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5423,13 +5423,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="363" t="s">
+      <c r="B134" s="364" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="363"/>
-      <c r="D134" s="363"/>
-      <c r="E134" s="363"/>
-      <c r="F134" s="363"/>
+      <c r="C134" s="364"/>
+      <c r="D134" s="364"/>
+      <c r="E134" s="364"/>
+      <c r="F134" s="364"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5442,22 +5442,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="361" t="s">
+      <c r="B138" s="365" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="361"/>
-      <c r="D138" s="361"/>
-      <c r="E138" s="361"/>
-      <c r="F138" s="361"/>
+      <c r="C138" s="365"/>
+      <c r="D138" s="365"/>
+      <c r="E138" s="365"/>
+      <c r="F138" s="365"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="B139" s="360" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="C139" s="360"/>
+      <c r="D139" s="360"/>
+      <c r="E139" s="360"/>
+      <c r="F139" s="360"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5790,13 +5790,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="365" t="s">
+      <c r="B179" s="359" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="C179" s="360"/>
+      <c r="D179" s="360"/>
+      <c r="E179" s="360"/>
+      <c r="F179" s="360"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5833,13 +5833,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+      <c r="B188" s="361" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="C188" s="361"/>
+      <c r="D188" s="361"/>
+      <c r="E188" s="361"/>
+      <c r="F188" s="361"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5847,22 +5847,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="364" t="s">
+      <c r="B191" s="358" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="364"/>
-      <c r="D191" s="364"/>
-      <c r="E191" s="364"/>
-      <c r="F191" s="364"/>
+      <c r="C191" s="358"/>
+      <c r="D191" s="358"/>
+      <c r="E191" s="358"/>
+      <c r="F191" s="358"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="364" t="s">
+      <c r="B192" s="358" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="364"/>
-      <c r="D192" s="364"/>
-      <c r="E192" s="364"/>
-      <c r="F192" s="364"/>
+      <c r="C192" s="358"/>
+      <c r="D192" s="358"/>
+      <c r="E192" s="358"/>
+      <c r="F192" s="358"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5886,17 +5886,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5913,6 +5902,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13503,32 +13503,32 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>2.6086956521739132E-2</v>
+        <v>2.5955299206921419E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>2.6086956521739132E-2</v>
+        <v>2.5955299206921419E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>2.6086956521739132E-2</v>
+        <v>2.5955299206921419E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>2.6086956521739132E-2</v>
+        <v>2.5955299206921419E-2</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
-        <v>2.6086956521739132E-2</v>
+        <v>2.5955299206921419E-2</v>
       </c>
       <c r="K94" s="23">
         <f t="shared" si="39"/>
-        <v>1.3043478260869566E-2</v>
+        <v>1.2977649603460709E-2</v>
       </c>
       <c r="L94" s="23">
         <f t="shared" si="39"/>
-        <v>1.3043478260869566E-2</v>
+        <v>1.2977649603460709E-2</v>
       </c>
       <c r="M94" s="23">
         <f t="shared" si="39"/>
@@ -14702,50 +14702,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>3.2147838400832747E-2</v>
+        <v>3.1985592641059261E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>3.6632328949197525E-2</v>
+        <v>3.6447450576706987E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>4.8172316409309322E-2</v>
+        <v>4.7929197292607695E-2</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>9.4748201089692188E-2</v>
+        <v>9.4270019829686552E-2</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>6.1355717885286896E-2</v>
+        <v>6.1046063937776444E-2</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>4.5881641542696895E-2</v>
+        <v>4.5650083149907511E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>3.8117402953011595E-2</v>
+        <v>3.7925029614387887E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>2.6878948667068976E-2</v>
+        <v>2.6743294275814844E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>2.4434428379920915E-2</v>
+        <v>2.4311111149452679E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>1.616609058788674E-2</v>
+        <v>1.6084502531567197E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>1.5806935461191468E-2</v>
+        <v>1.5727160011855968E-2</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14759,43 +14759,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.755436093871826E-2</v>
+        <v>4.7314360559070803E-2</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.8366966574057454E-2</v>
+        <v>5.807239644715162E-2</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10482702135529186</v>
+        <v>0.1042979736627994</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.2664926728831963E-2</v>
+        <v>6.2348665382687893E-2</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.4356698094913133E-2</v>
+        <v>4.4132835883907803E-2</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.5932141410245769E-2</v>
+        <v>3.575079678885304E-2</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.6255389700395322E-2</v>
+        <v>2.6122882326276527E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.8275407640166278E-2</v>
+        <v>1.8183174148110645E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.6035857113100203E-2</v>
+        <v>1.5954926327381602E-2</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.4273893136551162E-2</v>
+        <v>1.4201854742927617E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18745,7 +18745,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-13.8</v>
+        <v>-13.87</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18985,7 +18985,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>13.8</v>
+        <v>13.87</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19583,7 +19583,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>13.8</v>
+        <v>13.87</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19596,7 +19596,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>-6.5494409358920036E-2</v>
+        <v>-6.7115373860151983E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/300481.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/300481.SZ_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{769B58DA-BD30-426E-9542-279E31A9FFBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{240846BC-6399-4498-AF25-EDD6BE583ACE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3893,29 +3893,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4333,7 +4333,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>13.87</v>
+        <v>14.2</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>4048.0349250599998</v>
+        <v>4144.3472196000002</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4391,13 +4391,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="360" t="s">
+      <c r="B18" s="358" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="360"/>
-      <c r="D18" s="360"/>
-      <c r="E18" s="360"/>
-      <c r="F18" s="360"/>
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4480,7 +4480,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>-6.7115373860151983E-2</v>
+        <v>-7.4610007703045822E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4597,22 +4597,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="360" t="s">
+      <c r="B36" s="358" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="360"/>
-      <c r="D36" s="360"/>
-      <c r="E36" s="360"/>
-      <c r="F36" s="360"/>
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="363" t="s">
+      <c r="B37" s="360" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="363"/>
-      <c r="D37" s="363"/>
-      <c r="E37" s="363"/>
-      <c r="F37" s="363"/>
+      <c r="C37" s="360"/>
+      <c r="D37" s="360"/>
+      <c r="E37" s="360"/>
+      <c r="F37" s="360"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4624,13 +4624,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="361" t="s">
+      <c r="B40" s="359" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="361"/>
-      <c r="D40" s="361"/>
-      <c r="E40" s="361"/>
-      <c r="F40" s="361"/>
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4650,13 +4650,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="361" t="s">
+      <c r="B43" s="359" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="361"/>
-      <c r="D43" s="361"/>
-      <c r="E43" s="361"/>
-      <c r="F43" s="361"/>
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4685,13 +4685,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="361" t="s">
+      <c r="B47" s="359" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="361"/>
-      <c r="D47" s="361"/>
-      <c r="E47" s="361"/>
-      <c r="F47" s="361"/>
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4707,13 +4707,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="361" t="s">
+      <c r="B50" s="359" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="361"/>
-      <c r="D50" s="361"/>
-      <c r="E50" s="361"/>
-      <c r="F50" s="361"/>
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4777,13 +4777,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="361" t="s">
+      <c r="B58" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="361"/>
-      <c r="D58" s="361"/>
-      <c r="E58" s="361"/>
-      <c r="F58" s="361"/>
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4799,7 +4799,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="361" t="s">
+      <c r="B61" s="359" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4821,22 +4821,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="360" t="s">
+      <c r="B64" s="358" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="360"/>
-      <c r="D64" s="360"/>
-      <c r="E64" s="360"/>
-      <c r="F64" s="360"/>
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="360" t="s">
+      <c r="B65" s="358" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="360"/>
-      <c r="D65" s="360"/>
-      <c r="E65" s="360"/>
-      <c r="F65" s="360"/>
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4870,7 +4870,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>3.1985592641059261E-2</v>
+        <v>3.1242265488133233E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>2.5955299206921419E-2</v>
+        <v>2.5352112676056342E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>445</v>
@@ -4971,22 +4971,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="360" t="s">
+      <c r="B80" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="360"/>
-      <c r="D80" s="360"/>
-      <c r="E80" s="360"/>
-      <c r="F80" s="360"/>
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="363" t="s">
+      <c r="B81" s="360" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="363"/>
-      <c r="D81" s="363"/>
-      <c r="E81" s="363"/>
-      <c r="F81" s="363"/>
+      <c r="C81" s="360"/>
+      <c r="D81" s="360"/>
+      <c r="E81" s="360"/>
+      <c r="F81" s="360"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5030,22 +5030,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="360" t="s">
+      <c r="B89" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="360"/>
-      <c r="D89" s="360"/>
-      <c r="E89" s="360"/>
-      <c r="F89" s="360"/>
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="360" t="s">
+      <c r="B90" s="358" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="360"/>
-      <c r="D90" s="360"/>
-      <c r="E90" s="360"/>
-      <c r="F90" s="360"/>
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5082,13 +5082,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="360" t="s">
+      <c r="B97" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="360"/>
-      <c r="D97" s="360"/>
-      <c r="E97" s="360"/>
-      <c r="F97" s="360"/>
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5101,13 +5101,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="360" t="s">
+      <c r="B101" s="358" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="360"/>
-      <c r="D101" s="360"/>
-      <c r="E101" s="360"/>
-      <c r="F101" s="360"/>
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5229,13 +5229,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="360" t="s">
+      <c r="B116" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="360"/>
-      <c r="D116" s="360"/>
-      <c r="E116" s="360"/>
-      <c r="F116" s="360"/>
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5274,13 +5274,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="361" t="s">
+      <c r="B123" s="359" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="361"/>
-      <c r="D123" s="361"/>
-      <c r="E123" s="361"/>
-      <c r="F123" s="361"/>
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5423,13 +5423,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="364" t="s">
+      <c r="B134" s="363" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="364"/>
-      <c r="D134" s="364"/>
-      <c r="E134" s="364"/>
-      <c r="F134" s="364"/>
+      <c r="C134" s="363"/>
+      <c r="D134" s="363"/>
+      <c r="E134" s="363"/>
+      <c r="F134" s="363"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5442,22 +5442,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="365" t="s">
+      <c r="B138" s="361" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="365"/>
-      <c r="D138" s="365"/>
-      <c r="E138" s="365"/>
-      <c r="F138" s="365"/>
+      <c r="C138" s="361"/>
+      <c r="D138" s="361"/>
+      <c r="E138" s="361"/>
+      <c r="F138" s="361"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="360" t="s">
+      <c r="B139" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="360"/>
-      <c r="D139" s="360"/>
-      <c r="E139" s="360"/>
-      <c r="F139" s="360"/>
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5790,13 +5790,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="359" t="s">
+      <c r="B179" s="365" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="360"/>
-      <c r="D179" s="360"/>
-      <c r="E179" s="360"/>
-      <c r="F179" s="360"/>
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5833,13 +5833,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="361" t="s">
+      <c r="B188" s="359" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="361"/>
-      <c r="D188" s="361"/>
-      <c r="E188" s="361"/>
-      <c r="F188" s="361"/>
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5847,22 +5847,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="358" t="s">
+      <c r="B191" s="364" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="358"/>
-      <c r="D191" s="358"/>
-      <c r="E191" s="358"/>
-      <c r="F191" s="358"/>
+      <c r="C191" s="364"/>
+      <c r="D191" s="364"/>
+      <c r="E191" s="364"/>
+      <c r="F191" s="364"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="358" t="s">
+      <c r="B192" s="364" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="358"/>
-      <c r="D192" s="358"/>
-      <c r="E192" s="358"/>
-      <c r="F192" s="358"/>
+      <c r="C192" s="364"/>
+      <c r="D192" s="364"/>
+      <c r="E192" s="364"/>
+      <c r="F192" s="364"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5886,6 +5886,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5902,17 +5913,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13503,32 +13503,32 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>2.5955299206921419E-2</v>
+        <v>2.5352112676056342E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>2.5955299206921419E-2</v>
+        <v>2.5352112676056342E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>2.5955299206921419E-2</v>
+        <v>2.5352112676056342E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>2.5955299206921419E-2</v>
+        <v>2.5352112676056342E-2</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
-        <v>2.5955299206921419E-2</v>
+        <v>2.5352112676056342E-2</v>
       </c>
       <c r="K94" s="23">
         <f t="shared" si="39"/>
-        <v>1.2977649603460709E-2</v>
+        <v>1.2676056338028171E-2</v>
       </c>
       <c r="L94" s="23">
         <f t="shared" si="39"/>
-        <v>1.2977649603460709E-2</v>
+        <v>1.2676056338028171E-2</v>
       </c>
       <c r="M94" s="23">
         <f t="shared" si="39"/>
@@ -14702,50 +14702,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>3.1985592641059261E-2</v>
+        <v>3.1242265488133233E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>3.6447450576706987E-2</v>
+        <v>3.5600432359079288E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>4.7929197292607695E-2</v>
+        <v>4.6815349749892161E-2</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>9.4270019829686552E-2</v>
+        <v>9.2079237678714954E-2</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>6.1046063937776444E-2</v>
+        <v>5.9627387804011216E-2</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>4.5650083149907511E-2</v>
+        <v>4.4589200935860364E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>3.7925029614387887E-2</v>
+        <v>3.7043673292363383E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>2.6743294275814844E-2</v>
+        <v>2.612179518348957E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>2.4311111149452679E-2</v>
+        <v>2.3746134622740049E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>1.6084502531567197E-2</v>
+        <v>1.5710707754425145E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>1.5727160011855968E-2</v>
+        <v>1.5361669673552273E-2</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14759,43 +14759,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.7314360559070803E-2</v>
+        <v>4.6214801475655778E-2</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.807239644715162E-2</v>
+        <v>5.672282667056288E-2</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.1042979736627994</v>
+        <v>0.10187414751429771</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.2348665382687893E-2</v>
+        <v>6.0899717525202894E-2</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.4132835883907803E-2</v>
+        <v>4.3107213641535296E-2</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.575079678885304E-2</v>
+        <v>3.4919968412774061E-2</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.6122882326276527E-2</v>
+        <v>2.5515801258130664E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.8183174148110645E-2</v>
+        <v>1.7760607424950326E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.5954926327381602E-2</v>
+        <v>1.5584142828224141E-2</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.4201854742927617E-2</v>
+        <v>1.3871811639746904E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18745,7 +18745,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-13.87</v>
+        <v>-14.2</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18985,7 +18985,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>13.87</v>
+        <v>14.2</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19583,7 +19583,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>13.87</v>
+        <v>14.2</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19596,7 +19596,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>-6.7115373860151983E-2</v>
+        <v>-7.4610007703045822E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/300481.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/300481.SZ_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{240846BC-6399-4498-AF25-EDD6BE583ACE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E94B4D18-03D5-483E-8ED4-A589CE6E1930}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3893,29 +3893,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4333,7 +4333,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>14.2</v>
+        <v>14.28</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>4144.3472196000002</v>
+        <v>4167.6956546399997</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4391,13 +4391,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="358" t="s">
+      <c r="B18" s="360" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+      <c r="C18" s="360"/>
+      <c r="D18" s="360"/>
+      <c r="E18" s="360"/>
+      <c r="F18" s="360"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4480,7 +4480,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>-7.4610007703045822E-2</v>
+        <v>-7.6391321062616813E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4597,22 +4597,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="358" t="s">
+      <c r="B36" s="360" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
+      <c r="C36" s="360"/>
+      <c r="D36" s="360"/>
+      <c r="E36" s="360"/>
+      <c r="F36" s="360"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="360" t="s">
+      <c r="B37" s="363" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="360"/>
-      <c r="D37" s="360"/>
-      <c r="E37" s="360"/>
-      <c r="F37" s="360"/>
+      <c r="C37" s="363"/>
+      <c r="D37" s="363"/>
+      <c r="E37" s="363"/>
+      <c r="F37" s="363"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4624,13 +4624,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="359" t="s">
+      <c r="B40" s="361" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+      <c r="C40" s="361"/>
+      <c r="D40" s="361"/>
+      <c r="E40" s="361"/>
+      <c r="F40" s="361"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4650,13 +4650,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="359" t="s">
+      <c r="B43" s="361" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+      <c r="C43" s="361"/>
+      <c r="D43" s="361"/>
+      <c r="E43" s="361"/>
+      <c r="F43" s="361"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4685,13 +4685,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+      <c r="B47" s="361" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="C47" s="361"/>
+      <c r="D47" s="361"/>
+      <c r="E47" s="361"/>
+      <c r="F47" s="361"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4707,13 +4707,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+      <c r="B50" s="361" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="C50" s="361"/>
+      <c r="D50" s="361"/>
+      <c r="E50" s="361"/>
+      <c r="F50" s="361"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4777,13 +4777,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+      <c r="B58" s="361" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="C58" s="361"/>
+      <c r="D58" s="361"/>
+      <c r="E58" s="361"/>
+      <c r="F58" s="361"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4799,7 +4799,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+      <c r="B61" s="361" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4821,22 +4821,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="358" t="s">
+      <c r="B64" s="360" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
+      <c r="C64" s="360"/>
+      <c r="D64" s="360"/>
+      <c r="E64" s="360"/>
+      <c r="F64" s="360"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="B65" s="360" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+      <c r="C65" s="360"/>
+      <c r="D65" s="360"/>
+      <c r="E65" s="360"/>
+      <c r="F65" s="360"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4870,7 +4870,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>3.1242265488133233E-2</v>
+        <v>3.1067238790720722E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>2.5352112676056342E-2</v>
+        <v>2.5210084033613449E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>445</v>
@@ -4971,22 +4971,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="360" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="C80" s="360"/>
+      <c r="D80" s="360"/>
+      <c r="E80" s="360"/>
+      <c r="F80" s="360"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="360" t="s">
+      <c r="B81" s="363" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="360"/>
-      <c r="D81" s="360"/>
-      <c r="E81" s="360"/>
-      <c r="F81" s="360"/>
+      <c r="C81" s="363"/>
+      <c r="D81" s="363"/>
+      <c r="E81" s="363"/>
+      <c r="F81" s="363"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5030,22 +5030,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="358" t="s">
+      <c r="B89" s="360" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
+      <c r="C89" s="360"/>
+      <c r="D89" s="360"/>
+      <c r="E89" s="360"/>
+      <c r="F89" s="360"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="B90" s="360" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+      <c r="C90" s="360"/>
+      <c r="D90" s="360"/>
+      <c r="E90" s="360"/>
+      <c r="F90" s="360"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5082,13 +5082,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+      <c r="B97" s="360" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="C97" s="360"/>
+      <c r="D97" s="360"/>
+      <c r="E97" s="360"/>
+      <c r="F97" s="360"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5101,13 +5101,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="358" t="s">
+      <c r="B101" s="360" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+      <c r="C101" s="360"/>
+      <c r="D101" s="360"/>
+      <c r="E101" s="360"/>
+      <c r="F101" s="360"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5229,13 +5229,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="358" t="s">
+      <c r="B116" s="360" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+      <c r="C116" s="360"/>
+      <c r="D116" s="360"/>
+      <c r="E116" s="360"/>
+      <c r="F116" s="360"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5274,13 +5274,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="359" t="s">
+      <c r="B123" s="361" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+      <c r="C123" s="361"/>
+      <c r="D123" s="361"/>
+      <c r="E123" s="361"/>
+      <c r="F123" s="361"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5423,13 +5423,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="363" t="s">
+      <c r="B134" s="364" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="363"/>
-      <c r="D134" s="363"/>
-      <c r="E134" s="363"/>
-      <c r="F134" s="363"/>
+      <c r="C134" s="364"/>
+      <c r="D134" s="364"/>
+      <c r="E134" s="364"/>
+      <c r="F134" s="364"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5442,22 +5442,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="361" t="s">
+      <c r="B138" s="365" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="361"/>
-      <c r="D138" s="361"/>
-      <c r="E138" s="361"/>
-      <c r="F138" s="361"/>
+      <c r="C138" s="365"/>
+      <c r="D138" s="365"/>
+      <c r="E138" s="365"/>
+      <c r="F138" s="365"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="B139" s="360" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="C139" s="360"/>
+      <c r="D139" s="360"/>
+      <c r="E139" s="360"/>
+      <c r="F139" s="360"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5790,13 +5790,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="365" t="s">
+      <c r="B179" s="359" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="C179" s="360"/>
+      <c r="D179" s="360"/>
+      <c r="E179" s="360"/>
+      <c r="F179" s="360"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5833,13 +5833,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+      <c r="B188" s="361" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="C188" s="361"/>
+      <c r="D188" s="361"/>
+      <c r="E188" s="361"/>
+      <c r="F188" s="361"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5847,22 +5847,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="364" t="s">
+      <c r="B191" s="358" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="364"/>
-      <c r="D191" s="364"/>
-      <c r="E191" s="364"/>
-      <c r="F191" s="364"/>
+      <c r="C191" s="358"/>
+      <c r="D191" s="358"/>
+      <c r="E191" s="358"/>
+      <c r="F191" s="358"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="364" t="s">
+      <c r="B192" s="358" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="364"/>
-      <c r="D192" s="364"/>
-      <c r="E192" s="364"/>
-      <c r="F192" s="364"/>
+      <c r="C192" s="358"/>
+      <c r="D192" s="358"/>
+      <c r="E192" s="358"/>
+      <c r="F192" s="358"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5886,17 +5886,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5913,6 +5902,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13503,32 +13503,32 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>2.5352112676056342E-2</v>
+        <v>2.5210084033613449E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>2.5352112676056342E-2</v>
+        <v>2.5210084033613449E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>2.5352112676056342E-2</v>
+        <v>2.5210084033613449E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>2.5352112676056342E-2</v>
+        <v>2.5210084033613449E-2</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
-        <v>2.5352112676056342E-2</v>
+        <v>2.5210084033613449E-2</v>
       </c>
       <c r="K94" s="23">
         <f t="shared" si="39"/>
-        <v>1.2676056338028171E-2</v>
+        <v>1.2605042016806725E-2</v>
       </c>
       <c r="L94" s="23">
         <f t="shared" si="39"/>
-        <v>1.2676056338028171E-2</v>
+        <v>1.2605042016806725E-2</v>
       </c>
       <c r="M94" s="23">
         <f t="shared" si="39"/>
@@ -14702,50 +14702,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>3.1242265488133233E-2</v>
+        <v>3.1067238790720722E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>3.5600432359079288E-2</v>
+        <v>3.5400990160989208E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>4.6815349749892161E-2</v>
+        <v>4.6553078882945985E-2</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>9.2079237678714954E-2</v>
+        <v>9.1563387607685745E-2</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>5.9627387804011216E-2</v>
+        <v>5.9293340813512549E-2</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>4.4589200935860364E-2</v>
+        <v>4.4339401490841542E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>3.7043673292363383E-2</v>
+        <v>3.683614571089356E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>2.612179518348957E-2</v>
+        <v>2.5975454594226323E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>2.3746134622740049E-2</v>
+        <v>2.3613103056226097E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>1.5710707754425145E-2</v>
+        <v>1.5622692584932566E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>1.5361669673552273E-2</v>
+        <v>1.5275609899470747E-2</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14759,43 +14759,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.6214801475655778E-2</v>
+        <v>4.5955895024811767E-2</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.672282667056288E-2</v>
+        <v>5.6405051731231996E-2</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10187414751429771</v>
+        <v>0.10130342399881145</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.0899717525202894E-2</v>
+        <v>6.055854263710652E-2</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.3107213641535296E-2</v>
+        <v>4.2865716646344622E-2</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.4919968412774061E-2</v>
+        <v>3.4724338337632471E-2</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.5515801258130664E-2</v>
+        <v>2.5372855592819009E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.7760607424950326E-2</v>
+        <v>1.7661108223690099E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.5584142828224141E-2</v>
+        <v>1.5496836705937172E-2</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.3871811639746904E-2</v>
+        <v>1.3794098409272133E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18745,7 +18745,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-14.2</v>
+        <v>-14.28</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18985,7 +18985,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>14.2</v>
+        <v>14.28</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19583,7 +19583,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>14.2</v>
+        <v>14.28</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19596,7 +19596,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>-7.4610007703045822E-2</v>
+        <v>-7.6391321062616813E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/300481.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/300481.SZ_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E94B4D18-03D5-483E-8ED4-A589CE6E1930}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E8A7BB2-10DD-42AE-A319-A0180918EAD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3893,29 +3893,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4333,7 +4333,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>14.28</v>
+        <v>14.25</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>4167.6956546399997</v>
+        <v>4158.9399915000004</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4391,13 +4391,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="360" t="s">
+      <c r="B18" s="358" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="360"/>
-      <c r="D18" s="360"/>
-      <c r="E18" s="360"/>
-      <c r="F18" s="360"/>
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4480,7 +4480,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>-7.6391321062616813E-2</v>
+        <v>-7.5724920811838015E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4597,22 +4597,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="360" t="s">
+      <c r="B36" s="358" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="360"/>
-      <c r="D36" s="360"/>
-      <c r="E36" s="360"/>
-      <c r="F36" s="360"/>
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="363" t="s">
+      <c r="B37" s="360" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="363"/>
-      <c r="D37" s="363"/>
-      <c r="E37" s="363"/>
-      <c r="F37" s="363"/>
+      <c r="C37" s="360"/>
+      <c r="D37" s="360"/>
+      <c r="E37" s="360"/>
+      <c r="F37" s="360"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4624,13 +4624,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="361" t="s">
+      <c r="B40" s="359" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="361"/>
-      <c r="D40" s="361"/>
-      <c r="E40" s="361"/>
-      <c r="F40" s="361"/>
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4650,13 +4650,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="361" t="s">
+      <c r="B43" s="359" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="361"/>
-      <c r="D43" s="361"/>
-      <c r="E43" s="361"/>
-      <c r="F43" s="361"/>
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4685,13 +4685,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="361" t="s">
+      <c r="B47" s="359" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="361"/>
-      <c r="D47" s="361"/>
-      <c r="E47" s="361"/>
-      <c r="F47" s="361"/>
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4707,13 +4707,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="361" t="s">
+      <c r="B50" s="359" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="361"/>
-      <c r="D50" s="361"/>
-      <c r="E50" s="361"/>
-      <c r="F50" s="361"/>
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4777,13 +4777,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="361" t="s">
+      <c r="B58" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="361"/>
-      <c r="D58" s="361"/>
-      <c r="E58" s="361"/>
-      <c r="F58" s="361"/>
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4799,7 +4799,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="361" t="s">
+      <c r="B61" s="359" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4821,22 +4821,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="360" t="s">
+      <c r="B64" s="358" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="360"/>
-      <c r="D64" s="360"/>
-      <c r="E64" s="360"/>
-      <c r="F64" s="360"/>
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="360" t="s">
+      <c r="B65" s="358" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="360"/>
-      <c r="D65" s="360"/>
-      <c r="E65" s="360"/>
-      <c r="F65" s="360"/>
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4870,7 +4870,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>3.1067238790720722E-2</v>
+        <v>3.1132643503964344E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>2.5210084033613449E-2</v>
+        <v>2.5263157894736845E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>445</v>
@@ -4971,22 +4971,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="360" t="s">
+      <c r="B80" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="360"/>
-      <c r="D80" s="360"/>
-      <c r="E80" s="360"/>
-      <c r="F80" s="360"/>
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="363" t="s">
+      <c r="B81" s="360" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="363"/>
-      <c r="D81" s="363"/>
-      <c r="E81" s="363"/>
-      <c r="F81" s="363"/>
+      <c r="C81" s="360"/>
+      <c r="D81" s="360"/>
+      <c r="E81" s="360"/>
+      <c r="F81" s="360"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5030,22 +5030,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="360" t="s">
+      <c r="B89" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="360"/>
-      <c r="D89" s="360"/>
-      <c r="E89" s="360"/>
-      <c r="F89" s="360"/>
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="360" t="s">
+      <c r="B90" s="358" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="360"/>
-      <c r="D90" s="360"/>
-      <c r="E90" s="360"/>
-      <c r="F90" s="360"/>
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5082,13 +5082,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="360" t="s">
+      <c r="B97" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="360"/>
-      <c r="D97" s="360"/>
-      <c r="E97" s="360"/>
-      <c r="F97" s="360"/>
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5101,13 +5101,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="360" t="s">
+      <c r="B101" s="358" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="360"/>
-      <c r="D101" s="360"/>
-      <c r="E101" s="360"/>
-      <c r="F101" s="360"/>
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5229,13 +5229,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="360" t="s">
+      <c r="B116" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="360"/>
-      <c r="D116" s="360"/>
-      <c r="E116" s="360"/>
-      <c r="F116" s="360"/>
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5274,13 +5274,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="361" t="s">
+      <c r="B123" s="359" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="361"/>
-      <c r="D123" s="361"/>
-      <c r="E123" s="361"/>
-      <c r="F123" s="361"/>
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5423,13 +5423,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="364" t="s">
+      <c r="B134" s="363" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="364"/>
-      <c r="D134" s="364"/>
-      <c r="E134" s="364"/>
-      <c r="F134" s="364"/>
+      <c r="C134" s="363"/>
+      <c r="D134" s="363"/>
+      <c r="E134" s="363"/>
+      <c r="F134" s="363"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5442,22 +5442,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="365" t="s">
+      <c r="B138" s="361" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="365"/>
-      <c r="D138" s="365"/>
-      <c r="E138" s="365"/>
-      <c r="F138" s="365"/>
+      <c r="C138" s="361"/>
+      <c r="D138" s="361"/>
+      <c r="E138" s="361"/>
+      <c r="F138" s="361"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="360" t="s">
+      <c r="B139" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="360"/>
-      <c r="D139" s="360"/>
-      <c r="E139" s="360"/>
-      <c r="F139" s="360"/>
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5790,13 +5790,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="359" t="s">
+      <c r="B179" s="365" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="360"/>
-      <c r="D179" s="360"/>
-      <c r="E179" s="360"/>
-      <c r="F179" s="360"/>
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5833,13 +5833,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="361" t="s">
+      <c r="B188" s="359" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="361"/>
-      <c r="D188" s="361"/>
-      <c r="E188" s="361"/>
-      <c r="F188" s="361"/>
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5847,22 +5847,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="358" t="s">
+      <c r="B191" s="364" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="358"/>
-      <c r="D191" s="358"/>
-      <c r="E191" s="358"/>
-      <c r="F191" s="358"/>
+      <c r="C191" s="364"/>
+      <c r="D191" s="364"/>
+      <c r="E191" s="364"/>
+      <c r="F191" s="364"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="358" t="s">
+      <c r="B192" s="364" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="358"/>
-      <c r="D192" s="358"/>
-      <c r="E192" s="358"/>
-      <c r="F192" s="358"/>
+      <c r="C192" s="364"/>
+      <c r="D192" s="364"/>
+      <c r="E192" s="364"/>
+      <c r="F192" s="364"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5886,6 +5886,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5902,17 +5913,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13503,32 +13503,32 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>2.5210084033613449E-2</v>
+        <v>2.5263157894736845E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>2.5210084033613449E-2</v>
+        <v>2.5263157894736845E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>2.5210084033613449E-2</v>
+        <v>2.5263157894736845E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>2.5210084033613449E-2</v>
+        <v>2.5263157894736845E-2</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
-        <v>2.5210084033613449E-2</v>
+        <v>2.5263157894736845E-2</v>
       </c>
       <c r="K94" s="23">
         <f t="shared" si="39"/>
-        <v>1.2605042016806725E-2</v>
+        <v>1.2631578947368423E-2</v>
       </c>
       <c r="L94" s="23">
         <f t="shared" si="39"/>
-        <v>1.2605042016806725E-2</v>
+        <v>1.2631578947368423E-2</v>
       </c>
       <c r="M94" s="23">
         <f t="shared" si="39"/>
@@ -14702,50 +14702,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>3.1067238790720722E-2</v>
+        <v>3.1132643503964344E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>3.5400990160989208E-2</v>
+        <v>3.5475518561328134E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>4.6553078882945985E-2</v>
+        <v>4.665108536480482E-2</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>9.1563387607685745E-2</v>
+        <v>9.1756152634228233E-2</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>5.9293340813512549E-2</v>
+        <v>5.9418168899435735E-2</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>4.4339401490841542E-2</v>
+        <v>4.4432747599243309E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>3.683614571089356E-2</v>
+        <v>3.6913695491337543E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>2.5975454594226323E-2</v>
+        <v>2.6030139761793115E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>2.3613103056226097E-2</v>
+        <v>2.3662814852133941E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>1.5622692584932566E-2</v>
+        <v>1.5655582464058741E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>1.5275609899470747E-2</v>
+        <v>1.5307769078206475E-2</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14759,43 +14759,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.5955895024811767E-2</v>
+        <v>4.6052644277495579E-2</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.6405051731231996E-2</v>
+        <v>5.6523799208560904E-2</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10130342399881145</v>
+        <v>0.10151669436512474</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.055854263710652E-2</v>
+        <v>6.0686034305816212E-2</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.2865716646344622E-2</v>
+        <v>4.2955960260336927E-2</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.4724338337632471E-2</v>
+        <v>3.4797442207816956E-2</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.5372855592819009E-2</v>
+        <v>2.5426272130909155E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.7661108223690099E-2</v>
+        <v>1.7698289504161028E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.5496836705937172E-2</v>
+        <v>1.5529461625318092E-2</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.3794098409272133E-2</v>
+        <v>1.3823138616449546E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18745,7 +18745,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-14.28</v>
+        <v>-14.25</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18985,7 +18985,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>14.28</v>
+        <v>14.25</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19583,7 +19583,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>14.28</v>
+        <v>14.25</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19596,7 +19596,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>-7.6391321062616813E-2</v>
+        <v>-7.5724920811838015E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/300481.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/300481.SZ_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E8A7BB2-10DD-42AE-A319-A0180918EAD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0237EBA8-89AD-4703-944F-E138FEDBD616}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3893,29 +3893,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4333,7 +4333,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>14.25</v>
+        <v>14.38</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>4158.9399915000004</v>
+        <v>4196.8811984399999</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4391,13 +4391,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="358" t="s">
+      <c r="B18" s="360" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+      <c r="C18" s="360"/>
+      <c r="D18" s="360"/>
+      <c r="E18" s="360"/>
+      <c r="F18" s="360"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4480,7 +4480,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>-7.5724920811838015E-2</v>
+        <v>-7.859899226480771E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4597,22 +4597,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="358" t="s">
+      <c r="B36" s="360" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
+      <c r="C36" s="360"/>
+      <c r="D36" s="360"/>
+      <c r="E36" s="360"/>
+      <c r="F36" s="360"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="360" t="s">
+      <c r="B37" s="363" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="360"/>
-      <c r="D37" s="360"/>
-      <c r="E37" s="360"/>
-      <c r="F37" s="360"/>
+      <c r="C37" s="363"/>
+      <c r="D37" s="363"/>
+      <c r="E37" s="363"/>
+      <c r="F37" s="363"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4624,13 +4624,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="359" t="s">
+      <c r="B40" s="361" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+      <c r="C40" s="361"/>
+      <c r="D40" s="361"/>
+      <c r="E40" s="361"/>
+      <c r="F40" s="361"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4650,13 +4650,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="359" t="s">
+      <c r="B43" s="361" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+      <c r="C43" s="361"/>
+      <c r="D43" s="361"/>
+      <c r="E43" s="361"/>
+      <c r="F43" s="361"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4685,13 +4685,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+      <c r="B47" s="361" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="C47" s="361"/>
+      <c r="D47" s="361"/>
+      <c r="E47" s="361"/>
+      <c r="F47" s="361"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4707,13 +4707,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+      <c r="B50" s="361" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="C50" s="361"/>
+      <c r="D50" s="361"/>
+      <c r="E50" s="361"/>
+      <c r="F50" s="361"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4777,13 +4777,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+      <c r="B58" s="361" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="C58" s="361"/>
+      <c r="D58" s="361"/>
+      <c r="E58" s="361"/>
+      <c r="F58" s="361"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4799,7 +4799,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+      <c r="B61" s="361" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4821,22 +4821,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="358" t="s">
+      <c r="B64" s="360" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
+      <c r="C64" s="360"/>
+      <c r="D64" s="360"/>
+      <c r="E64" s="360"/>
+      <c r="F64" s="360"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="B65" s="360" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+      <c r="C65" s="360"/>
+      <c r="D65" s="360"/>
+      <c r="E65" s="360"/>
+      <c r="F65" s="360"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4870,7 +4870,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>3.1132643503964344E-2</v>
+        <v>3.0851194014707366E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>2.5263157894736845E-2</v>
+        <v>2.5034770514603618E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>445</v>
@@ -4971,22 +4971,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="360" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="C80" s="360"/>
+      <c r="D80" s="360"/>
+      <c r="E80" s="360"/>
+      <c r="F80" s="360"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="360" t="s">
+      <c r="B81" s="363" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="360"/>
-      <c r="D81" s="360"/>
-      <c r="E81" s="360"/>
-      <c r="F81" s="360"/>
+      <c r="C81" s="363"/>
+      <c r="D81" s="363"/>
+      <c r="E81" s="363"/>
+      <c r="F81" s="363"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5030,22 +5030,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="358" t="s">
+      <c r="B89" s="360" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
+      <c r="C89" s="360"/>
+      <c r="D89" s="360"/>
+      <c r="E89" s="360"/>
+      <c r="F89" s="360"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="B90" s="360" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+      <c r="C90" s="360"/>
+      <c r="D90" s="360"/>
+      <c r="E90" s="360"/>
+      <c r="F90" s="360"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5082,13 +5082,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+      <c r="B97" s="360" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="C97" s="360"/>
+      <c r="D97" s="360"/>
+      <c r="E97" s="360"/>
+      <c r="F97" s="360"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5101,13 +5101,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="358" t="s">
+      <c r="B101" s="360" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+      <c r="C101" s="360"/>
+      <c r="D101" s="360"/>
+      <c r="E101" s="360"/>
+      <c r="F101" s="360"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5229,13 +5229,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="358" t="s">
+      <c r="B116" s="360" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+      <c r="C116" s="360"/>
+      <c r="D116" s="360"/>
+      <c r="E116" s="360"/>
+      <c r="F116" s="360"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5274,13 +5274,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="359" t="s">
+      <c r="B123" s="361" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+      <c r="C123" s="361"/>
+      <c r="D123" s="361"/>
+      <c r="E123" s="361"/>
+      <c r="F123" s="361"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5423,13 +5423,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="363" t="s">
+      <c r="B134" s="364" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="363"/>
-      <c r="D134" s="363"/>
-      <c r="E134" s="363"/>
-      <c r="F134" s="363"/>
+      <c r="C134" s="364"/>
+      <c r="D134" s="364"/>
+      <c r="E134" s="364"/>
+      <c r="F134" s="364"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5442,22 +5442,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="361" t="s">
+      <c r="B138" s="365" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="361"/>
-      <c r="D138" s="361"/>
-      <c r="E138" s="361"/>
-      <c r="F138" s="361"/>
+      <c r="C138" s="365"/>
+      <c r="D138" s="365"/>
+      <c r="E138" s="365"/>
+      <c r="F138" s="365"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="B139" s="360" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="C139" s="360"/>
+      <c r="D139" s="360"/>
+      <c r="E139" s="360"/>
+      <c r="F139" s="360"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5790,13 +5790,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="365" t="s">
+      <c r="B179" s="359" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="C179" s="360"/>
+      <c r="D179" s="360"/>
+      <c r="E179" s="360"/>
+      <c r="F179" s="360"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5833,13 +5833,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+      <c r="B188" s="361" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="C188" s="361"/>
+      <c r="D188" s="361"/>
+      <c r="E188" s="361"/>
+      <c r="F188" s="361"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5847,22 +5847,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="364" t="s">
+      <c r="B191" s="358" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="364"/>
-      <c r="D191" s="364"/>
-      <c r="E191" s="364"/>
-      <c r="F191" s="364"/>
+      <c r="C191" s="358"/>
+      <c r="D191" s="358"/>
+      <c r="E191" s="358"/>
+      <c r="F191" s="358"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="364" t="s">
+      <c r="B192" s="358" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="364"/>
-      <c r="D192" s="364"/>
-      <c r="E192" s="364"/>
-      <c r="F192" s="364"/>
+      <c r="C192" s="358"/>
+      <c r="D192" s="358"/>
+      <c r="E192" s="358"/>
+      <c r="F192" s="358"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5886,17 +5886,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5913,6 +5902,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13503,32 +13503,32 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>2.5263157894736845E-2</v>
+        <v>2.5034770514603618E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>2.5263157894736845E-2</v>
+        <v>2.5034770514603618E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>2.5263157894736845E-2</v>
+        <v>2.5034770514603618E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>2.5263157894736845E-2</v>
+        <v>2.5034770514603618E-2</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
-        <v>2.5263157894736845E-2</v>
+        <v>2.5034770514603618E-2</v>
       </c>
       <c r="K94" s="23">
         <f t="shared" si="39"/>
-        <v>1.2631578947368423E-2</v>
+        <v>1.2517385257301809E-2</v>
       </c>
       <c r="L94" s="23">
         <f t="shared" si="39"/>
-        <v>1.2631578947368423E-2</v>
+        <v>1.2517385257301809E-2</v>
       </c>
       <c r="M94" s="23">
         <f t="shared" si="39"/>
@@ -14702,50 +14702,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>3.1132643503964344E-2</v>
+        <v>3.0851194014707366E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>3.5475518561328134E-2</v>
+        <v>3.5154808031914175E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>4.665108536480482E-2</v>
+        <v>4.6229343981117429E-2</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>9.1756152634228233E-2</v>
+        <v>9.0926646386491811E-2</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>5.9418168899435735E-2</v>
+        <v>5.888100881898186E-2</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>4.4432747599243309E-2</v>
+        <v>4.4031060729430957E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>3.6913695491337543E-2</v>
+        <v>3.6579983362417245E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>2.6030139761793115E-2</v>
+        <v>2.5794818609565499E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>2.3662814852133941E-2</v>
+        <v>2.3448895107295455E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>1.5655582464058741E-2</v>
+        <v>1.5514050772798124E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>1.5307769078206475E-2</v>
+        <v>1.5169381736053008E-2</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14759,43 +14759,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.6052644277495579E-2</v>
+        <v>4.5636313000995271E-2</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.6523799208560904E-2</v>
+        <v>5.601280519624429E-2</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10151669436512474</v>
+        <v>0.10059894956210205</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.0686034305816212E-2</v>
+        <v>6.0137412298879075E-2</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.2955960260336927E-2</v>
+        <v>4.2567624041015384E-2</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.4797442207816956E-2</v>
+        <v>3.4482861714978559E-2</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.5426272130909155E-2</v>
+        <v>2.5196410143633895E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.7698289504161028E-2</v>
+        <v>1.7538291059408528E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.5529461625318092E-2</v>
+        <v>1.5389070108538442E-2</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.3823138616449546E-2</v>
+        <v>1.3698172829235468E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18745,7 +18745,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-14.25</v>
+        <v>-14.38</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18985,7 +18985,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>14.25</v>
+        <v>14.38</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19583,7 +19583,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>14.25</v>
+        <v>14.38</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19596,7 +19596,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>-7.5724920811838015E-2</v>
+        <v>-7.859899226480771E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/300481.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/300481.SZ_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0237EBA8-89AD-4703-944F-E138FEDBD616}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22EA130F-D6B1-488A-9B6D-2EC52F5AAC40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3893,29 +3893,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4333,7 +4333,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>14.38</v>
+        <v>14.5</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>4196.8811984399999</v>
+        <v>4231.903851</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4391,13 +4391,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="360" t="s">
+      <c r="B18" s="358" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="360"/>
-      <c r="D18" s="360"/>
-      <c r="E18" s="360"/>
-      <c r="F18" s="360"/>
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4480,7 +4480,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>-7.859899226480771E-2</v>
+        <v>-8.1220829943830841E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4597,22 +4597,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="360" t="s">
+      <c r="B36" s="358" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="360"/>
-      <c r="D36" s="360"/>
-      <c r="E36" s="360"/>
-      <c r="F36" s="360"/>
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="363" t="s">
+      <c r="B37" s="360" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="363"/>
-      <c r="D37" s="363"/>
-      <c r="E37" s="363"/>
-      <c r="F37" s="363"/>
+      <c r="C37" s="360"/>
+      <c r="D37" s="360"/>
+      <c r="E37" s="360"/>
+      <c r="F37" s="360"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4624,13 +4624,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="361" t="s">
+      <c r="B40" s="359" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="361"/>
-      <c r="D40" s="361"/>
-      <c r="E40" s="361"/>
-      <c r="F40" s="361"/>
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4650,13 +4650,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="361" t="s">
+      <c r="B43" s="359" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="361"/>
-      <c r="D43" s="361"/>
-      <c r="E43" s="361"/>
-      <c r="F43" s="361"/>
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4685,13 +4685,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="361" t="s">
+      <c r="B47" s="359" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="361"/>
-      <c r="D47" s="361"/>
-      <c r="E47" s="361"/>
-      <c r="F47" s="361"/>
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4707,13 +4707,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="361" t="s">
+      <c r="B50" s="359" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="361"/>
-      <c r="D50" s="361"/>
-      <c r="E50" s="361"/>
-      <c r="F50" s="361"/>
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4777,13 +4777,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="361" t="s">
+      <c r="B58" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="361"/>
-      <c r="D58" s="361"/>
-      <c r="E58" s="361"/>
-      <c r="F58" s="361"/>
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4799,7 +4799,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="361" t="s">
+      <c r="B61" s="359" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4821,22 +4821,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="360" t="s">
+      <c r="B64" s="358" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="360"/>
-      <c r="D64" s="360"/>
-      <c r="E64" s="360"/>
-      <c r="F64" s="360"/>
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="360" t="s">
+      <c r="B65" s="358" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="360"/>
-      <c r="D65" s="360"/>
-      <c r="E65" s="360"/>
-      <c r="F65" s="360"/>
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4870,7 +4870,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>3.0851194014707366E-2</v>
+        <v>3.0595873788378754E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>2.5034770514603618E-2</v>
+        <v>2.4827586206896554E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>445</v>
@@ -4971,22 +4971,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="360" t="s">
+      <c r="B80" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="360"/>
-      <c r="D80" s="360"/>
-      <c r="E80" s="360"/>
-      <c r="F80" s="360"/>
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="363" t="s">
+      <c r="B81" s="360" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="363"/>
-      <c r="D81" s="363"/>
-      <c r="E81" s="363"/>
-      <c r="F81" s="363"/>
+      <c r="C81" s="360"/>
+      <c r="D81" s="360"/>
+      <c r="E81" s="360"/>
+      <c r="F81" s="360"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5030,22 +5030,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="360" t="s">
+      <c r="B89" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="360"/>
-      <c r="D89" s="360"/>
-      <c r="E89" s="360"/>
-      <c r="F89" s="360"/>
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="360" t="s">
+      <c r="B90" s="358" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="360"/>
-      <c r="D90" s="360"/>
-      <c r="E90" s="360"/>
-      <c r="F90" s="360"/>
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5082,13 +5082,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="360" t="s">
+      <c r="B97" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="360"/>
-      <c r="D97" s="360"/>
-      <c r="E97" s="360"/>
-      <c r="F97" s="360"/>
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5101,13 +5101,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="360" t="s">
+      <c r="B101" s="358" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="360"/>
-      <c r="D101" s="360"/>
-      <c r="E101" s="360"/>
-      <c r="F101" s="360"/>
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5229,13 +5229,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="360" t="s">
+      <c r="B116" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="360"/>
-      <c r="D116" s="360"/>
-      <c r="E116" s="360"/>
-      <c r="F116" s="360"/>
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5274,13 +5274,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="361" t="s">
+      <c r="B123" s="359" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="361"/>
-      <c r="D123" s="361"/>
-      <c r="E123" s="361"/>
-      <c r="F123" s="361"/>
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5423,13 +5423,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="364" t="s">
+      <c r="B134" s="363" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="364"/>
-      <c r="D134" s="364"/>
-      <c r="E134" s="364"/>
-      <c r="F134" s="364"/>
+      <c r="C134" s="363"/>
+      <c r="D134" s="363"/>
+      <c r="E134" s="363"/>
+      <c r="F134" s="363"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5442,22 +5442,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="365" t="s">
+      <c r="B138" s="361" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="365"/>
-      <c r="D138" s="365"/>
-      <c r="E138" s="365"/>
-      <c r="F138" s="365"/>
+      <c r="C138" s="361"/>
+      <c r="D138" s="361"/>
+      <c r="E138" s="361"/>
+      <c r="F138" s="361"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="360" t="s">
+      <c r="B139" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="360"/>
-      <c r="D139" s="360"/>
-      <c r="E139" s="360"/>
-      <c r="F139" s="360"/>
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5790,13 +5790,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="359" t="s">
+      <c r="B179" s="365" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="360"/>
-      <c r="D179" s="360"/>
-      <c r="E179" s="360"/>
-      <c r="F179" s="360"/>
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5833,13 +5833,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="361" t="s">
+      <c r="B188" s="359" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="361"/>
-      <c r="D188" s="361"/>
-      <c r="E188" s="361"/>
-      <c r="F188" s="361"/>
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5847,22 +5847,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="358" t="s">
+      <c r="B191" s="364" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="358"/>
-      <c r="D191" s="358"/>
-      <c r="E191" s="358"/>
-      <c r="F191" s="358"/>
+      <c r="C191" s="364"/>
+      <c r="D191" s="364"/>
+      <c r="E191" s="364"/>
+      <c r="F191" s="364"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="358" t="s">
+      <c r="B192" s="364" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="358"/>
-      <c r="D192" s="358"/>
-      <c r="E192" s="358"/>
-      <c r="F192" s="358"/>
+      <c r="C192" s="364"/>
+      <c r="D192" s="364"/>
+      <c r="E192" s="364"/>
+      <c r="F192" s="364"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5886,6 +5886,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5902,17 +5913,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13503,32 +13503,32 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>2.5034770514603618E-2</v>
+        <v>2.4827586206896554E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>2.5034770514603618E-2</v>
+        <v>2.4827586206896554E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>2.5034770514603618E-2</v>
+        <v>2.4827586206896554E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>2.5034770514603618E-2</v>
+        <v>2.4827586206896554E-2</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
-        <v>2.5034770514603618E-2</v>
+        <v>2.4827586206896554E-2</v>
       </c>
       <c r="K94" s="23">
         <f t="shared" si="39"/>
-        <v>1.2517385257301809E-2</v>
+        <v>1.2413793103448277E-2</v>
       </c>
       <c r="L94" s="23">
         <f t="shared" si="39"/>
-        <v>1.2517385257301809E-2</v>
+        <v>1.2413793103448277E-2</v>
       </c>
       <c r="M94" s="23">
         <f t="shared" si="39"/>
@@ -14702,50 +14702,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>3.0851194014707366E-2</v>
+        <v>3.0595873788378754E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>3.5154808031914175E-2</v>
+        <v>3.4863871689581098E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>4.6229343981117429E-2</v>
+        <v>4.5846756306790942E-2</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>9.0926646386491811E-2</v>
+        <v>9.0174150002603606E-2</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>5.888100881898186E-2</v>
+        <v>5.8393717711514428E-2</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>4.4031060729430957E-2</v>
+        <v>4.3666665744083941E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>3.6579983362417245E-2</v>
+        <v>3.6277252465624826E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>2.5794818609565499E-2</v>
+        <v>2.5581344248658752E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>2.3448895107295455E-2</v>
+        <v>2.325483528571784E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>1.5514050772798124E-2</v>
+        <v>1.538565862847152E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>1.5169381736053008E-2</v>
+        <v>1.5043842025133949E-2</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14759,43 +14759,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.5636313000995271E-2</v>
+        <v>4.5258633169262902E-2</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.601280519624429E-2</v>
+        <v>5.5549250946344338E-2</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10059894956210205</v>
+        <v>9.9766406531243287E-2</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.0137412298879075E-2</v>
+        <v>5.963972336950904E-2</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.2567624041015384E-2</v>
+        <v>4.221534025584836E-2</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.4482861714978559E-2</v>
+        <v>3.4197486307682184E-2</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.5196410143633895E-2</v>
+        <v>2.4987888128652099E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.7538291059408528E-2</v>
+        <v>1.7393146581675491E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.5389070108538442E-2</v>
+        <v>1.5261712286950538E-2</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.3698172829235468E-2</v>
+        <v>1.3584808640303866E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18745,7 +18745,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-14.38</v>
+        <v>-14.5</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18985,7 +18985,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>14.38</v>
+        <v>14.5</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19583,7 +19583,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>14.38</v>
+        <v>14.5</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19596,7 +19596,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>-7.859899226480771E-2</v>
+        <v>-8.1220829943830841E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/300481.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/300481.SZ_Valuation.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22EA130F-D6B1-488A-9B6D-2EC52F5AAC40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0937ACAA-3DA4-40E2-8191-786DF3994DD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3893,29 +3893,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4333,7 +4333,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>14.5</v>
+        <v>14.25</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>4231.903851</v>
+        <v>4158.9399915000004</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4391,13 +4391,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="358" t="s">
+      <c r="B18" s="360" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+      <c r="C18" s="360"/>
+      <c r="D18" s="360"/>
+      <c r="E18" s="360"/>
+      <c r="F18" s="360"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4480,7 +4480,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>-8.1220829943830841E-2</v>
+        <v>-7.5724920811838015E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4512,7 +4512,7 @@
       </c>
       <c r="C29" s="310">
         <f>C149</f>
-        <v>4.9106169541815241</v>
+        <v>4.777129606353653</v>
       </c>
       <c r="D29" s="310" t="str">
         <f>D149</f>
@@ -4522,7 +4522,7 @@
         <v>421</v>
       </c>
       <c r="F29" s="302">
-        <v>0.33699999999999997</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="30" spans="2:6">
@@ -4531,7 +4531,7 @@
       </c>
       <c r="C30" s="311">
         <f>C157</f>
-        <v>6.9036475281066911</v>
+        <v>5.951452290678974</v>
       </c>
       <c r="D30" s="311" t="str">
         <f>D157</f>
@@ -4541,7 +4541,7 @@
         <v>434</v>
       </c>
       <c r="F30" s="312">
-        <v>0.187</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="31" spans="2:6">
@@ -4597,22 +4597,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="358" t="s">
+      <c r="B36" s="360" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
+      <c r="C36" s="360"/>
+      <c r="D36" s="360"/>
+      <c r="E36" s="360"/>
+      <c r="F36" s="360"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="360" t="s">
+      <c r="B37" s="363" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="360"/>
-      <c r="D37" s="360"/>
-      <c r="E37" s="360"/>
-      <c r="F37" s="360"/>
+      <c r="C37" s="363"/>
+      <c r="D37" s="363"/>
+      <c r="E37" s="363"/>
+      <c r="F37" s="363"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4624,13 +4624,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="359" t="s">
+      <c r="B40" s="361" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+      <c r="C40" s="361"/>
+      <c r="D40" s="361"/>
+      <c r="E40" s="361"/>
+      <c r="F40" s="361"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4650,13 +4650,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="359" t="s">
+      <c r="B43" s="361" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+      <c r="C43" s="361"/>
+      <c r="D43" s="361"/>
+      <c r="E43" s="361"/>
+      <c r="F43" s="361"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4685,13 +4685,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+      <c r="B47" s="361" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="C47" s="361"/>
+      <c r="D47" s="361"/>
+      <c r="E47" s="361"/>
+      <c r="F47" s="361"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4707,13 +4707,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+      <c r="B50" s="361" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="C50" s="361"/>
+      <c r="D50" s="361"/>
+      <c r="E50" s="361"/>
+      <c r="F50" s="361"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4777,13 +4777,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+      <c r="B58" s="361" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="C58" s="361"/>
+      <c r="D58" s="361"/>
+      <c r="E58" s="361"/>
+      <c r="F58" s="361"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4799,7 +4799,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+      <c r="B61" s="361" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4821,22 +4821,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="358" t="s">
+      <c r="B64" s="360" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
+      <c r="C64" s="360"/>
+      <c r="D64" s="360"/>
+      <c r="E64" s="360"/>
+      <c r="F64" s="360"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="B65" s="360" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+      <c r="C65" s="360"/>
+      <c r="D65" s="360"/>
+      <c r="E65" s="360"/>
+      <c r="F65" s="360"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4870,7 +4870,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>3.0595873788378754E-2</v>
+        <v>3.1132643503964344E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>2.4827586206896554E-2</v>
+        <v>2.5263157894736845E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>445</v>
@@ -4971,22 +4971,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="360" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="C80" s="360"/>
+      <c r="D80" s="360"/>
+      <c r="E80" s="360"/>
+      <c r="F80" s="360"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="360" t="s">
+      <c r="B81" s="363" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="360"/>
-      <c r="D81" s="360"/>
-      <c r="E81" s="360"/>
-      <c r="F81" s="360"/>
+      <c r="C81" s="363"/>
+      <c r="D81" s="363"/>
+      <c r="E81" s="363"/>
+      <c r="F81" s="363"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5030,22 +5030,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="358" t="s">
+      <c r="B89" s="360" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
+      <c r="C89" s="360"/>
+      <c r="D89" s="360"/>
+      <c r="E89" s="360"/>
+      <c r="F89" s="360"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="B90" s="360" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+      <c r="C90" s="360"/>
+      <c r="D90" s="360"/>
+      <c r="E90" s="360"/>
+      <c r="F90" s="360"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5082,13 +5082,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+      <c r="B97" s="360" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="C97" s="360"/>
+      <c r="D97" s="360"/>
+      <c r="E97" s="360"/>
+      <c r="F97" s="360"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5101,13 +5101,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="358" t="s">
+      <c r="B101" s="360" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+      <c r="C101" s="360"/>
+      <c r="D101" s="360"/>
+      <c r="E101" s="360"/>
+      <c r="F101" s="360"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5229,13 +5229,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="358" t="s">
+      <c r="B116" s="360" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+      <c r="C116" s="360"/>
+      <c r="D116" s="360"/>
+      <c r="E116" s="360"/>
+      <c r="F116" s="360"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5274,13 +5274,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="359" t="s">
+      <c r="B123" s="361" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+      <c r="C123" s="361"/>
+      <c r="D123" s="361"/>
+      <c r="E123" s="361"/>
+      <c r="F123" s="361"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5423,13 +5423,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="363" t="s">
+      <c r="B134" s="364" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="363"/>
-      <c r="D134" s="363"/>
-      <c r="E134" s="363"/>
-      <c r="F134" s="363"/>
+      <c r="C134" s="364"/>
+      <c r="D134" s="364"/>
+      <c r="E134" s="364"/>
+      <c r="F134" s="364"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5442,22 +5442,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="361" t="s">
+      <c r="B138" s="365" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="361"/>
-      <c r="D138" s="361"/>
-      <c r="E138" s="361"/>
-      <c r="F138" s="361"/>
+      <c r="C138" s="365"/>
+      <c r="D138" s="365"/>
+      <c r="E138" s="365"/>
+      <c r="F138" s="365"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="B139" s="360" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="C139" s="360"/>
+      <c r="D139" s="360"/>
+      <c r="E139" s="360"/>
+      <c r="F139" s="360"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5479,7 +5479,7 @@
       </c>
       <c r="C142" s="224">
         <f>F29</f>
-        <v>0.33699999999999997</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -5514,7 +5514,7 @@
       </c>
       <c r="C146" s="297">
         <f>F29</f>
-        <v>0.33699999999999997</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="147" spans="2:4">
@@ -5524,7 +5524,7 @@
       </c>
       <c r="C147" s="216">
         <f>Scenarios!C81</f>
-        <v>0.62127925482890078</v>
+        <v>0.61051668952903537</v>
       </c>
     </row>
     <row r="148" spans="2:4">
@@ -5534,7 +5534,7 @@
       </c>
       <c r="C148" s="216">
         <f>Scenarios!C82</f>
-        <v>4.2893376993526235</v>
+        <v>4.1666129168246178</v>
       </c>
     </row>
     <row r="149" spans="2:4">
@@ -5543,7 +5543,7 @@
       </c>
       <c r="C149" s="215">
         <f>Scenarios!C83</f>
-        <v>4.9106169541815241</v>
+        <v>4.777129606353653</v>
       </c>
       <c r="D149" s="300" t="str">
         <f>IF($D$11="","",C149*$E$25)</f>
@@ -5569,7 +5569,7 @@
       </c>
       <c r="C151" s="92">
         <f>Scenarios!F83</f>
-        <v>0.52098225984855873</v>
+        <v>0.53400359877438697</v>
       </c>
     </row>
     <row r="153" spans="2:4">
@@ -5583,7 +5583,7 @@
       </c>
       <c r="C154" s="297">
         <f>Scenarios!C90</f>
-        <v>0.187</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="155" spans="2:4">
@@ -5593,7 +5593,7 @@
       </c>
       <c r="C155" s="216">
         <f>Scenarios!C91</f>
-        <v>0.77404513082565229</v>
+        <v>0.70272000000000001</v>
       </c>
     </row>
     <row r="156" spans="2:4">
@@ -5603,7 +5603,7 @@
       </c>
       <c r="C156" s="216">
         <f>Scenarios!C92</f>
-        <v>6.1296023972810385</v>
+        <v>5.2487322906789737</v>
       </c>
     </row>
     <row r="157" spans="2:4">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C157" s="215">
         <f>Scenarios!C93</f>
-        <v>6.9036475281066911</v>
+        <v>5.951452290678974</v>
       </c>
       <c r="D157" s="300" t="str">
         <f>IF($D$11="","",C157*$E$25)</f>
@@ -5638,7 +5638,7 @@
       </c>
       <c r="C159" s="92">
         <f>Scenarios!F93</f>
-        <v>0.32656738072396863</v>
+        <v>0.41945151627585542</v>
       </c>
     </row>
     <row r="161" spans="2:4">
@@ -5790,13 +5790,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="365" t="s">
+      <c r="B179" s="359" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="C179" s="360"/>
+      <c r="D179" s="360"/>
+      <c r="E179" s="360"/>
+      <c r="F179" s="360"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5833,13 +5833,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+      <c r="B188" s="361" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="C188" s="361"/>
+      <c r="D188" s="361"/>
+      <c r="E188" s="361"/>
+      <c r="F188" s="361"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5847,22 +5847,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="364" t="s">
+      <c r="B191" s="358" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="364"/>
-      <c r="D191" s="364"/>
-      <c r="E191" s="364"/>
-      <c r="F191" s="364"/>
+      <c r="C191" s="358"/>
+      <c r="D191" s="358"/>
+      <c r="E191" s="358"/>
+      <c r="F191" s="358"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="364" t="s">
+      <c r="B192" s="358" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="364"/>
-      <c r="D192" s="364"/>
-      <c r="E192" s="364"/>
-      <c r="F192" s="364"/>
+      <c r="C192" s="358"/>
+      <c r="D192" s="358"/>
+      <c r="E192" s="358"/>
+      <c r="F192" s="358"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5886,17 +5886,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5913,6 +5902,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13503,32 +13503,32 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>2.4827586206896554E-2</v>
+        <v>2.5263157894736845E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>2.4827586206896554E-2</v>
+        <v>2.5263157894736845E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>2.4827586206896554E-2</v>
+        <v>2.5263157894736845E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>2.4827586206896554E-2</v>
+        <v>2.5263157894736845E-2</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
-        <v>2.4827586206896554E-2</v>
+        <v>2.5263157894736845E-2</v>
       </c>
       <c r="K94" s="23">
         <f t="shared" si="39"/>
-        <v>1.2413793103448277E-2</v>
+        <v>1.2631578947368423E-2</v>
       </c>
       <c r="L94" s="23">
         <f t="shared" si="39"/>
-        <v>1.2413793103448277E-2</v>
+        <v>1.2631578947368423E-2</v>
       </c>
       <c r="M94" s="23">
         <f t="shared" si="39"/>
@@ -14702,50 +14702,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>3.0595873788378754E-2</v>
+        <v>3.1132643503964344E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>3.4863871689581098E-2</v>
+        <v>3.5475518561328134E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>4.5846756306790942E-2</v>
+        <v>4.665108536480482E-2</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>9.0174150002603606E-2</v>
+        <v>9.1756152634228233E-2</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>5.8393717711514428E-2</v>
+        <v>5.9418168899435735E-2</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>4.3666665744083941E-2</v>
+        <v>4.4432747599243309E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>3.6277252465624826E-2</v>
+        <v>3.6913695491337543E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>2.5581344248658752E-2</v>
+        <v>2.6030139761793115E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>2.325483528571784E-2</v>
+        <v>2.3662814852133941E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>1.538565862847152E-2</v>
+        <v>1.5655582464058741E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>1.5043842025133949E-2</v>
+        <v>1.5307769078206475E-2</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14759,43 +14759,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.5258633169262902E-2</v>
+        <v>4.6052644277495579E-2</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.5549250946344338E-2</v>
+        <v>5.6523799208560904E-2</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.9766406531243287E-2</v>
+        <v>0.10151669436512474</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.963972336950904E-2</v>
+        <v>6.0686034305816212E-2</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.221534025584836E-2</v>
+        <v>4.2955960260336927E-2</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.4197486307682184E-2</v>
+        <v>3.4797442207816956E-2</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.4987888128652099E-2</v>
+        <v>2.5426272130909155E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.7393146581675491E-2</v>
+        <v>1.7698289504161028E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.5261712286950538E-2</v>
+        <v>1.5529461625318092E-2</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.3584808640303866E-2</v>
+        <v>1.3823138616449546E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18745,7 +18745,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-14.5</v>
+        <v>-14.25</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18985,7 +18985,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>14.5</v>
+        <v>14.25</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19524,7 +19524,7 @@
       </c>
       <c r="C80" s="167">
         <f>Thesis!F29</f>
-        <v>0.33699999999999997</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="81" spans="2:8">
@@ -19533,7 +19533,7 @@
       </c>
       <c r="C81" s="116">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>0.62127925482890078</v>
+        <v>0.61051668952903537</v>
       </c>
       <c r="D81" s="116"/>
       <c r="E81" s="100"/>
@@ -19545,7 +19545,7 @@
       </c>
       <c r="C82" s="116">
         <f>C60/(1+C80)^C76</f>
-        <v>4.2893376993526235</v>
+        <v>4.1666129168246178</v>
       </c>
       <c r="D82" s="116"/>
     </row>
@@ -19555,7 +19555,7 @@
       </c>
       <c r="C83" s="111">
         <f>C81+C82</f>
-        <v>4.9106169541815241</v>
+        <v>4.777129606353653</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -19566,7 +19566,7 @@
       </c>
       <c r="F83" s="291">
         <f>(1-C83/C60)</f>
-        <v>0.52098225984855873</v>
+        <v>0.53400359877438697</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -19583,7 +19583,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>14.5</v>
+        <v>14.25</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19596,7 +19596,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>-8.1220829943830841E-2</v>
+        <v>-7.5724920811838015E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -19613,7 +19613,7 @@
       </c>
       <c r="C90" s="167">
         <f>Thesis!F30</f>
-        <v>0.187</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="91" spans="2:8">
@@ -19622,7 +19622,7 @@
       </c>
       <c r="C91" s="116">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>0.77404513082565229</v>
+        <v>0.70272000000000001</v>
       </c>
       <c r="D91" s="116"/>
       <c r="E91" s="100"/>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="C92" s="116">
         <f>C60/(1+C90)^C76</f>
-        <v>6.1296023972810385</v>
+        <v>5.2487322906789737</v>
       </c>
       <c r="D92" s="116"/>
     </row>
@@ -19644,7 +19644,7 @@
       </c>
       <c r="C93" s="111">
         <f>C91+C92</f>
-        <v>6.9036475281066911</v>
+        <v>5.951452290678974</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -19655,7 +19655,7 @@
       </c>
       <c r="F93" s="291">
         <f>(1-C93/C60)</f>
-        <v>0.32656738072396863</v>
+        <v>0.41945151627585542</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">

--- a/financial_models/opportunities/300481.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/300481.SZ_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0937ACAA-3DA4-40E2-8191-786DF3994DD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{870F0894-A9DB-4CE4-A3DC-4260A8EA3AE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3893,29 +3893,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4333,7 +4333,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>14.25</v>
+        <v>14.31</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>4158.9399915000004</v>
+        <v>4176.45131778</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4391,13 +4391,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="360" t="s">
+      <c r="B18" s="358" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="360"/>
-      <c r="D18" s="360"/>
-      <c r="E18" s="360"/>
-      <c r="F18" s="360"/>
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4480,7 +4480,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>-7.5724920811838015E-2</v>
+        <v>-7.7055822209717295E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4597,22 +4597,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="360" t="s">
+      <c r="B36" s="358" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="360"/>
-      <c r="D36" s="360"/>
-      <c r="E36" s="360"/>
-      <c r="F36" s="360"/>
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="363" t="s">
+      <c r="B37" s="360" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="363"/>
-      <c r="D37" s="363"/>
-      <c r="E37" s="363"/>
-      <c r="F37" s="363"/>
+      <c r="C37" s="360"/>
+      <c r="D37" s="360"/>
+      <c r="E37" s="360"/>
+      <c r="F37" s="360"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4624,13 +4624,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="361" t="s">
+      <c r="B40" s="359" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="361"/>
-      <c r="D40" s="361"/>
-      <c r="E40" s="361"/>
-      <c r="F40" s="361"/>
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4650,13 +4650,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="361" t="s">
+      <c r="B43" s="359" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="361"/>
-      <c r="D43" s="361"/>
-      <c r="E43" s="361"/>
-      <c r="F43" s="361"/>
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4685,13 +4685,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="361" t="s">
+      <c r="B47" s="359" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="361"/>
-      <c r="D47" s="361"/>
-      <c r="E47" s="361"/>
-      <c r="F47" s="361"/>
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4707,13 +4707,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="361" t="s">
+      <c r="B50" s="359" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="361"/>
-      <c r="D50" s="361"/>
-      <c r="E50" s="361"/>
-      <c r="F50" s="361"/>
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4777,13 +4777,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="361" t="s">
+      <c r="B58" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="361"/>
-      <c r="D58" s="361"/>
-      <c r="E58" s="361"/>
-      <c r="F58" s="361"/>
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4799,7 +4799,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="361" t="s">
+      <c r="B61" s="359" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4821,22 +4821,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="360" t="s">
+      <c r="B64" s="358" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="360"/>
-      <c r="D64" s="360"/>
-      <c r="E64" s="360"/>
-      <c r="F64" s="360"/>
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="360" t="s">
+      <c r="B65" s="358" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="360"/>
-      <c r="D65" s="360"/>
-      <c r="E65" s="360"/>
-      <c r="F65" s="360"/>
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4870,7 +4870,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>3.1132643503964344E-2</v>
+        <v>3.1002108311075603E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>2.5263157894736845E-2</v>
+        <v>2.5157232704402517E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>445</v>
@@ -4971,22 +4971,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="360" t="s">
+      <c r="B80" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="360"/>
-      <c r="D80" s="360"/>
-      <c r="E80" s="360"/>
-      <c r="F80" s="360"/>
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="363" t="s">
+      <c r="B81" s="360" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="363"/>
-      <c r="D81" s="363"/>
-      <c r="E81" s="363"/>
-      <c r="F81" s="363"/>
+      <c r="C81" s="360"/>
+      <c r="D81" s="360"/>
+      <c r="E81" s="360"/>
+      <c r="F81" s="360"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5030,22 +5030,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="360" t="s">
+      <c r="B89" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="360"/>
-      <c r="D89" s="360"/>
-      <c r="E89" s="360"/>
-      <c r="F89" s="360"/>
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="360" t="s">
+      <c r="B90" s="358" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="360"/>
-      <c r="D90" s="360"/>
-      <c r="E90" s="360"/>
-      <c r="F90" s="360"/>
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5082,13 +5082,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="360" t="s">
+      <c r="B97" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="360"/>
-      <c r="D97" s="360"/>
-      <c r="E97" s="360"/>
-      <c r="F97" s="360"/>
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5101,13 +5101,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="360" t="s">
+      <c r="B101" s="358" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="360"/>
-      <c r="D101" s="360"/>
-      <c r="E101" s="360"/>
-      <c r="F101" s="360"/>
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5229,13 +5229,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="360" t="s">
+      <c r="B116" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="360"/>
-      <c r="D116" s="360"/>
-      <c r="E116" s="360"/>
-      <c r="F116" s="360"/>
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5274,13 +5274,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="361" t="s">
+      <c r="B123" s="359" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="361"/>
-      <c r="D123" s="361"/>
-      <c r="E123" s="361"/>
-      <c r="F123" s="361"/>
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5423,13 +5423,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="364" t="s">
+      <c r="B134" s="363" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="364"/>
-      <c r="D134" s="364"/>
-      <c r="E134" s="364"/>
-      <c r="F134" s="364"/>
+      <c r="C134" s="363"/>
+      <c r="D134" s="363"/>
+      <c r="E134" s="363"/>
+      <c r="F134" s="363"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5442,22 +5442,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="365" t="s">
+      <c r="B138" s="361" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="365"/>
-      <c r="D138" s="365"/>
-      <c r="E138" s="365"/>
-      <c r="F138" s="365"/>
+      <c r="C138" s="361"/>
+      <c r="D138" s="361"/>
+      <c r="E138" s="361"/>
+      <c r="F138" s="361"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="360" t="s">
+      <c r="B139" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="360"/>
-      <c r="D139" s="360"/>
-      <c r="E139" s="360"/>
-      <c r="F139" s="360"/>
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5790,13 +5790,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="359" t="s">
+      <c r="B179" s="365" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="360"/>
-      <c r="D179" s="360"/>
-      <c r="E179" s="360"/>
-      <c r="F179" s="360"/>
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5833,13 +5833,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="361" t="s">
+      <c r="B188" s="359" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="361"/>
-      <c r="D188" s="361"/>
-      <c r="E188" s="361"/>
-      <c r="F188" s="361"/>
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5847,22 +5847,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="358" t="s">
+      <c r="B191" s="364" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="358"/>
-      <c r="D191" s="358"/>
-      <c r="E191" s="358"/>
-      <c r="F191" s="358"/>
+      <c r="C191" s="364"/>
+      <c r="D191" s="364"/>
+      <c r="E191" s="364"/>
+      <c r="F191" s="364"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="358" t="s">
+      <c r="B192" s="364" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="358"/>
-      <c r="D192" s="358"/>
-      <c r="E192" s="358"/>
-      <c r="F192" s="358"/>
+      <c r="C192" s="364"/>
+      <c r="D192" s="364"/>
+      <c r="E192" s="364"/>
+      <c r="F192" s="364"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5886,6 +5886,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5902,17 +5913,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13503,32 +13503,32 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>2.5263157894736845E-2</v>
+        <v>2.5157232704402517E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>2.5263157894736845E-2</v>
+        <v>2.5157232704402517E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>2.5263157894736845E-2</v>
+        <v>2.5157232704402517E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>2.5263157894736845E-2</v>
+        <v>2.5157232704402517E-2</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
-        <v>2.5263157894736845E-2</v>
+        <v>2.5157232704402517E-2</v>
       </c>
       <c r="K94" s="23">
         <f t="shared" si="39"/>
-        <v>1.2631578947368423E-2</v>
+        <v>1.2578616352201259E-2</v>
       </c>
       <c r="L94" s="23">
         <f t="shared" si="39"/>
-        <v>1.2631578947368423E-2</v>
+        <v>1.2578616352201259E-2</v>
       </c>
       <c r="M94" s="23">
         <f t="shared" si="39"/>
@@ -14702,50 +14702,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>3.1132643503964344E-2</v>
+        <v>3.1002108311075603E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>3.5475518561328134E-2</v>
+        <v>3.5326774248702016E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>4.665108536480482E-2</v>
+        <v>4.6455483329732261E-2</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>9.1756152634228233E-2</v>
+        <v>9.1371430820248234E-2</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>5.9418168899435735E-2</v>
+        <v>5.9169036115790302E-2</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>4.4432747599243309E-2</v>
+        <v>4.424644677073495E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>3.6913695491337543E-2</v>
+        <v>3.6758921086761702E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>2.6030139761793115E-2</v>
+        <v>2.5920998714573856E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>2.3662814852133941E-2</v>
+        <v>2.3563599695521218E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>1.5655582464058741E-2</v>
+        <v>1.5589940608863524E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>1.5307769078206475E-2</v>
+        <v>1.5243585560058857E-2</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14759,43 +14759,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.6052644277495579E-2</v>
+        <v>4.5859551429371911E-2</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.6523799208560904E-2</v>
+        <v>5.6286802146889789E-2</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10151669436512474</v>
+        <v>0.10109104784787054</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.0686034305816212E-2</v>
+        <v>6.0431585524659749E-2</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.2955960260336927E-2</v>
+        <v>4.2775851412285196E-2</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.4797442207816956E-2</v>
+        <v>3.4651540982626947E-2</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.5426272130909155E-2</v>
+        <v>2.5319663023442029E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.7698289504161028E-2</v>
+        <v>1.7624082839573348E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.5529461625318092E-2</v>
+        <v>1.5464348578671055E-2</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.3823138616449546E-2</v>
+        <v>1.3765179963969674E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18745,7 +18745,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-14.25</v>
+        <v>-14.31</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18985,7 +18985,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>14.25</v>
+        <v>14.31</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19583,7 +19583,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>14.25</v>
+        <v>14.31</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19596,7 +19596,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>-7.5724920811838015E-2</v>
+        <v>-7.7055822209717295E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/300481.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/300481.SZ_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{870F0894-A9DB-4CE4-A3DC-4260A8EA3AE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12B440CF-C6D6-4CB3-9BAD-1313A283E5D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3893,29 +3893,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4333,7 +4333,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>14.31</v>
+        <v>14.64</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>4176.45131778</v>
+        <v>4272.76361232</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4391,13 +4391,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="358" t="s">
+      <c r="B18" s="360" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+      <c r="C18" s="360"/>
+      <c r="D18" s="360"/>
+      <c r="E18" s="360"/>
+      <c r="F18" s="360"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4480,7 +4480,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>-7.7055822209717295E-2</v>
+        <v>-8.4242640912131184E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4597,22 +4597,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="358" t="s">
+      <c r="B36" s="360" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
+      <c r="C36" s="360"/>
+      <c r="D36" s="360"/>
+      <c r="E36" s="360"/>
+      <c r="F36" s="360"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="360" t="s">
+      <c r="B37" s="363" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="360"/>
-      <c r="D37" s="360"/>
-      <c r="E37" s="360"/>
-      <c r="F37" s="360"/>
+      <c r="C37" s="363"/>
+      <c r="D37" s="363"/>
+      <c r="E37" s="363"/>
+      <c r="F37" s="363"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4624,13 +4624,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="359" t="s">
+      <c r="B40" s="361" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+      <c r="C40" s="361"/>
+      <c r="D40" s="361"/>
+      <c r="E40" s="361"/>
+      <c r="F40" s="361"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4650,13 +4650,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="359" t="s">
+      <c r="B43" s="361" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+      <c r="C43" s="361"/>
+      <c r="D43" s="361"/>
+      <c r="E43" s="361"/>
+      <c r="F43" s="361"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4685,13 +4685,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+      <c r="B47" s="361" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="C47" s="361"/>
+      <c r="D47" s="361"/>
+      <c r="E47" s="361"/>
+      <c r="F47" s="361"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4707,13 +4707,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+      <c r="B50" s="361" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="C50" s="361"/>
+      <c r="D50" s="361"/>
+      <c r="E50" s="361"/>
+      <c r="F50" s="361"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4777,13 +4777,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+      <c r="B58" s="361" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="C58" s="361"/>
+      <c r="D58" s="361"/>
+      <c r="E58" s="361"/>
+      <c r="F58" s="361"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4799,7 +4799,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+      <c r="B61" s="361" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4821,22 +4821,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="358" t="s">
+      <c r="B64" s="360" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
+      <c r="C64" s="360"/>
+      <c r="D64" s="360"/>
+      <c r="E64" s="360"/>
+      <c r="F64" s="360"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="B65" s="360" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+      <c r="C65" s="360"/>
+      <c r="D65" s="360"/>
+      <c r="E65" s="360"/>
+      <c r="F65" s="360"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4870,7 +4870,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>3.1002108311075603E-2</v>
+        <v>3.0303290295866932E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>2.5157232704402517E-2</v>
+        <v>2.4590163934426233E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>445</v>
@@ -4971,22 +4971,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="360" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="C80" s="360"/>
+      <c r="D80" s="360"/>
+      <c r="E80" s="360"/>
+      <c r="F80" s="360"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="360" t="s">
+      <c r="B81" s="363" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="360"/>
-      <c r="D81" s="360"/>
-      <c r="E81" s="360"/>
-      <c r="F81" s="360"/>
+      <c r="C81" s="363"/>
+      <c r="D81" s="363"/>
+      <c r="E81" s="363"/>
+      <c r="F81" s="363"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5030,22 +5030,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="358" t="s">
+      <c r="B89" s="360" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
+      <c r="C89" s="360"/>
+      <c r="D89" s="360"/>
+      <c r="E89" s="360"/>
+      <c r="F89" s="360"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="B90" s="360" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+      <c r="C90" s="360"/>
+      <c r="D90" s="360"/>
+      <c r="E90" s="360"/>
+      <c r="F90" s="360"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5082,13 +5082,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+      <c r="B97" s="360" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="C97" s="360"/>
+      <c r="D97" s="360"/>
+      <c r="E97" s="360"/>
+      <c r="F97" s="360"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5101,13 +5101,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="358" t="s">
+      <c r="B101" s="360" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+      <c r="C101" s="360"/>
+      <c r="D101" s="360"/>
+      <c r="E101" s="360"/>
+      <c r="F101" s="360"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5229,13 +5229,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="358" t="s">
+      <c r="B116" s="360" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+      <c r="C116" s="360"/>
+      <c r="D116" s="360"/>
+      <c r="E116" s="360"/>
+      <c r="F116" s="360"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5274,13 +5274,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="359" t="s">
+      <c r="B123" s="361" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+      <c r="C123" s="361"/>
+      <c r="D123" s="361"/>
+      <c r="E123" s="361"/>
+      <c r="F123" s="361"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5423,13 +5423,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="363" t="s">
+      <c r="B134" s="364" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="363"/>
-      <c r="D134" s="363"/>
-      <c r="E134" s="363"/>
-      <c r="F134" s="363"/>
+      <c r="C134" s="364"/>
+      <c r="D134" s="364"/>
+      <c r="E134" s="364"/>
+      <c r="F134" s="364"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5442,22 +5442,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="361" t="s">
+      <c r="B138" s="365" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="361"/>
-      <c r="D138" s="361"/>
-      <c r="E138" s="361"/>
-      <c r="F138" s="361"/>
+      <c r="C138" s="365"/>
+      <c r="D138" s="365"/>
+      <c r="E138" s="365"/>
+      <c r="F138" s="365"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="B139" s="360" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="C139" s="360"/>
+      <c r="D139" s="360"/>
+      <c r="E139" s="360"/>
+      <c r="F139" s="360"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5790,13 +5790,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="365" t="s">
+      <c r="B179" s="359" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="C179" s="360"/>
+      <c r="D179" s="360"/>
+      <c r="E179" s="360"/>
+      <c r="F179" s="360"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5833,13 +5833,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+      <c r="B188" s="361" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="C188" s="361"/>
+      <c r="D188" s="361"/>
+      <c r="E188" s="361"/>
+      <c r="F188" s="361"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5847,22 +5847,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="364" t="s">
+      <c r="B191" s="358" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="364"/>
-      <c r="D191" s="364"/>
-      <c r="E191" s="364"/>
-      <c r="F191" s="364"/>
+      <c r="C191" s="358"/>
+      <c r="D191" s="358"/>
+      <c r="E191" s="358"/>
+      <c r="F191" s="358"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="364" t="s">
+      <c r="B192" s="358" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="364"/>
-      <c r="D192" s="364"/>
-      <c r="E192" s="364"/>
-      <c r="F192" s="364"/>
+      <c r="C192" s="358"/>
+      <c r="D192" s="358"/>
+      <c r="E192" s="358"/>
+      <c r="F192" s="358"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5886,17 +5886,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5913,6 +5902,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13503,32 +13503,32 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>2.5157232704402517E-2</v>
+        <v>2.4590163934426233E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>2.5157232704402517E-2</v>
+        <v>2.4590163934426233E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>2.5157232704402517E-2</v>
+        <v>2.4590163934426233E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>2.5157232704402517E-2</v>
+        <v>2.4590163934426233E-2</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
-        <v>2.5157232704402517E-2</v>
+        <v>2.4590163934426233E-2</v>
       </c>
       <c r="K94" s="23">
         <f t="shared" si="39"/>
-        <v>1.2578616352201259E-2</v>
+        <v>1.2295081967213116E-2</v>
       </c>
       <c r="L94" s="23">
         <f t="shared" si="39"/>
-        <v>1.2578616352201259E-2</v>
+        <v>1.2295081967213116E-2</v>
       </c>
       <c r="M94" s="23">
         <f t="shared" si="39"/>
@@ -14702,50 +14702,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>3.1002108311075603E-2</v>
+        <v>3.0303290295866932E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>3.5326774248702016E-2</v>
+        <v>3.453047400948947E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>4.6455483329732261E-2</v>
+        <v>4.5408331041562063E-2</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>9.1371430820248234E-2</v>
+        <v>8.9311828896021336E-2</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>5.9169036115790302E-2</v>
+        <v>5.783530784268847E-2</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>4.424644677073495E-2</v>
+        <v>4.3249088339427401E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>3.6758921086761702E-2</v>
+        <v>3.593033884915027E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>2.5920998714573856E-2</v>
+        <v>2.5336713907483051E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>2.3563599695521218E-2</v>
+        <v>2.3032452981072996E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>1.5589940608863524E-2</v>
+        <v>1.5238528013171928E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>1.5243585560058857E-2</v>
+        <v>1.4899980147844416E-2</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14759,43 +14759,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.5859551429371911E-2</v>
+        <v>4.4825832032398365E-2</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.6286802146889789E-2</v>
+        <v>5.5018042262431205E-2</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10109104784787054</v>
+        <v>9.8812356195561987E-2</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.0431585524659749E-2</v>
+        <v>5.9069398146030128E-2</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.2775851412285196E-2</v>
+        <v>4.1811641646844346E-2</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.4651540982626947E-2</v>
+        <v>3.3870461165395604E-2</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.5319663023442029E-2</v>
+        <v>2.4748932914307065E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.7624082839573348E-2</v>
+        <v>1.7226818677205918E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.5464348578671055E-2</v>
+        <v>1.5115766950873142E-2</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.3765179963969674E-2</v>
+        <v>1.3454899268060521E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18745,7 +18745,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-14.31</v>
+        <v>-14.64</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18985,7 +18985,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>14.31</v>
+        <v>14.64</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19583,7 +19583,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>14.31</v>
+        <v>14.64</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19596,7 +19596,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>-7.7055822209717295E-2</v>
+        <v>-8.4242640912131184E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/300481.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/300481.SZ_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12B440CF-C6D6-4CB3-9BAD-1313A283E5D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C5B5D34-9855-4F02-908B-62C12DF89F3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -20,6 +20,7 @@
     <sheet name="DCF" sheetId="8" r:id="rId5"/>
     <sheet name="DDM" sheetId="10" r:id="rId6"/>
     <sheet name="Scenarios" sheetId="9" r:id="rId7"/>
+    <sheet name="Breakdown" sheetId="11" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">DCF!$B$73:$H$73</definedName>
@@ -48,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="686" uniqueCount="465">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="687" uniqueCount="466">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -2444,6 +2445,9 @@
   </si>
   <si>
     <t>After-tax Dividend per share</t>
+  </si>
+  <si>
+    <t>Divisional Analysis (Optional)</t>
   </si>
   <si>
     <t>CN</t>
@@ -4237,13 +4241,13 @@
         <v>45797</v>
       </c>
       <c r="D1" s="316" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="E1" s="292" t="s">
         <v>350</v>
       </c>
       <c r="F1" s="254" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9">
@@ -4274,7 +4278,7 @@
         <v>312</v>
       </c>
       <c r="C5" s="294" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -4321,10 +4325,10 @@
         <v>414</v>
       </c>
       <c r="C11" s="49" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="D11" s="49" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="E11" s="34"/>
     </row>
@@ -4418,7 +4422,7 @@
         <v>436</v>
       </c>
       <c r="E21" s="308" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="22" spans="2:6">
@@ -4426,7 +4430,7 @@
         <v>56</v>
       </c>
       <c r="C22" s="48" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="D22" s="1" t="str">
         <f>IF(valuation_method="DDM","DDM Terminal Value","")</f>
@@ -4439,7 +4443,7 @@
         <v>431</v>
       </c>
       <c r="C23" s="262" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="24" spans="2:6">
@@ -4447,7 +4451,7 @@
         <v>432</v>
       </c>
       <c r="C24" s="262" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="25" spans="2:6">
@@ -6630,7 +6634,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -12799,7 +12803,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="266" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -19822,4 +19826,27 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F820689B-F36D-4933-9EEF-92EBF45B6A8E}">
+  <dimension ref="B2:E2"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
+  <cols>
+    <col min="1" max="1" width="2.59765625" customWidth="1"/>
+    <col min="2" max="2" width="22.73046875" customWidth="1"/>
+    <col min="3" max="5" width="20.73046875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:5" ht="13.9">
+      <c r="B2" s="36" t="s">
+        <v>456</v>
+      </c>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/financial_models/opportunities/300481.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/300481.SZ_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C5B5D34-9855-4F02-908B-62C12DF89F3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CDDC1FC-322D-4952-A63E-E6E8EF273182}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,20 +20,33 @@
     <sheet name="DCF" sheetId="8" r:id="rId5"/>
     <sheet name="DDM" sheetId="10" r:id="rId6"/>
     <sheet name="Scenarios" sheetId="9" r:id="rId7"/>
-    <sheet name="Breakdown" sheetId="11" r:id="rId8"/>
+    <sheet name="Breakdown" sheetId="12" r:id="rId8"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId9"/>
+  </externalReferences>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">DCF!$B$73:$H$73</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">DDM!$B$68:$H$68</definedName>
+    <definedName name="Common_Shares" localSheetId="7">[1]Thesis!$C$6</definedName>
     <definedName name="Common_Shares">Thesis!$C$6</definedName>
+    <definedName name="dividend_tax_rate" localSheetId="7">[1]Normalized_FCF!$C$93</definedName>
     <definedName name="dividend_tax_rate">Normalized_FCF!$C$93</definedName>
+    <definedName name="Equity_Cost" localSheetId="7">[1]Thesis!$C$86</definedName>
     <definedName name="Equity_Cost">Thesis!$C$86</definedName>
+    <definedName name="Exchange_Rate" localSheetId="7">[1]Thesis!$C$16</definedName>
     <definedName name="Exchange_Rate">Thesis!$C$16</definedName>
+    <definedName name="Market_currency" localSheetId="7">[1]Thesis!$C$13</definedName>
     <definedName name="Market_currency">Thesis!$C$13</definedName>
+    <definedName name="Market_Price" localSheetId="7">[1]Thesis!$C$12</definedName>
     <definedName name="Market_Price">Thesis!$C$12</definedName>
+    <definedName name="Reporting_currency" localSheetId="7">[1]Thesis!$C$25</definedName>
     <definedName name="Reporting_currency">Thesis!$C$25</definedName>
+    <definedName name="scaling_factor" localSheetId="7">[1]Data!$C$3</definedName>
     <definedName name="scaling_factor">Data!$C$3</definedName>
+    <definedName name="Terminal_Growth" localSheetId="7">[1]Thesis!$C$92</definedName>
     <definedName name="Terminal_Growth">Thesis!$C$92</definedName>
+    <definedName name="valuation_method" localSheetId="7">[1]Thesis!$E$21</definedName>
     <definedName name="valuation_method">Thesis!$E$21</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -42,7 +55,7 @@
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext uri="GoogleSheetsCustomDataVersion1">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId9" roundtripDataSignature="AMtx7mi73Cg0ax9bLfpeUuF69nNRn7idDQ=="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId10" roundtripDataSignature="AMtx7mi73Cg0ax9bLfpeUuF69nNRn7idDQ=="/>
     </ext>
   </extLst>
 </workbook>
@@ -2501,7 +2514,7 @@
     <numFmt numFmtId="180" formatCode="0.000000000000000%"/>
     <numFmt numFmtId="181" formatCode="#,##0_);\(#,##0\);0;@"/>
   </numFmts>
-  <fonts count="59">
+  <fonts count="60">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -2941,6 +2954,12 @@
       <family val="2"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="10">
     <fill>
@@ -3144,11 +3163,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="370">
+  <cellXfs count="373">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3933,9 +3953,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="1" xfId="2"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="常规 2" xfId="2" xr:uid="{84E26CB8-48BA-41B7-A5C3-FFB4C4D26709}"/>
     <cellStyle name="常规 2 2" xfId="1" xr:uid="{A35F4541-DCCE-4554-A311-39480A36979A}"/>
   </cellStyles>
   <dxfs count="8">
@@ -4020,6 +4046,89 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Thesis"/>
+      <sheetName val="Data"/>
+      <sheetName val="BS"/>
+      <sheetName val="Normalized_FCF"/>
+      <sheetName val="DCF"/>
+      <sheetName val="DDM"/>
+      <sheetName val="Scenarios"/>
+      <sheetName val="Breakdown"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="6">
+          <cell r="C6">
+            <v>291855438</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="C12">
+            <v>14.64</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="C13" t="str">
+            <v>CNY</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="C16">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="E21" t="str">
+            <v>DCF</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="C25" t="str">
+            <v>CNY</v>
+          </cell>
+        </row>
+        <row r="86">
+          <cell r="C86">
+            <v>0.06</v>
+          </cell>
+        </row>
+        <row r="92">
+          <cell r="C92">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1">
+        <row r="3">
+          <cell r="C3">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3">
+        <row r="93">
+          <cell r="C93">
+            <v>0.1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -19829,22 +19938,23 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F820689B-F36D-4933-9EEF-92EBF45B6A8E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7417C68D-4283-4D3F-A813-3C9F171BE969}">
   <dimension ref="B2:E2"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="2.59765625" customWidth="1"/>
-    <col min="2" max="2" width="22.73046875" customWidth="1"/>
-    <col min="3" max="5" width="20.73046875" customWidth="1"/>
+    <col min="1" max="1" width="2.59765625" style="372" customWidth="1"/>
+    <col min="2" max="2" width="22.73046875" style="372" customWidth="1"/>
+    <col min="3" max="5" width="20.73046875" style="372" customWidth="1"/>
+    <col min="6" max="16384" width="9.06640625" style="372"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:5" ht="13.9">
-      <c r="B2" s="36" t="s">
+      <c r="B2" s="370" t="s">
         <v>456</v>
       </c>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
+      <c r="C2" s="371"/>
+      <c r="D2" s="371"/>
+      <c r="E2" s="371"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/financial_models/opportunities/300481.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/300481.SZ_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CDDC1FC-322D-4952-A63E-E6E8EF273182}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B685264-67C8-459A-B17B-157DDE0EE77E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3917,47 +3917,47 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1"/>
     <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="59" fillId="0" borderId="1" xfId="2"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -4446,7 +4446,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>14.64</v>
+        <v>14.57</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4467,7 +4467,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>4272.76361232</v>
+        <v>4252.33373166</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4504,13 +4504,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="360" t="s">
+      <c r="B18" s="361" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="360"/>
-      <c r="D18" s="360"/>
-      <c r="E18" s="360"/>
-      <c r="F18" s="360"/>
+      <c r="C18" s="361"/>
+      <c r="D18" s="361"/>
+      <c r="E18" s="361"/>
+      <c r="F18" s="361"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4586,14 +4586,14 @@
       </c>
       <c r="C26" s="304">
         <f>C132</f>
-        <v>10.251430255232371</v>
+        <v>8.6992744860027944</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>396</v>
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>-8.4242640912131184E-2</v>
+        <v>-0.1284274085979954</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4625,7 +4625,7 @@
       </c>
       <c r="C29" s="310">
         <f>C149</f>
-        <v>4.777129606353653</v>
+        <v>3.3910941772119543</v>
       </c>
       <c r="D29" s="310" t="str">
         <f>D149</f>
@@ -4635,7 +4635,7 @@
         <v>421</v>
       </c>
       <c r="F29" s="302">
-        <v>0.35</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="30" spans="2:6">
@@ -4644,7 +4644,7 @@
       </c>
       <c r="C30" s="311">
         <f>C157</f>
-        <v>5.951452290678974</v>
+        <v>4.6134157878938522</v>
       </c>
       <c r="D30" s="311" t="str">
         <f>D157</f>
@@ -4654,7 +4654,7 @@
         <v>434</v>
       </c>
       <c r="F30" s="312">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="31" spans="2:6">
@@ -4663,7 +4663,7 @@
       </c>
       <c r="C31" s="311">
         <f>C165</f>
-        <v>9.5695828227600401</v>
+        <v>7.9387622109270746</v>
       </c>
       <c r="D31" s="311" t="str">
         <f>D165</f>
@@ -4673,7 +4673,7 @@
         <v>433</v>
       </c>
       <c r="F31" s="312">
-        <v>0.06</v>
+        <v>7.4999999999999997E-2</v>
       </c>
     </row>
     <row r="32" spans="2:6">
@@ -4682,7 +4682,7 @@
       </c>
       <c r="C32" s="311">
         <f>C173</f>
-        <v>8.8978683003699235</v>
+        <v>7.6893682545464594</v>
       </c>
       <c r="D32" s="311" t="str">
         <f>D173</f>
@@ -4710,13 +4710,13 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="360" t="s">
+      <c r="B36" s="361" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="360"/>
-      <c r="D36" s="360"/>
-      <c r="E36" s="360"/>
-      <c r="F36" s="360"/>
+      <c r="C36" s="361"/>
+      <c r="D36" s="361"/>
+      <c r="E36" s="361"/>
+      <c r="F36" s="361"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
       <c r="B37" s="363" t="s">
@@ -4737,13 +4737,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="361" t="s">
+      <c r="B40" s="362" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="361"/>
-      <c r="D40" s="361"/>
-      <c r="E40" s="361"/>
-      <c r="F40" s="361"/>
+      <c r="C40" s="362"/>
+      <c r="D40" s="362"/>
+      <c r="E40" s="362"/>
+      <c r="F40" s="362"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4763,13 +4763,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="361" t="s">
+      <c r="B43" s="362" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="361"/>
-      <c r="D43" s="361"/>
-      <c r="E43" s="361"/>
-      <c r="F43" s="361"/>
+      <c r="C43" s="362"/>
+      <c r="D43" s="362"/>
+      <c r="E43" s="362"/>
+      <c r="F43" s="362"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4798,13 +4798,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="361" t="s">
+      <c r="B47" s="362" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="361"/>
-      <c r="D47" s="361"/>
-      <c r="E47" s="361"/>
-      <c r="F47" s="361"/>
+      <c r="C47" s="362"/>
+      <c r="D47" s="362"/>
+      <c r="E47" s="362"/>
+      <c r="F47" s="362"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4820,13 +4820,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="361" t="s">
+      <c r="B50" s="362" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="361"/>
-      <c r="D50" s="361"/>
-      <c r="E50" s="361"/>
-      <c r="F50" s="361"/>
+      <c r="C50" s="362"/>
+      <c r="D50" s="362"/>
+      <c r="E50" s="362"/>
+      <c r="F50" s="362"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4890,13 +4890,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="361" t="s">
+      <c r="B58" s="362" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="361"/>
-      <c r="D58" s="361"/>
-      <c r="E58" s="361"/>
-      <c r="F58" s="361"/>
+      <c r="C58" s="362"/>
+      <c r="D58" s="362"/>
+      <c r="E58" s="362"/>
+      <c r="F58" s="362"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4912,13 +4912,13 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="361" t="s">
+      <c r="B61" s="362" t="s">
         <v>335</v>
       </c>
-      <c r="C61" s="362"/>
-      <c r="D61" s="362"/>
-      <c r="E61" s="362"/>
-      <c r="F61" s="362"/>
+      <c r="C61" s="365"/>
+      <c r="D61" s="365"/>
+      <c r="E61" s="365"/>
+      <c r="F61" s="365"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -4934,22 +4934,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="360" t="s">
+      <c r="B64" s="361" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="360"/>
-      <c r="D64" s="360"/>
-      <c r="E64" s="360"/>
-      <c r="F64" s="360"/>
+      <c r="C64" s="361"/>
+      <c r="D64" s="361"/>
+      <c r="E64" s="361"/>
+      <c r="F64" s="361"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="360" t="s">
+      <c r="B65" s="361" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="360"/>
-      <c r="D65" s="360"/>
-      <c r="E65" s="360"/>
-      <c r="F65" s="360"/>
+      <c r="C65" s="361"/>
+      <c r="D65" s="361"/>
+      <c r="E65" s="361"/>
+      <c r="F65" s="361"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4983,7 +4983,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>3.0303290295866932E-2</v>
+        <v>3.0448879199141517E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>2.4590163934426233E-2</v>
+        <v>2.4708304735758409E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>445</v>
@@ -5084,13 +5084,13 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="360" t="s">
+      <c r="B80" s="361" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="360"/>
-      <c r="D80" s="360"/>
-      <c r="E80" s="360"/>
-      <c r="F80" s="360"/>
+      <c r="C80" s="361"/>
+      <c r="D80" s="361"/>
+      <c r="E80" s="361"/>
+      <c r="F80" s="361"/>
     </row>
     <row r="81" spans="1:6">
       <c r="B81" s="363" t="s">
@@ -5112,7 +5112,7 @@
       </c>
       <c r="C84" s="92">
         <f>F31</f>
-        <v>0.06</v>
+        <v>7.4999999999999997E-2</v>
       </c>
     </row>
     <row r="85" spans="1:6">
@@ -5130,7 +5130,7 @@
       </c>
       <c r="C86" s="236">
         <f>F31+C85</f>
-        <v>0.06</v>
+        <v>7.4999999999999997E-2</v>
       </c>
     </row>
     <row r="87" spans="1:6">
@@ -5143,22 +5143,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="360" t="s">
+      <c r="B89" s="361" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="360"/>
-      <c r="D89" s="360"/>
-      <c r="E89" s="360"/>
-      <c r="F89" s="360"/>
+      <c r="C89" s="361"/>
+      <c r="D89" s="361"/>
+      <c r="E89" s="361"/>
+      <c r="F89" s="361"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="360" t="s">
+      <c r="B90" s="361" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="360"/>
-      <c r="D90" s="360"/>
-      <c r="E90" s="360"/>
-      <c r="F90" s="360"/>
+      <c r="C90" s="361"/>
+      <c r="D90" s="361"/>
+      <c r="E90" s="361"/>
+      <c r="F90" s="361"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5174,7 +5174,7 @@
       </c>
       <c r="C93" s="223">
         <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>7.3940028321915312</v>
+        <v>5.9152022657532255</v>
       </c>
       <c r="D93" s="1" t="str">
         <f>Market_currency</f>
@@ -5195,13 +5195,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="360" t="s">
+      <c r="B97" s="361" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="360"/>
-      <c r="D97" s="360"/>
-      <c r="E97" s="360"/>
-      <c r="F97" s="360"/>
+      <c r="C97" s="361"/>
+      <c r="D97" s="361"/>
+      <c r="E97" s="361"/>
+      <c r="F97" s="361"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5214,13 +5214,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="360" t="s">
+      <c r="B101" s="361" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="360"/>
-      <c r="D101" s="360"/>
-      <c r="E101" s="360"/>
-      <c r="F101" s="360"/>
+      <c r="C101" s="361"/>
+      <c r="D101" s="361"/>
+      <c r="E101" s="361"/>
+      <c r="F101" s="361"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5342,13 +5342,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="360" t="s">
+      <c r="B116" s="361" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="360"/>
-      <c r="D116" s="360"/>
-      <c r="E116" s="360"/>
-      <c r="F116" s="360"/>
+      <c r="C116" s="361"/>
+      <c r="D116" s="361"/>
+      <c r="E116" s="361"/>
+      <c r="F116" s="361"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5356,7 +5356,7 @@
       </c>
       <c r="C118" s="223">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>9.7477015390150097</v>
+        <v>8.268900972576704</v>
       </c>
       <c r="D118" s="1" t="str">
         <f>Market_currency</f>
@@ -5387,13 +5387,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="361" t="s">
+      <c r="B123" s="362" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="361"/>
-      <c r="D123" s="361"/>
-      <c r="E123" s="361"/>
-      <c r="F123" s="361"/>
+      <c r="C123" s="362"/>
+      <c r="D123" s="362"/>
+      <c r="E123" s="362"/>
+      <c r="F123" s="362"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5427,7 +5427,7 @@
       </c>
       <c r="E126" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E74,DDM!E69),2)&amp;" "&amp;Market_currency</f>
-        <v>11.74 CNY</v>
+        <v>10 CNY</v>
       </c>
       <c r="F126" s="232">
         <f>DCF!F74</f>
@@ -5449,7 +5449,7 @@
       </c>
       <c r="E127" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E75,DDM!E70),2)&amp;" "&amp;Market_currency</f>
-        <v>10.43 CNY</v>
+        <v>8.85 CNY</v>
       </c>
       <c r="F127" s="221">
         <f>DCF!F75</f>
@@ -5471,7 +5471,7 @@
       </c>
       <c r="E128" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E76,DDM!E71),2)&amp;" "&amp;Market_currency</f>
-        <v>10.2 CNY</v>
+        <v>8.65 CNY</v>
       </c>
       <c r="F128" s="221">
         <f>DCF!F76</f>
@@ -5493,7 +5493,7 @@
       </c>
       <c r="E129" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E77,DDM!E72),2)&amp;" "&amp;Market_currency</f>
-        <v>9.97 CNY</v>
+        <v>8.46 CNY</v>
       </c>
       <c r="F129" s="221">
         <f>DCF!F77</f>
@@ -5515,7 +5515,7 @@
       </c>
       <c r="E130" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E78,DDM!E73),2)&amp;" "&amp;Market_currency</f>
-        <v>9.75 CNY</v>
+        <v>8.27 CNY</v>
       </c>
       <c r="F130" s="221">
         <f>DCF!F78</f>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="C132" s="217">
         <f>Scenarios!C60</f>
-        <v>10.251430255232371</v>
+        <v>8.6992744860027944</v>
       </c>
       <c r="D132" s="212" t="str">
         <f>Market_currency</f>
@@ -5536,13 +5536,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="364" t="s">
+      <c r="B134" s="366" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="364"/>
-      <c r="D134" s="364"/>
-      <c r="E134" s="364"/>
-      <c r="F134" s="364"/>
+      <c r="C134" s="366"/>
+      <c r="D134" s="366"/>
+      <c r="E134" s="366"/>
+      <c r="F134" s="366"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5555,22 +5555,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="365" t="s">
+      <c r="B138" s="364" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="365"/>
-      <c r="D138" s="365"/>
-      <c r="E138" s="365"/>
-      <c r="F138" s="365"/>
+      <c r="C138" s="364"/>
+      <c r="D138" s="364"/>
+      <c r="E138" s="364"/>
+      <c r="F138" s="364"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="360" t="s">
+      <c r="B139" s="361" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="360"/>
-      <c r="D139" s="360"/>
-      <c r="E139" s="360"/>
-      <c r="F139" s="360"/>
+      <c r="C139" s="361"/>
+      <c r="D139" s="361"/>
+      <c r="E139" s="361"/>
+      <c r="F139" s="361"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="C142" s="224">
         <f>F29</f>
-        <v>0.35</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -5627,7 +5627,7 @@
       </c>
       <c r="C146" s="297">
         <f>F29</f>
-        <v>0.35</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="147" spans="2:4">
@@ -5637,7 +5637,7 @@
       </c>
       <c r="C147" s="216">
         <f>Scenarios!C81</f>
-        <v>0.61051668952903537</v>
+        <v>0.53758661691746279</v>
       </c>
     </row>
     <row r="148" spans="2:4">
@@ -5647,7 +5647,7 @@
       </c>
       <c r="C148" s="216">
         <f>Scenarios!C82</f>
-        <v>4.1666129168246178</v>
+        <v>2.8535075602944917</v>
       </c>
     </row>
     <row r="149" spans="2:4">
@@ -5656,7 +5656,7 @@
       </c>
       <c r="C149" s="215">
         <f>Scenarios!C83</f>
-        <v>4.777129606353653</v>
+        <v>3.3910941772119543</v>
       </c>
       <c r="D149" s="300" t="str">
         <f>IF($D$11="","",C149*$E$25)</f>
@@ -5682,7 +5682,7 @@
       </c>
       <c r="C151" s="92">
         <f>Scenarios!F83</f>
-        <v>0.53400359877438697</v>
+        <v>0.61018655260639809</v>
       </c>
     </row>
     <row r="153" spans="2:4">
@@ -5696,7 +5696,7 @@
       </c>
       <c r="C154" s="297">
         <f>Scenarios!C90</f>
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="155" spans="2:4">
@@ -5706,7 +5706,7 @@
       </c>
       <c r="C155" s="216">
         <f>Scenarios!C91</f>
-        <v>0.70272000000000001</v>
+        <v>0.65380063723259008</v>
       </c>
     </row>
     <row r="156" spans="2:4">
@@ -5716,7 +5716,7 @@
       </c>
       <c r="C156" s="216">
         <f>Scenarios!C92</f>
-        <v>5.2487322906789737</v>
+        <v>3.959615150661262</v>
       </c>
     </row>
     <row r="157" spans="2:4">
@@ -5725,7 +5725,7 @@
       </c>
       <c r="C157" s="215">
         <f>Scenarios!C93</f>
-        <v>5.951452290678974</v>
+        <v>4.6134157878938522</v>
       </c>
       <c r="D157" s="300" t="str">
         <f>IF($D$11="","",C157*$E$25)</f>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="C159" s="92">
         <f>Scenarios!F93</f>
-        <v>0.41945151627585542</v>
+        <v>0.4696780984073009</v>
       </c>
     </row>
     <row r="161" spans="2:4">
@@ -5765,7 +5765,7 @@
       </c>
       <c r="C162" s="92">
         <f>Scenarios!C96</f>
-        <v>0.06</v>
+        <v>7.4999999999999997E-2</v>
       </c>
     </row>
     <row r="163" spans="2:4">
@@ -5775,7 +5775,7 @@
       </c>
       <c r="C163" s="216">
         <f>Scenarios!C97</f>
-        <v>0.9622843018061904</v>
+        <v>0.93618926635390565</v>
       </c>
     </row>
     <row r="164" spans="2:4">
@@ -5785,7 +5785,7 @@
       </c>
       <c r="C164" s="216">
         <f>Scenarios!C98</f>
-        <v>8.6072985209538491</v>
+        <v>7.0025729445731688</v>
       </c>
     </row>
     <row r="165" spans="2:4">
@@ -5794,7 +5794,7 @@
       </c>
       <c r="C165" s="215">
         <f>Scenarios!C99</f>
-        <v>9.5695828227600401</v>
+        <v>7.9387622109270746</v>
       </c>
       <c r="D165" s="300" t="str">
         <f>IF($D$11="","",C165*$E$25)</f>
@@ -5820,7 +5820,7 @@
       </c>
       <c r="C167" s="92">
         <f>Scenarios!F99</f>
-        <v>6.6512419779114595E-2</v>
+        <v>8.7422494404492013E-2</v>
       </c>
     </row>
     <row r="169" spans="2:4">
@@ -5854,7 +5854,7 @@
       </c>
       <c r="C172" s="216">
         <f>Scenarios!C104</f>
-        <v>7.981707879328158</v>
+        <v>6.773207833504693</v>
       </c>
     </row>
     <row r="173" spans="2:4">
@@ -5863,7 +5863,7 @@
       </c>
       <c r="C173" s="215">
         <f>Scenarios!C105</f>
-        <v>8.8978683003699235</v>
+        <v>7.6893682545464594</v>
       </c>
       <c r="D173" s="300" t="str">
         <f>IF($D$11="","",C173*$E$25)</f>
@@ -5889,7 +5889,7 @@
       </c>
       <c r="C175" s="92">
         <f>Scenarios!F105</f>
-        <v>0.12975833843734319</v>
+        <v>0.11352968837267541</v>
       </c>
     </row>
     <row r="177" spans="1:6" ht="13.9">
@@ -5903,13 +5903,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="359" t="s">
+      <c r="B179" s="368" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="360"/>
-      <c r="D179" s="360"/>
-      <c r="E179" s="360"/>
-      <c r="F179" s="360"/>
+      <c r="C179" s="361"/>
+      <c r="D179" s="361"/>
+      <c r="E179" s="361"/>
+      <c r="F179" s="361"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5917,13 +5917,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="362" t="s">
+      <c r="B182" s="365" t="s">
         <v>377</v>
       </c>
-      <c r="C182" s="362"/>
-      <c r="D182" s="362"/>
-      <c r="E182" s="362"/>
-      <c r="F182" s="362"/>
+      <c r="C182" s="365"/>
+      <c r="D182" s="365"/>
+      <c r="E182" s="365"/>
+      <c r="F182" s="365"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -5946,13 +5946,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="361" t="s">
+      <c r="B188" s="362" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="361"/>
-      <c r="D188" s="361"/>
-      <c r="E188" s="361"/>
-      <c r="F188" s="361"/>
+      <c r="C188" s="362"/>
+      <c r="D188" s="362"/>
+      <c r="E188" s="362"/>
+      <c r="F188" s="362"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5960,22 +5960,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="358" t="s">
+      <c r="B191" s="367" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="358"/>
-      <c r="D191" s="358"/>
-      <c r="E191" s="358"/>
-      <c r="F191" s="358"/>
+      <c r="C191" s="367"/>
+      <c r="D191" s="367"/>
+      <c r="E191" s="367"/>
+      <c r="F191" s="367"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="358" t="s">
+      <c r="B192" s="367" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="358"/>
-      <c r="D192" s="358"/>
-      <c r="E192" s="358"/>
-      <c r="F192" s="358"/>
+      <c r="C192" s="367"/>
+      <c r="D192" s="367"/>
+      <c r="E192" s="367"/>
+      <c r="F192" s="367"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5999,6 +5999,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -6015,17 +6026,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13616,32 +13616,32 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>2.4590163934426233E-2</v>
+        <v>2.4708304735758409E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>2.4590163934426233E-2</v>
+        <v>2.4708304735758409E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>2.4590163934426233E-2</v>
+        <v>2.4708304735758409E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>2.4590163934426233E-2</v>
+        <v>2.4708304735758409E-2</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
-        <v>2.4590163934426233E-2</v>
+        <v>2.4708304735758409E-2</v>
       </c>
       <c r="K94" s="23">
         <f t="shared" si="39"/>
-        <v>1.2295081967213116E-2</v>
+        <v>1.2354152367879205E-2</v>
       </c>
       <c r="L94" s="23">
         <f t="shared" si="39"/>
-        <v>1.2295081967213116E-2</v>
+        <v>1.2354152367879205E-2</v>
       </c>
       <c r="M94" s="23">
         <f t="shared" si="39"/>
@@ -14815,50 +14815,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>3.0303290295866932E-2</v>
+        <v>3.0448879199141517E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>3.453047400948947E-2</v>
+        <v>3.469637196286382E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>4.5408331041562063E-2</v>
+        <v>4.5626490490629279E-2</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>8.9311828896021336E-2</v>
+        <v>8.9740917984746219E-2</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>5.783530784268847E-2</v>
+        <v>5.8113171366984157E-2</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>4.3249088339427401E-2</v>
+        <v>4.3456873938861849E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>3.593033884915027E-2</v>
+        <v>3.61029623027838E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>2.5336713907483051E-2</v>
+        <v>2.545844142797199E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>2.3032452981072996E-2</v>
+        <v>2.3143109927447402E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>1.5238528013171928E-2</v>
+        <v>1.5311739884202953E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>1.4899980147844416E-2</v>
+        <v>1.4971565502020745E-2</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -14872,43 +14872,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.4825832032398365E-2</v>
+        <v>4.5041192927543723E-2</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.5018042262431205E-2</v>
+        <v>5.5282370536856071E-2</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.8812356195561987E-2</v>
+        <v>9.9287089547222207E-2</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.9069398146030128E-2</v>
+        <v>5.9353190724631508E-2</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.1811641646844346E-2</v>
+        <v>4.2012521188044008E-2</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.3870461165395604E-2</v>
+        <v>3.4033188157954128E-2</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.4748932914307065E-2</v>
+        <v>2.486783650414931E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.7226818677205918E-2</v>
+        <v>1.7309583077165042E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.5115766950873142E-2</v>
+        <v>1.5188389029566426E-2</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.3454899268060521E-2</v>
+        <v>1.3519541886369666E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -15679,7 +15679,7 @@
       </c>
       <c r="C5" s="206">
         <f>Equity_Cost</f>
-        <v>0.06</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="E5" s="148"/>
       <c r="H5" s="120"/>
@@ -15690,16 +15690,16 @@
       </c>
       <c r="C6" s="347">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>2157979935.1624999</v>
+        <v>1726383948.1300001</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="366" t="s">
+      <c r="E6" s="369" t="s">
         <v>248</v>
       </c>
-      <c r="F6" s="366"/>
+      <c r="F6" s="369"/>
       <c r="H6" s="120"/>
     </row>
     <row r="7" spans="2:8">
@@ -15714,8 +15714,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="366"/>
-      <c r="F7" s="366"/>
+      <c r="E7" s="369"/>
+      <c r="F7" s="369"/>
       <c r="H7" s="120"/>
     </row>
     <row r="8" spans="2:8">
@@ -15730,8 +15730,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="366"/>
-      <c r="F8" s="366"/>
+      <c r="E8" s="369"/>
+      <c r="F8" s="369"/>
       <c r="H8" s="120"/>
     </row>
     <row r="9" spans="2:8">
@@ -15746,8 +15746,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="366"/>
-      <c r="F9" s="366"/>
+      <c r="E9" s="369"/>
+      <c r="F9" s="369"/>
       <c r="H9" s="120"/>
     </row>
     <row r="10" spans="2:8" ht="13.15">
@@ -15756,7 +15756,7 @@
       </c>
       <c r="C10" s="347">
         <f>C6-C7+C8+C9</f>
-        <v>2844919702.1624999</v>
+        <v>2413323715.1300001</v>
       </c>
       <c r="D10" t="str">
         <f>Reporting_currency</f>
@@ -15784,7 +15784,7 @@
       </c>
       <c r="C12" s="111">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>9.7477015390150097</v>
+        <v>8.268900972576704</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -15837,7 +15837,7 @@
       </c>
       <c r="C18" s="140">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>10.224594722795034</v>
+        <v>8.6741407508964592</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -15880,11 +15880,11 @@
       </c>
       <c r="E21" s="124">
         <f t="shared" ref="E21:E50" si="0">IF($C$17&lt;B21,0,1/(1+Equity_Cost)^B21)</f>
-        <v>0.94339622641509424</v>
+        <v>0.93023255813953487</v>
       </c>
       <c r="F21" s="125">
         <f t="shared" ref="F21:F51" si="1">C21*E21</f>
-        <v>127342434.64494029</v>
+        <v>125565563.46384811</v>
       </c>
       <c r="H21" s="120"/>
     </row>
@@ -15902,11 +15902,11 @@
       </c>
       <c r="E22" s="124">
         <f t="shared" si="0"/>
-        <v>0.88999644001423983</v>
+        <v>0.86533261222282321</v>
       </c>
       <c r="F22" s="125">
         <f t="shared" si="1"/>
-        <v>125241322.50623998</v>
+        <v>121770600.29681884</v>
       </c>
       <c r="H22" s="120"/>
     </row>
@@ -15924,11 +15924,11 @@
       </c>
       <c r="E23" s="124">
         <f t="shared" si="0"/>
-        <v>0.8396192830323016</v>
+        <v>0.80496056950960304</v>
       </c>
       <c r="F23" s="125">
         <f t="shared" si="1"/>
-        <v>123174878.09029604</v>
+        <v>118090332.15477748</v>
       </c>
       <c r="G23" s="338"/>
       <c r="H23" s="339"/>
@@ -15956,11 +15956,11 @@
       </c>
       <c r="E24" s="124">
         <f t="shared" si="0"/>
-        <v>0.79209366323802044</v>
+        <v>0.7488005297763749</v>
       </c>
       <c r="F24" s="125">
         <f t="shared" si="1"/>
-        <v>121142529.39003712</v>
+        <v>114521292.61442083</v>
       </c>
       <c r="G24" s="338"/>
       <c r="H24" s="339"/>
@@ -15988,11 +15988,11 @@
       </c>
       <c r="E25" s="124">
         <f t="shared" si="0"/>
-        <v>0.74725817286605689</v>
+        <v>0.69655863235011617</v>
       </c>
       <c r="F25" s="125">
         <f t="shared" si="1"/>
-        <v>119143713.83633763</v>
+        <v>111060120.01802312</v>
       </c>
       <c r="G25" s="338"/>
       <c r="H25" s="339"/>
@@ -16632,7 +16632,7 @@
       </c>
       <c r="C51" s="123">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
-        <v>2249716345.3939452</v>
+        <v>1799773076.3151562</v>
       </c>
       <c r="D51" s="139">
         <f>Terminal_Growth</f>
@@ -16640,11 +16640,11 @@
       </c>
       <c r="E51" s="124">
         <f>1/(1+Equity_Cost)^C17</f>
-        <v>0.74725817286605689</v>
+        <v>0.69655863235011617</v>
       </c>
       <c r="F51" s="125">
         <f t="shared" si="1"/>
-        <v>1681118925.7259824</v>
+        <v>1253647472.5786464</v>
       </c>
       <c r="H51" s="120"/>
     </row>
@@ -16655,7 +16655,7 @@
       </c>
       <c r="F52" s="137">
         <f>SUM(F21:F51)</f>
-        <v>2297163804.1938334</v>
+        <v>1844655381.1265349</v>
       </c>
       <c r="H52" s="120"/>
     </row>
@@ -16676,7 +16676,7 @@
     <row r="55" spans="1:17" ht="13.15">
       <c r="A55" s="133">
         <f>F52</f>
-        <v>2297163804.1938334</v>
+        <v>1844655381.1265349</v>
       </c>
       <c r="B55" s="131">
         <f>C78</f>
@@ -16706,19 +16706,19 @@
       </c>
       <c r="B56" s="123">
         <f t="dataTable" ref="B56:F61" dt2D="1" dtr="1" r1="C16" r2="C17"/>
-        <v>2157979935.1624994</v>
+        <v>1726383948.1300001</v>
       </c>
       <c r="C56" s="123">
-        <v>2222508344.6466813</v>
+        <v>1781128452.0407443</v>
       </c>
       <c r="D56" s="123">
-        <v>2288728845.3627577</v>
+        <v>1837467770.1914849</v>
       </c>
       <c r="E56" s="123">
-        <v>2356716212.5857601</v>
+        <v>1895472010.7253823</v>
       </c>
       <c r="F56" s="123">
-        <v>2426547547.4042039</v>
+        <v>1955213454.9935536</v>
       </c>
       <c r="H56" s="120"/>
     </row>
@@ -16727,19 +16727,19 @@
         <v>10</v>
       </c>
       <c r="B57" s="123">
-        <v>2157979935.1624994</v>
+        <v>1726383948.1300006</v>
       </c>
       <c r="C57" s="123">
-        <v>2283406245.8973122</v>
+        <v>1835414652.3367648</v>
       </c>
       <c r="D57" s="123">
-        <v>2420954078.2190294</v>
+        <v>1955303787.1642535</v>
       </c>
       <c r="E57" s="123">
-        <v>2572092969.0488067</v>
+        <v>2087355105.9847484</v>
       </c>
       <c r="F57" s="123">
-        <v>2738458134.2288399</v>
+        <v>2233018435.7353153</v>
       </c>
       <c r="H57" s="120"/>
     </row>
@@ -16748,19 +16748,19 @@
         <v>15</v>
       </c>
       <c r="B58" s="123">
-        <v>2157979935.1624985</v>
+        <v>1726383948.1300004</v>
       </c>
       <c r="C58" s="341">
-        <v>2365981354.4102435</v>
+        <v>1904147339.1729846</v>
       </c>
       <c r="D58" s="123">
-        <v>2609789209.6702719</v>
+        <v>2112436048.939971</v>
       </c>
       <c r="E58" s="123">
-        <v>2896658548.0806079</v>
+        <v>2357344911.5605655</v>
       </c>
       <c r="F58" s="123">
-        <v>3235296952.6150618</v>
+        <v>2646177585.3099537</v>
       </c>
       <c r="G58" s="338"/>
       <c r="H58" s="339"/>
@@ -16779,19 +16779,19 @@
         <v>20</v>
       </c>
       <c r="B59" s="123">
-        <v>2157979935.162499</v>
+        <v>1726383948.1300006</v>
       </c>
       <c r="C59" s="341">
-        <v>2458269156.9786062</v>
+        <v>1975802286.541908</v>
       </c>
       <c r="D59" s="123">
-        <v>2832747783.326704</v>
+        <v>2285492687.3498397</v>
       </c>
       <c r="E59" s="123">
-        <v>3302816367.1625328</v>
+        <v>2672490847.1437378</v>
       </c>
       <c r="F59" s="123">
-        <v>3896164894.664876</v>
+        <v>3158774767.9677143</v>
       </c>
       <c r="G59" s="338"/>
       <c r="H59" s="339"/>
@@ -16810,19 +16810,19 @@
         <v>25</v>
       </c>
       <c r="B60" s="123">
-        <v>2157979935.1624985</v>
+        <v>1726383948.1300001</v>
       </c>
       <c r="C60" s="341">
-        <v>2552463867.5166478</v>
+        <v>2044001258.5931115</v>
       </c>
       <c r="D60" s="123">
-        <v>3073769620.5883875</v>
+        <v>2459939952.0539422</v>
       </c>
       <c r="E60" s="123">
-        <v>3769944654.4643607</v>
+        <v>3010468474.8510451</v>
       </c>
       <c r="F60" s="123">
-        <v>4707976408.3152876</v>
+        <v>3745913314.9855828</v>
       </c>
       <c r="G60" s="338"/>
       <c r="H60" s="339"/>
@@ -16841,19 +16841,19 @@
         <v>30</v>
       </c>
       <c r="B61" s="123">
-        <v>2157979935.1624985</v>
+        <v>1726383948.1300001</v>
       </c>
       <c r="C61" s="341">
-        <v>2643668791.6912336</v>
+        <v>2105569663.7500298</v>
       </c>
       <c r="D61" s="123">
-        <v>3321529131.8641515</v>
+        <v>2627134023.495194</v>
       </c>
       <c r="E61" s="123">
-        <v>4282633622.4469824</v>
+        <v>3356312508.8060379</v>
       </c>
       <c r="F61" s="123">
-        <v>5663732687.2271729</v>
+        <v>4390375103.3764009</v>
       </c>
       <c r="G61" s="338"/>
       <c r="H61" s="339"/>
@@ -16933,23 +16933,23 @@
       </c>
       <c r="B65" s="124">
         <f>C12</f>
-        <v>9.7477015390150097</v>
+        <v>8.268900972576704</v>
       </c>
       <c r="C65" s="124">
         <f>C12</f>
-        <v>9.7477015390150097</v>
+        <v>8.268900972576704</v>
       </c>
       <c r="D65" s="124">
         <f>C12</f>
-        <v>9.7477015390150097</v>
+        <v>8.268900972576704</v>
       </c>
       <c r="E65" s="141">
         <f>C12</f>
-        <v>9.7477015390150097</v>
+        <v>8.268900972576704</v>
       </c>
       <c r="F65" s="124">
         <f>C12</f>
-        <v>9.7477015390150097</v>
+        <v>8.268900972576704</v>
       </c>
       <c r="H65" s="120"/>
     </row>
@@ -16960,23 +16960,23 @@
       </c>
       <c r="B66" s="124">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>9.7477015390150079</v>
+        <v>8.268900972576704</v>
       </c>
       <c r="C66" s="124">
         <f t="shared" si="4"/>
-        <v>9.968798702481882</v>
+        <v>8.4564750136358402</v>
       </c>
       <c r="D66" s="124">
         <f t="shared" si="4"/>
-        <v>10.195693569234635</v>
+        <v>8.649513452586362</v>
       </c>
       <c r="E66" s="124">
         <f t="shared" si="4"/>
-        <v>10.428642345823826</v>
+        <v>8.8482565047336283</v>
       </c>
       <c r="F66" s="124">
         <f t="shared" si="4"/>
-        <v>10.667909207859967</v>
+        <v>9.0529518315624244</v>
       </c>
       <c r="H66" s="120"/>
     </row>
@@ -16987,23 +16987,23 @@
       </c>
       <c r="B67" s="124">
         <f t="shared" si="4"/>
-        <v>9.7477015390150079</v>
+        <v>8.2689009725767058</v>
       </c>
       <c r="C67" s="124">
         <f t="shared" si="4"/>
-        <v>10.177456460130484</v>
+        <v>8.6424787443459081</v>
       </c>
       <c r="D67" s="124">
         <f t="shared" si="4"/>
-        <v>10.648744003252149</v>
+        <v>9.0532613415421554</v>
       </c>
       <c r="E67" s="124">
         <f t="shared" si="4"/>
-        <v>11.166599321849219</v>
+        <v>9.5057158845357836</v>
       </c>
       <c r="F67" s="124">
         <f t="shared" si="4"/>
-        <v>11.736625243997818</v>
+        <v>10.004809993416382</v>
       </c>
       <c r="H67" s="120"/>
     </row>
@@ -17014,23 +17014,23 @@
       </c>
       <c r="B68" s="124">
         <f t="shared" si="4"/>
-        <v>9.7477015390150061</v>
+        <v>8.268900972576704</v>
       </c>
       <c r="C68" s="124">
         <f t="shared" si="4"/>
-        <v>10.460388000069553</v>
+        <v>8.8779812496520432</v>
       </c>
       <c r="D68" s="124">
         <f t="shared" si="4"/>
-        <v>11.295759980563638</v>
+        <v>9.5916520696796841</v>
       </c>
       <c r="E68" s="124">
         <f t="shared" si="4"/>
-        <v>12.278675839100206</v>
+        <v>10.430796490968811</v>
       </c>
       <c r="F68" s="124">
         <f t="shared" si="4"/>
-        <v>13.438970836017322</v>
+        <v>11.42043943107873</v>
       </c>
       <c r="H68" s="120"/>
     </row>
@@ -17041,23 +17041,23 @@
       </c>
       <c r="B69" s="124">
         <f t="shared" si="4"/>
-        <v>9.7477015390150061</v>
+        <v>8.2689009725767058</v>
       </c>
       <c r="C69" s="124">
         <f t="shared" si="4"/>
-        <v>10.77659866655836</v>
+        <v>9.123496453548718</v>
       </c>
       <c r="D69" s="124">
         <f t="shared" si="4"/>
-        <v>12.059694945025161</v>
+        <v>10.184605346808167</v>
       </c>
       <c r="E69" s="124">
         <f t="shared" si="4"/>
-        <v>13.670316241160917</v>
+        <v>11.510597976741272</v>
       </c>
       <c r="F69" s="124">
         <f t="shared" si="4"/>
-        <v>15.703338245370901</v>
+        <v>13.176778754993471</v>
       </c>
       <c r="H69" s="120"/>
     </row>
@@ -17068,23 +17068,23 @@
       </c>
       <c r="B70" s="124">
         <f t="shared" si="4"/>
-        <v>9.7477015390150061</v>
+        <v>8.268900972576704</v>
       </c>
       <c r="C70" s="124">
         <f t="shared" si="4"/>
-        <v>11.099343074486924</v>
+        <v>9.3571702631530602</v>
       </c>
       <c r="D70" s="124">
         <f t="shared" si="4"/>
-        <v>12.885521042059143</v>
+        <v>10.782323401676491</v>
       </c>
       <c r="E70" s="124">
         <f t="shared" si="4"/>
-        <v>15.270863040983876</v>
+        <v>12.668628918440934</v>
       </c>
       <c r="F70" s="124">
         <f t="shared" si="4"/>
-        <v>18.484891740531104</v>
+        <v>15.188523168739392</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15">
@@ -17094,23 +17094,23 @@
       </c>
       <c r="B71" s="124">
         <f t="shared" si="4"/>
-        <v>9.7477015390150061</v>
+        <v>8.268900972576704</v>
       </c>
       <c r="C71" s="124">
         <f t="shared" si="4"/>
-        <v>11.411843416435618</v>
+        <v>9.5681254044340598</v>
       </c>
       <c r="D71" s="124">
         <f t="shared" si="4"/>
-        <v>13.734432794307404</v>
+        <v>11.355189449974182</v>
       </c>
       <c r="E71" s="124">
         <f t="shared" si="4"/>
-        <v>17.027516853898685</v>
+        <v>13.85361295137505</v>
       </c>
       <c r="F71" s="124">
         <f t="shared" si="4"/>
-        <v>21.759650934539629</v>
+        <v>17.396677290544098</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15">
@@ -17145,7 +17145,7 @@
       </c>
       <c r="E74" s="135">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>11.736625243997818</v>
+        <v>10.004809993416382</v>
       </c>
       <c r="F74" s="142">
         <f>Scenarios!C58</f>
@@ -17167,7 +17167,7 @@
       </c>
       <c r="E75" s="135">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>10.428642345823826</v>
+        <v>8.8482565047336283</v>
       </c>
       <c r="F75" s="142">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -17190,7 +17190,7 @@
       </c>
       <c r="E76" s="135">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>10.195693569234635</v>
+        <v>8.649513452586362</v>
       </c>
       <c r="F76" s="142">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -17213,7 +17213,7 @@
       </c>
       <c r="E77" s="135">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>9.968798702481882</v>
+        <v>8.4564750136358402</v>
       </c>
       <c r="F77" s="142">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -17236,7 +17236,7 @@
       </c>
       <c r="E78" s="135">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>9.7477015390150079</v>
+        <v>8.2689009725767058</v>
       </c>
       <c r="F78" s="142">
         <f>Scenarios!C52</f>
@@ -17439,7 +17439,7 @@
       </c>
       <c r="C5" s="206">
         <f>Equity_Cost</f>
-        <v>0.06</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="E5" s="148"/>
       <c r="H5" s="120"/>
@@ -17450,14 +17450,14 @@
       </c>
       <c r="C6" s="319">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>1751132628.0000002</v>
+        <v>1400906102.4000001</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="366"/>
-      <c r="F6" s="366"/>
+      <c r="E6" s="369"/>
+      <c r="F6" s="369"/>
       <c r="H6" s="120"/>
     </row>
     <row r="7" spans="2:8" ht="13.15">
@@ -17466,7 +17466,7 @@
       </c>
       <c r="C7" s="111">
         <f>(C6*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>6.0000000000000009</v>
+        <v>4.8000000000000007</v>
       </c>
       <c r="D7" t="str">
         <f>Market_currency</f>
@@ -17519,7 +17519,7 @@
       </c>
       <c r="C13" s="140">
         <f>F47/Common_Shares*scaling_factor</f>
-        <v>6.3869837715266424</v>
+        <v>5.1288392938304934</v>
       </c>
       <c r="D13" t="str">
         <f>Market_currency</f>
@@ -17562,11 +17562,11 @@
       </c>
       <c r="E16" s="124">
         <f t="shared" ref="E16:E45" si="0">IF($C$12&lt;B16,0,1/(1+Equity_Cost)^B16)</f>
-        <v>0.94339622641509424</v>
+        <v>0.93023255813953487</v>
       </c>
       <c r="F16" s="125">
         <f t="shared" ref="F16:F46" si="1">C16*E16</f>
-        <v>103334367.75857729</v>
+        <v>101892492.85962041</v>
       </c>
       <c r="H16" s="120"/>
     </row>
@@ -17584,11 +17584,11 @@
       </c>
       <c r="E17" s="124">
         <f t="shared" si="0"/>
-        <v>0.88999644001423983</v>
+        <v>0.86533261222282321</v>
       </c>
       <c r="F17" s="125">
         <f t="shared" si="1"/>
-        <v>101629381.55309252</v>
+        <v>98812999.989663407</v>
       </c>
       <c r="H17" s="120"/>
     </row>
@@ -17606,11 +17606,11 @@
       </c>
       <c r="E18" s="124">
         <f t="shared" si="0"/>
-        <v>0.8396192830323016</v>
+        <v>0.80496056950960304</v>
       </c>
       <c r="F18" s="125">
         <f t="shared" si="1"/>
-        <v>99952527.110775679</v>
+        <v>95826578.513584092</v>
       </c>
       <c r="H18" s="120"/>
     </row>
@@ -17628,11 +17628,11 @@
       </c>
       <c r="E19" s="124">
         <f t="shared" si="0"/>
-        <v>0.79209366323802044</v>
+        <v>0.7488005297763749</v>
       </c>
       <c r="F19" s="125">
         <f t="shared" si="1"/>
-        <v>98303340.265936553</v>
+        <v>92930415.538245767</v>
       </c>
       <c r="H19" s="120"/>
     </row>
@@ -17650,11 +17650,11 @@
       </c>
       <c r="E20" s="124">
         <f t="shared" si="0"/>
-        <v>0.74725817286605689</v>
+        <v>0.69655863235011617</v>
       </c>
       <c r="F20" s="125">
         <f t="shared" si="1"/>
-        <v>96681364.511480108</v>
+        <v>90121783.184472218</v>
       </c>
       <c r="H20" s="120"/>
     </row>
@@ -18214,7 +18214,7 @@
       </c>
       <c r="C46" s="123">
         <f>C$16*(1+F4)^$C$12/Equity_Cost</f>
-        <v>1825573830.4015324</v>
+        <v>1460459064.3212259</v>
       </c>
       <c r="D46" s="139">
         <f>Terminal_Growth</f>
@@ -18222,11 +18222,11 @@
       </c>
       <c r="E46" s="124">
         <f>1/(1+Equity_Cost)^C12</f>
-        <v>0.74725817286605689</v>
+        <v>0.69655863235011617</v>
       </c>
       <c r="F46" s="125">
         <f t="shared" si="1"/>
-        <v>1364174964.937938</v>
+        <v>1017295368.4469235</v>
       </c>
       <c r="H46" s="120"/>
     </row>
@@ -18237,7 +18237,7 @@
       </c>
       <c r="F47" s="137">
         <f>SUM(F16:F46)</f>
-        <v>1864075946.1378002</v>
+        <v>1496879638.5325093</v>
       </c>
       <c r="H47" s="120"/>
     </row>
@@ -18258,7 +18258,7 @@
     <row r="50" spans="1:8" ht="13.15">
       <c r="A50" s="133">
         <f>F47</f>
-        <v>1864075946.1378002</v>
+        <v>1496879638.5325093</v>
       </c>
       <c r="B50" s="131">
         <f>C73</f>
@@ -18288,19 +18288,19 @@
       </c>
       <c r="B51" s="123">
         <f t="dataTable" ref="B51:F56" dt2D="1" dtr="1" r1="C11" r2="C12"/>
-        <v>1751132627.9999995</v>
+        <v>1400906102.4000001</v>
       </c>
       <c r="C51" s="123">
-        <v>1803495396.2720721</v>
+        <v>1445329540.0046501</v>
       </c>
       <c r="D51" s="123">
-        <v>1857231243.1893353</v>
+        <v>1491047119.0448856</v>
       </c>
       <c r="E51" s="123">
-        <v>1912400846.5281417</v>
+        <v>1538115730.0668044</v>
       </c>
       <c r="F51" s="123">
-        <v>1969066771.3890979</v>
+        <v>1586594027.1061878</v>
       </c>
       <c r="H51" s="120"/>
     </row>
@@ -18309,19 +18309,19 @@
         <v>10</v>
       </c>
       <c r="B52" s="123">
-        <v>1751132627.9999995</v>
+        <v>1400906102.4000006</v>
       </c>
       <c r="C52" s="123">
-        <v>1852912121.6637621</v>
+        <v>1489381078.6865177</v>
       </c>
       <c r="D52" s="123">
-        <v>1964527847.6325455</v>
+        <v>1586667328.8125165</v>
       </c>
       <c r="E52" s="123">
-        <v>2087172288.750495</v>
+        <v>1693822807.5030942</v>
       </c>
       <c r="F52" s="123">
-        <v>2222172371.0786138</v>
+        <v>1812024003.5722013</v>
       </c>
       <c r="H52" s="120"/>
     </row>
@@ -18330,19 +18330,19 @@
         <v>15</v>
       </c>
       <c r="B53" s="123">
-        <v>1751132627.999999</v>
+        <v>1400906102.4000003</v>
       </c>
       <c r="C53" s="123">
-        <v>1919919216.7815142</v>
+        <v>1545155485.3748481</v>
       </c>
       <c r="D53" s="123">
-        <v>2117761598.6090295</v>
+        <v>1714175201.3480301</v>
       </c>
       <c r="E53" s="123">
-        <v>2350547015.3211112</v>
+        <v>1912911015.9092524</v>
       </c>
       <c r="F53" s="123">
-        <v>2625341395.756114</v>
+        <v>2147289617.3010886</v>
       </c>
       <c r="H53" s="120"/>
     </row>
@@ -18351,19 +18351,19 @@
         <v>20</v>
       </c>
       <c r="B54" s="123">
-        <v>1751132627.999999</v>
+        <v>1400906102.4000006</v>
       </c>
       <c r="C54" s="123">
-        <v>1994807856.6667194</v>
+        <v>1603301214.2812183</v>
       </c>
       <c r="D54" s="123">
-        <v>2298685446.2595038</v>
+        <v>1854605203.0703115</v>
       </c>
       <c r="E54" s="123">
-        <v>2680131270.2637429</v>
+        <v>2168641999.0333948</v>
       </c>
       <c r="F54" s="123">
-        <v>3161614878.7787895</v>
+        <v>2563246057.3711805</v>
       </c>
       <c r="H54" s="120"/>
     </row>
@@ -18372,19 +18372,19 @@
         <v>25</v>
       </c>
       <c r="B55" s="123">
-        <v>1751132627.999999</v>
+        <v>1400906102.4000006</v>
       </c>
       <c r="C55" s="123">
-        <v>2071243892.2018504</v>
+        <v>1658642528.2614753</v>
       </c>
       <c r="D55" s="123">
-        <v>2494267062.386837</v>
+        <v>1996163654.1528065</v>
       </c>
       <c r="E55" s="123">
-        <v>3059191136.4039683</v>
+        <v>2442900179.9222441</v>
       </c>
       <c r="F55" s="123">
-        <v>3820374307.5277209</v>
+        <v>3039690462.6626868</v>
       </c>
       <c r="H55" s="120"/>
     </row>
@@ -18393,19 +18393,19 @@
         <v>30</v>
       </c>
       <c r="B56" s="123">
-        <v>1751132627.9999988</v>
+        <v>1400906102.4000006</v>
       </c>
       <c r="C56" s="123">
-        <v>2145253810.4378872</v>
+        <v>1708603346.4171288</v>
       </c>
       <c r="D56" s="123">
-        <v>2695316088.3870044</v>
+        <v>2131836367.7579458</v>
       </c>
       <c r="E56" s="123">
-        <v>3475222057.3691401</v>
+        <v>2723541701.277317</v>
       </c>
       <c r="F56" s="123">
-        <v>4595940371.4876442</v>
+        <v>3562650869.6441412</v>
       </c>
       <c r="H56" s="120"/>
     </row>
@@ -18455,23 +18455,23 @@
       </c>
       <c r="B60" s="124">
         <f>C7</f>
-        <v>6.0000000000000009</v>
+        <v>4.8000000000000007</v>
       </c>
       <c r="C60" s="124">
         <f>C7</f>
-        <v>6.0000000000000009</v>
+        <v>4.8000000000000007</v>
       </c>
       <c r="D60" s="124">
         <f>C7</f>
-        <v>6.0000000000000009</v>
+        <v>4.8000000000000007</v>
       </c>
       <c r="E60" s="141">
         <f>C7</f>
-        <v>6.0000000000000009</v>
+        <v>4.8000000000000007</v>
       </c>
       <c r="F60" s="124">
         <f>C7</f>
-        <v>6.0000000000000009</v>
+        <v>4.8000000000000007</v>
       </c>
       <c r="H60" s="120"/>
     </row>
@@ -18482,23 +18482,23 @@
       </c>
       <c r="B61" s="124">
         <f t="shared" ref="B61:F66" si="4">B51/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>5.9999999999999982</v>
+        <v>4.8000000000000007</v>
       </c>
       <c r="C61" s="124">
         <f t="shared" si="4"/>
-        <v>6.1794133720135518</v>
+        <v>4.9522104159136831</v>
       </c>
       <c r="D61" s="124">
         <f t="shared" si="4"/>
-        <v>6.3635313973123067</v>
+        <v>5.1088550183015116</v>
       </c>
       <c r="E61" s="124">
         <f t="shared" si="4"/>
-        <v>6.5525619794281225</v>
+        <v>5.2701287343044276</v>
       </c>
       <c r="F61" s="124">
         <f t="shared" si="4"/>
-        <v>6.7467194885335591</v>
+        <v>5.436232533403019</v>
       </c>
       <c r="H61" s="120"/>
     </row>
@@ -18509,23 +18509,23 @@
       </c>
       <c r="B62" s="124">
         <f t="shared" si="4"/>
-        <v>5.9999999999999982</v>
+        <v>4.8000000000000016</v>
       </c>
       <c r="C62" s="124">
         <f t="shared" si="4"/>
-        <v>6.3487325586983312</v>
+        <v>5.1031465745261109</v>
       </c>
       <c r="D62" s="124">
         <f t="shared" si="4"/>
-        <v>6.7311675297019669</v>
+        <v>5.4364836909857974</v>
       </c>
       <c r="E62" s="124">
         <f t="shared" si="4"/>
-        <v>7.15139078118015</v>
+        <v>5.8036362766113481</v>
       </c>
       <c r="F62" s="124">
         <f t="shared" si="4"/>
-        <v>7.6139488313341408</v>
+        <v>6.2086353983652733</v>
       </c>
       <c r="H62" s="120"/>
     </row>
@@ -18536,23 +18536,23 @@
       </c>
       <c r="B63" s="124">
         <f t="shared" si="4"/>
-        <v>5.9999999999999964</v>
+        <v>4.8000000000000007</v>
       </c>
       <c r="C63" s="124">
         <f t="shared" si="4"/>
-        <v>6.5783225761978574</v>
+        <v>5.2942494269195288</v>
       </c>
       <c r="D63" s="124">
         <f t="shared" si="4"/>
-        <v>7.2562005804018277</v>
+        <v>5.8733707793651941</v>
       </c>
       <c r="E63" s="124">
         <f t="shared" si="4"/>
-        <v>8.0538057862780388</v>
+        <v>6.5543100002448895</v>
       </c>
       <c r="F63" s="124">
         <f t="shared" si="4"/>
-        <v>8.9953485662176149</v>
+        <v>7.3573740205624967</v>
       </c>
       <c r="H63" s="120"/>
     </row>
@@ -18563,23 +18563,23 @@
       </c>
       <c r="B64" s="124">
         <f t="shared" si="4"/>
-        <v>5.9999999999999964</v>
+        <v>4.8000000000000016</v>
       </c>
       <c r="C64" s="124">
         <f t="shared" si="4"/>
-        <v>6.8349175548571397</v>
+        <v>5.4934772682947859</v>
       </c>
       <c r="D64" s="124">
         <f t="shared" si="4"/>
-        <v>7.8761097001026377</v>
+        <v>6.3545336546729398</v>
       </c>
       <c r="E64" s="124">
         <f t="shared" si="4"/>
-        <v>9.1830780629954987</v>
+        <v>7.4305348356517342</v>
       </c>
       <c r="F64" s="124">
         <f t="shared" si="4"/>
-        <v>10.832811272746577</v>
+        <v>8.7825879652486734</v>
       </c>
       <c r="H64" s="120"/>
     </row>
@@ -18590,23 +18590,23 @@
       </c>
       <c r="B65" s="124">
         <f t="shared" si="4"/>
-        <v>5.9999999999999964</v>
+        <v>4.8000000000000016</v>
       </c>
       <c r="C65" s="124">
         <f t="shared" si="4"/>
-        <v>7.0968144585397459</v>
+        <v>5.683096191825884</v>
       </c>
       <c r="D65" s="124">
         <f t="shared" si="4"/>
-        <v>8.5462415210739948</v>
+        <v>6.8395629967765288</v>
       </c>
       <c r="E65" s="124">
         <f t="shared" si="4"/>
-        <v>10.481871290004774</v>
+        <v>8.3702404062186577</v>
       </c>
       <c r="F65" s="124">
         <f t="shared" si="4"/>
-        <v>13.089954169460158</v>
+        <v>10.4150550816966</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="13.15">
@@ -18616,23 +18616,23 @@
       </c>
       <c r="B66" s="124">
         <f t="shared" si="4"/>
-        <v>5.9999999999999956</v>
+        <v>4.8000000000000016</v>
       </c>
       <c r="C66" s="124">
         <f t="shared" si="4"/>
-        <v>7.3503986259042646</v>
+        <v>5.8542796328404503</v>
       </c>
       <c r="D66" s="124">
         <f t="shared" si="4"/>
-        <v>9.235106622844576</v>
+        <v>7.3044257196877922</v>
       </c>
       <c r="E66" s="124">
         <f t="shared" si="4"/>
-        <v>11.907340432591631</v>
+        <v>9.331817559888389</v>
       </c>
       <c r="F66" s="124">
         <f t="shared" si="4"/>
-        <v>15.747317928979772</v>
+        <v>12.20690247904218</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="13.15">
@@ -18667,7 +18667,7 @@
       </c>
       <c r="E69" s="135">
         <f>INDEX(B$60:F$66, MATCH(D69, A$60:A$66, 0), MATCH(C69, B$59:F$59, 0))</f>
-        <v>7.6139488313341408</v>
+        <v>6.2086353983652733</v>
       </c>
       <c r="F69" s="142">
         <f>Scenarios!C58</f>
@@ -18689,7 +18689,7 @@
       </c>
       <c r="E70" s="135">
         <f>INDEX(B$60:F$66, MATCH(D70, A$60:A$66, 0), MATCH(C70, B$59:F$59, 0))</f>
-        <v>6.5525619794281225</v>
+        <v>5.2701287343044276</v>
       </c>
       <c r="F70" s="142">
         <f>Scenarios!C40*(1-F$69-F$73)</f>
@@ -18712,7 +18712,7 @@
       </c>
       <c r="E71" s="135">
         <f>INDEX(B$60:F$66, MATCH(D71, A$60:A$66, 0), MATCH(C71, B$59:F$59, 0))</f>
-        <v>6.3635313973123067</v>
+        <v>5.1088550183015116</v>
       </c>
       <c r="F71" s="142">
         <f>Scenarios!C28*(1-F$69-F$73)</f>
@@ -18735,7 +18735,7 @@
       </c>
       <c r="E72" s="135">
         <f>INDEX(B$60:F$66, MATCH(D72, A$60:A$66, 0), MATCH(C72, B$59:F$59, 0))</f>
-        <v>6.1794133720135518</v>
+        <v>4.9522104159136831</v>
       </c>
       <c r="F72" s="142">
         <f>Scenarios!C34*(1-F$69-F$73)</f>
@@ -18758,7 +18758,7 @@
       </c>
       <c r="E73" s="135">
         <f>INDEX(B$60:F$66, MATCH(D73, A$60:A$66, 0), MATCH(C73, B$59:F$59, 0))</f>
-        <v>5.9999999999999982</v>
+        <v>4.8000000000000016</v>
       </c>
       <c r="F73" s="142">
         <f>Scenarios!C52</f>
@@ -18858,7 +18858,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-14.64</v>
+        <v>-14.57</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18907,7 +18907,7 @@
       </c>
       <c r="I6" s="124">
         <f t="shared" si="0"/>
-        <v>10.611430255232371</v>
+        <v>9.0592744860027938</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
@@ -18922,11 +18922,11 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="368" t="str">
+      <c r="E7" s="371" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!C11&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 5-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 10-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 濮阳惠成(300481.SZ). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="368"/>
+      <c r="F7" s="371"/>
       <c r="H7" s="247">
         <v>4</v>
       </c>
@@ -18947,8 +18947,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="368"/>
-      <c r="F8" s="368"/>
+      <c r="E8" s="371"/>
+      <c r="F8" s="371"/>
       <c r="H8" s="247">
         <v>5</v>
       </c>
@@ -18969,8 +18969,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="368"/>
-      <c r="F9" s="368"/>
+      <c r="E9" s="371"/>
+      <c r="F9" s="371"/>
       <c r="H9" s="247">
         <v>6</v>
       </c>
@@ -18980,8 +18980,8 @@
       </c>
     </row>
     <row r="10" spans="2:9">
-      <c r="E10" s="368"/>
-      <c r="F10" s="368"/>
+      <c r="E10" s="371"/>
+      <c r="F10" s="371"/>
       <c r="H10" s="247">
         <v>7</v>
       </c>
@@ -18994,8 +18994,8 @@
       <c r="B11" s="159" t="s">
         <v>444</v>
       </c>
-      <c r="E11" s="368"/>
-      <c r="F11" s="368"/>
+      <c r="E11" s="371"/>
+      <c r="F11" s="371"/>
       <c r="H11" s="247">
         <v>8</v>
       </c>
@@ -19013,8 +19013,8 @@
         <v>4.2279727191083527E-3</v>
       </c>
       <c r="D12" s="158"/>
-      <c r="E12" s="368"/>
-      <c r="F12" s="368"/>
+      <c r="E12" s="371"/>
+      <c r="F12" s="371"/>
       <c r="H12" s="247">
         <v>9</v>
       </c>
@@ -19031,8 +19031,8 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-0.15075343519689044</v>
       </c>
-      <c r="E13" s="368"/>
-      <c r="F13" s="368"/>
+      <c r="E13" s="371"/>
+      <c r="F13" s="371"/>
       <c r="H13" s="247">
         <v>10</v>
       </c>
@@ -19049,8 +19049,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-0.15795268346639479</v>
       </c>
-      <c r="E14" s="368"/>
-      <c r="F14" s="368"/>
+      <c r="E14" s="371"/>
+      <c r="F14" s="371"/>
     </row>
     <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
@@ -19076,21 +19076,21 @@
       <c r="C18" s="150">
         <v>5</v>
       </c>
-      <c r="E18" s="368" t="s">
+      <c r="E18" s="371" t="s">
         <v>327</v>
       </c>
-      <c r="F18" s="369"/>
+      <c r="F18" s="372"/>
     </row>
     <row r="19" spans="2:6">
-      <c r="E19" s="369"/>
-      <c r="F19" s="369"/>
+      <c r="E19" s="372"/>
+      <c r="F19" s="372"/>
     </row>
     <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="159" t="s">
         <v>302</v>
       </c>
-      <c r="E20" s="369"/>
-      <c r="F20" s="369"/>
+      <c r="E20" s="372"/>
+      <c r="F20" s="372"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
@@ -19098,14 +19098,14 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>14.64</v>
+        <v>14.57</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E21" s="369"/>
-      <c r="F21" s="369"/>
+      <c r="E21" s="372"/>
+      <c r="F21" s="372"/>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
@@ -19113,14 +19113,14 @@
       </c>
       <c r="C22" s="160">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>9.7477015390150097</v>
+        <v>8.268900972576704</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E22" s="369"/>
-      <c r="F22" s="369"/>
+      <c r="E22" s="372"/>
+      <c r="F22" s="372"/>
     </row>
     <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="159" t="s">
@@ -19140,8 +19140,8 @@
         <v>5</v>
       </c>
       <c r="D25" s="163"/>
-      <c r="E25" s="367"/>
-      <c r="F25" s="367"/>
+      <c r="E25" s="370"/>
+      <c r="F25" s="370"/>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" s="118" t="s">
@@ -19151,8 +19151,8 @@
         <v>0.04</v>
       </c>
       <c r="D26" s="164"/>
-      <c r="E26" s="367"/>
-      <c r="F26" s="367"/>
+      <c r="E26" s="370"/>
+      <c r="F26" s="370"/>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
@@ -19160,14 +19160,14 @@
       </c>
       <c r="C27" s="160">
         <f>IF(valuation_method="DCF",DCF!E76,DDM!E71)</f>
-        <v>10.195693569234635</v>
+        <v>8.649513452586362</v>
       </c>
       <c r="D27" s="160" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E27" s="367"/>
-      <c r="F27" s="367"/>
+      <c r="E27" s="370"/>
+      <c r="F27" s="370"/>
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
@@ -19177,8 +19177,8 @@
         <v>0.6</v>
       </c>
       <c r="D28" s="165"/>
-      <c r="E28" s="367"/>
-      <c r="F28" s="367"/>
+      <c r="E28" s="370"/>
+      <c r="F28" s="370"/>
     </row>
     <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="159" t="s">
@@ -19198,8 +19198,8 @@
         <v>5</v>
       </c>
       <c r="D31" s="163"/>
-      <c r="E31" s="367"/>
-      <c r="F31" s="367"/>
+      <c r="E31" s="370"/>
+      <c r="F31" s="370"/>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="118" t="s">
@@ -19209,8 +19209,8 @@
         <v>0.02</v>
       </c>
       <c r="D32" s="164"/>
-      <c r="E32" s="367"/>
-      <c r="F32" s="367"/>
+      <c r="E32" s="370"/>
+      <c r="F32" s="370"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
@@ -19218,14 +19218,14 @@
       </c>
       <c r="C33" s="160">
         <f>IF(valuation_method="DCF",DCF!E77,DDM!E72)</f>
-        <v>9.968798702481882</v>
+        <v>8.4564750136358402</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E33" s="367"/>
-      <c r="F33" s="367"/>
+      <c r="E33" s="370"/>
+      <c r="F33" s="370"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
@@ -19235,8 +19235,8 @@
         <v>0.2</v>
       </c>
       <c r="D34" s="165"/>
-      <c r="E34" s="367"/>
-      <c r="F34" s="367"/>
+      <c r="E34" s="370"/>
+      <c r="F34" s="370"/>
     </row>
     <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="159" t="s">
@@ -19256,8 +19256,8 @@
         <v>5</v>
       </c>
       <c r="D37" s="163"/>
-      <c r="E37" s="367"/>
-      <c r="F37" s="367"/>
+      <c r="E37" s="370"/>
+      <c r="F37" s="370"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="118" t="s">
@@ -19267,8 +19267,8 @@
         <v>0.06</v>
       </c>
       <c r="D38" s="164"/>
-      <c r="E38" s="367"/>
-      <c r="F38" s="367"/>
+      <c r="E38" s="370"/>
+      <c r="F38" s="370"/>
     </row>
     <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
@@ -19276,14 +19276,14 @@
       </c>
       <c r="C39" s="160">
         <f>IF(valuation_method="DCF",DCF!E75,DDM!E70)</f>
-        <v>10.428642345823826</v>
+        <v>8.8482565047336283</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E39" s="367"/>
-      <c r="F39" s="367"/>
+      <c r="E39" s="370"/>
+      <c r="F39" s="370"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
@@ -19294,8 +19294,8 @@
         <v>0.2</v>
       </c>
       <c r="D40" s="165"/>
-      <c r="E40" s="367"/>
-      <c r="F40" s="367"/>
+      <c r="E40" s="370"/>
+      <c r="F40" s="370"/>
     </row>
     <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
@@ -19303,7 +19303,7 @@
       </c>
       <c r="C42" s="154">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>10.196904351201923</v>
+        <v>8.6506543752257112</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -19357,8 +19357,8 @@
         <v>10</v>
       </c>
       <c r="D49" s="163"/>
-      <c r="E49" s="367"/>
-      <c r="F49" s="367"/>
+      <c r="E49" s="370"/>
+      <c r="F49" s="370"/>
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="118" t="s">
@@ -19368,8 +19368,8 @@
         <v>0</v>
       </c>
       <c r="D50" s="164"/>
-      <c r="E50" s="367"/>
-      <c r="F50" s="367"/>
+      <c r="E50" s="370"/>
+      <c r="F50" s="370"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
@@ -19377,14 +19377,14 @@
       </c>
       <c r="C51" s="160">
         <f>IF(valuation_method="DCF",DCF!E78,DDM!E73)</f>
-        <v>9.7477015390150079</v>
+        <v>8.2689009725767058</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E51" s="367"/>
-      <c r="F51" s="367"/>
+      <c r="E51" s="370"/>
+      <c r="F51" s="370"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
@@ -19394,8 +19394,8 @@
         <v>0.05</v>
       </c>
       <c r="D52" s="165"/>
-      <c r="E52" s="367"/>
-      <c r="F52" s="367"/>
+      <c r="E52" s="370"/>
+      <c r="F52" s="370"/>
     </row>
     <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="159" t="s">
@@ -19415,8 +19415,8 @@
         <v>10</v>
       </c>
       <c r="D55" s="163"/>
-      <c r="E55" s="367"/>
-      <c r="F55" s="367"/>
+      <c r="E55" s="370"/>
+      <c r="F55" s="370"/>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="118" t="s">
@@ -19426,8 +19426,8 @@
         <v>0.08</v>
       </c>
       <c r="D56" s="164"/>
-      <c r="E56" s="367"/>
-      <c r="F56" s="367"/>
+      <c r="E56" s="370"/>
+      <c r="F56" s="370"/>
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
@@ -19435,14 +19435,14 @@
       </c>
       <c r="C57" s="160">
         <f>IF(valuation_method="DCF",DCF!E74,DDM!E69)</f>
-        <v>11.736625243997818</v>
+        <v>10.004809993416382</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E57" s="367"/>
-      <c r="F57" s="367"/>
+      <c r="E57" s="370"/>
+      <c r="F57" s="370"/>
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
@@ -19452,8 +19452,8 @@
         <v>0.05</v>
       </c>
       <c r="D58" s="165"/>
-      <c r="E58" s="367"/>
-      <c r="F58" s="367"/>
+      <c r="E58" s="370"/>
+      <c r="F58" s="370"/>
     </row>
     <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
@@ -19461,7 +19461,7 @@
       </c>
       <c r="C60" s="154">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>10.251430255232371</v>
+        <v>8.6992744860027944</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -19523,7 +19523,7 @@
       </c>
       <c r="C66" s="160">
         <f>IF(valuation_method="DCF",DCF!C18,DDM!C13)</f>
-        <v>10.224594722795034</v>
+        <v>8.6741407508964592</v>
       </c>
       <c r="D66" s="160" t="str">
         <f>Market_currency</f>
@@ -19586,7 +19586,7 @@
       </c>
       <c r="F72" s="291">
         <f>BS!D89/C60</f>
-        <v>0.22959710481590032</v>
+        <v>0.27056264411596614</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9">
@@ -19637,7 +19637,7 @@
       </c>
       <c r="C80" s="167">
         <f>Thesis!F29</f>
-        <v>0.35</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="81" spans="2:8">
@@ -19646,7 +19646,7 @@
       </c>
       <c r="C81" s="116">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>0.61051668952903537</v>
+        <v>0.53758661691746279</v>
       </c>
       <c r="D81" s="116"/>
       <c r="E81" s="100"/>
@@ -19658,7 +19658,7 @@
       </c>
       <c r="C82" s="116">
         <f>C60/(1+C80)^C76</f>
-        <v>4.1666129168246178</v>
+        <v>2.8535075602944917</v>
       </c>
       <c r="D82" s="116"/>
     </row>
@@ -19668,7 +19668,7 @@
       </c>
       <c r="C83" s="111">
         <f>C81+C82</f>
-        <v>4.777129606353653</v>
+        <v>3.3910941772119543</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -19679,7 +19679,7 @@
       </c>
       <c r="F83" s="291">
         <f>(1-C83/C60)</f>
-        <v>0.53400359877438697</v>
+        <v>0.61018655260639809</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -19696,7 +19696,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>14.64</v>
+        <v>14.57</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19709,7 +19709,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>-8.4242640912131184E-2</v>
+        <v>-0.1284274085979954</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -19726,7 +19726,7 @@
       </c>
       <c r="C90" s="167">
         <f>Thesis!F30</f>
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="91" spans="2:8">
@@ -19735,7 +19735,7 @@
       </c>
       <c r="C91" s="116">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>0.70272000000000001</v>
+        <v>0.65380063723259008</v>
       </c>
       <c r="D91" s="116"/>
       <c r="E91" s="100"/>
@@ -19747,7 +19747,7 @@
       </c>
       <c r="C92" s="116">
         <f>C60/(1+C90)^C76</f>
-        <v>5.2487322906789737</v>
+        <v>3.959615150661262</v>
       </c>
       <c r="D92" s="116"/>
     </row>
@@ -19757,7 +19757,7 @@
       </c>
       <c r="C93" s="111">
         <f>C91+C92</f>
-        <v>5.951452290678974</v>
+        <v>4.6134157878938522</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -19768,7 +19768,7 @@
       </c>
       <c r="F93" s="291">
         <f>(1-C93/C60)</f>
-        <v>0.41945151627585542</v>
+        <v>0.4696780984073009</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
@@ -19784,7 +19784,7 @@
       </c>
       <c r="C96" s="134">
         <f>Thesis!F31</f>
-        <v>0.06</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="G96" s="2"/>
       <c r="H96" s="281"/>
@@ -19795,7 +19795,7 @@
       </c>
       <c r="C97" s="116">
         <f>PV(C96, C76, -C77, 0)</f>
-        <v>0.9622843018061904</v>
+        <v>0.93618926635390565</v>
       </c>
       <c r="D97" s="116"/>
       <c r="G97" s="2"/>
@@ -19807,7 +19807,7 @@
       </c>
       <c r="C98" s="116">
         <f>C60/(1+C96)^C76</f>
-        <v>8.6072985209538491</v>
+        <v>7.0025729445731688</v>
       </c>
       <c r="D98" s="116"/>
       <c r="G98" s="2"/>
@@ -19819,7 +19819,7 @@
       </c>
       <c r="C99" s="111">
         <f>C97+C98</f>
-        <v>9.5695828227600401</v>
+        <v>7.9387622109270746</v>
       </c>
       <c r="D99" t="s">
         <v>393</v>
@@ -19829,7 +19829,7 @@
       </c>
       <c r="F99" s="291">
         <f>(1-C99/C60)</f>
-        <v>6.6512419779114595E-2</v>
+        <v>8.7422494404492013E-2</v>
       </c>
     </row>
     <row r="100" spans="2:8">
@@ -19865,7 +19865,7 @@
       </c>
       <c r="C104" s="116">
         <f>C60/(1+C102)^C76</f>
-        <v>7.981707879328158</v>
+        <v>6.773207833504693</v>
       </c>
       <c r="D104" s="116"/>
     </row>
@@ -19875,7 +19875,7 @@
       </c>
       <c r="C105" s="111">
         <f>C103+C104</f>
-        <v>8.8978683003699235</v>
+        <v>7.6893682545464594</v>
       </c>
       <c r="D105" t="s">
         <v>393</v>
@@ -19885,7 +19885,7 @@
       </c>
       <c r="F105" s="291">
         <f>(1-C105/C66)</f>
-        <v>0.12975833843734319</v>
+        <v>0.11352968837267541</v>
       </c>
     </row>
     <row r="106" spans="2:8">
@@ -19942,19 +19942,19 @@
   <dimension ref="B2:E2"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="2.59765625" style="372" customWidth="1"/>
-    <col min="2" max="2" width="22.73046875" style="372" customWidth="1"/>
-    <col min="3" max="5" width="20.73046875" style="372" customWidth="1"/>
-    <col min="6" max="16384" width="9.06640625" style="372"/>
+    <col min="1" max="1" width="2.59765625" style="360" customWidth="1"/>
+    <col min="2" max="2" width="22.73046875" style="360" customWidth="1"/>
+    <col min="3" max="5" width="20.73046875" style="360" customWidth="1"/>
+    <col min="6" max="16384" width="9.06640625" style="360"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:5" ht="13.9">
-      <c r="B2" s="370" t="s">
+      <c r="B2" s="358" t="s">
         <v>456</v>
       </c>
-      <c r="C2" s="371"/>
-      <c r="D2" s="371"/>
-      <c r="E2" s="371"/>
+      <c r="C2" s="359"/>
+      <c r="D2" s="359"/>
+      <c r="E2" s="359"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/financial_models/opportunities/300481.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/300481.SZ_Valuation.xlsx
@@ -8,45 +8,46 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B685264-67C8-459A-B17B-157DDE0EE77E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3417BC96-91DA-4A6F-8125-E4752006199F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Thesis" sheetId="6" r:id="rId1"/>
-    <sheet name="Data" sheetId="4" r:id="rId2"/>
-    <sheet name="BS" sheetId="3" r:id="rId3"/>
-    <sheet name="Normalized_FCF" sheetId="2" r:id="rId4"/>
-    <sheet name="DCF" sheetId="8" r:id="rId5"/>
-    <sheet name="DDM" sheetId="10" r:id="rId6"/>
-    <sheet name="Scenarios" sheetId="9" r:id="rId7"/>
-    <sheet name="Breakdown" sheetId="12" r:id="rId8"/>
+    <sheet name="投资主题" sheetId="12" r:id="rId1"/>
+    <sheet name="Thesis" sheetId="6" r:id="rId2"/>
+    <sheet name="Data" sheetId="4" r:id="rId3"/>
+    <sheet name="BS" sheetId="3" r:id="rId4"/>
+    <sheet name="Normalized_FCF" sheetId="2" r:id="rId5"/>
+    <sheet name="DCF" sheetId="8" r:id="rId6"/>
+    <sheet name="DDM" sheetId="10" r:id="rId7"/>
+    <sheet name="Scenarios" sheetId="9" r:id="rId8"/>
+    <sheet name="Breakdown" sheetId="13" r:id="rId9"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId9"/>
+    <externalReference r:id="rId10"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">DCF!$B$73:$H$73</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">DDM!$B$68:$H$68</definedName>
-    <definedName name="Common_Shares" localSheetId="7">[1]Thesis!$C$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">DCF!$B$73:$H$73</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">DDM!$B$68:$H$68</definedName>
+    <definedName name="Common_Shares" localSheetId="8">[1]Thesis!$C$6</definedName>
     <definedName name="Common_Shares">Thesis!$C$6</definedName>
-    <definedName name="dividend_tax_rate" localSheetId="7">[1]Normalized_FCF!$C$93</definedName>
+    <definedName name="dividend_tax_rate" localSheetId="8">[1]Normalized_FCF!$C$93</definedName>
     <definedName name="dividend_tax_rate">Normalized_FCF!$C$93</definedName>
-    <definedName name="Equity_Cost" localSheetId="7">[1]Thesis!$C$86</definedName>
+    <definedName name="Equity_Cost" localSheetId="8">[1]Thesis!$C$86</definedName>
     <definedName name="Equity_Cost">Thesis!$C$86</definedName>
-    <definedName name="Exchange_Rate" localSheetId="7">[1]Thesis!$C$16</definedName>
+    <definedName name="Exchange_Rate" localSheetId="8">[1]Thesis!$C$16</definedName>
     <definedName name="Exchange_Rate">Thesis!$C$16</definedName>
-    <definedName name="Market_currency" localSheetId="7">[1]Thesis!$C$13</definedName>
+    <definedName name="Market_currency" localSheetId="8">[1]Thesis!$C$13</definedName>
     <definedName name="Market_currency">Thesis!$C$13</definedName>
-    <definedName name="Market_Price" localSheetId="7">[1]Thesis!$C$12</definedName>
+    <definedName name="Market_Price" localSheetId="8">[1]Thesis!$C$12</definedName>
     <definedName name="Market_Price">Thesis!$C$12</definedName>
-    <definedName name="Reporting_currency" localSheetId="7">[1]Thesis!$C$25</definedName>
+    <definedName name="Reporting_currency" localSheetId="8">[1]Thesis!$C$25</definedName>
     <definedName name="Reporting_currency">Thesis!$C$25</definedName>
-    <definedName name="scaling_factor" localSheetId="7">[1]Data!$C$3</definedName>
+    <definedName name="scaling_factor" localSheetId="8">[1]Data!$C$3</definedName>
     <definedName name="scaling_factor">Data!$C$3</definedName>
-    <definedName name="Terminal_Growth" localSheetId="7">[1]Thesis!$C$92</definedName>
+    <definedName name="Terminal_Growth" localSheetId="8">[1]Thesis!$C$92</definedName>
     <definedName name="Terminal_Growth">Thesis!$C$92</definedName>
-    <definedName name="valuation_method" localSheetId="7">[1]Thesis!$E$21</definedName>
+    <definedName name="valuation_method" localSheetId="8">[1]Thesis!$E$21</definedName>
     <definedName name="valuation_method">Thesis!$E$21</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -55,20 +56,14 @@
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext uri="GoogleSheetsCustomDataVersion1">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId10" roundtripDataSignature="AMtx7mi73Cg0ax9bLfpeUuF69nNRn7idDQ=="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId11" roundtripDataSignature="AMtx7mi73Cg0ax9bLfpeUuF69nNRn7idDQ=="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="687" uniqueCount="466">
-  <si>
-    <t>Number of Shares:</t>
-  </si>
-  <si>
-    <t>Exchange Rate:</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="836" uniqueCount="560">
   <si>
     <t>Sales</t>
   </si>
@@ -411,10 +406,6 @@
   </si>
   <si>
     <t>Debt/EBIT</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Market Price:</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1348,10 +1339,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Update Required After:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>FCFE/Market Cap</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1504,10 +1491,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Report Interval:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Note of the formulas:</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1525,10 +1508,6 @@
   </si>
   <si>
     <t>Note on the logic</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Company Name</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1760,71 +1739,11 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Step 2: The No-Growth Baseline (Calculating Stable Income Value)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Note:</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>Step 3: Adjusting for Financial Structure (Calculating No Growth Equity Value)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Step 4: Incorporating Future Potential &amp; Risk (Scenario Analysis)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t xml:space="preserve">Guidance Note: </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>This model determines a target buy price consistent with defined investment criteria. It follows a logical progression: establishing current sustainable earnings, adjusting for financial structure, incorporating growth scenarios, and finally applying the investor’s required return.</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>Goal:</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t xml:space="preserve"> To quantify the underlying FCFE the business consistently generates for its equity owners, stripping away temporary fluctuations or accounting choices.The FCFE/Market Cap yield gives a direct measure of this cash generation relative to the current market price.</t>
-    </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1864,32 +1783,6 @@
         <family val="2"/>
         <scheme val="major"/>
       </rPr>
-      <t>Goal:</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t xml:space="preserve"> To determine the intrinsic value of the company’s equity if the Normalized FCFE (calculated in Step 1) were to remain constant perpetually, with zero future growth. This establishes a baseline value derived solely from the current sustainable earnings power.</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
       <t>Cost of Equity:</t>
     </r>
     <r>
@@ -1987,30 +1880,6 @@
     <r>
       <rPr>
         <b/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>Goal:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t xml:space="preserve"> To estimate the company’s intrinsic value by considering plausible future scenarios beyond the static no-growth assumption. Based on fundamental research, each scenario defines high growth periods (HGP), high growth rates (HGR), and its probability.</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
         <i/>
         <sz val="9"/>
         <color rgb="FF000000"/>
@@ -2034,58 +1903,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>Calculation Logic:</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t xml:space="preserve"> The Target Buy Price is determined by discounting future cash flows—expected annual dividends and the Expected Equity Value—at the Target Annual Return, realized over the holding period.</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>Insight:</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t xml:space="preserve"> Significant market volatility is analyzed as an indicator of the range of market-perceived outcomes, including extremes that define boundaries for scenarios like "Snowball" or "Devil’s Advocate." Scenario Analysis then filters these using fundamental reasoning to evaluate their likelihood.</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>CFO</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2103,23 +1920,6 @@
   </si>
   <si>
     <t>Key Risk Factors</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Goal: </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
-      <t>To identify and assess the key risk factors inherent in this valuation model, focusing on those with the greatest potential impact on the final result.</t>
-    </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -2162,10 +1962,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>The Cost of Equity is established as an investor’s hurdle rate. This rate serves as an opportunity cost threshold for capital allocation, prioritizing consistency and long-term decision-making over market-derived metrics.The model calculates intrinsic value using a standardized base cost of equity as the discount rate in DCF analysis. This rate serves as the minimum acceptable long-term return threshold, reflecting long-term risk-free rates plus an equity risk premium to account for ownership risks.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>- The Expected Equity Value is heavily dependent on the specific growth rates (HGR), durations (HGP), and probabilities assigned to each scenario. These are inherently forecasts about an uncertain future.</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2284,10 +2080,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Step 5: Determining the Investment Decision</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>@Selling Yield</t>
     <phoneticPr fontId="28" type="noConversion"/>
   </si>
@@ -2334,133 +2126,1148 @@
     <t>Market Currency</t>
   </si>
   <si>
+    <t>Listing Information</t>
+  </si>
+  <si>
+    <t>@Benchmark Yield</t>
+  </si>
+  <si>
+    <t>Exit Price Output</t>
+  </si>
+  <si>
+    <t>Benchmark Yield</t>
+  </si>
+  <si>
+    <t>Target return</t>
+  </si>
+  <si>
+    <t>Target Price</t>
+  </si>
+  <si>
+    <t>Entry Price</t>
+  </si>
+  <si>
+    <t>Sell Price</t>
+  </si>
+  <si>
+    <t>Exit Price</t>
+  </si>
+  <si>
+    <t>Holding Period</t>
+  </si>
+  <si>
+    <t>Risk Premium</t>
+  </si>
+  <si>
+    <t>Base Cost of Equity</t>
+  </si>
+  <si>
+    <t>Result (Exit)</t>
+  </si>
+  <si>
+    <t>Valuation Outputs</t>
+  </si>
+  <si>
+    <t>Business Model Risk Premium:</t>
+  </si>
+  <si>
+    <t>Management Risk Premium:</t>
+  </si>
+  <si>
+    <t>Base equity cost</t>
+  </si>
+  <si>
+    <t>Entry yield</t>
+  </si>
+  <si>
+    <t>Benchmark yield</t>
+  </si>
+  <si>
+    <t>Valuation Method</t>
+  </si>
+  <si>
+    <t>Dividend</t>
+  </si>
+  <si>
+    <t>Dividend Value</t>
+  </si>
+  <si>
+    <t>No-Growth DDM</t>
+  </si>
+  <si>
+    <t>No-Growth DDM Valuation</t>
+  </si>
+  <si>
+    <t>Dividend Value per share</t>
+  </si>
+  <si>
+    <t>PV of Dividends</t>
+  </si>
+  <si>
+    <t>Dividends</t>
+  </si>
+  <si>
+    <t>YoY CAGR</t>
+  </si>
+  <si>
+    <t>Payout Ratio:</t>
+  </si>
+  <si>
+    <t>No Growth Equity Value per share =</t>
+  </si>
+  <si>
+    <t>DuPont Analysis</t>
+  </si>
+  <si>
+    <t>ROE =</t>
+  </si>
+  <si>
+    <t>Normalized</t>
+  </si>
+  <si>
+    <t>Latest</t>
+  </si>
+  <si>
+    <t>LT AR and Prepayments</t>
+  </si>
+  <si>
+    <t>Dividend after tax Yield</t>
+  </si>
+  <si>
+    <t>Dividend tax rate</t>
+  </si>
+  <si>
+    <t>After tax Dividend/Market Cap =</t>
+  </si>
+  <si>
+    <t>After-tax Dividend per share</t>
+  </si>
+  <si>
+    <t>Divisional Analysis (Optional)</t>
+  </si>
+  <si>
+    <t>模型最后更新日期:</t>
+  </si>
+  <si>
+    <t>执行摘要</t>
+  </si>
+  <si>
+    <t>公司信息</t>
+  </si>
+  <si>
+    <t>上市信息</t>
+  </si>
+  <si>
+    <t>增长分类:</t>
+  </si>
+  <si>
+    <t>对比板块:</t>
+  </si>
+  <si>
+    <t>商业模式风险溢价:</t>
+  </si>
+  <si>
+    <t>管理风险溢价:</t>
+  </si>
+  <si>
+    <t>报告货币:</t>
+  </si>
+  <si>
+    <t>市场隐含年回报率:</t>
+  </si>
+  <si>
+    <t>估值方法</t>
+  </si>
+  <si>
+    <t>估值输出</t>
+  </si>
+  <si>
+    <t>目标价格</t>
+  </si>
+  <si>
+    <t>入场价格</t>
+  </si>
+  <si>
+    <t>卖出价格</t>
+  </si>
+  <si>
+    <t>退出价格</t>
+  </si>
+  <si>
+    <t>持有期</t>
+  </si>
+  <si>
+    <t>入场收益率</t>
+  </si>
+  <si>
+    <t>目标回报率</t>
+  </si>
+  <si>
+    <t>基准收益率</t>
+  </si>
+  <si>
+    <t>步骤1：确定公司可持续盈利能力（计算标准化FCFE）</t>
+  </si>
+  <si>
+    <t>Company Name:</t>
+  </si>
+  <si>
+    <t>Number of Shares:</t>
+  </si>
+  <si>
+    <t>Report Interval:</t>
+  </si>
+  <si>
+    <t>Update Required After:</t>
+  </si>
+  <si>
     <t>Symbol:</t>
   </si>
   <si>
-    <t>Listing Information</t>
+    <t>Market Price:</t>
+  </si>
+  <si>
+    <t>Market Currency:</t>
+  </si>
+  <si>
+    <t>Market Capitalization:</t>
   </si>
   <si>
     <t>Forex Symbol:</t>
   </si>
   <si>
-    <t>Capitalization:</t>
-  </si>
-  <si>
-    <t>@Benchmark Yield</t>
-  </si>
-  <si>
-    <t>Exit Price Output</t>
-  </si>
-  <si>
-    <t>Benchmark Yield</t>
-  </si>
-  <si>
-    <t>Target return</t>
-  </si>
-  <si>
-    <t>Target Price</t>
-  </si>
-  <si>
-    <t>Entry Price</t>
-  </si>
-  <si>
-    <t>Sell Price</t>
-  </si>
-  <si>
-    <t>Exit Price</t>
-  </si>
-  <si>
-    <t>Holding Period</t>
-  </si>
-  <si>
-    <t>Risk Premium</t>
-  </si>
-  <si>
-    <t>Base Cost of Equity</t>
-  </si>
-  <si>
-    <t>Result (Exit)</t>
-  </si>
-  <si>
-    <t>Valuation Outputs</t>
-  </si>
-  <si>
-    <t>Business Model Risk Premium:</t>
-  </si>
-  <si>
-    <t>Management Risk Premium:</t>
-  </si>
-  <si>
-    <t>Base equity cost</t>
-  </si>
-  <si>
-    <t>Entry yield</t>
-  </si>
-  <si>
-    <t>Benchmark yield</t>
-  </si>
-  <si>
-    <t>Valuation Method</t>
-  </si>
-  <si>
-    <t>Dividend</t>
-  </si>
-  <si>
-    <t>Dividend Value</t>
-  </si>
-  <si>
-    <t>No-Growth DDM</t>
-  </si>
-  <si>
-    <t>No-Growth DDM Valuation</t>
-  </si>
-  <si>
-    <t>Dividend Value per share</t>
-  </si>
-  <si>
-    <t>PV of Dividends</t>
-  </si>
-  <si>
-    <t>Dividends</t>
-  </si>
-  <si>
-    <t>YoY CAGR</t>
-  </si>
-  <si>
-    <t>Payout Ratio:</t>
-  </si>
-  <si>
-    <t>No Growth Equity Value per share =</t>
-  </si>
-  <si>
-    <t>DuPont Analysis</t>
-  </si>
-  <si>
-    <t>ROE =</t>
-  </si>
-  <si>
-    <t>Normalized</t>
-  </si>
-  <si>
-    <t>Latest</t>
-  </si>
-  <si>
-    <t>LT AR and Prepayments</t>
-  </si>
-  <si>
-    <t>Dividend after tax Yield</t>
-  </si>
-  <si>
-    <t>Dividend tax rate</t>
-  </si>
-  <si>
-    <t>After tax Dividend/Market Cap =</t>
-  </si>
-  <si>
-    <t>After-tax Dividend per share</t>
-  </si>
-  <si>
-    <t>Divisional Analysis (Optional)</t>
+    <t>Exchange Rate:</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve">Guidance Note: </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>This model evaluates the company using a structured investment process to determine its intrinsic value and target prices. It focuses on sustainable FCF capacity, adjusts for financial structure, incorporates growth scenarios, and calculates expected returns based on the derived intrinsic value.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Goal:</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> To quantify the underlying FCFE the business consistently generates, stripping away temporary fluctuations or accounting choices.</t>
+    </r>
+  </si>
+  <si>
+    <t>Step 2: Calculating the No-Growth Baseline (Calculating Stable Income Value)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Goal:</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> Determine the intrinsic value assuming the current Normalized FCFE remains constant with no growth, providing a conservative baseline.</t>
+    </r>
+  </si>
+  <si>
+    <t>Step 4: Incorporating Future Potential (Scenario Analysis)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Goal:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> Estimate intrinsic value by modeling plausible FCFE/Dividend, high growth periods (HGP), and high growth rates (HGR) scenarios, weighted by probability.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Insight:</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> Significant market volatility is analyzed as an indicator of the range of market-perceived outcomes, including extremes that define boundaries for scenarios like "Snowball" or "Devil’s Advocate." Scenario Analysis then filters these using fundamental reasoning to evaluate their likelihood.</t>
+    </r>
+  </si>
+  <si>
+    <t>Step 5: Determining Investment Decisions</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Calculation Logic:</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> Discount future dividends and the expected equity value at the target return rates.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Goal: </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Highlight risks impacting the valuation, focusing on factors affecting FCFE/dividend sustainability.</t>
+    </r>
+  </si>
+  <si>
+    <t>The Cost of Equity is established as an investor’s hurdle rate. This rate serves as an opportunity cost threshold for capital allocation.The model calculates intrinsic value using a standardized base cost of equity as the discount rate in DCF/DDM analysis. This rate serves as the minimum acceptable long-term return threshold, reflecting long-term risk-free rates plus an equity risk premium.</t>
+  </si>
+  <si>
+    <t>公司名称：</t>
+  </si>
+  <si>
+    <t>股份数量：</t>
+  </si>
+  <si>
+    <t>报告间隔：</t>
+  </si>
+  <si>
+    <t>下次更新日期：</t>
+  </si>
+  <si>
+    <t>股票代码：</t>
+  </si>
+  <si>
+    <t>市场价格：</t>
+  </si>
+  <si>
+    <t>市价货币：</t>
+  </si>
+  <si>
+    <t>市值：</t>
+  </si>
+  <si>
+    <t>外汇符号：</t>
+  </si>
+  <si>
+    <t>汇率：</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>指导说明：</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>该模型使用结构化的投资流程来评估公司，确定其内在价值和目标价格。它关注可持续的自由现金流（FCF）能力，调整财务结构，纳入增长情景，并根据得出的内在价值计算预期回报。</t>
+    </r>
+  </si>
+  <si>
+    <t>估值概述</t>
+  </si>
+  <si>
+    <t>基础Equity Cost</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>目标：</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>量化业务持续生成的潜在自由现金流（FCFE），去除临时波动或会计选择的影响。</t>
+    </r>
+  </si>
+  <si>
+    <t>关键组成部分</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">• </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Normalized Operating EBIT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>：核心业务运营的税前息前利润，调整以剔除一次性或非经常性项目，形成可持续盈利基础。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">• </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Depreciation &amp; Amortization (D&amp;A):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> 非现金费用，加入以反映运营产生的现金。
+• </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Capital Expenditures (Capex)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>: 维持或扩展运营资产所需的现金流出。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">• </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve">Stable Non-Operating EBIT: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>来自非核心资产的持续收益，如固定收益投资、支付股息的股票或租赁物业。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">• </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Net Interest Income:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> 利息收入减去利息支出</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>• NCI’s Share of Profits:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> NCI代表子公司中母公司未拥有的股权部分。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">• </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Working Capital Investment (WCInv):</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> WCInv仅在显著扭曲FCFE时纳入。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>关于净借款的说明：</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>理论上，本金偿还通过净借款核算。然而，该模型旨在避免明确预测债务发行或偿还。相反，本金偿还通过有息债务在股权价值调整中反映。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>洞察：</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>这一步骤通过纳入运营和稳定的非运营来源，同时考虑税金和再投资需求，确保现金流的全面衡量。</t>
+    </r>
+  </si>
+  <si>
+    <t>最新FCFE =</t>
+  </si>
+  <si>
+    <t>派息比率:</t>
+  </si>
+  <si>
+    <t>最新</t>
+  </si>
+  <si>
+    <t>步骤2：计算无增长基线（计算稳定收入价值）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>目标：</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>确定内在价值，假设当前的标准化FCFE保持不变且无增长，提供保守的基线。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Cost of Equity:</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> 反映公司的风险概况，代表投资者为承担拥有此类业务一般风险所需的最低回报，而目标年回报率作为投资者要求的回报率。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Terminal Growth Rate:</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> 将g设为0%是一个保守假设，仅基于公司当前表现的盈利能力估值，不依赖潜在乐观的未来增长预测。</t>
+    </r>
+  </si>
+  <si>
+    <t>步骤3：调整财务结构（计算无增长股权价值）</t>
+  </si>
+  <si>
+    <t>目标：通过纳入公司的资产负债表结构，细化稳定收入价值（SIV）。</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>关于债务的说明：</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>总有息债务包括本金偿还。理想情况下，应根据偿还时间表贴现。但为简单和保守起见，该模型使用总有息债务的账面价值。</t>
+    </r>
+  </si>
+  <si>
+    <t>说明：</t>
+  </si>
+  <si>
+    <t>杜邦分析</t>
+  </si>
+  <si>
+    <t>• Non-Operating Cash: 运营不需要的超额现金</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">• </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Other Non-Operating Assets:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> 不贡献FCFE的资产（如非收益性投资或物业）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>洞察：</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>无增长股权价值每股代表公司在考虑未来增长潜力前，基于当前可持续运营和净财务状况的内在价值估计，作为基本锚定的估值基线。</t>
+    </r>
+  </si>
+  <si>
+    <t>无增长股权价值每股 =</t>
+  </si>
+  <si>
+    <t>步骤4：纳入未来潜力（情景分析）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>目标：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>通过建模合理的FCFE/股息、高增长期（HGP）和高增长率（HGR）情景，并按概率加权，估计内在价值。</t>
+    </r>
+  </si>
+  <si>
+    <t>情景</t>
+  </si>
+  <si>
+    <t>HGR</t>
+  </si>
+  <si>
+    <t>每股EV</t>
+  </si>
+  <si>
+    <t>概率</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>洞察：</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>分析市场大幅波动作为市场感知结果范围的指标，包括定义“雪球”或“魔鬼代言人”等情景边界的极端情况。情景分析使用基本推理评估这些情景的可能性。</t>
+    </r>
+  </si>
+  <si>
+    <t>步骤5：确定投资决策</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>目标：</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>将公司内在价值估计（来自步骤4）转化为满足特定投资要求的具体买入价格。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>计算逻辑：</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>The Target Buy Price is determined by discounting future cash flows—expected annual dividends and the Expected Equity Value—at the Target Annual Return, realized over the holding period.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">预期持有期 = </t>
+  </si>
+  <si>
+    <t>目标年回报率 =</t>
+  </si>
+  <si>
+    <t xml:space="preserve">每股年度股息 = </t>
+  </si>
+  <si>
+    <t>结果 (Target)</t>
+  </si>
+  <si>
+    <t>市场货币</t>
+  </si>
+  <si>
+    <t>@ 安全边际</t>
+  </si>
+  <si>
+    <r>
+      <t>目标：</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>关注影响FCFE/股息可持续性的估值风险因素。</t>
+    </r>
+  </si>
+  <si>
+    <t>关键风险因素</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>标准化FCFE的准确性</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>, 受不确定性影响，包括：</t>
+    </r>
+  </si>
+  <si>
+    <t>- 可持续收入和利润率</t>
+  </si>
+  <si>
+    <t>- 资本支出</t>
+  </si>
+  <si>
+    <t>- 营运资金</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">2. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Cost of Equity的适当性</t>
+    </r>
+  </si>
+  <si>
+    <t>作为资本配置的机会成本门槛。该模型在DCF/DDM分析中使用标准化的贴现率，计算内在价值。此利率作为最低可接受的长期回报门槛，反映长期无风险利率加上股权风险溢价。</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">3. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>增长情景的可靠性</t>
+    </r>
+  </si>
+  <si>
+    <t>- 预期股权价值高度依赖各情景的特定增长率（HGR）、持续时间（HGP）和概率，这些是对不确定未来的预测。</t>
+  </si>
+  <si>
+    <t>- 极端情景（“雪球”、“魔鬼代言人”）概率较低；若市场条件剧变，可能变得比预期更相关。</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">4. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>外部和公司特定风险</t>
+    </r>
+  </si>
+  <si>
+    <t>- 宏观经济敏感性</t>
+  </si>
+  <si>
+    <t>- 投入成本波动</t>
+  </si>
+  <si>
+    <t>- 激烈竞争等</t>
+  </si>
+  <si>
+    <t>Est. (Net Asset) Realizable Value</t>
+  </si>
+  <si>
+    <t>估计(净资产)可变现价值</t>
   </si>
   <si>
     <t>CN</t>
@@ -3168,7 +3975,7 @@
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
     <xf numFmtId="0" fontId="59" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="373">
+  <cellXfs count="382">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3917,33 +4724,55 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="177" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="175" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="59" fillId="0" borderId="1" xfId="2"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
@@ -3958,10 +4787,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="1" xfId="2"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="2" xr:uid="{84E26CB8-48BA-41B7-A5C3-FFB4C4D26709}"/>
+    <cellStyle name="常规 2" xfId="2" xr:uid="{8C4A8B21-D36C-4E74-AD26-7653C3D45E31}"/>
     <cellStyle name="常规 2 2" xfId="1" xr:uid="{A35F4541-DCCE-4554-A311-39480A36979A}"/>
   </cellStyles>
   <dxfs count="8">
@@ -4073,7 +4907,7 @@
         </row>
         <row r="12">
           <cell r="C12">
-            <v>14.64</v>
+            <v>14.57</v>
           </cell>
         </row>
         <row r="13">
@@ -4098,7 +4932,7 @@
         </row>
         <row r="86">
           <cell r="C86">
-            <v>0.06</v>
+            <v>7.4999999999999997E-2</v>
           </cell>
         </row>
         <row r="92">
@@ -4328,6 +5162,1749 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA287911-AF8F-41DE-9E8E-72556F041FFB}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:J197"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
+  <cols>
+    <col min="1" max="1" width="2.73046875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="32.73046875" style="1" customWidth="1"/>
+    <col min="3" max="4" width="25.73046875" style="1" customWidth="1"/>
+    <col min="5" max="6" width="15.73046875" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10">
+      <c r="B1" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="C1" s="33">
+        <f>Thesis!C1</f>
+        <v>45797</v>
+      </c>
+      <c r="D1" s="358" t="str">
+        <f>Thesis!D1</f>
+        <v>CN</v>
+      </c>
+      <c r="E1" s="292" t="s">
+        <v>344</v>
+      </c>
+      <c r="F1" s="307" t="str">
+        <f>Thesis!F1</f>
+        <v>N</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="13.9">
+      <c r="A2" s="222" t="s">
+        <v>438</v>
+      </c>
+      <c r="B2" s="36"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="36"/>
+      <c r="E2" s="36"/>
+      <c r="F2" s="36"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
+      <c r="I2" s="22"/>
+      <c r="J2" s="22"/>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="B4" s="45" t="s">
+        <v>439</v>
+      </c>
+      <c r="C4" s="46"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+    </row>
+    <row r="5" spans="1:10" ht="12.4">
+      <c r="B5" s="4" t="s">
+        <v>479</v>
+      </c>
+      <c r="C5" s="359" t="str">
+        <f>Thesis!C5</f>
+        <v>濮阳惠成</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="B6" s="4" t="s">
+        <v>480</v>
+      </c>
+      <c r="C6" s="34">
+        <f>Common_Shares</f>
+        <v>291855438</v>
+      </c>
+      <c r="E6" s="48"/>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="B7" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="C7" s="360">
+        <f>Thesis!C7</f>
+        <v>6</v>
+      </c>
+      <c r="D7" s="48"/>
+      <c r="E7" s="48"/>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="B8" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="C8" s="33">
+        <f>EOMONTH(EDATE(BS!C1,C7+2),0)</f>
+        <v>45900</v>
+      </c>
+      <c r="E8" s="48"/>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="E9" s="34"/>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="B10" s="45" t="s">
+        <v>440</v>
+      </c>
+      <c r="C10" s="46"/>
+      <c r="E10" s="34"/>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="B11" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="C11" s="365" t="str">
+        <f>Thesis!C11</f>
+        <v>300481.SZ</v>
+      </c>
+      <c r="D11" s="49"/>
+      <c r="E11" s="34"/>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="B12" s="4" t="s">
+        <v>484</v>
+      </c>
+      <c r="C12" s="366">
+        <f>Market_Price</f>
+        <v>14.57</v>
+      </c>
+      <c r="D12" s="50"/>
+      <c r="E12" s="48"/>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="B13" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="C13" s="32" t="str">
+        <f>Market_currency</f>
+        <v>CNY</v>
+      </c>
+      <c r="D13" s="48"/>
+      <c r="E13" s="5"/>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="B14" s="4" t="s">
+        <v>486</v>
+      </c>
+      <c r="C14" s="35">
+        <f>投资主题!C12*Common_Shares/1000000</f>
+        <v>4252.33373166</v>
+      </c>
+      <c r="D14" s="35" t="str">
+        <f>IF(D11="","",投资主题!D12*Common_Shares/1000000)</f>
+        <v/>
+      </c>
+      <c r="E14" s="5"/>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="B15" s="4" t="s">
+        <v>487</v>
+      </c>
+      <c r="C15" s="32" t="str">
+        <f>IF(C25=C13,C13,C25&amp;"/"&amp;C13)</f>
+        <v>CNY</v>
+      </c>
+      <c r="D15" s="32" t="str">
+        <f>IF(D11="","",IF(C25=D13,D13,C25&amp;"/"&amp;D13))</f>
+        <v/>
+      </c>
+      <c r="E15" s="5"/>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="B16" s="4" t="s">
+        <v>488</v>
+      </c>
+      <c r="C16" s="366">
+        <f>Exchange_Rate</f>
+        <v>1</v>
+      </c>
+      <c r="D16" s="50"/>
+      <c r="E16" s="5"/>
+    </row>
+    <row r="17" spans="2:6">
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+    </row>
+    <row r="18" spans="2:6" ht="24.6" customHeight="1">
+      <c r="B18" s="371" t="s">
+        <v>489</v>
+      </c>
+      <c r="C18" s="371"/>
+      <c r="D18" s="371"/>
+      <c r="E18" s="371"/>
+      <c r="F18" s="371"/>
+    </row>
+    <row r="20" spans="2:6">
+      <c r="B20" s="45" t="s">
+        <v>490</v>
+      </c>
+      <c r="C20" s="46"/>
+      <c r="D20" s="5"/>
+    </row>
+    <row r="21" spans="2:6">
+      <c r="B21" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="C21" s="32" t="str">
+        <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
+        <v xml:space="preserve">Low Growth </v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="E21" s="363" t="str">
+        <f>valuation_method</f>
+        <v>DCF</v>
+      </c>
+    </row>
+    <row r="22" spans="2:6">
+      <c r="B22" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="C22" s="32" t="str">
+        <f>Thesis!C22</f>
+        <v>IND_01</v>
+      </c>
+      <c r="D22" s="1" t="str">
+        <f>IF(valuation_method="DDM","终值贴现率","")</f>
+        <v/>
+      </c>
+      <c r="E22" s="364">
+        <f>Thesis!E22</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="2:6">
+      <c r="B23" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="C23" s="253" t="str">
+        <f>Thesis!C23</f>
+        <v>N</v>
+      </c>
+    </row>
+    <row r="24" spans="2:6">
+      <c r="B24" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="C24" s="253" t="str">
+        <f>Thesis!C24</f>
+        <v>N</v>
+      </c>
+    </row>
+    <row r="25" spans="2:6">
+      <c r="B25" s="4" t="s">
+        <v>445</v>
+      </c>
+      <c r="C25" s="32" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+      <c r="D25" s="32" t="str">
+        <f>IF(D11="","",Market_currency&amp;"/"&amp;D13&amp;":")</f>
+        <v/>
+      </c>
+      <c r="E25" s="299" t="str">
+        <f>IF(D11="","",1/Exchange_Rate*D16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" spans="2:6">
+      <c r="B26" s="1" t="str">
+        <f>"预期股权价值 ("&amp;C13&amp;") :"</f>
+        <v>预期股权价值 (CNY) :</v>
+      </c>
+      <c r="C26" s="304">
+        <f>C132</f>
+        <v>8.6992744860027944</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="E26" s="301">
+        <f ca="1">Scenarios!C87</f>
+        <v>-0.1284274085979954</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6">
+      <c r="D27" s="5"/>
+      <c r="E27" s="5"/>
+    </row>
+    <row r="28" spans="2:6">
+      <c r="B28" s="45" t="s">
+        <v>448</v>
+      </c>
+      <c r="C28" s="309" t="str">
+        <f>C145&amp;" ("&amp;Market_currency&amp;")"</f>
+        <v>300481.SZ (CNY)</v>
+      </c>
+      <c r="D28" s="309" t="str">
+        <f>IF(D11="","",D145&amp;" ("&amp;D13&amp;")")</f>
+        <v/>
+      </c>
+      <c r="E28" s="305" t="s">
+        <v>453</v>
+      </c>
+      <c r="F28" s="361">
+        <f>Thesis!F28</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="2:6">
+      <c r="B29" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="C29" s="310">
+        <f>C149</f>
+        <v>3.3910941772119543</v>
+      </c>
+      <c r="D29" s="310" t="str">
+        <f>D149</f>
+        <v/>
+      </c>
+      <c r="E29" s="306" t="s">
+        <v>455</v>
+      </c>
+      <c r="F29" s="362">
+        <f>Thesis!F29</f>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6">
+      <c r="B30" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="C30" s="311">
+        <f>C157</f>
+        <v>4.6134157878938522</v>
+      </c>
+      <c r="D30" s="311" t="str">
+        <f>D157</f>
+        <v/>
+      </c>
+      <c r="E30" s="307" t="s">
+        <v>454</v>
+      </c>
+      <c r="F30" s="224">
+        <f>Thesis!F30</f>
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="31" spans="2:6">
+      <c r="B31" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="C31" s="311">
+        <f>C165</f>
+        <v>7.9387622109270746</v>
+      </c>
+      <c r="D31" s="311" t="str">
+        <f>D165</f>
+        <v/>
+      </c>
+      <c r="E31" s="307" t="s">
+        <v>491</v>
+      </c>
+      <c r="F31" s="224">
+        <f>Thesis!F31</f>
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="2:6">
+      <c r="B32" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="C32" s="311">
+        <f>C173</f>
+        <v>7.6893682545464594</v>
+      </c>
+      <c r="D32" s="311" t="str">
+        <f>D173</f>
+        <v/>
+      </c>
+      <c r="E32" s="307" t="s">
+        <v>456</v>
+      </c>
+      <c r="F32" s="224">
+        <f>Thesis!F32</f>
+        <v>8.6999999999999994E-2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="D33" s="5"/>
+      <c r="E33" s="5"/>
+    </row>
+    <row r="34" spans="1:6" ht="13.9">
+      <c r="A34" s="222" t="s">
+        <v>457</v>
+      </c>
+      <c r="B34" s="36"/>
+      <c r="C34" s="36"/>
+      <c r="D34" s="36"/>
+      <c r="E34" s="36"/>
+      <c r="F34" s="36"/>
+    </row>
+    <row r="36" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B36" s="371" t="s">
+        <v>492</v>
+      </c>
+      <c r="C36" s="371"/>
+      <c r="D36" s="371"/>
+      <c r="E36" s="371"/>
+      <c r="F36" s="371"/>
+    </row>
+    <row r="37" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B37" s="374" t="s">
+        <v>330</v>
+      </c>
+      <c r="C37" s="374"/>
+      <c r="D37" s="374"/>
+      <c r="E37" s="374"/>
+      <c r="F37" s="374"/>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="B39" s="210" t="s">
+        <v>493</v>
+      </c>
+      <c r="C39" s="108">
+        <f>scaling_factor</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6">
+      <c r="B40" s="367" t="s">
+        <v>494</v>
+      </c>
+      <c r="C40" s="367"/>
+      <c r="D40" s="367"/>
+      <c r="E40" s="367"/>
+      <c r="F40" s="367"/>
+    </row>
+    <row r="41" spans="1:6">
+      <c r="B41" s="47" t="s">
+        <v>228</v>
+      </c>
+      <c r="C41" s="349">
+        <f>Normalized_FCF!C8</f>
+        <v>174475161</v>
+      </c>
+      <c r="D41" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6">
+      <c r="B42" s="47"/>
+      <c r="C42" s="76"/>
+    </row>
+    <row r="43" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B43" s="367" t="s">
+        <v>495</v>
+      </c>
+      <c r="C43" s="367"/>
+      <c r="D43" s="367"/>
+      <c r="E43" s="367"/>
+      <c r="F43" s="367"/>
+    </row>
+    <row r="44" spans="1:6">
+      <c r="B44" s="47" t="s">
+        <v>230</v>
+      </c>
+      <c r="C44" s="349">
+        <f>Normalized_FCF!C9</f>
+        <v>61093655</v>
+      </c>
+      <c r="D44" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6">
+      <c r="B45" s="52" t="s">
+        <v>231</v>
+      </c>
+      <c r="C45" s="349">
+        <f>Normalized_FCF!C10</f>
+        <v>-61093655</v>
+      </c>
+      <c r="D45" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6">
+      <c r="B47" s="367" t="s">
+        <v>496</v>
+      </c>
+      <c r="C47" s="367"/>
+      <c r="D47" s="367"/>
+      <c r="E47" s="367"/>
+      <c r="F47" s="367"/>
+    </row>
+    <row r="48" spans="1:6">
+      <c r="B48" s="47" t="s">
+        <v>233</v>
+      </c>
+      <c r="C48" s="349">
+        <f>Normalized_FCF!C11</f>
+        <v>0</v>
+      </c>
+      <c r="D48" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="50" spans="2:6">
+      <c r="B50" s="367" t="s">
+        <v>497</v>
+      </c>
+      <c r="C50" s="367"/>
+      <c r="D50" s="367"/>
+      <c r="E50" s="367"/>
+      <c r="F50" s="367"/>
+    </row>
+    <row r="51" spans="2:6">
+      <c r="B51" s="47" t="s">
+        <v>331</v>
+      </c>
+      <c r="C51" s="350">
+        <f>Normalized_FCF!C48</f>
+        <v>3383184.8130000001</v>
+      </c>
+      <c r="D51" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+      <c r="E51" s="286"/>
+      <c r="F51" s="286"/>
+    </row>
+    <row r="52" spans="2:6">
+      <c r="B52" s="47" t="s">
+        <v>332</v>
+      </c>
+      <c r="C52" s="350">
+        <f>Normalized_FCF!C47</f>
+        <v>-5219951</v>
+      </c>
+      <c r="D52" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+      <c r="E52" s="286"/>
+      <c r="F52" s="286"/>
+    </row>
+    <row r="53" spans="2:6">
+      <c r="B53" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="C53" s="349">
+        <f>Normalized_FCF!C12</f>
+        <v>-1836766.1869999999</v>
+      </c>
+      <c r="D53" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="55" spans="2:6">
+      <c r="B55" s="1" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="56" spans="2:6">
+      <c r="B56" s="47" t="s">
+        <v>261</v>
+      </c>
+      <c r="C56" s="349">
+        <f>Normalized_FCF!C15</f>
+        <v>0</v>
+      </c>
+      <c r="D56" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="58" spans="2:6">
+      <c r="B58" s="367" t="s">
+        <v>237</v>
+      </c>
+      <c r="C58" s="367"/>
+      <c r="D58" s="367"/>
+      <c r="E58" s="367"/>
+      <c r="F58" s="367"/>
+    </row>
+    <row r="59" spans="2:6">
+      <c r="B59" s="47" t="s">
+        <v>235</v>
+      </c>
+      <c r="C59" s="349">
+        <f>Normalized_FCF!C14</f>
+        <v>-43159598.703249998</v>
+      </c>
+      <c r="D59" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="61" spans="2:6">
+      <c r="B61" s="367" t="s">
+        <v>499</v>
+      </c>
+      <c r="C61" s="373"/>
+      <c r="D61" s="373"/>
+      <c r="E61" s="373"/>
+      <c r="F61" s="373"/>
+    </row>
+    <row r="62" spans="2:6">
+      <c r="B62" s="47" t="s">
+        <v>238</v>
+      </c>
+      <c r="C62" s="349">
+        <f>Normalized_FCF!C17</f>
+        <v>0</v>
+      </c>
+      <c r="D62" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="64" spans="2:6">
+      <c r="B64" s="371" t="s">
+        <v>500</v>
+      </c>
+      <c r="C64" s="371"/>
+      <c r="D64" s="371"/>
+      <c r="E64" s="371"/>
+      <c r="F64" s="371"/>
+    </row>
+    <row r="65" spans="1:6">
+      <c r="B65" s="371" t="s">
+        <v>501</v>
+      </c>
+      <c r="C65" s="371"/>
+      <c r="D65" s="371"/>
+      <c r="E65" s="371"/>
+      <c r="F65" s="371"/>
+    </row>
+    <row r="67" spans="1:6">
+      <c r="B67" s="47" t="s">
+        <v>502</v>
+      </c>
+      <c r="C67" s="349">
+        <f>Normalized_FCF!G19</f>
+        <v>147540552.86390811</v>
+      </c>
+      <c r="D67" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6">
+      <c r="B68" s="47" t="s">
+        <v>244</v>
+      </c>
+      <c r="C68" s="349">
+        <f>Normalized_FCF!C19</f>
+        <v>129478796.10975</v>
+      </c>
+      <c r="D68" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6">
+      <c r="B69" s="227" t="s">
+        <v>371</v>
+      </c>
+      <c r="C69" s="92">
+        <f>Normalized_FCF!C126</f>
+        <v>3.0448879199141517E-2</v>
+      </c>
+      <c r="F69" s="314"/>
+    </row>
+    <row r="70" spans="1:6">
+      <c r="B70" s="227" t="s">
+        <v>434</v>
+      </c>
+      <c r="C70" s="92">
+        <f>Normalized_FCF!C94</f>
+        <v>2.4708304735758409E-2</v>
+      </c>
+      <c r="E70" s="47" t="s">
+        <v>503</v>
+      </c>
+      <c r="F70" s="315">
+        <f>Normalized_FCF!C92</f>
+        <v>0.90163160847623214</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6">
+      <c r="B72" s="210" t="s">
+        <v>513</v>
+      </c>
+      <c r="C72" s="323" t="s">
+        <v>429</v>
+      </c>
+      <c r="D72" s="323" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6">
+      <c r="B73" s="47" t="s">
+        <v>428</v>
+      </c>
+      <c r="C73" s="92">
+        <f>Normalized_FCF!C121</f>
+        <v>7.1587241945726146E-2</v>
+      </c>
+      <c r="D73" s="92">
+        <f>Normalized_FCF!G121</f>
+        <v>7.2897649409175577E-2</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6">
+      <c r="B74" s="259" t="str">
+        <f>Normalized_FCF!B118</f>
+        <v>Pre-tax Profit/Sales</v>
+      </c>
+      <c r="C74" s="322">
+        <f>Normalized_FCF!C118</f>
+        <v>0.12235120428336442</v>
+      </c>
+      <c r="D74" s="322">
+        <f>Normalized_FCF!G118</f>
+        <v>0.12459084820450472</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6">
+      <c r="B75" s="259" t="str">
+        <f>Normalized_FCF!B119</f>
+        <v>Sales/Total Assets</v>
+      </c>
+      <c r="C75" s="324">
+        <f>Normalized_FCF!C119</f>
+        <v>0.50157874313934503</v>
+      </c>
+      <c r="D75" s="324">
+        <f>Normalized_FCF!G119</f>
+        <v>0.50157874313934503</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6">
+      <c r="B76" s="259" t="str">
+        <f>Normalized_FCF!B120</f>
+        <v>Total Assets/Equity</v>
+      </c>
+      <c r="C76" s="324">
+        <f>Normalized_FCF!C120</f>
+        <v>1.1665094444773738</v>
+      </c>
+      <c r="D76" s="324">
+        <f>Normalized_FCF!G120</f>
+        <v>1.1665094444773738</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" ht="13.9">
+      <c r="A78" s="222" t="s">
+        <v>505</v>
+      </c>
+      <c r="B78" s="36"/>
+      <c r="C78" s="36"/>
+      <c r="D78" s="36"/>
+      <c r="E78" s="36"/>
+      <c r="F78" s="36"/>
+    </row>
+    <row r="79" spans="1:6">
+      <c r="A79" s="209"/>
+    </row>
+    <row r="80" spans="1:6">
+      <c r="A80" s="17"/>
+      <c r="B80" s="371" t="s">
+        <v>506</v>
+      </c>
+      <c r="C80" s="371"/>
+      <c r="D80" s="371"/>
+      <c r="E80" s="371"/>
+      <c r="F80" s="371"/>
+    </row>
+    <row r="81" spans="1:6">
+      <c r="B81" s="374" t="s">
+        <v>248</v>
+      </c>
+      <c r="C81" s="374"/>
+      <c r="D81" s="374"/>
+      <c r="E81" s="374"/>
+      <c r="F81" s="374"/>
+    </row>
+    <row r="83" spans="1:6">
+      <c r="B83" s="210" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6">
+      <c r="B84" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="C84" s="92">
+        <f>F31</f>
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6">
+      <c r="B85" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="C85" s="92">
+        <f>IF(C23="Y",1%,0)+IF(C24="Y",1%,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6">
+      <c r="B86" s="80" t="s">
+        <v>243</v>
+      </c>
+      <c r="C86" s="236">
+        <f>F31+C85</f>
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6">
+      <c r="C87" s="121"/>
+    </row>
+    <row r="88" spans="1:6">
+      <c r="B88" s="293" t="s">
+        <v>512</v>
+      </c>
+      <c r="C88" s="121"/>
+    </row>
+    <row r="89" spans="1:6">
+      <c r="B89" s="371" t="s">
+        <v>507</v>
+      </c>
+      <c r="C89" s="371"/>
+      <c r="D89" s="371"/>
+      <c r="E89" s="371"/>
+      <c r="F89" s="371"/>
+    </row>
+    <row r="90" spans="1:6">
+      <c r="B90" s="371" t="s">
+        <v>508</v>
+      </c>
+      <c r="C90" s="371"/>
+      <c r="D90" s="371"/>
+      <c r="E90" s="371"/>
+      <c r="F90" s="371"/>
+    </row>
+    <row r="92" spans="1:6">
+      <c r="B92" s="47" t="s">
+        <v>247</v>
+      </c>
+      <c r="C92" s="236">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6">
+      <c r="B93" s="47" t="s">
+        <v>275</v>
+      </c>
+      <c r="C93" s="223">
+        <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
+        <v>5.9152022657532255</v>
+      </c>
+      <c r="D93" s="1" t="str">
+        <f>Market_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" ht="13.9">
+      <c r="A95" s="222" t="s">
+        <v>509</v>
+      </c>
+      <c r="B95" s="36"/>
+      <c r="C95" s="36"/>
+      <c r="D95" s="36"/>
+      <c r="E95" s="36"/>
+      <c r="F95" s="36"/>
+    </row>
+    <row r="96" spans="1:6">
+      <c r="A96" s="209"/>
+    </row>
+    <row r="97" spans="2:6">
+      <c r="B97" s="371" t="s">
+        <v>510</v>
+      </c>
+      <c r="C97" s="371"/>
+      <c r="D97" s="371"/>
+      <c r="E97" s="371"/>
+      <c r="F97" s="371"/>
+    </row>
+    <row r="98" spans="2:6">
+      <c r="B98" s="1" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="100" spans="2:6">
+      <c r="B100" s="210" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="101" spans="2:6">
+      <c r="B101" s="371" t="s">
+        <v>511</v>
+      </c>
+      <c r="C101" s="371"/>
+      <c r="D101" s="371"/>
+      <c r="E101" s="371"/>
+      <c r="F101" s="371"/>
+    </row>
+    <row r="102" spans="2:6">
+      <c r="B102" s="47" t="s">
+        <v>251</v>
+      </c>
+      <c r="C102" s="349">
+        <f>DCF!C7</f>
+        <v>100067739.72</v>
+      </c>
+      <c r="D102" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="103" spans="2:6">
+      <c r="B103" s="47" t="s">
+        <v>276</v>
+      </c>
+      <c r="C103" s="223">
+        <f>C102*scaling_factor*Exchange_Rate/Common_Shares</f>
+        <v>0.34286748400418704</v>
+      </c>
+      <c r="D103" s="1" t="str">
+        <f>Market_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="104" spans="2:6">
+      <c r="B104" s="296" t="s">
+        <v>384</v>
+      </c>
+      <c r="C104" s="325">
+        <f>IF(BS!G31/BS!G27&gt;300%,"nm",BS!G31/BS!G27)</f>
+        <v>4.1494671576720196E-2</v>
+      </c>
+    </row>
+    <row r="105" spans="2:6">
+      <c r="B105" s="296" t="s">
+        <v>386</v>
+      </c>
+      <c r="C105" s="326">
+        <f>IF(BS!C50&gt;30,"nm",BS!C50)</f>
+        <v>0.57353573509526667</v>
+      </c>
+    </row>
+    <row r="107" spans="2:6">
+      <c r="B107" s="1" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="108" spans="2:6">
+      <c r="B108" s="47" t="s">
+        <v>260</v>
+      </c>
+      <c r="C108" s="349">
+        <f>BS!C66</f>
+        <v>1012553160.92</v>
+      </c>
+      <c r="D108" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="109" spans="2:6">
+      <c r="B109" s="47" t="s">
+        <v>262</v>
+      </c>
+      <c r="C109" s="349">
+        <f>DCF!C8</f>
+        <v>787007506.71999991</v>
+      </c>
+      <c r="D109" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="110" spans="2:6">
+      <c r="B110" s="47" t="s">
+        <v>277</v>
+      </c>
+      <c r="C110" s="223">
+        <f>C109*scaling_factor*Exchange_Rate/Common_Shares</f>
+        <v>2.6965661908276655</v>
+      </c>
+      <c r="D110" s="1" t="str">
+        <f>Market_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="112" spans="2:6">
+      <c r="B112" s="1" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6">
+      <c r="B113" s="47" t="s">
+        <v>253</v>
+      </c>
+      <c r="C113" s="349">
+        <f>DCF!C9</f>
+        <v>0</v>
+      </c>
+      <c r="D113" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6">
+      <c r="B114" s="47" t="s">
+        <v>278</v>
+      </c>
+      <c r="C114" s="223">
+        <f>C113*scaling_factor*Exchange_Rate/Common_Shares</f>
+        <v>0</v>
+      </c>
+      <c r="D114" s="1" t="str">
+        <f>Market_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6">
+      <c r="B116" s="371" t="s">
+        <v>516</v>
+      </c>
+      <c r="C116" s="371"/>
+      <c r="D116" s="371"/>
+      <c r="E116" s="371"/>
+      <c r="F116" s="371"/>
+    </row>
+    <row r="118" spans="1:6">
+      <c r="B118" s="47" t="s">
+        <v>517</v>
+      </c>
+      <c r="C118" s="223">
+        <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
+        <v>8.268900972576704</v>
+      </c>
+      <c r="D118" s="1" t="str">
+        <f>Market_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6">
+      <c r="B119" s="296" t="s">
+        <v>550</v>
+      </c>
+      <c r="C119" s="223">
+        <f>BS!D47</f>
+        <v>3.275077370273292</v>
+      </c>
+      <c r="D119" s="1" t="str">
+        <f>Market_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" ht="13.9">
+      <c r="A121" s="222" t="s">
+        <v>518</v>
+      </c>
+      <c r="B121" s="36"/>
+      <c r="C121" s="36"/>
+      <c r="D121" s="36"/>
+      <c r="E121" s="36"/>
+      <c r="F121" s="36"/>
+    </row>
+    <row r="123" spans="1:6">
+      <c r="B123" s="367" t="s">
+        <v>519</v>
+      </c>
+      <c r="C123" s="367"/>
+      <c r="D123" s="367"/>
+      <c r="E123" s="367"/>
+      <c r="F123" s="367"/>
+    </row>
+    <row r="125" spans="1:6" ht="12.4">
+      <c r="B125" s="233" t="s">
+        <v>520</v>
+      </c>
+      <c r="C125" s="233" t="s">
+        <v>521</v>
+      </c>
+      <c r="D125" s="233" t="s">
+        <v>108</v>
+      </c>
+      <c r="E125" s="233" t="s">
+        <v>522</v>
+      </c>
+      <c r="F125" s="233" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6">
+      <c r="B126" s="228" t="str">
+        <f>DCF!B74</f>
+        <v>Snowball Scenario</v>
+      </c>
+      <c r="C126" s="229">
+        <f>DCF!C74</f>
+        <v>0.08</v>
+      </c>
+      <c r="D126" s="230">
+        <f>DCF!D74</f>
+        <v>10</v>
+      </c>
+      <c r="E126" s="231" t="str">
+        <f>ROUND(IF(valuation_method="DCF",DCF!E74,DDM!E69),2)&amp;" "&amp;Market_currency</f>
+        <v>10 CNY</v>
+      </c>
+      <c r="F126" s="232">
+        <f>DCF!F74</f>
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6">
+      <c r="B127" s="218" t="str">
+        <f>DCF!B75</f>
+        <v>Optimistic</v>
+      </c>
+      <c r="C127" s="219">
+        <f>DCF!C75</f>
+        <v>0.06</v>
+      </c>
+      <c r="D127" s="220">
+        <f>DCF!D75</f>
+        <v>5</v>
+      </c>
+      <c r="E127" s="231" t="str">
+        <f>ROUND(IF(valuation_method="DCF",DCF!E75,DDM!E70),2)&amp;" "&amp;Market_currency</f>
+        <v>8.85 CNY</v>
+      </c>
+      <c r="F127" s="221">
+        <f>DCF!F75</f>
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6">
+      <c r="B128" s="218" t="str">
+        <f>DCF!B76</f>
+        <v>Base</v>
+      </c>
+      <c r="C128" s="219">
+        <f>DCF!C76</f>
+        <v>0.04</v>
+      </c>
+      <c r="D128" s="220">
+        <f>DCF!D76</f>
+        <v>5</v>
+      </c>
+      <c r="E128" s="231" t="str">
+        <f>ROUND(IF(valuation_method="DCF",DCF!E76,DDM!E71),2)&amp;" "&amp;Market_currency</f>
+        <v>8.65 CNY</v>
+      </c>
+      <c r="F128" s="221">
+        <f>DCF!F76</f>
+        <v>0.53999999999999992</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6">
+      <c r="B129" s="218" t="str">
+        <f>DCF!B77</f>
+        <v>Pessimistic</v>
+      </c>
+      <c r="C129" s="219">
+        <f>DCF!C77</f>
+        <v>0.02</v>
+      </c>
+      <c r="D129" s="220">
+        <f>DCF!D77</f>
+        <v>5</v>
+      </c>
+      <c r="E129" s="231" t="str">
+        <f>ROUND(IF(valuation_method="DCF",DCF!E77,DDM!E72),2)&amp;" "&amp;Market_currency</f>
+        <v>8.46 CNY</v>
+      </c>
+      <c r="F129" s="221">
+        <f>DCF!F77</f>
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6">
+      <c r="B130" s="218" t="str">
+        <f>DCF!B78</f>
+        <v>Devil's advocate</v>
+      </c>
+      <c r="C130" s="219">
+        <f>DCF!C78</f>
+        <v>0</v>
+      </c>
+      <c r="D130" s="220">
+        <f>DCF!D78</f>
+        <v>10</v>
+      </c>
+      <c r="E130" s="231" t="str">
+        <f>ROUND(IF(valuation_method="DCF",DCF!E78,DDM!E73),2)&amp;" "&amp;Market_currency</f>
+        <v>8.27 CNY</v>
+      </c>
+      <c r="F130" s="221">
+        <f>DCF!F78</f>
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6">
+      <c r="B132" s="211" t="s">
+        <v>254</v>
+      </c>
+      <c r="C132" s="217">
+        <f>Scenarios!C60</f>
+        <v>8.6992744860027944</v>
+      </c>
+      <c r="D132" s="212" t="str">
+        <f>Market_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6">
+      <c r="B134" s="369" t="s">
+        <v>524</v>
+      </c>
+      <c r="C134" s="369"/>
+      <c r="D134" s="369"/>
+      <c r="E134" s="369"/>
+      <c r="F134" s="369"/>
+    </row>
+    <row r="136" spans="1:6" ht="13.9">
+      <c r="A136" s="222" t="s">
+        <v>525</v>
+      </c>
+      <c r="B136" s="36"/>
+      <c r="C136" s="36"/>
+      <c r="D136" s="36"/>
+      <c r="E136" s="36"/>
+      <c r="F136" s="36"/>
+    </row>
+    <row r="138" spans="1:6">
+      <c r="B138" s="370" t="s">
+        <v>526</v>
+      </c>
+      <c r="C138" s="370"/>
+      <c r="D138" s="370"/>
+      <c r="E138" s="370"/>
+      <c r="F138" s="370"/>
+    </row>
+    <row r="139" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B139" s="371" t="s">
+        <v>527</v>
+      </c>
+      <c r="C139" s="371"/>
+      <c r="D139" s="371"/>
+      <c r="E139" s="371"/>
+      <c r="F139" s="371"/>
+    </row>
+    <row r="140" spans="1:6">
+      <c r="B140" s="210" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6">
+      <c r="B141" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="C141" s="225">
+        <f>F28</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6">
+      <c r="B142" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="C142" s="224">
+        <f>F29</f>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6">
+      <c r="B143" s="212" t="s">
+        <v>530</v>
+      </c>
+      <c r="C143" s="213">
+        <f>Scenarios!C77</f>
+        <v>0.36000000000000004</v>
+      </c>
+      <c r="D143" s="212" t="str">
+        <f>Market_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="145" spans="2:4">
+      <c r="B145" s="210" t="s">
+        <v>531</v>
+      </c>
+      <c r="C145" s="241" t="str">
+        <f>C11</f>
+        <v>300481.SZ</v>
+      </c>
+      <c r="D145" s="241" t="str">
+        <f>IF(D11="","",D11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="146" spans="2:4">
+      <c r="B146" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="C146" s="297">
+        <f>F29</f>
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="147" spans="2:4">
+      <c r="B147" s="212" t="str">
+        <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
+        <v>PV(3 yrs of Dividends)</v>
+      </c>
+      <c r="C147" s="216">
+        <f>Scenarios!C81</f>
+        <v>0.53758661691746279</v>
+      </c>
+    </row>
+    <row r="148" spans="2:4">
+      <c r="B148" s="212" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
+        <v>+ PV(Equity Value realized at year 3)</v>
+      </c>
+      <c r="C148" s="216">
+        <f>Scenarios!C82</f>
+        <v>2.8535075602944917</v>
+      </c>
+    </row>
+    <row r="149" spans="2:4">
+      <c r="B149" s="80" t="s">
+        <v>256</v>
+      </c>
+      <c r="C149" s="215">
+        <f>Scenarios!C83</f>
+        <v>3.3910941772119543</v>
+      </c>
+      <c r="D149" s="300" t="str">
+        <f>IF($D$11="","",C149*$E$25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="150" spans="2:4">
+      <c r="B150" s="259" t="s">
+        <v>532</v>
+      </c>
+      <c r="C150" s="298" t="str">
+        <f>Market_currency</f>
+        <v>CNY</v>
+      </c>
+      <c r="D150" s="298" t="str">
+        <f>IF($D$11="","",D$13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="151" spans="2:4">
+      <c r="B151" s="214" t="s">
+        <v>533</v>
+      </c>
+      <c r="C151" s="92">
+        <f>Scenarios!F83</f>
+        <v>0.61018655260639809</v>
+      </c>
+    </row>
+    <row r="153" spans="2:4">
+      <c r="B153" s="210" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="154" spans="2:4">
+      <c r="B154" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="C154" s="297">
+        <f>Scenarios!C90</f>
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="155" spans="2:4">
+      <c r="B155" s="212" t="str">
+        <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
+        <v>PV(3 yrs of Dividends)</v>
+      </c>
+      <c r="C155" s="216">
+        <f>Scenarios!C91</f>
+        <v>0.65380063723259008</v>
+      </c>
+    </row>
+    <row r="156" spans="2:4">
+      <c r="B156" s="212" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
+        <v>+ PV(Equity Value realized at year 3)</v>
+      </c>
+      <c r="C156" s="216">
+        <f>Scenarios!C92</f>
+        <v>3.959615150661262</v>
+      </c>
+    </row>
+    <row r="157" spans="2:4">
+      <c r="B157" s="80" t="s">
+        <v>256</v>
+      </c>
+      <c r="C157" s="215">
+        <f>Scenarios!C93</f>
+        <v>4.6134157878938522</v>
+      </c>
+      <c r="D157" s="300" t="str">
+        <f>IF($D$11="","",C157*$E$25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="158" spans="2:4">
+      <c r="B158" s="259" t="s">
+        <v>532</v>
+      </c>
+      <c r="C158" s="298" t="str">
+        <f>Market_currency</f>
+        <v>CNY</v>
+      </c>
+      <c r="D158" s="298" t="str">
+        <f>IF($D$11="","",D$13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="159" spans="2:4">
+      <c r="B159" s="214" t="s">
+        <v>533</v>
+      </c>
+      <c r="C159" s="92">
+        <f>Scenarios!F93</f>
+        <v>0.4696780984073009</v>
+      </c>
+    </row>
+    <row r="161" spans="2:4">
+      <c r="B161" s="210" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="162" spans="2:4">
+      <c r="B162" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="C162" s="92">
+        <f>Scenarios!C96</f>
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="163" spans="2:4">
+      <c r="B163" s="212" t="str">
+        <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
+        <v>PV(3 yrs of Dividends)</v>
+      </c>
+      <c r="C163" s="216">
+        <f>Scenarios!C97</f>
+        <v>0.93618926635390565</v>
+      </c>
+    </row>
+    <row r="164" spans="2:4">
+      <c r="B164" s="212" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
+        <v>+ PV(Equity Value realized at year 3)</v>
+      </c>
+      <c r="C164" s="216">
+        <f>Scenarios!C98</f>
+        <v>7.0025729445731688</v>
+      </c>
+    </row>
+    <row r="165" spans="2:4">
+      <c r="B165" s="80" t="s">
+        <v>382</v>
+      </c>
+      <c r="C165" s="215">
+        <f>Scenarios!C99</f>
+        <v>7.9387622109270746</v>
+      </c>
+      <c r="D165" s="300" t="str">
+        <f>IF($D$11="","",C165*$E$25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="166" spans="2:4">
+      <c r="B166" s="259" t="s">
+        <v>532</v>
+      </c>
+      <c r="C166" s="298" t="str">
+        <f>Market_currency</f>
+        <v>CNY</v>
+      </c>
+      <c r="D166" s="298" t="str">
+        <f>IF($D$11="","",D$13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="167" spans="2:4">
+      <c r="B167" s="214" t="s">
+        <v>533</v>
+      </c>
+      <c r="C167" s="92">
+        <f>Scenarios!F99</f>
+        <v>8.7422494404492013E-2</v>
+      </c>
+    </row>
+    <row r="169" spans="2:4">
+      <c r="B169" s="210" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="170" spans="2:4">
+      <c r="B170" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="C170" s="92">
+        <f>F32</f>
+        <v>8.6999999999999994E-2</v>
+      </c>
+    </row>
+    <row r="171" spans="2:4">
+      <c r="B171" s="212" t="str">
+        <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
+        <v>PV(3 yrs of Dividends)</v>
+      </c>
+      <c r="C171" s="216">
+        <f>Scenarios!C103</f>
+        <v>0.91616042104176609</v>
+      </c>
+    </row>
+    <row r="172" spans="2:4">
+      <c r="B172" s="212" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
+        <v>+ PV(Equity Value realized at year 3)</v>
+      </c>
+      <c r="C172" s="216">
+        <f>Scenarios!C104</f>
+        <v>6.773207833504693</v>
+      </c>
+    </row>
+    <row r="173" spans="2:4">
+      <c r="B173" s="80" t="s">
+        <v>382</v>
+      </c>
+      <c r="C173" s="215">
+        <f>Scenarios!C105</f>
+        <v>7.6893682545464594</v>
+      </c>
+      <c r="D173" s="300" t="str">
+        <f>IF($D$11="","",C173*$E$25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="174" spans="2:4">
+      <c r="B174" s="259" t="s">
+        <v>532</v>
+      </c>
+      <c r="C174" s="298" t="str">
+        <f>Market_currency</f>
+        <v>CNY</v>
+      </c>
+      <c r="D174" s="298" t="str">
+        <f>IF($D$11="","",D$13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="175" spans="2:4">
+      <c r="B175" s="214" t="s">
+        <v>533</v>
+      </c>
+      <c r="C175" s="92">
+        <f>Scenarios!F105</f>
+        <v>0.11352968837267541</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6" ht="13.9">
+      <c r="A177" s="222" t="s">
+        <v>357</v>
+      </c>
+      <c r="B177" s="36"/>
+      <c r="C177" s="36"/>
+      <c r="D177" s="36"/>
+      <c r="E177" s="36"/>
+      <c r="F177" s="36"/>
+    </row>
+    <row r="179" spans="1:6">
+      <c r="B179" s="372" t="s">
+        <v>534</v>
+      </c>
+      <c r="C179" s="371"/>
+      <c r="D179" s="371"/>
+      <c r="E179" s="371"/>
+      <c r="F179" s="371"/>
+    </row>
+    <row r="181" spans="1:6">
+      <c r="B181" s="210" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6">
+      <c r="B182" s="373" t="s">
+        <v>536</v>
+      </c>
+      <c r="C182" s="373"/>
+      <c r="D182" s="373"/>
+      <c r="E182" s="373"/>
+      <c r="F182" s="373"/>
+    </row>
+    <row r="183" spans="1:6">
+      <c r="B183" s="214" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="184" spans="1:6">
+      <c r="B184" s="214" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6">
+      <c r="B185" s="214" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6">
+      <c r="B187" s="1" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6" ht="24.6" customHeight="1">
+      <c r="B188" s="367" t="s">
+        <v>541</v>
+      </c>
+      <c r="C188" s="367"/>
+      <c r="D188" s="367"/>
+      <c r="E188" s="367"/>
+      <c r="F188" s="367"/>
+    </row>
+    <row r="190" spans="1:6">
+      <c r="B190" s="1" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="191" spans="1:6">
+      <c r="B191" s="368" t="s">
+        <v>543</v>
+      </c>
+      <c r="C191" s="368"/>
+      <c r="D191" s="368"/>
+      <c r="E191" s="368"/>
+      <c r="F191" s="368"/>
+    </row>
+    <row r="192" spans="1:6">
+      <c r="B192" s="368" t="s">
+        <v>544</v>
+      </c>
+      <c r="C192" s="368"/>
+      <c r="D192" s="368"/>
+      <c r="E192" s="368"/>
+      <c r="F192" s="368"/>
+    </row>
+    <row r="194" spans="2:2">
+      <c r="B194" s="1" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="195" spans="2:2">
+      <c r="B195" s="214" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="196" spans="2:2">
+      <c r="B196" s="214" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="197" spans="2:2">
+      <c r="B197" s="214" t="s">
+        <v>548</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="27">
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="B116:F116"/>
+    <mergeCell ref="B50:F50"/>
+    <mergeCell ref="B58:F58"/>
+    <mergeCell ref="B61:F61"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B65:F65"/>
+    <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B90:F90"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B138:F138"/>
+    <mergeCell ref="B139:F139"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B182:F182"/>
+  </mergeCells>
+  <dataValidations count="5">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">
+      <formula1>"INT,CN"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E21 E25" xr:uid="{0BE1D34E-D50B-41CB-99F3-E9F8694C38CA}">
+      <formula1>"DCF,DDM"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="C25:D25" xr:uid="{4F076B80-6574-480B-B48C-99BFFF6B4B13}">
+      <formula1>"HKD,USD,CNY,EUR"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C23:C24" xr:uid="{B605A743-B0FC-4D89-AD54-945707F01FA1}">
+      <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F1" xr:uid="{CF966412-2762-45A3-9589-2A9D9DD6B905}">
+      <formula1>"Y, N"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="85" fitToHeight="0" orientation="portrait" verticalDpi="300" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E03CB28-CABF-4F73-9474-1674E7E6FB22}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -4344,24 +6921,24 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="B1" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C1" s="44">
         <v>45797</v>
       </c>
       <c r="D1" s="316" t="s">
-        <v>457</v>
+        <v>551</v>
       </c>
       <c r="E1" s="292" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="F1" s="254" t="s">
-        <v>458</v>
+        <v>552</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9">
       <c r="A2" s="222" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="B2" s="36"/>
       <c r="C2" s="36"/>
@@ -4375,7 +6952,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="B4" s="45" t="s">
-        <v>412</v>
+        <v>395</v>
       </c>
       <c r="C4" s="46"/>
       <c r="D4" s="5"/>
@@ -4384,15 +6961,15 @@
     </row>
     <row r="5" spans="1:10" ht="12.4">
       <c r="B5" s="4" t="s">
-        <v>312</v>
+        <v>458</v>
       </c>
       <c r="C5" s="294" t="s">
-        <v>459</v>
+        <v>553</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="B6" s="4" t="s">
-        <v>0</v>
+        <v>459</v>
       </c>
       <c r="C6" s="51">
         <v>291855438</v>
@@ -4401,7 +6978,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="B7" s="2" t="s">
-        <v>306</v>
+        <v>460</v>
       </c>
       <c r="C7" s="250">
         <v>6</v>
@@ -4411,7 +6988,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="B8" s="1" t="s">
-        <v>267</v>
+        <v>461</v>
       </c>
       <c r="C8" s="33">
         <f>EOMONTH(EDATE(BS!C1,C7+2),0)</f>
@@ -4424,26 +7001,26 @@
     </row>
     <row r="10" spans="1:10">
       <c r="B10" s="45" t="s">
-        <v>415</v>
+        <v>397</v>
       </c>
       <c r="C10" s="46"/>
       <c r="E10" s="34"/>
     </row>
     <row r="11" spans="1:10">
       <c r="B11" s="1" t="s">
-        <v>414</v>
+        <v>462</v>
       </c>
       <c r="C11" s="49" t="s">
-        <v>460</v>
+        <v>554</v>
       </c>
       <c r="D11" s="49" t="s">
-        <v>461</v>
+        <v>555</v>
       </c>
       <c r="E11" s="34"/>
     </row>
     <row r="12" spans="1:10">
       <c r="B12" s="4" t="s">
-        <v>94</v>
+        <v>463</v>
       </c>
       <c r="C12" s="50">
         <v>14.57</v>
@@ -4453,17 +7030,17 @@
     </row>
     <row r="13" spans="1:10">
       <c r="B13" s="1" t="s">
-        <v>413</v>
+        <v>464</v>
       </c>
       <c r="C13" s="48" t="s">
-        <v>411</v>
+        <v>394</v>
       </c>
       <c r="D13" s="48"/>
       <c r="E13" s="5"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="4" t="s">
-        <v>417</v>
+        <v>465</v>
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
@@ -4477,7 +7054,7 @@
     </row>
     <row r="15" spans="1:10">
       <c r="B15" s="4" t="s">
-        <v>416</v>
+        <v>466</v>
       </c>
       <c r="C15" s="32" t="str">
         <f>IF(C25=C13,C13,C25&amp;"/"&amp;C13)</f>
@@ -4491,7 +7068,7 @@
     </row>
     <row r="16" spans="1:10">
       <c r="B16" s="4" t="s">
-        <v>1</v>
+        <v>467</v>
       </c>
       <c r="C16" s="50">
         <v>1</v>
@@ -4504,71 +7081,71 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="361" t="s">
-        <v>356</v>
-      </c>
-      <c r="C18" s="361"/>
-      <c r="D18" s="361"/>
-      <c r="E18" s="361"/>
-      <c r="F18" s="361"/>
+      <c r="B18" s="371" t="s">
+        <v>468</v>
+      </c>
+      <c r="C18" s="371"/>
+      <c r="D18" s="371"/>
+      <c r="E18" s="371"/>
+      <c r="F18" s="371"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="C20" s="46"/>
       <c r="D20" s="5"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="2" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="C21" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
         <v xml:space="preserve">Low Growth </v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>436</v>
+        <v>416</v>
       </c>
       <c r="E21" s="308" t="s">
-        <v>463</v>
+        <v>557</v>
       </c>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C22" s="48" t="s">
-        <v>462</v>
+        <v>556</v>
       </c>
       <c r="D22" s="1" t="str">
-        <f>IF(valuation_method="DDM","DDM Terminal Value","")</f>
+        <f>IF(valuation_method="DDM","Terminal Value Discount Rate","")</f>
         <v/>
       </c>
       <c r="E22" s="313"/>
     </row>
     <row r="23" spans="2:6">
       <c r="B23" s="1" t="s">
-        <v>431</v>
+        <v>411</v>
       </c>
       <c r="C23" s="262" t="s">
-        <v>458</v>
+        <v>552</v>
       </c>
     </row>
     <row r="24" spans="2:6">
       <c r="B24" s="1" t="s">
-        <v>432</v>
+        <v>412</v>
       </c>
       <c r="C24" s="262" t="s">
-        <v>458</v>
+        <v>552</v>
       </c>
     </row>
     <row r="25" spans="2:6">
       <c r="B25" s="4" t="s">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="C25" s="48" t="s">
-        <v>411</v>
+        <v>394</v>
       </c>
       <c r="D25" s="32" t="str">
         <f>IF(D11="","",Market_currency&amp;"/"&amp;D13&amp;":")</f>
@@ -4589,7 +7166,7 @@
         <v>8.6992744860027944</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>396</v>
+        <v>380</v>
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
@@ -4602,7 +7179,7 @@
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="45" t="s">
-        <v>430</v>
+        <v>410</v>
       </c>
       <c r="C28" s="309" t="str">
         <f>C145&amp;" ("&amp;Market_currency&amp;")"</f>
@@ -4613,7 +7190,7 @@
         <v/>
       </c>
       <c r="E28" s="305" t="s">
-        <v>426</v>
+        <v>406</v>
       </c>
       <c r="F28" s="303">
         <v>3</v>
@@ -4621,7 +7198,7 @@
     </row>
     <row r="29" spans="2:6">
       <c r="B29" s="1" t="s">
-        <v>422</v>
+        <v>402</v>
       </c>
       <c r="C29" s="310">
         <f>C149</f>
@@ -4632,7 +7209,7 @@
         <v/>
       </c>
       <c r="E29" s="306" t="s">
-        <v>421</v>
+        <v>401</v>
       </c>
       <c r="F29" s="302">
         <v>0.45</v>
@@ -4640,7 +7217,7 @@
     </row>
     <row r="30" spans="2:6">
       <c r="B30" s="1" t="s">
-        <v>423</v>
+        <v>403</v>
       </c>
       <c r="C30" s="311">
         <f>C157</f>
@@ -4651,7 +7228,7 @@
         <v/>
       </c>
       <c r="E30" s="307" t="s">
-        <v>434</v>
+        <v>414</v>
       </c>
       <c r="F30" s="312">
         <v>0.3</v>
@@ -4659,7 +7236,7 @@
     </row>
     <row r="31" spans="2:6">
       <c r="B31" s="1" t="s">
-        <v>424</v>
+        <v>404</v>
       </c>
       <c r="C31" s="311">
         <f>C165</f>
@@ -4670,7 +7247,7 @@
         <v/>
       </c>
       <c r="E31" s="307" t="s">
-        <v>433</v>
+        <v>413</v>
       </c>
       <c r="F31" s="312">
         <v>7.4999999999999997E-2</v>
@@ -4678,7 +7255,7 @@
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="1" t="s">
-        <v>425</v>
+        <v>405</v>
       </c>
       <c r="C32" s="311">
         <f>C173</f>
@@ -4689,7 +7266,7 @@
         <v/>
       </c>
       <c r="E32" s="307" t="s">
-        <v>435</v>
+        <v>415</v>
       </c>
       <c r="F32" s="312">
         <v>8.6999999999999994E-2</v>
@@ -4701,7 +7278,7 @@
     </row>
     <row r="34" spans="1:6" ht="13.9">
       <c r="A34" s="222" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="B34" s="36"/>
       <c r="C34" s="36"/>
@@ -4709,27 +7286,27 @@
       <c r="E34" s="36"/>
       <c r="F34" s="36"/>
     </row>
-    <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="361" t="s">
-        <v>357</v>
-      </c>
-      <c r="C36" s="361"/>
-      <c r="D36" s="361"/>
-      <c r="E36" s="361"/>
-      <c r="F36" s="361"/>
+    <row r="36" spans="1:6">
+      <c r="B36" s="371" t="s">
+        <v>469</v>
+      </c>
+      <c r="C36" s="371"/>
+      <c r="D36" s="371"/>
+      <c r="E36" s="371"/>
+      <c r="F36" s="371"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="363" t="s">
-        <v>336</v>
-      </c>
-      <c r="C37" s="363"/>
-      <c r="D37" s="363"/>
-      <c r="E37" s="363"/>
-      <c r="F37" s="363"/>
+      <c r="B37" s="374" t="s">
+        <v>330</v>
+      </c>
+      <c r="C37" s="374"/>
+      <c r="D37" s="374"/>
+      <c r="E37" s="374"/>
+      <c r="F37" s="374"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="C39" s="108">
         <f>scaling_factor</f>
@@ -4737,17 +7314,17 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="362" t="s">
-        <v>230</v>
-      </c>
-      <c r="C40" s="362"/>
-      <c r="D40" s="362"/>
-      <c r="E40" s="362"/>
-      <c r="F40" s="362"/>
+      <c r="B40" s="367" t="s">
+        <v>227</v>
+      </c>
+      <c r="C40" s="367"/>
+      <c r="D40" s="367"/>
+      <c r="E40" s="367"/>
+      <c r="F40" s="367"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="C41" s="349">
         <f>Normalized_FCF!C8</f>
@@ -4763,17 +7340,17 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="362" t="s">
-        <v>232</v>
-      </c>
-      <c r="C43" s="362"/>
-      <c r="D43" s="362"/>
-      <c r="E43" s="362"/>
-      <c r="F43" s="362"/>
+      <c r="B43" s="367" t="s">
+        <v>229</v>
+      </c>
+      <c r="C43" s="367"/>
+      <c r="D43" s="367"/>
+      <c r="E43" s="367"/>
+      <c r="F43" s="367"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="C44" s="349">
         <f>Normalized_FCF!C9</f>
@@ -4786,7 +7363,7 @@
     </row>
     <row r="45" spans="1:6">
       <c r="B45" s="52" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="C45" s="349">
         <f>Normalized_FCF!C10</f>
@@ -4798,17 +7375,17 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="362" t="s">
-        <v>235</v>
-      </c>
-      <c r="C47" s="362"/>
-      <c r="D47" s="362"/>
-      <c r="E47" s="362"/>
-      <c r="F47" s="362"/>
+      <c r="B47" s="367" t="s">
+        <v>232</v>
+      </c>
+      <c r="C47" s="367"/>
+      <c r="D47" s="367"/>
+      <c r="E47" s="367"/>
+      <c r="F47" s="367"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="C48" s="349">
         <f>Normalized_FCF!C11</f>
@@ -4820,17 +7397,17 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="362" t="s">
-        <v>239</v>
-      </c>
-      <c r="C50" s="362"/>
-      <c r="D50" s="362"/>
-      <c r="E50" s="362"/>
-      <c r="F50" s="362"/>
+      <c r="B50" s="367" t="s">
+        <v>236</v>
+      </c>
+      <c r="C50" s="367"/>
+      <c r="D50" s="367"/>
+      <c r="E50" s="367"/>
+      <c r="F50" s="367"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="C51" s="350">
         <f>Normalized_FCF!C48</f>
@@ -4845,7 +7422,7 @@
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="47" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="C52" s="350">
         <f>Normalized_FCF!C47</f>
@@ -4860,7 +7437,7 @@
     </row>
     <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="C53" s="349">
         <f>Normalized_FCF!C12</f>
@@ -4873,12 +7450,12 @@
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="1" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="47" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="C56" s="349">
         <f>Normalized_FCF!C15</f>
@@ -4890,17 +7467,17 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="362" t="s">
-        <v>240</v>
-      </c>
-      <c r="C58" s="362"/>
-      <c r="D58" s="362"/>
-      <c r="E58" s="362"/>
-      <c r="F58" s="362"/>
+      <c r="B58" s="367" t="s">
+        <v>237</v>
+      </c>
+      <c r="C58" s="367"/>
+      <c r="D58" s="367"/>
+      <c r="E58" s="367"/>
+      <c r="F58" s="367"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="C59" s="349">
         <f>Normalized_FCF!C14</f>
@@ -4912,17 +7489,17 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="362" t="s">
-        <v>335</v>
-      </c>
-      <c r="C61" s="365"/>
-      <c r="D61" s="365"/>
-      <c r="E61" s="365"/>
-      <c r="F61" s="365"/>
+      <c r="B61" s="367" t="s">
+        <v>329</v>
+      </c>
+      <c r="C61" s="373"/>
+      <c r="D61" s="373"/>
+      <c r="E61" s="373"/>
+      <c r="F61" s="373"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="C62" s="349">
         <f>Normalized_FCF!C17</f>
@@ -4934,26 +7511,26 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="361" t="s">
-        <v>340</v>
-      </c>
-      <c r="C64" s="361"/>
-      <c r="D64" s="361"/>
-      <c r="E64" s="361"/>
-      <c r="F64" s="361"/>
+      <c r="B64" s="371" t="s">
+        <v>334</v>
+      </c>
+      <c r="C64" s="371"/>
+      <c r="D64" s="371"/>
+      <c r="E64" s="371"/>
+      <c r="F64" s="371"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="361" t="s">
-        <v>358</v>
-      </c>
-      <c r="C65" s="361"/>
-      <c r="D65" s="361"/>
-      <c r="E65" s="361"/>
-      <c r="F65" s="361"/>
+      <c r="B65" s="371" t="s">
+        <v>348</v>
+      </c>
+      <c r="C65" s="371"/>
+      <c r="D65" s="371"/>
+      <c r="E65" s="371"/>
+      <c r="F65" s="371"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="C67" s="349">
         <f>Normalized_FCF!G19</f>
@@ -4966,7 +7543,7 @@
     </row>
     <row r="68" spans="1:6">
       <c r="B68" s="47" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="C68" s="349">
         <f>Normalized_FCF!C19</f>
@@ -4979,7 +7556,7 @@
     </row>
     <row r="69" spans="1:6">
       <c r="B69" s="227" t="s">
-        <v>387</v>
+        <v>371</v>
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
@@ -4989,14 +7566,14 @@
     </row>
     <row r="70" spans="1:6">
       <c r="B70" s="227" t="s">
-        <v>454</v>
+        <v>434</v>
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
         <v>2.4708304735758409E-2</v>
       </c>
       <c r="E70" s="47" t="s">
-        <v>445</v>
+        <v>425</v>
       </c>
       <c r="F70" s="315">
         <f>Normalized_FCF!C92</f>
@@ -5005,18 +7582,18 @@
     </row>
     <row r="72" spans="1:6">
       <c r="B72" s="210" t="s">
-        <v>447</v>
+        <v>427</v>
       </c>
       <c r="C72" s="323" t="s">
-        <v>449</v>
+        <v>429</v>
       </c>
       <c r="D72" s="323" t="s">
-        <v>450</v>
+        <v>430</v>
       </c>
     </row>
     <row r="73" spans="1:6">
       <c r="B73" s="47" t="s">
-        <v>448</v>
+        <v>428</v>
       </c>
       <c r="C73" s="92">
         <f>Normalized_FCF!C121</f>
@@ -5071,7 +7648,7 @@
     </row>
     <row r="78" spans="1:6" ht="13.9">
       <c r="A78" s="222" t="s">
-        <v>352</v>
+        <v>470</v>
       </c>
       <c r="B78" s="36"/>
       <c r="C78" s="36"/>
@@ -5082,33 +7659,33 @@
     <row r="79" spans="1:6">
       <c r="A79" s="209"/>
     </row>
-    <row r="80" spans="1:6" ht="24.6" customHeight="1">
+    <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="361" t="s">
-        <v>359</v>
-      </c>
-      <c r="C80" s="361"/>
-      <c r="D80" s="361"/>
-      <c r="E80" s="361"/>
-      <c r="F80" s="361"/>
+      <c r="B80" s="371" t="s">
+        <v>471</v>
+      </c>
+      <c r="C80" s="371"/>
+      <c r="D80" s="371"/>
+      <c r="E80" s="371"/>
+      <c r="F80" s="371"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="363" t="s">
-        <v>251</v>
-      </c>
-      <c r="C81" s="363"/>
-      <c r="D81" s="363"/>
-      <c r="E81" s="363"/>
-      <c r="F81" s="363"/>
+      <c r="B81" s="374" t="s">
+        <v>248</v>
+      </c>
+      <c r="C81" s="374"/>
+      <c r="D81" s="374"/>
+      <c r="E81" s="374"/>
+      <c r="F81" s="374"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
     </row>
     <row r="84" spans="1:6">
       <c r="B84" s="1" t="s">
-        <v>428</v>
+        <v>408</v>
       </c>
       <c r="C84" s="92">
         <f>F31</f>
@@ -5117,7 +7694,7 @@
     </row>
     <row r="85" spans="1:6">
       <c r="B85" s="1" t="s">
-        <v>427</v>
+        <v>407</v>
       </c>
       <c r="C85" s="92">
         <f>IF(C23="Y",1%,0)+IF(C24="Y",1%,0)</f>
@@ -5126,7 +7703,7 @@
     </row>
     <row r="86" spans="1:6">
       <c r="B86" s="80" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="C86" s="236">
         <f>F31+C85</f>
@@ -5138,31 +7715,31 @@
     </row>
     <row r="88" spans="1:6">
       <c r="B88" s="293" t="s">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="361" t="s">
-        <v>360</v>
-      </c>
-      <c r="C89" s="361"/>
-      <c r="D89" s="361"/>
-      <c r="E89" s="361"/>
-      <c r="F89" s="361"/>
+      <c r="B89" s="371" t="s">
+        <v>349</v>
+      </c>
+      <c r="C89" s="371"/>
+      <c r="D89" s="371"/>
+      <c r="E89" s="371"/>
+      <c r="F89" s="371"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="361" t="s">
-        <v>361</v>
-      </c>
-      <c r="C90" s="361"/>
-      <c r="D90" s="361"/>
-      <c r="E90" s="361"/>
-      <c r="F90" s="361"/>
+      <c r="B90" s="371" t="s">
+        <v>350</v>
+      </c>
+      <c r="C90" s="371"/>
+      <c r="D90" s="371"/>
+      <c r="E90" s="371"/>
+      <c r="F90" s="371"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="C92" s="236">
         <v>0</v>
@@ -5170,7 +7747,7 @@
     </row>
     <row r="93" spans="1:6">
       <c r="B93" s="47" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="C93" s="223">
         <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
@@ -5183,7 +7760,7 @@
     </row>
     <row r="95" spans="1:6" ht="13.9">
       <c r="A95" s="222" t="s">
-        <v>354</v>
+        <v>347</v>
       </c>
       <c r="B95" s="36"/>
       <c r="C95" s="36"/>
@@ -5195,36 +7772,36 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="361" t="s">
-        <v>362</v>
-      </c>
-      <c r="C97" s="361"/>
-      <c r="D97" s="361"/>
-      <c r="E97" s="361"/>
-      <c r="F97" s="361"/>
+      <c r="B97" s="371" t="s">
+        <v>351</v>
+      </c>
+      <c r="C97" s="371"/>
+      <c r="D97" s="371"/>
+      <c r="E97" s="371"/>
+      <c r="F97" s="371"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="210" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="361" t="s">
-        <v>341</v>
-      </c>
-      <c r="C101" s="361"/>
-      <c r="D101" s="361"/>
-      <c r="E101" s="361"/>
-      <c r="F101" s="361"/>
+      <c r="B101" s="371" t="s">
+        <v>335</v>
+      </c>
+      <c r="C101" s="371"/>
+      <c r="D101" s="371"/>
+      <c r="E101" s="371"/>
+      <c r="F101" s="371"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C102" s="349">
         <f>DCF!C7</f>
@@ -5237,7 +7814,7 @@
     </row>
     <row r="103" spans="2:6">
       <c r="B103" s="47" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="C103" s="223">
         <f>C102*scaling_factor*Exchange_Rate/Common_Shares</f>
@@ -5250,7 +7827,7 @@
     </row>
     <row r="104" spans="2:6">
       <c r="B104" s="296" t="s">
-        <v>401</v>
+        <v>384</v>
       </c>
       <c r="C104" s="325">
         <f>IF(BS!G31/BS!G27&gt;300%,"nm",BS!G31/BS!G27)</f>
@@ -5259,7 +7836,7 @@
     </row>
     <row r="105" spans="2:6">
       <c r="B105" s="296" t="s">
-        <v>403</v>
+        <v>386</v>
       </c>
       <c r="C105" s="326">
         <f>IF(BS!C50&gt;30,"nm",BS!C50)</f>
@@ -5268,12 +7845,12 @@
     </row>
     <row r="107" spans="2:6">
       <c r="B107" s="1" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
     </row>
     <row r="108" spans="2:6">
       <c r="B108" s="47" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="C108" s="349">
         <f>BS!C66</f>
@@ -5286,7 +7863,7 @@
     </row>
     <row r="109" spans="2:6">
       <c r="B109" s="47" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="C109" s="349">
         <f>DCF!C8</f>
@@ -5299,7 +7876,7 @@
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="47" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="C110" s="223">
         <f>C109*scaling_factor*Exchange_Rate/Common_Shares</f>
@@ -5312,12 +7889,12 @@
     </row>
     <row r="112" spans="2:6">
       <c r="B112" s="1" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
     </row>
     <row r="113" spans="1:6">
       <c r="B113" s="47" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="C113" s="349">
         <f>DCF!C9</f>
@@ -5330,7 +7907,7 @@
     </row>
     <row r="114" spans="1:6">
       <c r="B114" s="47" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="C114" s="223">
         <f>C113*scaling_factor*Exchange_Rate/Common_Shares</f>
@@ -5342,17 +7919,17 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="361" t="s">
-        <v>363</v>
-      </c>
-      <c r="C116" s="361"/>
-      <c r="D116" s="361"/>
-      <c r="E116" s="361"/>
-      <c r="F116" s="361"/>
+      <c r="B116" s="371" t="s">
+        <v>352</v>
+      </c>
+      <c r="C116" s="371"/>
+      <c r="D116" s="371"/>
+      <c r="E116" s="371"/>
+      <c r="F116" s="371"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
-        <v>446</v>
+        <v>426</v>
       </c>
       <c r="C118" s="223">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
@@ -5365,7 +7942,7 @@
     </row>
     <row r="119" spans="1:6">
       <c r="B119" s="296" t="s">
-        <v>402</v>
+        <v>549</v>
       </c>
       <c r="C119" s="223">
         <f>BS!D47</f>
@@ -5378,7 +7955,7 @@
     </row>
     <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="222" t="s">
-        <v>355</v>
+        <v>472</v>
       </c>
       <c r="B121" s="36"/>
       <c r="C121" s="36"/>
@@ -5386,30 +7963,30 @@
       <c r="E121" s="36"/>
       <c r="F121" s="36"/>
     </row>
-    <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="362" t="s">
-        <v>364</v>
-      </c>
-      <c r="C123" s="362"/>
-      <c r="D123" s="362"/>
-      <c r="E123" s="362"/>
-      <c r="F123" s="362"/>
+    <row r="123" spans="1:6">
+      <c r="B123" s="367" t="s">
+        <v>473</v>
+      </c>
+      <c r="C123" s="367"/>
+      <c r="D123" s="367"/>
+      <c r="E123" s="367"/>
+      <c r="F123" s="367"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C125" s="233" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D125" s="233" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E125" s="233" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="F125" s="233" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
     </row>
     <row r="126" spans="1:6">
@@ -5524,7 +8101,7 @@
     </row>
     <row r="132" spans="1:6">
       <c r="B132" s="211" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="C132" s="217">
         <f>Scenarios!C60</f>
@@ -5536,17 +8113,17 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="366" t="s">
-        <v>367</v>
-      </c>
-      <c r="C134" s="366"/>
-      <c r="D134" s="366"/>
-      <c r="E134" s="366"/>
-      <c r="F134" s="366"/>
+      <c r="B134" s="369" t="s">
+        <v>474</v>
+      </c>
+      <c r="C134" s="369"/>
+      <c r="D134" s="369"/>
+      <c r="E134" s="369"/>
+      <c r="F134" s="369"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
-        <v>399</v>
+        <v>475</v>
       </c>
       <c r="B136" s="36"/>
       <c r="C136" s="36"/>
@@ -5555,31 +8132,31 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="364" t="s">
-        <v>365</v>
-      </c>
-      <c r="C138" s="364"/>
-      <c r="D138" s="364"/>
-      <c r="E138" s="364"/>
-      <c r="F138" s="364"/>
-    </row>
-    <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="361" t="s">
-        <v>366</v>
-      </c>
-      <c r="C139" s="361"/>
-      <c r="D139" s="361"/>
-      <c r="E139" s="361"/>
-      <c r="F139" s="361"/>
+      <c r="B138" s="370" t="s">
+        <v>353</v>
+      </c>
+      <c r="C138" s="370"/>
+      <c r="D138" s="370"/>
+      <c r="E138" s="370"/>
+      <c r="F138" s="370"/>
+    </row>
+    <row r="139" spans="1:6">
+      <c r="B139" s="371" t="s">
+        <v>476</v>
+      </c>
+      <c r="C139" s="371"/>
+      <c r="D139" s="371"/>
+      <c r="E139" s="371"/>
+      <c r="F139" s="371"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
     </row>
     <row r="141" spans="1:6">
       <c r="B141" s="1" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="C141" s="225">
         <f>F28</f>
@@ -5588,7 +8165,7 @@
     </row>
     <row r="142" spans="1:6">
       <c r="B142" s="1" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="C142" s="224">
         <f>F29</f>
@@ -5597,7 +8174,7 @@
     </row>
     <row r="143" spans="1:6">
       <c r="B143" s="212" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="C143" s="213">
         <f>Scenarios!C77</f>
@@ -5610,7 +8187,7 @@
     </row>
     <row r="145" spans="2:4">
       <c r="B145" s="210" t="s">
-        <v>405</v>
+        <v>388</v>
       </c>
       <c r="C145" s="241" t="str">
         <f>C11</f>
@@ -5623,7 +8200,7 @@
     </row>
     <row r="146" spans="2:4">
       <c r="B146" s="1" t="s">
-        <v>404</v>
+        <v>387</v>
       </c>
       <c r="C146" s="297">
         <f>F29</f>
@@ -5652,7 +8229,7 @@
     </row>
     <row r="149" spans="2:4">
       <c r="B149" s="80" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C149" s="215">
         <f>Scenarios!C83</f>
@@ -5665,7 +8242,7 @@
     </row>
     <row r="150" spans="2:4">
       <c r="B150" s="259" t="s">
-        <v>413</v>
+        <v>396</v>
       </c>
       <c r="C150" s="298" t="str">
         <f>Market_currency</f>
@@ -5678,7 +8255,7 @@
     </row>
     <row r="151" spans="2:4">
       <c r="B151" s="214" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C151" s="92">
         <f>Scenarios!F83</f>
@@ -5687,12 +8264,12 @@
     </row>
     <row r="153" spans="2:4">
       <c r="B153" s="210" t="s">
-        <v>408</v>
+        <v>391</v>
       </c>
     </row>
     <row r="154" spans="2:4">
       <c r="B154" s="1" t="s">
-        <v>407</v>
+        <v>390</v>
       </c>
       <c r="C154" s="297">
         <f>Scenarios!C90</f>
@@ -5721,7 +8298,7 @@
     </row>
     <row r="157" spans="2:4">
       <c r="B157" s="80" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C157" s="215">
         <f>Scenarios!C93</f>
@@ -5734,7 +8311,7 @@
     </row>
     <row r="158" spans="2:4">
       <c r="B158" s="259" t="s">
-        <v>413</v>
+        <v>396</v>
       </c>
       <c r="C158" s="298" t="str">
         <f>Market_currency</f>
@@ -5747,7 +8324,7 @@
     </row>
     <row r="159" spans="2:4">
       <c r="B159" s="214" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C159" s="92">
         <f>Scenarios!F93</f>
@@ -5756,12 +8333,12 @@
     </row>
     <row r="161" spans="2:4">
       <c r="B161" s="210" t="s">
-        <v>397</v>
+        <v>381</v>
       </c>
     </row>
     <row r="162" spans="2:4">
       <c r="B162" s="1" t="s">
-        <v>406</v>
+        <v>389</v>
       </c>
       <c r="C162" s="92">
         <f>Scenarios!C96</f>
@@ -5790,7 +8367,7 @@
     </row>
     <row r="165" spans="2:4">
       <c r="B165" s="80" t="s">
-        <v>398</v>
+        <v>382</v>
       </c>
       <c r="C165" s="215">
         <f>Scenarios!C99</f>
@@ -5803,7 +8380,7 @@
     </row>
     <row r="166" spans="2:4">
       <c r="B166" s="259" t="s">
-        <v>413</v>
+        <v>396</v>
       </c>
       <c r="C166" s="298" t="str">
         <f>Market_currency</f>
@@ -5816,7 +8393,7 @@
     </row>
     <row r="167" spans="2:4">
       <c r="B167" s="214" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C167" s="92">
         <f>Scenarios!F99</f>
@@ -5825,12 +8402,12 @@
     </row>
     <row r="169" spans="2:4">
       <c r="B169" s="210" t="s">
-        <v>429</v>
+        <v>409</v>
       </c>
     </row>
     <row r="170" spans="2:4">
       <c r="B170" s="1" t="s">
-        <v>420</v>
+        <v>400</v>
       </c>
       <c r="C170" s="92">
         <f>F32</f>
@@ -5859,7 +8436,7 @@
     </row>
     <row r="173" spans="2:4">
       <c r="B173" s="80" t="s">
-        <v>398</v>
+        <v>382</v>
       </c>
       <c r="C173" s="215">
         <f>Scenarios!C105</f>
@@ -5872,7 +8449,7 @@
     </row>
     <row r="174" spans="2:4">
       <c r="B174" s="259" t="s">
-        <v>413</v>
+        <v>396</v>
       </c>
       <c r="C174" s="298" t="str">
         <f>Market_currency</f>
@@ -5885,7 +8462,7 @@
     </row>
     <row r="175" spans="2:4">
       <c r="B175" s="214" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C175" s="92">
         <f>Scenarios!F105</f>
@@ -5894,7 +8471,7 @@
     </row>
     <row r="177" spans="1:6" ht="13.9">
       <c r="A177" s="222" t="s">
-        <v>371</v>
+        <v>357</v>
       </c>
       <c r="B177" s="36"/>
       <c r="C177" s="36"/>
@@ -5903,113 +8480,102 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="368" t="s">
-        <v>373</v>
-      </c>
-      <c r="C179" s="361"/>
-      <c r="D179" s="361"/>
-      <c r="E179" s="361"/>
-      <c r="F179" s="361"/>
+      <c r="B179" s="372" t="s">
+        <v>477</v>
+      </c>
+      <c r="C179" s="371"/>
+      <c r="D179" s="371"/>
+      <c r="E179" s="371"/>
+      <c r="F179" s="371"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
-        <v>372</v>
+        <v>358</v>
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="365" t="s">
-        <v>377</v>
-      </c>
-      <c r="C182" s="365"/>
-      <c r="D182" s="365"/>
-      <c r="E182" s="365"/>
-      <c r="F182" s="365"/>
+      <c r="B182" s="373" t="s">
+        <v>362</v>
+      </c>
+      <c r="C182" s="373"/>
+      <c r="D182" s="373"/>
+      <c r="E182" s="373"/>
+      <c r="F182" s="373"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
-        <v>374</v>
+        <v>359</v>
       </c>
     </row>
     <row r="184" spans="1:6">
       <c r="B184" s="214" t="s">
-        <v>375</v>
+        <v>360</v>
       </c>
     </row>
     <row r="185" spans="1:6">
       <c r="B185" s="214" t="s">
-        <v>376</v>
+        <v>361</v>
       </c>
     </row>
     <row r="187" spans="1:6">
       <c r="B187" s="1" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="362" t="s">
-        <v>378</v>
-      </c>
-      <c r="C188" s="362"/>
-      <c r="D188" s="362"/>
-      <c r="E188" s="362"/>
-      <c r="F188" s="362"/>
+        <v>365</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6" ht="34.35" customHeight="1">
+      <c r="B188" s="367" t="s">
+        <v>478</v>
+      </c>
+      <c r="C188" s="367"/>
+      <c r="D188" s="367"/>
+      <c r="E188" s="367"/>
+      <c r="F188" s="367"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
-        <v>382</v>
+        <v>366</v>
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="367" t="s">
-        <v>379</v>
-      </c>
-      <c r="C191" s="367"/>
-      <c r="D191" s="367"/>
-      <c r="E191" s="367"/>
-      <c r="F191" s="367"/>
+      <c r="B191" s="368" t="s">
+        <v>363</v>
+      </c>
+      <c r="C191" s="368"/>
+      <c r="D191" s="368"/>
+      <c r="E191" s="368"/>
+      <c r="F191" s="368"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="367" t="s">
-        <v>380</v>
-      </c>
-      <c r="C192" s="367"/>
-      <c r="D192" s="367"/>
-      <c r="E192" s="367"/>
-      <c r="F192" s="367"/>
+      <c r="B192" s="368" t="s">
+        <v>364</v>
+      </c>
+      <c r="C192" s="368"/>
+      <c r="D192" s="368"/>
+      <c r="E192" s="368"/>
+      <c r="F192" s="368"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
-        <v>386</v>
+        <v>370</v>
       </c>
     </row>
     <row r="195" spans="2:2">
       <c r="B195" s="214" t="s">
-        <v>383</v>
+        <v>367</v>
       </c>
     </row>
     <row r="196" spans="2:2">
       <c r="B196" s="214" t="s">
-        <v>384</v>
+        <v>368</v>
       </c>
     </row>
     <row r="197" spans="2:2">
       <c r="B197" s="214" t="s">
-        <v>385</v>
+        <v>369</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -6026,6 +8592,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -6050,7 +8627,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48ED7348-D356-493F-B1FA-0B9102624322}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -6115,7 +8692,7 @@
     </row>
     <row r="2" spans="2:13" ht="13.9">
       <c r="B2" s="36" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
@@ -6131,7 +8708,7 @@
     </row>
     <row r="3" spans="2:13">
       <c r="B3" s="16" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C3" s="106">
         <v>1</v>
@@ -6139,7 +8716,7 @@
     </row>
     <row r="4" spans="2:13">
       <c r="B4" s="32" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C4" s="351">
         <v>1411006911</v>
@@ -6175,7 +8752,7 @@
     </row>
     <row r="5" spans="2:13">
       <c r="B5" s="40" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C5" s="351">
         <v>1115025379</v>
@@ -6211,7 +8788,7 @@
     </row>
     <row r="6" spans="2:13">
       <c r="B6" s="40" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C6" s="351">
         <v>43790640</v>
@@ -6247,7 +8824,7 @@
     </row>
     <row r="7" spans="2:13">
       <c r="B7" s="69" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C7" s="352">
         <v>10699910</v>
@@ -6283,7 +8860,7 @@
     </row>
     <row r="8" spans="2:13">
       <c r="B8" s="40" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C8" s="351">
         <v>77948987</v>
@@ -6313,7 +8890,7 @@
     </row>
     <row r="9" spans="2:13">
       <c r="B9" s="40" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C9" s="351"/>
       <c r="D9" s="351"/>
@@ -6329,7 +8906,7 @@
     </row>
     <row r="10" spans="2:13">
       <c r="B10" s="40" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="C10" s="351"/>
       <c r="D10" s="351"/>
@@ -6345,7 +8922,7 @@
     </row>
     <row r="11" spans="2:13">
       <c r="B11" s="40" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C11" s="351"/>
       <c r="D11" s="351"/>
@@ -6361,7 +8938,7 @@
     </row>
     <row r="12" spans="2:13">
       <c r="B12" s="40" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C12" s="351">
         <v>5219951</v>
@@ -6391,7 +8968,7 @@
     </row>
     <row r="13" spans="2:13">
       <c r="B13" s="40" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C13" s="351">
         <v>30422495</v>
@@ -6421,7 +8998,7 @@
     </row>
     <row r="14" spans="2:13">
       <c r="B14" s="40" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C14" s="351">
         <v>28257995</v>
@@ -6457,7 +9034,7 @@
     </row>
     <row r="15" spans="2:13">
       <c r="B15" s="43" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C15" s="353">
         <v>191530184</v>
@@ -6493,7 +9070,7 @@
     </row>
     <row r="16" spans="2:13">
       <c r="B16" s="28" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C16" s="351">
         <v>-21781</v>
@@ -6529,13 +9106,13 @@
     </row>
     <row r="18" spans="2:13">
       <c r="B18" s="16" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C18" s="9"/>
     </row>
     <row r="19" spans="2:13">
       <c r="B19" s="27" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C19" s="351">
         <v>61093655</v>
@@ -6565,7 +9142,7 @@
     </row>
     <row r="20" spans="2:13">
       <c r="B20" s="27" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C20" s="351"/>
       <c r="D20" s="351"/>
@@ -6581,7 +9158,7 @@
     </row>
     <row r="21" spans="2:13">
       <c r="B21" s="27" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C21" s="351"/>
       <c r="D21" s="351"/>
@@ -6597,7 +9174,7 @@
     </row>
     <row r="22" spans="2:13">
       <c r="B22" s="27" t="s">
-        <v>368</v>
+        <v>354</v>
       </c>
       <c r="C22" s="351">
         <v>246703905</v>
@@ -6633,7 +9210,7 @@
     </row>
     <row r="23" spans="2:13">
       <c r="B23" s="27" t="s">
-        <v>370</v>
+        <v>356</v>
       </c>
       <c r="C23" s="351">
         <v>12280558</v>
@@ -6669,7 +9246,7 @@
     </row>
     <row r="24" spans="2:13">
       <c r="B24" s="27" t="s">
-        <v>369</v>
+        <v>355</v>
       </c>
       <c r="C24" s="351">
         <v>-205377752</v>
@@ -6740,15 +9317,15 @@
     </row>
     <row r="27" spans="2:13">
       <c r="B27" s="16" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>464</v>
+        <v>558</v>
       </c>
     </row>
     <row r="28" spans="2:13">
       <c r="B28" s="26" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C28" s="333">
         <f>BS!C4</f>
@@ -6785,7 +9362,7 @@
     </row>
     <row r="29" spans="2:13">
       <c r="B29" s="26" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C29" s="333">
         <f>BS!C6</f>
@@ -6822,7 +9399,7 @@
     </row>
     <row r="30" spans="2:13">
       <c r="B30" s="29" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C30" s="334">
         <f>BS!C33+BS!C42</f>
@@ -6859,7 +9436,7 @@
     </row>
     <row r="31" spans="2:13">
       <c r="B31" s="29" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C31" s="334">
         <f>BS!G27</f>
@@ -6896,7 +9473,7 @@
     </row>
     <row r="32" spans="2:13">
       <c r="B32" s="26" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="C32" s="333">
         <f>BS!G28</f>
@@ -6933,7 +9510,7 @@
     </row>
     <row r="34" spans="2:13" ht="13.9">
       <c r="B34" s="36" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C34" s="37"/>
       <c r="D34" s="37"/>
@@ -6949,12 +9526,12 @@
     </row>
     <row r="35" spans="2:13">
       <c r="B35" s="16" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="36" spans="2:13">
       <c r="B36" s="32" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C36" s="333">
         <f t="shared" ref="C36:M36" si="1">IF(C$4="","",C4)</f>
@@ -7003,7 +9580,7 @@
     </row>
     <row r="37" spans="2:13">
       <c r="B37" s="40" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C37" s="333">
         <f t="shared" ref="C37:M37" si="2">IF(C$4="","",-C5)</f>
@@ -7052,7 +9629,7 @@
     </row>
     <row r="38" spans="2:13">
       <c r="B38" s="31" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C38" s="329">
         <f>IF(C36="","",C36+C37)</f>
@@ -7101,7 +9678,7 @@
     </row>
     <row r="39" spans="2:13">
       <c r="B39" s="40" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C39" s="333">
         <f t="shared" ref="C39:M39" si="13">IF(C$4="","",-C6)</f>
@@ -7150,7 +9727,7 @@
     </row>
     <row r="40" spans="2:13">
       <c r="B40" s="69" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C40" s="346">
         <f t="shared" ref="C40:M40" si="14">IF(C$4="","",-C7)</f>
@@ -7199,7 +9776,7 @@
     </row>
     <row r="41" spans="2:13">
       <c r="B41" s="69" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C41" s="346">
         <f>IF(C$4="","",C39-C40)</f>
@@ -7248,7 +9825,7 @@
     </row>
     <row r="42" spans="2:13">
       <c r="B42" s="40" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C42" s="333">
         <f t="shared" ref="C42:M42" si="16">IF(C$4="","",-C8)</f>
@@ -7297,7 +9874,7 @@
     </row>
     <row r="43" spans="2:13">
       <c r="B43" s="43" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C43" s="334">
         <f>IF(C$4="","",C38+C39+C42)</f>
@@ -7346,7 +9923,7 @@
     </row>
     <row r="44" spans="2:13">
       <c r="B44" s="43" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C44" s="354">
         <f t="shared" ref="C44:M44" si="18">IF(C$4="","",C47-C46-C45-C43)</f>
@@ -7395,7 +9972,7 @@
     </row>
     <row r="45" spans="2:13">
       <c r="B45" s="40" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C45" s="349">
         <f t="shared" ref="C45:M45" si="19">IF(C$4="","",C51+C52)</f>
@@ -7444,7 +10021,7 @@
     </row>
     <row r="46" spans="2:13">
       <c r="B46" s="40" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C46" s="333">
         <f t="shared" ref="C46:M46" si="20">IF(C$4="","",-C14)</f>
@@ -7493,7 +10070,7 @@
     </row>
     <row r="47" spans="2:13">
       <c r="B47" s="43" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C47" s="334">
         <f t="shared" ref="C47:M47" si="21">IF(C$4="","",C15)</f>
@@ -7542,7 +10119,7 @@
     </row>
     <row r="48" spans="2:13">
       <c r="B48" s="28" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C48" s="333">
         <f t="shared" ref="C48:M48" si="22">IF(C$4="","",MIN(-C16,0))</f>
@@ -7591,12 +10168,12 @@
     </row>
     <row r="50" spans="2:13">
       <c r="B50" s="16" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="51" spans="2:13">
       <c r="B51" s="40" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C51" s="333">
         <f t="shared" ref="C51:M51" si="23">IF(C$4="","",-C12)</f>
@@ -7645,7 +10222,7 @@
     </row>
     <row r="52" spans="2:13">
       <c r="B52" s="40" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C52" s="333">
         <f t="shared" ref="C52:M52" si="24">IF(C$4="","",C13)</f>
@@ -7694,12 +10271,12 @@
     </row>
     <row r="54" spans="2:13">
       <c r="B54" s="174" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="55" spans="2:13">
       <c r="B55" s="40" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C55" s="349">
         <f t="shared" ref="C55:M55" si="25">IF(C$4="","",C9)</f>
@@ -7748,7 +10325,7 @@
     </row>
     <row r="56" spans="2:13">
       <c r="B56" s="40" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="C56" s="349">
         <f t="shared" ref="C56:M56" si="26">IF(C$4="","",C10)</f>
@@ -7797,7 +10374,7 @@
     </row>
     <row r="57" spans="2:13">
       <c r="B57" s="40" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C57" s="349">
         <f t="shared" ref="C57:M57" si="27">IF(C$4="","",C11)</f>
@@ -7846,7 +10423,7 @@
     </row>
     <row r="58" spans="2:13">
       <c r="B58" s="40" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C58" s="349">
         <f>IF(C$4="","",C44-C55-C56-C57)</f>
@@ -7895,13 +10472,13 @@
     </row>
     <row r="60" spans="2:13">
       <c r="B60" s="16" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C60" s="9"/>
     </row>
     <row r="61" spans="2:13">
       <c r="B61" s="27" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C61" s="333">
         <f>IF(C$4="","",-C19)</f>
@@ -7950,7 +10527,7 @@
     </row>
     <row r="62" spans="2:13">
       <c r="B62" s="27" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C62" s="333">
         <f>IF(C$4="","",IF(C20=0,C61,-C20))</f>
@@ -7999,7 +10576,7 @@
     </row>
     <row r="63" spans="2:13">
       <c r="B63" s="27" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C63" s="333">
         <f>IF(C$4="","",-C21)</f>
@@ -8048,7 +10625,7 @@
     </row>
     <row r="64" spans="2:13">
       <c r="B64" s="27" t="s">
-        <v>390</v>
+        <v>374</v>
       </c>
       <c r="C64" s="333">
         <f>IF(C$4="","",C22+C23+C24)</f>
@@ -8097,7 +10674,7 @@
     </row>
     <row r="65" spans="2:13">
       <c r="B65" s="24" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C65" s="73">
         <f>IF(C$4="","",C25)</f>
@@ -8146,7 +10723,7 @@
     </row>
     <row r="67" spans="2:13">
       <c r="B67" s="91" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="68" spans="2:13">
@@ -8201,7 +10778,7 @@
     </row>
     <row r="69" spans="2:13">
       <c r="B69" s="31" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C69" s="92">
         <f>IF(D$36="","",C38/D38-1)</f>
@@ -8300,7 +10877,7 @@
     </row>
     <row r="71" spans="2:13">
       <c r="B71" s="43" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C71" s="101">
         <f>IF(D$36="","",C44/D44-1)</f>
@@ -8399,7 +10976,7 @@
     </row>
     <row r="74" spans="2:13" ht="13.9">
       <c r="B74" s="36" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C74" s="37"/>
       <c r="D74" s="37"/>
@@ -8415,13 +10992,13 @@
     </row>
     <row r="75" spans="2:13">
       <c r="B75" s="16" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C75" s="9"/>
     </row>
     <row r="76" spans="2:13">
       <c r="B76" s="26" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C76" s="76">
         <f>IF(C$4="","",C79+C80)</f>
@@ -8470,7 +11047,7 @@
     </row>
     <row r="77" spans="2:13">
       <c r="B77" s="93" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C77" s="318">
         <f t="shared" ref="C77:H78" si="40">IF(C$4="","",C28)</f>
@@ -8504,7 +11081,7 @@
     </row>
     <row r="78" spans="2:13">
       <c r="B78" s="93" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C78" s="318">
         <f t="shared" si="40"/>
@@ -8538,7 +11115,7 @@
     </row>
     <row r="79" spans="2:13">
       <c r="B79" s="26" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C79" s="317">
         <f t="shared" ref="C79:M79" si="41">IF(C$4="","",C30)</f>
@@ -8587,7 +11164,7 @@
     </row>
     <row r="80" spans="2:13">
       <c r="B80" s="26" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C80" s="317">
         <f t="shared" ref="C80:M80" si="42">IF(C$4="","",C31)</f>
@@ -8659,7 +11236,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet3">
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -8679,7 +11256,7 @@
   <sheetData>
     <row r="1" spans="2:8" ht="15" customHeight="1">
       <c r="B1" s="18" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C1" s="99">
         <v>45657</v>
@@ -8695,7 +11272,7 @@
     </row>
     <row r="2" spans="2:8" ht="15" customHeight="1">
       <c r="B2" s="79" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
@@ -8706,27 +11283,27 @@
     </row>
     <row r="3" spans="2:8" ht="15" customHeight="1">
       <c r="B3" s="16" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C3" s="182" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D3" s="183" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F3" s="16" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="G3" s="182" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="H3" s="183" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="2:8" ht="15" customHeight="1">
       <c r="B4" s="4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C4" s="19">
         <f>13283183.2+236303288.15+178454040.19+7467764.76</f>
@@ -8737,7 +11314,7 @@
       </c>
       <c r="E4" s="25"/>
       <c r="F4" s="4" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="G4" s="19">
         <v>1012553160.92</v>
@@ -8748,7 +11325,7 @@
     </row>
     <row r="5" spans="2:8" ht="15" customHeight="1">
       <c r="B5" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C5" s="19">
         <v>0</v>
@@ -8758,7 +11335,7 @@
       </c>
       <c r="E5" s="25"/>
       <c r="F5" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G5" s="19">
         <v>0</v>
@@ -8769,7 +11346,7 @@
     </row>
     <row r="6" spans="2:8" ht="15" customHeight="1">
       <c r="B6" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C6" s="19">
         <v>149619822.47999999</v>
@@ -8779,7 +11356,7 @@
       </c>
       <c r="E6" s="25"/>
       <c r="F6" s="4" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="G6" s="19">
         <v>0</v>
@@ -8790,7 +11367,7 @@
     </row>
     <row r="7" spans="2:8" ht="15" customHeight="1">
       <c r="B7" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C7" s="19">
         <v>0</v>
@@ -8800,7 +11377,7 @@
       </c>
       <c r="E7" s="25"/>
       <c r="F7" s="4" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="G7" s="19">
         <v>0</v>
@@ -8811,7 +11388,7 @@
     </row>
     <row r="8" spans="2:8" ht="15" customHeight="1">
       <c r="B8" s="1" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C8" s="19">
         <v>0</v>
@@ -8821,7 +11398,7 @@
       </c>
       <c r="E8" s="25"/>
       <c r="F8" s="1" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="G8" s="19">
         <v>0</v>
@@ -8832,7 +11409,7 @@
     </row>
     <row r="9" spans="2:8" ht="15" customHeight="1">
       <c r="B9" s="4" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C9" s="19">
         <v>16483520.83</v>
@@ -8842,7 +11419,7 @@
       </c>
       <c r="E9" s="25"/>
       <c r="F9" s="4" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="G9" s="19">
         <v>0</v>
@@ -8853,7 +11430,7 @@
     </row>
     <row r="10" spans="2:8" ht="15" customHeight="1">
       <c r="B10" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C10" s="19">
         <v>0</v>
@@ -8865,7 +11442,7 @@
     </row>
     <row r="11" spans="2:8" ht="15" customHeight="1">
       <c r="B11" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C11" s="19">
         <v>164978329.56</v>
@@ -8877,7 +11454,7 @@
     </row>
     <row r="12" spans="2:8" ht="15" customHeight="1">
       <c r="B12" s="80" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C12" s="81">
         <f>SUM(C4:C11)</f>
@@ -8888,7 +11465,7 @@
         <v>346012145.58099997</v>
       </c>
       <c r="F12" s="80" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G12" s="81">
         <f>SUM(G4:G9)</f>
@@ -8906,27 +11483,27 @@
     </row>
     <row r="14" spans="2:8" ht="15" customHeight="1">
       <c r="B14" s="16" t="s">
+        <v>179</v>
+      </c>
+      <c r="C14" s="182" t="s">
+        <v>132</v>
+      </c>
+      <c r="D14" s="183" t="s">
+        <v>33</v>
+      </c>
+      <c r="F14" s="16" t="s">
         <v>182</v>
       </c>
-      <c r="C14" s="182" t="s">
-        <v>135</v>
-      </c>
-      <c r="D14" s="183" t="s">
-        <v>35</v>
-      </c>
-      <c r="F14" s="16" t="s">
-        <v>185</v>
-      </c>
       <c r="G14" s="182" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="H14" s="183" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15" spans="2:8" ht="15" customHeight="1">
       <c r="B15" s="4" t="s">
-        <v>451</v>
+        <v>431</v>
       </c>
       <c r="C15" s="19">
         <v>0</v>
@@ -8935,7 +11512,7 @@
         <v>0.4</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="G15" s="19">
         <v>0</v>
@@ -8946,7 +11523,7 @@
     </row>
     <row r="16" spans="2:8" ht="15" customHeight="1">
       <c r="B16" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C16" s="19">
         <v>0</v>
@@ -8955,7 +11532,7 @@
         <v>0.5</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="G16" s="19">
         <v>0</v>
@@ -8966,7 +11543,7 @@
     </row>
     <row r="17" spans="2:8" ht="15" customHeight="1">
       <c r="B17" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C17" s="19">
         <v>0</v>
@@ -8975,7 +11552,7 @@
         <v>0.6</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="G17" s="19">
         <v>0</v>
@@ -8986,7 +11563,7 @@
     </row>
     <row r="18" spans="2:8" ht="15" customHeight="1">
       <c r="B18" s="4" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C18" s="19">
         <v>0</v>
@@ -8995,7 +11572,7 @@
         <v>0.6</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="G18" s="19">
         <v>0</v>
@@ -9006,7 +11583,7 @@
     </row>
     <row r="19" spans="2:8" ht="15" customHeight="1">
       <c r="B19" s="4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C19" s="19">
         <f>821663933.94+22285856.97+7210.09</f>
@@ -9016,7 +11593,7 @@
         <v>0.1</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="G19" s="19">
         <v>0</v>
@@ -9027,7 +11604,7 @@
     </row>
     <row r="20" spans="2:8" ht="15" customHeight="1">
       <c r="B20" s="4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C20" s="19">
         <v>0</v>
@@ -9036,7 +11613,7 @@
         <v>0.05</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="G20" s="19">
         <v>0</v>
@@ -9047,7 +11624,7 @@
     </row>
     <row r="21" spans="2:8" ht="15" customHeight="1">
       <c r="B21" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C21" s="19">
         <v>167917128.12</v>
@@ -9056,7 +11633,7 @@
         <v>0.05</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="G21" s="19">
         <v>0</v>
@@ -9067,7 +11644,7 @@
     </row>
     <row r="22" spans="2:8" ht="15" customHeight="1">
       <c r="B22" s="4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C22" s="19">
         <v>7696458.4000000004</v>
@@ -9079,7 +11656,7 @@
     </row>
     <row r="23" spans="2:8" ht="15" customHeight="1">
       <c r="B23" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C23" s="19">
         <f>1233797.84+2162051.55+11021851.21</f>
@@ -9092,7 +11669,7 @@
     </row>
     <row r="24" spans="2:8" ht="15" customHeight="1">
       <c r="B24" s="80" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C24" s="81">
         <f>SUM(C15:C23)</f>
@@ -9103,7 +11680,7 @@
         <v>99718369.066000029</v>
       </c>
       <c r="F24" s="80" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G24" s="81">
         <f>SUM(G15:G21)</f>
@@ -9116,30 +11693,30 @@
     </row>
     <row r="26" spans="2:8" ht="15" customHeight="1">
       <c r="B26" s="16" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="C26" s="182" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="F26" s="184" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="G26" s="185" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="H26" s="186" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="27" spans="2:8" ht="15" customHeight="1">
       <c r="B27" s="4" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C27" s="19">
         <v>100067739.72</v>
       </c>
       <c r="F27" s="187" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G27" s="85">
         <f>G32-G30</f>
@@ -9152,13 +11729,13 @@
     </row>
     <row r="28" spans="2:8" ht="15" customHeight="1">
       <c r="B28" s="4" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C28" s="19">
         <v>0</v>
       </c>
       <c r="F28" s="189" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="G28" s="12">
         <v>-371705.83</v>
@@ -9167,13 +11744,13 @@
     </row>
     <row r="29" spans="2:8" ht="15" customHeight="1">
       <c r="B29" s="4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C29" s="19">
         <v>0</v>
       </c>
       <c r="F29" s="190" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="G29" s="14">
         <f>G27-G28</f>
@@ -9186,13 +11763,13 @@
     </row>
     <row r="30" spans="2:8" ht="15" customHeight="1">
       <c r="B30" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C30" s="19">
         <v>0</v>
       </c>
       <c r="F30" s="187" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G30" s="85">
         <f>C33+C42</f>
@@ -9202,14 +11779,14 @@
     </row>
     <row r="31" spans="2:8" ht="15" customHeight="1">
       <c r="B31" s="80" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="C31" s="81">
         <f>SUM(C27:C30)</f>
         <v>100067739.72</v>
       </c>
       <c r="F31" s="190" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="G31" s="191">
         <f>C31+C40</f>
@@ -9219,14 +11796,14 @@
     </row>
     <row r="32" spans="2:8" ht="15" customHeight="1">
       <c r="B32" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C32" s="21">
         <f>C33-C31</f>
         <v>281060529.83000004</v>
       </c>
       <c r="F32" s="192" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G32" s="193">
         <f>G35+G40</f>
@@ -9239,7 +11816,7 @@
     </row>
     <row r="33" spans="2:8" ht="15" customHeight="1">
       <c r="B33" s="83" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C33" s="84">
         <v>381128269.55000001</v>
@@ -9252,24 +11829,24 @@
       <c r="B34" s="83"/>
       <c r="C34" s="84"/>
       <c r="F34" s="196" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="G34" s="197" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="H34" s="198" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="35" spans="2:8" ht="15" customHeight="1">
       <c r="B35" s="16" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="C35" s="182" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="F35" s="199" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G35" s="193">
         <f>C12+C24</f>
@@ -9282,13 +11859,13 @@
     </row>
     <row r="36" spans="2:8" ht="15" customHeight="1">
       <c r="B36" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C36" s="19">
         <v>0</v>
       </c>
       <c r="F36" s="190" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="G36" s="191">
         <f>C4+C15</f>
@@ -9298,13 +11875,13 @@
     </row>
     <row r="37" spans="2:8" ht="15" customHeight="1">
       <c r="B37" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C37" s="19">
         <v>0</v>
       </c>
       <c r="F37" s="190" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="G37" s="191">
         <f>C6</f>
@@ -9314,13 +11891,13 @@
     </row>
     <row r="38" spans="2:8" ht="15" customHeight="1">
       <c r="B38" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C38" s="19">
         <v>0</v>
       </c>
       <c r="F38" s="190" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="G38" s="191">
         <f>C7+C17</f>
@@ -9330,13 +11907,13 @@
     </row>
     <row r="39" spans="2:8" ht="15" customHeight="1">
       <c r="B39" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C39" s="19">
         <v>0</v>
       </c>
       <c r="F39" s="190" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G39" s="191">
         <f>C7+C17+C19+C20</f>
@@ -9349,14 +11926,14 @@
     </row>
     <row r="40" spans="2:8" ht="15" customHeight="1">
       <c r="B40" s="80" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="C40" s="81">
         <f>SUM(C36:C39)</f>
         <v>0</v>
       </c>
       <c r="F40" s="199" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="G40" s="193">
         <f>G12+G24</f>
@@ -9369,14 +11946,14 @@
     </row>
     <row r="41" spans="2:8" ht="15" customHeight="1">
       <c r="B41" s="4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C41" s="21">
         <f>C42-C40</f>
         <v>20422655.370000001</v>
       </c>
       <c r="F41" s="190" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="G41" s="191">
         <f>C70</f>
@@ -9389,13 +11966,13 @@
     </row>
     <row r="42" spans="2:8" ht="15" customHeight="1">
       <c r="B42" s="83" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C42" s="84">
         <v>20422655.370000001</v>
       </c>
       <c r="F42" s="201" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="G42" s="202">
         <f>C82</f>
@@ -9408,7 +11985,7 @@
     </row>
     <row r="44" spans="2:8" ht="15" customHeight="1">
       <c r="B44" s="79" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C44" s="37"/>
       <c r="D44" s="37"/>
@@ -9419,21 +11996,21 @@
     </row>
     <row r="45" spans="2:8" ht="15" customHeight="1">
       <c r="B45" s="16" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C45" s="234" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D45" s="182" t="s">
-        <v>402</v>
+        <v>385</v>
       </c>
       <c r="F45" s="256" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="46" spans="2:8" ht="15" customHeight="1">
       <c r="B46" s="1" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="C46" s="76">
         <f>G29</f>
@@ -9465,20 +12042,20 @@
     </row>
     <row r="49" spans="2:8" ht="15" customHeight="1">
       <c r="B49" s="157" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C49" s="235" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D49" s="197" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" s="253"/>
     </row>
     <row r="50" spans="2:8" ht="15" customHeight="1">
       <c r="B50" s="8" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C50" s="95">
         <f>G31/Normalized_FCF!C8</f>
@@ -9492,7 +12069,7 @@
     </row>
     <row r="51" spans="2:8" ht="15" customHeight="1">
       <c r="B51" s="1" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="C51" s="181"/>
       <c r="D51" s="92">
@@ -9506,19 +12083,19 @@
     </row>
     <row r="53" spans="2:8" ht="15" customHeight="1">
       <c r="B53" s="157" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C53" s="235" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D53" s="197" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F53" s="253"/>
     </row>
     <row r="54" spans="2:8" ht="15" customHeight="1">
       <c r="B54" s="1" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C54" s="92">
         <f>Normalized_FCF!C8/G35</f>
@@ -9532,7 +12109,7 @@
     </row>
     <row r="55" spans="2:8" ht="15" customHeight="1">
       <c r="B55" s="1" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C55" s="92">
         <f>Normalized_FCF!C11/G40</f>
@@ -9549,19 +12126,19 @@
     </row>
     <row r="57" spans="2:8" ht="15" customHeight="1">
       <c r="B57" s="157" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="C57" s="235" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D57" s="197" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F57" s="253"/>
     </row>
     <row r="58" spans="2:8" ht="15" customHeight="1">
       <c r="B58" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C58" s="98"/>
       <c r="D58" s="23">
@@ -9572,7 +12149,7 @@
     </row>
     <row r="59" spans="2:8" ht="15" customHeight="1">
       <c r="B59" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C59" s="98"/>
       <c r="D59" s="92">
@@ -9586,19 +12163,19 @@
     </row>
     <row r="61" spans="2:8" ht="15" customHeight="1">
       <c r="B61" s="157" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="C61" s="235" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="D61" s="197" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F61" s="253"/>
     </row>
     <row r="62" spans="2:8" ht="15" customHeight="1">
       <c r="B62" s="1" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="C62" s="92">
         <f>IF(G28&lt;=0,0,G28/G29)</f>
@@ -9609,12 +12186,12 @@
         <v>-1.5410995011336286E-4</v>
       </c>
       <c r="F62" s="253" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
     </row>
     <row r="64" spans="2:8" ht="15" customHeight="1">
       <c r="B64" s="79" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="C64" s="37"/>
       <c r="D64" s="37"/>
@@ -9625,21 +12202,21 @@
     </row>
     <row r="65" spans="2:6" ht="15" customHeight="1">
       <c r="B65" s="16" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C65" s="234" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D65" s="183" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="F65" s="256" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="66" spans="2:6" ht="15" customHeight="1">
       <c r="B66" s="105" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C66" s="20">
         <f>G4+G5+G15</f>
@@ -9650,12 +12227,12 @@
         <v>787007506.71999991</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
     </row>
     <row r="67" spans="2:6" ht="15" customHeight="1">
       <c r="B67" s="105" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="C67" s="20">
         <f>G6+G16</f>
@@ -9665,7 +12242,7 @@
     </row>
     <row r="68" spans="2:6" ht="15" customHeight="1">
       <c r="B68" s="105" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="C68" s="20">
         <f>G18</f>
@@ -9675,7 +12252,7 @@
     </row>
     <row r="69" spans="2:6" ht="15" customHeight="1">
       <c r="B69" s="105" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="C69" s="20">
         <f>G8+G20</f>
@@ -9685,7 +12262,7 @@
     </row>
     <row r="70" spans="2:6" ht="15" customHeight="1">
       <c r="B70" s="80" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C70" s="81">
         <f>SUM(C66:C69)</f>
@@ -9698,19 +12275,19 @@
     </row>
     <row r="72" spans="2:6" ht="15" customHeight="1">
       <c r="B72" s="255" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="C72" s="234" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D72" s="182" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F72" s="253"/>
     </row>
     <row r="73" spans="2:6" ht="15" customHeight="1">
       <c r="B73" s="105" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="C73" s="349">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
@@ -9721,12 +12298,12 @@
         <v>-112772827.10000001</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="15" customHeight="1">
       <c r="B74" s="257" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="C74" s="258">
         <f>-$C$66/C73</f>
@@ -9737,12 +12314,12 @@
         <v>8.978698033544287</v>
       </c>
       <c r="F74" s="253" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
     </row>
     <row r="75" spans="2:6" ht="15" customHeight="1">
       <c r="B75" s="80" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="C75" s="320"/>
       <c r="D75" s="321">
@@ -9750,12 +12327,12 @@
         <v>225545654.20000002</v>
       </c>
       <c r="F75" s="253" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
     </row>
     <row r="76" spans="2:6" ht="15" customHeight="1">
       <c r="B76" s="259" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="C76" s="260"/>
       <c r="D76" s="290">
@@ -9763,7 +12340,7 @@
         <v>2</v>
       </c>
       <c r="F76" s="253" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="15" customHeight="1">
@@ -9771,19 +12348,19 @@
     </row>
     <row r="78" spans="2:6" ht="15" customHeight="1">
       <c r="B78" s="16" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="C78" s="234" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D78" s="183" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F78" s="253"/>
     </row>
     <row r="79" spans="2:6" ht="15" customHeight="1">
       <c r="B79" s="105" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="C79" s="20">
         <f>G7+G17</f>
@@ -9797,7 +12374,7 @@
     </row>
     <row r="80" spans="2:6" ht="15" customHeight="1">
       <c r="B80" s="105" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="C80" s="20">
         <f>G19</f>
@@ -9811,7 +12388,7 @@
     </row>
     <row r="81" spans="2:8" ht="15" customHeight="1">
       <c r="B81" s="105" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="C81" s="20">
         <f>G9+G21</f>
@@ -9825,7 +12402,7 @@
     </row>
     <row r="82" spans="2:8" ht="15" customHeight="1">
       <c r="B82" s="80" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="C82" s="81">
         <f>SUM(C79:C81)</f>
@@ -9839,7 +12416,7 @@
     </row>
     <row r="84" spans="2:8" ht="15" customHeight="1">
       <c r="B84" s="79" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="C84" s="37"/>
       <c r="D84" s="37"/>
@@ -9850,15 +12427,15 @@
     </row>
     <row r="85" spans="2:8" ht="15" customHeight="1">
       <c r="B85" s="16" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D85" s="241" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
     </row>
     <row r="86" spans="2:8" ht="15" customHeight="1">
       <c r="B86" s="238" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="C86" s="76">
         <f>-DCF!C7*Exchange_Rate</f>
@@ -9875,7 +12452,7 @@
     </row>
     <row r="87" spans="2:8" ht="15" customHeight="1">
       <c r="B87" s="238" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="C87" s="76">
         <f>DCF!C8*Exchange_Rate</f>
@@ -9892,7 +12469,7 @@
     </row>
     <row r="88" spans="2:8" ht="15" customHeight="1">
       <c r="B88" s="239" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="C88" s="76">
         <f>DCF!C9*Exchange_Rate</f>
@@ -9909,7 +12486,7 @@
     </row>
     <row r="89" spans="2:8" ht="15" customHeight="1">
       <c r="B89" s="80" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="C89" s="180">
         <f>SUM(C86:C88)</f>
@@ -9931,7 +12508,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2">
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -9957,7 +12534,7 @@
         <v>CNY</v>
       </c>
       <c r="C1" s="53" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D1" s="53"/>
       <c r="E1" s="53"/>
@@ -10010,12 +12587,12 @@
     <row r="2" spans="1:17" ht="15.75" customHeight="1">
       <c r="A2" s="3"/>
       <c r="B2" s="54" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C2" s="54"/>
       <c r="D2" s="56"/>
       <c r="E2" s="66" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F2" s="56"/>
       <c r="G2" s="37"/>
@@ -10033,7 +12610,7 @@
     <row r="3" spans="1:17" ht="15.75" customHeight="1">
       <c r="A3" s="10"/>
       <c r="B3" s="16" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C3" s="107">
         <f>scaling_factor</f>
@@ -10047,7 +12624,7 @@
     <row r="4" spans="1:17" ht="15.75" customHeight="1">
       <c r="A4" s="10"/>
       <c r="B4" s="26" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C4" s="327">
         <f>G4</f>
@@ -10104,7 +12681,7 @@
     <row r="5" spans="1:17" ht="15.75" customHeight="1">
       <c r="A5" s="10"/>
       <c r="B5" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C5" s="328">
         <f>C25</f>
@@ -10159,7 +12736,7 @@
     <row r="6" spans="1:17" ht="15.75" customHeight="1">
       <c r="A6" s="10"/>
       <c r="B6" s="31" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C6" s="329">
         <f>C4+C5</f>
@@ -10214,7 +12791,7 @@
     <row r="7" spans="1:17" ht="15.75" customHeight="1">
       <c r="A7" s="10"/>
       <c r="B7" s="8" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C7" s="328">
         <f>C35</f>
@@ -10269,7 +12846,7 @@
     <row r="8" spans="1:17" ht="15.75" customHeight="1">
       <c r="A8" s="10"/>
       <c r="B8" s="29" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C8" s="330">
         <f>C6+C7</f>
@@ -10326,7 +12903,7 @@
     <row r="9" spans="1:17" ht="15.75" customHeight="1">
       <c r="A9" s="10"/>
       <c r="B9" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C9" s="328">
         <f>BS!$G$39*BS!D58</f>
@@ -10381,7 +12958,7 @@
     <row r="10" spans="1:17" ht="15.75" customHeight="1">
       <c r="A10" s="10"/>
       <c r="B10" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C10" s="328">
         <f>-C4*C78</f>
@@ -10436,7 +13013,7 @@
     <row r="11" spans="1:17" ht="15.75" customHeight="1">
       <c r="A11" s="10"/>
       <c r="B11" s="31" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C11" s="331">
         <f>C63</f>
@@ -10493,7 +13070,7 @@
     <row r="12" spans="1:17" ht="15.75" customHeight="1">
       <c r="A12" s="10"/>
       <c r="B12" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C12" s="328">
         <f>C50</f>
@@ -10548,7 +13125,7 @@
     <row r="13" spans="1:17" ht="15.75" customHeight="1">
       <c r="A13" s="10"/>
       <c r="B13" s="70" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C13" s="329">
         <f>SUM(C8:C12)</f>
@@ -10603,7 +13180,7 @@
     <row r="14" spans="1:17" ht="15.75" customHeight="1">
       <c r="A14" s="10"/>
       <c r="B14" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C14" s="328">
         <f>-SUM(C8+C11,C12)*C43</f>
@@ -10658,7 +13235,7 @@
     <row r="15" spans="1:17" ht="15.75" customHeight="1">
       <c r="A15" s="10"/>
       <c r="B15" s="40" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="C15" s="328">
         <f>-C4*C83</f>
@@ -10715,7 +13292,7 @@
     <row r="16" spans="1:17" ht="15.75" customHeight="1">
       <c r="A16" s="10"/>
       <c r="B16" s="41" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C16" s="332">
         <f>SUM(C13:C15)</f>
@@ -10772,7 +13349,7 @@
     <row r="17" spans="1:17" ht="15.75" customHeight="1">
       <c r="A17" s="10"/>
       <c r="B17" s="27" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C17" s="328">
         <f>-C4*C85</f>
@@ -10780,7 +13357,7 @@
       </c>
       <c r="D17" s="58"/>
       <c r="E17" s="267" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="F17" s="58"/>
       <c r="G17" s="335"/>
@@ -10798,14 +13375,14 @@
     <row r="18" spans="1:17" ht="15.75" customHeight="1">
       <c r="A18" s="10"/>
       <c r="B18" s="27" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C18" s="328">
         <v>0</v>
       </c>
       <c r="D18" s="58"/>
       <c r="E18" s="267" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="F18" s="58"/>
       <c r="G18" s="336"/>
@@ -10823,7 +13400,7 @@
     <row r="19" spans="1:17" ht="15.75" customHeight="1">
       <c r="A19" s="10"/>
       <c r="B19" s="31" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C19" s="329">
         <f>C16+C17</f>
@@ -10899,12 +13476,12 @@
     <row r="21" spans="1:17" ht="15.75" customHeight="1">
       <c r="A21" s="10"/>
       <c r="B21" s="54" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="C21" s="54"/>
       <c r="D21" s="56"/>
       <c r="E21" s="66" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F21" s="56"/>
       <c r="G21" s="37"/>
@@ -10922,7 +13499,7 @@
     <row r="22" spans="1:17" ht="15.75" customHeight="1">
       <c r="A22" s="10"/>
       <c r="B22" s="64" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C22" s="62"/>
       <c r="D22" s="27"/>
@@ -10943,7 +13520,7 @@
     <row r="23" spans="1:17" ht="15.75" customHeight="1">
       <c r="A23" s="10"/>
       <c r="B23" s="27" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C23" s="337">
         <f>-C4*C28</f>
@@ -11000,7 +13577,7 @@
     <row r="24" spans="1:17" ht="15.75" customHeight="1">
       <c r="A24" s="10"/>
       <c r="B24" s="68" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C24" s="328">
         <f>-C4*C29</f>
@@ -11057,7 +13634,7 @@
     <row r="25" spans="1:17" ht="15.75" customHeight="1">
       <c r="A25" s="10"/>
       <c r="B25" s="70" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C25" s="329">
         <f>C23+C24</f>
@@ -11118,14 +13695,14 @@
     <row r="27" spans="1:17" ht="15.75" customHeight="1">
       <c r="A27" s="10"/>
       <c r="B27" s="64" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="E27" s="268"/>
     </row>
     <row r="28" spans="1:17" ht="15.75" customHeight="1">
       <c r="A28" s="10"/>
       <c r="B28" s="26" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C28" s="63">
         <f>G28</f>
@@ -11133,7 +13710,7 @@
       </c>
       <c r="D28" s="26"/>
       <c r="E28" s="266" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="F28" s="26"/>
       <c r="G28" s="13">
@@ -11193,7 +13770,7 @@
       </c>
       <c r="D29" s="26"/>
       <c r="E29" s="266" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="F29" s="26"/>
       <c r="G29" s="13">
@@ -11244,7 +13821,7 @@
     <row r="30" spans="1:17" ht="15.75" customHeight="1">
       <c r="A30" s="10"/>
       <c r="B30" s="70" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C30" s="71">
         <f>ABS(C25/$C$4)</f>
@@ -11303,21 +13880,21 @@
     <row r="32" spans="1:17" ht="15.75" customHeight="1">
       <c r="A32" s="10"/>
       <c r="B32" s="64" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E32" s="268"/>
     </row>
     <row r="33" spans="1:17" ht="15.75" customHeight="1">
       <c r="A33" s="10"/>
       <c r="B33" s="8" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="C33" s="340">
         <f>G33</f>
         <v>-33090730</v>
       </c>
       <c r="E33" s="266" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="G33" s="328">
         <f>Data!C41</f>
@@ -11367,7 +13944,7 @@
     <row r="34" spans="1:17" ht="15.75" customHeight="1">
       <c r="A34" s="10"/>
       <c r="B34" s="27" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C34" s="340">
         <f>AVERAGE(G34:J34)</f>
@@ -11375,7 +13952,7 @@
       </c>
       <c r="D34" s="58"/>
       <c r="E34" s="266" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="F34" s="58"/>
       <c r="G34" s="333">
@@ -11426,7 +14003,7 @@
     <row r="35" spans="1:17" ht="15.75" customHeight="1">
       <c r="A35" s="10"/>
       <c r="B35" s="70" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C35" s="329">
         <f>C33+C34</f>
@@ -11487,7 +14064,7 @@
     <row r="37" spans="1:17" ht="15.75" customHeight="1">
       <c r="A37" s="10"/>
       <c r="B37" s="64" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="E37" s="268"/>
     </row>
@@ -11610,7 +14187,7 @@
     <row r="40" spans="1:17" ht="15.75" customHeight="1">
       <c r="A40" s="10"/>
       <c r="B40" s="70" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C40" s="71">
         <f>ABS(C35/$C$4)</f>
@@ -11669,21 +14246,21 @@
     <row r="42" spans="1:17" ht="15.75" customHeight="1">
       <c r="A42" s="10"/>
       <c r="B42" s="64" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="E42" s="268"/>
     </row>
     <row r="43" spans="1:17" ht="15.75" customHeight="1">
       <c r="A43" s="10"/>
       <c r="B43" s="27" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="C43" s="263">
         <v>0.25</v>
       </c>
       <c r="D43" s="27"/>
       <c r="E43" s="265" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="F43" s="27"/>
       <c r="G43" s="6">
@@ -11737,12 +14314,12 @@
     <row r="45" spans="1:17" ht="15.75" customHeight="1">
       <c r="A45" s="10"/>
       <c r="B45" s="54" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="C45" s="54"/>
       <c r="D45" s="56"/>
       <c r="E45" s="66" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F45" s="56"/>
       <c r="G45" s="37"/>
@@ -11760,14 +14337,14 @@
     <row r="46" spans="1:17" ht="15.75" customHeight="1">
       <c r="A46" s="10"/>
       <c r="B46" s="64" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E46" s="268"/>
     </row>
     <row r="47" spans="1:17" ht="15.75" customHeight="1">
       <c r="A47" s="10"/>
       <c r="B47" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C47" s="328">
         <f>-BS!G31*Normalized_FCF!C54</f>
@@ -11822,7 +14399,7 @@
     <row r="48" spans="1:17" ht="15.75" customHeight="1">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="C48" s="328">
         <f>BS!D75*C53</f>
@@ -11877,7 +14454,7 @@
     <row r="49" spans="1:17" ht="15.75" customHeight="1">
       <c r="A49" s="10"/>
       <c r="B49" s="287" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="C49" s="342">
         <f>BS!$C$66*C53</f>
@@ -11934,7 +14511,7 @@
     <row r="50" spans="1:17" ht="15.75" customHeight="1">
       <c r="A50" s="10"/>
       <c r="B50" s="70" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C50" s="329">
         <f>C47+C48</f>
@@ -11993,23 +14570,23 @@
     <row r="52" spans="1:17" ht="15.75" customHeight="1">
       <c r="A52" s="10"/>
       <c r="B52" s="72" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="E52" s="268"/>
       <c r="G52" s="97" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
     </row>
     <row r="53" spans="1:17" ht="15.75" customHeight="1">
       <c r="A53" s="10"/>
       <c r="B53" s="8" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C53" s="87">
         <v>1.4999999999999999E-2</v>
       </c>
       <c r="E53" s="265" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="G53" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G49/BS!$C$66)</f>
@@ -12029,14 +14606,14 @@
     <row r="54" spans="1:17" ht="15.75" customHeight="1">
       <c r="A54" s="10"/>
       <c r="B54" s="8" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C54" s="82">
         <f>G54</f>
         <v>5.216417413450098E-2</v>
       </c>
       <c r="E54" s="265" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="G54" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
@@ -12056,7 +14633,7 @@
     <row r="55" spans="1:17" ht="15.75" customHeight="1">
       <c r="A55" s="10"/>
       <c r="B55" s="26" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C55" s="42">
         <f>-C8/C47</f>
@@ -12115,17 +14692,17 @@
     <row r="57" spans="1:17" ht="15.75" customHeight="1">
       <c r="A57" s="10"/>
       <c r="B57" s="64" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="E57" s="268"/>
       <c r="G57" s="97" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
     </row>
     <row r="58" spans="1:17" ht="15.75" customHeight="1">
       <c r="A58" s="10"/>
       <c r="B58" s="40" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="C58" s="328">
         <f>BS!$C67*C66</f>
@@ -12180,7 +14757,7 @@
     <row r="59" spans="1:17" ht="15.75" customHeight="1">
       <c r="A59" s="10"/>
       <c r="B59" s="40" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C59" s="328">
         <f>BS!$C68*C67</f>
@@ -12235,7 +14812,7 @@
     <row r="60" spans="1:17" ht="15.75" customHeight="1">
       <c r="A60" s="10"/>
       <c r="B60" s="40" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C60" s="328">
         <f>BS!$C69*C68</f>
@@ -12290,7 +14867,7 @@
     <row r="61" spans="1:17" ht="15.75" customHeight="1">
       <c r="A61" s="10"/>
       <c r="B61" s="31" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C61" s="329">
         <f>SUM(C58:C60)</f>
@@ -12345,13 +14922,13 @@
     <row r="62" spans="1:17" ht="15.75" customHeight="1">
       <c r="A62" s="10"/>
       <c r="B62" s="40" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C62" s="343">
         <v>0</v>
       </c>
       <c r="E62" s="266" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="G62" s="328">
         <f>Data!C58</f>
@@ -12401,7 +14978,7 @@
     <row r="63" spans="1:17" ht="15.75" customHeight="1">
       <c r="A63" s="10"/>
       <c r="B63" s="31" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="C63" s="329">
         <f>C61+C62</f>
@@ -12460,17 +15037,17 @@
     <row r="65" spans="1:17" ht="15.75" customHeight="1">
       <c r="A65" s="10"/>
       <c r="B65" s="96" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="E65" s="268"/>
       <c r="G65" s="97" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
     </row>
     <row r="66" spans="1:17" ht="15.75" customHeight="1">
       <c r="A66" s="10"/>
       <c r="B66" s="40" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="C66" s="176">
         <f>G66</f>
@@ -12495,7 +15072,7 @@
     <row r="67" spans="1:17" ht="15.75" customHeight="1">
       <c r="A67" s="10"/>
       <c r="B67" s="105" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C67" s="176">
         <f>G67</f>
@@ -12520,7 +15097,7 @@
     <row r="68" spans="1:17" ht="15.75" customHeight="1">
       <c r="A68" s="10"/>
       <c r="B68" s="105" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C68" s="176">
         <f>G68</f>
@@ -12545,7 +15122,7 @@
     <row r="69" spans="1:17" ht="15.75" customHeight="1">
       <c r="A69" s="10"/>
       <c r="B69" s="31" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C69" s="71">
         <f>C61/BS!C70</f>
@@ -12575,12 +15152,12 @@
     <row r="71" spans="1:17" ht="15.75" customHeight="1">
       <c r="A71" s="10"/>
       <c r="B71" s="54" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="C71" s="54"/>
       <c r="D71" s="56"/>
       <c r="E71" s="66" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F71" s="56"/>
       <c r="G71" s="37"/>
@@ -12598,7 +15175,7 @@
     <row r="72" spans="1:17" ht="15.75" customHeight="1">
       <c r="A72" s="10"/>
       <c r="B72" s="72" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="C72" s="62"/>
       <c r="D72" s="27"/>
@@ -12619,7 +15196,7 @@
     <row r="73" spans="1:17" ht="15.75" customHeight="1">
       <c r="A73" s="10"/>
       <c r="B73" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C73" s="77">
         <f>ABS(C5/C$4)</f>
@@ -12676,7 +15253,7 @@
     <row r="74" spans="1:17" ht="15.75" customHeight="1">
       <c r="A74" s="10"/>
       <c r="B74" s="31" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C74" s="78">
         <f>ABS(C6/C$4)</f>
@@ -12733,7 +15310,7 @@
     <row r="75" spans="1:17" ht="15.75" customHeight="1">
       <c r="A75" s="10"/>
       <c r="B75" s="8" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C75" s="77">
         <f>ABS(C7/C$4)</f>
@@ -12790,7 +15367,7 @@
     <row r="76" spans="1:17" ht="15.75" customHeight="1">
       <c r="A76" s="10"/>
       <c r="B76" s="29" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C76" s="78">
         <f>ABS(C8/C$4)</f>
@@ -12847,7 +15424,7 @@
     <row r="77" spans="1:17" ht="15.75" customHeight="1">
       <c r="A77" s="10"/>
       <c r="B77" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C77" s="77">
         <f>ABS(C9/C$4)</f>
@@ -12904,7 +15481,7 @@
     <row r="78" spans="1:17" ht="15.75" customHeight="1">
       <c r="A78" s="10"/>
       <c r="B78" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C78" s="88">
         <f>MAX(AVERAGE(G78:J78),C77)</f>
@@ -12912,7 +15489,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="266" t="s">
-        <v>465</v>
+        <v>559</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -12963,7 +15540,7 @@
     <row r="79" spans="1:17" ht="15.75" customHeight="1">
       <c r="A79" s="10"/>
       <c r="B79" s="31" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C79" s="78">
         <f>ABS(C11/C$4)</f>
@@ -13020,7 +15597,7 @@
     <row r="80" spans="1:17" ht="15.75" customHeight="1">
       <c r="A80" s="10"/>
       <c r="B80" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C80" s="77">
         <f>ABS(C12/C$4)</f>
@@ -13077,7 +15654,7 @@
     <row r="81" spans="1:17" ht="15.75" customHeight="1">
       <c r="A81" s="10"/>
       <c r="B81" s="70" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C81" s="78">
         <f>C13/C4</f>
@@ -13134,7 +15711,7 @@
     <row r="82" spans="1:17" ht="15.75" customHeight="1">
       <c r="A82" s="10"/>
       <c r="B82" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C82" s="77">
         <f>ABS(C14/C$4)</f>
@@ -13249,7 +15826,7 @@
     <row r="84" spans="1:17" ht="15.75" customHeight="1">
       <c r="A84" s="10"/>
       <c r="B84" s="41" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C84" s="78">
         <f>ABS(C16/C$4)</f>
@@ -13306,7 +15883,7 @@
     <row r="85" spans="1:17" ht="15.75" customHeight="1">
       <c r="A85" s="10"/>
       <c r="B85" s="27" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C85" s="264">
         <v>0</v>
@@ -13332,7 +15909,7 @@
     <row r="86" spans="1:17" ht="15.75" customHeight="1">
       <c r="A86" s="10"/>
       <c r="B86" s="8" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C86" s="77">
         <v>0</v>
@@ -13356,7 +15933,7 @@
     <row r="87" spans="1:17" ht="15.75" customHeight="1">
       <c r="A87" s="10"/>
       <c r="B87" s="31" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C87" s="78">
         <f>ABS(C19/C$4)</f>
@@ -13417,7 +15994,7 @@
     <row r="89" spans="1:17" ht="15.75" customHeight="1">
       <c r="A89" s="10"/>
       <c r="B89" s="64" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="E89" s="268"/>
     </row>
@@ -13536,7 +16113,7 @@
     <row r="92" spans="1:17" ht="15.75" customHeight="1">
       <c r="A92" s="10"/>
       <c r="B92" s="2" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*scaling_factor/Common_Shares)</f>
@@ -13591,7 +16168,7 @@
     <row r="93" spans="1:17" ht="15.75" customHeight="1">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
-        <v>453</v>
+        <v>433</v>
       </c>
       <c r="C93" s="356">
         <v>0.1</v>
@@ -13612,7 +16189,7 @@
     <row r="94" spans="1:17" ht="15.75" customHeight="1">
       <c r="A94" s="10"/>
       <c r="B94" s="2" t="s">
-        <v>452</v>
+        <v>432</v>
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
@@ -13671,7 +16248,7 @@
     <row r="96" spans="1:17" ht="15.75" customHeight="1">
       <c r="A96" s="10"/>
       <c r="B96" s="157" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C96" s="62"/>
       <c r="D96" s="27"/>
@@ -13692,7 +16269,7 @@
     <row r="97" spans="1:17" ht="15.75" customHeight="1">
       <c r="A97" s="10"/>
       <c r="B97" s="27" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C97" s="77">
         <f>C4/G4-1</f>
@@ -13749,7 +16326,7 @@
     <row r="98" spans="1:17" ht="15.75" customHeight="1">
       <c r="A98" s="10"/>
       <c r="B98" s="70" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C98" s="77">
         <f>C13/G13-1</f>
@@ -13809,12 +16386,12 @@
     <row r="100" spans="1:17" ht="15.75" customHeight="1">
       <c r="A100" s="3"/>
       <c r="B100" s="54" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="C100" s="54"/>
       <c r="D100" s="56"/>
       <c r="E100" s="66" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F100" s="56"/>
       <c r="G100" s="37"/>
@@ -13832,17 +16409,17 @@
     <row r="101" spans="1:17" ht="15.75" customHeight="1">
       <c r="A101" s="10"/>
       <c r="B101" s="64" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E101" s="268"/>
       <c r="G101" s="97" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
     </row>
     <row r="102" spans="1:17" ht="15.75" customHeight="1">
       <c r="A102" s="10"/>
       <c r="B102" s="26" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C102" s="344">
         <f>BS!G32</f>
@@ -13899,7 +16476,7 @@
     <row r="103" spans="1:17" ht="15.75" customHeight="1">
       <c r="A103" s="10"/>
       <c r="B103" s="93" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="C103" s="345">
         <f>BS!C4</f>
@@ -13956,7 +16533,7 @@
     <row r="104" spans="1:17" ht="15.75" customHeight="1">
       <c r="A104" s="10"/>
       <c r="B104" s="93" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="C104" s="345">
         <f>BS!C6+BS!C7</f>
@@ -14013,7 +16590,7 @@
     <row r="105" spans="1:17" ht="15.75" customHeight="1">
       <c r="A105" s="10"/>
       <c r="B105" s="26" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C105" s="344">
         <f>BS!G30</f>
@@ -14070,7 +16647,7 @@
     <row r="106" spans="1:17" ht="15.75" customHeight="1">
       <c r="A106" s="10"/>
       <c r="B106" s="26" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C106" s="344">
         <f>BS!G27</f>
@@ -14131,14 +16708,14 @@
     <row r="108" spans="1:17" ht="15.75" customHeight="1">
       <c r="A108" s="10"/>
       <c r="B108" s="91" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="C108" s="26"/>
       <c r="D108" s="26"/>
       <c r="E108" s="269"/>
       <c r="F108" s="26"/>
       <c r="G108" s="97" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="H108" s="12"/>
       <c r="I108" s="12"/>
@@ -14154,7 +16731,7 @@
     <row r="109" spans="1:17" ht="15.75" customHeight="1">
       <c r="A109" s="10"/>
       <c r="B109" s="26" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="C109" s="94">
         <f>C103/C$4</f>
@@ -14211,7 +16788,7 @@
     <row r="110" spans="1:17" ht="15.75" customHeight="1">
       <c r="A110" s="10"/>
       <c r="B110" s="26" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="C110" s="94">
         <f>C104/C$4</f>
@@ -14268,7 +16845,7 @@
     <row r="111" spans="1:17" ht="15.75" customHeight="1">
       <c r="A111" s="10"/>
       <c r="B111" s="26" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C111" s="94">
         <f>BS!$G$38/C$4</f>
@@ -14299,14 +16876,14 @@
     <row r="113" spans="1:17" ht="15.75" customHeight="1">
       <c r="A113" s="10"/>
       <c r="B113" s="64" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E113" s="268"/>
     </row>
     <row r="114" spans="1:17" ht="15.75" customHeight="1">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
-        <v>388</v>
+        <v>372</v>
       </c>
       <c r="C114" s="169"/>
       <c r="E114" s="268"/>
@@ -14358,7 +16935,7 @@
     <row r="115" spans="1:17" ht="15.75" customHeight="1">
       <c r="A115" s="10"/>
       <c r="B115" s="2" t="s">
-        <v>389</v>
+        <v>373</v>
       </c>
       <c r="C115" s="169"/>
       <c r="E115" s="268"/>
@@ -14414,7 +16991,7 @@
     <row r="117" spans="1:17" ht="15.75" customHeight="1">
       <c r="A117" s="10"/>
       <c r="B117" s="91" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C117" s="55"/>
       <c r="D117" s="55"/>
@@ -14468,7 +17045,7 @@
     <row r="118" spans="1:17" ht="15.75" customHeight="1">
       <c r="A118" s="10"/>
       <c r="B118" s="7" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C118" s="23">
         <f>IF(valuation_method="DDM",C13/(C4+C12),C81)</f>
@@ -14522,7 +17099,7 @@
     </row>
     <row r="119" spans="1:17" ht="15.75" customHeight="1">
       <c r="B119" s="7" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C119" s="42">
         <f>IF(valuation_method="DDM",(C4+C12)/C102,C4/C102)</f>
@@ -14576,7 +17153,7 @@
     </row>
     <row r="120" spans="1:17" ht="15.75" customHeight="1">
       <c r="B120" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C120" s="15">
         <f>C102/C106</f>
@@ -14633,7 +17210,7 @@
     <row r="121" spans="1:17" ht="15.75" customHeight="1">
       <c r="A121" s="10"/>
       <c r="B121" s="70" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="C121" s="102">
         <f>C13/C106</f>
@@ -14709,12 +17286,12 @@
     <row r="123" spans="1:17" ht="15.75" customHeight="1">
       <c r="A123" s="10"/>
       <c r="B123" s="54" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="C123" s="54"/>
       <c r="D123" s="56"/>
       <c r="E123" s="66" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F123" s="56"/>
       <c r="G123" s="37"/>
@@ -14732,7 +17309,7 @@
     <row r="124" spans="1:17" ht="15.75" customHeight="1">
       <c r="A124" s="10"/>
       <c r="B124" s="178" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C124" s="179"/>
       <c r="D124" s="27"/>
@@ -14811,7 +17388,7 @@
     <row r="126" spans="1:17" ht="15.75" customHeight="1">
       <c r="A126" s="10"/>
       <c r="B126" s="27" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
@@ -14867,7 +17444,7 @@
     </row>
     <row r="127" spans="1:17" ht="15.75" customHeight="1">
       <c r="B127" s="2" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
       <c r="C127" s="169"/>
       <c r="G127" s="23">
@@ -15612,7 +18189,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3EAD7ED-D484-47B2-9C7C-1D1BCBEAE5A9}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -15629,32 +18206,32 @@
   <sheetData>
     <row r="2" spans="2:8" ht="13.9">
       <c r="B2" s="36" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
       <c r="H2" s="130" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="2:8" ht="13.15">
       <c r="B3" s="109" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C3" s="107">
         <f>scaling_factor</f>
         <v>1</v>
       </c>
       <c r="E3" s="109" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="H3" s="120"/>
     </row>
     <row r="4" spans="2:8">
       <c r="B4" s="100" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C4" s="338">
         <f>Normalized_FCF!C19</f>
@@ -15665,7 +18242,7 @@
         <v>CNY</v>
       </c>
       <c r="E4" s="100" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="F4" s="134">
         <f>Terminal_Growth</f>
@@ -15675,7 +18252,7 @@
     </row>
     <row r="5" spans="2:8">
       <c r="B5" s="205" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C5" s="206">
         <f>Equity_Cost</f>
@@ -15686,7 +18263,7 @@
     </row>
     <row r="6" spans="2:8" ht="13.35" customHeight="1">
       <c r="B6" s="149" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="C6" s="347">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
@@ -15696,15 +18273,15 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="369" t="s">
-        <v>248</v>
-      </c>
-      <c r="F6" s="369"/>
+      <c r="E6" s="375" t="s">
+        <v>245</v>
+      </c>
+      <c r="F6" s="375"/>
       <c r="H6" s="120"/>
     </row>
     <row r="7" spans="2:8">
       <c r="B7" s="148" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="C7" s="338">
         <f>BS!G31</f>
@@ -15714,13 +18291,13 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="369"/>
-      <c r="F7" s="369"/>
+      <c r="E7" s="375"/>
+      <c r="F7" s="375"/>
       <c r="H7" s="120"/>
     </row>
     <row r="8" spans="2:8">
       <c r="B8" s="148" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="C8" s="338">
         <f>BS!D66</f>
@@ -15730,13 +18307,13 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="369"/>
-      <c r="F8" s="369"/>
+      <c r="E8" s="375"/>
+      <c r="F8" s="375"/>
       <c r="H8" s="120"/>
     </row>
     <row r="9" spans="2:8">
       <c r="B9" s="205" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C9" s="348">
         <f>BS!H42</f>
@@ -15746,13 +18323,13 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="369"/>
-      <c r="F9" s="369"/>
+      <c r="E9" s="375"/>
+      <c r="F9" s="375"/>
       <c r="H9" s="120"/>
     </row>
     <row r="10" spans="2:8" ht="13.15">
       <c r="B10" s="149" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="C10" s="347">
         <f>C6-C7+C8+C9</f>
@@ -15766,7 +18343,7 @@
     </row>
     <row r="11" spans="2:8" ht="13.15" thickBot="1">
       <c r="B11" s="207" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C11" s="208">
         <f>Exchange_Rate</f>
@@ -15780,7 +18357,7 @@
     </row>
     <row r="12" spans="2:8" ht="13.5" thickTop="1">
       <c r="B12" s="149" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C12" s="111">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
@@ -15797,7 +18374,7 @@
     </row>
     <row r="14" spans="2:8" ht="13.9">
       <c r="B14" s="36" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="C14" s="37"/>
       <c r="D14" s="37"/>
@@ -15807,13 +18384,13 @@
     </row>
     <row r="15" spans="2:8" ht="13.15">
       <c r="B15" s="119" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="H15" s="120"/>
     </row>
     <row r="16" spans="2:8" ht="13.35" customHeight="1">
       <c r="B16" s="152" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C16" s="161">
         <f>Scenarios!C65</f>
@@ -15823,7 +18400,7 @@
     </row>
     <row r="17" spans="2:17" ht="13.35" customHeight="1">
       <c r="B17" s="118" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C17" s="162">
         <f>Scenarios!C64</f>
@@ -15833,7 +18410,7 @@
     </row>
     <row r="18" spans="2:17" ht="13.35" customHeight="1">
       <c r="B18" s="153" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C18" s="140">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
@@ -15850,19 +18427,19 @@
     </row>
     <row r="20" spans="2:17" ht="13.15">
       <c r="B20" s="128" t="s">
+        <v>104</v>
+      </c>
+      <c r="C20" s="128" t="s">
+        <v>105</v>
+      </c>
+      <c r="D20" s="128" t="s">
+        <v>114</v>
+      </c>
+      <c r="E20" s="128" t="s">
+        <v>106</v>
+      </c>
+      <c r="F20" s="129" t="s">
         <v>107</v>
-      </c>
-      <c r="C20" s="128" t="s">
-        <v>108</v>
-      </c>
-      <c r="D20" s="128" t="s">
-        <v>117</v>
-      </c>
-      <c r="E20" s="128" t="s">
-        <v>109</v>
-      </c>
-      <c r="F20" s="129" t="s">
-        <v>110</v>
       </c>
       <c r="H20" s="120"/>
     </row>
@@ -16628,7 +19205,7 @@
     </row>
     <row r="51" spans="1:17">
       <c r="B51" s="126" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C51" s="123">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
@@ -16651,7 +19228,7 @@
     <row r="52" spans="1:17">
       <c r="C52" s="114"/>
       <c r="E52" s="127" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F52" s="137">
         <f>SUM(F21:F51)</f>
@@ -16665,7 +19242,7 @@
     </row>
     <row r="54" spans="1:17" ht="13.15">
       <c r="B54" s="119" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C54" s="136"/>
       <c r="D54" s="136"/>
@@ -16886,7 +19463,7 @@
     </row>
     <row r="63" spans="1:17" ht="13.15">
       <c r="B63" s="119" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C63" s="338"/>
       <c r="D63" s="114"/>
@@ -17115,19 +19692,19 @@
     </row>
     <row r="73" spans="1:8" ht="13.15">
       <c r="B73" s="171" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C73" s="171" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D73" s="171" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E73" s="172" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="F73" s="172" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="74" spans="1:8">
@@ -17252,20 +19829,20 @@
     </row>
     <row r="80" spans="1:8">
       <c r="B80" s="155" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="C80" s="155" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="81" spans="3:3">
       <c r="C81" s="155" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
     </row>
     <row r="82" spans="3:3">
       <c r="C82" s="155" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="92" spans="3:3">
@@ -17372,7 +19949,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A27DB9BF-8D77-49A8-A09B-23E6CA7BEA90}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -17389,32 +19966,32 @@
   <sheetData>
     <row r="2" spans="2:8" ht="13.9">
       <c r="B2" s="36" t="s">
-        <v>440</v>
+        <v>420</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
       <c r="H2" s="130" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="2:8" ht="13.15">
       <c r="B3" s="109" t="s">
-        <v>439</v>
+        <v>419</v>
       </c>
       <c r="C3" s="107">
         <f>scaling_factor</f>
         <v>1</v>
       </c>
       <c r="E3" s="109" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="H3" s="120"/>
     </row>
     <row r="4" spans="2:8">
       <c r="B4" s="100" t="s">
-        <v>437</v>
+        <v>417</v>
       </c>
       <c r="C4" s="114">
         <f>Normalized_FCF!C91*(1-dividend_tax_rate)</f>
@@ -17425,7 +20002,7 @@
         <v>CNY</v>
       </c>
       <c r="E4" s="100" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="F4" s="134">
         <f>Thesis!E22</f>
@@ -17435,7 +20012,7 @@
     </row>
     <row r="5" spans="2:8">
       <c r="B5" s="205" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C5" s="206">
         <f>Equity_Cost</f>
@@ -17446,7 +20023,7 @@
     </row>
     <row r="6" spans="2:8" ht="13.35" customHeight="1">
       <c r="B6" s="149" t="s">
-        <v>438</v>
+        <v>418</v>
       </c>
       <c r="C6" s="319">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
@@ -17456,13 +20033,13 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="369"/>
-      <c r="F6" s="369"/>
+      <c r="E6" s="375"/>
+      <c r="F6" s="375"/>
       <c r="H6" s="120"/>
     </row>
     <row r="7" spans="2:8" ht="13.15">
       <c r="B7" s="149" t="s">
-        <v>441</v>
+        <v>421</v>
       </c>
       <c r="C7" s="111">
         <f>(C6*scaling_factor)/Common_Shares*Exchange_Rate</f>
@@ -17479,7 +20056,7 @@
     </row>
     <row r="9" spans="2:8" ht="13.9">
       <c r="B9" s="36" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="C9" s="37"/>
       <c r="D9" s="37"/>
@@ -17489,13 +20066,13 @@
     </row>
     <row r="10" spans="2:8" ht="13.15">
       <c r="B10" s="119" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="H10" s="120"/>
     </row>
     <row r="11" spans="2:8" ht="13.35" customHeight="1">
       <c r="B11" s="152" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C11" s="161">
         <f>Scenarios!C65</f>
@@ -17505,7 +20082,7 @@
     </row>
     <row r="12" spans="2:8" ht="13.35" customHeight="1">
       <c r="B12" s="118" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C12" s="162">
         <f>Scenarios!C64</f>
@@ -17515,7 +20092,7 @@
     </row>
     <row r="13" spans="2:8" ht="13.35" customHeight="1">
       <c r="B13" s="153" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C13" s="140">
         <f>F47/Common_Shares*scaling_factor</f>
@@ -17532,19 +20109,19 @@
     </row>
     <row r="15" spans="2:8" ht="13.15">
       <c r="B15" s="128" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C15" s="128" t="s">
-        <v>443</v>
+        <v>423</v>
       </c>
       <c r="D15" s="128" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E15" s="128" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="F15" s="129" t="s">
-        <v>442</v>
+        <v>422</v>
       </c>
       <c r="H15" s="120"/>
     </row>
@@ -18210,7 +20787,7 @@
     </row>
     <row r="46" spans="2:8">
       <c r="B46" s="126" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C46" s="123">
         <f>C$16*(1+F4)^$C$12/Equity_Cost</f>
@@ -18233,7 +20810,7 @@
     <row r="47" spans="2:8">
       <c r="C47" s="114"/>
       <c r="E47" s="127" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F47" s="137">
         <f>SUM(F16:F46)</f>
@@ -18247,7 +20824,7 @@
     </row>
     <row r="49" spans="1:8" ht="13.15">
       <c r="B49" s="119" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C49" s="136"/>
       <c r="D49" s="136"/>
@@ -18418,7 +20995,7 @@
     </row>
     <row r="58" spans="1:8" ht="13.15">
       <c r="B58" s="119" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C58" s="114"/>
       <c r="D58" s="114"/>
@@ -18637,19 +21214,19 @@
     </row>
     <row r="68" spans="1:8" ht="13.15">
       <c r="B68" s="171" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C68" s="171" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D68" s="171" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E68" s="172" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="F68" s="172" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="69" spans="1:8">
@@ -18774,20 +21351,20 @@
     </row>
     <row r="75" spans="1:8">
       <c r="B75" s="155" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="C75" s="155" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="76" spans="1:8">
       <c r="C76" s="155" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
     </row>
     <row r="77" spans="1:8">
       <c r="C77" s="155" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="87" spans="3:3">
@@ -18823,7 +21400,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
   <dimension ref="B2:I110"/>
   <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
@@ -18838,20 +21415,20 @@
   <sheetData>
     <row r="2" spans="2:9" ht="13.9">
       <c r="B2" s="36" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
       <c r="H2" s="248" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="I2" s="249"/>
     </row>
     <row r="3" spans="2:9" ht="13.15">
       <c r="B3" s="159" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="H3" s="247">
         <v>0</v>
@@ -18863,14 +21440,14 @@
     </row>
     <row r="4" spans="2:9">
       <c r="B4" s="152" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C4" s="120">
         <v>3</v>
       </c>
       <c r="D4" s="120"/>
       <c r="E4" s="155" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="F4" s="155"/>
       <c r="H4" s="247">
@@ -18892,14 +21469,14 @@
     </row>
     <row r="6" spans="2:9" ht="13.15">
       <c r="B6" s="159" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C6" s="107">
         <f>DCF!C3</f>
         <v>1</v>
       </c>
       <c r="E6" s="100" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="F6" s="100"/>
       <c r="H6" s="247">
@@ -18912,7 +21489,7 @@
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
       <c r="B7" s="100" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="C7" s="338">
         <f>Normalized_FCF!G8</f>
@@ -18922,11 +21499,11 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="371" t="str">
+      <c r="E7" s="377" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!C11&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 5-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 10-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 濮阳惠成(300481.SZ). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="371"/>
+      <c r="F7" s="377"/>
       <c r="H7" s="247">
         <v>4</v>
       </c>
@@ -18937,7 +21514,7 @@
     </row>
     <row r="8" spans="2:9">
       <c r="B8" s="100" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C8" s="338">
         <f>Normalized_FCF!G19</f>
@@ -18947,8 +21524,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="371"/>
-      <c r="F8" s="371"/>
+      <c r="E8" s="377"/>
+      <c r="F8" s="377"/>
       <c r="H8" s="247">
         <v>5</v>
       </c>
@@ -18959,7 +21536,7 @@
     </row>
     <row r="9" spans="2:9">
       <c r="B9" s="100" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C9" s="338">
         <f>Normalized_FCF!C19</f>
@@ -18969,8 +21546,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="371"/>
-      <c r="F9" s="371"/>
+      <c r="E9" s="377"/>
+      <c r="F9" s="377"/>
       <c r="H9" s="247">
         <v>6</v>
       </c>
@@ -18980,8 +21557,8 @@
       </c>
     </row>
     <row r="10" spans="2:9">
-      <c r="E10" s="371"/>
-      <c r="F10" s="371"/>
+      <c r="E10" s="377"/>
+      <c r="F10" s="377"/>
       <c r="H10" s="247">
         <v>7</v>
       </c>
@@ -18992,10 +21569,10 @@
     </row>
     <row r="11" spans="2:9" ht="13.15">
       <c r="B11" s="159" t="s">
-        <v>444</v>
-      </c>
-      <c r="E11" s="371"/>
-      <c r="F11" s="371"/>
+        <v>424</v>
+      </c>
+      <c r="E11" s="377"/>
+      <c r="F11" s="377"/>
       <c r="H11" s="247">
         <v>8</v>
       </c>
@@ -19006,15 +21583,15 @@
     </row>
     <row r="12" spans="2:9">
       <c r="B12" s="118" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C12" s="158">
         <f ca="1">(Normalized_FCF!G4/OFFSET(Normalized_FCF!G4, 0, $C$4))^(1/$C$4) - 1</f>
         <v>4.2279727191083527E-3</v>
       </c>
       <c r="D12" s="158"/>
-      <c r="E12" s="371"/>
-      <c r="F12" s="371"/>
+      <c r="E12" s="377"/>
+      <c r="F12" s="377"/>
       <c r="H12" s="247">
         <v>9</v>
       </c>
@@ -19025,14 +21602,14 @@
     </row>
     <row r="13" spans="2:9">
       <c r="B13" s="148" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C13" s="158">
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-0.15075343519689044</v>
       </c>
-      <c r="E13" s="371"/>
-      <c r="F13" s="371"/>
+      <c r="E13" s="377"/>
+      <c r="F13" s="377"/>
       <c r="H13" s="247">
         <v>10</v>
       </c>
@@ -19043,18 +21620,18 @@
     </row>
     <row r="14" spans="2:9">
       <c r="B14" s="100" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C14" s="158">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-0.15795268346639479</v>
       </c>
-      <c r="E14" s="371"/>
-      <c r="F14" s="371"/>
+      <c r="E14" s="377"/>
+      <c r="F14" s="377"/>
     </row>
     <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C16" s="37"/>
       <c r="D16" s="37"/>
@@ -19063,38 +21640,38 @@
     </row>
     <row r="17" spans="2:6" ht="13.15">
       <c r="B17" s="109" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="E17" s="159" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
     </row>
     <row r="18" spans="2:6">
       <c r="B18" s="152" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C18" s="150">
         <v>5</v>
       </c>
-      <c r="E18" s="371" t="s">
-        <v>327</v>
-      </c>
-      <c r="F18" s="372"/>
+      <c r="E18" s="377" t="s">
+        <v>321</v>
+      </c>
+      <c r="F18" s="378"/>
     </row>
     <row r="19" spans="2:6">
-      <c r="E19" s="372"/>
-      <c r="F19" s="372"/>
+      <c r="E19" s="378"/>
+      <c r="F19" s="378"/>
     </row>
     <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="159" t="s">
-        <v>302</v>
-      </c>
-      <c r="E20" s="372"/>
-      <c r="F20" s="372"/>
+        <v>298</v>
+      </c>
+      <c r="E20" s="378"/>
+      <c r="F20" s="378"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
@@ -19104,12 +21681,12 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E21" s="372"/>
-      <c r="F21" s="372"/>
+      <c r="E21" s="378"/>
+      <c r="F21" s="378"/>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="C22" s="160">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
@@ -19119,44 +21696,44 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E22" s="372"/>
-      <c r="F22" s="372"/>
+      <c r="E22" s="378"/>
+      <c r="F22" s="378"/>
     </row>
     <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="159" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E24" s="159" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F24" s="159"/>
     </row>
     <row r="25" spans="2:6">
       <c r="B25" s="152" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C25" s="166">
         <f>C18</f>
         <v>5</v>
       </c>
       <c r="D25" s="163"/>
-      <c r="E25" s="370"/>
-      <c r="F25" s="370"/>
+      <c r="E25" s="376"/>
+      <c r="F25" s="376"/>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" s="118" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C26" s="164">
         <v>0.04</v>
       </c>
       <c r="D26" s="164"/>
-      <c r="E26" s="370"/>
-      <c r="F26" s="370"/>
+      <c r="E26" s="376"/>
+      <c r="F26" s="376"/>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C27" s="160">
         <f>IF(valuation_method="DCF",DCF!E76,DDM!E71)</f>
@@ -19166,55 +21743,55 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E27" s="370"/>
-      <c r="F27" s="370"/>
+      <c r="E27" s="376"/>
+      <c r="F27" s="376"/>
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C28" s="165">
         <v>0.6</v>
       </c>
       <c r="D28" s="165"/>
-      <c r="E28" s="370"/>
-      <c r="F28" s="370"/>
+      <c r="E28" s="376"/>
+      <c r="F28" s="376"/>
     </row>
     <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="159" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="E30" s="159" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F30" s="159"/>
     </row>
     <row r="31" spans="2:6">
       <c r="B31" s="152" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C31" s="166">
         <f>C18</f>
         <v>5</v>
       </c>
       <c r="D31" s="163"/>
-      <c r="E31" s="370"/>
-      <c r="F31" s="370"/>
+      <c r="E31" s="376"/>
+      <c r="F31" s="376"/>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="118" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C32" s="164">
         <v>0.02</v>
       </c>
       <c r="D32" s="164"/>
-      <c r="E32" s="370"/>
-      <c r="F32" s="370"/>
+      <c r="E32" s="376"/>
+      <c r="F32" s="376"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C33" s="160">
         <f>IF(valuation_method="DCF",DCF!E77,DDM!E72)</f>
@@ -19224,55 +21801,55 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E33" s="370"/>
-      <c r="F33" s="370"/>
+      <c r="E33" s="376"/>
+      <c r="F33" s="376"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C34" s="165">
         <v>0.2</v>
       </c>
       <c r="D34" s="165"/>
-      <c r="E34" s="370"/>
-      <c r="F34" s="370"/>
+      <c r="E34" s="376"/>
+      <c r="F34" s="376"/>
     </row>
     <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="159" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="E36" s="159" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F36" s="159"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="152" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C37" s="166">
         <f>C18</f>
         <v>5</v>
       </c>
       <c r="D37" s="163"/>
-      <c r="E37" s="370"/>
-      <c r="F37" s="370"/>
+      <c r="E37" s="376"/>
+      <c r="F37" s="376"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="118" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C38" s="164">
         <v>0.06</v>
       </c>
       <c r="D38" s="164"/>
-      <c r="E38" s="370"/>
-      <c r="F38" s="370"/>
+      <c r="E38" s="376"/>
+      <c r="F38" s="376"/>
     </row>
     <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C39" s="160">
         <f>IF(valuation_method="DCF",DCF!E75,DDM!E70)</f>
@@ -19282,24 +21859,24 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E39" s="370"/>
-      <c r="F39" s="370"/>
+      <c r="E39" s="376"/>
+      <c r="F39" s="376"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C40" s="167">
         <f>1-C28-C34</f>
         <v>0.2</v>
       </c>
       <c r="D40" s="165"/>
-      <c r="E40" s="370"/>
-      <c r="F40" s="370"/>
+      <c r="E40" s="376"/>
+      <c r="F40" s="376"/>
     </row>
     <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C42" s="154">
         <f>C27*C28+C33*C34+C39*C40</f>
@@ -19312,7 +21889,7 @@
     </row>
     <row r="44" spans="2:6" ht="13.9">
       <c r="B44" s="36" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C44" s="37"/>
       <c r="D44" s="37"/>
@@ -19321,12 +21898,12 @@
     </row>
     <row r="45" spans="2:6" ht="13.15">
       <c r="B45" s="109" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="46" spans="2:6">
       <c r="B46" s="152" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C46" s="150">
         <v>10</v>
@@ -19341,39 +21918,39 @@
     </row>
     <row r="48" spans="2:6" ht="13.15">
       <c r="B48" s="159" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="E48" s="159" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F48" s="159"/>
     </row>
     <row r="49" spans="2:6" ht="12.75" customHeight="1">
       <c r="B49" s="152" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C49" s="166">
         <f>C46</f>
         <v>10</v>
       </c>
       <c r="D49" s="163"/>
-      <c r="E49" s="370"/>
-      <c r="F49" s="370"/>
+      <c r="E49" s="376"/>
+      <c r="F49" s="376"/>
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="118" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C50" s="164">
         <v>0</v>
       </c>
       <c r="D50" s="164"/>
-      <c r="E50" s="370"/>
-      <c r="F50" s="370"/>
+      <c r="E50" s="376"/>
+      <c r="F50" s="376"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C51" s="160">
         <f>IF(valuation_method="DCF",DCF!E78,DDM!E73)</f>
@@ -19383,55 +21960,55 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E51" s="370"/>
-      <c r="F51" s="370"/>
+      <c r="E51" s="376"/>
+      <c r="F51" s="376"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C52" s="165">
         <v>0.05</v>
       </c>
       <c r="D52" s="165"/>
-      <c r="E52" s="370"/>
-      <c r="F52" s="370"/>
+      <c r="E52" s="376"/>
+      <c r="F52" s="376"/>
     </row>
     <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="159" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="E54" s="159" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F54" s="159"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="152" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C55" s="166">
         <f>C46</f>
         <v>10</v>
       </c>
       <c r="D55" s="163"/>
-      <c r="E55" s="370"/>
-      <c r="F55" s="370"/>
+      <c r="E55" s="376"/>
+      <c r="F55" s="376"/>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="118" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C56" s="164">
         <v>0.08</v>
       </c>
       <c r="D56" s="164"/>
-      <c r="E56" s="370"/>
-      <c r="F56" s="370"/>
+      <c r="E56" s="376"/>
+      <c r="F56" s="376"/>
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C57" s="160">
         <f>IF(valuation_method="DCF",DCF!E74,DDM!E69)</f>
@@ -19441,23 +22018,23 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E57" s="370"/>
-      <c r="F57" s="370"/>
+      <c r="E57" s="376"/>
+      <c r="F57" s="376"/>
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C58" s="165">
         <v>0.05</v>
       </c>
       <c r="D58" s="165"/>
-      <c r="E58" s="370"/>
-      <c r="F58" s="370"/>
+      <c r="E58" s="376"/>
+      <c r="F58" s="376"/>
     </row>
     <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C60" s="154">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
@@ -19468,7 +22045,7 @@
         <v>CNY</v>
       </c>
       <c r="E60" s="100" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="F60" s="277">
         <f>Thesis!F28</f>
@@ -19477,7 +22054,7 @@
     </row>
     <row r="62" spans="2:6" ht="13.9">
       <c r="B62" s="36" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="C62" s="37"/>
       <c r="D62" s="37"/>
@@ -19486,15 +22063,15 @@
     </row>
     <row r="63" spans="2:6" ht="13.15">
       <c r="B63" s="109" t="s">
+        <v>299</v>
+      </c>
+      <c r="E63" s="252" t="s">
         <v>303</v>
-      </c>
-      <c r="E63" s="252" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="64" spans="2:6">
       <c r="B64" s="152" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C64" s="166">
         <f>C18</f>
@@ -19502,24 +22079,24 @@
       </c>
       <c r="D64" s="150"/>
       <c r="E64" s="251" t="s">
-        <v>392</v>
+        <v>376</v>
       </c>
     </row>
     <row r="65" spans="2:6">
       <c r="B65" s="118" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C65" s="151">
         <v>4.25103165866728E-2</v>
       </c>
       <c r="D65" s="151"/>
       <c r="E65" s="251" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
     </row>
     <row r="66" spans="2:6">
       <c r="B66" s="100" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C66" s="160">
         <f>IF(valuation_method="DCF",DCF!C18,DDM!C13)</f>
@@ -19530,20 +22107,20 @@
         <v>CNY</v>
       </c>
       <c r="E66" s="251" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
     </row>
     <row r="68" spans="2:6" ht="13.15">
       <c r="B68" s="109" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="E68" s="252" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
     </row>
     <row r="69" spans="2:6">
       <c r="B69" s="100" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="C69" s="244" t="str">
         <f>IF(C60&lt;C22,"Y","N")</f>
@@ -19553,19 +22130,19 @@
     </row>
     <row r="70" spans="2:6">
       <c r="B70" s="100" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="C70" s="244" t="str">
         <f>IF(C69="Y","N",IF(C65&gt;8%,"N","Y"))</f>
         <v>Y</v>
       </c>
       <c r="E70" s="251" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
     </row>
     <row r="71" spans="2:6">
       <c r="B71" s="100" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="C71" s="244" t="str">
         <f>IF(C65&gt;8%,"Y","N")</f>
@@ -19575,14 +22152,14 @@
     </row>
     <row r="72" spans="2:6">
       <c r="B72" s="100" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="C72" s="243" t="str">
         <f>IF(F72&gt;50%,"Y","N")</f>
         <v>N</v>
       </c>
       <c r="E72" s="134" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="F72" s="291">
         <f>BS!D89/C60</f>
@@ -19591,7 +22168,7 @@
     </row>
     <row r="74" spans="2:6" ht="13.9">
       <c r="B74" s="36" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C74" s="37"/>
       <c r="D74" s="37"/>
@@ -19600,12 +22177,12 @@
     </row>
     <row r="75" spans="2:6" ht="13.15">
       <c r="B75" s="109" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="76" spans="2:6">
       <c r="B76" s="246" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="C76" s="245">
         <f>F60</f>
@@ -19615,7 +22192,7 @@
     </row>
     <row r="77" spans="2:6">
       <c r="B77" s="100" t="s">
-        <v>455</v>
+        <v>435</v>
       </c>
       <c r="C77" s="173">
         <f>Normalized_FCF!C90*(1-dividend_tax_rate)</f>
@@ -19628,12 +22205,12 @@
     </row>
     <row r="79" spans="2:6" ht="13.15">
       <c r="B79" s="109" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
     </row>
     <row r="80" spans="2:6">
       <c r="B80" s="148" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="C80" s="167">
         <f>Thesis!F29</f>
@@ -19642,7 +22219,7 @@
     </row>
     <row r="81" spans="2:8">
       <c r="B81" s="100" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C81" s="116">
         <f>PV(C80, C76, -C77, 0)</f>
@@ -19654,7 +22231,7 @@
     </row>
     <row r="82" spans="2:8">
       <c r="B82" s="100" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C82" s="116">
         <f>C60/(1+C80)^C76</f>
@@ -19664,7 +22241,7 @@
     </row>
     <row r="83" spans="2:8" ht="13.15">
       <c r="B83" s="110" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C83" s="111">
         <f>C81+C82</f>
@@ -19675,7 +22252,7 @@
         <v>CNY</v>
       </c>
       <c r="E83" s="146" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F83" s="291">
         <f>(1-C83/C60)</f>
@@ -19687,12 +22264,12 @@
     </row>
     <row r="85" spans="2:8" ht="13.15">
       <c r="B85" s="109" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
     </row>
     <row r="86" spans="2:8">
       <c r="B86" s="148" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
@@ -19705,7 +22282,7 @@
     </row>
     <row r="87" spans="2:8" ht="13.15">
       <c r="B87" s="100" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
@@ -19717,12 +22294,12 @@
     </row>
     <row r="89" spans="2:8" ht="13.15">
       <c r="B89" s="109" t="s">
-        <v>409</v>
+        <v>392</v>
       </c>
     </row>
     <row r="90" spans="2:8">
       <c r="B90" s="148" t="s">
-        <v>410</v>
+        <v>393</v>
       </c>
       <c r="C90" s="167">
         <f>Thesis!F30</f>
@@ -19731,7 +22308,7 @@
     </row>
     <row r="91" spans="2:8">
       <c r="B91" s="100" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C91" s="116">
         <f>PV(C90, C76, -C77, 0)</f>
@@ -19743,7 +22320,7 @@
     </row>
     <row r="92" spans="2:8">
       <c r="B92" s="100" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C92" s="116">
         <f>C60/(1+C90)^C76</f>
@@ -19753,7 +22330,7 @@
     </row>
     <row r="93" spans="2:8" ht="13.15">
       <c r="B93" s="110" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C93" s="111">
         <f>C91+C92</f>
@@ -19764,7 +22341,7 @@
         <v>CNY</v>
       </c>
       <c r="E93" s="146" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F93" s="291">
         <f>(1-C93/C60)</f>
@@ -19773,14 +22350,14 @@
     </row>
     <row r="95" spans="2:8" ht="13.15">
       <c r="B95" s="109" t="s">
-        <v>394</v>
+        <v>378</v>
       </c>
       <c r="G95" s="2"/>
       <c r="H95" s="281"/>
     </row>
     <row r="96" spans="2:8">
       <c r="B96" s="148" t="s">
-        <v>400</v>
+        <v>383</v>
       </c>
       <c r="C96" s="134">
         <f>Thesis!F31</f>
@@ -19791,7 +22368,7 @@
     </row>
     <row r="97" spans="2:8">
       <c r="B97" s="100" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C97" s="116">
         <f>PV(C96, C76, -C77, 0)</f>
@@ -19803,7 +22380,7 @@
     </row>
     <row r="98" spans="2:8">
       <c r="B98" s="100" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C98" s="116">
         <f>C60/(1+C96)^C76</f>
@@ -19815,17 +22392,17 @@
     </row>
     <row r="99" spans="2:8" ht="13.15">
       <c r="B99" s="110" t="s">
-        <v>395</v>
+        <v>379</v>
       </c>
       <c r="C99" s="111">
         <f>C97+C98</f>
         <v>7.9387622109270746</v>
       </c>
       <c r="D99" t="s">
-        <v>393</v>
+        <v>377</v>
       </c>
       <c r="E99" s="146" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F99" s="291">
         <f>(1-C99/C60)</f>
@@ -19837,12 +22414,12 @@
     </row>
     <row r="101" spans="2:8" ht="13.15">
       <c r="B101" s="109" t="s">
-        <v>419</v>
+        <v>399</v>
       </c>
     </row>
     <row r="102" spans="2:8">
       <c r="B102" s="148" t="s">
-        <v>418</v>
+        <v>398</v>
       </c>
       <c r="C102" s="134">
         <f>Thesis!F32</f>
@@ -19851,7 +22428,7 @@
     </row>
     <row r="103" spans="2:8">
       <c r="B103" s="100" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C103" s="116">
         <f>PV(C102, C76, -C77, 0)</f>
@@ -19861,7 +22438,7 @@
     </row>
     <row r="104" spans="2:8">
       <c r="B104" s="100" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C104" s="116">
         <f>C60/(1+C102)^C76</f>
@@ -19871,17 +22448,17 @@
     </row>
     <row r="105" spans="2:8" ht="13.15">
       <c r="B105" s="110" t="s">
-        <v>395</v>
+        <v>379</v>
       </c>
       <c r="C105" s="111">
         <f>C103+C104</f>
         <v>7.6893682545464594</v>
       </c>
       <c r="D105" t="s">
-        <v>393</v>
+        <v>377</v>
       </c>
       <c r="E105" s="146" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F105" s="291">
         <f>(1-C105/C66)</f>
@@ -19893,32 +22470,32 @@
     </row>
     <row r="107" spans="2:8" ht="14.65">
       <c r="E107" s="285" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="F107" s="282"/>
     </row>
     <row r="108" spans="2:8" ht="13.9">
       <c r="E108" s="278" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="F108" s="283" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
     </row>
     <row r="109" spans="2:8" ht="13.9">
       <c r="E109" s="279" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="F109" s="283" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
     </row>
     <row r="110" spans="2:8" ht="13.9">
       <c r="E110" s="280" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="F110" s="284" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
   </sheetData>
@@ -19937,24 +22514,24 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7417C68D-4283-4D3F-A813-3C9F171BE969}">
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{011B0E59-A794-4E8A-B6F7-7F4312BBCFF3}">
   <dimension ref="B2:E2"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="2.59765625" style="360" customWidth="1"/>
-    <col min="2" max="2" width="22.73046875" style="360" customWidth="1"/>
-    <col min="3" max="5" width="20.73046875" style="360" customWidth="1"/>
-    <col min="6" max="16384" width="9.06640625" style="360"/>
+    <col min="1" max="1" width="2.59765625" style="381" customWidth="1"/>
+    <col min="2" max="2" width="22.73046875" style="381" customWidth="1"/>
+    <col min="3" max="5" width="20.73046875" style="381" customWidth="1"/>
+    <col min="6" max="16384" width="9.06640625" style="381"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:5" ht="13.9">
-      <c r="B2" s="358" t="s">
-        <v>456</v>
-      </c>
-      <c r="C2" s="359"/>
-      <c r="D2" s="359"/>
-      <c r="E2" s="359"/>
+      <c r="B2" s="379" t="s">
+        <v>436</v>
+      </c>
+      <c r="C2" s="380"/>
+      <c r="D2" s="380"/>
+      <c r="E2" s="380"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/financial_models/opportunities/300481.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/300481.SZ_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3417BC96-91DA-4A6F-8125-E4752006199F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28AB9F6A-E2E3-4455-B1EC-21B0F8107570}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4751,8 +4751,22 @@
     <xf numFmtId="4" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="1" xfId="2"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4763,16 +4777,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
@@ -4787,11 +4792,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="0" borderId="1" xfId="2"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="C12" s="366">
         <f>Market_Price</f>
-        <v>14.57</v>
+        <v>14.41</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C14" s="35">
         <f>投资主题!C12*Common_Shares/1000000</f>
-        <v>4252.33373166</v>
+        <v>4205.6368615800002</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",投资主题!D12*Common_Shares/1000000)</f>
@@ -5443,7 +5443,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>-0.1284274085979954</v>
+        <v>-0.12511446453186559</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -5574,13 +5574,13 @@
       <c r="F36" s="371"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="374" t="s">
+      <c r="B37" s="372" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="374"/>
-      <c r="D37" s="374"/>
-      <c r="E37" s="374"/>
-      <c r="F37" s="374"/>
+      <c r="C37" s="372"/>
+      <c r="D37" s="372"/>
+      <c r="E37" s="372"/>
+      <c r="F37" s="372"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -5592,13 +5592,13 @@
       </c>
     </row>
     <row r="40" spans="1:6">
-      <c r="B40" s="367" t="s">
+      <c r="B40" s="370" t="s">
         <v>494</v>
       </c>
-      <c r="C40" s="367"/>
-      <c r="D40" s="367"/>
-      <c r="E40" s="367"/>
-      <c r="F40" s="367"/>
+      <c r="C40" s="370"/>
+      <c r="D40" s="370"/>
+      <c r="E40" s="370"/>
+      <c r="F40" s="370"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -5618,13 +5618,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="367" t="s">
+      <c r="B43" s="370" t="s">
         <v>495</v>
       </c>
-      <c r="C43" s="367"/>
-      <c r="D43" s="367"/>
-      <c r="E43" s="367"/>
-      <c r="F43" s="367"/>
+      <c r="C43" s="370"/>
+      <c r="D43" s="370"/>
+      <c r="E43" s="370"/>
+      <c r="F43" s="370"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -5653,13 +5653,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="367" t="s">
+      <c r="B47" s="370" t="s">
         <v>496</v>
       </c>
-      <c r="C47" s="367"/>
-      <c r="D47" s="367"/>
-      <c r="E47" s="367"/>
-      <c r="F47" s="367"/>
+      <c r="C47" s="370"/>
+      <c r="D47" s="370"/>
+      <c r="E47" s="370"/>
+      <c r="F47" s="370"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -5675,13 +5675,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="367" t="s">
+      <c r="B50" s="370" t="s">
         <v>497</v>
       </c>
-      <c r="C50" s="367"/>
-      <c r="D50" s="367"/>
-      <c r="E50" s="367"/>
-      <c r="F50" s="367"/>
+      <c r="C50" s="370"/>
+      <c r="D50" s="370"/>
+      <c r="E50" s="370"/>
+      <c r="F50" s="370"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -5745,13 +5745,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="367" t="s">
+      <c r="B58" s="370" t="s">
         <v>237</v>
       </c>
-      <c r="C58" s="367"/>
-      <c r="D58" s="367"/>
-      <c r="E58" s="367"/>
-      <c r="F58" s="367"/>
+      <c r="C58" s="370"/>
+      <c r="D58" s="370"/>
+      <c r="E58" s="370"/>
+      <c r="F58" s="370"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -5767,7 +5767,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="367" t="s">
+      <c r="B61" s="370" t="s">
         <v>499</v>
       </c>
       <c r="C61" s="373"/>
@@ -5838,7 +5838,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>3.0448879199141517E-2</v>
+        <v>3.0786965297119495E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -5848,7 +5848,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>2.4708304735758409E-2</v>
+        <v>2.4982650936849413E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>503</v>
@@ -5948,13 +5948,13 @@
       <c r="F80" s="371"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="374" t="s">
+      <c r="B81" s="372" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="374"/>
-      <c r="D81" s="374"/>
-      <c r="E81" s="374"/>
-      <c r="F81" s="374"/>
+      <c r="C81" s="372"/>
+      <c r="D81" s="372"/>
+      <c r="E81" s="372"/>
+      <c r="F81" s="372"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -6242,13 +6242,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="B123" s="367" t="s">
+      <c r="B123" s="370" t="s">
         <v>519</v>
       </c>
-      <c r="C123" s="367"/>
-      <c r="D123" s="367"/>
-      <c r="E123" s="367"/>
-      <c r="F123" s="367"/>
+      <c r="C123" s="370"/>
+      <c r="D123" s="370"/>
+      <c r="E123" s="370"/>
+      <c r="F123" s="370"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -6391,13 +6391,13 @@
       </c>
     </row>
     <row r="134" spans="1:6">
-      <c r="B134" s="369" t="s">
+      <c r="B134" s="375" t="s">
         <v>524</v>
       </c>
-      <c r="C134" s="369"/>
-      <c r="D134" s="369"/>
-      <c r="E134" s="369"/>
-      <c r="F134" s="369"/>
+      <c r="C134" s="375"/>
+      <c r="D134" s="375"/>
+      <c r="E134" s="375"/>
+      <c r="F134" s="375"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -6410,13 +6410,13 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="370" t="s">
+      <c r="B138" s="376" t="s">
         <v>526</v>
       </c>
-      <c r="C138" s="370"/>
-      <c r="D138" s="370"/>
-      <c r="E138" s="370"/>
-      <c r="F138" s="370"/>
+      <c r="C138" s="376"/>
+      <c r="D138" s="376"/>
+      <c r="E138" s="376"/>
+      <c r="F138" s="376"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
       <c r="B139" s="371" t="s">
@@ -6758,7 +6758,7 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="372" t="s">
+      <c r="B179" s="377" t="s">
         <v>534</v>
       </c>
       <c r="C179" s="371"/>
@@ -6801,13 +6801,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B188" s="367" t="s">
+      <c r="B188" s="370" t="s">
         <v>541</v>
       </c>
-      <c r="C188" s="367"/>
-      <c r="D188" s="367"/>
-      <c r="E188" s="367"/>
-      <c r="F188" s="367"/>
+      <c r="C188" s="370"/>
+      <c r="D188" s="370"/>
+      <c r="E188" s="370"/>
+      <c r="F188" s="370"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -6815,22 +6815,22 @@
       </c>
     </row>
     <row r="191" spans="1:6">
-      <c r="B191" s="368" t="s">
+      <c r="B191" s="374" t="s">
         <v>543</v>
       </c>
-      <c r="C191" s="368"/>
-      <c r="D191" s="368"/>
-      <c r="E191" s="368"/>
-      <c r="F191" s="368"/>
+      <c r="C191" s="374"/>
+      <c r="D191" s="374"/>
+      <c r="E191" s="374"/>
+      <c r="F191" s="374"/>
     </row>
     <row r="192" spans="1:6">
-      <c r="B192" s="368" t="s">
+      <c r="B192" s="374" t="s">
         <v>544</v>
       </c>
-      <c r="C192" s="368"/>
-      <c r="D192" s="368"/>
-      <c r="E192" s="368"/>
-      <c r="F192" s="368"/>
+      <c r="C192" s="374"/>
+      <c r="D192" s="374"/>
+      <c r="E192" s="374"/>
+      <c r="F192" s="374"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -6854,12 +6854,15 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B47:F47"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B138:F138"/>
+    <mergeCell ref="B139:F139"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B182:F182"/>
     <mergeCell ref="B116:F116"/>
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B58:F58"/>
@@ -6872,15 +6875,12 @@
     <mergeCell ref="B90:F90"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B138:F138"/>
-    <mergeCell ref="B139:F139"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B43:F43"/>
   </mergeCells>
   <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">
@@ -7023,7 +7023,7 @@
         <v>463</v>
       </c>
       <c r="C12" s="50">
-        <v>14.57</v>
+        <v>14.41</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -7044,7 +7044,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>4252.33373166</v>
+        <v>4205.6368615800002</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -7170,7 +7170,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>-0.1284274085979954</v>
+        <v>-0.12511446453186559</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -7296,13 +7296,13 @@
       <c r="F36" s="371"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="374" t="s">
+      <c r="B37" s="372" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="374"/>
-      <c r="D37" s="374"/>
-      <c r="E37" s="374"/>
-      <c r="F37" s="374"/>
+      <c r="C37" s="372"/>
+      <c r="D37" s="372"/>
+      <c r="E37" s="372"/>
+      <c r="F37" s="372"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -7314,13 +7314,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="367" t="s">
+      <c r="B40" s="370" t="s">
         <v>227</v>
       </c>
-      <c r="C40" s="367"/>
-      <c r="D40" s="367"/>
-      <c r="E40" s="367"/>
-      <c r="F40" s="367"/>
+      <c r="C40" s="370"/>
+      <c r="D40" s="370"/>
+      <c r="E40" s="370"/>
+      <c r="F40" s="370"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -7340,13 +7340,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="367" t="s">
+      <c r="B43" s="370" t="s">
         <v>229</v>
       </c>
-      <c r="C43" s="367"/>
-      <c r="D43" s="367"/>
-      <c r="E43" s="367"/>
-      <c r="F43" s="367"/>
+      <c r="C43" s="370"/>
+      <c r="D43" s="370"/>
+      <c r="E43" s="370"/>
+      <c r="F43" s="370"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -7375,13 +7375,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="367" t="s">
+      <c r="B47" s="370" t="s">
         <v>232</v>
       </c>
-      <c r="C47" s="367"/>
-      <c r="D47" s="367"/>
-      <c r="E47" s="367"/>
-      <c r="F47" s="367"/>
+      <c r="C47" s="370"/>
+      <c r="D47" s="370"/>
+      <c r="E47" s="370"/>
+      <c r="F47" s="370"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -7397,13 +7397,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="367" t="s">
+      <c r="B50" s="370" t="s">
         <v>236</v>
       </c>
-      <c r="C50" s="367"/>
-      <c r="D50" s="367"/>
-      <c r="E50" s="367"/>
-      <c r="F50" s="367"/>
+      <c r="C50" s="370"/>
+      <c r="D50" s="370"/>
+      <c r="E50" s="370"/>
+      <c r="F50" s="370"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -7467,13 +7467,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="367" t="s">
+      <c r="B58" s="370" t="s">
         <v>237</v>
       </c>
-      <c r="C58" s="367"/>
-      <c r="D58" s="367"/>
-      <c r="E58" s="367"/>
-      <c r="F58" s="367"/>
+      <c r="C58" s="370"/>
+      <c r="D58" s="370"/>
+      <c r="E58" s="370"/>
+      <c r="F58" s="370"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -7489,7 +7489,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="367" t="s">
+      <c r="B61" s="370" t="s">
         <v>329</v>
       </c>
       <c r="C61" s="373"/>
@@ -7560,7 +7560,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>3.0448879199141517E-2</v>
+        <v>3.0786965297119495E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -7570,7 +7570,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>2.4708304735758409E-2</v>
+        <v>2.4982650936849413E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>425</v>
@@ -7670,13 +7670,13 @@
       <c r="F80" s="371"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="374" t="s">
+      <c r="B81" s="372" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="374"/>
-      <c r="D81" s="374"/>
-      <c r="E81" s="374"/>
-      <c r="F81" s="374"/>
+      <c r="C81" s="372"/>
+      <c r="D81" s="372"/>
+      <c r="E81" s="372"/>
+      <c r="F81" s="372"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -7964,13 +7964,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="B123" s="367" t="s">
+      <c r="B123" s="370" t="s">
         <v>473</v>
       </c>
-      <c r="C123" s="367"/>
-      <c r="D123" s="367"/>
-      <c r="E123" s="367"/>
-      <c r="F123" s="367"/>
+      <c r="C123" s="370"/>
+      <c r="D123" s="370"/>
+      <c r="E123" s="370"/>
+      <c r="F123" s="370"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -8113,13 +8113,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="369" t="s">
+      <c r="B134" s="375" t="s">
         <v>474</v>
       </c>
-      <c r="C134" s="369"/>
-      <c r="D134" s="369"/>
-      <c r="E134" s="369"/>
-      <c r="F134" s="369"/>
+      <c r="C134" s="375"/>
+      <c r="D134" s="375"/>
+      <c r="E134" s="375"/>
+      <c r="F134" s="375"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -8132,13 +8132,13 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="370" t="s">
+      <c r="B138" s="376" t="s">
         <v>353</v>
       </c>
-      <c r="C138" s="370"/>
-      <c r="D138" s="370"/>
-      <c r="E138" s="370"/>
-      <c r="F138" s="370"/>
+      <c r="C138" s="376"/>
+      <c r="D138" s="376"/>
+      <c r="E138" s="376"/>
+      <c r="F138" s="376"/>
     </row>
     <row r="139" spans="1:6">
       <c r="B139" s="371" t="s">
@@ -8480,7 +8480,7 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="372" t="s">
+      <c r="B179" s="377" t="s">
         <v>477</v>
       </c>
       <c r="C179" s="371"/>
@@ -8523,13 +8523,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="34.35" customHeight="1">
-      <c r="B188" s="367" t="s">
+      <c r="B188" s="370" t="s">
         <v>478</v>
       </c>
-      <c r="C188" s="367"/>
-      <c r="D188" s="367"/>
-      <c r="E188" s="367"/>
-      <c r="F188" s="367"/>
+      <c r="C188" s="370"/>
+      <c r="D188" s="370"/>
+      <c r="E188" s="370"/>
+      <c r="F188" s="370"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -8537,22 +8537,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="368" t="s">
+      <c r="B191" s="374" t="s">
         <v>363</v>
       </c>
-      <c r="C191" s="368"/>
-      <c r="D191" s="368"/>
-      <c r="E191" s="368"/>
-      <c r="F191" s="368"/>
+      <c r="C191" s="374"/>
+      <c r="D191" s="374"/>
+      <c r="E191" s="374"/>
+      <c r="F191" s="374"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="368" t="s">
+      <c r="B192" s="374" t="s">
         <v>364</v>
       </c>
-      <c r="C192" s="368"/>
-      <c r="D192" s="368"/>
-      <c r="E192" s="368"/>
-      <c r="F192" s="368"/>
+      <c r="C192" s="374"/>
+      <c r="D192" s="374"/>
+      <c r="E192" s="374"/>
+      <c r="F192" s="374"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -8576,6 +8576,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -8592,17 +8603,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -16193,32 +16193,32 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>2.4708304735758409E-2</v>
+        <v>2.4982650936849413E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>2.4708304735758409E-2</v>
+        <v>2.4982650936849413E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>2.4708304735758409E-2</v>
+        <v>2.4982650936849413E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>2.4708304735758409E-2</v>
+        <v>2.4982650936849413E-2</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
-        <v>2.4708304735758409E-2</v>
+        <v>2.4982650936849413E-2</v>
       </c>
       <c r="K94" s="23">
         <f t="shared" si="39"/>
-        <v>1.2354152367879205E-2</v>
+        <v>1.2491325468424706E-2</v>
       </c>
       <c r="L94" s="23">
         <f t="shared" si="39"/>
-        <v>1.2354152367879205E-2</v>
+        <v>1.2491325468424706E-2</v>
       </c>
       <c r="M94" s="23">
         <f t="shared" si="39"/>
@@ -17392,50 +17392,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>3.0448879199141517E-2</v>
+        <v>3.0786965297119495E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>3.469637196286382E-2</v>
+        <v>3.5081619673763074E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>4.5626490490629279E-2</v>
+        <v>4.6133099684140783E-2</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>8.9740917984746219E-2</v>
+        <v>9.0737347330864151E-2</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>5.8113171366984157E-2</v>
+        <v>5.8758425178137348E-2</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>4.3456873938861849E-2</v>
+        <v>4.3939393011049072E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>3.61029623027838E-2</v>
+        <v>3.6503827949448994E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>2.545844142797199E-2</v>
+        <v>2.5741116697123655E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>2.3143109927447402E-2</v>
+        <v>2.3400077143852092E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>1.5311739884202953E-2</v>
+        <v>1.5481752263208677E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>1.4971565502020745E-2</v>
+        <v>1.5137800788649706E-2</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -17449,43 +17449,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.5041192927543723E-2</v>
+        <v>4.5541303327849551E-2</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.5282370536856071E-2</v>
+        <v>5.5896192832893335E-2</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.9287089547222207E-2</v>
+        <v>0.10038951385864175</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.9353190724631508E-2</v>
+        <v>6.0012212967236717E-2</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.2012521188044008E-2</v>
+        <v>4.2479003033296409E-2</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.4033188157954128E-2</v>
+        <v>3.4411072273517813E-2</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.486783650414931E-2</v>
+        <v>2.5143954050343888E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.7309583077165042E-2</v>
+        <v>1.7501778309111357E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.5188389029566426E-2</v>
+        <v>1.5357031794641417E-2</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.3519541886369666E-2</v>
+        <v>1.3669654773380018E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18273,10 +18273,10 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="375" t="s">
+      <c r="E6" s="378" t="s">
         <v>245</v>
       </c>
-      <c r="F6" s="375"/>
+      <c r="F6" s="378"/>
       <c r="H6" s="120"/>
     </row>
     <row r="7" spans="2:8">
@@ -18291,8 +18291,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="375"/>
-      <c r="F7" s="375"/>
+      <c r="E7" s="378"/>
+      <c r="F7" s="378"/>
       <c r="H7" s="120"/>
     </row>
     <row r="8" spans="2:8">
@@ -18307,8 +18307,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="375"/>
-      <c r="F8" s="375"/>
+      <c r="E8" s="378"/>
+      <c r="F8" s="378"/>
       <c r="H8" s="120"/>
     </row>
     <row r="9" spans="2:8">
@@ -18323,8 +18323,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="375"/>
-      <c r="F9" s="375"/>
+      <c r="E9" s="378"/>
+      <c r="F9" s="378"/>
       <c r="H9" s="120"/>
     </row>
     <row r="10" spans="2:8" ht="13.15">
@@ -20033,8 +20033,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="375"/>
-      <c r="F6" s="375"/>
+      <c r="E6" s="378"/>
+      <c r="F6" s="378"/>
       <c r="H6" s="120"/>
     </row>
     <row r="7" spans="2:8" ht="13.15">
@@ -21435,7 +21435,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-14.57</v>
+        <v>-14.41</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -21499,11 +21499,11 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="377" t="str">
+      <c r="E7" s="380" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!C11&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 5-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 10-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 濮阳惠成(300481.SZ). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="377"/>
+      <c r="F7" s="380"/>
       <c r="H7" s="247">
         <v>4</v>
       </c>
@@ -21524,8 +21524,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="377"/>
-      <c r="F8" s="377"/>
+      <c r="E8" s="380"/>
+      <c r="F8" s="380"/>
       <c r="H8" s="247">
         <v>5</v>
       </c>
@@ -21546,8 +21546,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="377"/>
-      <c r="F9" s="377"/>
+      <c r="E9" s="380"/>
+      <c r="F9" s="380"/>
       <c r="H9" s="247">
         <v>6</v>
       </c>
@@ -21557,8 +21557,8 @@
       </c>
     </row>
     <row r="10" spans="2:9">
-      <c r="E10" s="377"/>
-      <c r="F10" s="377"/>
+      <c r="E10" s="380"/>
+      <c r="F10" s="380"/>
       <c r="H10" s="247">
         <v>7</v>
       </c>
@@ -21571,8 +21571,8 @@
       <c r="B11" s="159" t="s">
         <v>424</v>
       </c>
-      <c r="E11" s="377"/>
-      <c r="F11" s="377"/>
+      <c r="E11" s="380"/>
+      <c r="F11" s="380"/>
       <c r="H11" s="247">
         <v>8</v>
       </c>
@@ -21590,8 +21590,8 @@
         <v>4.2279727191083527E-3</v>
       </c>
       <c r="D12" s="158"/>
-      <c r="E12" s="377"/>
-      <c r="F12" s="377"/>
+      <c r="E12" s="380"/>
+      <c r="F12" s="380"/>
       <c r="H12" s="247">
         <v>9</v>
       </c>
@@ -21608,8 +21608,8 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-0.15075343519689044</v>
       </c>
-      <c r="E13" s="377"/>
-      <c r="F13" s="377"/>
+      <c r="E13" s="380"/>
+      <c r="F13" s="380"/>
       <c r="H13" s="247">
         <v>10</v>
       </c>
@@ -21626,8 +21626,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-0.15795268346639479</v>
       </c>
-      <c r="E14" s="377"/>
-      <c r="F14" s="377"/>
+      <c r="E14" s="380"/>
+      <c r="F14" s="380"/>
     </row>
     <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
@@ -21653,21 +21653,21 @@
       <c r="C18" s="150">
         <v>5</v>
       </c>
-      <c r="E18" s="377" t="s">
+      <c r="E18" s="380" t="s">
         <v>321</v>
       </c>
-      <c r="F18" s="378"/>
+      <c r="F18" s="381"/>
     </row>
     <row r="19" spans="2:6">
-      <c r="E19" s="378"/>
-      <c r="F19" s="378"/>
+      <c r="E19" s="381"/>
+      <c r="F19" s="381"/>
     </row>
     <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="159" t="s">
         <v>298</v>
       </c>
-      <c r="E20" s="378"/>
-      <c r="F20" s="378"/>
+      <c r="E20" s="381"/>
+      <c r="F20" s="381"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
@@ -21675,14 +21675,14 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>14.57</v>
+        <v>14.41</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E21" s="378"/>
-      <c r="F21" s="378"/>
+      <c r="E21" s="381"/>
+      <c r="F21" s="381"/>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
@@ -21696,8 +21696,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E22" s="378"/>
-      <c r="F22" s="378"/>
+      <c r="E22" s="381"/>
+      <c r="F22" s="381"/>
     </row>
     <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="159" t="s">
@@ -21717,8 +21717,8 @@
         <v>5</v>
       </c>
       <c r="D25" s="163"/>
-      <c r="E25" s="376"/>
-      <c r="F25" s="376"/>
+      <c r="E25" s="379"/>
+      <c r="F25" s="379"/>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" s="118" t="s">
@@ -21728,8 +21728,8 @@
         <v>0.04</v>
       </c>
       <c r="D26" s="164"/>
-      <c r="E26" s="376"/>
-      <c r="F26" s="376"/>
+      <c r="E26" s="379"/>
+      <c r="F26" s="379"/>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
@@ -21743,8 +21743,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E27" s="376"/>
-      <c r="F27" s="376"/>
+      <c r="E27" s="379"/>
+      <c r="F27" s="379"/>
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
@@ -21754,8 +21754,8 @@
         <v>0.6</v>
       </c>
       <c r="D28" s="165"/>
-      <c r="E28" s="376"/>
-      <c r="F28" s="376"/>
+      <c r="E28" s="379"/>
+      <c r="F28" s="379"/>
     </row>
     <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="159" t="s">
@@ -21775,8 +21775,8 @@
         <v>5</v>
       </c>
       <c r="D31" s="163"/>
-      <c r="E31" s="376"/>
-      <c r="F31" s="376"/>
+      <c r="E31" s="379"/>
+      <c r="F31" s="379"/>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="118" t="s">
@@ -21786,8 +21786,8 @@
         <v>0.02</v>
       </c>
       <c r="D32" s="164"/>
-      <c r="E32" s="376"/>
-      <c r="F32" s="376"/>
+      <c r="E32" s="379"/>
+      <c r="F32" s="379"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
@@ -21801,8 +21801,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E33" s="376"/>
-      <c r="F33" s="376"/>
+      <c r="E33" s="379"/>
+      <c r="F33" s="379"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
@@ -21812,8 +21812,8 @@
         <v>0.2</v>
       </c>
       <c r="D34" s="165"/>
-      <c r="E34" s="376"/>
-      <c r="F34" s="376"/>
+      <c r="E34" s="379"/>
+      <c r="F34" s="379"/>
     </row>
     <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="159" t="s">
@@ -21833,8 +21833,8 @@
         <v>5</v>
       </c>
       <c r="D37" s="163"/>
-      <c r="E37" s="376"/>
-      <c r="F37" s="376"/>
+      <c r="E37" s="379"/>
+      <c r="F37" s="379"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="118" t="s">
@@ -21844,8 +21844,8 @@
         <v>0.06</v>
       </c>
       <c r="D38" s="164"/>
-      <c r="E38" s="376"/>
-      <c r="F38" s="376"/>
+      <c r="E38" s="379"/>
+      <c r="F38" s="379"/>
     </row>
     <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
@@ -21859,8 +21859,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E39" s="376"/>
-      <c r="F39" s="376"/>
+      <c r="E39" s="379"/>
+      <c r="F39" s="379"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
@@ -21871,8 +21871,8 @@
         <v>0.2</v>
       </c>
       <c r="D40" s="165"/>
-      <c r="E40" s="376"/>
-      <c r="F40" s="376"/>
+      <c r="E40" s="379"/>
+      <c r="F40" s="379"/>
     </row>
     <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
@@ -21934,8 +21934,8 @@
         <v>10</v>
       </c>
       <c r="D49" s="163"/>
-      <c r="E49" s="376"/>
-      <c r="F49" s="376"/>
+      <c r="E49" s="379"/>
+      <c r="F49" s="379"/>
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="118" t="s">
@@ -21945,8 +21945,8 @@
         <v>0</v>
       </c>
       <c r="D50" s="164"/>
-      <c r="E50" s="376"/>
-      <c r="F50" s="376"/>
+      <c r="E50" s="379"/>
+      <c r="F50" s="379"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
@@ -21960,8 +21960,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E51" s="376"/>
-      <c r="F51" s="376"/>
+      <c r="E51" s="379"/>
+      <c r="F51" s="379"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
@@ -21971,8 +21971,8 @@
         <v>0.05</v>
       </c>
       <c r="D52" s="165"/>
-      <c r="E52" s="376"/>
-      <c r="F52" s="376"/>
+      <c r="E52" s="379"/>
+      <c r="F52" s="379"/>
     </row>
     <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="159" t="s">
@@ -21992,8 +21992,8 @@
         <v>10</v>
       </c>
       <c r="D55" s="163"/>
-      <c r="E55" s="376"/>
-      <c r="F55" s="376"/>
+      <c r="E55" s="379"/>
+      <c r="F55" s="379"/>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="118" t="s">
@@ -22003,8 +22003,8 @@
         <v>0.08</v>
       </c>
       <c r="D56" s="164"/>
-      <c r="E56" s="376"/>
-      <c r="F56" s="376"/>
+      <c r="E56" s="379"/>
+      <c r="F56" s="379"/>
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
@@ -22018,8 +22018,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E57" s="376"/>
-      <c r="F57" s="376"/>
+      <c r="E57" s="379"/>
+      <c r="F57" s="379"/>
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
@@ -22029,8 +22029,8 @@
         <v>0.05</v>
       </c>
       <c r="D58" s="165"/>
-      <c r="E58" s="376"/>
-      <c r="F58" s="376"/>
+      <c r="E58" s="379"/>
+      <c r="F58" s="379"/>
     </row>
     <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
@@ -22273,7 +22273,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>14.57</v>
+        <v>14.41</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -22286,7 +22286,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>-0.1284274085979954</v>
+        <v>-0.12511446453186559</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -22519,19 +22519,19 @@
   <dimension ref="B2:E2"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="2.59765625" style="381" customWidth="1"/>
-    <col min="2" max="2" width="22.73046875" style="381" customWidth="1"/>
-    <col min="3" max="5" width="20.73046875" style="381" customWidth="1"/>
-    <col min="6" max="16384" width="9.06640625" style="381"/>
+    <col min="1" max="1" width="2.59765625" style="369" customWidth="1"/>
+    <col min="2" max="2" width="22.73046875" style="369" customWidth="1"/>
+    <col min="3" max="5" width="20.73046875" style="369" customWidth="1"/>
+    <col min="6" max="16384" width="9.06640625" style="369"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:5" ht="13.9">
-      <c r="B2" s="379" t="s">
+      <c r="B2" s="367" t="s">
         <v>436</v>
       </c>
-      <c r="C2" s="380"/>
-      <c r="D2" s="380"/>
-      <c r="E2" s="380"/>
+      <c r="C2" s="368"/>
+      <c r="D2" s="368"/>
+      <c r="E2" s="368"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/financial_models/opportunities/300481.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/300481.SZ_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28AB9F6A-E2E3-4455-B1EC-21B0F8107570}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B89D6117-2068-4CB0-9B68-25311A571A79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1470" yWindow="1470" windowWidth="12690" windowHeight="7643" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="投资主题" sheetId="12" r:id="rId1"/>
@@ -4759,15 +4759,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -4777,7 +4768,16 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="C12" s="366">
         <f>Market_Price</f>
-        <v>14.41</v>
+        <v>14.5</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C14" s="35">
         <f>投资主题!C12*Common_Shares/1000000</f>
-        <v>4205.6368615800002</v>
+        <v>4231.903851</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",投资主题!D12*Common_Shares/1000000)</f>
@@ -5346,13 +5346,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="371" t="s">
+      <c r="B18" s="374" t="s">
         <v>489</v>
       </c>
-      <c r="C18" s="371"/>
-      <c r="D18" s="371"/>
-      <c r="E18" s="371"/>
-      <c r="F18" s="371"/>
+      <c r="C18" s="374"/>
+      <c r="D18" s="374"/>
+      <c r="E18" s="374"/>
+      <c r="F18" s="374"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -5443,7 +5443,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>-0.12511446453186559</v>
+        <v>-0.12698411363037332</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -5565,22 +5565,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="371" t="s">
+      <c r="B36" s="374" t="s">
         <v>492</v>
       </c>
-      <c r="C36" s="371"/>
-      <c r="D36" s="371"/>
-      <c r="E36" s="371"/>
-      <c r="F36" s="371"/>
+      <c r="C36" s="374"/>
+      <c r="D36" s="374"/>
+      <c r="E36" s="374"/>
+      <c r="F36" s="374"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="372" t="s">
+      <c r="B37" s="377" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="372"/>
-      <c r="D37" s="372"/>
-      <c r="E37" s="372"/>
-      <c r="F37" s="372"/>
+      <c r="C37" s="377"/>
+      <c r="D37" s="377"/>
+      <c r="E37" s="377"/>
+      <c r="F37" s="377"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -5770,10 +5770,10 @@
       <c r="B61" s="370" t="s">
         <v>499</v>
       </c>
-      <c r="C61" s="373"/>
-      <c r="D61" s="373"/>
-      <c r="E61" s="373"/>
-      <c r="F61" s="373"/>
+      <c r="C61" s="376"/>
+      <c r="D61" s="376"/>
+      <c r="E61" s="376"/>
+      <c r="F61" s="376"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -5789,22 +5789,22 @@
       </c>
     </row>
     <row r="64" spans="2:6">
-      <c r="B64" s="371" t="s">
+      <c r="B64" s="374" t="s">
         <v>500</v>
       </c>
-      <c r="C64" s="371"/>
-      <c r="D64" s="371"/>
-      <c r="E64" s="371"/>
-      <c r="F64" s="371"/>
+      <c r="C64" s="374"/>
+      <c r="D64" s="374"/>
+      <c r="E64" s="374"/>
+      <c r="F64" s="374"/>
     </row>
     <row r="65" spans="1:6">
-      <c r="B65" s="371" t="s">
+      <c r="B65" s="374" t="s">
         <v>501</v>
       </c>
-      <c r="C65" s="371"/>
-      <c r="D65" s="371"/>
-      <c r="E65" s="371"/>
-      <c r="F65" s="371"/>
+      <c r="C65" s="374"/>
+      <c r="D65" s="374"/>
+      <c r="E65" s="374"/>
+      <c r="F65" s="374"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -5838,7 +5838,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>3.0786965297119495E-2</v>
+        <v>3.0595873788378754E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -5848,7 +5848,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>2.4982650936849413E-2</v>
+        <v>2.4827586206896554E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>503</v>
@@ -5939,22 +5939,22 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="371" t="s">
+      <c r="B80" s="374" t="s">
         <v>506</v>
       </c>
-      <c r="C80" s="371"/>
-      <c r="D80" s="371"/>
-      <c r="E80" s="371"/>
-      <c r="F80" s="371"/>
+      <c r="C80" s="374"/>
+      <c r="D80" s="374"/>
+      <c r="E80" s="374"/>
+      <c r="F80" s="374"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="372" t="s">
+      <c r="B81" s="377" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="372"/>
-      <c r="D81" s="372"/>
-      <c r="E81" s="372"/>
-      <c r="F81" s="372"/>
+      <c r="C81" s="377"/>
+      <c r="D81" s="377"/>
+      <c r="E81" s="377"/>
+      <c r="F81" s="377"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5998,22 +5998,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6">
-      <c r="B89" s="371" t="s">
+      <c r="B89" s="374" t="s">
         <v>507</v>
       </c>
-      <c r="C89" s="371"/>
-      <c r="D89" s="371"/>
-      <c r="E89" s="371"/>
-      <c r="F89" s="371"/>
+      <c r="C89" s="374"/>
+      <c r="D89" s="374"/>
+      <c r="E89" s="374"/>
+      <c r="F89" s="374"/>
     </row>
     <row r="90" spans="1:6">
-      <c r="B90" s="371" t="s">
+      <c r="B90" s="374" t="s">
         <v>508</v>
       </c>
-      <c r="C90" s="371"/>
-      <c r="D90" s="371"/>
-      <c r="E90" s="371"/>
-      <c r="F90" s="371"/>
+      <c r="C90" s="374"/>
+      <c r="D90" s="374"/>
+      <c r="E90" s="374"/>
+      <c r="F90" s="374"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -6050,13 +6050,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="371" t="s">
+      <c r="B97" s="374" t="s">
         <v>510</v>
       </c>
-      <c r="C97" s="371"/>
-      <c r="D97" s="371"/>
-      <c r="E97" s="371"/>
-      <c r="F97" s="371"/>
+      <c r="C97" s="374"/>
+      <c r="D97" s="374"/>
+      <c r="E97" s="374"/>
+      <c r="F97" s="374"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -6069,13 +6069,13 @@
       </c>
     </row>
     <row r="101" spans="2:6">
-      <c r="B101" s="371" t="s">
+      <c r="B101" s="374" t="s">
         <v>511</v>
       </c>
-      <c r="C101" s="371"/>
-      <c r="D101" s="371"/>
-      <c r="E101" s="371"/>
-      <c r="F101" s="371"/>
+      <c r="C101" s="374"/>
+      <c r="D101" s="374"/>
+      <c r="E101" s="374"/>
+      <c r="F101" s="374"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -6197,13 +6197,13 @@
       </c>
     </row>
     <row r="116" spans="1:6">
-      <c r="B116" s="371" t="s">
+      <c r="B116" s="374" t="s">
         <v>516</v>
       </c>
-      <c r="C116" s="371"/>
-      <c r="D116" s="371"/>
-      <c r="E116" s="371"/>
-      <c r="F116" s="371"/>
+      <c r="C116" s="374"/>
+      <c r="D116" s="374"/>
+      <c r="E116" s="374"/>
+      <c r="F116" s="374"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -6391,13 +6391,13 @@
       </c>
     </row>
     <row r="134" spans="1:6">
-      <c r="B134" s="375" t="s">
+      <c r="B134" s="372" t="s">
         <v>524</v>
       </c>
-      <c r="C134" s="375"/>
-      <c r="D134" s="375"/>
-      <c r="E134" s="375"/>
-      <c r="F134" s="375"/>
+      <c r="C134" s="372"/>
+      <c r="D134" s="372"/>
+      <c r="E134" s="372"/>
+      <c r="F134" s="372"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -6410,22 +6410,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="376" t="s">
+      <c r="B138" s="373" t="s">
         <v>526</v>
       </c>
-      <c r="C138" s="376"/>
-      <c r="D138" s="376"/>
-      <c r="E138" s="376"/>
-      <c r="F138" s="376"/>
+      <c r="C138" s="373"/>
+      <c r="D138" s="373"/>
+      <c r="E138" s="373"/>
+      <c r="F138" s="373"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="371" t="s">
+      <c r="B139" s="374" t="s">
         <v>527</v>
       </c>
-      <c r="C139" s="371"/>
-      <c r="D139" s="371"/>
-      <c r="E139" s="371"/>
-      <c r="F139" s="371"/>
+      <c r="C139" s="374"/>
+      <c r="D139" s="374"/>
+      <c r="E139" s="374"/>
+      <c r="F139" s="374"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -6758,13 +6758,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="377" t="s">
+      <c r="B179" s="375" t="s">
         <v>534</v>
       </c>
-      <c r="C179" s="371"/>
-      <c r="D179" s="371"/>
-      <c r="E179" s="371"/>
-      <c r="F179" s="371"/>
+      <c r="C179" s="374"/>
+      <c r="D179" s="374"/>
+      <c r="E179" s="374"/>
+      <c r="F179" s="374"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -6772,13 +6772,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="373" t="s">
+      <c r="B182" s="376" t="s">
         <v>536</v>
       </c>
-      <c r="C182" s="373"/>
-      <c r="D182" s="373"/>
-      <c r="E182" s="373"/>
-      <c r="F182" s="373"/>
+      <c r="C182" s="376"/>
+      <c r="D182" s="376"/>
+      <c r="E182" s="376"/>
+      <c r="F182" s="376"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -6815,22 +6815,22 @@
       </c>
     </row>
     <row r="191" spans="1:6">
-      <c r="B191" s="374" t="s">
+      <c r="B191" s="371" t="s">
         <v>543</v>
       </c>
-      <c r="C191" s="374"/>
-      <c r="D191" s="374"/>
-      <c r="E191" s="374"/>
-      <c r="F191" s="374"/>
+      <c r="C191" s="371"/>
+      <c r="D191" s="371"/>
+      <c r="E191" s="371"/>
+      <c r="F191" s="371"/>
     </row>
     <row r="192" spans="1:6">
-      <c r="B192" s="374" t="s">
+      <c r="B192" s="371" t="s">
         <v>544</v>
       </c>
-      <c r="C192" s="374"/>
-      <c r="D192" s="374"/>
-      <c r="E192" s="374"/>
-      <c r="F192" s="374"/>
+      <c r="C192" s="371"/>
+      <c r="D192" s="371"/>
+      <c r="E192" s="371"/>
+      <c r="F192" s="371"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -6854,15 +6854,12 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B138:F138"/>
-    <mergeCell ref="B139:F139"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B43:F43"/>
     <mergeCell ref="B116:F116"/>
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B58:F58"/>
@@ -6875,12 +6872,15 @@
     <mergeCell ref="B90:F90"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B47:F47"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B138:F138"/>
+    <mergeCell ref="B139:F139"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">
@@ -7023,7 +7023,7 @@
         <v>463</v>
       </c>
       <c r="C12" s="50">
-        <v>14.41</v>
+        <v>14.5</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -7044,7 +7044,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>4205.6368615800002</v>
+        <v>4231.903851</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -7081,13 +7081,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="371" t="s">
+      <c r="B18" s="374" t="s">
         <v>468</v>
       </c>
-      <c r="C18" s="371"/>
-      <c r="D18" s="371"/>
-      <c r="E18" s="371"/>
-      <c r="F18" s="371"/>
+      <c r="C18" s="374"/>
+      <c r="D18" s="374"/>
+      <c r="E18" s="374"/>
+      <c r="F18" s="374"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -7170,7 +7170,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>-0.12511446453186559</v>
+        <v>-0.12698411363037332</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -7287,22 +7287,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6">
-      <c r="B36" s="371" t="s">
+      <c r="B36" s="374" t="s">
         <v>469</v>
       </c>
-      <c r="C36" s="371"/>
-      <c r="D36" s="371"/>
-      <c r="E36" s="371"/>
-      <c r="F36" s="371"/>
+      <c r="C36" s="374"/>
+      <c r="D36" s="374"/>
+      <c r="E36" s="374"/>
+      <c r="F36" s="374"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="372" t="s">
+      <c r="B37" s="377" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="372"/>
-      <c r="D37" s="372"/>
-      <c r="E37" s="372"/>
-      <c r="F37" s="372"/>
+      <c r="C37" s="377"/>
+      <c r="D37" s="377"/>
+      <c r="E37" s="377"/>
+      <c r="F37" s="377"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -7492,10 +7492,10 @@
       <c r="B61" s="370" t="s">
         <v>329</v>
       </c>
-      <c r="C61" s="373"/>
-      <c r="D61" s="373"/>
-      <c r="E61" s="373"/>
-      <c r="F61" s="373"/>
+      <c r="C61" s="376"/>
+      <c r="D61" s="376"/>
+      <c r="E61" s="376"/>
+      <c r="F61" s="376"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -7511,22 +7511,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="371" t="s">
+      <c r="B64" s="374" t="s">
         <v>334</v>
       </c>
-      <c r="C64" s="371"/>
-      <c r="D64" s="371"/>
-      <c r="E64" s="371"/>
-      <c r="F64" s="371"/>
+      <c r="C64" s="374"/>
+      <c r="D64" s="374"/>
+      <c r="E64" s="374"/>
+      <c r="F64" s="374"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="371" t="s">
+      <c r="B65" s="374" t="s">
         <v>348</v>
       </c>
-      <c r="C65" s="371"/>
-      <c r="D65" s="371"/>
-      <c r="E65" s="371"/>
-      <c r="F65" s="371"/>
+      <c r="C65" s="374"/>
+      <c r="D65" s="374"/>
+      <c r="E65" s="374"/>
+      <c r="F65" s="374"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -7560,7 +7560,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>3.0786965297119495E-2</v>
+        <v>3.0595873788378754E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -7570,7 +7570,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>2.4982650936849413E-2</v>
+        <v>2.4827586206896554E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>425</v>
@@ -7661,22 +7661,22 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="371" t="s">
+      <c r="B80" s="374" t="s">
         <v>471</v>
       </c>
-      <c r="C80" s="371"/>
-      <c r="D80" s="371"/>
-      <c r="E80" s="371"/>
-      <c r="F80" s="371"/>
+      <c r="C80" s="374"/>
+      <c r="D80" s="374"/>
+      <c r="E80" s="374"/>
+      <c r="F80" s="374"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="372" t="s">
+      <c r="B81" s="377" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="372"/>
-      <c r="D81" s="372"/>
-      <c r="E81" s="372"/>
-      <c r="F81" s="372"/>
+      <c r="C81" s="377"/>
+      <c r="D81" s="377"/>
+      <c r="E81" s="377"/>
+      <c r="F81" s="377"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -7720,22 +7720,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="371" t="s">
+      <c r="B89" s="374" t="s">
         <v>349</v>
       </c>
-      <c r="C89" s="371"/>
-      <c r="D89" s="371"/>
-      <c r="E89" s="371"/>
-      <c r="F89" s="371"/>
+      <c r="C89" s="374"/>
+      <c r="D89" s="374"/>
+      <c r="E89" s="374"/>
+      <c r="F89" s="374"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="371" t="s">
+      <c r="B90" s="374" t="s">
         <v>350</v>
       </c>
-      <c r="C90" s="371"/>
-      <c r="D90" s="371"/>
-      <c r="E90" s="371"/>
-      <c r="F90" s="371"/>
+      <c r="C90" s="374"/>
+      <c r="D90" s="374"/>
+      <c r="E90" s="374"/>
+      <c r="F90" s="374"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -7772,13 +7772,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="371" t="s">
+      <c r="B97" s="374" t="s">
         <v>351</v>
       </c>
-      <c r="C97" s="371"/>
-      <c r="D97" s="371"/>
-      <c r="E97" s="371"/>
-      <c r="F97" s="371"/>
+      <c r="C97" s="374"/>
+      <c r="D97" s="374"/>
+      <c r="E97" s="374"/>
+      <c r="F97" s="374"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -7791,13 +7791,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="371" t="s">
+      <c r="B101" s="374" t="s">
         <v>335</v>
       </c>
-      <c r="C101" s="371"/>
-      <c r="D101" s="371"/>
-      <c r="E101" s="371"/>
-      <c r="F101" s="371"/>
+      <c r="C101" s="374"/>
+      <c r="D101" s="374"/>
+      <c r="E101" s="374"/>
+      <c r="F101" s="374"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -7919,13 +7919,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="371" t="s">
+      <c r="B116" s="374" t="s">
         <v>352</v>
       </c>
-      <c r="C116" s="371"/>
-      <c r="D116" s="371"/>
-      <c r="E116" s="371"/>
-      <c r="F116" s="371"/>
+      <c r="C116" s="374"/>
+      <c r="D116" s="374"/>
+      <c r="E116" s="374"/>
+      <c r="F116" s="374"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -8113,13 +8113,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="375" t="s">
+      <c r="B134" s="372" t="s">
         <v>474</v>
       </c>
-      <c r="C134" s="375"/>
-      <c r="D134" s="375"/>
-      <c r="E134" s="375"/>
-      <c r="F134" s="375"/>
+      <c r="C134" s="372"/>
+      <c r="D134" s="372"/>
+      <c r="E134" s="372"/>
+      <c r="F134" s="372"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -8132,22 +8132,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="376" t="s">
+      <c r="B138" s="373" t="s">
         <v>353</v>
       </c>
-      <c r="C138" s="376"/>
-      <c r="D138" s="376"/>
-      <c r="E138" s="376"/>
-      <c r="F138" s="376"/>
+      <c r="C138" s="373"/>
+      <c r="D138" s="373"/>
+      <c r="E138" s="373"/>
+      <c r="F138" s="373"/>
     </row>
     <row r="139" spans="1:6">
-      <c r="B139" s="371" t="s">
+      <c r="B139" s="374" t="s">
         <v>476</v>
       </c>
-      <c r="C139" s="371"/>
-      <c r="D139" s="371"/>
-      <c r="E139" s="371"/>
-      <c r="F139" s="371"/>
+      <c r="C139" s="374"/>
+      <c r="D139" s="374"/>
+      <c r="E139" s="374"/>
+      <c r="F139" s="374"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -8480,13 +8480,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="377" t="s">
+      <c r="B179" s="375" t="s">
         <v>477</v>
       </c>
-      <c r="C179" s="371"/>
-      <c r="D179" s="371"/>
-      <c r="E179" s="371"/>
-      <c r="F179" s="371"/>
+      <c r="C179" s="374"/>
+      <c r="D179" s="374"/>
+      <c r="E179" s="374"/>
+      <c r="F179" s="374"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -8494,13 +8494,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="373" t="s">
+      <c r="B182" s="376" t="s">
         <v>362</v>
       </c>
-      <c r="C182" s="373"/>
-      <c r="D182" s="373"/>
-      <c r="E182" s="373"/>
-      <c r="F182" s="373"/>
+      <c r="C182" s="376"/>
+      <c r="D182" s="376"/>
+      <c r="E182" s="376"/>
+      <c r="F182" s="376"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -8537,22 +8537,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="374" t="s">
+      <c r="B191" s="371" t="s">
         <v>363</v>
       </c>
-      <c r="C191" s="374"/>
-      <c r="D191" s="374"/>
-      <c r="E191" s="374"/>
-      <c r="F191" s="374"/>
+      <c r="C191" s="371"/>
+      <c r="D191" s="371"/>
+      <c r="E191" s="371"/>
+      <c r="F191" s="371"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="374" t="s">
+      <c r="B192" s="371" t="s">
         <v>364</v>
       </c>
-      <c r="C192" s="374"/>
-      <c r="D192" s="374"/>
-      <c r="E192" s="374"/>
-      <c r="F192" s="374"/>
+      <c r="C192" s="371"/>
+      <c r="D192" s="371"/>
+      <c r="E192" s="371"/>
+      <c r="F192" s="371"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -8576,17 +8576,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -8603,6 +8592,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -16193,32 +16193,32 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>2.4982650936849413E-2</v>
+        <v>2.4827586206896554E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>2.4982650936849413E-2</v>
+        <v>2.4827586206896554E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>2.4982650936849413E-2</v>
+        <v>2.4827586206896554E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>2.4982650936849413E-2</v>
+        <v>2.4827586206896554E-2</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
-        <v>2.4982650936849413E-2</v>
+        <v>2.4827586206896554E-2</v>
       </c>
       <c r="K94" s="23">
         <f t="shared" si="39"/>
-        <v>1.2491325468424706E-2</v>
+        <v>1.2413793103448277E-2</v>
       </c>
       <c r="L94" s="23">
         <f t="shared" si="39"/>
-        <v>1.2491325468424706E-2</v>
+        <v>1.2413793103448277E-2</v>
       </c>
       <c r="M94" s="23">
         <f t="shared" si="39"/>
@@ -17392,50 +17392,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>3.0786965297119495E-2</v>
+        <v>3.0595873788378754E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>3.5081619673763074E-2</v>
+        <v>3.4863871689581098E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>4.6133099684140783E-2</v>
+        <v>4.5846756306790942E-2</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>9.0737347330864151E-2</v>
+        <v>9.0174150002603606E-2</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>5.8758425178137348E-2</v>
+        <v>5.8393717711514428E-2</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>4.3939393011049072E-2</v>
+        <v>4.3666665744083941E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>3.6503827949448994E-2</v>
+        <v>3.6277252465624826E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>2.5741116697123655E-2</v>
+        <v>2.5581344248658752E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>2.3400077143852092E-2</v>
+        <v>2.325483528571784E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>1.5481752263208677E-2</v>
+        <v>1.538565862847152E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>1.5137800788649706E-2</v>
+        <v>1.5043842025133949E-2</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -17449,43 +17449,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.5541303327849551E-2</v>
+        <v>4.5258633169262902E-2</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.5896192832893335E-2</v>
+        <v>5.5549250946344338E-2</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>0.10038951385864175</v>
+        <v>9.9766406531243287E-2</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.0012212967236717E-2</v>
+        <v>5.963972336950904E-2</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.2479003033296409E-2</v>
+        <v>4.221534025584836E-2</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.4411072273517813E-2</v>
+        <v>3.4197486307682184E-2</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.5143954050343888E-2</v>
+        <v>2.4987888128652099E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.7501778309111357E-2</v>
+        <v>1.7393146581675491E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.5357031794641417E-2</v>
+        <v>1.5261712286950538E-2</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.3669654773380018E-2</v>
+        <v>1.3584808640303866E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -21435,7 +21435,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-14.41</v>
+        <v>-14.5</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -21675,7 +21675,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>14.41</v>
+        <v>14.5</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -22273,7 +22273,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>14.41</v>
+        <v>14.5</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -22286,7 +22286,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>-0.12511446453186559</v>
+        <v>-0.12698411363037332</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/300481.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/300481.SZ_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B89D6117-2068-4CB0-9B68-25311A571A79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2D99EB7-1E62-4B03-8263-A5F24AB0B4F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1470" yWindow="1470" windowWidth="12690" windowHeight="7643" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4759,6 +4759,15 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -4768,16 +4777,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="C12" s="366">
         <f>Market_Price</f>
-        <v>14.5</v>
+        <v>14.48</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C14" s="35">
         <f>投资主题!C12*Common_Shares/1000000</f>
-        <v>4231.903851</v>
+        <v>4226.0667422400002</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",投资主题!D12*Common_Shares/1000000)</f>
@@ -5346,13 +5346,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="374" t="s">
+      <c r="B18" s="371" t="s">
         <v>489</v>
       </c>
-      <c r="C18" s="374"/>
-      <c r="D18" s="374"/>
-      <c r="E18" s="374"/>
-      <c r="F18" s="374"/>
+      <c r="C18" s="371"/>
+      <c r="D18" s="371"/>
+      <c r="E18" s="371"/>
+      <c r="F18" s="371"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -5443,7 +5443,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>-0.12698411363037332</v>
+        <v>-0.12657000229994997</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -5565,22 +5565,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="374" t="s">
+      <c r="B36" s="371" t="s">
         <v>492</v>
       </c>
-      <c r="C36" s="374"/>
-      <c r="D36" s="374"/>
-      <c r="E36" s="374"/>
-      <c r="F36" s="374"/>
+      <c r="C36" s="371"/>
+      <c r="D36" s="371"/>
+      <c r="E36" s="371"/>
+      <c r="F36" s="371"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="377" t="s">
+      <c r="B37" s="372" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="377"/>
-      <c r="D37" s="377"/>
-      <c r="E37" s="377"/>
-      <c r="F37" s="377"/>
+      <c r="C37" s="372"/>
+      <c r="D37" s="372"/>
+      <c r="E37" s="372"/>
+      <c r="F37" s="372"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -5770,10 +5770,10 @@
       <c r="B61" s="370" t="s">
         <v>499</v>
       </c>
-      <c r="C61" s="376"/>
-      <c r="D61" s="376"/>
-      <c r="E61" s="376"/>
-      <c r="F61" s="376"/>
+      <c r="C61" s="373"/>
+      <c r="D61" s="373"/>
+      <c r="E61" s="373"/>
+      <c r="F61" s="373"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -5789,22 +5789,22 @@
       </c>
     </row>
     <row r="64" spans="2:6">
-      <c r="B64" s="374" t="s">
+      <c r="B64" s="371" t="s">
         <v>500</v>
       </c>
-      <c r="C64" s="374"/>
-      <c r="D64" s="374"/>
-      <c r="E64" s="374"/>
-      <c r="F64" s="374"/>
+      <c r="C64" s="371"/>
+      <c r="D64" s="371"/>
+      <c r="E64" s="371"/>
+      <c r="F64" s="371"/>
     </row>
     <row r="65" spans="1:6">
-      <c r="B65" s="374" t="s">
+      <c r="B65" s="371" t="s">
         <v>501</v>
       </c>
-      <c r="C65" s="374"/>
-      <c r="D65" s="374"/>
-      <c r="E65" s="374"/>
-      <c r="F65" s="374"/>
+      <c r="C65" s="371"/>
+      <c r="D65" s="371"/>
+      <c r="E65" s="371"/>
+      <c r="F65" s="371"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -5838,7 +5838,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>3.0595873788378754E-2</v>
+        <v>3.0638133282561594E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -5848,7 +5848,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>2.4827586206896554E-2</v>
+        <v>2.4861878453038676E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>503</v>
@@ -5939,22 +5939,22 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="374" t="s">
+      <c r="B80" s="371" t="s">
         <v>506</v>
       </c>
-      <c r="C80" s="374"/>
-      <c r="D80" s="374"/>
-      <c r="E80" s="374"/>
-      <c r="F80" s="374"/>
+      <c r="C80" s="371"/>
+      <c r="D80" s="371"/>
+      <c r="E80" s="371"/>
+      <c r="F80" s="371"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="377" t="s">
+      <c r="B81" s="372" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="377"/>
-      <c r="D81" s="377"/>
-      <c r="E81" s="377"/>
-      <c r="F81" s="377"/>
+      <c r="C81" s="372"/>
+      <c r="D81" s="372"/>
+      <c r="E81" s="372"/>
+      <c r="F81" s="372"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5998,22 +5998,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6">
-      <c r="B89" s="374" t="s">
+      <c r="B89" s="371" t="s">
         <v>507</v>
       </c>
-      <c r="C89" s="374"/>
-      <c r="D89" s="374"/>
-      <c r="E89" s="374"/>
-      <c r="F89" s="374"/>
+      <c r="C89" s="371"/>
+      <c r="D89" s="371"/>
+      <c r="E89" s="371"/>
+      <c r="F89" s="371"/>
     </row>
     <row r="90" spans="1:6">
-      <c r="B90" s="374" t="s">
+      <c r="B90" s="371" t="s">
         <v>508</v>
       </c>
-      <c r="C90" s="374"/>
-      <c r="D90" s="374"/>
-      <c r="E90" s="374"/>
-      <c r="F90" s="374"/>
+      <c r="C90" s="371"/>
+      <c r="D90" s="371"/>
+      <c r="E90" s="371"/>
+      <c r="F90" s="371"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -6050,13 +6050,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="374" t="s">
+      <c r="B97" s="371" t="s">
         <v>510</v>
       </c>
-      <c r="C97" s="374"/>
-      <c r="D97" s="374"/>
-      <c r="E97" s="374"/>
-      <c r="F97" s="374"/>
+      <c r="C97" s="371"/>
+      <c r="D97" s="371"/>
+      <c r="E97" s="371"/>
+      <c r="F97" s="371"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -6069,13 +6069,13 @@
       </c>
     </row>
     <row r="101" spans="2:6">
-      <c r="B101" s="374" t="s">
+      <c r="B101" s="371" t="s">
         <v>511</v>
       </c>
-      <c r="C101" s="374"/>
-      <c r="D101" s="374"/>
-      <c r="E101" s="374"/>
-      <c r="F101" s="374"/>
+      <c r="C101" s="371"/>
+      <c r="D101" s="371"/>
+      <c r="E101" s="371"/>
+      <c r="F101" s="371"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -6197,13 +6197,13 @@
       </c>
     </row>
     <row r="116" spans="1:6">
-      <c r="B116" s="374" t="s">
+      <c r="B116" s="371" t="s">
         <v>516</v>
       </c>
-      <c r="C116" s="374"/>
-      <c r="D116" s="374"/>
-      <c r="E116" s="374"/>
-      <c r="F116" s="374"/>
+      <c r="C116" s="371"/>
+      <c r="D116" s="371"/>
+      <c r="E116" s="371"/>
+      <c r="F116" s="371"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -6391,13 +6391,13 @@
       </c>
     </row>
     <row r="134" spans="1:6">
-      <c r="B134" s="372" t="s">
+      <c r="B134" s="375" t="s">
         <v>524</v>
       </c>
-      <c r="C134" s="372"/>
-      <c r="D134" s="372"/>
-      <c r="E134" s="372"/>
-      <c r="F134" s="372"/>
+      <c r="C134" s="375"/>
+      <c r="D134" s="375"/>
+      <c r="E134" s="375"/>
+      <c r="F134" s="375"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -6410,22 +6410,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="373" t="s">
+      <c r="B138" s="376" t="s">
         <v>526</v>
       </c>
-      <c r="C138" s="373"/>
-      <c r="D138" s="373"/>
-      <c r="E138" s="373"/>
-      <c r="F138" s="373"/>
+      <c r="C138" s="376"/>
+      <c r="D138" s="376"/>
+      <c r="E138" s="376"/>
+      <c r="F138" s="376"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="374" t="s">
+      <c r="B139" s="371" t="s">
         <v>527</v>
       </c>
-      <c r="C139" s="374"/>
-      <c r="D139" s="374"/>
-      <c r="E139" s="374"/>
-      <c r="F139" s="374"/>
+      <c r="C139" s="371"/>
+      <c r="D139" s="371"/>
+      <c r="E139" s="371"/>
+      <c r="F139" s="371"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -6758,13 +6758,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="375" t="s">
+      <c r="B179" s="377" t="s">
         <v>534</v>
       </c>
-      <c r="C179" s="374"/>
-      <c r="D179" s="374"/>
-      <c r="E179" s="374"/>
-      <c r="F179" s="374"/>
+      <c r="C179" s="371"/>
+      <c r="D179" s="371"/>
+      <c r="E179" s="371"/>
+      <c r="F179" s="371"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -6772,13 +6772,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="376" t="s">
+      <c r="B182" s="373" t="s">
         <v>536</v>
       </c>
-      <c r="C182" s="376"/>
-      <c r="D182" s="376"/>
-      <c r="E182" s="376"/>
-      <c r="F182" s="376"/>
+      <c r="C182" s="373"/>
+      <c r="D182" s="373"/>
+      <c r="E182" s="373"/>
+      <c r="F182" s="373"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -6815,22 +6815,22 @@
       </c>
     </row>
     <row r="191" spans="1:6">
-      <c r="B191" s="371" t="s">
+      <c r="B191" s="374" t="s">
         <v>543</v>
       </c>
-      <c r="C191" s="371"/>
-      <c r="D191" s="371"/>
-      <c r="E191" s="371"/>
-      <c r="F191" s="371"/>
+      <c r="C191" s="374"/>
+      <c r="D191" s="374"/>
+      <c r="E191" s="374"/>
+      <c r="F191" s="374"/>
     </row>
     <row r="192" spans="1:6">
-      <c r="B192" s="371" t="s">
+      <c r="B192" s="374" t="s">
         <v>544</v>
       </c>
-      <c r="C192" s="371"/>
-      <c r="D192" s="371"/>
-      <c r="E192" s="371"/>
-      <c r="F192" s="371"/>
+      <c r="C192" s="374"/>
+      <c r="D192" s="374"/>
+      <c r="E192" s="374"/>
+      <c r="F192" s="374"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -6854,12 +6854,15 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B47:F47"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B138:F138"/>
+    <mergeCell ref="B139:F139"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B182:F182"/>
     <mergeCell ref="B116:F116"/>
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B58:F58"/>
@@ -6872,15 +6875,12 @@
     <mergeCell ref="B90:F90"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B138:F138"/>
-    <mergeCell ref="B139:F139"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B43:F43"/>
   </mergeCells>
   <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">
@@ -7023,7 +7023,7 @@
         <v>463</v>
       </c>
       <c r="C12" s="50">
-        <v>14.5</v>
+        <v>14.48</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -7044,7 +7044,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>4231.903851</v>
+        <v>4226.0667422400002</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -7081,13 +7081,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="374" t="s">
+      <c r="B18" s="371" t="s">
         <v>468</v>
       </c>
-      <c r="C18" s="374"/>
-      <c r="D18" s="374"/>
-      <c r="E18" s="374"/>
-      <c r="F18" s="374"/>
+      <c r="C18" s="371"/>
+      <c r="D18" s="371"/>
+      <c r="E18" s="371"/>
+      <c r="F18" s="371"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -7170,7 +7170,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>-0.12698411363037332</v>
+        <v>-0.12657000229994997</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -7287,22 +7287,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6">
-      <c r="B36" s="374" t="s">
+      <c r="B36" s="371" t="s">
         <v>469</v>
       </c>
-      <c r="C36" s="374"/>
-      <c r="D36" s="374"/>
-      <c r="E36" s="374"/>
-      <c r="F36" s="374"/>
+      <c r="C36" s="371"/>
+      <c r="D36" s="371"/>
+      <c r="E36" s="371"/>
+      <c r="F36" s="371"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="377" t="s">
+      <c r="B37" s="372" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="377"/>
-      <c r="D37" s="377"/>
-      <c r="E37" s="377"/>
-      <c r="F37" s="377"/>
+      <c r="C37" s="372"/>
+      <c r="D37" s="372"/>
+      <c r="E37" s="372"/>
+      <c r="F37" s="372"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -7492,10 +7492,10 @@
       <c r="B61" s="370" t="s">
         <v>329</v>
       </c>
-      <c r="C61" s="376"/>
-      <c r="D61" s="376"/>
-      <c r="E61" s="376"/>
-      <c r="F61" s="376"/>
+      <c r="C61" s="373"/>
+      <c r="D61" s="373"/>
+      <c r="E61" s="373"/>
+      <c r="F61" s="373"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -7511,22 +7511,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="374" t="s">
+      <c r="B64" s="371" t="s">
         <v>334</v>
       </c>
-      <c r="C64" s="374"/>
-      <c r="D64" s="374"/>
-      <c r="E64" s="374"/>
-      <c r="F64" s="374"/>
+      <c r="C64" s="371"/>
+      <c r="D64" s="371"/>
+      <c r="E64" s="371"/>
+      <c r="F64" s="371"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="374" t="s">
+      <c r="B65" s="371" t="s">
         <v>348</v>
       </c>
-      <c r="C65" s="374"/>
-      <c r="D65" s="374"/>
-      <c r="E65" s="374"/>
-      <c r="F65" s="374"/>
+      <c r="C65" s="371"/>
+      <c r="D65" s="371"/>
+      <c r="E65" s="371"/>
+      <c r="F65" s="371"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -7560,7 +7560,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>3.0595873788378754E-2</v>
+        <v>3.0638133282561594E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -7570,7 +7570,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>2.4827586206896554E-2</v>
+        <v>2.4861878453038676E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>425</v>
@@ -7661,22 +7661,22 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="374" t="s">
+      <c r="B80" s="371" t="s">
         <v>471</v>
       </c>
-      <c r="C80" s="374"/>
-      <c r="D80" s="374"/>
-      <c r="E80" s="374"/>
-      <c r="F80" s="374"/>
+      <c r="C80" s="371"/>
+      <c r="D80" s="371"/>
+      <c r="E80" s="371"/>
+      <c r="F80" s="371"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="377" t="s">
+      <c r="B81" s="372" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="377"/>
-      <c r="D81" s="377"/>
-      <c r="E81" s="377"/>
-      <c r="F81" s="377"/>
+      <c r="C81" s="372"/>
+      <c r="D81" s="372"/>
+      <c r="E81" s="372"/>
+      <c r="F81" s="372"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -7720,22 +7720,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="374" t="s">
+      <c r="B89" s="371" t="s">
         <v>349</v>
       </c>
-      <c r="C89" s="374"/>
-      <c r="D89" s="374"/>
-      <c r="E89" s="374"/>
-      <c r="F89" s="374"/>
+      <c r="C89" s="371"/>
+      <c r="D89" s="371"/>
+      <c r="E89" s="371"/>
+      <c r="F89" s="371"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="374" t="s">
+      <c r="B90" s="371" t="s">
         <v>350</v>
       </c>
-      <c r="C90" s="374"/>
-      <c r="D90" s="374"/>
-      <c r="E90" s="374"/>
-      <c r="F90" s="374"/>
+      <c r="C90" s="371"/>
+      <c r="D90" s="371"/>
+      <c r="E90" s="371"/>
+      <c r="F90" s="371"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -7772,13 +7772,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="374" t="s">
+      <c r="B97" s="371" t="s">
         <v>351</v>
       </c>
-      <c r="C97" s="374"/>
-      <c r="D97" s="374"/>
-      <c r="E97" s="374"/>
-      <c r="F97" s="374"/>
+      <c r="C97" s="371"/>
+      <c r="D97" s="371"/>
+      <c r="E97" s="371"/>
+      <c r="F97" s="371"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -7791,13 +7791,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="374" t="s">
+      <c r="B101" s="371" t="s">
         <v>335</v>
       </c>
-      <c r="C101" s="374"/>
-      <c r="D101" s="374"/>
-      <c r="E101" s="374"/>
-      <c r="F101" s="374"/>
+      <c r="C101" s="371"/>
+      <c r="D101" s="371"/>
+      <c r="E101" s="371"/>
+      <c r="F101" s="371"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -7919,13 +7919,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="374" t="s">
+      <c r="B116" s="371" t="s">
         <v>352</v>
       </c>
-      <c r="C116" s="374"/>
-      <c r="D116" s="374"/>
-      <c r="E116" s="374"/>
-      <c r="F116" s="374"/>
+      <c r="C116" s="371"/>
+      <c r="D116" s="371"/>
+      <c r="E116" s="371"/>
+      <c r="F116" s="371"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -8113,13 +8113,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="372" t="s">
+      <c r="B134" s="375" t="s">
         <v>474</v>
       </c>
-      <c r="C134" s="372"/>
-      <c r="D134" s="372"/>
-      <c r="E134" s="372"/>
-      <c r="F134" s="372"/>
+      <c r="C134" s="375"/>
+      <c r="D134" s="375"/>
+      <c r="E134" s="375"/>
+      <c r="F134" s="375"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -8132,22 +8132,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="373" t="s">
+      <c r="B138" s="376" t="s">
         <v>353</v>
       </c>
-      <c r="C138" s="373"/>
-      <c r="D138" s="373"/>
-      <c r="E138" s="373"/>
-      <c r="F138" s="373"/>
+      <c r="C138" s="376"/>
+      <c r="D138" s="376"/>
+      <c r="E138" s="376"/>
+      <c r="F138" s="376"/>
     </row>
     <row r="139" spans="1:6">
-      <c r="B139" s="374" t="s">
+      <c r="B139" s="371" t="s">
         <v>476</v>
       </c>
-      <c r="C139" s="374"/>
-      <c r="D139" s="374"/>
-      <c r="E139" s="374"/>
-      <c r="F139" s="374"/>
+      <c r="C139" s="371"/>
+      <c r="D139" s="371"/>
+      <c r="E139" s="371"/>
+      <c r="F139" s="371"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -8480,13 +8480,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="375" t="s">
+      <c r="B179" s="377" t="s">
         <v>477</v>
       </c>
-      <c r="C179" s="374"/>
-      <c r="D179" s="374"/>
-      <c r="E179" s="374"/>
-      <c r="F179" s="374"/>
+      <c r="C179" s="371"/>
+      <c r="D179" s="371"/>
+      <c r="E179" s="371"/>
+      <c r="F179" s="371"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -8494,13 +8494,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="376" t="s">
+      <c r="B182" s="373" t="s">
         <v>362</v>
       </c>
-      <c r="C182" s="376"/>
-      <c r="D182" s="376"/>
-      <c r="E182" s="376"/>
-      <c r="F182" s="376"/>
+      <c r="C182" s="373"/>
+      <c r="D182" s="373"/>
+      <c r="E182" s="373"/>
+      <c r="F182" s="373"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -8537,22 +8537,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="371" t="s">
+      <c r="B191" s="374" t="s">
         <v>363</v>
       </c>
-      <c r="C191" s="371"/>
-      <c r="D191" s="371"/>
-      <c r="E191" s="371"/>
-      <c r="F191" s="371"/>
+      <c r="C191" s="374"/>
+      <c r="D191" s="374"/>
+      <c r="E191" s="374"/>
+      <c r="F191" s="374"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="371" t="s">
+      <c r="B192" s="374" t="s">
         <v>364</v>
       </c>
-      <c r="C192" s="371"/>
-      <c r="D192" s="371"/>
-      <c r="E192" s="371"/>
-      <c r="F192" s="371"/>
+      <c r="C192" s="374"/>
+      <c r="D192" s="374"/>
+      <c r="E192" s="374"/>
+      <c r="F192" s="374"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -8576,6 +8576,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -8592,17 +8603,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -16193,32 +16193,32 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>2.4827586206896554E-2</v>
+        <v>2.4861878453038676E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>2.4827586206896554E-2</v>
+        <v>2.4861878453038676E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>2.4827586206896554E-2</v>
+        <v>2.4861878453038676E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>2.4827586206896554E-2</v>
+        <v>2.4861878453038676E-2</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
-        <v>2.4827586206896554E-2</v>
+        <v>2.4861878453038676E-2</v>
       </c>
       <c r="K94" s="23">
         <f t="shared" si="39"/>
-        <v>1.2413793103448277E-2</v>
+        <v>1.2430939226519338E-2</v>
       </c>
       <c r="L94" s="23">
         <f t="shared" si="39"/>
-        <v>1.2413793103448277E-2</v>
+        <v>1.2430939226519338E-2</v>
       </c>
       <c r="M94" s="23">
         <f t="shared" si="39"/>
@@ -17392,50 +17392,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>3.0595873788378754E-2</v>
+        <v>3.0638133282561594E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>3.4863871689581098E-2</v>
+        <v>3.4912026208489357E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>4.5846756306790942E-2</v>
+        <v>4.5910080555833468E-2</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>9.0174150002603606E-2</v>
+        <v>9.0298699933546431E-2</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>5.8393717711514428E-2</v>
+        <v>5.8474372017745802E-2</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>4.3666665744083941E-2</v>
+        <v>4.3726978818316102E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>3.6277252465624826E-2</v>
+        <v>3.6327359167925413E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>2.5581344248658752E-2</v>
+        <v>2.56166775970685E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>2.325483528571784E-2</v>
+        <v>2.3286955223957781E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>1.538565862847152E-2</v>
+        <v>1.5406909538179353E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>1.5043842025133949E-2</v>
+        <v>1.5064620812461483E-2</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -17449,43 +17449,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.5258633169262902E-2</v>
+        <v>4.5321145093529837E-2</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.5549250946344338E-2</v>
+        <v>5.5625976431076855E-2</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.9766406531243287E-2</v>
+        <v>9.9904205435291951E-2</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.963972336950904E-2</v>
+        <v>5.9722098678030459E-2</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.221534025584836E-2</v>
+        <v>4.2273648736864726E-2</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.4197486307682184E-2</v>
+        <v>3.4244720404792241E-2</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.4987888128652099E-2</v>
+        <v>2.5022401786288357E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.7393146581675491E-2</v>
+        <v>1.7417170264799352E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.5261712286950538E-2</v>
+        <v>1.5282792000054061E-2</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.3584808640303866E-2</v>
+        <v>1.3603572188149587E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -21435,7 +21435,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-14.5</v>
+        <v>-14.48</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -21675,7 +21675,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>14.5</v>
+        <v>14.48</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -22273,7 +22273,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>14.5</v>
+        <v>14.48</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -22286,7 +22286,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>-0.12698411363037332</v>
+        <v>-0.12657000229994997</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/300481.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/300481.SZ_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2D99EB7-1E62-4B03-8263-A5F24AB0B4F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33F7FBDB-E1BA-4686-9710-D5F999BB8DC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1470" yWindow="1470" windowWidth="12690" windowHeight="7643" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1837" yWindow="1837" windowWidth="12691" windowHeight="7643" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="投资主题" sheetId="12" r:id="rId1"/>
@@ -4759,15 +4759,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -4777,7 +4768,16 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="C12" s="366">
         <f>Market_Price</f>
-        <v>14.48</v>
+        <v>14.57</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C14" s="35">
         <f>投资主题!C12*Common_Shares/1000000</f>
-        <v>4226.0667422400002</v>
+        <v>4252.33373166</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",投资主题!D12*Common_Shares/1000000)</f>
@@ -5346,13 +5346,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="371" t="s">
+      <c r="B18" s="374" t="s">
         <v>489</v>
       </c>
-      <c r="C18" s="371"/>
-      <c r="D18" s="371"/>
-      <c r="E18" s="371"/>
-      <c r="F18" s="371"/>
+      <c r="C18" s="374"/>
+      <c r="D18" s="374"/>
+      <c r="E18" s="374"/>
+      <c r="F18" s="374"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -5443,7 +5443,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>-0.12657000229994997</v>
+        <v>-0.1284274085979954</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -5565,22 +5565,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="371" t="s">
+      <c r="B36" s="374" t="s">
         <v>492</v>
       </c>
-      <c r="C36" s="371"/>
-      <c r="D36" s="371"/>
-      <c r="E36" s="371"/>
-      <c r="F36" s="371"/>
+      <c r="C36" s="374"/>
+      <c r="D36" s="374"/>
+      <c r="E36" s="374"/>
+      <c r="F36" s="374"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="372" t="s">
+      <c r="B37" s="377" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="372"/>
-      <c r="D37" s="372"/>
-      <c r="E37" s="372"/>
-      <c r="F37" s="372"/>
+      <c r="C37" s="377"/>
+      <c r="D37" s="377"/>
+      <c r="E37" s="377"/>
+      <c r="F37" s="377"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -5770,10 +5770,10 @@
       <c r="B61" s="370" t="s">
         <v>499</v>
       </c>
-      <c r="C61" s="373"/>
-      <c r="D61" s="373"/>
-      <c r="E61" s="373"/>
-      <c r="F61" s="373"/>
+      <c r="C61" s="376"/>
+      <c r="D61" s="376"/>
+      <c r="E61" s="376"/>
+      <c r="F61" s="376"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -5789,22 +5789,22 @@
       </c>
     </row>
     <row r="64" spans="2:6">
-      <c r="B64" s="371" t="s">
+      <c r="B64" s="374" t="s">
         <v>500</v>
       </c>
-      <c r="C64" s="371"/>
-      <c r="D64" s="371"/>
-      <c r="E64" s="371"/>
-      <c r="F64" s="371"/>
+      <c r="C64" s="374"/>
+      <c r="D64" s="374"/>
+      <c r="E64" s="374"/>
+      <c r="F64" s="374"/>
     </row>
     <row r="65" spans="1:6">
-      <c r="B65" s="371" t="s">
+      <c r="B65" s="374" t="s">
         <v>501</v>
       </c>
-      <c r="C65" s="371"/>
-      <c r="D65" s="371"/>
-      <c r="E65" s="371"/>
-      <c r="F65" s="371"/>
+      <c r="C65" s="374"/>
+      <c r="D65" s="374"/>
+      <c r="E65" s="374"/>
+      <c r="F65" s="374"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -5838,7 +5838,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>3.0638133282561594E-2</v>
+        <v>3.0448879199141517E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -5848,7 +5848,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>2.4861878453038676E-2</v>
+        <v>2.4708304735758409E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>503</v>
@@ -5939,22 +5939,22 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="371" t="s">
+      <c r="B80" s="374" t="s">
         <v>506</v>
       </c>
-      <c r="C80" s="371"/>
-      <c r="D80" s="371"/>
-      <c r="E80" s="371"/>
-      <c r="F80" s="371"/>
+      <c r="C80" s="374"/>
+      <c r="D80" s="374"/>
+      <c r="E80" s="374"/>
+      <c r="F80" s="374"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="372" t="s">
+      <c r="B81" s="377" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="372"/>
-      <c r="D81" s="372"/>
-      <c r="E81" s="372"/>
-      <c r="F81" s="372"/>
+      <c r="C81" s="377"/>
+      <c r="D81" s="377"/>
+      <c r="E81" s="377"/>
+      <c r="F81" s="377"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5998,22 +5998,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6">
-      <c r="B89" s="371" t="s">
+      <c r="B89" s="374" t="s">
         <v>507</v>
       </c>
-      <c r="C89" s="371"/>
-      <c r="D89" s="371"/>
-      <c r="E89" s="371"/>
-      <c r="F89" s="371"/>
+      <c r="C89" s="374"/>
+      <c r="D89" s="374"/>
+      <c r="E89" s="374"/>
+      <c r="F89" s="374"/>
     </row>
     <row r="90" spans="1:6">
-      <c r="B90" s="371" t="s">
+      <c r="B90" s="374" t="s">
         <v>508</v>
       </c>
-      <c r="C90" s="371"/>
-      <c r="D90" s="371"/>
-      <c r="E90" s="371"/>
-      <c r="F90" s="371"/>
+      <c r="C90" s="374"/>
+      <c r="D90" s="374"/>
+      <c r="E90" s="374"/>
+      <c r="F90" s="374"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -6050,13 +6050,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="371" t="s">
+      <c r="B97" s="374" t="s">
         <v>510</v>
       </c>
-      <c r="C97" s="371"/>
-      <c r="D97" s="371"/>
-      <c r="E97" s="371"/>
-      <c r="F97" s="371"/>
+      <c r="C97" s="374"/>
+      <c r="D97" s="374"/>
+      <c r="E97" s="374"/>
+      <c r="F97" s="374"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -6069,13 +6069,13 @@
       </c>
     </row>
     <row r="101" spans="2:6">
-      <c r="B101" s="371" t="s">
+      <c r="B101" s="374" t="s">
         <v>511</v>
       </c>
-      <c r="C101" s="371"/>
-      <c r="D101" s="371"/>
-      <c r="E101" s="371"/>
-      <c r="F101" s="371"/>
+      <c r="C101" s="374"/>
+      <c r="D101" s="374"/>
+      <c r="E101" s="374"/>
+      <c r="F101" s="374"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -6197,13 +6197,13 @@
       </c>
     </row>
     <row r="116" spans="1:6">
-      <c r="B116" s="371" t="s">
+      <c r="B116" s="374" t="s">
         <v>516</v>
       </c>
-      <c r="C116" s="371"/>
-      <c r="D116" s="371"/>
-      <c r="E116" s="371"/>
-      <c r="F116" s="371"/>
+      <c r="C116" s="374"/>
+      <c r="D116" s="374"/>
+      <c r="E116" s="374"/>
+      <c r="F116" s="374"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -6391,13 +6391,13 @@
       </c>
     </row>
     <row r="134" spans="1:6">
-      <c r="B134" s="375" t="s">
+      <c r="B134" s="372" t="s">
         <v>524</v>
       </c>
-      <c r="C134" s="375"/>
-      <c r="D134" s="375"/>
-      <c r="E134" s="375"/>
-      <c r="F134" s="375"/>
+      <c r="C134" s="372"/>
+      <c r="D134" s="372"/>
+      <c r="E134" s="372"/>
+      <c r="F134" s="372"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -6410,22 +6410,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="376" t="s">
+      <c r="B138" s="373" t="s">
         <v>526</v>
       </c>
-      <c r="C138" s="376"/>
-      <c r="D138" s="376"/>
-      <c r="E138" s="376"/>
-      <c r="F138" s="376"/>
+      <c r="C138" s="373"/>
+      <c r="D138" s="373"/>
+      <c r="E138" s="373"/>
+      <c r="F138" s="373"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="371" t="s">
+      <c r="B139" s="374" t="s">
         <v>527</v>
       </c>
-      <c r="C139" s="371"/>
-      <c r="D139" s="371"/>
-      <c r="E139" s="371"/>
-      <c r="F139" s="371"/>
+      <c r="C139" s="374"/>
+      <c r="D139" s="374"/>
+      <c r="E139" s="374"/>
+      <c r="F139" s="374"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -6758,13 +6758,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="377" t="s">
+      <c r="B179" s="375" t="s">
         <v>534</v>
       </c>
-      <c r="C179" s="371"/>
-      <c r="D179" s="371"/>
-      <c r="E179" s="371"/>
-      <c r="F179" s="371"/>
+      <c r="C179" s="374"/>
+      <c r="D179" s="374"/>
+      <c r="E179" s="374"/>
+      <c r="F179" s="374"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -6772,13 +6772,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="373" t="s">
+      <c r="B182" s="376" t="s">
         <v>536</v>
       </c>
-      <c r="C182" s="373"/>
-      <c r="D182" s="373"/>
-      <c r="E182" s="373"/>
-      <c r="F182" s="373"/>
+      <c r="C182" s="376"/>
+      <c r="D182" s="376"/>
+      <c r="E182" s="376"/>
+      <c r="F182" s="376"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -6815,22 +6815,22 @@
       </c>
     </row>
     <row r="191" spans="1:6">
-      <c r="B191" s="374" t="s">
+      <c r="B191" s="371" t="s">
         <v>543</v>
       </c>
-      <c r="C191" s="374"/>
-      <c r="D191" s="374"/>
-      <c r="E191" s="374"/>
-      <c r="F191" s="374"/>
+      <c r="C191" s="371"/>
+      <c r="D191" s="371"/>
+      <c r="E191" s="371"/>
+      <c r="F191" s="371"/>
     </row>
     <row r="192" spans="1:6">
-      <c r="B192" s="374" t="s">
+      <c r="B192" s="371" t="s">
         <v>544</v>
       </c>
-      <c r="C192" s="374"/>
-      <c r="D192" s="374"/>
-      <c r="E192" s="374"/>
-      <c r="F192" s="374"/>
+      <c r="C192" s="371"/>
+      <c r="D192" s="371"/>
+      <c r="E192" s="371"/>
+      <c r="F192" s="371"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -6854,15 +6854,12 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B138:F138"/>
-    <mergeCell ref="B139:F139"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B43:F43"/>
     <mergeCell ref="B116:F116"/>
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B58:F58"/>
@@ -6875,12 +6872,15 @@
     <mergeCell ref="B90:F90"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B47:F47"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B138:F138"/>
+    <mergeCell ref="B139:F139"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">
@@ -7023,7 +7023,7 @@
         <v>463</v>
       </c>
       <c r="C12" s="50">
-        <v>14.48</v>
+        <v>14.57</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -7044,7 +7044,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>4226.0667422400002</v>
+        <v>4252.33373166</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -7081,13 +7081,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="371" t="s">
+      <c r="B18" s="374" t="s">
         <v>468</v>
       </c>
-      <c r="C18" s="371"/>
-      <c r="D18" s="371"/>
-      <c r="E18" s="371"/>
-      <c r="F18" s="371"/>
+      <c r="C18" s="374"/>
+      <c r="D18" s="374"/>
+      <c r="E18" s="374"/>
+      <c r="F18" s="374"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -7170,7 +7170,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>-0.12657000229994997</v>
+        <v>-0.1284274085979954</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -7287,22 +7287,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6">
-      <c r="B36" s="371" t="s">
+      <c r="B36" s="374" t="s">
         <v>469</v>
       </c>
-      <c r="C36" s="371"/>
-      <c r="D36" s="371"/>
-      <c r="E36" s="371"/>
-      <c r="F36" s="371"/>
+      <c r="C36" s="374"/>
+      <c r="D36" s="374"/>
+      <c r="E36" s="374"/>
+      <c r="F36" s="374"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="372" t="s">
+      <c r="B37" s="377" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="372"/>
-      <c r="D37" s="372"/>
-      <c r="E37" s="372"/>
-      <c r="F37" s="372"/>
+      <c r="C37" s="377"/>
+      <c r="D37" s="377"/>
+      <c r="E37" s="377"/>
+      <c r="F37" s="377"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -7492,10 +7492,10 @@
       <c r="B61" s="370" t="s">
         <v>329</v>
       </c>
-      <c r="C61" s="373"/>
-      <c r="D61" s="373"/>
-      <c r="E61" s="373"/>
-      <c r="F61" s="373"/>
+      <c r="C61" s="376"/>
+      <c r="D61" s="376"/>
+      <c r="E61" s="376"/>
+      <c r="F61" s="376"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -7511,22 +7511,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="371" t="s">
+      <c r="B64" s="374" t="s">
         <v>334</v>
       </c>
-      <c r="C64" s="371"/>
-      <c r="D64" s="371"/>
-      <c r="E64" s="371"/>
-      <c r="F64" s="371"/>
+      <c r="C64" s="374"/>
+      <c r="D64" s="374"/>
+      <c r="E64" s="374"/>
+      <c r="F64" s="374"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="371" t="s">
+      <c r="B65" s="374" t="s">
         <v>348</v>
       </c>
-      <c r="C65" s="371"/>
-      <c r="D65" s="371"/>
-      <c r="E65" s="371"/>
-      <c r="F65" s="371"/>
+      <c r="C65" s="374"/>
+      <c r="D65" s="374"/>
+      <c r="E65" s="374"/>
+      <c r="F65" s="374"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -7560,7 +7560,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>3.0638133282561594E-2</v>
+        <v>3.0448879199141517E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -7570,7 +7570,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>2.4861878453038676E-2</v>
+        <v>2.4708304735758409E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>425</v>
@@ -7661,22 +7661,22 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="371" t="s">
+      <c r="B80" s="374" t="s">
         <v>471</v>
       </c>
-      <c r="C80" s="371"/>
-      <c r="D80" s="371"/>
-      <c r="E80" s="371"/>
-      <c r="F80" s="371"/>
+      <c r="C80" s="374"/>
+      <c r="D80" s="374"/>
+      <c r="E80" s="374"/>
+      <c r="F80" s="374"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="372" t="s">
+      <c r="B81" s="377" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="372"/>
-      <c r="D81" s="372"/>
-      <c r="E81" s="372"/>
-      <c r="F81" s="372"/>
+      <c r="C81" s="377"/>
+      <c r="D81" s="377"/>
+      <c r="E81" s="377"/>
+      <c r="F81" s="377"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -7720,22 +7720,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="371" t="s">
+      <c r="B89" s="374" t="s">
         <v>349</v>
       </c>
-      <c r="C89" s="371"/>
-      <c r="D89" s="371"/>
-      <c r="E89" s="371"/>
-      <c r="F89" s="371"/>
+      <c r="C89" s="374"/>
+      <c r="D89" s="374"/>
+      <c r="E89" s="374"/>
+      <c r="F89" s="374"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="371" t="s">
+      <c r="B90" s="374" t="s">
         <v>350</v>
       </c>
-      <c r="C90" s="371"/>
-      <c r="D90" s="371"/>
-      <c r="E90" s="371"/>
-      <c r="F90" s="371"/>
+      <c r="C90" s="374"/>
+      <c r="D90" s="374"/>
+      <c r="E90" s="374"/>
+      <c r="F90" s="374"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -7772,13 +7772,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="371" t="s">
+      <c r="B97" s="374" t="s">
         <v>351</v>
       </c>
-      <c r="C97" s="371"/>
-      <c r="D97" s="371"/>
-      <c r="E97" s="371"/>
-      <c r="F97" s="371"/>
+      <c r="C97" s="374"/>
+      <c r="D97" s="374"/>
+      <c r="E97" s="374"/>
+      <c r="F97" s="374"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -7791,13 +7791,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="371" t="s">
+      <c r="B101" s="374" t="s">
         <v>335</v>
       </c>
-      <c r="C101" s="371"/>
-      <c r="D101" s="371"/>
-      <c r="E101" s="371"/>
-      <c r="F101" s="371"/>
+      <c r="C101" s="374"/>
+      <c r="D101" s="374"/>
+      <c r="E101" s="374"/>
+      <c r="F101" s="374"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -7919,13 +7919,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="371" t="s">
+      <c r="B116" s="374" t="s">
         <v>352</v>
       </c>
-      <c r="C116" s="371"/>
-      <c r="D116" s="371"/>
-      <c r="E116" s="371"/>
-      <c r="F116" s="371"/>
+      <c r="C116" s="374"/>
+      <c r="D116" s="374"/>
+      <c r="E116" s="374"/>
+      <c r="F116" s="374"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -8113,13 +8113,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="375" t="s">
+      <c r="B134" s="372" t="s">
         <v>474</v>
       </c>
-      <c r="C134" s="375"/>
-      <c r="D134" s="375"/>
-      <c r="E134" s="375"/>
-      <c r="F134" s="375"/>
+      <c r="C134" s="372"/>
+      <c r="D134" s="372"/>
+      <c r="E134" s="372"/>
+      <c r="F134" s="372"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -8132,22 +8132,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="376" t="s">
+      <c r="B138" s="373" t="s">
         <v>353</v>
       </c>
-      <c r="C138" s="376"/>
-      <c r="D138" s="376"/>
-      <c r="E138" s="376"/>
-      <c r="F138" s="376"/>
+      <c r="C138" s="373"/>
+      <c r="D138" s="373"/>
+      <c r="E138" s="373"/>
+      <c r="F138" s="373"/>
     </row>
     <row r="139" spans="1:6">
-      <c r="B139" s="371" t="s">
+      <c r="B139" s="374" t="s">
         <v>476</v>
       </c>
-      <c r="C139" s="371"/>
-      <c r="D139" s="371"/>
-      <c r="E139" s="371"/>
-      <c r="F139" s="371"/>
+      <c r="C139" s="374"/>
+      <c r="D139" s="374"/>
+      <c r="E139" s="374"/>
+      <c r="F139" s="374"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -8480,13 +8480,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="377" t="s">
+      <c r="B179" s="375" t="s">
         <v>477</v>
       </c>
-      <c r="C179" s="371"/>
-      <c r="D179" s="371"/>
-      <c r="E179" s="371"/>
-      <c r="F179" s="371"/>
+      <c r="C179" s="374"/>
+      <c r="D179" s="374"/>
+      <c r="E179" s="374"/>
+      <c r="F179" s="374"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -8494,13 +8494,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="373" t="s">
+      <c r="B182" s="376" t="s">
         <v>362</v>
       </c>
-      <c r="C182" s="373"/>
-      <c r="D182" s="373"/>
-      <c r="E182" s="373"/>
-      <c r="F182" s="373"/>
+      <c r="C182" s="376"/>
+      <c r="D182" s="376"/>
+      <c r="E182" s="376"/>
+      <c r="F182" s="376"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -8537,22 +8537,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="374" t="s">
+      <c r="B191" s="371" t="s">
         <v>363</v>
       </c>
-      <c r="C191" s="374"/>
-      <c r="D191" s="374"/>
-      <c r="E191" s="374"/>
-      <c r="F191" s="374"/>
+      <c r="C191" s="371"/>
+      <c r="D191" s="371"/>
+      <c r="E191" s="371"/>
+      <c r="F191" s="371"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="374" t="s">
+      <c r="B192" s="371" t="s">
         <v>364</v>
       </c>
-      <c r="C192" s="374"/>
-      <c r="D192" s="374"/>
-      <c r="E192" s="374"/>
-      <c r="F192" s="374"/>
+      <c r="C192" s="371"/>
+      <c r="D192" s="371"/>
+      <c r="E192" s="371"/>
+      <c r="F192" s="371"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -8576,17 +8576,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -8603,6 +8592,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -16193,32 +16193,32 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>2.4861878453038676E-2</v>
+        <v>2.4708304735758409E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>2.4861878453038676E-2</v>
+        <v>2.4708304735758409E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>2.4861878453038676E-2</v>
+        <v>2.4708304735758409E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>2.4861878453038676E-2</v>
+        <v>2.4708304735758409E-2</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
-        <v>2.4861878453038676E-2</v>
+        <v>2.4708304735758409E-2</v>
       </c>
       <c r="K94" s="23">
         <f t="shared" si="39"/>
-        <v>1.2430939226519338E-2</v>
+        <v>1.2354152367879205E-2</v>
       </c>
       <c r="L94" s="23">
         <f t="shared" si="39"/>
-        <v>1.2430939226519338E-2</v>
+        <v>1.2354152367879205E-2</v>
       </c>
       <c r="M94" s="23">
         <f t="shared" si="39"/>
@@ -17392,50 +17392,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>3.0638133282561594E-2</v>
+        <v>3.0448879199141517E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>3.4912026208489357E-2</v>
+        <v>3.469637196286382E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>4.5910080555833468E-2</v>
+        <v>4.5626490490629279E-2</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>9.0298699933546431E-2</v>
+        <v>8.9740917984746219E-2</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>5.8474372017745802E-2</v>
+        <v>5.8113171366984157E-2</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>4.3726978818316102E-2</v>
+        <v>4.3456873938861849E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>3.6327359167925413E-2</v>
+        <v>3.61029623027838E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>2.56166775970685E-2</v>
+        <v>2.545844142797199E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>2.3286955223957781E-2</v>
+        <v>2.3143109927447402E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>1.5406909538179353E-2</v>
+        <v>1.5311739884202953E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>1.5064620812461483E-2</v>
+        <v>1.4971565502020745E-2</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -17449,43 +17449,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.5321145093529837E-2</v>
+        <v>4.5041192927543723E-2</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.5625976431076855E-2</v>
+        <v>5.5282370536856071E-2</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.9904205435291951E-2</v>
+        <v>9.9287089547222207E-2</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.9722098678030459E-2</v>
+        <v>5.9353190724631508E-2</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.2273648736864726E-2</v>
+        <v>4.2012521188044008E-2</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.4244720404792241E-2</v>
+        <v>3.4033188157954128E-2</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.5022401786288357E-2</v>
+        <v>2.486783650414931E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.7417170264799352E-2</v>
+        <v>1.7309583077165042E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.5282792000054061E-2</v>
+        <v>1.5188389029566426E-2</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.3603572188149587E-2</v>
+        <v>1.3519541886369666E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -21435,7 +21435,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-14.48</v>
+        <v>-14.57</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -21675,7 +21675,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>14.48</v>
+        <v>14.57</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -22273,7 +22273,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>14.48</v>
+        <v>14.57</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -22286,7 +22286,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>-0.12657000229994997</v>
+        <v>-0.1284274085979954</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/300481.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/300481.SZ_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33F7FBDB-E1BA-4686-9710-D5F999BB8DC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5AF9926-460B-430C-B29C-B33A0691777B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1837" yWindow="1837" windowWidth="12691" windowHeight="7643" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="投资主题" sheetId="12" r:id="rId1"/>
@@ -4759,6 +4759,15 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -4768,16 +4777,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="C12" s="366">
         <f>Market_Price</f>
-        <v>14.57</v>
+        <v>14.88</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C14" s="35">
         <f>投资主题!C12*Common_Shares/1000000</f>
-        <v>4252.33373166</v>
+        <v>4342.8089174400002</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",投资主题!D12*Common_Shares/1000000)</f>
@@ -5346,13 +5346,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="374" t="s">
+      <c r="B18" s="371" t="s">
         <v>489</v>
       </c>
-      <c r="C18" s="374"/>
-      <c r="D18" s="374"/>
-      <c r="E18" s="374"/>
-      <c r="F18" s="374"/>
+      <c r="C18" s="371"/>
+      <c r="D18" s="371"/>
+      <c r="E18" s="371"/>
+      <c r="F18" s="371"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -5443,7 +5443,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>-0.1284274085979954</v>
+        <v>-0.13470761287399891</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -5565,22 +5565,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="374" t="s">
+      <c r="B36" s="371" t="s">
         <v>492</v>
       </c>
-      <c r="C36" s="374"/>
-      <c r="D36" s="374"/>
-      <c r="E36" s="374"/>
-      <c r="F36" s="374"/>
+      <c r="C36" s="371"/>
+      <c r="D36" s="371"/>
+      <c r="E36" s="371"/>
+      <c r="F36" s="371"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="377" t="s">
+      <c r="B37" s="372" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="377"/>
-      <c r="D37" s="377"/>
-      <c r="E37" s="377"/>
-      <c r="F37" s="377"/>
+      <c r="C37" s="372"/>
+      <c r="D37" s="372"/>
+      <c r="E37" s="372"/>
+      <c r="F37" s="372"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -5770,10 +5770,10 @@
       <c r="B61" s="370" t="s">
         <v>499</v>
       </c>
-      <c r="C61" s="376"/>
-      <c r="D61" s="376"/>
-      <c r="E61" s="376"/>
-      <c r="F61" s="376"/>
+      <c r="C61" s="373"/>
+      <c r="D61" s="373"/>
+      <c r="E61" s="373"/>
+      <c r="F61" s="373"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -5789,22 +5789,22 @@
       </c>
     </row>
     <row r="64" spans="2:6">
-      <c r="B64" s="374" t="s">
+      <c r="B64" s="371" t="s">
         <v>500</v>
       </c>
-      <c r="C64" s="374"/>
-      <c r="D64" s="374"/>
-      <c r="E64" s="374"/>
-      <c r="F64" s="374"/>
+      <c r="C64" s="371"/>
+      <c r="D64" s="371"/>
+      <c r="E64" s="371"/>
+      <c r="F64" s="371"/>
     </row>
     <row r="65" spans="1:6">
-      <c r="B65" s="374" t="s">
+      <c r="B65" s="371" t="s">
         <v>501</v>
       </c>
-      <c r="C65" s="374"/>
-      <c r="D65" s="374"/>
-      <c r="E65" s="374"/>
-      <c r="F65" s="374"/>
+      <c r="C65" s="371"/>
+      <c r="D65" s="371"/>
+      <c r="E65" s="371"/>
+      <c r="F65" s="371"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -5838,7 +5838,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>3.0448879199141517E-2</v>
+        <v>2.9814527549159399E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -5848,7 +5848,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>2.4708304735758409E-2</v>
+        <v>2.4193548387096777E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>503</v>
@@ -5939,22 +5939,22 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="374" t="s">
+      <c r="B80" s="371" t="s">
         <v>506</v>
       </c>
-      <c r="C80" s="374"/>
-      <c r="D80" s="374"/>
-      <c r="E80" s="374"/>
-      <c r="F80" s="374"/>
+      <c r="C80" s="371"/>
+      <c r="D80" s="371"/>
+      <c r="E80" s="371"/>
+      <c r="F80" s="371"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="377" t="s">
+      <c r="B81" s="372" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="377"/>
-      <c r="D81" s="377"/>
-      <c r="E81" s="377"/>
-      <c r="F81" s="377"/>
+      <c r="C81" s="372"/>
+      <c r="D81" s="372"/>
+      <c r="E81" s="372"/>
+      <c r="F81" s="372"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5998,22 +5998,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6">
-      <c r="B89" s="374" t="s">
+      <c r="B89" s="371" t="s">
         <v>507</v>
       </c>
-      <c r="C89" s="374"/>
-      <c r="D89" s="374"/>
-      <c r="E89" s="374"/>
-      <c r="F89" s="374"/>
+      <c r="C89" s="371"/>
+      <c r="D89" s="371"/>
+      <c r="E89" s="371"/>
+      <c r="F89" s="371"/>
     </row>
     <row r="90" spans="1:6">
-      <c r="B90" s="374" t="s">
+      <c r="B90" s="371" t="s">
         <v>508</v>
       </c>
-      <c r="C90" s="374"/>
-      <c r="D90" s="374"/>
-      <c r="E90" s="374"/>
-      <c r="F90" s="374"/>
+      <c r="C90" s="371"/>
+      <c r="D90" s="371"/>
+      <c r="E90" s="371"/>
+      <c r="F90" s="371"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -6050,13 +6050,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="374" t="s">
+      <c r="B97" s="371" t="s">
         <v>510</v>
       </c>
-      <c r="C97" s="374"/>
-      <c r="D97" s="374"/>
-      <c r="E97" s="374"/>
-      <c r="F97" s="374"/>
+      <c r="C97" s="371"/>
+      <c r="D97" s="371"/>
+      <c r="E97" s="371"/>
+      <c r="F97" s="371"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -6069,13 +6069,13 @@
       </c>
     </row>
     <row r="101" spans="2:6">
-      <c r="B101" s="374" t="s">
+      <c r="B101" s="371" t="s">
         <v>511</v>
       </c>
-      <c r="C101" s="374"/>
-      <c r="D101" s="374"/>
-      <c r="E101" s="374"/>
-      <c r="F101" s="374"/>
+      <c r="C101" s="371"/>
+      <c r="D101" s="371"/>
+      <c r="E101" s="371"/>
+      <c r="F101" s="371"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -6197,13 +6197,13 @@
       </c>
     </row>
     <row r="116" spans="1:6">
-      <c r="B116" s="374" t="s">
+      <c r="B116" s="371" t="s">
         <v>516</v>
       </c>
-      <c r="C116" s="374"/>
-      <c r="D116" s="374"/>
-      <c r="E116" s="374"/>
-      <c r="F116" s="374"/>
+      <c r="C116" s="371"/>
+      <c r="D116" s="371"/>
+      <c r="E116" s="371"/>
+      <c r="F116" s="371"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -6391,13 +6391,13 @@
       </c>
     </row>
     <row r="134" spans="1:6">
-      <c r="B134" s="372" t="s">
+      <c r="B134" s="375" t="s">
         <v>524</v>
       </c>
-      <c r="C134" s="372"/>
-      <c r="D134" s="372"/>
-      <c r="E134" s="372"/>
-      <c r="F134" s="372"/>
+      <c r="C134" s="375"/>
+      <c r="D134" s="375"/>
+      <c r="E134" s="375"/>
+      <c r="F134" s="375"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -6410,22 +6410,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="373" t="s">
+      <c r="B138" s="376" t="s">
         <v>526</v>
       </c>
-      <c r="C138" s="373"/>
-      <c r="D138" s="373"/>
-      <c r="E138" s="373"/>
-      <c r="F138" s="373"/>
+      <c r="C138" s="376"/>
+      <c r="D138" s="376"/>
+      <c r="E138" s="376"/>
+      <c r="F138" s="376"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="374" t="s">
+      <c r="B139" s="371" t="s">
         <v>527</v>
       </c>
-      <c r="C139" s="374"/>
-      <c r="D139" s="374"/>
-      <c r="E139" s="374"/>
-      <c r="F139" s="374"/>
+      <c r="C139" s="371"/>
+      <c r="D139" s="371"/>
+      <c r="E139" s="371"/>
+      <c r="F139" s="371"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -6758,13 +6758,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="375" t="s">
+      <c r="B179" s="377" t="s">
         <v>534</v>
       </c>
-      <c r="C179" s="374"/>
-      <c r="D179" s="374"/>
-      <c r="E179" s="374"/>
-      <c r="F179" s="374"/>
+      <c r="C179" s="371"/>
+      <c r="D179" s="371"/>
+      <c r="E179" s="371"/>
+      <c r="F179" s="371"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -6772,13 +6772,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="376" t="s">
+      <c r="B182" s="373" t="s">
         <v>536</v>
       </c>
-      <c r="C182" s="376"/>
-      <c r="D182" s="376"/>
-      <c r="E182" s="376"/>
-      <c r="F182" s="376"/>
+      <c r="C182" s="373"/>
+      <c r="D182" s="373"/>
+      <c r="E182" s="373"/>
+      <c r="F182" s="373"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -6815,22 +6815,22 @@
       </c>
     </row>
     <row r="191" spans="1:6">
-      <c r="B191" s="371" t="s">
+      <c r="B191" s="374" t="s">
         <v>543</v>
       </c>
-      <c r="C191" s="371"/>
-      <c r="D191" s="371"/>
-      <c r="E191" s="371"/>
-      <c r="F191" s="371"/>
+      <c r="C191" s="374"/>
+      <c r="D191" s="374"/>
+      <c r="E191" s="374"/>
+      <c r="F191" s="374"/>
     </row>
     <row r="192" spans="1:6">
-      <c r="B192" s="371" t="s">
+      <c r="B192" s="374" t="s">
         <v>544</v>
       </c>
-      <c r="C192" s="371"/>
-      <c r="D192" s="371"/>
-      <c r="E192" s="371"/>
-      <c r="F192" s="371"/>
+      <c r="C192" s="374"/>
+      <c r="D192" s="374"/>
+      <c r="E192" s="374"/>
+      <c r="F192" s="374"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -6854,12 +6854,15 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B47:F47"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B138:F138"/>
+    <mergeCell ref="B139:F139"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B182:F182"/>
     <mergeCell ref="B116:F116"/>
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B58:F58"/>
@@ -6872,15 +6875,12 @@
     <mergeCell ref="B90:F90"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B138:F138"/>
-    <mergeCell ref="B139:F139"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B43:F43"/>
   </mergeCells>
   <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">
@@ -7023,7 +7023,7 @@
         <v>463</v>
       </c>
       <c r="C12" s="50">
-        <v>14.57</v>
+        <v>14.88</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -7044,7 +7044,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>4252.33373166</v>
+        <v>4342.8089174400002</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -7081,13 +7081,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="374" t="s">
+      <c r="B18" s="371" t="s">
         <v>468</v>
       </c>
-      <c r="C18" s="374"/>
-      <c r="D18" s="374"/>
-      <c r="E18" s="374"/>
-      <c r="F18" s="374"/>
+      <c r="C18" s="371"/>
+      <c r="D18" s="371"/>
+      <c r="E18" s="371"/>
+      <c r="F18" s="371"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -7170,7 +7170,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>-0.1284274085979954</v>
+        <v>-0.13470761287399891</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -7287,22 +7287,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6">
-      <c r="B36" s="374" t="s">
+      <c r="B36" s="371" t="s">
         <v>469</v>
       </c>
-      <c r="C36" s="374"/>
-      <c r="D36" s="374"/>
-      <c r="E36" s="374"/>
-      <c r="F36" s="374"/>
+      <c r="C36" s="371"/>
+      <c r="D36" s="371"/>
+      <c r="E36" s="371"/>
+      <c r="F36" s="371"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="377" t="s">
+      <c r="B37" s="372" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="377"/>
-      <c r="D37" s="377"/>
-      <c r="E37" s="377"/>
-      <c r="F37" s="377"/>
+      <c r="C37" s="372"/>
+      <c r="D37" s="372"/>
+      <c r="E37" s="372"/>
+      <c r="F37" s="372"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -7492,10 +7492,10 @@
       <c r="B61" s="370" t="s">
         <v>329</v>
       </c>
-      <c r="C61" s="376"/>
-      <c r="D61" s="376"/>
-      <c r="E61" s="376"/>
-      <c r="F61" s="376"/>
+      <c r="C61" s="373"/>
+      <c r="D61" s="373"/>
+      <c r="E61" s="373"/>
+      <c r="F61" s="373"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -7511,22 +7511,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="374" t="s">
+      <c r="B64" s="371" t="s">
         <v>334</v>
       </c>
-      <c r="C64" s="374"/>
-      <c r="D64" s="374"/>
-      <c r="E64" s="374"/>
-      <c r="F64" s="374"/>
+      <c r="C64" s="371"/>
+      <c r="D64" s="371"/>
+      <c r="E64" s="371"/>
+      <c r="F64" s="371"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="374" t="s">
+      <c r="B65" s="371" t="s">
         <v>348</v>
       </c>
-      <c r="C65" s="374"/>
-      <c r="D65" s="374"/>
-      <c r="E65" s="374"/>
-      <c r="F65" s="374"/>
+      <c r="C65" s="371"/>
+      <c r="D65" s="371"/>
+      <c r="E65" s="371"/>
+      <c r="F65" s="371"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -7560,7 +7560,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>3.0448879199141517E-2</v>
+        <v>2.9814527549159399E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -7570,7 +7570,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>2.4708304735758409E-2</v>
+        <v>2.4193548387096777E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>425</v>
@@ -7661,22 +7661,22 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="374" t="s">
+      <c r="B80" s="371" t="s">
         <v>471</v>
       </c>
-      <c r="C80" s="374"/>
-      <c r="D80" s="374"/>
-      <c r="E80" s="374"/>
-      <c r="F80" s="374"/>
+      <c r="C80" s="371"/>
+      <c r="D80" s="371"/>
+      <c r="E80" s="371"/>
+      <c r="F80" s="371"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="377" t="s">
+      <c r="B81" s="372" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="377"/>
-      <c r="D81" s="377"/>
-      <c r="E81" s="377"/>
-      <c r="F81" s="377"/>
+      <c r="C81" s="372"/>
+      <c r="D81" s="372"/>
+      <c r="E81" s="372"/>
+      <c r="F81" s="372"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -7720,22 +7720,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="374" t="s">
+      <c r="B89" s="371" t="s">
         <v>349</v>
       </c>
-      <c r="C89" s="374"/>
-      <c r="D89" s="374"/>
-      <c r="E89" s="374"/>
-      <c r="F89" s="374"/>
+      <c r="C89" s="371"/>
+      <c r="D89" s="371"/>
+      <c r="E89" s="371"/>
+      <c r="F89" s="371"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="374" t="s">
+      <c r="B90" s="371" t="s">
         <v>350</v>
       </c>
-      <c r="C90" s="374"/>
-      <c r="D90" s="374"/>
-      <c r="E90" s="374"/>
-      <c r="F90" s="374"/>
+      <c r="C90" s="371"/>
+      <c r="D90" s="371"/>
+      <c r="E90" s="371"/>
+      <c r="F90" s="371"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -7772,13 +7772,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="374" t="s">
+      <c r="B97" s="371" t="s">
         <v>351</v>
       </c>
-      <c r="C97" s="374"/>
-      <c r="D97" s="374"/>
-      <c r="E97" s="374"/>
-      <c r="F97" s="374"/>
+      <c r="C97" s="371"/>
+      <c r="D97" s="371"/>
+      <c r="E97" s="371"/>
+      <c r="F97" s="371"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -7791,13 +7791,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="374" t="s">
+      <c r="B101" s="371" t="s">
         <v>335</v>
       </c>
-      <c r="C101" s="374"/>
-      <c r="D101" s="374"/>
-      <c r="E101" s="374"/>
-      <c r="F101" s="374"/>
+      <c r="C101" s="371"/>
+      <c r="D101" s="371"/>
+      <c r="E101" s="371"/>
+      <c r="F101" s="371"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -7919,13 +7919,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="374" t="s">
+      <c r="B116" s="371" t="s">
         <v>352</v>
       </c>
-      <c r="C116" s="374"/>
-      <c r="D116" s="374"/>
-      <c r="E116" s="374"/>
-      <c r="F116" s="374"/>
+      <c r="C116" s="371"/>
+      <c r="D116" s="371"/>
+      <c r="E116" s="371"/>
+      <c r="F116" s="371"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -8113,13 +8113,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="372" t="s">
+      <c r="B134" s="375" t="s">
         <v>474</v>
       </c>
-      <c r="C134" s="372"/>
-      <c r="D134" s="372"/>
-      <c r="E134" s="372"/>
-      <c r="F134" s="372"/>
+      <c r="C134" s="375"/>
+      <c r="D134" s="375"/>
+      <c r="E134" s="375"/>
+      <c r="F134" s="375"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -8132,22 +8132,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="373" t="s">
+      <c r="B138" s="376" t="s">
         <v>353</v>
       </c>
-      <c r="C138" s="373"/>
-      <c r="D138" s="373"/>
-      <c r="E138" s="373"/>
-      <c r="F138" s="373"/>
+      <c r="C138" s="376"/>
+      <c r="D138" s="376"/>
+      <c r="E138" s="376"/>
+      <c r="F138" s="376"/>
     </row>
     <row r="139" spans="1:6">
-      <c r="B139" s="374" t="s">
+      <c r="B139" s="371" t="s">
         <v>476</v>
       </c>
-      <c r="C139" s="374"/>
-      <c r="D139" s="374"/>
-      <c r="E139" s="374"/>
-      <c r="F139" s="374"/>
+      <c r="C139" s="371"/>
+      <c r="D139" s="371"/>
+      <c r="E139" s="371"/>
+      <c r="F139" s="371"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -8480,13 +8480,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="375" t="s">
+      <c r="B179" s="377" t="s">
         <v>477</v>
       </c>
-      <c r="C179" s="374"/>
-      <c r="D179" s="374"/>
-      <c r="E179" s="374"/>
-      <c r="F179" s="374"/>
+      <c r="C179" s="371"/>
+      <c r="D179" s="371"/>
+      <c r="E179" s="371"/>
+      <c r="F179" s="371"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -8494,13 +8494,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="376" t="s">
+      <c r="B182" s="373" t="s">
         <v>362</v>
       </c>
-      <c r="C182" s="376"/>
-      <c r="D182" s="376"/>
-      <c r="E182" s="376"/>
-      <c r="F182" s="376"/>
+      <c r="C182" s="373"/>
+      <c r="D182" s="373"/>
+      <c r="E182" s="373"/>
+      <c r="F182" s="373"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -8537,22 +8537,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="371" t="s">
+      <c r="B191" s="374" t="s">
         <v>363</v>
       </c>
-      <c r="C191" s="371"/>
-      <c r="D191" s="371"/>
-      <c r="E191" s="371"/>
-      <c r="F191" s="371"/>
+      <c r="C191" s="374"/>
+      <c r="D191" s="374"/>
+      <c r="E191" s="374"/>
+      <c r="F191" s="374"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="371" t="s">
+      <c r="B192" s="374" t="s">
         <v>364</v>
       </c>
-      <c r="C192" s="371"/>
-      <c r="D192" s="371"/>
-      <c r="E192" s="371"/>
-      <c r="F192" s="371"/>
+      <c r="C192" s="374"/>
+      <c r="D192" s="374"/>
+      <c r="E192" s="374"/>
+      <c r="F192" s="374"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -8576,6 +8576,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -8592,17 +8603,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -16193,32 +16193,32 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>2.4708304735758409E-2</v>
+        <v>2.4193548387096777E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>2.4708304735758409E-2</v>
+        <v>2.4193548387096777E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>2.4708304735758409E-2</v>
+        <v>2.4193548387096777E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>2.4708304735758409E-2</v>
+        <v>2.4193548387096777E-2</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
-        <v>2.4708304735758409E-2</v>
+        <v>2.4193548387096777E-2</v>
       </c>
       <c r="K94" s="23">
         <f t="shared" si="39"/>
-        <v>1.2354152367879205E-2</v>
+        <v>1.2096774193548388E-2</v>
       </c>
       <c r="L94" s="23">
         <f t="shared" si="39"/>
-        <v>1.2354152367879205E-2</v>
+        <v>1.2096774193548388E-2</v>
       </c>
       <c r="M94" s="23">
         <f t="shared" si="39"/>
@@ -17392,50 +17392,50 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>3.0448879199141517E-2</v>
+        <v>2.9814527549159399E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>3.469637196286382E-2</v>
+        <v>3.3973530880304158E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>4.5626490490629279E-2</v>
+        <v>4.467593860540784E-2</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>8.9740917984746219E-2</v>
+        <v>8.7871315526730664E-2</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>5.8113171366984157E-2</v>
+        <v>5.6902480296838656E-2</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>4.3456873938861849E-2</v>
+        <v>4.2551522398468891E-2</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>3.61029623027838E-2</v>
+        <v>3.5350817254809139E-2</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>2.545844142797199E-2</v>
+        <v>2.4928057231555906E-2</v>
       </c>
       <c r="N126" s="77">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
-        <v>2.3143109927447402E-2</v>
+        <v>2.2660961803958914E-2</v>
       </c>
       <c r="O126" s="77">
         <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
-        <v>1.5311739884202953E-2</v>
+        <v>1.4992745303282057E-2</v>
       </c>
       <c r="P126" s="77">
         <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
-        <v>1.4971565502020745E-2</v>
+        <v>1.4659657887395313E-2</v>
       </c>
       <c r="Q126" s="77" t="str">
         <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
@@ -17449,43 +17449,43 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.5041192927543723E-2</v>
+        <v>4.4102834741553222E-2</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.5282370536856071E-2</v>
+        <v>5.4130654484004892E-2</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.9287089547222207E-2</v>
+        <v>9.7218608514988397E-2</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.9353190724631508E-2</v>
+        <v>5.8116665917868342E-2</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.2012521188044008E-2</v>
+        <v>4.1137260329959756E-2</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.4033188157954128E-2</v>
+        <v>3.3324163404663411E-2</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.486783650414931E-2</v>
+        <v>2.434975657697953E-2</v>
       </c>
       <c r="N127" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.7309583077165042E-2</v>
+        <v>1.6948966763057433E-2</v>
       </c>
       <c r="O127" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.5188389029566426E-2</v>
+        <v>1.4871964258117123E-2</v>
       </c>
       <c r="P127" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.3519541886369666E-2</v>
+        <v>1.3237884763736964E-2</v>
       </c>
       <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -21435,7 +21435,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-14.57</v>
+        <v>-14.88</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -21675,7 +21675,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>14.57</v>
+        <v>14.88</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -22273,7 +22273,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>14.57</v>
+        <v>14.88</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -22286,7 +22286,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>-0.1284274085979954</v>
+        <v>-0.13470761287399891</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/300481.SZ_Valuation.xlsx
+++ b/financial_models/opportunities/300481.SZ_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5AF9926-460B-430C-B29C-B33A0691777B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C06A030-3A63-4B5D-B6F1-39A88E7EAE0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4759,15 +4759,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -4777,7 +4768,16 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="C12" s="366">
         <f>Market_Price</f>
-        <v>14.88</v>
+        <v>14.97</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C14" s="35">
         <f>投资主题!C12*Common_Shares/1000000</f>
-        <v>4342.8089174400002</v>
+        <v>4369.0759068600009</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",投资主题!D12*Common_Shares/1000000)</f>
@@ -5346,13 +5346,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="371" t="s">
+      <c r="B18" s="374" t="s">
         <v>489</v>
       </c>
-      <c r="C18" s="371"/>
-      <c r="D18" s="371"/>
-      <c r="E18" s="371"/>
-      <c r="F18" s="371"/>
+      <c r="C18" s="374"/>
+      <c r="D18" s="374"/>
+      <c r="E18" s="374"/>
+      <c r="F18" s="374"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -5443,7 +5443,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>-0.13470761287399891</v>
+        <v>-0.13649766245236539</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -5565,22 +5565,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="371" t="s">
+      <c r="B36" s="374" t="s">
         <v>492</v>
       </c>
-      <c r="C36" s="371"/>
-      <c r="D36" s="371"/>
-      <c r="E36" s="371"/>
-      <c r="F36" s="371"/>
+      <c r="C36" s="374"/>
+      <c r="D36" s="374"/>
+      <c r="E36" s="374"/>
+      <c r="F36" s="374"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="372" t="s">
+      <c r="B37" s="377" t="s">
         <v>330</v>
       </c>
-      <c r="C37" s="372"/>
-      <c r="D37" s="372"/>
-      <c r="E37" s="372"/>
-      <c r="F37" s="372"/>
+      <c r="C37" s="377"/>
+      <c r="D37" s="377"/>
+      <c r="E37" s="377"/>
+      <c r="F37" s="377"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -5770,10 +5770,10 @@
       <c r="B61" s="370" t="s">
         <v>499</v>
       </c>
-      <c r="C61" s="373"/>
-      <c r="D61" s="373"/>
-      <c r="E61" s="373"/>
-      <c r="F61" s="373"/>
+      <c r="C61" s="376"/>
+      <c r="D61" s="376"/>
+      <c r="E61" s="376"/>
+      <c r="F61" s="376"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -5789,22 +5789,22 @@
       </c>
     </row>
     <row r="64" spans="2:6">
-      <c r="B64" s="371" t="s">
+      <c r="B64" s="374" t="s">
         <v>500</v>
       </c>
-      <c r="C64" s="371"/>
-      <c r="D64" s="371"/>
-      <c r="E64" s="371"/>
-      <c r="F64" s="371"/>
+      <c r="C64" s="374"/>
+      <c r="D64" s="374"/>
+      <c r="E64" s="374"/>
+      <c r="F64" s="374"/>
     </row>
     <row r="65" spans="1:6">
-      <c r="B65" s="371" t="s">
+      <c r="B65" s="374" t="s">
         <v>501</v>
       </c>
-      <c r="C65" s="371"/>
-      <c r="D65" s="371"/>
-      <c r="E65" s="371"/>
-      <c r="F65" s="371"/>
+      <c r="C65" s="374"/>
+      <c r="D65" s="374"/>
+      <c r="E65" s="374"/>
+      <c r="F65" s="374"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -5838,7 +5838,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>2.9814527549159399E-2</v>
+        <v>2.9635281892551227E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -5848,7 +5848,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>2.4193548387096777E-2</v>
+        <v>2.4048096192384773E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>503</v>
@@ -5939,22 +5939,22 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" s="17"/>
-      <c r="B80" s="371" t="s">
+      <c r="B80" s="374" t="s">
         <v>506</v>
       </c>
-      <c r="C80" s="371"/>
-      <c r="D80" s="371"/>
-      <c r="E80" s="371"/>
-      <c r="F80" s="371"/>
+      <c r="C80" s="374"/>
+      <c r="D80" s="374"/>
+      <c r="E80" s="374"/>
+      <c r="F80" s="374"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="372" t="s">
+      <c r="B81" s="377" t="s">
         <v>248</v>
       </c>
-      <c r="C81" s="372"/>
-      <c r="D81" s="372"/>
-      <c r="E81" s="372"/>
-      <c r="F81" s="372"/>
+      <c r="C81" s="377"/>
+      <c r="D81" s="377"/>
+      <c r="E81" s="377"/>
+      <c r="F81" s="377"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5998,22 +5998,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6">
-      <c r="B89" s="371" t="s">
+      <c r="B89" s="374" t="s">
         <v>507</v>
       </c>
-      <c r="C89" s="371"/>
-      <c r="D89" s="371"/>
-      <c r="E89" s="371"/>
-      <c r="F89" s="371"/>
+      <c r="C89" s="374"/>
+      <c r="D89" s="374"/>
+      <c r="E89" s="374"/>
+      <c r="F89" s="374"/>
     </row>
     <row r="90" spans="1:6">
-      <c r="B90" s="371" t="s">
+      <c r="B90" s="374" t="s">
         <v>508</v>
       </c>
-      <c r="C90" s="371"/>
-      <c r="D90" s="371"/>
-      <c r="E90" s="371"/>
-      <c r="F90" s="371"/>
+      <c r="C90" s="374"/>
+      <c r="D90" s="374"/>
+      <c r="E90" s="374"/>
+      <c r="F90" s="374"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -6050,13 +6050,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="371" t="s">
+      <c r="B97" s="374" t="s">
         <v>510</v>
       </c>
-      <c r="C97" s="371"/>
-      <c r="D97" s="371"/>
-      <c r="E97" s="371"/>
-      <c r="F97" s="371"/>
+      <c r="C97" s="374"/>
+      <c r="D97" s="374"/>
+      <c r="E97" s="374"/>
+      <c r="F97" s="374"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -6069,13 +6069,13 @@
       </c>
     </row>
     <row r="101" spans="2:6">
-      <c r="B101" s="371" t="s">
+      <c r="B101" s="374" t="s">
         <v>511</v>
       </c>
-      <c r="C101" s="371"/>
-      <c r="D101" s="371"/>
-      <c r="E101" s="371"/>
-      <c r="F101" s="371"/>
+      <c r="C101" s="374"/>
+      <c r="D101" s="374"/>
+      <c r="E101" s="374"/>
+      <c r="F101" s="374"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -6197,13 +6197,13 @@
       </c>
     </row>
     <row r="116" spans="1:6">
-      <c r="B116" s="371" t="s">
+      <c r="B116" s="374" t="s">
         <v>516</v>
       </c>
-      <c r="C116" s="371"/>
-      <c r="D116" s="371"/>
-      <c r="E116" s="371"/>
-      <c r="F116" s="371"/>
+      <c r="C116" s="374"/>
+      <c r="D116" s="374"/>
+      <c r="E116" s="374"/>
+      <c r="F116" s="374"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -6391,13 +6391,13 @@
       </c>
     </row>
     <row r="134" spans="1:6">
-      <c r="B134" s="375" t="s">
+      <c r="B134" s="372" t="s">
         <v>524</v>
       </c>
-      <c r="C134" s="375"/>
-      <c r="D134" s="375"/>
-      <c r="E134" s="375"/>
-      <c r="F134" s="375"/>
+      <c r="C134" s="372"/>
+      <c r="D134" s="372"/>
+      <c r="E134" s="372"/>
+      <c r="F134" s="372"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -6410,22 +6410,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="376" t="s">
+      <c r="B138" s="373" t="s">
         <v>526</v>
       </c>
-      <c r="C138" s="376"/>
-      <c r="D138" s="376"/>
-      <c r="E138" s="376"/>
-      <c r="F138" s="376"/>
+      <c r="C138" s="373"/>
+      <c r="D138" s="373"/>
+      <c r="E138" s="373"/>
+      <c r="F138" s="373"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="371" t="s">
+      <c r="B139" s="374" t="s">
         <v>527</v>
       </c>
-      <c r="C139" s="371"/>
-      <c r="D139" s="371"/>
-      <c r="E139" s="371"/>
-      <c r="F139" s="371"/>
+      <c r="C139" s="374"/>
+      <c r="D139" s="374"/>
+      <c r="E139" s="374"/>
+      <c r="F139" s="374"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -6758,13 +6758,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="377" t="s">
+      <c r="B179" s="375" t="s">
         <v>534</v>
       </c>
-      <c r="C179" s="371"/>
-      <c r="D179" s="371"/>
-      <c r="E179" s="371"/>
-      <c r="F179" s="371"/>
+      <c r="C179" s="374"/>
+      <c r="D179" s="374"/>
+      <c r="E179" s="374"/>
+      <c r="F179" s="374"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -6772,13 +6772,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="373" t="s">
+      <c r="B182" s="376" t="s">
         <v>536</v>
       </c>
-      <c r="C182" s="373"/>
-      <c r="D182" s="373"/>
-      <c r="E182" s="373"/>
-      <c r="F182" s="373"/>
+      <c r="C182" s="376"/>
+      <c r="D182" s="376"/>
+      <c r="E182" s="376"/>
+      <c r="F182" s="376"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -6815,22 +6815,22 @@
       </c>
     </row>
     <row r="191" spans="1:6">
-      <c r="B191" s="374" t="s">
+      <c r="B191" s="371" t="s">
         <v>543</v>
       </c>
-      <c r="C191" s="374"/>
-      <c r="D191" s="374"/>
-      <c r="E191" s="374"/>
-      <c r="F191" s="374"/>
+      <c r="C191" s="371"/>
+      <c r="D191" s="371"/>
+      <c r="E191" s="371"/>
+      <c r="F191" s="371"/>
     </row>
     <row r="192" spans="1:6">
-      <c r="B192" s="374" t="s">
+      <c r="B192" s="371" t="s">
         <v>544</v>
       </c>
-      <c r="C192" s="374"/>
-      <c r="D192" s="374"/>
-      <c r="E192" s="374"/>
-      <c r="F192" s="374"/>
+      <c r="C192" s="371"/>
+      <c r="D192" s="371"/>
+      <c r="E192" s="371"/>
+      <c r="F192" s="371"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -6854,15 +6854,12 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B138:F138"/>
-    <mergeCell ref="B139:F139"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B43:F43"/>
     <mergeCell ref="B116:F116"/>
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B58:F58"/>
@@ -6875,12 +6872,15 @@
     <mergeCell ref="B90:F90"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B47:F47"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B138:F138"/>
+    <mergeCell ref="B139:F139"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1" xr:uid="{42FF